--- a/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
+++ b/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
@@ -14,8 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Method" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'UI Components'!$A$1:$H$109</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Shared Code'!$A$1:$H$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'UI Components'!$A$1:$H$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Shared Code'!$A$1:$H$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -88,12 +88,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E3F2FD"/>
+        <fgColor rgb="00FDECEA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FDECEA"/>
+        <fgColor rgb="00E3F2FD"/>
       </patternFill>
     </fill>
     <fill>
@@ -667,16 +667,16 @@
         </is>
       </c>
       <c r="C5" s="17" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D5" s="17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5" s="17" t="n">
         <v>2</v>
       </c>
       <c r="F5" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="C7" s="17" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D7" s="17" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E7" s="17" t="n">
         <v>4</v>
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="C8" s="17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="17" t="n">
         <v>8</v>
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="C9" s="17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D9" s="17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E9" s="17" t="n">
         <v>4</v>
@@ -811,13 +811,13 @@
         </is>
       </c>
       <c r="C11" s="17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D11" s="17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" s="17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="17" t="n">
         <v>0</v>
@@ -855,17 +855,17 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>108 UI components + 51 non-UI files</t>
+          <t>110 UI components + 54 non-UI files</t>
         </is>
       </c>
       <c r="C13" s="18" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E13" s="18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F13" s="18" t="n">
         <v>5</v>
@@ -1046,69 +1046,15 @@
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
         <is>
-          <t>Activity Comments</t>
+          <t>Number Selection</t>
         </is>
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>The closing note on the actions performed, with an optional channel.</t>
+          <t>Choose a number: search, Free and Star bands, price filter, plan entitlement note, reserve and clear.</t>
         </is>
       </c>
       <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>capabilities/ActivityComments/ActivityComments.tsx
-capabilities/ActivityComments/index.ts
-capabilities/ActivityComments/step.tsx
-components/patterns/ActivityCommentsStep.tsx</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="inlineStr">
-        <is>
-          <t>Guided activation wizard</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>The step shell every activation / migration / port-in journey runs in.</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>capabilities/GuidedActivationWizard/GuidedActivationWizard.tsx
-capabilities/GuidedActivationWizard/index.ts</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>Number Selection</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>Choose a number: search, Free and Star bands, price filter, plan entitlement note, reserve and clear.</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>capabilities/NumberSelection/NumberSelection.tsx
 capabilities/NumberSelection/index.ts
@@ -1118,27 +1064,147 @@
 components/domain/msisdnPickerModel.ts</t>
         </is>
       </c>
+      <c r="D5" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>Guided activation wizard</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>The step shell every activation / migration / port-in journey runs in.</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>capabilities/GuidedActivationWizard/GuidedActivationWizard.tsx
+capabilities/GuidedActivationWizard/index.ts</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>SIM Type</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>Choose and validate the SIM: Physical (scan or enter the serial) or eSIM (issued, handed over after payment).</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>capabilities/SimType/SimSerial.tsx
+capabilities/SimType/SimType.tsx
+capabilities/SimType/index.ts
+capabilities/SimType/step.tsx
+capabilities/SimType/summary.ts
+components/domain/SimTypeStep.tsx
+components/domain/SimSerialScanner.tsx</t>
+        </is>
+      </c>
       <c r="D7" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
+          <t>Billing Account</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>Set up what an order bills to: pick or create a billing account, or just the order's billing settings.</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>capabilities/BillingAccount/BillingAccount.tsx
+capabilities/BillingAccount/index.ts
+capabilities/BillingAccount/persistBillingAccount.ts
+capabilities/BillingAccount/step.tsx
+capabilities/BillingAccount/summary.ts
+components/patterns/BillingAccountStep.tsx
+components/patterns/BillingProfileStep.tsx
+components/patterns/BillingProfileSetupDrawer.tsx
+components/patterns/BillingAccountAutoResolver.tsx
+components/patterns/billingAccountModel.ts</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>Service Address</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>The address a service is activated at: one layout everywhere: Service Information (Kahramaa Meter ID / Vodafone Premise ID with Search), then Zone / Street / Building, then Additional Details, with Qatari-ID prefill.</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>capabilities/ServiceAddress/ServiceAddress.tsx
+capabilities/ServiceAddress/index.ts
+capabilities/ServiceAddress/step.tsx
+capabilities/ServiceAddress/summary.ts
+components/patterns/ZsbAddressStep.tsx</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
           <t>Plan Selection</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>Choose the plan: postpaid with add-ons, prepaid packs, or a catalogue plan with optional credit check.</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>Choose the plan: postpaid plan cards then Add-ons (discounts, bill limit), prepaid packs then Add-ons, or the fixed-line / fibre plan cards with the credit check.</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>capabilities/PlanSelection/PlanSelection.tsx
 capabilities/PlanSelection/index.ts
@@ -1147,32 +1213,32 @@
 capabilities/PlanSelection/summary.ts
 components/patterns/PostpaidPlanAddonsStep.tsx
 components/patterns/PrepaidPlanStep.tsx
-components/patterns/ProductPlanStep.tsx
+components/patterns/FixedPlanStep.tsx
 components/patterns/PostpaidPlanCard.tsx
 components/patterns/PlanGroupPanel.tsx</t>
         </is>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D10" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>CAF &amp; Signature</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>The Customer Agreement Form: terms, CAF type, signature and supporting documents; standard and full variants, postpaid and prepaid forms.</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>The Customer Agreement Form: terms, CAF type, signature and supporting documents. Standard variant (name, key information, signature) and full variant (the customer reads back the Checkout Summary order, agrees the terms and signs; the journey locks once signed); postpaid and prepaid forms.</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>capabilities/CafSignature/CafSignature.tsx
 capabilities/CafSignature/index.ts
@@ -1183,27 +1249,27 @@
 components/patterns/cafTypes.ts</t>
         </is>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D11" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>Checkout Summary</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>The order read-back before signing and payment; publishes the totals the CAF and Payment reuse. Includes the prepaid cart (Add another subscription) and prepaid checkout.</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>The order read-back before signing and payment (plan, add-ons, discount, number, billing, monthly and one-off totals); publishes the totals and read-back rows the CAF and Payment reuse. An optional panel above it (the port-in validation gate). Includes the prepaid cart (Add another subscription) and prepaid checkout.</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>capabilities/CheckoutSummary/CheckoutSummary.tsx
 capabilities/CheckoutSummary/PrepaidCartBody.tsx
@@ -1222,53 +1288,168 @@
 components/patterns/prepaidCartModel.ts</t>
         </is>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D12" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>Payment</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>Take the amount due at the counter through WinCash and record the outcome.</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>capabilities/Payment/Payment.tsx
+capabilities/Payment/index.ts
+capabilities/Payment/step.tsx
+components/patterns/WinCashPaymentStep.tsx</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E13" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>Activation Complete</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>The confirmation page for a submitted activation (facts, status, follow-on actions, eSIM handover, email) and the confirmed-order shape journeys hand it.</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>capabilities/ActivationComplete/ActivationComplete.tsx
+capabilities/ActivationComplete/confirmedOrder.ts
+capabilities/ActivationComplete/index.ts
+components/patterns/ActivationCompleteScreen.tsx
+components/patterns/OrderConfirmationScreen.tsx</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>Eligibility gate</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>Hard-stop / soft-stop / pass eligibility check shown after identification, with the outcome panel, checks report and footer actions.</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>capabilities/EligibilityGate/EligibilityGateStep.tsx
+capabilities/EligibilityGate/EligibilityOutcomes.tsx
+capabilities/EligibilityGate/eligibilityOutcomesModel.ts
+capabilities/EligibilityGate/index.ts</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>Add-ons selection</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>Add-on cards with included-benefit handling.</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>capabilities/AddonsSelection/AddonsPicker.tsx
 capabilities/AddonsSelection/index.ts</t>
         </is>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D16" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>Customer Type &amp; Discounts</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>Special customer types (retired, MADA, B2B2C): the evidence the agent collects, the rules for accepting or rejecting the benefit, and the customer's benefits.</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>capabilities/CustomerType/CustomerTypeStep.tsx
+capabilities/CustomerType/customerTypeModel.ts
+capabilities/CustomerType/index.ts
+capabilities/CustomerType/useCustomerBenefits.ts
+components/domain/CompanySearchInput.tsx
+components/domain/SupportingDocumentUpload.tsx</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E17" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>Cross-Sell Offers</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>Recommended offers for the identified customer: offer cards, details drawer, interested (lead) and select actions, and hand-off to the other journeys.</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>capabilities/CrossSellOffers/CrossSalesStep.tsx
 capabilities/CrossSellOffers/HandOff.tsx
@@ -1281,150 +1462,27 @@
 capabilities/CrossSellOffers/summary.ts</t>
         </is>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D18" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>SIM Type</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>Choose and validate the SIM: Physical (scan or enter the serial) or eSIM (issued, handed over after payment).</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>capabilities/SimType/SimSerial.tsx
-capabilities/SimType/SimType.tsx
-capabilities/SimType/index.ts
-capabilities/SimType/step.tsx
-capabilities/SimType/summary.ts
-components/domain/SimTypeStep.tsx
-components/domain/SimSerialScanner.tsx</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, sim-number-management, administration</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>Billing Account</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>Set up what an order bills to: pick or create a billing account, or just the order's billing settings.</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>capabilities/BillingAccount/BillingAccount.tsx
-capabilities/BillingAccount/index.ts
-capabilities/BillingAccount/persistBillingAccount.ts
-capabilities/BillingAccount/step.tsx
-capabilities/BillingAccount/summary.ts
-components/patterns/BillingAccountStep.tsx
-components/patterns/BillingProfileStep.tsx
-components/patterns/BillingProfileSetupDrawer.tsx
-components/patterns/BillingAccountAutoResolver.tsx
-components/patterns/billingAccountModel.ts</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, administration</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>Service Address</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>The address a service is activated at: structured ZSB entry with Qatari-ID prefill, or pick from saved addresses.</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>capabilities/ServiceAddress/ServiceAddress.tsx
-capabilities/ServiceAddress/index.ts
-capabilities/ServiceAddress/step.tsx
-capabilities/ServiceAddress/summary.ts
-components/patterns/ZsbAddressStep.tsx
-components/patterns/AddressSelectionStep.tsx</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, administration</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>Payment</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>Take the amount due at the counter through WinCash and record the outcome.</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>capabilities/Payment/Payment.tsx
-capabilities/Payment/index.ts
-capabilities/Payment/step.tsx
-components/patterns/WinCashPaymentStep.tsx</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, administration</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>Appointment Booking</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>Book the installation visit: cluster, date and time slot.</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>capabilities/AppointmentBooking/AppointmentBooking.tsx
 capabilities/AppointmentBooking/index.ts
@@ -1432,114 +1490,27 @@
 components/patterns/AppointmentBookingStep.tsx</t>
         </is>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D19" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, administration</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>Customer Type &amp; Discounts</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>Special customer types (retired, MADA, B2B2C): the evidence the agent collects, the rules for accepting or rejecting the benefit, and the customer's benefits.</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>capabilities/CustomerType/CustomerTypeStep.tsx
-capabilities/CustomerType/customerTypeModel.ts
-capabilities/CustomerType/index.ts
-capabilities/CustomerType/useCustomerBenefits.ts
-components/domain/CompanySearchInput.tsx
-components/domain/SupportingDocumentUpload.tsx</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, administration</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>Activation Complete</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>The confirmation page for a submitted activation (facts, status, follow-on actions, eSIM handover, email) and the confirmed-order shape journeys hand it.</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>capabilities/ActivationComplete/ActivationComplete.tsx
-capabilities/ActivationComplete/confirmedOrder.ts
-capabilities/ActivationComplete/index.ts
-components/patterns/ActivationCompleteScreen.tsx
-components/patterns/OrderConfirmationScreen.tsx</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t>Eligibility gate</t>
+          <t>Customer Qualification</t>
         </is>
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>Hard-stop / soft-stop / pass eligibility check shown after identification, with the outcome panel, checks report and footer actions.</t>
+          <t>Identify the customer, run eligibility, then offer the special-discount types - the whole "Customer Identification" step of an activation, with its outcomes and footer actions.</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>capabilities/EligibilityGate/EligibilityGateStep.tsx
-capabilities/EligibilityGate/EligibilityOutcomes.tsx
-capabilities/EligibilityGate/eligibilityOutcomesModel.ts
-capabilities/EligibilityGate/index.ts</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="17" t="inlineStr">
-        <is>
-          <t>Customer Qualification</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>Identify the customer, run eligibility, then offer the special-discount types - the whole "Customer Identification" step of an activation, with its outcomes and footer actions.</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>capabilities/CustomerQualification/JourneyBanners.tsx
 capabilities/CustomerQualification/index.ts
@@ -1547,12 +1518,40 @@
 capabilities/CustomerQualification/summary.ts</t>
         </is>
       </c>
+      <c r="D20" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>Activity Comments</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>The closing note on the actions performed, with an optional channel.</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>capabilities/ActivityComments/ActivityComments.tsx
+capabilities/ActivityComments/index.ts
+capabilities/ActivityComments/step.tsx
+components/patterns/ActivityCommentsStep.tsx</t>
+        </is>
+      </c>
       <c r="D21" s="17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E21" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
+          <t>pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
     </row>
@@ -1573,9 +1572,13 @@
         </is>
       </c>
       <c r="D22" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>administration</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="17" t="inlineStr">
@@ -1594,9 +1597,13 @@
         </is>
       </c>
       <c r="D23" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>administration</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1609,7 +1616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H109"/>
+  <dimension ref="A1:H111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.85" customWidth="1" min="1" max="1"/>
@@ -1695,12 +1702,12 @@
       </c>
       <c r="G2" s="17" t="inlineStr">
         <is>
-          <t>CreditCheckPanel, MsisdnPicker, SimTypeStep, ActivationCompleteScreen, AppointmentBookingStep, BillingAccountStep, BulkOperationPortal, CafSignatureCapture, DonorAttachmentStep, IdLookupStep, PrepaidCartStep, PrepaidCheckoutStep, PrepaidPlanStep, SimSwapFormStep, TicketCreationModal, WinCashPaymentStep, ConnectionTypeTag, Tooltip</t>
+          <t>CreditCheckPanel, MsisdnPicker, SimTypeStep, ActivationCompleteScreen, AppointmentBookingStep, BillingAccountStep, BulkOperationPortal, CafSignatureCapture, DonorAttachmentStep, IdLookupStep, PrepaidCartStep, PrepaidCheckoutStep, SimSwapFormStep, TicketCreationModal, WinCashPaymentStep, ConnectionTypeTag, Tooltip</t>
         </is>
       </c>
       <c r="H2" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1742,7 @@
       </c>
       <c r="G3" s="17" t="inlineStr">
         <is>
-          <t>AdditionalDocumentsUpload, CafDocumentUpload, CompanySearchInput, ContactPhoneInput, EligibilityRows, FibreReadinessBanner, MsisdnPicker, PassportScanSections, QidImageUpload, QidInput, SimSerialScanner, StarStat, BillingAccountStep, CafSignatureCapture, DiscountCard, OrderConfirmationScreen, PostpaidPlanAddonsStep, PostpaidPlanCard, ValidationStatus, StepSummarySection, WizardFooter, WizardStepHeader, DataTable, IconButton, LocationInput, Pager, PhoneNumberInput, SearchField, Select, Tabs</t>
+          <t>AdditionalDocumentsUpload, CafDocumentUpload, CompanySearchInput, ContactPhoneInput, EligibilityRows, FibreReadinessBanner, MsisdnPicker, PassportScanSections, QidImageUpload, QidInput, SimSerialScanner, BillingAccountStep, CafSignatureCapture, DiscountCard, FixedPlanStep, OrderConfirmationScreen, PostpaidPlanAddonsStep, PostpaidPlanCard, PrepaidPlanCard, PrepaidPlanStep, ValidationStatus, ZsbAddressStep, StepSummarySection, WizardFooter, WizardStepHeader, ChoiceCards, DataTable, IconButton, LocationInput, Pager, PhoneNumberInput, SearchField, Select, Tabs</t>
         </is>
       </c>
       <c r="H3" s="17" t="inlineStr">
@@ -1775,12 +1782,12 @@
       </c>
       <c r="G4" s="17" t="inlineStr">
         <is>
-          <t>ErrorBoundary, AdditionalDocumentsUpload, BillLimitEditor, CafDocumentUpload, EligibilityRows, MsisdnPicker, PassportScanSections, QidImageUpload, QidInput, SimSerialScanner, SimTypeStep, SupportingDocumentUpload, ActivationCompleteScreen, AddressSelectionStep, BillingAccountStep, BillingProfileSetupDrawer, BulkOperationPortal, CafSignatureCapture, CheckoutDefaultLayout, DemoFaultPanel, IdLookupStatus, OrderConfirmationScreen, PostpaidDiscountsPanel, PostpaidPlanCard, PrepaidCartStep, PrepaidCheckoutStep, SignatureCapture, TicketCreationModal, ValidationStatus, VerificationGate, WinCashPaymentStep, StepSummarySection, SummaryFieldRow, WizardDialogs, WizardFooter, WizardStepHeader, WizardTitleBand, SignaturePad</t>
+          <t>ErrorBoundary, AdditionalDocumentsUpload, BillLimitEditor, CafDocumentUpload, EligibilityRows, MsisdnPicker, PassportScanSections, QidImageUpload, QidInput, SimSerialScanner, SimTypeStep, SupportingDocumentUpload, ActivationCompleteScreen, BillingAccountStep, BillingProfileSetupDrawer, BulkOperationPortal, CafSignatureCapture, CheckoutDefaultLayout, DemoFaultPanel, FixedPlanStep, IdLookupStatus, OrderConfirmationScreen, PostpaidDiscountsPanel, PostpaidPlanCard, PrepaidCartStep, PrepaidCheckoutStep, PrepaidPackDetailsDrawer, PrepaidPlanCard, TicketCreationModal, ValidationStatus, VerificationGate, WinCashPaymentStep, ZsbAddressStep, StepSummarySection, SummaryFieldRow, WizardDialogs, WizardFooter, WizardStepHeader, WizardTitleBand, SignaturePad</t>
         </is>
       </c>
       <c r="H4" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1827,7 @@
       </c>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -1855,12 +1862,12 @@
       </c>
       <c r="G6" s="17" t="inlineStr">
         <is>
-          <t>AdditionalDocumentsUpload, BillLimitEditor, CpeSerialScanner, MsisdnPicker, SimSerialScanner, AddressSelectionStep, BillingAccountStep, BillingProfileSetupDrawer, BulkOperationPortal, DonorDetailsStep, GuidedContactStep, IdLookupStep, PostpaidDiscountsPanel, TicketCreationModal, VerificationGate, ZsbAddressStep, PhoneNumberInput</t>
+          <t>AdditionalDocumentsUpload, BillLimitEditor, CpeSerialScanner, MsisdnPicker, SimSerialScanner, BillingAccountStep, BillingProfileSetupDrawer, BulkOperationPortal, DonorDetailsStep, GuidedContactStep, IdLookupStep, PostpaidDiscountsPanel, TicketCreationModal, VerificationGate, ZsbAddressStep, PhoneNumberInput</t>
         </is>
       </c>
       <c r="H6" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1879,12 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>Tooltip</t>
+          <t>SearchField</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/Tooltip.tsx</t>
+          <t>components/primitives/SearchField.tsx</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -1886,21 +1893,21 @@
         </is>
       </c>
       <c r="E7" s="17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, support, tickets</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, support</t>
         </is>
       </c>
       <c r="G7" s="17" t="inlineStr">
         <is>
-          <t>WizardStepHeader, CloseButton, Tabs</t>
+          <t>CompanySearchInput, MsisdnPicker, PlanSearchBox</t>
         </is>
       </c>
       <c r="H7" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1912,12 +1919,12 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>TooltipGroup</t>
+          <t>Textarea</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/TooltipContext.tsx</t>
+          <t>components/primitives/Textarea.tsx</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -1926,21 +1933,21 @@
         </is>
       </c>
       <c r="E8" s="17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, support, tickets</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, support</t>
         </is>
       </c>
       <c r="G8" s="17" t="inlineStr">
         <is>
-          <t>Tooltip</t>
+          <t>ActivationCompleteScreen, ActivityCommentsStep, AppointmentBookingStep, TicketCreationModal, ZsbAddressStep, WizardDialogs</t>
         </is>
       </c>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -1952,12 +1959,12 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>SearchField</t>
+          <t>Tooltip</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/SearchField.tsx</t>
+          <t>components/primitives/Tooltip.tsx</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -1970,17 +1977,17 @@
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, support</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, support</t>
         </is>
       </c>
       <c r="G9" s="17" t="inlineStr">
         <is>
-          <t>CompanySearchInput, MsisdnPicker, PlanSearchBox</t>
+          <t>WizardStepHeader, CloseButton, Tabs</t>
         </is>
       </c>
       <c r="H9" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1992,12 +1999,12 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>SegmentedTabs</t>
+          <t>TooltipGroup</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/SegmentedTabs.tsx</t>
+          <t>components/primitives/TooltipContext.tsx</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -2010,17 +2017,17 @@
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, orders, support, tickets</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, support</t>
         </is>
       </c>
       <c r="G10" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, PlanTabStrip, Tabs</t>
+          <t>Tooltip</t>
         </is>
       </c>
       <c r="H10" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2039,12 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>Textarea</t>
+          <t>CloseButton</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/Textarea.tsx</t>
+          <t>components/primitives/CloseButton.tsx</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -2046,21 +2053,21 @@
         </is>
       </c>
       <c r="E11" s="17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, support</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, support</t>
         </is>
       </c>
       <c r="G11" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen, ActivityCommentsStep, AppointmentBookingStep, TicketCreationModal, ZsbAddressStep, WizardDialogs</t>
+          <t>Drawer, Modal</t>
         </is>
       </c>
       <c r="H11" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2072,12 +2079,12 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>CloseButton</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/CloseButton.tsx</t>
+          <t>components/primitives/Checkbox.tsx</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -2086,21 +2093,21 @@
         </is>
       </c>
       <c r="E12" s="17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, support</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, support</t>
         </is>
       </c>
       <c r="G12" s="17" t="inlineStr">
         <is>
-          <t>Drawer, Modal</t>
+          <t>CreditCheckPanel, MsisdnPicker, BillingAccountStep, CafSignatureCapture, PrepaidPlanStep</t>
         </is>
       </c>
       <c r="H12" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2112,12 +2119,12 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>DataTable</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/Checkbox.tsx</t>
+          <t>components/primitives/DataTable.tsx</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -2130,17 +2137,17 @@
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, support</t>
+          <t>enterprise-iot-b2b, lead-management, mnp-fnp-porting, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, customer360, orders, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G13" s="17" t="inlineStr">
         <is>
-          <t>CreditCheckPanel, MsisdnPicker, BillingAccountStep, CafSignatureCapture, PrepaidPlanStep</t>
+          <t>BulkOperationPortal</t>
         </is>
       </c>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2152,12 +2159,12 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>DataTable</t>
+          <t>Pager</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/DataTable.tsx</t>
+          <t>components/primitives/Pager.tsx</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -2175,12 +2182,12 @@
       </c>
       <c r="G14" s="17" t="inlineStr">
         <is>
-          <t>BulkOperationPortal</t>
+          <t>DataTable</t>
         </is>
       </c>
       <c r="H14" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2192,12 +2199,12 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>Pager</t>
+          <t>TabStrip</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/Pager.tsx</t>
+          <t>components/primitives/TabStrip.tsx</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -2210,17 +2217,17 @@
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, lead-management, mnp-fnp-porting, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, customer360, orders, sales, support, tasks, tickets</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, trouble-ticketing-complaints, administration, customer360, orders, support</t>
         </is>
       </c>
       <c r="G15" s="17" t="inlineStr">
         <is>
-          <t>DataTable</t>
+          <t>PlanTabStrip, Tabs</t>
         </is>
       </c>
       <c r="H15" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2267,7 @@
       </c>
       <c r="H16" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2295,12 +2302,12 @@
       </c>
       <c r="G17" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, QidInput, AddressSelectionStep, BillingAccountStep, DiscountCard, PostpaidPlanCard, PrepaidPlanStep, ProductPlanStep</t>
+          <t>MsisdnPicker, QidInput, BillingAccountStep, DiscountCard, FixedPlanStep, PostpaidPlanCard, PrepaidPlanCard, PrepaidPlanStep, ChoiceCards</t>
         </is>
       </c>
       <c r="H17" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2347,7 @@
       </c>
       <c r="H18" s="17" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2375,12 +2382,12 @@
       </c>
       <c r="G19" s="17" t="inlineStr">
         <is>
-          <t>EligibilityRows, BillingProfileSetupDrawer, TicketCreationModal, VerificationGate</t>
+          <t>EligibilityRows, BillingProfileSetupDrawer, PrepaidPackDetailsDrawer, TicketCreationModal, VerificationGate</t>
         </is>
       </c>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2392,12 +2399,12 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>PhoneNumberInput</t>
+          <t>Modal</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/PhoneNumberInput.tsx</t>
+          <t>components/primitives/Modal.tsx</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -2410,17 +2417,17 @@
       </c>
       <c r="F20" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, navigation, administration</t>
         </is>
       </c>
       <c r="G20" s="17" t="inlineStr">
         <is>
-          <t>ContactPhoneInput, GuidedContactStep</t>
+          <t>ActivationCompleteScreen, WizardDialogs</t>
         </is>
       </c>
       <c r="H20" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2432,12 +2439,12 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>Spinner</t>
+          <t>PhoneNumberInput</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/Spinner.tsx</t>
+          <t>components/primitives/PhoneNumberInput.tsx</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -2455,12 +2462,12 @@
       </c>
       <c r="G21" s="17" t="inlineStr">
         <is>
-          <t>PassportScanSections, QidImageUpload, ValidationStatus</t>
+          <t>ContactPhoneInput, GuidedContactStep</t>
         </is>
       </c>
       <c r="H21" s="17" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2472,12 +2479,12 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>Modal</t>
+          <t>SegmentedTabs</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/Modal.tsx</t>
+          <t>components/primitives/SegmentedTabs.tsx</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -2486,21 +2493,21 @@
         </is>
       </c>
       <c r="E22" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F22" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, navigation</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration, customer360, tickets</t>
         </is>
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen, WizardDialogs</t>
+          <t>MsisdnPicker</t>
         </is>
       </c>
       <c r="H22" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2512,12 +2519,12 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>SignaturePad</t>
+          <t>Spinner</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/SignaturePad.tsx</t>
+          <t>components/primitives/Spinner.tsx</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -2526,21 +2533,21 @@
         </is>
       </c>
       <c r="E23" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F23" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G23" s="17" t="inlineStr">
         <is>
-          <t>SignatureCapture</t>
+          <t>PassportScanSections, QidImageUpload, ValidationStatus</t>
         </is>
       </c>
       <c r="H23" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2559,12 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>ConnectionTypeTag</t>
+          <t>SignaturePad</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/ConnectionTypeTag.tsx</t>
+          <t>components/primitives/SignaturePad.tsx</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -2566,21 +2573,21 @@
         </is>
       </c>
       <c r="E24" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G24" s="17" t="inlineStr">
         <is>
-          <t>PostpaidPlanCard</t>
+          <t>SignatureCapture</t>
         </is>
       </c>
       <c r="H24" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2592,12 +2599,12 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>IconButton</t>
+          <t>ConnectionTypeTag</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/IconButton.tsx</t>
+          <t>components/primitives/ConnectionTypeTag.tsx</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -2615,12 +2622,12 @@
       </c>
       <c r="G25" s="17" t="inlineStr">
         <is>
-          <t>AdditionalDocumentsUpload, CafDocumentUpload</t>
+          <t>FixedPlanStep, PostpaidPlanCard, PrepaidPlanCard</t>
         </is>
       </c>
       <c r="H25" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2632,12 +2639,12 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>IconButton</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/Radio.tsx</t>
+          <t>components/primitives/IconButton.tsx</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -2646,21 +2653,21 @@
         </is>
       </c>
       <c r="E26" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration, customer360</t>
         </is>
       </c>
       <c r="G26" s="17" t="inlineStr">
         <is>
-          <t>PrepaidPlanStep</t>
+          <t>AdditionalDocumentsUpload, CafDocumentUpload</t>
         </is>
       </c>
       <c r="H26" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2672,12 +2679,12 @@
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>LocationInput</t>
+          <t>ChoiceCards</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/LocationInput.tsx</t>
+          <t>components/primitives/ChoiceCards.tsx</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -2686,21 +2693,17 @@
         </is>
       </c>
       <c r="E27" s="17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F27" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, administration</t>
-        </is>
-      </c>
-      <c r="G27" s="17" t="inlineStr">
-        <is>
-          <t>AddressSelectionStep</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="inlineStr"/>
       <c r="H27" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>uncommitted</t>
         </is>
       </c>
     </row>
@@ -2726,11 +2729,11 @@
         </is>
       </c>
       <c r="E28" s="17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>trouble-ticketing-complaints, navigation, administration, customer360, orders, support, tickets</t>
+          <t>trouble-ticketing-complaints, navigation, administration, customer360, orders, support</t>
         </is>
       </c>
       <c r="G28" s="17" t="inlineStr">
@@ -2740,7 +2743,7 @@
       </c>
       <c r="H28" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2752,12 +2755,12 @@
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>Tabs</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/Tabs.tsx</t>
+          <t>components/primitives/Radio.tsx</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -2770,13 +2773,13 @@
       </c>
       <c r="F29" s="17" t="inlineStr">
         <is>
-          <t>trouble-ticketing-complaints, administration, customer360, orders, support, tickets</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
         </is>
       </c>
       <c r="G29" s="17" t="inlineStr"/>
       <c r="H29" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2788,31 +2791,31 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>VodafoneMark</t>
+          <t>Tabs</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/VodafoneMark.tsx</t>
-        </is>
-      </c>
-      <c r="D30" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>components/primitives/Tabs.tsx</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E30" s="17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F30" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
+          <t>trouble-ticketing-complaints, administration, customer360, orders, support</t>
         </is>
       </c>
       <c r="G30" s="17" t="inlineStr"/>
       <c r="H30" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2824,12 +2827,12 @@
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>VodafoneWordmark</t>
+          <t>VodafoneMark</t>
         </is>
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/VodafoneWordmark.tsx</t>
+          <t>components/primitives/VodafoneMark.tsx</t>
         </is>
       </c>
       <c r="D31" s="21" t="inlineStr">
@@ -2848,7 +2851,7 @@
       <c r="G31" s="17" t="inlineStr"/>
       <c r="H31" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2860,107 +2863,95 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>OoredooMark</t>
+          <t>VodafoneWordmark</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/OoredooMark.tsx</t>
-        </is>
-      </c>
-      <c r="D32" s="22" t="inlineStr">
-        <is>
-          <t>App shell only</t>
+          <t>components/primitives/VodafoneWordmark.tsx</t>
+        </is>
+      </c>
+      <c r="D32" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E32" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F32" s="17" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
       <c r="G32" s="17" t="inlineStr"/>
       <c r="H32" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="17" t="inlineStr">
         <is>
-          <t>Domain</t>
+          <t>Primitive</t>
         </is>
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>ScannedIdPreview</t>
+          <t>LocationInput</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>components/domain/ScannedIdPreview.tsx</t>
-        </is>
-      </c>
-      <c r="D33" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>components/primitives/LocationInput.tsx</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="inlineStr">
+        <is>
+          <t>No consumer</t>
         </is>
       </c>
       <c r="E33" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="F33" s="17" t="inlineStr">
-        <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, administration, customer360</t>
-        </is>
-      </c>
-      <c r="G33" s="17" t="inlineStr">
-        <is>
-          <t>PassportScanSections, QidImageUpload, qidImageUploadModel, IdScannerPanel, useIdLookup</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F33" s="17" t="inlineStr"/>
+      <c r="G33" s="17" t="inlineStr"/>
       <c r="H33" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="17" t="inlineStr">
         <is>
-          <t>Domain</t>
+          <t>Primitive</t>
         </is>
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>PassportScanSections</t>
+          <t>OoredooMark</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>components/domain/PassportScanSections.tsx</t>
-        </is>
-      </c>
-      <c r="D34" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>components/primitives/OoredooMark.tsx</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="inlineStr">
+        <is>
+          <t>App shell only</t>
         </is>
       </c>
       <c r="E34" s="17" t="n">
-        <v>11</v>
-      </c>
-      <c r="F34" s="17" t="inlineStr">
-        <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
-        </is>
-      </c>
-      <c r="G34" s="17" t="inlineStr">
-        <is>
-          <t>QidImageUpload</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F34" s="17" t="inlineStr"/>
+      <c r="G34" s="17" t="inlineStr"/>
       <c r="H34" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2972,12 +2963,12 @@
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>QidImageUpload</t>
+          <t>ScannedIdPreview</t>
         </is>
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
-          <t>components/domain/QidImageUpload.tsx</t>
+          <t>components/domain/ScannedIdPreview.tsx</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -2986,21 +2977,21 @@
         </is>
       </c>
       <c r="E35" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F35" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G35" s="17" t="inlineStr">
         <is>
-          <t>IdScannerPanel</t>
+          <t>PassportScanSections, QidImageUpload, qidImageUploadModel, IdScannerPanel, useIdLookup</t>
         </is>
       </c>
       <c r="H35" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3003,12 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>QidTypeSelector</t>
+          <t>PassportScanSections</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>components/domain/QidInput.tsx</t>
+          <t>components/domain/PassportScanSections.tsx</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
@@ -3035,12 +3026,12 @@
       </c>
       <c r="G36" s="17" t="inlineStr">
         <is>
-          <t>GuidedContactStep, IdLookupStep, IdScannerPanel, MoiResultPanel, guidedContactModel, idLookupModel, useIdLookup</t>
+          <t>QidImageUpload</t>
         </is>
       </c>
       <c r="H36" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3052,12 +3043,12 @@
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>AdditionalDocumentsUpload</t>
+          <t>QidImageUpload</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>components/domain/AdditionalDocumentsUpload.tsx</t>
+          <t>components/domain/QidImageUpload.tsx</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
@@ -3066,21 +3057,21 @@
         </is>
       </c>
       <c r="E37" s="17" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F37" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G37" s="17" t="inlineStr">
         <is>
-          <t>CafSignatureCapture</t>
+          <t>IdScannerPanel</t>
         </is>
       </c>
       <c r="H37" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3092,12 +3083,12 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>BillLimitEditor</t>
+          <t>QidTypeSelector</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>components/domain/BillLimitEditor.tsx</t>
+          <t>components/domain/QidInput.tsx</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
@@ -3106,21 +3097,21 @@
         </is>
       </c>
       <c r="E38" s="17" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F38" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G38" s="17" t="inlineStr">
         <is>
-          <t>PostpaidAddonsPanel</t>
+          <t>GuidedContactStep, IdLookupStep, IdScannerPanel, MoiResultPanel, guidedContactModel, idLookupModel, useIdLookup</t>
         </is>
       </c>
       <c r="H38" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3123,12 @@
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>CafDocumentUpload</t>
+          <t>MsisdnPicker</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>components/domain/CafDocumentUpload.tsx</t>
+          <t>components/domain/MsisdnPicker.tsx</t>
         </is>
       </c>
       <c r="D39" s="20" t="inlineStr">
@@ -3146,21 +3137,17 @@
         </is>
       </c>
       <c r="E39" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F39" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G39" s="17" t="inlineStr">
-        <is>
-          <t>CafSignatureCapture</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+      <c r="G39" s="17" t="inlineStr"/>
       <c r="H39" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3172,12 +3159,12 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>CreditCheckPanel</t>
+          <t>SimSerialScanner</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>components/domain/CreditCheckPanel.tsx</t>
+          <t>components/domain/SimSerialScanner.tsx</t>
         </is>
       </c>
       <c r="D40" s="20" t="inlineStr">
@@ -3186,21 +3173,21 @@
         </is>
       </c>
       <c r="E40" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F40" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G40" s="17" t="inlineStr">
         <is>
-          <t>ProductPlanStep</t>
+          <t>SimTypeStep</t>
         </is>
       </c>
       <c r="H40" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3212,31 +3199,35 @@
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
+          <t>StarStat</t>
+        </is>
+      </c>
+      <c r="C41" s="17" t="inlineStr">
+        <is>
+          <t>components/domain/StarStat.tsx</t>
+        </is>
+      </c>
+      <c r="D41" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
+        </is>
+      </c>
+      <c r="E41" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="F41" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+      <c r="G41" s="17" t="inlineStr">
+        <is>
           <t>MsisdnPicker</t>
         </is>
       </c>
-      <c r="C41" s="17" t="inlineStr">
-        <is>
-          <t>components/domain/MsisdnPicker.tsx</t>
-        </is>
-      </c>
-      <c r="D41" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
-        </is>
-      </c>
-      <c r="E41" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="F41" s="17" t="inlineStr">
-        <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, sim-number-management, administration</t>
-        </is>
-      </c>
-      <c r="G41" s="17" t="inlineStr"/>
       <c r="H41" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3248,12 +3239,12 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>SimSerialScanner</t>
+          <t>AdditionalDocumentsUpload</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>components/domain/SimSerialScanner.tsx</t>
+          <t>components/domain/AdditionalDocumentsUpload.tsx</t>
         </is>
       </c>
       <c r="D42" s="20" t="inlineStr">
@@ -3266,17 +3257,17 @@
       </c>
       <c r="F42" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G42" s="17" t="inlineStr">
         <is>
-          <t>SimTypeStep</t>
+          <t>CafSignatureCapture</t>
         </is>
       </c>
       <c r="H42" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3288,12 +3279,12 @@
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>StarStat</t>
+          <t>BillLimitEditor</t>
         </is>
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>components/domain/StarStat.tsx</t>
+          <t>components/domain/BillLimitEditor.tsx</t>
         </is>
       </c>
       <c r="D43" s="20" t="inlineStr">
@@ -3306,17 +3297,17 @@
       </c>
       <c r="F43" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G43" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker</t>
+          <t>PostpaidAddonsPanel, PostpaidPlanAddonsStep</t>
         </is>
       </c>
       <c r="H43" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3328,12 +3319,12 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>CompanySearchInput</t>
+          <t>CafDocumentUpload</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>components/domain/CompanySearchInput.tsx</t>
+          <t>components/domain/CafDocumentUpload.tsx</t>
         </is>
       </c>
       <c r="D44" s="20" t="inlineStr">
@@ -3342,17 +3333,21 @@
         </is>
       </c>
       <c r="E44" s="17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F44" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, administration</t>
-        </is>
-      </c>
-      <c r="G44" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G44" s="17" t="inlineStr">
+        <is>
+          <t>CafSignatureCapture</t>
+        </is>
+      </c>
       <c r="H44" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3359,12 @@
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>FibreReadinessBanner</t>
+          <t>CompanySearchInput</t>
         </is>
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>components/domain/FibreReadinessBanner.tsx</t>
+          <t>components/domain/CompanySearchInput.tsx</t>
         </is>
       </c>
       <c r="D45" s="20" t="inlineStr">
@@ -3378,21 +3373,17 @@
         </is>
       </c>
       <c r="E45" s="17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F45" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, administration</t>
-        </is>
-      </c>
-      <c r="G45" s="17" t="inlineStr">
-        <is>
-          <t>ZsbAddressStep</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G45" s="17" t="inlineStr"/>
       <c r="H45" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3404,12 +3395,12 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>SimTypeStep</t>
+          <t>CreditCheckPanel</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>components/domain/SimTypeStep.tsx</t>
+          <t>components/domain/CreditCheckPanel.tsx</t>
         </is>
       </c>
       <c r="D46" s="20" t="inlineStr">
@@ -3418,21 +3409,21 @@
         </is>
       </c>
       <c r="E46" s="17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F46" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G46" s="17" t="inlineStr">
         <is>
-          <t>CheckoutSummaryStep, checkoutDetailedTables, checkoutSummaryRows, prepaidCartModel, useCheckoutSummary</t>
+          <t>FixedPlanStep</t>
         </is>
       </c>
       <c r="H46" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3458,17 +3449,17 @@
         </is>
       </c>
       <c r="E47" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F47" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G47" s="17" t="inlineStr"/>
       <c r="H47" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3494,11 +3485,11 @@
         </is>
       </c>
       <c r="E48" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F48" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G48" s="17" t="inlineStr">
@@ -3508,7 +3499,7 @@
       </c>
       <c r="H48" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3520,12 +3511,12 @@
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>SupportingDocumentUpload</t>
+          <t>FibreReadinessBanner</t>
         </is>
       </c>
       <c r="C49" s="17" t="inlineStr">
         <is>
-          <t>components/domain/SupportingDocumentUpload.tsx</t>
+          <t>components/domain/FibreReadinessBanner.tsx</t>
         </is>
       </c>
       <c r="D49" s="20" t="inlineStr">
@@ -3534,17 +3525,21 @@
         </is>
       </c>
       <c r="E49" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F49" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
-        </is>
-      </c>
-      <c r="G49" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G49" s="17" t="inlineStr">
+        <is>
+          <t>ZsbAddressStep</t>
+        </is>
+      </c>
       <c r="H49" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3556,31 +3551,35 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>ContactPhoneInput</t>
+          <t>SimTypeStep</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>components/domain/ContactPhoneInput.tsx</t>
-        </is>
-      </c>
-      <c r="D50" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>components/domain/SimTypeStep.tsx</t>
+        </is>
+      </c>
+      <c r="D50" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E50" s="17" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F50" s="17" t="inlineStr">
         <is>
-          <t>customer360</t>
-        </is>
-      </c>
-      <c r="G50" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G50" s="17" t="inlineStr">
+        <is>
+          <t>CheckoutSummaryStep, checkoutDetailedTables, checkoutSummaryRows, prepaidCartModel, useCheckoutSummary</t>
+        </is>
+      </c>
       <c r="H50" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3592,35 +3591,31 @@
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>CpeSerialScanner</t>
+          <t>SupportingDocumentUpload</t>
         </is>
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>components/domain/CpeSerialScanner.tsx</t>
-        </is>
-      </c>
-      <c r="D51" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>components/domain/SupportingDocumentUpload.tsx</t>
+        </is>
+      </c>
+      <c r="D51" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E51" s="17" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F51" s="17" t="inlineStr">
         <is>
-          <t>fwa-5g-home</t>
-        </is>
-      </c>
-      <c r="G51" s="17" t="inlineStr">
-        <is>
-          <t>DualPlaySerialCheckStep</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G51" s="17" t="inlineStr"/>
       <c r="H51" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3632,12 +3627,12 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>OsmEmbed</t>
+          <t>ContactPhoneInput</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>components/domain/OsmEmbed.tsx</t>
+          <t>components/domain/ContactPhoneInput.tsx</t>
         </is>
       </c>
       <c r="D52" s="21" t="inlineStr">
@@ -3656,79 +3651,83 @@
       <c r="G52" s="17" t="inlineStr"/>
       <c r="H52" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="17" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>PageHeader</t>
+          <t>CpeSerialScanner</t>
         </is>
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PageHeader.tsx</t>
-        </is>
-      </c>
-      <c r="D53" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>components/domain/CpeSerialScanner.tsx</t>
+        </is>
+      </c>
+      <c r="D53" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E53" s="17" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F53" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fwa-5g-home, lead-management, mnp-fnp-porting, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
-        </is>
-      </c>
-      <c r="G53" s="17" t="inlineStr"/>
+          <t>fwa-5g-home</t>
+        </is>
+      </c>
+      <c r="G53" s="17" t="inlineStr">
+        <is>
+          <t>DualPlaySerialCheckStep</t>
+        </is>
+      </c>
       <c r="H53" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="17" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>GuidedContactStep</t>
+          <t>OsmEmbed</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/GuidedContactStep.tsx</t>
-        </is>
-      </c>
-      <c r="D54" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>components/domain/OsmEmbed.tsx</t>
+        </is>
+      </c>
+      <c r="D54" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E54" s="17" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F54" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>customer360</t>
         </is>
       </c>
       <c r="G54" s="17" t="inlineStr"/>
       <c r="H54" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -3740,12 +3739,12 @@
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>IdLookupStatus</t>
+          <t>PageHeader</t>
         </is>
       </c>
       <c r="C55" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/IdLookupStatus.tsx</t>
+          <t>components/patterns/PageHeader.tsx</t>
         </is>
       </c>
       <c r="D55" s="20" t="inlineStr">
@@ -3754,21 +3753,17 @@
         </is>
       </c>
       <c r="E55" s="17" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F55" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
-        </is>
-      </c>
-      <c r="G55" s="17" t="inlineStr">
-        <is>
-          <t>IdLookupStep</t>
-        </is>
-      </c>
+          <t>enterprise-iot-b2b, fwa-5g-home, lead-management, mnp-fnp-porting, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
+        </is>
+      </c>
+      <c r="G55" s="17" t="inlineStr"/>
       <c r="H55" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3780,12 +3775,12 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>IdLookupStep</t>
+          <t>GuidedContactStep</t>
         </is>
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/IdLookupStep.tsx</t>
+          <t>components/patterns/GuidedContactStep.tsx</t>
         </is>
       </c>
       <c r="D56" s="20" t="inlineStr">
@@ -3801,14 +3796,10 @@
           <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
-      <c r="G56" s="17" t="inlineStr">
-        <is>
-          <t>GuidedContactStep</t>
-        </is>
-      </c>
+      <c r="G56" s="17" t="inlineStr"/>
       <c r="H56" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3820,12 +3811,12 @@
       </c>
       <c r="B57" s="17" t="inlineStr">
         <is>
-          <t>IdScannerPanel</t>
+          <t>IdLookupStatus</t>
         </is>
       </c>
       <c r="C57" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/IdScannerPanel.tsx</t>
+          <t>components/patterns/IdLookupStatus.tsx</t>
         </is>
       </c>
       <c r="D57" s="20" t="inlineStr">
@@ -3848,7 +3839,7 @@
       </c>
       <c r="H57" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3860,12 +3851,12 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>MoiResultPanel</t>
+          <t>IdLookupStep</t>
         </is>
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/MoiResultPanel.tsx</t>
+          <t>components/patterns/IdLookupStep.tsx</t>
         </is>
       </c>
       <c r="D58" s="20" t="inlineStr">
@@ -3883,12 +3874,12 @@
       </c>
       <c r="G58" s="17" t="inlineStr">
         <is>
-          <t>IdLookupStep</t>
+          <t>GuidedContactStep</t>
         </is>
       </c>
       <c r="H58" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3900,12 +3891,12 @@
       </c>
       <c r="B59" s="17" t="inlineStr">
         <is>
-          <t>ValidationStatus</t>
+          <t>IdScannerPanel</t>
         </is>
       </c>
       <c r="C59" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/ValidationStatus.tsx</t>
+          <t>components/patterns/IdScannerPanel.tsx</t>
         </is>
       </c>
       <c r="D59" s="20" t="inlineStr">
@@ -3923,12 +3914,12 @@
       </c>
       <c r="G59" s="17" t="inlineStr">
         <is>
-          <t>IdLookupStatus</t>
+          <t>IdLookupStep</t>
         </is>
       </c>
       <c r="H59" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3940,12 +3931,12 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>SignatureCapture</t>
+          <t>MoiResultPanel</t>
         </is>
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/SignatureCapture.tsx</t>
+          <t>components/patterns/MoiResultPanel.tsx</t>
         </is>
       </c>
       <c r="D60" s="20" t="inlineStr">
@@ -3954,21 +3945,21 @@
         </is>
       </c>
       <c r="E60" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F60" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G60" s="17" t="inlineStr">
         <is>
-          <t>CafSignatureCapture, DonorAttachmentStep, SimSwapFormStep</t>
+          <t>IdLookupStep</t>
         </is>
       </c>
       <c r="H60" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3980,12 +3971,12 @@
       </c>
       <c r="B61" s="17" t="inlineStr">
         <is>
-          <t>ActivityCommentsStep</t>
+          <t>ValidationStatus</t>
         </is>
       </c>
       <c r="C61" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/ActivityCommentsStep.tsx</t>
+          <t>components/patterns/ValidationStatus.tsx</t>
         </is>
       </c>
       <c r="D61" s="20" t="inlineStr">
@@ -3994,17 +3985,21 @@
         </is>
       </c>
       <c r="E61" s="17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F61" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
-        </is>
-      </c>
-      <c r="G61" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G61" s="17" t="inlineStr">
+        <is>
+          <t>IdLookupStatus</t>
+        </is>
+      </c>
       <c r="H61" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4016,12 +4011,12 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>CafSignatureCapture</t>
+          <t>SignatureCapture</t>
         </is>
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CafSignatureCapture.tsx</t>
+          <t>components/patterns/SignatureCapture.tsx</t>
         </is>
       </c>
       <c r="D62" s="20" t="inlineStr">
@@ -4030,17 +4025,21 @@
         </is>
       </c>
       <c r="E62" s="17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F62" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G62" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+      <c r="G62" s="17" t="inlineStr">
+        <is>
+          <t>CafSignatureCapture, DonorAttachmentStep, SimSwapFormStep</t>
+        </is>
+      </c>
       <c r="H62" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4051,12 @@
       </c>
       <c r="B63" s="17" t="inlineStr">
         <is>
-          <t>DiscountCard</t>
+          <t>ActivationCompleteScreen</t>
         </is>
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DiscountCard.tsx</t>
+          <t>components/patterns/ActivationCompleteScreen.tsx</t>
         </is>
       </c>
       <c r="D63" s="20" t="inlineStr">
@@ -4073,14 +4072,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G63" s="17" t="inlineStr">
-        <is>
-          <t>PostpaidDiscountsPanel</t>
-        </is>
-      </c>
+      <c r="G63" s="17" t="inlineStr"/>
       <c r="H63" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4092,12 +4087,12 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>FullTerms</t>
+          <t>BillingAccountAutoResolver</t>
         </is>
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CafTerms.tsx</t>
+          <t>components/patterns/BillingAccountAutoResolver.tsx</t>
         </is>
       </c>
       <c r="D64" s="20" t="inlineStr">
@@ -4113,14 +4108,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G64" s="17" t="inlineStr">
-        <is>
-          <t>CafSignatureCapture</t>
-        </is>
-      </c>
+      <c r="G64" s="17" t="inlineStr"/>
       <c r="H64" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4132,12 +4123,12 @@
       </c>
       <c r="B65" s="17" t="inlineStr">
         <is>
-          <t>KeyInformationPanel</t>
+          <t>BillingAccountStep</t>
         </is>
       </c>
       <c r="C65" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/KeyInformationPanel.tsx</t>
+          <t>components/patterns/BillingAccountStep.tsx</t>
         </is>
       </c>
       <c r="D65" s="20" t="inlineStr">
@@ -4156,7 +4147,7 @@
       <c r="G65" s="17" t="inlineStr"/>
       <c r="H65" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4159,12 @@
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>PlanDetailsDrawer</t>
+          <t>BillingProfileSetupDrawer</t>
         </is>
       </c>
       <c r="C66" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PlanDetailsDrawer.tsx</t>
+          <t>components/patterns/BillingProfileSetupDrawer.tsx</t>
         </is>
       </c>
       <c r="D66" s="20" t="inlineStr">
@@ -4191,12 +4182,12 @@
       </c>
       <c r="G66" s="17" t="inlineStr">
         <is>
-          <t>PostpaidPlanAddonsStep</t>
+          <t>BillingAccountStep</t>
         </is>
       </c>
       <c r="H66" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4208,12 +4199,12 @@
       </c>
       <c r="B67" s="17" t="inlineStr">
         <is>
-          <t>PlanGroupPanel</t>
+          <t>BillingProfileStep</t>
         </is>
       </c>
       <c r="C67" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PlanGroupPanel.tsx</t>
+          <t>components/patterns/BillingProfileStep.tsx</t>
         </is>
       </c>
       <c r="D67" s="20" t="inlineStr">
@@ -4229,14 +4220,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G67" s="17" t="inlineStr">
-        <is>
-          <t>PostpaidPlanAddonsStep</t>
-        </is>
-      </c>
+      <c r="G67" s="17" t="inlineStr"/>
       <c r="H67" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -4248,12 +4235,12 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>PlanSearchBox</t>
+          <t>CafSignatureCapture</t>
         </is>
       </c>
       <c r="C68" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PlanSearchBox.tsx</t>
+          <t>components/patterns/CafSignatureCapture.tsx</t>
         </is>
       </c>
       <c r="D68" s="20" t="inlineStr">
@@ -4269,14 +4256,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G68" s="17" t="inlineStr">
-        <is>
-          <t>PostpaidPlanAddonsStep</t>
-        </is>
-      </c>
+      <c r="G68" s="17" t="inlineStr"/>
       <c r="H68" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4288,12 +4271,12 @@
       </c>
       <c r="B69" s="17" t="inlineStr">
         <is>
-          <t>PlanTabStrip</t>
+          <t>CheckoutDefaultLayout</t>
         </is>
       </c>
       <c r="C69" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PlanTabStrip.tsx</t>
+          <t>components/patterns/CheckoutDefaultLayout.tsx</t>
         </is>
       </c>
       <c r="D69" s="20" t="inlineStr">
@@ -4311,12 +4294,12 @@
       </c>
       <c r="G69" s="17" t="inlineStr">
         <is>
-          <t>PostpaidPlanAddonsStep</t>
+          <t>CheckoutSummaryStep</t>
         </is>
       </c>
       <c r="H69" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4328,12 +4311,12 @@
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>PostpaidAddonsPanel</t>
+          <t>CheckoutSummaryStep</t>
         </is>
       </c>
       <c r="C70" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidAddonsPanel.tsx</t>
+          <t>components/patterns/CheckoutSummaryStep.tsx</t>
         </is>
       </c>
       <c r="D70" s="20" t="inlineStr">
@@ -4349,14 +4332,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G70" s="17" t="inlineStr">
-        <is>
-          <t>PostpaidPlanAddonsStep</t>
-        </is>
-      </c>
+      <c r="G70" s="17" t="inlineStr"/>
       <c r="H70" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4347,12 @@
       </c>
       <c r="B71" s="17" t="inlineStr">
         <is>
-          <t>PostpaidDiscountsPanel</t>
+          <t>DiscountCard</t>
         </is>
       </c>
       <c r="C71" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidDiscountsPanel.tsx</t>
+          <t>components/patterns/DiscountCard.tsx</t>
         </is>
       </c>
       <c r="D71" s="20" t="inlineStr">
@@ -4391,12 +4370,12 @@
       </c>
       <c r="G71" s="17" t="inlineStr">
         <is>
-          <t>PostpaidPlanAddonsStep</t>
+          <t>PostpaidDiscountsPanel</t>
         </is>
       </c>
       <c r="H71" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4408,12 +4387,12 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>PostpaidMonthlySummary</t>
+          <t>FixedPlanStep</t>
         </is>
       </c>
       <c r="C72" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidMonthlySummary.tsx</t>
+          <t>components/patterns/FixedPlanStep.tsx</t>
         </is>
       </c>
       <c r="D72" s="20" t="inlineStr">
@@ -4429,14 +4408,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G72" s="17" t="inlineStr">
-        <is>
-          <t>PostpaidPlanAddonsStep</t>
-        </is>
-      </c>
+      <c r="G72" s="17" t="inlineStr"/>
       <c r="H72" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>uncommitted</t>
         </is>
       </c>
     </row>
@@ -4448,12 +4423,12 @@
       </c>
       <c r="B73" s="17" t="inlineStr">
         <is>
-          <t>PostpaidPlanAddonsStep</t>
+          <t>FullTerms</t>
         </is>
       </c>
       <c r="C73" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidPlanAddonsStep.tsx</t>
+          <t>components/patterns/CafTerms.tsx</t>
         </is>
       </c>
       <c r="D73" s="20" t="inlineStr">
@@ -4469,10 +4444,14 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G73" s="17" t="inlineStr"/>
+      <c r="G73" s="17" t="inlineStr">
+        <is>
+          <t>CafSignatureCapture</t>
+        </is>
+      </c>
       <c r="H73" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4484,12 +4463,12 @@
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>PostpaidPlanCard</t>
+          <t>KeyInformationPanel</t>
         </is>
       </c>
       <c r="C74" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidPlanCard.tsx</t>
+          <t>components/patterns/KeyInformationPanel.tsx</t>
         </is>
       </c>
       <c r="D74" s="20" t="inlineStr">
@@ -4505,14 +4484,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G74" s="17" t="inlineStr">
-        <is>
-          <t>PlanGroupPanel</t>
-        </is>
-      </c>
+      <c r="G74" s="17" t="inlineStr"/>
       <c r="H74" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4524,12 +4499,12 @@
       </c>
       <c r="B75" s="17" t="inlineStr">
         <is>
-          <t>PrepaidPlanStep</t>
+          <t>OrderConfirmationScreen</t>
         </is>
       </c>
       <c r="C75" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidPlanStep.tsx</t>
+          <t>components/patterns/OrderConfirmationScreen.tsx</t>
         </is>
       </c>
       <c r="D75" s="20" t="inlineStr">
@@ -4545,10 +4520,14 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G75" s="17" t="inlineStr"/>
+      <c r="G75" s="17" t="inlineStr">
+        <is>
+          <t>ActivationCompleteScreen</t>
+        </is>
+      </c>
       <c r="H75" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4560,12 +4539,12 @@
       </c>
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>ProductPlanStep</t>
+          <t>PlanDetailsDrawer</t>
         </is>
       </c>
       <c r="C76" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/ProductPlanStep.tsx</t>
+          <t>components/patterns/PlanDetailsDrawer.tsx</t>
         </is>
       </c>
       <c r="D76" s="20" t="inlineStr">
@@ -4581,10 +4560,14 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G76" s="17" t="inlineStr"/>
+      <c r="G76" s="17" t="inlineStr">
+        <is>
+          <t>PostpaidPlanAddonsStep</t>
+        </is>
+      </c>
       <c r="H76" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4596,12 +4579,12 @@
       </c>
       <c r="B77" s="17" t="inlineStr">
         <is>
-          <t>AddressSelectionStep</t>
+          <t>PlanGroupPanel</t>
         </is>
       </c>
       <c r="C77" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/AddressSelectionStep.tsx</t>
+          <t>components/patterns/PlanGroupPanel.tsx</t>
         </is>
       </c>
       <c r="D77" s="20" t="inlineStr">
@@ -4610,17 +4593,21 @@
         </is>
       </c>
       <c r="E77" s="17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F77" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, administration</t>
-        </is>
-      </c>
-      <c r="G77" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G77" s="17" t="inlineStr">
+        <is>
+          <t>PostpaidPlanAddonsStep</t>
+        </is>
+      </c>
       <c r="H77" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4632,12 +4619,12 @@
       </c>
       <c r="B78" s="17" t="inlineStr">
         <is>
-          <t>AppointmentBookingStep</t>
+          <t>PlanSearchBox</t>
         </is>
       </c>
       <c r="C78" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/AppointmentBookingStep.tsx</t>
+          <t>components/patterns/PlanSearchBox.tsx</t>
         </is>
       </c>
       <c r="D78" s="20" t="inlineStr">
@@ -4646,21 +4633,21 @@
         </is>
       </c>
       <c r="E78" s="17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F78" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G78" s="17" t="inlineStr">
         <is>
-          <t>InstallationActivationWizard</t>
+          <t>PostpaidPlanAddonsStep</t>
         </is>
       </c>
       <c r="H78" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4672,12 +4659,12 @@
       </c>
       <c r="B79" s="17" t="inlineStr">
         <is>
-          <t>BillingAccountAutoResolver</t>
+          <t>PlanTabStrip</t>
         </is>
       </c>
       <c r="C79" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/BillingAccountAutoResolver.tsx</t>
+          <t>components/patterns/PlanTabStrip.tsx</t>
         </is>
       </c>
       <c r="D79" s="20" t="inlineStr">
@@ -4686,17 +4673,21 @@
         </is>
       </c>
       <c r="E79" s="17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F79" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, administration</t>
-        </is>
-      </c>
-      <c r="G79" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G79" s="17" t="inlineStr">
+        <is>
+          <t>PostpaidPlanAddonsStep</t>
+        </is>
+      </c>
       <c r="H79" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4708,12 +4699,12 @@
       </c>
       <c r="B80" s="17" t="inlineStr">
         <is>
-          <t>BillingAccountStep</t>
+          <t>PostpaidAddonsPanel</t>
         </is>
       </c>
       <c r="C80" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/BillingAccountStep.tsx</t>
+          <t>components/patterns/PostpaidAddonsPanel.tsx</t>
         </is>
       </c>
       <c r="D80" s="20" t="inlineStr">
@@ -4722,17 +4713,21 @@
         </is>
       </c>
       <c r="E80" s="17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F80" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, administration</t>
-        </is>
-      </c>
-      <c r="G80" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G80" s="17" t="inlineStr">
+        <is>
+          <t>PostpaidPlanAddonsStep</t>
+        </is>
+      </c>
       <c r="H80" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4744,12 +4739,12 @@
       </c>
       <c r="B81" s="17" t="inlineStr">
         <is>
-          <t>BillingProfileSetupDrawer</t>
+          <t>PostpaidDiscountsPanel</t>
         </is>
       </c>
       <c r="C81" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/BillingProfileSetupDrawer.tsx</t>
+          <t>components/patterns/PostpaidDiscountsPanel.tsx</t>
         </is>
       </c>
       <c r="D81" s="20" t="inlineStr">
@@ -4758,21 +4753,21 @@
         </is>
       </c>
       <c r="E81" s="17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F81" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G81" s="17" t="inlineStr">
         <is>
-          <t>BillingAccountStep</t>
+          <t>PostpaidPlanAddonsStep</t>
         </is>
       </c>
       <c r="H81" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4784,12 +4779,12 @@
       </c>
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>BillingProfileStep</t>
+          <t>PostpaidMonthlySummary</t>
         </is>
       </c>
       <c r="C82" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/BillingProfileStep.tsx</t>
+          <t>components/patterns/PostpaidMonthlySummary.tsx</t>
         </is>
       </c>
       <c r="D82" s="20" t="inlineStr">
@@ -4798,17 +4793,21 @@
         </is>
       </c>
       <c r="E82" s="17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F82" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, administration</t>
-        </is>
-      </c>
-      <c r="G82" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G82" s="17" t="inlineStr">
+        <is>
+          <t>PostpaidPlanAddonsStep</t>
+        </is>
+      </c>
       <c r="H82" s="17" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4820,12 +4819,12 @@
       </c>
       <c r="B83" s="17" t="inlineStr">
         <is>
-          <t>WinCashPaymentStep</t>
+          <t>PostpaidPlanAddonsStep</t>
         </is>
       </c>
       <c r="C83" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/WinCashPaymentStep.tsx</t>
+          <t>components/patterns/PostpaidPlanAddonsStep.tsx</t>
         </is>
       </c>
       <c r="D83" s="20" t="inlineStr">
@@ -4834,17 +4833,17 @@
         </is>
       </c>
       <c r="E83" s="17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F83" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G83" s="17" t="inlineStr"/>
       <c r="H83" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4856,12 +4855,12 @@
       </c>
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>ZsbAddressStep</t>
+          <t>PostpaidPlanCard</t>
         </is>
       </c>
       <c r="C84" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/ZsbAddressStep.tsx</t>
+          <t>components/patterns/PostpaidPlanCard.tsx</t>
         </is>
       </c>
       <c r="D84" s="20" t="inlineStr">
@@ -4870,17 +4869,21 @@
         </is>
       </c>
       <c r="E84" s="17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F84" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, administration</t>
-        </is>
-      </c>
-      <c r="G84" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G84" s="17" t="inlineStr">
+        <is>
+          <t>PlanGroupPanel</t>
+        </is>
+      </c>
       <c r="H84" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4892,12 +4895,12 @@
       </c>
       <c r="B85" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen</t>
+          <t>PrepaidCartStep</t>
         </is>
       </c>
       <c r="C85" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/ActivationCompleteScreen.tsx</t>
+          <t>components/patterns/PrepaidCartStep.tsx</t>
         </is>
       </c>
       <c r="D85" s="20" t="inlineStr">
@@ -4906,17 +4909,17 @@
         </is>
       </c>
       <c r="E85" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F85" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G85" s="17" t="inlineStr"/>
       <c r="H85" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4928,12 +4931,12 @@
       </c>
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>CheckoutDefaultLayout</t>
+          <t>PrepaidCheckoutStep</t>
         </is>
       </c>
       <c r="C86" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CheckoutDefaultLayout.tsx</t>
+          <t>components/patterns/PrepaidCheckoutStep.tsx</t>
         </is>
       </c>
       <c r="D86" s="20" t="inlineStr">
@@ -4942,21 +4945,17 @@
         </is>
       </c>
       <c r="E86" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F86" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
-        </is>
-      </c>
-      <c r="G86" s="17" t="inlineStr">
-        <is>
-          <t>CheckoutSummaryStep</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G86" s="17" t="inlineStr"/>
       <c r="H86" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4967,12 @@
       </c>
       <c r="B87" s="17" t="inlineStr">
         <is>
-          <t>CheckoutSummaryStep</t>
+          <t>PrepaidPackDetailsDrawer</t>
         </is>
       </c>
       <c r="C87" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CheckoutSummaryStep.tsx</t>
+          <t>components/patterns/PrepaidPackDetailsDrawer.tsx</t>
         </is>
       </c>
       <c r="D87" s="20" t="inlineStr">
@@ -4982,17 +4981,21 @@
         </is>
       </c>
       <c r="E87" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F87" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
-        </is>
-      </c>
-      <c r="G87" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G87" s="17" t="inlineStr">
+        <is>
+          <t>PrepaidPlanStep</t>
+        </is>
+      </c>
       <c r="H87" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>uncommitted</t>
         </is>
       </c>
     </row>
@@ -5004,12 +5007,12 @@
       </c>
       <c r="B88" s="17" t="inlineStr">
         <is>
-          <t>DemoFaultPanel</t>
+          <t>PrepaidPlanCard</t>
         </is>
       </c>
       <c r="C88" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DemoFaultPanel.tsx</t>
+          <t>components/patterns/PrepaidPlanCard.tsx</t>
         </is>
       </c>
       <c r="D88" s="20" t="inlineStr">
@@ -5018,17 +5021,21 @@
         </is>
       </c>
       <c r="E88" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F88" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
-        </is>
-      </c>
-      <c r="G88" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G88" s="17" t="inlineStr">
+        <is>
+          <t>PrepaidPlanStep</t>
+        </is>
+      </c>
       <c r="H88" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>uncommitted</t>
         </is>
       </c>
     </row>
@@ -5040,12 +5047,12 @@
       </c>
       <c r="B89" s="17" t="inlineStr">
         <is>
-          <t>DonorAttachmentStep</t>
+          <t>PrepaidPlanStep</t>
         </is>
       </c>
       <c r="C89" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DonorAttachmentStep.tsx</t>
+          <t>components/patterns/PrepaidPlanStep.tsx</t>
         </is>
       </c>
       <c r="D89" s="20" t="inlineStr">
@@ -5054,17 +5061,17 @@
         </is>
       </c>
       <c r="E89" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F89" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G89" s="17" t="inlineStr"/>
       <c r="H89" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5076,12 +5083,12 @@
       </c>
       <c r="B90" s="17" t="inlineStr">
         <is>
-          <t>DonorDetailsStep</t>
+          <t>SummaryTables</t>
         </is>
       </c>
       <c r="C90" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DonorDetailsStep.tsx</t>
+          <t>components/patterns/CheckoutSummaryTables.tsx</t>
         </is>
       </c>
       <c r="D90" s="20" t="inlineStr">
@@ -5090,21 +5097,21 @@
         </is>
       </c>
       <c r="E90" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F90" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G90" s="17" t="inlineStr">
         <is>
-          <t>DonorAttachmentStep</t>
+          <t>CheckoutSummaryStep, checkoutDetailedTables</t>
         </is>
       </c>
       <c r="H90" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5116,12 +5123,12 @@
       </c>
       <c r="B91" s="17" t="inlineStr">
         <is>
-          <t>EntityMissing</t>
+          <t>WinCashPaymentStep</t>
         </is>
       </c>
       <c r="C91" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/EntityMissing.tsx</t>
+          <t>components/patterns/WinCashPaymentStep.tsx</t>
         </is>
       </c>
       <c r="D91" s="20" t="inlineStr">
@@ -5130,17 +5137,17 @@
         </is>
       </c>
       <c r="E91" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F91" s="17" t="inlineStr">
         <is>
-          <t>lead-management, order-management, sim-number-management, trouble-ticketing-complaints, customer360, tasks</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G91" s="17" t="inlineStr"/>
       <c r="H91" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5152,12 +5159,12 @@
       </c>
       <c r="B92" s="17" t="inlineStr">
         <is>
-          <t>OrderConfirmationScreen</t>
+          <t>ZsbAddressStep</t>
         </is>
       </c>
       <c r="C92" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/OrderConfirmationScreen.tsx</t>
+          <t>components/patterns/ZsbAddressStep.tsx</t>
         </is>
       </c>
       <c r="D92" s="20" t="inlineStr">
@@ -5166,21 +5173,17 @@
         </is>
       </c>
       <c r="E92" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F92" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
-        </is>
-      </c>
-      <c r="G92" s="17" t="inlineStr">
-        <is>
-          <t>ActivationCompleteScreen</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G92" s="17" t="inlineStr"/>
       <c r="H92" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5192,12 +5195,12 @@
       </c>
       <c r="B93" s="17" t="inlineStr">
         <is>
-          <t>PrepaidCartStep</t>
+          <t>AppointmentBookingStep</t>
         </is>
       </c>
       <c r="C93" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidCartStep.tsx</t>
+          <t>components/patterns/AppointmentBookingStep.tsx</t>
         </is>
       </c>
       <c r="D93" s="20" t="inlineStr">
@@ -5206,17 +5209,17 @@
         </is>
       </c>
       <c r="E93" s="17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F93" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, administration</t>
         </is>
       </c>
       <c r="G93" s="17" t="inlineStr"/>
       <c r="H93" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5228,12 +5231,12 @@
       </c>
       <c r="B94" s="17" t="inlineStr">
         <is>
-          <t>PrepaidCheckoutStep</t>
+          <t>DemoFaultPanel</t>
         </is>
       </c>
       <c r="C94" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidCheckoutStep.tsx</t>
+          <t>components/patterns/DemoFaultPanel.tsx</t>
         </is>
       </c>
       <c r="D94" s="20" t="inlineStr">
@@ -5252,7 +5255,7 @@
       <c r="G94" s="17" t="inlineStr"/>
       <c r="H94" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5264,12 +5267,12 @@
       </c>
       <c r="B95" s="17" t="inlineStr">
         <is>
-          <t>SummaryTables</t>
+          <t>DonorAttachmentStep</t>
         </is>
       </c>
       <c r="C95" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CheckoutSummaryTables.tsx</t>
+          <t>components/patterns/DonorAttachmentStep.tsx</t>
         </is>
       </c>
       <c r="D95" s="20" t="inlineStr">
@@ -5285,14 +5288,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
         </is>
       </c>
-      <c r="G95" s="17" t="inlineStr">
-        <is>
-          <t>CheckoutSummaryStep, checkoutDetailedTables</t>
-        </is>
-      </c>
+      <c r="G95" s="17" t="inlineStr"/>
       <c r="H95" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5304,12 +5303,12 @@
       </c>
       <c r="B96" s="17" t="inlineStr">
         <is>
-          <t>TicketCreationModal</t>
+          <t>DonorDetailsStep</t>
         </is>
       </c>
       <c r="C96" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/TicketCreationModal.tsx</t>
+          <t>components/patterns/DonorDetailsStep.tsx</t>
         </is>
       </c>
       <c r="D96" s="20" t="inlineStr">
@@ -5318,17 +5317,21 @@
         </is>
       </c>
       <c r="E96" s="17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F96" s="17" t="inlineStr">
         <is>
-          <t>trouble-ticketing-complaints, customer360, support</t>
-        </is>
-      </c>
-      <c r="G96" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
+        </is>
+      </c>
+      <c r="G96" s="17" t="inlineStr">
+        <is>
+          <t>DonorAttachmentStep</t>
+        </is>
+      </c>
       <c r="H96" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5340,31 +5343,31 @@
       </c>
       <c r="B97" s="17" t="inlineStr">
         <is>
-          <t>BulkOperationPortal</t>
+          <t>EntityMissing</t>
         </is>
       </c>
       <c r="C97" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/BulkOperationPortal.tsx</t>
-        </is>
-      </c>
-      <c r="D97" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>components/patterns/EntityMissing.tsx</t>
+        </is>
+      </c>
+      <c r="D97" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E97" s="17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F97" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b</t>
+          <t>lead-management, order-management, sim-number-management, trouble-ticketing-complaints, customer360, tasks</t>
         </is>
       </c>
       <c r="G97" s="17" t="inlineStr"/>
       <c r="H97" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5376,25 +5379,25 @@
       </c>
       <c r="B98" s="17" t="inlineStr">
         <is>
-          <t>DualPlaySerialCheckStep</t>
+          <t>ActivityCommentsStep</t>
         </is>
       </c>
       <c r="C98" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DualPlaySerialCheckStep.tsx</t>
-        </is>
-      </c>
-      <c r="D98" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>components/patterns/ActivityCommentsStep.tsx</t>
+        </is>
+      </c>
+      <c r="D98" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E98" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F98" s="17" t="inlineStr">
         <is>
-          <t>fwa-5g-home</t>
+          <t>pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G98" s="17" t="inlineStr"/>
@@ -5412,31 +5415,31 @@
       </c>
       <c r="B99" s="17" t="inlineStr">
         <is>
-          <t>SimSwapFormStep</t>
+          <t>TicketCreationModal</t>
         </is>
       </c>
       <c r="C99" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/SimSwapFormStep.tsx</t>
-        </is>
-      </c>
-      <c r="D99" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>components/patterns/TicketCreationModal.tsx</t>
+        </is>
+      </c>
+      <c r="D99" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E99" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F99" s="17" t="inlineStr">
         <is>
-          <t>sim-number-management</t>
+          <t>trouble-ticketing-complaints, customer360, support</t>
         </is>
       </c>
       <c r="G99" s="17" t="inlineStr"/>
       <c r="H99" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5448,12 +5451,12 @@
       </c>
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>VerificationGate</t>
+          <t>BulkOperationPortal</t>
         </is>
       </c>
       <c r="C100" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/VerificationGate.tsx</t>
+          <t>components/patterns/BulkOperationPortal.tsx</t>
         </is>
       </c>
       <c r="D100" s="21" t="inlineStr">
@@ -5466,121 +5469,121 @@
       </c>
       <c r="F100" s="17" t="inlineStr">
         <is>
-          <t>customer360</t>
+          <t>enterprise-iot-b2b</t>
         </is>
       </c>
       <c r="G100" s="17" t="inlineStr"/>
       <c r="H100" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="17" t="inlineStr">
         <is>
-          <t>Wizard</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="B101" s="17" t="inlineStr">
         <is>
-          <t>AbandonDialog</t>
+          <t>DualPlaySerialCheckStep</t>
         </is>
       </c>
       <c r="C101" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/WizardDialogs.tsx</t>
-        </is>
-      </c>
-      <c r="D101" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>components/patterns/DualPlaySerialCheckStep.tsx</t>
+        </is>
+      </c>
+      <c r="D101" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E101" s="17" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F101" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management</t>
+          <t>fwa-5g-home</t>
         </is>
       </c>
       <c r="G101" s="17" t="inlineStr"/>
       <c r="H101" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="17" t="inlineStr">
         <is>
-          <t>Wizard</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="B102" s="17" t="inlineStr">
         <is>
-          <t>CustomerMirrorPanel</t>
+          <t>SimSwapFormStep</t>
         </is>
       </c>
       <c r="C102" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/CustomerMirrorPanel.tsx</t>
-        </is>
-      </c>
-      <c r="D102" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>components/patterns/SimSwapFormStep.tsx</t>
+        </is>
+      </c>
+      <c r="D102" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E102" s="17" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F102" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management</t>
+          <t>sim-number-management</t>
         </is>
       </c>
       <c r="G102" s="17" t="inlineStr"/>
       <c r="H102" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="17" t="inlineStr">
         <is>
-          <t>Wizard</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="B103" s="17" t="inlineStr">
         <is>
-          <t>StepSummaryPanel</t>
+          <t>VerificationGate</t>
         </is>
       </c>
       <c r="C103" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/StepSummaryPanel.tsx</t>
-        </is>
-      </c>
-      <c r="D103" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>components/patterns/VerificationGate.tsx</t>
+        </is>
+      </c>
+      <c r="D103" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E103" s="17" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F103" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management</t>
+          <t>customer360</t>
         </is>
       </c>
       <c r="G103" s="17" t="inlineStr"/>
       <c r="H103" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5592,12 +5595,12 @@
       </c>
       <c r="B104" s="17" t="inlineStr">
         <is>
-          <t>StepSummarySection</t>
+          <t>AbandonDialog</t>
         </is>
       </c>
       <c r="C104" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/StepSummarySection.tsx</t>
+          <t>components/patterns/wizard/WizardDialogs.tsx</t>
         </is>
       </c>
       <c r="D104" s="20" t="inlineStr">
@@ -5613,14 +5616,10 @@
           <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management</t>
         </is>
       </c>
-      <c r="G104" s="17" t="inlineStr">
-        <is>
-          <t>StepSummaryPanel</t>
-        </is>
-      </c>
+      <c r="G104" s="17" t="inlineStr"/>
       <c r="H104" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5632,12 +5631,12 @@
       </c>
       <c r="B105" s="17" t="inlineStr">
         <is>
-          <t>SummaryFieldRow</t>
+          <t>CustomerMirrorPanel</t>
         </is>
       </c>
       <c r="C105" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/SummaryFieldRow.tsx</t>
+          <t>components/patterns/wizard/CustomerMirrorPanel.tsx</t>
         </is>
       </c>
       <c r="D105" s="20" t="inlineStr">
@@ -5653,14 +5652,10 @@
           <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management</t>
         </is>
       </c>
-      <c r="G105" s="17" t="inlineStr">
-        <is>
-          <t>StepSummaryPanel</t>
-        </is>
-      </c>
+      <c r="G105" s="17" t="inlineStr"/>
       <c r="H105" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5672,12 +5667,12 @@
       </c>
       <c r="B106" s="17" t="inlineStr">
         <is>
-          <t>WizardFooter</t>
+          <t>StepSummaryPanel</t>
         </is>
       </c>
       <c r="C106" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/WizardFooter.tsx</t>
+          <t>components/patterns/wizard/StepSummaryPanel.tsx</t>
         </is>
       </c>
       <c r="D106" s="20" t="inlineStr">
@@ -5696,7 +5691,7 @@
       <c r="G106" s="17" t="inlineStr"/>
       <c r="H106" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5708,12 +5703,12 @@
       </c>
       <c r="B107" s="17" t="inlineStr">
         <is>
-          <t>WizardStepHeader</t>
+          <t>StepSummarySection</t>
         </is>
       </c>
       <c r="C107" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/WizardStepHeader.tsx</t>
+          <t>components/patterns/wizard/StepSummarySection.tsx</t>
         </is>
       </c>
       <c r="D107" s="20" t="inlineStr">
@@ -5729,10 +5724,14 @@
           <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management</t>
         </is>
       </c>
-      <c r="G107" s="17" t="inlineStr"/>
+      <c r="G107" s="17" t="inlineStr">
+        <is>
+          <t>StepSummaryPanel</t>
+        </is>
+      </c>
       <c r="H107" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5744,12 +5743,12 @@
       </c>
       <c r="B108" s="17" t="inlineStr">
         <is>
-          <t>WizardTitleBand</t>
+          <t>SummaryFieldRow</t>
         </is>
       </c>
       <c r="C108" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/WizardTitleBand.tsx</t>
+          <t>components/patterns/wizard/SummaryFieldRow.tsx</t>
         </is>
       </c>
       <c r="D108" s="20" t="inlineStr">
@@ -5765,10 +5764,14 @@
           <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management</t>
         </is>
       </c>
-      <c r="G108" s="17" t="inlineStr"/>
+      <c r="G108" s="17" t="inlineStr">
+        <is>
+          <t>StepSummaryPanel</t>
+        </is>
+      </c>
       <c r="H108" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5780,32 +5783,108 @@
       </c>
       <c r="B109" s="17" t="inlineStr">
         <is>
-          <t>InstallationActivationWizard</t>
+          <t>WizardFooter</t>
         </is>
       </c>
       <c r="C109" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/InstallationActivationWizard.tsx</t>
-        </is>
-      </c>
-      <c r="D109" s="23" t="inlineStr">
-        <is>
-          <t>No consumer</t>
+          <t>components/patterns/wizard/WizardFooter.tsx</t>
+        </is>
+      </c>
+      <c r="D109" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E109" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F109" s="17" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="F109" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management</t>
+        </is>
+      </c>
       <c r="G109" s="17" t="inlineStr"/>
       <c r="H109" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="17" t="inlineStr">
+        <is>
+          <t>Wizard</t>
+        </is>
+      </c>
+      <c r="B110" s="17" t="inlineStr">
+        <is>
+          <t>WizardStepHeader</t>
+        </is>
+      </c>
+      <c r="C110" s="17" t="inlineStr">
+        <is>
+          <t>components/patterns/wizard/WizardStepHeader.tsx</t>
+        </is>
+      </c>
+      <c r="D110" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
+        </is>
+      </c>
+      <c r="E110" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="F110" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management</t>
+        </is>
+      </c>
+      <c r="G110" s="17" t="inlineStr"/>
+      <c r="H110" s="17" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="17" t="inlineStr">
+        <is>
+          <t>Wizard</t>
+        </is>
+      </c>
+      <c r="B111" s="17" t="inlineStr">
+        <is>
+          <t>WizardTitleBand</t>
+        </is>
+      </c>
+      <c r="C111" s="17" t="inlineStr">
+        <is>
+          <t>components/patterns/wizard/WizardTitleBand.tsx</t>
+        </is>
+      </c>
+      <c r="D111" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
+        </is>
+      </c>
+      <c r="E111" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="F111" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management</t>
+        </is>
+      </c>
+      <c r="G111" s="17" t="inlineStr"/>
+      <c r="H111" s="17" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H109"/>
+  <autoFilter ref="A1:H111"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5816,7 +5895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.50" customWidth="1" min="1" max="1"/>
@@ -5902,12 +5981,12 @@
       </c>
       <c r="G2" s="17" t="inlineStr">
         <is>
-          <t>CompanySearchInput, ContactPhoneInput, CpeSerialScanner, FibreReadinessBanner, MsisdnPicker, SimSerialScanner, AddressSelectionStep, AppointmentBookingStep, BillingAccountAutoResolver, BillingAccountStep, CafSignatureCapture, CafTerms, PrepaidCartStep, PrepaidCheckoutStep, PrepaidPlanStep, ProductPlanStep, TicketCreationModal, VerificationGate, ZsbAddressStep, useCheckoutSummary, useIdLookup, usePostpaidPlanAddons, StepSummaryPanel, stepSummary, useDraftStepSync, useJourneyStartResume, useWizardDraftActions, LocationInput, activityEngine, agentProfileEngine, businessAccountEngine, customer360Engine, fibreServiceability, configStore, entityStore</t>
+          <t>CompanySearchInput, ContactPhoneInput, CpeSerialScanner, FibreReadinessBanner, MsisdnPicker, SimSerialScanner, AppointmentBookingStep, BillingAccountAutoResolver, BillingAccountStep, CafSignatureCapture, CafTerms, FixedPlanStep, PrepaidCartStep, PrepaidCheckoutStep, PrepaidPlanStep, TicketCreationModal, VerificationGate, ZsbAddressStep, useCheckoutSummary, useIdLookup, usePostpaidPlanAddons, StepSummaryPanel, stepSummary, useDraftStepSync, useJourneyStartResume, useWizardDraftActions, LocationInput, activityEngine, agentProfileEngine, businessAccountEngine, customer360Engine, fibreServiceability, serviceLocationLookup, useAreaOptions, configStore, entityStore</t>
         </is>
       </c>
       <c r="H2" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5933,11 +6012,11 @@
         </is>
       </c>
       <c r="E3" s="17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" s="17" t="inlineStr">
         <is>
-          <t>dashboard, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, sales, tasks, tickets</t>
+          <t>dashboard, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, sales, tasks, tickets</t>
         </is>
       </c>
       <c r="G3" s="17" t="inlineStr">
@@ -5947,7 +6026,7 @@
       </c>
       <c r="H3" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5982,12 +6061,12 @@
       </c>
       <c r="G4" s="17" t="inlineStr">
         <is>
-          <t>BillLimitEditor, CreditCheckPanel, eligibilityRowsModel, ProductPlanStep, TicketCreationModal</t>
+          <t>BillLimitEditor, CreditCheckPanel, eligibilityRowsModel, FixedPlanStep, TicketCreationModal</t>
         </is>
       </c>
       <c r="H4" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6013,11 +6092,11 @@
         </is>
       </c>
       <c r="E5" s="17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, product-lines, navigation, customer-search, customer360, orders</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, product-lines, navigation, administration, customer-search, customer360, orders</t>
         </is>
       </c>
       <c r="G5" s="17" t="inlineStr">
@@ -6079,12 +6158,12 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>postpaidPricing</t>
+          <t>activityEngine</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>engines/postpaidPricing.ts</t>
+          <t>engines/activityEngine.ts</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -6097,17 +6176,17 @@
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G7" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, CheckoutDefaultLayout, PostpaidMonthlySummary, PostpaidPlanAddonsStep, checkoutDetailedTables, checkoutSummaryRows, useCheckoutSummary, usePostpaidPlanAddons</t>
+          <t>ActivationCompleteScreen, useWizardDraftActions</t>
         </is>
       </c>
       <c r="H7" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6119,12 +6198,12 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>activityEngine</t>
+          <t>postpaidPricing</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>engines/activityEngine.ts</t>
+          <t>engines/postpaidPricing.ts</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -6133,21 +6212,21 @@
         </is>
       </c>
       <c r="E8" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G8" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen, useWizardDraftActions</t>
+          <t>MsisdnPicker, CheckoutDefaultLayout, PostpaidMonthlySummary, PostpaidPlanAddonsStep, checkoutDetailedTables, checkoutSummaryRows, useCheckoutSummary, usePostpaidPlanAddons</t>
         </is>
       </c>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6266,7 @@
       </c>
       <c r="H9" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6289,11 +6368,11 @@
         </is>
       </c>
       <c r="E12" s="17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G12" s="17" t="inlineStr">
@@ -6303,7 +6382,7 @@
       </c>
       <c r="H12" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6315,12 +6394,12 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>agentPrivilegeEngine</t>
+          <t>fibreServiceability</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>engines/agentPrivilegeEngine.ts</t>
+          <t>engines/fibreServiceability.ts</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -6329,17 +6408,21 @@
         </is>
       </c>
       <c r="E13" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>trouble-ticketing-complaints, navigation, administration, customer360, profile, tasks</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G13" s="17" t="inlineStr">
+        <is>
+          <t>ActivationCompleteScreen</t>
+        </is>
+      </c>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -6351,12 +6434,12 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>agentTaskEngine</t>
+          <t>serviceLocationLookup</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>engines/agentTaskEngine.ts</t>
+          <t>engines/serviceLocationLookup.ts</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -6365,17 +6448,21 @@
         </is>
       </c>
       <c r="E14" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t>dashboard, order-management, trouble-ticketing-complaints, orders, support, tasks</t>
-        </is>
-      </c>
-      <c r="G14" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G14" s="17" t="inlineStr">
+        <is>
+          <t>ZsbAddressStep</t>
+        </is>
+      </c>
       <c r="H14" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6387,12 +6474,12 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>fibreServiceability</t>
+          <t>agentPrivilegeEngine</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>engines/fibreServiceability.ts</t>
+          <t>engines/agentPrivilegeEngine.ts</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -6405,17 +6492,13 @@
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
-        </is>
-      </c>
-      <c r="G15" s="17" t="inlineStr">
-        <is>
-          <t>ActivationCompleteScreen</t>
-        </is>
-      </c>
+          <t>trouble-ticketing-complaints, navigation, administration, customer360, profile, tasks</t>
+        </is>
+      </c>
+      <c r="G15" s="17" t="inlineStr"/>
       <c r="H15" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6427,12 +6510,12 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>portInEngine</t>
+          <t>agentTaskEngine</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>engines/portInEngine.ts</t>
+          <t>engines/agentTaskEngine.ts</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -6445,13 +6528,13 @@
       </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
+          <t>dashboard, order-management, trouble-ticketing-complaints, orders, support, tasks</t>
         </is>
       </c>
       <c r="G16" s="17" t="inlineStr"/>
       <c r="H16" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -6463,12 +6546,12 @@
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>approvalAuthority</t>
+          <t>portInEngine</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>engines/approvalAuthority.ts</t>
+          <t>engines/portInEngine.ts</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -6477,17 +6560,17 @@
         </is>
       </c>
       <c r="E17" s="17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F17" s="17" t="inlineStr">
         <is>
-          <t>dashboard, order-management, sim-number-management, navigation, orders</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
         </is>
       </c>
       <c r="G17" s="17" t="inlineStr"/>
       <c r="H17" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6499,12 +6582,12 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>csvExport</t>
+          <t>approvalAuthority</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>engines/csvExport.ts</t>
+          <t>engines/approvalAuthority.ts</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -6513,17 +6596,17 @@
         </is>
       </c>
       <c r="E18" s="17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>trouble-ticketing-complaints, customer360, profile, support</t>
+          <t>dashboard, order-management, sim-number-management, navigation, orders</t>
         </is>
       </c>
       <c r="G18" s="17" t="inlineStr"/>
       <c r="H18" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6618,12 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>customerServicesEngine</t>
+          <t>csvExport</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>engines/customerServicesEngine.ts</t>
+          <t>engines/csvExport.ts</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -6553,17 +6636,13 @@
       </c>
       <c r="F19" s="17" t="inlineStr">
         <is>
-          <t>product-lines, navigation, customer360, orders</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>customer360Demo</t>
-        </is>
-      </c>
+          <t>trouble-ticketing-complaints, customer360, profile, support</t>
+        </is>
+      </c>
+      <c r="G19" s="17" t="inlineStr"/>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -6575,12 +6654,12 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>bellNotificationExpiry</t>
+          <t>customerServicesEngine</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>engines/bellNotificationExpiry.ts</t>
+          <t>engines/customerServicesEngine.ts</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -6589,17 +6668,21 @@
         </is>
       </c>
       <c r="E20" s="17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F20" s="17" t="inlineStr">
         <is>
-          <t>administration, customer360</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr"/>
+          <t>product-lines, navigation, customer360, orders</t>
+        </is>
+      </c>
+      <c r="G20" s="17" t="inlineStr">
+        <is>
+          <t>customer360Demo</t>
+        </is>
+      </c>
       <c r="H20" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6611,12 +6694,12 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>businessAccountEngine</t>
+          <t>bellNotificationExpiry</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>engines/businessAccountEngine.ts</t>
+          <t>engines/bellNotificationExpiry.ts</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -6629,13 +6712,13 @@
       </c>
       <c r="F21" s="17" t="inlineStr">
         <is>
-          <t>customer-search, customer360</t>
+          <t>administration, customer360</t>
         </is>
       </c>
       <c r="G21" s="17" t="inlineStr"/>
       <c r="H21" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6730,12 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>businessSegment</t>
+          <t>businessAccountEngine</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>engines/businessSegment.ts</t>
+          <t>engines/businessAccountEngine.ts</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -6668,11 +6751,7 @@
           <t>customer-search, customer360</t>
         </is>
       </c>
-      <c r="G22" s="17" t="inlineStr">
-        <is>
-          <t>businessAccountEngine</t>
-        </is>
-      </c>
+      <c r="G22" s="17" t="inlineStr"/>
       <c r="H22" s="17" t="inlineStr">
         <is>
           <t>2026-10-06</t>
@@ -6687,12 +6766,12 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>navigationEngine</t>
+          <t>businessSegment</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>engines/navigationEngine.ts</t>
+          <t>engines/businessSegment.ts</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -6705,13 +6784,17 @@
       </c>
       <c r="F23" s="17" t="inlineStr">
         <is>
-          <t>navigation, customer360</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr"/>
+          <t>customer-search, customer360</t>
+        </is>
+      </c>
+      <c r="G23" s="17" t="inlineStr">
+        <is>
+          <t>businessAccountEngine</t>
+        </is>
+      </c>
       <c r="H23" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -6723,12 +6806,12 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>qnomyQueueEngine</t>
+          <t>navigationEngine</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>engines/qnomyQueueEngine.ts</t>
+          <t>engines/navigationEngine.ts</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -6741,13 +6824,13 @@
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>navigation, tickets</t>
+          <t>navigation, customer360</t>
         </is>
       </c>
       <c r="G24" s="17" t="inlineStr"/>
       <c r="H24" s="17" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6759,31 +6842,31 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>agentProfileEngine</t>
+          <t>qnomyQueueEngine</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>engines/agentProfileEngine.ts</t>
-        </is>
-      </c>
-      <c r="D25" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>engines/qnomyQueueEngine.ts</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E25" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
+          <t>navigation, tickets</t>
         </is>
       </c>
       <c r="G25" s="17" t="inlineStr"/>
       <c r="H25" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6795,12 +6878,12 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>customer360VisibilityEngine</t>
+          <t>agentProfileEngine</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>engines/customer360VisibilityEngine.ts</t>
+          <t>engines/agentProfileEngine.ts</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -6813,13 +6896,13 @@
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>customer360</t>
+          <t>navigation</t>
         </is>
       </c>
       <c r="G26" s="17" t="inlineStr"/>
       <c r="H26" s="17" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -6831,12 +6914,12 @@
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>profileChangeTicket</t>
+          <t>customer360VisibilityEngine</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
-          <t>engines/profileChangeTicket.ts</t>
+          <t>engines/customer360VisibilityEngine.ts</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -6855,7 +6938,7 @@
       <c r="G27" s="17" t="inlineStr"/>
       <c r="H27" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6867,12 +6950,12 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>searchScopeEngine</t>
+          <t>profileChangeTicket</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>engines/searchScopeEngine.ts</t>
+          <t>engines/profileChangeTicket.ts</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -6885,13 +6968,13 @@
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
+          <t>customer360</t>
         </is>
       </c>
       <c r="G28" s="17" t="inlineStr"/>
       <c r="H28" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6903,27 +6986,31 @@
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>moduleDescriptions</t>
+          <t>searchScopeEngine</t>
         </is>
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>engines/moduleDescriptions.ts</t>
-        </is>
-      </c>
-      <c r="D29" s="22" t="inlineStr">
-        <is>
-          <t>App shell only</t>
+          <t>engines/searchScopeEngine.ts</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E29" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F29" s="17" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
       <c r="G29" s="17" t="inlineStr"/>
       <c r="H29" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -6935,15 +7022,15 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>screenGrouping</t>
+          <t>moduleDescriptions</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>engines/screenGrouping.ts</t>
-        </is>
-      </c>
-      <c r="D30" s="22" t="inlineStr">
+          <t>engines/moduleDescriptions.ts</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
         <is>
           <t>App shell only</t>
         </is>
@@ -6962,37 +7049,29 @@
     <row r="31">
       <c r="A31" s="17" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Engine</t>
         </is>
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>entityStore</t>
+          <t>screenGrouping</t>
         </is>
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>stores/entityStore.ts</t>
-        </is>
-      </c>
-      <c r="D31" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>engines/screenGrouping.ts</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="inlineStr">
+        <is>
+          <t>App shell only</t>
         </is>
       </c>
       <c r="E31" s="17" t="n">
-        <v>23</v>
-      </c>
-      <c r="F31" s="17" t="inlineStr">
-        <is>
-          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, sales, support, tasks, tickets</t>
-        </is>
-      </c>
-      <c r="G31" s="17" t="inlineStr">
-        <is>
-          <t>ActivationCompleteScreen, AddressSelectionStep, DonorAttachmentStep, DonorDetailsStep, InstallationActivationWizard, bellNotificationExpiry, profileChangeTicket</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F31" s="17" t="inlineStr"/>
+      <c r="G31" s="17" t="inlineStr"/>
       <c r="H31" s="17" t="inlineStr">
         <is>
           <t>2026-09-24</t>
@@ -7007,12 +7086,12 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>customerContextStore</t>
+          <t>entityStore</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>stores/customerContextStore.ts</t>
+          <t>stores/entityStore.ts</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -7021,21 +7100,21 @@
         </is>
       </c>
       <c r="E32" s="17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F32" s="17" t="inlineStr">
         <is>
-          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
+          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G32" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen, useWizardDraftActions, authStore</t>
+          <t>ActivationCompleteScreen, DonorAttachmentStep, DonorDetailsStep, bellNotificationExpiry, profileChangeTicket</t>
         </is>
       </c>
       <c r="H32" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7047,12 +7126,12 @@
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>authStore</t>
+          <t>customerContextStore</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>stores/authStore.ts</t>
+          <t>stores/customerContextStore.ts</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -7061,21 +7140,21 @@
         </is>
       </c>
       <c r="E33" s="17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F33" s="17" t="inlineStr">
         <is>
-          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, support, tasks, tickets</t>
+          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G33" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, ActivationCompleteScreen, useWizardDraftActions, activityEngine, agentProfileEngine, profileChangeTicket, configStore</t>
+          <t>ActivationCompleteScreen, useWizardDraftActions, authStore</t>
         </is>
       </c>
       <c r="H33" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7087,12 +7166,12 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>notificationStore</t>
+          <t>authStore</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>stores/notificationStore.ts</t>
+          <t>stores/authStore.ts</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -7101,21 +7180,21 @@
         </is>
       </c>
       <c r="E34" s="17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F34" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, profile, support, tasks</t>
+          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G34" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, ActivationCompleteScreen, TicketCreationModal, InstallationActivationWizard, useWizardDraftActions, profileChangeTicket, useSubmit</t>
+          <t>MsisdnPicker, ActivationCompleteScreen, useWizardDraftActions, activityEngine, agentProfileEngine, profileChangeTicket, configStore</t>
         </is>
       </c>
       <c r="H34" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7127,12 +7206,12 @@
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>personaStore</t>
+          <t>notificationStore</t>
         </is>
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
-          <t>stores/personaStore.ts</t>
+          <t>stores/notificationStore.ts</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -7141,21 +7220,21 @@
         </is>
       </c>
       <c r="E35" s="17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F35" s="17" t="inlineStr">
         <is>
-          <t>dashboard, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, tasks</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, profile, support, tasks</t>
         </is>
       </c>
       <c r="G35" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, ActivationCompleteScreen, configStore</t>
+          <t>MsisdnPicker, ActivationCompleteScreen, TicketCreationModal, useWizardDraftActions, profileChangeTicket, useSubmit</t>
         </is>
       </c>
       <c r="H35" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -7167,12 +7246,12 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>workflowStore</t>
+          <t>personaStore</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>stores/workflowStore.ts</t>
+          <t>stores/personaStore.ts</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
@@ -7181,21 +7260,21 @@
         </is>
       </c>
       <c r="E36" s="17" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F36" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, navigation</t>
+          <t>dashboard, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, tasks</t>
         </is>
       </c>
       <c r="G36" s="17" t="inlineStr">
         <is>
-          <t>useJourneyStartResume, useMirrorChannel, useWizardDraftActions, useWizardStepNavigation</t>
+          <t>MsisdnPicker, ActivationCompleteScreen, configStore</t>
         </is>
       </c>
       <c r="H36" s="17" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7207,35 +7286,35 @@
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>customerVerificationStore</t>
+          <t>workflowStore</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>stores/customerVerificationStore.ts</t>
-        </is>
-      </c>
-      <c r="D37" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>stores/workflowStore.ts</t>
+        </is>
+      </c>
+      <c r="D37" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E37" s="17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F37" s="17" t="inlineStr">
         <is>
-          <t>customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, navigation</t>
         </is>
       </c>
       <c r="G37" s="17" t="inlineStr">
         <is>
-          <t>VerificationGate</t>
+          <t>useJourneyStartResume, useMirrorChannel, useWizardDraftActions, useWizardStepNavigation</t>
         </is>
       </c>
       <c r="H37" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7247,12 +7326,12 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>qnomyQueueStore</t>
+          <t>customerVerificationStore</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>stores/qnomyQueueStore.ts</t>
+          <t>stores/customerVerificationStore.ts</t>
         </is>
       </c>
       <c r="D38" s="21" t="inlineStr">
@@ -7265,13 +7344,17 @@
       </c>
       <c r="F38" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="G38" s="17" t="inlineStr"/>
+          <t>customer360</t>
+        </is>
+      </c>
+      <c r="G38" s="17" t="inlineStr">
+        <is>
+          <t>VerificationGate</t>
+        </is>
+      </c>
       <c r="H38" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7283,12 +7366,12 @@
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>regionStore</t>
+          <t>qnomyQueueStore</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>stores/regionStore.ts</t>
+          <t>stores/qnomyQueueStore.ts</t>
         </is>
       </c>
       <c r="D39" s="21" t="inlineStr">
@@ -7307,7 +7390,7 @@
       <c r="G39" s="17" t="inlineStr"/>
       <c r="H39" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -7319,12 +7402,12 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>sidebarStore</t>
+          <t>regionStore</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>stores/sidebarStore.ts</t>
+          <t>stores/regionStore.ts</t>
         </is>
       </c>
       <c r="D40" s="21" t="inlineStr">
@@ -7343,7 +7426,7 @@
       <c r="G40" s="17" t="inlineStr"/>
       <c r="H40" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7355,12 +7438,12 @@
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>themeStore</t>
+          <t>sidebarStore</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>stores/themeStore.ts</t>
+          <t>stores/sidebarStore.ts</t>
         </is>
       </c>
       <c r="D41" s="21" t="inlineStr">
@@ -7379,7 +7462,7 @@
       <c r="G41" s="17" t="inlineStr"/>
       <c r="H41" s="17" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7391,67 +7474,63 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>configStore</t>
+          <t>themeStore</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>stores/configStore.ts</t>
-        </is>
-      </c>
-      <c r="D42" s="22" t="inlineStr">
-        <is>
-          <t>App shell only</t>
+          <t>stores/themeStore.ts</t>
+        </is>
+      </c>
+      <c r="D42" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E42" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F42" s="17" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
       <c r="G42" s="17" t="inlineStr"/>
       <c r="H42" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="17" t="inlineStr">
         <is>
-          <t>Hook</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>useEnterToSubmit</t>
+          <t>configStore</t>
         </is>
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>hooks/useEnterToSubmit.ts</t>
-        </is>
-      </c>
-      <c r="D43" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>stores/configStore.ts</t>
+        </is>
+      </c>
+      <c r="D43" s="23" t="inlineStr">
+        <is>
+          <t>App shell only</t>
         </is>
       </c>
       <c r="E43" s="17" t="n">
-        <v>11</v>
-      </c>
-      <c r="F43" s="17" t="inlineStr">
-        <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
-        </is>
-      </c>
-      <c r="G43" s="17" t="inlineStr">
-        <is>
-          <t>VerificationGate, useIdLookup</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F43" s="17" t="inlineStr"/>
+      <c r="G43" s="17" t="inlineStr"/>
       <c r="H43" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7463,12 +7542,12 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>useSearchListNav</t>
+          <t>useEnterToSubmit</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>hooks/useSearchListNav.ts</t>
+          <t>hooks/useEnterToSubmit.ts</t>
         </is>
       </c>
       <c r="D44" s="20" t="inlineStr">
@@ -7477,21 +7556,21 @@
         </is>
       </c>
       <c r="E44" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F44" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, navigation, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G44" s="17" t="inlineStr">
         <is>
-          <t>CompanySearchInput, ContactPhoneInput, PlanSearchBox, LocationInput</t>
+          <t>VerificationGate, useIdLookup</t>
         </is>
       </c>
       <c r="H44" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7503,12 +7582,12 @@
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>useSubmit</t>
+          <t>useSearchListNav</t>
         </is>
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>hooks/useSubmit.ts</t>
+          <t>hooks/useSearchListNav.ts</t>
         </is>
       </c>
       <c r="D45" s="20" t="inlineStr">
@@ -7517,34 +7596,38 @@
         </is>
       </c>
       <c r="E45" s="17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F45" s="17" t="inlineStr">
         <is>
-          <t>lead-management, mnp-fnp-porting, sim-number-management, trouble-ticketing-complaints, customer360, tasks</t>
-        </is>
-      </c>
-      <c r="G45" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, navigation, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G45" s="17" t="inlineStr">
+        <is>
+          <t>CompanySearchInput, ContactPhoneInput, PlanSearchBox, LocationInput</t>
+        </is>
+      </c>
       <c r="H45" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="17" t="inlineStr">
         <is>
-          <t>Helper</t>
+          <t>Hook</t>
         </is>
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>statusTone</t>
+          <t>useAreaOptions</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>lib/statusTone.ts</t>
+          <t>hooks/useAreaOptions.ts</t>
         </is>
       </c>
       <c r="D46" s="20" t="inlineStr">
@@ -7553,38 +7636,38 @@
         </is>
       </c>
       <c r="E46" s="17" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F46" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, orders, sales, support, tasks, tickets</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G46" s="17" t="inlineStr">
         <is>
-          <t>ruleEngine</t>
+          <t>BillingAccountStep, ZsbAddressStep</t>
         </is>
       </c>
       <c r="H46" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="17" t="inlineStr">
         <is>
-          <t>Helper</t>
+          <t>Hook</t>
         </is>
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>format</t>
+          <t>useSubmit</t>
         </is>
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>lib/format.ts</t>
+          <t>hooks/useSubmit.ts</t>
         </is>
       </c>
       <c r="D47" s="20" t="inlineStr">
@@ -7593,61 +7676,53 @@
         </is>
       </c>
       <c r="E47" s="17" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F47" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, tasks</t>
-        </is>
-      </c>
-      <c r="G47" s="17" t="inlineStr">
-        <is>
-          <t>AdditionalDocumentsUpload, CafDocumentUpload, MsisdnPicker, SupportingDocumentUpload, GuidedContactStep, IdLookupStep, postpaidPlanModel, StepSummaryPanel, stepSummary, postpaidPricing</t>
-        </is>
-      </c>
+          <t>lead-management, mnp-fnp-porting, sim-number-management, trouble-ticketing-complaints, customer360, tasks</t>
+        </is>
+      </c>
+      <c r="G47" s="17" t="inlineStr"/>
       <c r="H47" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="17" t="inlineStr">
         <is>
-          <t>Helper</t>
+          <t>Hook</t>
         </is>
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>connectionType</t>
+          <t>useMinWidth</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>lib/connectionType.ts</t>
-        </is>
-      </c>
-      <c r="D48" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>hooks/useMinWidth.ts</t>
+        </is>
+      </c>
+      <c r="D48" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E48" s="17" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F48" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration, customer360</t>
-        </is>
-      </c>
-      <c r="G48" s="17" t="inlineStr">
-        <is>
-          <t>ConnectionTypeTag</t>
-        </is>
-      </c>
+          <t>navigation</t>
+        </is>
+      </c>
+      <c r="G48" s="17" t="inlineStr"/>
       <c r="H48" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7659,12 +7734,12 @@
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>deviceType</t>
+          <t>statusTone</t>
         </is>
       </c>
       <c r="C49" s="17" t="inlineStr">
         <is>
-          <t>lib/deviceType.ts</t>
+          <t>lib/statusTone.ts</t>
         </is>
       </c>
       <c r="D49" s="20" t="inlineStr">
@@ -7673,21 +7748,21 @@
         </is>
       </c>
       <c r="E49" s="17" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F49" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, orders, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G49" s="17" t="inlineStr">
         <is>
-          <t>SimSerialScanner, SimTypeStep, cafTypes</t>
+          <t>ruleEngine</t>
         </is>
       </c>
       <c r="H49" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7699,12 +7774,12 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>taskId</t>
+          <t>format</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>lib/taskId.ts</t>
+          <t>lib/format.ts</t>
         </is>
       </c>
       <c r="D50" s="20" t="inlineStr">
@@ -7713,21 +7788,21 @@
         </is>
       </c>
       <c r="E50" s="17" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F50" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, tasks</t>
         </is>
       </c>
       <c r="G50" s="17" t="inlineStr">
         <is>
-          <t>useWizardDraftActions</t>
+          <t>AdditionalDocumentsUpload, CafDocumentUpload, MsisdnPicker, SupportingDocumentUpload, GuidedContactStep, IdLookupStep, postpaidPlanModel, StepSummaryPanel, stepSummary, postpaidPricing</t>
         </is>
       </c>
       <c r="H50" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7739,31 +7814,35 @@
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>screenName</t>
+          <t>deviceType</t>
         </is>
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>lib/screenName.ts</t>
-        </is>
-      </c>
-      <c r="D51" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>lib/deviceType.ts</t>
+        </is>
+      </c>
+      <c r="D51" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E51" s="17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F51" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="G51" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, navigation, administration</t>
+        </is>
+      </c>
+      <c r="G51" s="17" t="inlineStr">
+        <is>
+          <t>SimSerialScanner, SimTypeStep, cafTypes</t>
+        </is>
+      </c>
       <c r="H51" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7775,40 +7854,156 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
+          <t>connectionType</t>
+        </is>
+      </c>
+      <c r="C52" s="17" t="inlineStr">
+        <is>
+          <t>lib/connectionType.ts</t>
+        </is>
+      </c>
+      <c r="D52" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
+        </is>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="F52" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G52" s="17" t="inlineStr">
+        <is>
+          <t>ConnectionTypeTag</t>
+        </is>
+      </c>
+      <c r="H52" s="17" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="17" t="inlineStr">
+        <is>
+          <t>Helper</t>
+        </is>
+      </c>
+      <c r="B53" s="17" t="inlineStr">
+        <is>
+          <t>taskId</t>
+        </is>
+      </c>
+      <c r="C53" s="17" t="inlineStr">
+        <is>
+          <t>lib/taskId.ts</t>
+        </is>
+      </c>
+      <c r="D53" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
+        </is>
+      </c>
+      <c r="E53" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="F53" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management</t>
+        </is>
+      </c>
+      <c r="G53" s="17" t="inlineStr">
+        <is>
+          <t>useWizardDraftActions</t>
+        </is>
+      </c>
+      <c r="H53" s="17" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="17" t="inlineStr">
+        <is>
+          <t>Helper</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="inlineStr">
+        <is>
+          <t>screenName</t>
+        </is>
+      </c>
+      <c r="C54" s="17" t="inlineStr">
+        <is>
+          <t>lib/screenName.ts</t>
+        </is>
+      </c>
+      <c r="D54" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
+        </is>
+      </c>
+      <c r="E54" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="17" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
+      <c r="G54" s="17" t="inlineStr"/>
+      <c r="H54" s="17" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="17" t="inlineStr">
+        <is>
+          <t>Helper</t>
+        </is>
+      </c>
+      <c r="B55" s="17" t="inlineStr">
+        <is>
           <t>values</t>
         </is>
       </c>
-      <c r="C52" s="17" t="inlineStr">
+      <c r="C55" s="17" t="inlineStr">
         <is>
           <t>lib/values.ts</t>
         </is>
       </c>
-      <c r="D52" s="21" t="inlineStr">
+      <c r="D55" s="21" t="inlineStr">
         <is>
           <t>Single area</t>
         </is>
       </c>
-      <c r="E52" s="17" t="n">
+      <c r="E55" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F52" s="17" t="inlineStr">
+      <c r="F55" s="17" t="inlineStr">
         <is>
           <t>customer360</t>
         </is>
       </c>
-      <c r="G52" s="17" t="inlineStr">
+      <c r="G55" s="17" t="inlineStr">
         <is>
           <t>customer360Demo</t>
         </is>
       </c>
-      <c r="H52" s="17" t="inlineStr">
+      <c r="H55" s="17" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H52"/>
+  <autoFilter ref="A1:H55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
+++ b/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>The order read-back before signing and payment (plan, add-ons, discount, number, billing, monthly and one-off totals); publishes the totals and read-back rows the CAF and Payment reuse. An optional panel above it (the port-in validation gate). Includes the prepaid cart (Add another subscription) and prepaid checkout.</t>
+          <t>The order read-back before signing and payment (plan, add-ons, discount, number, billing, monthly and one-off totals); publishes the totals and read-back rows the CAF and Payment reuse. An optional panel above it (the port-in validation gate). Includes the prepaid cart (Add another subscription) and the prepaid checkout, which a prepaid port-in also uses with its own lines, details and fees.</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
@@ -2703,7 +2703,7 @@
       <c r="G27" s="17" t="inlineStr"/>
       <c r="H27" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
       <c r="G39" s="17" t="inlineStr"/>
       <c r="H39" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="H41" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="H43" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4411,7 +4411,7 @@
       <c r="G72" s="17" t="inlineStr"/>
       <c r="H72" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="H80" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4995,7 +4995,7 @@
       </c>
       <c r="H87" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5035,7 +5035,7 @@
       </c>
       <c r="H88" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       <c r="G89" s="17" t="inlineStr"/>
       <c r="H89" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>

--- a/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
+++ b/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Method" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'UI Components'!$A$1:$H$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'UI Components'!$A$1:$H$110</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Shared Code'!$A$1:$H$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="C7" s="17" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D7" s="17" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E7" s="17" t="n">
         <v>4</v>
@@ -855,14 +855,14 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>110 UI components + 54 non-UI files</t>
+          <t>109 UI components + 54 non-UI files</t>
         </is>
       </c>
       <c r="C13" s="18" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E13" s="18" t="n">
         <v>21</v>
@@ -887,11 +887,11 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>22 named - see the Capabilities sheet</t>
+          <t>21 named - see the Capabilities sheet</t>
         </is>
       </c>
       <c r="C15" s="17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D15" s="17" t="inlineStr"/>
       <c r="E15" s="17" t="inlineStr"/>
@@ -908,7 +908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.80" customWidth="1" min="1" max="1"/>
@@ -948,72 +948,42 @@
     <row r="2">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Journey customer lock</t>
+          <t>Toasts and notifications</t>
         </is>
       </c>
       <c r="B2" s="17" t="inlineStr">
         <is>
-          <t>The state every guided journey keeps: the customer lock, draft, confirmed order, header badge (name, QID, customer ID) and exit destinations.</t>
+          <t>One-line toasts below the header; structured cards at the bottom.</t>
         </is>
       </c>
       <c r="C2" s="17" t="inlineStr">
-        <is>
-          <t>capabilities/JourneyCustomerLock/JourneyCustomerBadge.tsx
-capabilities/JourneyCustomerLock/index.ts
-capabilities/JourneyCustomerLock/journeyModel.ts
-capabilities/JourneyCustomerLock/useJourneyCustomerLock.ts
-capabilities/JourneyCustomerLock/useJourneySession.ts
-stores/customerContextStore.ts</t>
-        </is>
-      </c>
-      <c r="D2" s="17" t="n">
-        <v>22</v>
-      </c>
-      <c r="E2" s="17" t="inlineStr">
-        <is>
-          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="17" t="inlineStr">
-        <is>
-          <t>Toasts and notifications</t>
-        </is>
-      </c>
-      <c r="B3" s="17" t="inlineStr">
-        <is>
-          <t>One-line toasts below the header; structured cards at the bottom.</t>
-        </is>
-      </c>
-      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>capabilities/Toasts/Toast.tsx
 capabilities/Toasts/index.ts
 stores/notificationStore.ts</t>
         </is>
       </c>
-      <c r="D3" s="17" t="n">
+      <c r="D2" s="17" t="n">
         <v>19</v>
       </c>
-      <c r="E3" s="17" t="inlineStr">
+      <c r="E2" s="17" t="inlineStr">
         <is>
           <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, profile, support, tasks</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>Customer Identification</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>Select an ID type, scan the document, validate with MOI and show the validated Identity Details in one card, in every journey.</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>capabilities/CustomerIdentification/CustomerIdentification.tsx
 capabilities/CustomerIdentification/IdentityDetailsCard.tsx
@@ -1034,12 +1004,38 @@
 components/domain/qidImageUploadModel.ts</t>
         </is>
       </c>
+      <c r="D3" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, administration, customer360</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>Guided activation wizard</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>The step shell every activation / migration / port-in journey runs in.</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>capabilities/GuidedActivationWizard/GuidedActivationWizard.tsx
+capabilities/GuidedActivationWizard/index.ts</t>
+        </is>
+      </c>
       <c r="D4" s="17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E4" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
     </row>
@@ -1076,41 +1072,15 @@
     <row r="6">
       <c r="A6" s="17" t="inlineStr">
         <is>
-          <t>Guided activation wizard</t>
+          <t>SIM Type</t>
         </is>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>The step shell every activation / migration / port-in journey runs in.</t>
+          <t>Choose and validate the SIM: Physical (scan or enter the serial) or eSIM (issued, handed over after payment).</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>capabilities/GuidedActivationWizard/GuidedActivationWizard.tsx
-capabilities/GuidedActivationWizard/index.ts</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>SIM Type</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>Choose and validate the SIM: Physical (scan or enter the serial) or eSIM (issued, handed over after payment).</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>capabilities/SimType/SimSerial.tsx
 capabilities/SimType/SimType.tsx
@@ -1121,27 +1091,27 @@
 components/domain/SimSerialScanner.tsx</t>
         </is>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D6" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>Billing Account</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>Set up what an order bills to: pick or create a billing account, or just the order's billing settings.</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>Set up what an order bills to: one layout everywhere - the customer's existing billing accounts, or Create New Billing Account (contact, billing address, payment, card on file, primary payment profile, billing profile setup).</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>capabilities/BillingAccount/BillingAccount.tsx
 capabilities/BillingAccount/index.ts
@@ -1149,33 +1119,32 @@
 capabilities/BillingAccount/step.tsx
 capabilities/BillingAccount/summary.ts
 components/patterns/BillingAccountStep.tsx
-components/patterns/BillingProfileStep.tsx
 components/patterns/BillingProfileSetupDrawer.tsx
 components/patterns/BillingAccountAutoResolver.tsx
 components/patterns/billingAccountModel.ts</t>
         </is>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D7" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Service Address</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>The address a service is activated at: one layout everywhere: Service Information (Kahramaa Meter ID / Vodafone Premise ID with Search), then Zone / Street / Building, then Additional Details, with Qatari-ID prefill.</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>capabilities/ServiceAddress/ServiceAddress.tsx
 capabilities/ServiceAddress/index.ts
@@ -1184,27 +1153,27 @@
 components/patterns/ZsbAddressStep.tsx</t>
         </is>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D8" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Plan Selection</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>Choose the plan: postpaid plan cards then Add-ons (discounts, bill limit), prepaid packs then Add-ons, or the fixed-line / fibre plan cards with the credit check.</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>capabilities/PlanSelection/PlanSelection.tsx
 capabilities/PlanSelection/index.ts
@@ -1218,27 +1187,27 @@
 components/patterns/PlanGroupPanel.tsx</t>
         </is>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D9" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>CAF &amp; Signature</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>The Customer Agreement Form: terms, CAF type, signature and supporting documents. Standard variant (name, key information, signature) and full variant (the customer reads back the Checkout Summary order, agrees the terms and signs; the journey locks once signed); postpaid and prepaid forms.</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>capabilities/CafSignature/CafSignature.tsx
 capabilities/CafSignature/index.ts
@@ -1249,27 +1218,27 @@
 components/patterns/cafTypes.ts</t>
         </is>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D10" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Checkout Summary</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>The order read-back before signing and payment (plan, add-ons, discount, number, billing, monthly and one-off totals); publishes the totals and read-back rows the CAF and Payment reuse. An optional panel above it (the port-in validation gate). Includes the prepaid cart (Add another subscription) and the prepaid checkout, which a prepaid port-in also uses with its own lines, details and fees.</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>capabilities/CheckoutSummary/CheckoutSummary.tsx
 capabilities/CheckoutSummary/PrepaidCartBody.tsx
@@ -1288,27 +1257,27 @@
 components/patterns/prepaidCartModel.ts</t>
         </is>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D11" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>Payment</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>Take the amount due at the counter through WinCash and record the outcome.</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>capabilities/Payment/Payment.tsx
 capabilities/Payment/index.ts
@@ -1316,27 +1285,27 @@
 components/patterns/WinCashPaymentStep.tsx</t>
         </is>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D12" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>Activation Complete</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>The confirmation page for a submitted activation (facts, status, follow-on actions, eSIM handover, email) and the confirmed-order shape journeys hand it.</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>capabilities/ActivationComplete/ActivationComplete.tsx
 capabilities/ActivationComplete/confirmedOrder.ts
@@ -1345,27 +1314,27 @@
 components/patterns/OrderConfirmationScreen.tsx</t>
         </is>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D13" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>Eligibility gate</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>Hard-stop / soft-stop / pass eligibility check shown after identification, with the outcome panel, checks report and footer actions.</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>capabilities/EligibilityGate/EligibilityGateStep.tsx
 capabilities/EligibilityGate/EligibilityOutcomes.tsx
@@ -1373,6 +1342,32 @@
 capabilities/EligibilityGate/index.ts</t>
         </is>
       </c>
+      <c r="D14" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>Add-ons selection</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>Add-on cards with included-benefit handling.</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>capabilities/AddonsSelection/AddonsPicker.tsx
+capabilities/AddonsSelection/index.ts</t>
+        </is>
+      </c>
       <c r="D15" s="17" t="n">
         <v>8</v>
       </c>
@@ -1385,18 +1380,20 @@
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
         <is>
-          <t>Add-ons selection</t>
+          <t>Customer Qualification</t>
         </is>
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>Add-on cards with included-benefit handling.</t>
+          <t>Identify the customer, run eligibility, then offer the special-discount types - the whole "Customer Identification" step of an activation, with its outcomes and footer actions.</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>capabilities/AddonsSelection/AddonsPicker.tsx
-capabilities/AddonsSelection/index.ts</t>
+          <t>capabilities/CustomerQualification/JourneyBanners.tsx
+capabilities/CustomerQualification/index.ts
+capabilities/CustomerQualification/step.tsx
+capabilities/CustomerQualification/summary.ts</t>
         </is>
       </c>
       <c r="D16" s="17" t="n">
@@ -1479,7 +1476,7 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>Book the installation visit: cluster, date and time slot.</t>
+          <t>Book the installation visit: SLA cluster, the date strip (next working days from the earliest, with each day's open slots), the day's time slots and technicians free, the customer's request for a specific date and time (a later date makes the order future-dated), appointment notes and the documents the technician collects (defaulted from the persona).</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
@@ -1487,7 +1484,8 @@
           <t>capabilities/AppointmentBooking/AppointmentBooking.tsx
 capabilities/AppointmentBooking/index.ts
 capabilities/AppointmentBooking/step.tsx
-components/patterns/AppointmentBookingStep.tsx</t>
+components/patterns/AppointmentBookingStep.tsx
+components/patterns/appointmentModel.ts</t>
         </is>
       </c>
       <c r="D19" s="17" t="n">
@@ -1502,43 +1500,15 @@
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t>Customer Qualification</t>
+          <t>Activity Comments</t>
         </is>
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>Identify the customer, run eligibility, then offer the special-discount types - the whole "Customer Identification" step of an activation, with its outcomes and footer actions.</t>
+          <t>The closing note on the actions performed, with an optional channel.</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>capabilities/CustomerQualification/JourneyBanners.tsx
-capabilities/CustomerQualification/index.ts
-capabilities/CustomerQualification/step.tsx
-capabilities/CustomerQualification/summary.ts</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="17" t="inlineStr">
-        <is>
-          <t>Activity Comments</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>The closing note on the actions performed, with an optional channel.</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>capabilities/ActivityComments/ActivityComments.tsx
 capabilities/ActivityComments/index.ts
@@ -1546,60 +1516,60 @@
 components/patterns/ActivityCommentsStep.tsx</t>
         </is>
       </c>
+      <c r="D20" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>Selectable card styling</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>One selected / idle / highlighted surface for plans, offers, numbers, add-ons, discounts and ID/customer type.</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>capabilities/SelectableCard/index.ts</t>
+        </is>
+      </c>
       <c r="D21" s="17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E21" s="17" t="inlineStr">
         <is>
-          <t>pre-to-post-migration, sim-number-management, administration</t>
+          <t>administration</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="17" t="inlineStr">
         <is>
-          <t>Selectable card styling</t>
+          <t>Side drawer</t>
         </is>
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>One selected / idle / highlighted surface for plans, offers, numbers, add-ons, discounts and ID/customer type.</t>
+          <t>Fixed 50%-width drawer for forms, details and multi-step flows: the title as a small uppercase label beside the close control, the body on the page tint, and a footer whose buttons share its width equally.</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>capabilities/SelectableCard/index.ts</t>
+          <t>capabilities/SideDrawer/index.ts</t>
         </is>
       </c>
       <c r="D22" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>administration</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="17" t="inlineStr">
-        <is>
-          <t>Side drawer</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>Fixed 50%-width drawer for forms, details and multi-step flows.</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>capabilities/SideDrawer/index.ts</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>administration</t>
         </is>
@@ -1616,7 +1586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H111"/>
+  <dimension ref="A1:H110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.85" customWidth="1" min="1" max="1"/>
@@ -1742,7 +1712,7 @@
       </c>
       <c r="G3" s="17" t="inlineStr">
         <is>
-          <t>AdditionalDocumentsUpload, CafDocumentUpload, CompanySearchInput, ContactPhoneInput, EligibilityRows, FibreReadinessBanner, MsisdnPicker, PassportScanSections, QidImageUpload, QidInput, SimSerialScanner, BillingAccountStep, CafSignatureCapture, DiscountCard, FixedPlanStep, OrderConfirmationScreen, PostpaidPlanAddonsStep, PostpaidPlanCard, PrepaidPlanCard, PrepaidPlanStep, ValidationStatus, ZsbAddressStep, StepSummarySection, WizardFooter, WizardStepHeader, ChoiceCards, DataTable, IconButton, LocationInput, Pager, PhoneNumberInput, SearchField, Select, Tabs</t>
+          <t>AdditionalDocumentsUpload, CafDocumentUpload, CompanySearchInput, ContactPhoneInput, EligibilityRows, FibreReadinessBanner, MsisdnPicker, PassportScanSections, QidImageUpload, QidInput, SimSerialScanner, AppointmentBookingStep, BillingAccountStep, CafSignatureCapture, DiscountCard, FixedPlanStep, OrderConfirmationScreen, PostpaidPlanAddonsStep, PostpaidPlanCard, PrepaidPlanCard, PrepaidPlanStep, ValidationStatus, ZsbAddressStep, StepSummarySection, WizardFooter, WizardStepHeader, ChoiceCards, DataTable, IconButton, LocationInput, Pager, PhoneNumberInput, SearchField, Select, Tabs</t>
         </is>
       </c>
       <c r="H3" s="17" t="inlineStr">
@@ -1822,7 +1792,7 @@
       </c>
       <c r="G5" s="17" t="inlineStr">
         <is>
-          <t>AdditionalDocumentsUpload, CafDocumentUpload, MsisdnPicker, BillingAccountStep, BillingProfileSetupDrawer, BillingProfileStep, BulkOperationPortal, DonorAttachmentStep, DonorDetailsStep, GuidedContactStep, TicketCreationModal, ZsbAddressStep</t>
+          <t>AdditionalDocumentsUpload, CafDocumentUpload, MsisdnPicker, BillingAccountStep, BillingProfileSetupDrawer, BulkOperationPortal, DonorAttachmentStep, DonorDetailsStep, GuidedContactStep, TicketCreationModal, ZsbAddressStep</t>
         </is>
       </c>
       <c r="H5" s="17" t="inlineStr">
@@ -1862,7 +1832,7 @@
       </c>
       <c r="G6" s="17" t="inlineStr">
         <is>
-          <t>AdditionalDocumentsUpload, BillLimitEditor, CpeSerialScanner, MsisdnPicker, SimSerialScanner, BillingAccountStep, BillingProfileSetupDrawer, BulkOperationPortal, DonorDetailsStep, GuidedContactStep, IdLookupStep, PostpaidDiscountsPanel, TicketCreationModal, VerificationGate, ZsbAddressStep, PhoneNumberInput</t>
+          <t>AdditionalDocumentsUpload, BillLimitEditor, CpeSerialScanner, SimSerialScanner, AppointmentBookingStep, BillingAccountStep, BillingProfileSetupDrawer, BulkOperationPortal, DonorDetailsStep, GuidedContactStep, IdLookupStep, PostpaidDiscountsPanel, TicketCreationModal, VerificationGate, ZsbAddressStep, PhoneNumberInput</t>
         </is>
       </c>
       <c r="H6" s="17" t="inlineStr">
@@ -2102,7 +2072,7 @@
       </c>
       <c r="G12" s="17" t="inlineStr">
         <is>
-          <t>CreditCheckPanel, MsisdnPicker, BillingAccountStep, CafSignatureCapture, PrepaidPlanStep</t>
+          <t>CreditCheckPanel, MsisdnPicker, AppointmentBookingStep, BillingAccountStep, CafSignatureCapture, PrepaidPlanStep</t>
         </is>
       </c>
       <c r="H12" s="17" t="inlineStr">
@@ -2302,7 +2272,7 @@
       </c>
       <c r="G17" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, QidInput, BillingAccountStep, DiscountCard, FixedPlanStep, PostpaidPlanCard, PrepaidPlanCard, PrepaidPlanStep, ChoiceCards</t>
+          <t>MsisdnPicker, QidInput, AppointmentBookingStep, BillingAccountStep, DiscountCard, FixedPlanStep, PostpaidPlanCard, PrepaidPlanCard, PrepaidPlanStep, ChoiceCards</t>
         </is>
       </c>
       <c r="H17" s="17" t="inlineStr">
@@ -4199,12 +4169,12 @@
       </c>
       <c r="B67" s="17" t="inlineStr">
         <is>
-          <t>BillingProfileStep</t>
+          <t>CafSignatureCapture</t>
         </is>
       </c>
       <c r="C67" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/BillingProfileStep.tsx</t>
+          <t>components/patterns/CafSignatureCapture.tsx</t>
         </is>
       </c>
       <c r="D67" s="20" t="inlineStr">
@@ -4223,7 +4193,7 @@
       <c r="G67" s="17" t="inlineStr"/>
       <c r="H67" s="17" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4235,12 +4205,12 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>CafSignatureCapture</t>
+          <t>CheckoutDefaultLayout</t>
         </is>
       </c>
       <c r="C68" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CafSignatureCapture.tsx</t>
+          <t>components/patterns/CheckoutDefaultLayout.tsx</t>
         </is>
       </c>
       <c r="D68" s="20" t="inlineStr">
@@ -4256,7 +4226,11 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G68" s="17" t="inlineStr"/>
+      <c r="G68" s="17" t="inlineStr">
+        <is>
+          <t>CheckoutSummaryStep</t>
+        </is>
+      </c>
       <c r="H68" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
@@ -4271,12 +4245,12 @@
       </c>
       <c r="B69" s="17" t="inlineStr">
         <is>
-          <t>CheckoutDefaultLayout</t>
+          <t>CheckoutSummaryStep</t>
         </is>
       </c>
       <c r="C69" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CheckoutDefaultLayout.tsx</t>
+          <t>components/patterns/CheckoutSummaryStep.tsx</t>
         </is>
       </c>
       <c r="D69" s="20" t="inlineStr">
@@ -4292,14 +4266,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G69" s="17" t="inlineStr">
-        <is>
-          <t>CheckoutSummaryStep</t>
-        </is>
-      </c>
+      <c r="G69" s="17" t="inlineStr"/>
       <c r="H69" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4311,12 +4281,12 @@
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>CheckoutSummaryStep</t>
+          <t>DiscountCard</t>
         </is>
       </c>
       <c r="C70" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CheckoutSummaryStep.tsx</t>
+          <t>components/patterns/DiscountCard.tsx</t>
         </is>
       </c>
       <c r="D70" s="20" t="inlineStr">
@@ -4332,7 +4302,11 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G70" s="17" t="inlineStr"/>
+      <c r="G70" s="17" t="inlineStr">
+        <is>
+          <t>PostpaidDiscountsPanel</t>
+        </is>
+      </c>
       <c r="H70" s="17" t="inlineStr">
         <is>
           <t>2026-10-15</t>
@@ -4347,12 +4321,12 @@
       </c>
       <c r="B71" s="17" t="inlineStr">
         <is>
-          <t>DiscountCard</t>
+          <t>FixedPlanStep</t>
         </is>
       </c>
       <c r="C71" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DiscountCard.tsx</t>
+          <t>components/patterns/FixedPlanStep.tsx</t>
         </is>
       </c>
       <c r="D71" s="20" t="inlineStr">
@@ -4368,14 +4342,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G71" s="17" t="inlineStr">
-        <is>
-          <t>PostpaidDiscountsPanel</t>
-        </is>
-      </c>
+      <c r="G71" s="17" t="inlineStr"/>
       <c r="H71" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4387,12 +4357,12 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>FixedPlanStep</t>
+          <t>FullTerms</t>
         </is>
       </c>
       <c r="C72" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/FixedPlanStep.tsx</t>
+          <t>components/patterns/CafTerms.tsx</t>
         </is>
       </c>
       <c r="D72" s="20" t="inlineStr">
@@ -4408,10 +4378,14 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G72" s="17" t="inlineStr"/>
+      <c r="G72" s="17" t="inlineStr">
+        <is>
+          <t>CafSignatureCapture</t>
+        </is>
+      </c>
       <c r="H72" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4423,12 +4397,12 @@
       </c>
       <c r="B73" s="17" t="inlineStr">
         <is>
-          <t>FullTerms</t>
+          <t>KeyInformationPanel</t>
         </is>
       </c>
       <c r="C73" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CafTerms.tsx</t>
+          <t>components/patterns/KeyInformationPanel.tsx</t>
         </is>
       </c>
       <c r="D73" s="20" t="inlineStr">
@@ -4444,11 +4418,7 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G73" s="17" t="inlineStr">
-        <is>
-          <t>CafSignatureCapture</t>
-        </is>
-      </c>
+      <c r="G73" s="17" t="inlineStr"/>
       <c r="H73" s="17" t="inlineStr">
         <is>
           <t>2026-10-15</t>
@@ -4463,12 +4433,12 @@
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>KeyInformationPanel</t>
+          <t>OrderConfirmationScreen</t>
         </is>
       </c>
       <c r="C74" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/KeyInformationPanel.tsx</t>
+          <t>components/patterns/OrderConfirmationScreen.tsx</t>
         </is>
       </c>
       <c r="D74" s="20" t="inlineStr">
@@ -4484,10 +4454,14 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G74" s="17" t="inlineStr"/>
+      <c r="G74" s="17" t="inlineStr">
+        <is>
+          <t>ActivationCompleteScreen</t>
+        </is>
+      </c>
       <c r="H74" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4499,12 +4473,12 @@
       </c>
       <c r="B75" s="17" t="inlineStr">
         <is>
-          <t>OrderConfirmationScreen</t>
+          <t>PlanDetailsDrawer</t>
         </is>
       </c>
       <c r="C75" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/OrderConfirmationScreen.tsx</t>
+          <t>components/patterns/PlanDetailsDrawer.tsx</t>
         </is>
       </c>
       <c r="D75" s="20" t="inlineStr">
@@ -4522,12 +4496,12 @@
       </c>
       <c r="G75" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen</t>
+          <t>PostpaidPlanAddonsStep</t>
         </is>
       </c>
       <c r="H75" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4539,12 +4513,12 @@
       </c>
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>PlanDetailsDrawer</t>
+          <t>PlanGroupPanel</t>
         </is>
       </c>
       <c r="C76" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PlanDetailsDrawer.tsx</t>
+          <t>components/patterns/PlanGroupPanel.tsx</t>
         </is>
       </c>
       <c r="D76" s="20" t="inlineStr">
@@ -4579,12 +4553,12 @@
       </c>
       <c r="B77" s="17" t="inlineStr">
         <is>
-          <t>PlanGroupPanel</t>
+          <t>PlanSearchBox</t>
         </is>
       </c>
       <c r="C77" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PlanGroupPanel.tsx</t>
+          <t>components/patterns/PlanSearchBox.tsx</t>
         </is>
       </c>
       <c r="D77" s="20" t="inlineStr">
@@ -4619,12 +4593,12 @@
       </c>
       <c r="B78" s="17" t="inlineStr">
         <is>
-          <t>PlanSearchBox</t>
+          <t>PlanTabStrip</t>
         </is>
       </c>
       <c r="C78" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PlanSearchBox.tsx</t>
+          <t>components/patterns/PlanTabStrip.tsx</t>
         </is>
       </c>
       <c r="D78" s="20" t="inlineStr">
@@ -4647,7 +4621,7 @@
       </c>
       <c r="H78" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4659,12 +4633,12 @@
       </c>
       <c r="B79" s="17" t="inlineStr">
         <is>
-          <t>PlanTabStrip</t>
+          <t>PostpaidAddonsPanel</t>
         </is>
       </c>
       <c r="C79" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PlanTabStrip.tsx</t>
+          <t>components/patterns/PostpaidAddonsPanel.tsx</t>
         </is>
       </c>
       <c r="D79" s="20" t="inlineStr">
@@ -4699,12 +4673,12 @@
       </c>
       <c r="B80" s="17" t="inlineStr">
         <is>
-          <t>PostpaidAddonsPanel</t>
+          <t>PostpaidDiscountsPanel</t>
         </is>
       </c>
       <c r="C80" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidAddonsPanel.tsx</t>
+          <t>components/patterns/PostpaidDiscountsPanel.tsx</t>
         </is>
       </c>
       <c r="D80" s="20" t="inlineStr">
@@ -4727,7 +4701,7 @@
       </c>
       <c r="H80" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4713,12 @@
       </c>
       <c r="B81" s="17" t="inlineStr">
         <is>
-          <t>PostpaidDiscountsPanel</t>
+          <t>PostpaidMonthlySummary</t>
         </is>
       </c>
       <c r="C81" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidDiscountsPanel.tsx</t>
+          <t>components/patterns/PostpaidMonthlySummary.tsx</t>
         </is>
       </c>
       <c r="D81" s="20" t="inlineStr">
@@ -4767,7 +4741,7 @@
       </c>
       <c r="H81" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4779,12 +4753,12 @@
       </c>
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>PostpaidMonthlySummary</t>
+          <t>PostpaidPlanAddonsStep</t>
         </is>
       </c>
       <c r="C82" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidMonthlySummary.tsx</t>
+          <t>components/patterns/PostpaidPlanAddonsStep.tsx</t>
         </is>
       </c>
       <c r="D82" s="20" t="inlineStr">
@@ -4800,11 +4774,7 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G82" s="17" t="inlineStr">
-        <is>
-          <t>PostpaidPlanAddonsStep</t>
-        </is>
-      </c>
+      <c r="G82" s="17" t="inlineStr"/>
       <c r="H82" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
@@ -4819,12 +4789,12 @@
       </c>
       <c r="B83" s="17" t="inlineStr">
         <is>
-          <t>PostpaidPlanAddonsStep</t>
+          <t>PostpaidPlanCard</t>
         </is>
       </c>
       <c r="C83" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidPlanAddonsStep.tsx</t>
+          <t>components/patterns/PostpaidPlanCard.tsx</t>
         </is>
       </c>
       <c r="D83" s="20" t="inlineStr">
@@ -4840,7 +4810,11 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G83" s="17" t="inlineStr"/>
+      <c r="G83" s="17" t="inlineStr">
+        <is>
+          <t>PlanGroupPanel</t>
+        </is>
+      </c>
       <c r="H83" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
@@ -4855,12 +4829,12 @@
       </c>
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>PostpaidPlanCard</t>
+          <t>PrepaidCartStep</t>
         </is>
       </c>
       <c r="C84" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidPlanCard.tsx</t>
+          <t>components/patterns/PrepaidCartStep.tsx</t>
         </is>
       </c>
       <c r="D84" s="20" t="inlineStr">
@@ -4876,14 +4850,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G84" s="17" t="inlineStr">
-        <is>
-          <t>PlanGroupPanel</t>
-        </is>
-      </c>
+      <c r="G84" s="17" t="inlineStr"/>
       <c r="H84" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4895,12 +4865,12 @@
       </c>
       <c r="B85" s="17" t="inlineStr">
         <is>
-          <t>PrepaidCartStep</t>
+          <t>PrepaidCheckoutStep</t>
         </is>
       </c>
       <c r="C85" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidCartStep.tsx</t>
+          <t>components/patterns/PrepaidCheckoutStep.tsx</t>
         </is>
       </c>
       <c r="D85" s="20" t="inlineStr">
@@ -4919,7 +4889,7 @@
       <c r="G85" s="17" t="inlineStr"/>
       <c r="H85" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4931,12 +4901,12 @@
       </c>
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>PrepaidCheckoutStep</t>
+          <t>PrepaidPackDetailsDrawer</t>
         </is>
       </c>
       <c r="C86" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidCheckoutStep.tsx</t>
+          <t>components/patterns/PrepaidPackDetailsDrawer.tsx</t>
         </is>
       </c>
       <c r="D86" s="20" t="inlineStr">
@@ -4952,7 +4922,11 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G86" s="17" t="inlineStr"/>
+      <c r="G86" s="17" t="inlineStr">
+        <is>
+          <t>PrepaidPlanStep</t>
+        </is>
+      </c>
       <c r="H86" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
@@ -4967,12 +4941,12 @@
       </c>
       <c r="B87" s="17" t="inlineStr">
         <is>
-          <t>PrepaidPackDetailsDrawer</t>
+          <t>PrepaidPlanCard</t>
         </is>
       </c>
       <c r="C87" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidPackDetailsDrawer.tsx</t>
+          <t>components/patterns/PrepaidPlanCard.tsx</t>
         </is>
       </c>
       <c r="D87" s="20" t="inlineStr">
@@ -5007,12 +4981,12 @@
       </c>
       <c r="B88" s="17" t="inlineStr">
         <is>
-          <t>PrepaidPlanCard</t>
+          <t>PrepaidPlanStep</t>
         </is>
       </c>
       <c r="C88" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidPlanCard.tsx</t>
+          <t>components/patterns/PrepaidPlanStep.tsx</t>
         </is>
       </c>
       <c r="D88" s="20" t="inlineStr">
@@ -5028,11 +5002,7 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G88" s="17" t="inlineStr">
-        <is>
-          <t>PrepaidPlanStep</t>
-        </is>
-      </c>
+      <c r="G88" s="17" t="inlineStr"/>
       <c r="H88" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
@@ -5047,12 +5017,12 @@
       </c>
       <c r="B89" s="17" t="inlineStr">
         <is>
-          <t>PrepaidPlanStep</t>
+          <t>SummaryTables</t>
         </is>
       </c>
       <c r="C89" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidPlanStep.tsx</t>
+          <t>components/patterns/CheckoutSummaryTables.tsx</t>
         </is>
       </c>
       <c r="D89" s="20" t="inlineStr">
@@ -5068,10 +5038,14 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G89" s="17" t="inlineStr"/>
+      <c r="G89" s="17" t="inlineStr">
+        <is>
+          <t>CheckoutSummaryStep, checkoutDetailedTables</t>
+        </is>
+      </c>
       <c r="H89" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5057,12 @@
       </c>
       <c r="B90" s="17" t="inlineStr">
         <is>
-          <t>SummaryTables</t>
+          <t>WinCashPaymentStep</t>
         </is>
       </c>
       <c r="C90" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CheckoutSummaryTables.tsx</t>
+          <t>components/patterns/WinCashPaymentStep.tsx</t>
         </is>
       </c>
       <c r="D90" s="20" t="inlineStr">
@@ -5104,11 +5078,7 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G90" s="17" t="inlineStr">
-        <is>
-          <t>CheckoutSummaryStep, checkoutDetailedTables</t>
-        </is>
-      </c>
+      <c r="G90" s="17" t="inlineStr"/>
       <c r="H90" s="17" t="inlineStr">
         <is>
           <t>2026-10-15</t>
@@ -5123,12 +5093,12 @@
       </c>
       <c r="B91" s="17" t="inlineStr">
         <is>
-          <t>WinCashPaymentStep</t>
+          <t>ZsbAddressStep</t>
         </is>
       </c>
       <c r="C91" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/WinCashPaymentStep.tsx</t>
+          <t>components/patterns/ZsbAddressStep.tsx</t>
         </is>
       </c>
       <c r="D91" s="20" t="inlineStr">
@@ -5147,7 +5117,7 @@
       <c r="G91" s="17" t="inlineStr"/>
       <c r="H91" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5159,12 +5129,12 @@
       </c>
       <c r="B92" s="17" t="inlineStr">
         <is>
-          <t>ZsbAddressStep</t>
+          <t>AppointmentBookingStep</t>
         </is>
       </c>
       <c r="C92" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/ZsbAddressStep.tsx</t>
+          <t>components/patterns/AppointmentBookingStep.tsx</t>
         </is>
       </c>
       <c r="D92" s="20" t="inlineStr">
@@ -5173,11 +5143,11 @@
         </is>
       </c>
       <c r="E92" s="17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F92" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, administration</t>
         </is>
       </c>
       <c r="G92" s="17" t="inlineStr"/>
@@ -5195,12 +5165,12 @@
       </c>
       <c r="B93" s="17" t="inlineStr">
         <is>
-          <t>AppointmentBookingStep</t>
+          <t>DemoFaultPanel</t>
         </is>
       </c>
       <c r="C93" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/AppointmentBookingStep.tsx</t>
+          <t>components/patterns/DemoFaultPanel.tsx</t>
         </is>
       </c>
       <c r="D93" s="20" t="inlineStr">
@@ -5209,17 +5179,17 @@
         </is>
       </c>
       <c r="E93" s="17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F93" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
         </is>
       </c>
       <c r="G93" s="17" t="inlineStr"/>
       <c r="H93" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5231,12 +5201,12 @@
       </c>
       <c r="B94" s="17" t="inlineStr">
         <is>
-          <t>DemoFaultPanel</t>
+          <t>DonorAttachmentStep</t>
         </is>
       </c>
       <c r="C94" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DemoFaultPanel.tsx</t>
+          <t>components/patterns/DonorAttachmentStep.tsx</t>
         </is>
       </c>
       <c r="D94" s="20" t="inlineStr">
@@ -5267,12 +5237,12 @@
       </c>
       <c r="B95" s="17" t="inlineStr">
         <is>
-          <t>DonorAttachmentStep</t>
+          <t>DonorDetailsStep</t>
         </is>
       </c>
       <c r="C95" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DonorAttachmentStep.tsx</t>
+          <t>components/patterns/DonorDetailsStep.tsx</t>
         </is>
       </c>
       <c r="D95" s="20" t="inlineStr">
@@ -5288,7 +5258,11 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
         </is>
       </c>
-      <c r="G95" s="17" t="inlineStr"/>
+      <c r="G95" s="17" t="inlineStr">
+        <is>
+          <t>DonorAttachmentStep</t>
+        </is>
+      </c>
       <c r="H95" s="17" t="inlineStr">
         <is>
           <t>2026-10-15</t>
@@ -5303,12 +5277,12 @@
       </c>
       <c r="B96" s="17" t="inlineStr">
         <is>
-          <t>DonorDetailsStep</t>
+          <t>EntityMissing</t>
         </is>
       </c>
       <c r="C96" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DonorDetailsStep.tsx</t>
+          <t>components/patterns/EntityMissing.tsx</t>
         </is>
       </c>
       <c r="D96" s="20" t="inlineStr">
@@ -5321,14 +5295,10 @@
       </c>
       <c r="F96" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
-        </is>
-      </c>
-      <c r="G96" s="17" t="inlineStr">
-        <is>
-          <t>DonorAttachmentStep</t>
-        </is>
-      </c>
+          <t>lead-management, order-management, sim-number-management, trouble-ticketing-complaints, customer360, tasks</t>
+        </is>
+      </c>
+      <c r="G96" s="17" t="inlineStr"/>
       <c r="H96" s="17" t="inlineStr">
         <is>
           <t>2026-10-15</t>
@@ -5343,12 +5313,12 @@
       </c>
       <c r="B97" s="17" t="inlineStr">
         <is>
-          <t>EntityMissing</t>
+          <t>ActivityCommentsStep</t>
         </is>
       </c>
       <c r="C97" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/EntityMissing.tsx</t>
+          <t>components/patterns/ActivityCommentsStep.tsx</t>
         </is>
       </c>
       <c r="D97" s="20" t="inlineStr">
@@ -5357,17 +5327,17 @@
         </is>
       </c>
       <c r="E97" s="17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F97" s="17" t="inlineStr">
         <is>
-          <t>lead-management, order-management, sim-number-management, trouble-ticketing-complaints, customer360, tasks</t>
+          <t>pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G97" s="17" t="inlineStr"/>
       <c r="H97" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -5379,12 +5349,12 @@
       </c>
       <c r="B98" s="17" t="inlineStr">
         <is>
-          <t>ActivityCommentsStep</t>
+          <t>TicketCreationModal</t>
         </is>
       </c>
       <c r="C98" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/ActivityCommentsStep.tsx</t>
+          <t>components/patterns/TicketCreationModal.tsx</t>
         </is>
       </c>
       <c r="D98" s="20" t="inlineStr">
@@ -5397,13 +5367,13 @@
       </c>
       <c r="F98" s="17" t="inlineStr">
         <is>
-          <t>pre-to-post-migration, sim-number-management, administration</t>
+          <t>trouble-ticketing-complaints, customer360, support</t>
         </is>
       </c>
       <c r="G98" s="17" t="inlineStr"/>
       <c r="H98" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5415,25 +5385,25 @@
       </c>
       <c r="B99" s="17" t="inlineStr">
         <is>
-          <t>TicketCreationModal</t>
+          <t>BulkOperationPortal</t>
         </is>
       </c>
       <c r="C99" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/TicketCreationModal.tsx</t>
-        </is>
-      </c>
-      <c r="D99" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>components/patterns/BulkOperationPortal.tsx</t>
+        </is>
+      </c>
+      <c r="D99" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E99" s="17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F99" s="17" t="inlineStr">
         <is>
-          <t>trouble-ticketing-complaints, customer360, support</t>
+          <t>enterprise-iot-b2b</t>
         </is>
       </c>
       <c r="G99" s="17" t="inlineStr"/>
@@ -5451,12 +5421,12 @@
       </c>
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>BulkOperationPortal</t>
+          <t>DualPlaySerialCheckStep</t>
         </is>
       </c>
       <c r="C100" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/BulkOperationPortal.tsx</t>
+          <t>components/patterns/DualPlaySerialCheckStep.tsx</t>
         </is>
       </c>
       <c r="D100" s="21" t="inlineStr">
@@ -5469,7 +5439,7 @@
       </c>
       <c r="F100" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b</t>
+          <t>fwa-5g-home</t>
         </is>
       </c>
       <c r="G100" s="17" t="inlineStr"/>
@@ -5487,12 +5457,12 @@
       </c>
       <c r="B101" s="17" t="inlineStr">
         <is>
-          <t>DualPlaySerialCheckStep</t>
+          <t>SimSwapFormStep</t>
         </is>
       </c>
       <c r="C101" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DualPlaySerialCheckStep.tsx</t>
+          <t>components/patterns/SimSwapFormStep.tsx</t>
         </is>
       </c>
       <c r="D101" s="21" t="inlineStr">
@@ -5505,7 +5475,7 @@
       </c>
       <c r="F101" s="17" t="inlineStr">
         <is>
-          <t>fwa-5g-home</t>
+          <t>sim-number-management</t>
         </is>
       </c>
       <c r="G101" s="17" t="inlineStr"/>
@@ -5523,12 +5493,12 @@
       </c>
       <c r="B102" s="17" t="inlineStr">
         <is>
-          <t>SimSwapFormStep</t>
+          <t>VerificationGate</t>
         </is>
       </c>
       <c r="C102" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/SimSwapFormStep.tsx</t>
+          <t>components/patterns/VerificationGate.tsx</t>
         </is>
       </c>
       <c r="D102" s="21" t="inlineStr">
@@ -5541,7 +5511,7 @@
       </c>
       <c r="F102" s="17" t="inlineStr">
         <is>
-          <t>sim-number-management</t>
+          <t>customer360</t>
         </is>
       </c>
       <c r="G102" s="17" t="inlineStr"/>
@@ -5554,30 +5524,30 @@
     <row r="103">
       <c r="A103" s="17" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>Wizard</t>
         </is>
       </c>
       <c r="B103" s="17" t="inlineStr">
         <is>
-          <t>VerificationGate</t>
+          <t>AbandonDialog</t>
         </is>
       </c>
       <c r="C103" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/VerificationGate.tsx</t>
-        </is>
-      </c>
-      <c r="D103" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>components/patterns/wizard/WizardDialogs.tsx</t>
+        </is>
+      </c>
+      <c r="D103" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E103" s="17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F103" s="17" t="inlineStr">
         <is>
-          <t>customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G103" s="17" t="inlineStr"/>
@@ -5595,12 +5565,12 @@
       </c>
       <c r="B104" s="17" t="inlineStr">
         <is>
-          <t>AbandonDialog</t>
+          <t>CustomerMirrorPanel</t>
         </is>
       </c>
       <c r="C104" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/WizardDialogs.tsx</t>
+          <t>components/patterns/wizard/CustomerMirrorPanel.tsx</t>
         </is>
       </c>
       <c r="D104" s="20" t="inlineStr">
@@ -5609,11 +5579,11 @@
         </is>
       </c>
       <c r="E104" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F104" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G104" s="17" t="inlineStr"/>
@@ -5631,12 +5601,12 @@
       </c>
       <c r="B105" s="17" t="inlineStr">
         <is>
-          <t>CustomerMirrorPanel</t>
+          <t>StepSummaryPanel</t>
         </is>
       </c>
       <c r="C105" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/CustomerMirrorPanel.tsx</t>
+          <t>components/patterns/wizard/StepSummaryPanel.tsx</t>
         </is>
       </c>
       <c r="D105" s="20" t="inlineStr">
@@ -5645,17 +5615,17 @@
         </is>
       </c>
       <c r="E105" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F105" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G105" s="17" t="inlineStr"/>
       <c r="H105" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5667,31 +5637,35 @@
       </c>
       <c r="B106" s="17" t="inlineStr">
         <is>
+          <t>StepSummarySection</t>
+        </is>
+      </c>
+      <c r="C106" s="17" t="inlineStr">
+        <is>
+          <t>components/patterns/wizard/StepSummarySection.tsx</t>
+        </is>
+      </c>
+      <c r="D106" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
+        </is>
+      </c>
+      <c r="E106" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="F106" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+      <c r="G106" s="17" t="inlineStr">
+        <is>
           <t>StepSummaryPanel</t>
         </is>
       </c>
-      <c r="C106" s="17" t="inlineStr">
-        <is>
-          <t>components/patterns/wizard/StepSummaryPanel.tsx</t>
-        </is>
-      </c>
-      <c r="D106" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
-        </is>
-      </c>
-      <c r="E106" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="F106" s="17" t="inlineStr">
-        <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management</t>
-        </is>
-      </c>
-      <c r="G106" s="17" t="inlineStr"/>
       <c r="H106" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5703,12 +5677,12 @@
       </c>
       <c r="B107" s="17" t="inlineStr">
         <is>
-          <t>StepSummarySection</t>
+          <t>SummaryFieldRow</t>
         </is>
       </c>
       <c r="C107" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/StepSummarySection.tsx</t>
+          <t>components/patterns/wizard/SummaryFieldRow.tsx</t>
         </is>
       </c>
       <c r="D107" s="20" t="inlineStr">
@@ -5717,11 +5691,11 @@
         </is>
       </c>
       <c r="E107" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F107" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G107" s="17" t="inlineStr">
@@ -5731,7 +5705,7 @@
       </c>
       <c r="H107" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5717,12 @@
       </c>
       <c r="B108" s="17" t="inlineStr">
         <is>
-          <t>SummaryFieldRow</t>
+          <t>WizardFooter</t>
         </is>
       </c>
       <c r="C108" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/SummaryFieldRow.tsx</t>
+          <t>components/patterns/wizard/WizardFooter.tsx</t>
         </is>
       </c>
       <c r="D108" s="20" t="inlineStr">
@@ -5757,21 +5731,17 @@
         </is>
       </c>
       <c r="E108" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F108" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management</t>
-        </is>
-      </c>
-      <c r="G108" s="17" t="inlineStr">
-        <is>
-          <t>StepSummaryPanel</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+      <c r="G108" s="17" t="inlineStr"/>
       <c r="H108" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5783,12 +5753,12 @@
       </c>
       <c r="B109" s="17" t="inlineStr">
         <is>
-          <t>WizardFooter</t>
+          <t>WizardStepHeader</t>
         </is>
       </c>
       <c r="C109" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/WizardFooter.tsx</t>
+          <t>components/patterns/wizard/WizardStepHeader.tsx</t>
         </is>
       </c>
       <c r="D109" s="20" t="inlineStr">
@@ -5797,11 +5767,11 @@
         </is>
       </c>
       <c r="E109" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F109" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G109" s="17" t="inlineStr"/>
@@ -5819,12 +5789,12 @@
       </c>
       <c r="B110" s="17" t="inlineStr">
         <is>
-          <t>WizardStepHeader</t>
+          <t>WizardTitleBand</t>
         </is>
       </c>
       <c r="C110" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/WizardStepHeader.tsx</t>
+          <t>components/patterns/wizard/WizardTitleBand.tsx</t>
         </is>
       </c>
       <c r="D110" s="20" t="inlineStr">
@@ -5833,58 +5803,22 @@
         </is>
       </c>
       <c r="E110" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F110" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G110" s="17" t="inlineStr"/>
       <c r="H110" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="17" t="inlineStr">
-        <is>
-          <t>Wizard</t>
-        </is>
-      </c>
-      <c r="B111" s="17" t="inlineStr">
-        <is>
-          <t>WizardTitleBand</t>
-        </is>
-      </c>
-      <c r="C111" s="17" t="inlineStr">
-        <is>
-          <t>components/patterns/wizard/WizardTitleBand.tsx</t>
-        </is>
-      </c>
-      <c r="D111" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
-        </is>
-      </c>
-      <c r="E111" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="F111" s="17" t="inlineStr">
-        <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management</t>
-        </is>
-      </c>
-      <c r="G111" s="17" t="inlineStr"/>
-      <c r="H111" s="17" t="inlineStr">
-        <is>
           <t>2026-10-18</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H111"/>
+  <autoFilter ref="A1:H110"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7269,7 +7203,7 @@
       </c>
       <c r="G36" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, ActivationCompleteScreen, configStore</t>
+          <t>MsisdnPicker, ActivationCompleteScreen, AppointmentBookingStep, configStore</t>
         </is>
       </c>
       <c r="H36" s="17" t="inlineStr">
@@ -7300,11 +7234,11 @@
         </is>
       </c>
       <c r="E37" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F37" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, navigation</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, navigation, administration</t>
         </is>
       </c>
       <c r="G37" s="17" t="inlineStr">
@@ -7854,12 +7788,12 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>connectionType</t>
+          <t>taskId</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>lib/connectionType.ts</t>
+          <t>lib/taskId.ts</t>
         </is>
       </c>
       <c r="D52" s="20" t="inlineStr">
@@ -7868,16 +7802,16 @@
         </is>
       </c>
       <c r="E52" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F52" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G52" s="17" t="inlineStr">
         <is>
-          <t>ConnectionTypeTag</t>
+          <t>useWizardDraftActions</t>
         </is>
       </c>
       <c r="H52" s="17" t="inlineStr">
@@ -7894,12 +7828,12 @@
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>taskId</t>
+          <t>connectionType</t>
         </is>
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>lib/taskId.ts</t>
+          <t>lib/connectionType.ts</t>
         </is>
       </c>
       <c r="D53" s="20" t="inlineStr">
@@ -7912,12 +7846,12 @@
       </c>
       <c r="F53" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration, customer360</t>
         </is>
       </c>
       <c r="G53" s="17" t="inlineStr">
         <is>
-          <t>useWizardDraftActions</t>
+          <t>ConnectionTypeTag</t>
         </is>
       </c>
       <c r="H53" s="17" t="inlineStr">

--- a/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
+++ b/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
@@ -14,8 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Method" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'UI Components'!$A$1:$H$110</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Shared Code'!$A$1:$H$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'UI Components'!$A$1:$H$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Shared Code'!$A$1:$H$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="C7" s="17" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D7" s="17" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E7" s="17" t="n">
         <v>4</v>
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="C9" s="17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D9" s="17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E9" s="17" t="n">
         <v>4</v>
@@ -855,14 +855,14 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>109 UI components + 54 non-UI files</t>
+          <t>110 UI components + 55 non-UI files</t>
         </is>
       </c>
       <c r="C13" s="18" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E13" s="18" t="n">
         <v>21</v>
@@ -887,11 +887,11 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>21 named - see the Capabilities sheet</t>
+          <t>22 named - see the Capabilities sheet</t>
         </is>
       </c>
       <c r="C15" s="17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D15" s="17" t="inlineStr"/>
       <c r="E15" s="17" t="inlineStr"/>
@@ -908,7 +908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.80" customWidth="1" min="1" max="1"/>
@@ -964,11 +964,11 @@
         </is>
       </c>
       <c r="D2" s="17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, profile, support, tasks</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, profile, support, tasks</t>
         </is>
       </c>
     </row>
@@ -1005,11 +1005,11 @@
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
     </row>
@@ -1031,41 +1031,44 @@
         </is>
       </c>
       <c r="D4" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
         <is>
-          <t>Number Selection</t>
+          <t>Cross-Sell Offers</t>
         </is>
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>Choose a number: search, Free and Star bands, price filter, plan entitlement note, reserve and clear.</t>
+          <t>Recommended offers for the identified customer: offer cards, details drawer, interested (lead) and select actions, and hand-off to the other journeys.</t>
         </is>
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>capabilities/NumberSelection/NumberSelection.tsx
-capabilities/NumberSelection/index.ts
-capabilities/NumberSelection/step.tsx
-capabilities/NumberSelection/summary.ts
-components/domain/MsisdnPicker.tsx
-components/domain/msisdnPickerModel.ts</t>
+          <t>capabilities/CrossSellOffers/CrossSalesStep.tsx
+capabilities/CrossSellOffers/HandOff.tsx
+capabilities/CrossSellOffers/JourneyActions.tsx
+capabilities/CrossSellOffers/OfferDetailsDrawer.tsx
+capabilities/CrossSellOffers/crossSalesModel.ts
+capabilities/CrossSellOffers/index.ts
+capabilities/CrossSellOffers/serviceJourneys.ts
+capabilities/CrossSellOffers/step.tsx
+capabilities/CrossSellOffers/summary.ts</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
         </is>
       </c>
     </row>
@@ -1092,26 +1095,56 @@
         </is>
       </c>
       <c r="D6" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="inlineStr">
         <is>
+          <t>Number Selection</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>Choose a number: search, Free and Star bands, price filter, plan entitlement note, reserve and clear.</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>capabilities/NumberSelection/NumberSelection.tsx
+capabilities/NumberSelection/index.ts
+capabilities/NumberSelection/step.tsx
+capabilities/NumberSelection/summary.ts
+components/domain/MsisdnPicker.tsx
+components/domain/msisdnPickerModel.ts</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
           <t>Billing Account</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Set up what an order bills to: one layout everywhere - the customer's existing billing accounts, or Create New Billing Account (contact, billing address, payment, card on file, primary payment profile, billing profile setup).</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>capabilities/BillingAccount/BillingAccount.tsx
 capabilities/BillingAccount/index.ts
@@ -1124,41 +1157,12 @@
 components/patterns/billingAccountModel.ts</t>
         </is>
       </c>
-      <c r="D7" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="17" t="inlineStr">
-        <is>
-          <t>Service Address</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>The address a service is activated at: one layout everywhere: Service Information (Kahramaa Meter ID / Vodafone Premise ID with Search), then Zone / Street / Building, then Additional Details, with Qatari-ID prefill.</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>capabilities/ServiceAddress/ServiceAddress.tsx
-capabilities/ServiceAddress/index.ts
-capabilities/ServiceAddress/step.tsx
-capabilities/ServiceAddress/summary.ts
-components/patterns/ZsbAddressStep.tsx</t>
-        </is>
-      </c>
       <c r="D8" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1174,7 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>Choose the plan: postpaid plan cards then Add-ons (discounts, bill limit), prepaid packs then Add-ons, or the fixed-line / fibre plan cards with the credit check.</t>
+          <t>Choose the plan: postpaid plan cards then Add-ons (discounts, bill limit), prepaid packs then Add-ons, or the fixed-line / fibre plan cards with the credit check. The line's current plan or pack can be left out of the choices when a journey changes it.</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
@@ -1188,11 +1192,11 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
@@ -1219,11 +1223,11 @@
         </is>
       </c>
       <c r="D10" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
@@ -1258,11 +1262,11 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
@@ -1286,11 +1290,11 @@
         </is>
       </c>
       <c r="D12" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
@@ -1315,11 +1319,11 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
@@ -1343,11 +1347,11 @@
         </is>
       </c>
       <c r="D14" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
@@ -1359,21 +1363,22 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>Add-on cards with included-benefit handling.</t>
+          <t>Add-on rows for a plan or prepaid pack, with included-benefit handling; on its own (Add Add-On) as a step that needs at least one add-on.</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
           <t>capabilities/AddonsSelection/AddonsPicker.tsx
-capabilities/AddonsSelection/index.ts</t>
+capabilities/AddonsSelection/index.ts
+capabilities/AddonsSelection/step.tsx</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E15" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
@@ -1397,11 +1402,11 @@
         </is>
       </c>
       <c r="D16" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
@@ -1427,36 +1432,32 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="17" t="inlineStr">
         <is>
-          <t>Cross-Sell Offers</t>
+          <t>Service Address</t>
         </is>
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>Recommended offers for the identified customer: offer cards, details drawer, interested (lead) and select actions, and hand-off to the other journeys.</t>
+          <t>The address a service is activated at: one layout everywhere: Service Information (Kahramaa Meter ID / Vodafone Premise ID with Search), then Zone / Street / Building, then Additional Details, with Qatari-ID prefill.</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>capabilities/CrossSellOffers/CrossSalesStep.tsx
-capabilities/CrossSellOffers/HandOff.tsx
-capabilities/CrossSellOffers/JourneyActions.tsx
-capabilities/CrossSellOffers/OfferDetailsDrawer.tsx
-capabilities/CrossSellOffers/crossSalesModel.ts
-capabilities/CrossSellOffers/index.ts
-capabilities/CrossSellOffers/serviceJourneys.ts
-capabilities/CrossSellOffers/step.tsx
-capabilities/CrossSellOffers/summary.ts</t>
+          <t>capabilities/ServiceAddress/ServiceAddress.tsx
+capabilities/ServiceAddress/index.ts
+capabilities/ServiceAddress/step.tsx
+capabilities/ServiceAddress/summary.ts
+components/patterns/ZsbAddressStep.tsx</t>
         </is>
       </c>
       <c r="D18" s="17" t="n">
@@ -1528,48 +1529,77 @@
     <row r="21">
       <c r="A21" s="17" t="inlineStr">
         <is>
-          <t>Selectable card styling</t>
+          <t>Line Selection</t>
         </is>
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>One selected / idle / highlighted surface for plans, offers, numbers, add-ons, discounts and ID/customer type.</t>
+          <t>Choose which of the identified customer's existing mobile lines an order changes (Change Postpaid Plan, Change Prepaid Pack, Add Add-On): postpaid and / or prepaid lines with their current plan and price; a line that is not active, is barred or whose billing profile is in collections is shown with its reason and cannot be chosen.</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>capabilities/SelectableCard/index.ts</t>
+          <t>capabilities/LineSelection/LineSelection.tsx
+capabilities/LineSelection/index.ts
+capabilities/LineSelection/step.tsx
+components/patterns/LineSelectionStep.tsx
+components/patterns/lineSelectionModel.ts</t>
         </is>
       </c>
       <c r="D21" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E21" s="17" t="inlineStr">
         <is>
-          <t>administration</t>
+          <t>mobile-service-changes, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="17" t="inlineStr">
         <is>
-          <t>Side drawer</t>
+          <t>Selectable card styling</t>
         </is>
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>Fixed 50%-width drawer for forms, details and multi-step flows: the title as a small uppercase label beside the close control, the body on the page tint, and a footer whose buttons share its width equally.</t>
+          <t>One selected / idle / highlighted surface for plans, offers, numbers, add-ons, discounts and ID/customer type.</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>capabilities/SideDrawer/index.ts</t>
+          <t>capabilities/SelectableCard/index.ts</t>
         </is>
       </c>
       <c r="D22" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>administration</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>Side drawer</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>Fixed 50%-width drawer for forms, details and multi-step flows: the title as a small uppercase label beside the close control, the body on the page tint, and a footer whose buttons share its width equally.</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>capabilities/SideDrawer/index.ts</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>administration</t>
         </is>
@@ -1586,7 +1616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H110"/>
+  <dimension ref="A1:H111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.85" customWidth="1" min="1" max="1"/>
@@ -1663,16 +1693,16 @@
         </is>
       </c>
       <c r="E2" s="17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2" s="17" t="inlineStr">
         <is>
-          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
+          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G2" s="17" t="inlineStr">
         <is>
-          <t>CreditCheckPanel, MsisdnPicker, SimTypeStep, ActivationCompleteScreen, AppointmentBookingStep, BillingAccountStep, BulkOperationPortal, CafSignatureCapture, DonorAttachmentStep, IdLookupStep, PrepaidCartStep, PrepaidCheckoutStep, SimSwapFormStep, TicketCreationModal, WinCashPaymentStep, ConnectionTypeTag, Tooltip</t>
+          <t>CreditCheckPanel, MsisdnPicker, SimTypeStep, ActivationCompleteScreen, AppointmentBookingStep, BillingAccountStep, BulkOperationPortal, CafSignatureCapture, DonorAttachmentStep, IdLookupStep, LineSelectionStep, PrepaidCartStep, PrepaidCheckoutStep, SimSwapFormStep, TicketCreationModal, WinCashPaymentStep, ConnectionTypeTag, Tooltip</t>
         </is>
       </c>
       <c r="H2" s="17" t="inlineStr">
@@ -1703,11 +1733,11 @@
         </is>
       </c>
       <c r="E3" s="17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F3" s="17" t="inlineStr">
         <is>
-          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
+          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G3" s="17" t="inlineStr">
@@ -1743,11 +1773,11 @@
         </is>
       </c>
       <c r="E4" s="17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4" s="17" t="inlineStr">
         <is>
-          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, sales, support, tasks</t>
+          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, sales, support, tasks</t>
         </is>
       </c>
       <c r="G4" s="17" t="inlineStr">
@@ -1783,11 +1813,11 @@
         </is>
       </c>
       <c r="E5" s="17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, profile, support, tasks</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, profile, support, tasks</t>
         </is>
       </c>
       <c r="G5" s="17" t="inlineStr">
@@ -1823,11 +1853,11 @@
         </is>
       </c>
       <c r="E6" s="17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, profile, support</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, profile, support</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
@@ -1863,11 +1893,11 @@
         </is>
       </c>
       <c r="E7" s="17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, support</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, support</t>
         </is>
       </c>
       <c r="G7" s="17" t="inlineStr">
@@ -1903,11 +1933,11 @@
         </is>
       </c>
       <c r="E8" s="17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, support</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, support</t>
         </is>
       </c>
       <c r="G8" s="17" t="inlineStr">
@@ -1943,11 +1973,11 @@
         </is>
       </c>
       <c r="E9" s="17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, support</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, support</t>
         </is>
       </c>
       <c r="G9" s="17" t="inlineStr">
@@ -1983,11 +2013,11 @@
         </is>
       </c>
       <c r="E10" s="17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, support</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, support</t>
         </is>
       </c>
       <c r="G10" s="17" t="inlineStr">
@@ -2023,11 +2053,11 @@
         </is>
       </c>
       <c r="E11" s="17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, support</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, support</t>
         </is>
       </c>
       <c r="G11" s="17" t="inlineStr">
@@ -2063,11 +2093,11 @@
         </is>
       </c>
       <c r="E12" s="17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, support</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, support</t>
         </is>
       </c>
       <c r="G12" s="17" t="inlineStr">
@@ -2089,12 +2119,12 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>DataTable</t>
+          <t>TabStrip</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/DataTable.tsx</t>
+          <t>components/primitives/TabStrip.tsx</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -2103,21 +2133,21 @@
         </is>
       </c>
       <c r="E13" s="17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, lead-management, mnp-fnp-porting, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, customer360, orders, sales, support, tasks, tickets</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, trouble-ticketing-complaints, administration, customer360, orders, support</t>
         </is>
       </c>
       <c r="G13" s="17" t="inlineStr">
         <is>
-          <t>BulkOperationPortal</t>
+          <t>PlanTabStrip, Tabs</t>
         </is>
       </c>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2129,12 +2159,12 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>Pager</t>
+          <t>DataTable</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/Pager.tsx</t>
+          <t>components/primitives/DataTable.tsx</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -2152,7 +2182,7 @@
       </c>
       <c r="G14" s="17" t="inlineStr">
         <is>
-          <t>DataTable</t>
+          <t>BulkOperationPortal</t>
         </is>
       </c>
       <c r="H14" s="17" t="inlineStr">
@@ -2169,12 +2199,12 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>TabStrip</t>
+          <t>Pager</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/TabStrip.tsx</t>
+          <t>components/primitives/Pager.tsx</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -2187,17 +2217,17 @@
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, trouble-ticketing-complaints, administration, customer360, orders, support</t>
+          <t>enterprise-iot-b2b, lead-management, mnp-fnp-porting, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, customer360, orders, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G15" s="17" t="inlineStr">
         <is>
-          <t>PlanTabStrip, Tabs</t>
+          <t>DataTable</t>
         </is>
       </c>
       <c r="H15" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2239,12 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>ErrorBanner</t>
+          <t>CARD_SELECTED</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/ErrorBanner.tsx</t>
+          <t>components/primitives/offerCardParts.tsx</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -2227,17 +2257,17 @@
       </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
-          <t>lead-management, mnp-fnp-porting, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, customer360, orders, sales, support, tasks, tickets</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G16" s="17" t="inlineStr">
         <is>
-          <t>VerificationGate</t>
+          <t>MsisdnPicker, QidInput, AppointmentBookingStep, BillingAccountStep, DiscountCard, FixedPlanStep, LineSelectionStep, PostpaidPlanCard, PrepaidPlanCard, PrepaidPlanStep, ChoiceCards</t>
         </is>
       </c>
       <c r="H16" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2249,12 +2279,12 @@
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>CARD_SELECTED</t>
+          <t>CountryMarker</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/offerCardParts.tsx</t>
+          <t>components/primitives/CountryMarker.tsx</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -2263,21 +2293,21 @@
         </is>
       </c>
       <c r="E17" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F17" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G17" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, QidInput, AppointmentBookingStep, BillingAccountStep, DiscountCard, FixedPlanStep, PostpaidPlanCard, PrepaidPlanCard, PrepaidPlanStep, ChoiceCards</t>
+          <t>PhoneNumberInput</t>
         </is>
       </c>
       <c r="H17" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2289,12 +2319,12 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>CountryMarker</t>
+          <t>Drawer</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/CountryMarker.tsx</t>
+          <t>components/primitives/Drawer.tsx</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -2303,21 +2333,21 @@
         </is>
       </c>
       <c r="E18" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, trouble-ticketing-complaints, administration, customer360, support</t>
         </is>
       </c>
       <c r="G18" s="17" t="inlineStr">
         <is>
-          <t>PhoneNumberInput</t>
+          <t>EligibilityRows, BillingProfileSetupDrawer, PrepaidPackDetailsDrawer, TicketCreationModal, VerificationGate</t>
         </is>
       </c>
       <c r="H18" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2329,12 +2359,12 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>Drawer</t>
+          <t>ErrorBanner</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/Drawer.tsx</t>
+          <t>components/primitives/ErrorBanner.tsx</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -2343,16 +2373,16 @@
         </is>
       </c>
       <c r="E19" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F19" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, trouble-ticketing-complaints, administration, customer360, support</t>
+          <t>lead-management, mnp-fnp-porting, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, customer360, orders, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G19" s="17" t="inlineStr">
         <is>
-          <t>EligibilityRows, BillingProfileSetupDrawer, PrepaidPackDetailsDrawer, TicketCreationModal, VerificationGate</t>
+          <t>VerificationGate</t>
         </is>
       </c>
       <c r="H19" s="17" t="inlineStr">
@@ -2383,11 +2413,11 @@
         </is>
       </c>
       <c r="E20" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F20" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, navigation, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration</t>
         </is>
       </c>
       <c r="G20" s="17" t="inlineStr">
@@ -2423,11 +2453,11 @@
         </is>
       </c>
       <c r="E21" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F21" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G21" s="17" t="inlineStr">
@@ -2449,12 +2479,12 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>SegmentedTabs</t>
+          <t>Spinner</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/SegmentedTabs.tsx</t>
+          <t>components/primitives/Spinner.tsx</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -2463,21 +2493,21 @@
         </is>
       </c>
       <c r="E22" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F22" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration, customer360, tickets</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker</t>
+          <t>PassportScanSections, QidImageUpload, ValidationStatus</t>
         </is>
       </c>
       <c r="H22" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2489,12 +2519,12 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>Spinner</t>
+          <t>SegmentedTabs</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/Spinner.tsx</t>
+          <t>components/primitives/SegmentedTabs.tsx</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -2507,17 +2537,17 @@
       </c>
       <c r="F23" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration, customer360, tickets</t>
         </is>
       </c>
       <c r="G23" s="17" t="inlineStr">
         <is>
-          <t>PassportScanSections, QidImageUpload, ValidationStatus</t>
+          <t>MsisdnPicker</t>
         </is>
       </c>
       <c r="H23" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2543,11 +2573,11 @@
         </is>
       </c>
       <c r="E24" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G24" s="17" t="inlineStr">
@@ -2583,11 +2613,11 @@
         </is>
       </c>
       <c r="E25" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F25" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
         </is>
       </c>
       <c r="G25" s="17" t="inlineStr">
@@ -2623,11 +2653,11 @@
         </is>
       </c>
       <c r="E26" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
         </is>
       </c>
       <c r="G26" s="17" t="inlineStr">
@@ -2947,11 +2977,11 @@
         </is>
       </c>
       <c r="E35" s="17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F35" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G35" s="17" t="inlineStr">
@@ -2987,11 +3017,11 @@
         </is>
       </c>
       <c r="E36" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F36" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G36" s="17" t="inlineStr">
@@ -3027,11 +3057,11 @@
         </is>
       </c>
       <c r="E37" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F37" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G37" s="17" t="inlineStr">
@@ -3067,11 +3097,11 @@
         </is>
       </c>
       <c r="E38" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F38" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G38" s="17" t="inlineStr">
@@ -3093,12 +3123,12 @@
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker</t>
+          <t>SimSerialScanner</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>components/domain/MsisdnPicker.tsx</t>
+          <t>components/domain/SimSerialScanner.tsx</t>
         </is>
       </c>
       <c r="D39" s="20" t="inlineStr">
@@ -3107,17 +3137,21 @@
         </is>
       </c>
       <c r="E39" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F39" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
-        </is>
-      </c>
-      <c r="G39" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+      <c r="G39" s="17" t="inlineStr">
+        <is>
+          <t>SimTypeStep</t>
+        </is>
+      </c>
       <c r="H39" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3129,12 +3163,12 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>SimSerialScanner</t>
+          <t>AdditionalDocumentsUpload</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>components/domain/SimSerialScanner.tsx</t>
+          <t>components/domain/AdditionalDocumentsUpload.tsx</t>
         </is>
       </c>
       <c r="D40" s="20" t="inlineStr">
@@ -3147,12 +3181,12 @@
       </c>
       <c r="F40" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G40" s="17" t="inlineStr">
         <is>
-          <t>SimTypeStep</t>
+          <t>CafSignatureCapture</t>
         </is>
       </c>
       <c r="H40" s="17" t="inlineStr">
@@ -3169,12 +3203,12 @@
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>StarStat</t>
+          <t>BillLimitEditor</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>components/domain/StarStat.tsx</t>
+          <t>components/domain/BillLimitEditor.tsx</t>
         </is>
       </c>
       <c r="D41" s="20" t="inlineStr">
@@ -3187,12 +3221,12 @@
       </c>
       <c r="F41" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G41" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker</t>
+          <t>PostpaidAddonsPanel, PostpaidPlanAddonsStep</t>
         </is>
       </c>
       <c r="H41" s="17" t="inlineStr">
@@ -3209,12 +3243,12 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>AdditionalDocumentsUpload</t>
+          <t>CafDocumentUpload</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>components/domain/AdditionalDocumentsUpload.tsx</t>
+          <t>components/domain/CafDocumentUpload.tsx</t>
         </is>
       </c>
       <c r="D42" s="20" t="inlineStr">
@@ -3223,11 +3257,11 @@
         </is>
       </c>
       <c r="E42" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F42" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G42" s="17" t="inlineStr">
@@ -3249,12 +3283,12 @@
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>BillLimitEditor</t>
+          <t>CompanySearchInput</t>
         </is>
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>components/domain/BillLimitEditor.tsx</t>
+          <t>components/domain/CompanySearchInput.tsx</t>
         </is>
       </c>
       <c r="D43" s="20" t="inlineStr">
@@ -3263,18 +3297,14 @@
         </is>
       </c>
       <c r="E43" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F43" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G43" s="17" t="inlineStr">
-        <is>
-          <t>PostpaidAddonsPanel, PostpaidPlanAddonsStep</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G43" s="17" t="inlineStr"/>
       <c r="H43" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
@@ -3289,12 +3319,12 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>CafDocumentUpload</t>
+          <t>CreditCheckPanel</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>components/domain/CafDocumentUpload.tsx</t>
+          <t>components/domain/CreditCheckPanel.tsx</t>
         </is>
       </c>
       <c r="D44" s="20" t="inlineStr">
@@ -3303,16 +3333,16 @@
         </is>
       </c>
       <c r="E44" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F44" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G44" s="17" t="inlineStr">
         <is>
-          <t>CafSignatureCapture</t>
+          <t>FixedPlanStep</t>
         </is>
       </c>
       <c r="H44" s="17" t="inlineStr">
@@ -3329,12 +3359,12 @@
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>CompanySearchInput</t>
+          <t>EligibilityChecksList</t>
         </is>
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>components/domain/CompanySearchInput.tsx</t>
+          <t>components/domain/EligibilityRows.tsx</t>
         </is>
       </c>
       <c r="D45" s="20" t="inlineStr">
@@ -3343,11 +3373,11 @@
         </is>
       </c>
       <c r="E45" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F45" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G45" s="17" t="inlineStr"/>
@@ -3365,12 +3395,12 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>CreditCheckPanel</t>
+          <t>EsimActivationPanel</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>components/domain/CreditCheckPanel.tsx</t>
+          <t>components/domain/EsimActivationPanel.tsx</t>
         </is>
       </c>
       <c r="D46" s="20" t="inlineStr">
@@ -3379,21 +3409,21 @@
         </is>
       </c>
       <c r="E46" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F46" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G46" s="17" t="inlineStr">
         <is>
-          <t>FixedPlanStep</t>
+          <t>ActivationCompleteScreen</t>
         </is>
       </c>
       <c r="H46" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3405,12 +3435,12 @@
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>EligibilityChecksList</t>
+          <t>MsisdnPicker</t>
         </is>
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>components/domain/EligibilityRows.tsx</t>
+          <t>components/domain/MsisdnPicker.tsx</t>
         </is>
       </c>
       <c r="D47" s="20" t="inlineStr">
@@ -3419,17 +3449,17 @@
         </is>
       </c>
       <c r="E47" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F47" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G47" s="17" t="inlineStr"/>
       <c r="H47" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3441,12 +3471,12 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>EsimActivationPanel</t>
+          <t>SimTypeStep</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>components/domain/EsimActivationPanel.tsx</t>
+          <t>components/domain/SimTypeStep.tsx</t>
         </is>
       </c>
       <c r="D48" s="20" t="inlineStr">
@@ -3455,16 +3485,16 @@
         </is>
       </c>
       <c r="E48" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F48" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G48" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen</t>
+          <t>CheckoutSummaryStep, checkoutDetailedTables, checkoutSummaryRows, prepaidCartModel, useCheckoutSummary</t>
         </is>
       </c>
       <c r="H48" s="17" t="inlineStr">
@@ -3481,12 +3511,12 @@
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>FibreReadinessBanner</t>
+          <t>StarStat</t>
         </is>
       </c>
       <c r="C49" s="17" t="inlineStr">
         <is>
-          <t>components/domain/FibreReadinessBanner.tsx</t>
+          <t>components/domain/StarStat.tsx</t>
         </is>
       </c>
       <c r="D49" s="20" t="inlineStr">
@@ -3495,21 +3525,21 @@
         </is>
       </c>
       <c r="E49" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F49" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G49" s="17" t="inlineStr">
         <is>
-          <t>ZsbAddressStep</t>
+          <t>MsisdnPicker</t>
         </is>
       </c>
       <c r="H49" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3521,12 +3551,12 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>SimTypeStep</t>
+          <t>SupportingDocumentUpload</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>components/domain/SimTypeStep.tsx</t>
+          <t>components/domain/SupportingDocumentUpload.tsx</t>
         </is>
       </c>
       <c r="D50" s="20" t="inlineStr">
@@ -3535,21 +3565,17 @@
         </is>
       </c>
       <c r="E50" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F50" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G50" s="17" t="inlineStr">
-        <is>
-          <t>CheckoutSummaryStep, checkoutDetailedTables, checkoutSummaryRows, prepaidCartModel, useCheckoutSummary</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G50" s="17" t="inlineStr"/>
       <c r="H50" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3561,12 +3587,12 @@
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>SupportingDocumentUpload</t>
+          <t>FibreReadinessBanner</t>
         </is>
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>components/domain/SupportingDocumentUpload.tsx</t>
+          <t>components/domain/FibreReadinessBanner.tsx</t>
         </is>
       </c>
       <c r="D51" s="20" t="inlineStr">
@@ -3582,7 +3608,11 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G51" s="17" t="inlineStr"/>
+      <c r="G51" s="17" t="inlineStr">
+        <is>
+          <t>ZsbAddressStep</t>
+        </is>
+      </c>
       <c r="H51" s="17" t="inlineStr">
         <is>
           <t>2026-10-15</t>
@@ -3759,17 +3789,17 @@
         </is>
       </c>
       <c r="E56" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F56" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G56" s="17" t="inlineStr"/>
       <c r="H56" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3795,11 +3825,11 @@
         </is>
       </c>
       <c r="E57" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F57" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G57" s="17" t="inlineStr">
@@ -3835,11 +3865,11 @@
         </is>
       </c>
       <c r="E58" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F58" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G58" s="17" t="inlineStr">
@@ -3875,11 +3905,11 @@
         </is>
       </c>
       <c r="E59" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F59" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G59" s="17" t="inlineStr">
@@ -3915,11 +3945,11 @@
         </is>
       </c>
       <c r="E60" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F60" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G60" s="17" t="inlineStr">
@@ -3955,11 +3985,11 @@
         </is>
       </c>
       <c r="E61" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F61" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G61" s="17" t="inlineStr">
@@ -3995,11 +4025,11 @@
         </is>
       </c>
       <c r="E62" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F62" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G62" s="17" t="inlineStr">
@@ -4035,11 +4065,11 @@
         </is>
       </c>
       <c r="E63" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F63" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G63" s="17" t="inlineStr"/>
@@ -4071,11 +4101,11 @@
         </is>
       </c>
       <c r="E64" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G64" s="17" t="inlineStr"/>
@@ -4093,12 +4123,12 @@
       </c>
       <c r="B65" s="17" t="inlineStr">
         <is>
-          <t>BillingAccountStep</t>
+          <t>CafSignatureCapture</t>
         </is>
       </c>
       <c r="C65" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/BillingAccountStep.tsx</t>
+          <t>components/patterns/CafSignatureCapture.tsx</t>
         </is>
       </c>
       <c r="D65" s="20" t="inlineStr">
@@ -4107,11 +4137,11 @@
         </is>
       </c>
       <c r="E65" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F65" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G65" s="17" t="inlineStr"/>
@@ -4129,12 +4159,12 @@
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>BillingProfileSetupDrawer</t>
+          <t>CheckoutDefaultLayout</t>
         </is>
       </c>
       <c r="C66" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/BillingProfileSetupDrawer.tsx</t>
+          <t>components/patterns/CheckoutDefaultLayout.tsx</t>
         </is>
       </c>
       <c r="D66" s="20" t="inlineStr">
@@ -4143,21 +4173,21 @@
         </is>
       </c>
       <c r="E66" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F66" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G66" s="17" t="inlineStr">
         <is>
-          <t>BillingAccountStep</t>
+          <t>CheckoutSummaryStep</t>
         </is>
       </c>
       <c r="H66" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4199,12 @@
       </c>
       <c r="B67" s="17" t="inlineStr">
         <is>
-          <t>CafSignatureCapture</t>
+          <t>CheckoutSummaryStep</t>
         </is>
       </c>
       <c r="C67" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CafSignatureCapture.tsx</t>
+          <t>components/patterns/CheckoutSummaryStep.tsx</t>
         </is>
       </c>
       <c r="D67" s="20" t="inlineStr">
@@ -4183,17 +4213,17 @@
         </is>
       </c>
       <c r="E67" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F67" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G67" s="17" t="inlineStr"/>
       <c r="H67" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4205,12 +4235,12 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>CheckoutDefaultLayout</t>
+          <t>DiscountCard</t>
         </is>
       </c>
       <c r="C68" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CheckoutDefaultLayout.tsx</t>
+          <t>components/patterns/DiscountCard.tsx</t>
         </is>
       </c>
       <c r="D68" s="20" t="inlineStr">
@@ -4219,21 +4249,21 @@
         </is>
       </c>
       <c r="E68" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F68" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G68" s="17" t="inlineStr">
         <is>
-          <t>CheckoutSummaryStep</t>
+          <t>PostpaidDiscountsPanel</t>
         </is>
       </c>
       <c r="H68" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4245,12 +4275,12 @@
       </c>
       <c r="B69" s="17" t="inlineStr">
         <is>
-          <t>CheckoutSummaryStep</t>
+          <t>FixedPlanStep</t>
         </is>
       </c>
       <c r="C69" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CheckoutSummaryStep.tsx</t>
+          <t>components/patterns/FixedPlanStep.tsx</t>
         </is>
       </c>
       <c r="D69" s="20" t="inlineStr">
@@ -4259,17 +4289,17 @@
         </is>
       </c>
       <c r="E69" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F69" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G69" s="17" t="inlineStr"/>
       <c r="H69" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4311,12 @@
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>DiscountCard</t>
+          <t>FullTerms</t>
         </is>
       </c>
       <c r="C70" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DiscountCard.tsx</t>
+          <t>components/patterns/CafTerms.tsx</t>
         </is>
       </c>
       <c r="D70" s="20" t="inlineStr">
@@ -4295,16 +4325,16 @@
         </is>
       </c>
       <c r="E70" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F70" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G70" s="17" t="inlineStr">
         <is>
-          <t>PostpaidDiscountsPanel</t>
+          <t>CafSignatureCapture</t>
         </is>
       </c>
       <c r="H70" s="17" t="inlineStr">
@@ -4321,12 +4351,12 @@
       </c>
       <c r="B71" s="17" t="inlineStr">
         <is>
-          <t>FixedPlanStep</t>
+          <t>KeyInformationPanel</t>
         </is>
       </c>
       <c r="C71" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/FixedPlanStep.tsx</t>
+          <t>components/patterns/KeyInformationPanel.tsx</t>
         </is>
       </c>
       <c r="D71" s="20" t="inlineStr">
@@ -4335,17 +4365,17 @@
         </is>
       </c>
       <c r="E71" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F71" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G71" s="17" t="inlineStr"/>
       <c r="H71" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4357,12 +4387,12 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>FullTerms</t>
+          <t>OrderConfirmationScreen</t>
         </is>
       </c>
       <c r="C72" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CafTerms.tsx</t>
+          <t>components/patterns/OrderConfirmationScreen.tsx</t>
         </is>
       </c>
       <c r="D72" s="20" t="inlineStr">
@@ -4371,21 +4401,21 @@
         </is>
       </c>
       <c r="E72" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F72" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G72" s="17" t="inlineStr">
         <is>
-          <t>CafSignatureCapture</t>
+          <t>ActivationCompleteScreen</t>
         </is>
       </c>
       <c r="H72" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4427,12 @@
       </c>
       <c r="B73" s="17" t="inlineStr">
         <is>
-          <t>KeyInformationPanel</t>
+          <t>PlanDetailsDrawer</t>
         </is>
       </c>
       <c r="C73" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/KeyInformationPanel.tsx</t>
+          <t>components/patterns/PlanDetailsDrawer.tsx</t>
         </is>
       </c>
       <c r="D73" s="20" t="inlineStr">
@@ -4411,14 +4441,18 @@
         </is>
       </c>
       <c r="E73" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G73" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G73" s="17" t="inlineStr">
+        <is>
+          <t>PostpaidPlanAddonsStep</t>
+        </is>
+      </c>
       <c r="H73" s="17" t="inlineStr">
         <is>
           <t>2026-10-15</t>
@@ -4433,12 +4467,12 @@
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>OrderConfirmationScreen</t>
+          <t>PlanGroupPanel</t>
         </is>
       </c>
       <c r="C74" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/OrderConfirmationScreen.tsx</t>
+          <t>components/patterns/PlanGroupPanel.tsx</t>
         </is>
       </c>
       <c r="D74" s="20" t="inlineStr">
@@ -4447,21 +4481,21 @@
         </is>
       </c>
       <c r="E74" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F74" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G74" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen</t>
+          <t>PostpaidPlanAddonsStep</t>
         </is>
       </c>
       <c r="H74" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4473,12 +4507,12 @@
       </c>
       <c r="B75" s="17" t="inlineStr">
         <is>
-          <t>PlanDetailsDrawer</t>
+          <t>PlanSearchBox</t>
         </is>
       </c>
       <c r="C75" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PlanDetailsDrawer.tsx</t>
+          <t>components/patterns/PlanSearchBox.tsx</t>
         </is>
       </c>
       <c r="D75" s="20" t="inlineStr">
@@ -4487,11 +4521,11 @@
         </is>
       </c>
       <c r="E75" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F75" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G75" s="17" t="inlineStr">
@@ -4513,12 +4547,12 @@
       </c>
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>PlanGroupPanel</t>
+          <t>PlanTabStrip</t>
         </is>
       </c>
       <c r="C76" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PlanGroupPanel.tsx</t>
+          <t>components/patterns/PlanTabStrip.tsx</t>
         </is>
       </c>
       <c r="D76" s="20" t="inlineStr">
@@ -4527,11 +4561,11 @@
         </is>
       </c>
       <c r="E76" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F76" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G76" s="17" t="inlineStr">
@@ -4541,7 +4575,7 @@
       </c>
       <c r="H76" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4553,12 +4587,12 @@
       </c>
       <c r="B77" s="17" t="inlineStr">
         <is>
-          <t>PlanSearchBox</t>
+          <t>PostpaidAddonsPanel</t>
         </is>
       </c>
       <c r="C77" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PlanSearchBox.tsx</t>
+          <t>components/patterns/PostpaidAddonsPanel.tsx</t>
         </is>
       </c>
       <c r="D77" s="20" t="inlineStr">
@@ -4567,11 +4601,11 @@
         </is>
       </c>
       <c r="E77" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F77" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G77" s="17" t="inlineStr">
@@ -4581,7 +4615,7 @@
       </c>
       <c r="H77" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4627,12 @@
       </c>
       <c r="B78" s="17" t="inlineStr">
         <is>
-          <t>PlanTabStrip</t>
+          <t>PostpaidDiscountsPanel</t>
         </is>
       </c>
       <c r="C78" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PlanTabStrip.tsx</t>
+          <t>components/patterns/PostpaidDiscountsPanel.tsx</t>
         </is>
       </c>
       <c r="D78" s="20" t="inlineStr">
@@ -4607,11 +4641,11 @@
         </is>
       </c>
       <c r="E78" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F78" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G78" s="17" t="inlineStr">
@@ -4621,7 +4655,7 @@
       </c>
       <c r="H78" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4633,12 +4667,12 @@
       </c>
       <c r="B79" s="17" t="inlineStr">
         <is>
-          <t>PostpaidAddonsPanel</t>
+          <t>PostpaidMonthlySummary</t>
         </is>
       </c>
       <c r="C79" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidAddonsPanel.tsx</t>
+          <t>components/patterns/PostpaidMonthlySummary.tsx</t>
         </is>
       </c>
       <c r="D79" s="20" t="inlineStr">
@@ -4647,11 +4681,11 @@
         </is>
       </c>
       <c r="E79" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F79" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G79" s="17" t="inlineStr">
@@ -4673,12 +4707,12 @@
       </c>
       <c r="B80" s="17" t="inlineStr">
         <is>
-          <t>PostpaidDiscountsPanel</t>
+          <t>PostpaidPlanAddonsStep</t>
         </is>
       </c>
       <c r="C80" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidDiscountsPanel.tsx</t>
+          <t>components/patterns/PostpaidPlanAddonsStep.tsx</t>
         </is>
       </c>
       <c r="D80" s="20" t="inlineStr">
@@ -4687,21 +4721,17 @@
         </is>
       </c>
       <c r="E80" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F80" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G80" s="17" t="inlineStr">
-        <is>
-          <t>PostpaidPlanAddonsStep</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G80" s="17" t="inlineStr"/>
       <c r="H80" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4743,12 @@
       </c>
       <c r="B81" s="17" t="inlineStr">
         <is>
-          <t>PostpaidMonthlySummary</t>
+          <t>PostpaidPlanCard</t>
         </is>
       </c>
       <c r="C81" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidMonthlySummary.tsx</t>
+          <t>components/patterns/PostpaidPlanCard.tsx</t>
         </is>
       </c>
       <c r="D81" s="20" t="inlineStr">
@@ -4727,16 +4757,16 @@
         </is>
       </c>
       <c r="E81" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F81" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G81" s="17" t="inlineStr">
         <is>
-          <t>PostpaidPlanAddonsStep</t>
+          <t>PlanGroupPanel</t>
         </is>
       </c>
       <c r="H81" s="17" t="inlineStr">
@@ -4753,12 +4783,12 @@
       </c>
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>PostpaidPlanAddonsStep</t>
+          <t>PrepaidCartStep</t>
         </is>
       </c>
       <c r="C82" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidPlanAddonsStep.tsx</t>
+          <t>components/patterns/PrepaidCartStep.tsx</t>
         </is>
       </c>
       <c r="D82" s="20" t="inlineStr">
@@ -4767,17 +4797,17 @@
         </is>
       </c>
       <c r="E82" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F82" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G82" s="17" t="inlineStr"/>
       <c r="H82" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4789,12 +4819,12 @@
       </c>
       <c r="B83" s="17" t="inlineStr">
         <is>
-          <t>PostpaidPlanCard</t>
+          <t>PrepaidCheckoutStep</t>
         </is>
       </c>
       <c r="C83" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidPlanCard.tsx</t>
+          <t>components/patterns/PrepaidCheckoutStep.tsx</t>
         </is>
       </c>
       <c r="D83" s="20" t="inlineStr">
@@ -4803,18 +4833,14 @@
         </is>
       </c>
       <c r="E83" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F83" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G83" s="17" t="inlineStr">
-        <is>
-          <t>PlanGroupPanel</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G83" s="17" t="inlineStr"/>
       <c r="H83" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
@@ -4829,12 +4855,12 @@
       </c>
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>PrepaidCartStep</t>
+          <t>PrepaidPackDetailsDrawer</t>
         </is>
       </c>
       <c r="C84" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidCartStep.tsx</t>
+          <t>components/patterns/PrepaidPackDetailsDrawer.tsx</t>
         </is>
       </c>
       <c r="D84" s="20" t="inlineStr">
@@ -4843,17 +4869,21 @@
         </is>
       </c>
       <c r="E84" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F84" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G84" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G84" s="17" t="inlineStr">
+        <is>
+          <t>PrepaidPlanStep</t>
+        </is>
+      </c>
       <c r="H84" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4865,12 +4895,12 @@
       </c>
       <c r="B85" s="17" t="inlineStr">
         <is>
-          <t>PrepaidCheckoutStep</t>
+          <t>PrepaidPlanCard</t>
         </is>
       </c>
       <c r="C85" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidCheckoutStep.tsx</t>
+          <t>components/patterns/PrepaidPlanCard.tsx</t>
         </is>
       </c>
       <c r="D85" s="20" t="inlineStr">
@@ -4879,14 +4909,18 @@
         </is>
       </c>
       <c r="E85" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F85" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G85" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G85" s="17" t="inlineStr">
+        <is>
+          <t>PrepaidPlanStep</t>
+        </is>
+      </c>
       <c r="H85" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
@@ -4901,12 +4935,12 @@
       </c>
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>PrepaidPackDetailsDrawer</t>
+          <t>PrepaidPlanStep</t>
         </is>
       </c>
       <c r="C86" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidPackDetailsDrawer.tsx</t>
+          <t>components/patterns/PrepaidPlanStep.tsx</t>
         </is>
       </c>
       <c r="D86" s="20" t="inlineStr">
@@ -4915,18 +4949,14 @@
         </is>
       </c>
       <c r="E86" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F86" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G86" s="17" t="inlineStr">
-        <is>
-          <t>PrepaidPlanStep</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G86" s="17" t="inlineStr"/>
       <c r="H86" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
@@ -4941,12 +4971,12 @@
       </c>
       <c r="B87" s="17" t="inlineStr">
         <is>
-          <t>PrepaidPlanCard</t>
+          <t>SummaryTables</t>
         </is>
       </c>
       <c r="C87" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidPlanCard.tsx</t>
+          <t>components/patterns/CheckoutSummaryTables.tsx</t>
         </is>
       </c>
       <c r="D87" s="20" t="inlineStr">
@@ -4955,21 +4985,21 @@
         </is>
       </c>
       <c r="E87" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F87" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G87" s="17" t="inlineStr">
         <is>
-          <t>PrepaidPlanStep</t>
+          <t>CheckoutSummaryStep, checkoutDetailedTables</t>
         </is>
       </c>
       <c r="H87" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4981,12 +5011,12 @@
       </c>
       <c r="B88" s="17" t="inlineStr">
         <is>
-          <t>PrepaidPlanStep</t>
+          <t>WinCashPaymentStep</t>
         </is>
       </c>
       <c r="C88" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidPlanStep.tsx</t>
+          <t>components/patterns/WinCashPaymentStep.tsx</t>
         </is>
       </c>
       <c r="D88" s="20" t="inlineStr">
@@ -4995,17 +5025,17 @@
         </is>
       </c>
       <c r="E88" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F88" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G88" s="17" t="inlineStr"/>
       <c r="H88" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5017,12 +5047,12 @@
       </c>
       <c r="B89" s="17" t="inlineStr">
         <is>
-          <t>SummaryTables</t>
+          <t>BillingAccountStep</t>
         </is>
       </c>
       <c r="C89" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CheckoutSummaryTables.tsx</t>
+          <t>components/patterns/BillingAccountStep.tsx</t>
         </is>
       </c>
       <c r="D89" s="20" t="inlineStr">
@@ -5038,14 +5068,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G89" s="17" t="inlineStr">
-        <is>
-          <t>CheckoutSummaryStep, checkoutDetailedTables</t>
-        </is>
-      </c>
+      <c r="G89" s="17" t="inlineStr"/>
       <c r="H89" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5083,12 @@
       </c>
       <c r="B90" s="17" t="inlineStr">
         <is>
-          <t>WinCashPaymentStep</t>
+          <t>BillingProfileSetupDrawer</t>
         </is>
       </c>
       <c r="C90" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/WinCashPaymentStep.tsx</t>
+          <t>components/patterns/BillingProfileSetupDrawer.tsx</t>
         </is>
       </c>
       <c r="D90" s="20" t="inlineStr">
@@ -5078,7 +5104,11 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G90" s="17" t="inlineStr"/>
+      <c r="G90" s="17" t="inlineStr">
+        <is>
+          <t>BillingAccountStep</t>
+        </is>
+      </c>
       <c r="H90" s="17" t="inlineStr">
         <is>
           <t>2026-10-15</t>
@@ -5349,12 +5379,12 @@
       </c>
       <c r="B98" s="17" t="inlineStr">
         <is>
-          <t>TicketCreationModal</t>
+          <t>LineSelectionStep</t>
         </is>
       </c>
       <c r="C98" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/TicketCreationModal.tsx</t>
+          <t>components/patterns/LineSelectionStep.tsx</t>
         </is>
       </c>
       <c r="D98" s="20" t="inlineStr">
@@ -5367,13 +5397,13 @@
       </c>
       <c r="F98" s="17" t="inlineStr">
         <is>
-          <t>trouble-ticketing-complaints, customer360, support</t>
+          <t>mobile-service-changes, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G98" s="17" t="inlineStr"/>
       <c r="H98" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>uncommitted</t>
         </is>
       </c>
     </row>
@@ -5385,25 +5415,25 @@
       </c>
       <c r="B99" s="17" t="inlineStr">
         <is>
-          <t>BulkOperationPortal</t>
+          <t>TicketCreationModal</t>
         </is>
       </c>
       <c r="C99" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/BulkOperationPortal.tsx</t>
-        </is>
-      </c>
-      <c r="D99" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>components/patterns/TicketCreationModal.tsx</t>
+        </is>
+      </c>
+      <c r="D99" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E99" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F99" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b</t>
+          <t>trouble-ticketing-complaints, customer360, support</t>
         </is>
       </c>
       <c r="G99" s="17" t="inlineStr"/>
@@ -5421,12 +5451,12 @@
       </c>
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>DualPlaySerialCheckStep</t>
+          <t>BulkOperationPortal</t>
         </is>
       </c>
       <c r="C100" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DualPlaySerialCheckStep.tsx</t>
+          <t>components/patterns/BulkOperationPortal.tsx</t>
         </is>
       </c>
       <c r="D100" s="21" t="inlineStr">
@@ -5439,7 +5469,7 @@
       </c>
       <c r="F100" s="17" t="inlineStr">
         <is>
-          <t>fwa-5g-home</t>
+          <t>enterprise-iot-b2b</t>
         </is>
       </c>
       <c r="G100" s="17" t="inlineStr"/>
@@ -5457,12 +5487,12 @@
       </c>
       <c r="B101" s="17" t="inlineStr">
         <is>
-          <t>SimSwapFormStep</t>
+          <t>DualPlaySerialCheckStep</t>
         </is>
       </c>
       <c r="C101" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/SimSwapFormStep.tsx</t>
+          <t>components/patterns/DualPlaySerialCheckStep.tsx</t>
         </is>
       </c>
       <c r="D101" s="21" t="inlineStr">
@@ -5475,7 +5505,7 @@
       </c>
       <c r="F101" s="17" t="inlineStr">
         <is>
-          <t>sim-number-management</t>
+          <t>fwa-5g-home</t>
         </is>
       </c>
       <c r="G101" s="17" t="inlineStr"/>
@@ -5493,12 +5523,12 @@
       </c>
       <c r="B102" s="17" t="inlineStr">
         <is>
-          <t>VerificationGate</t>
+          <t>SimSwapFormStep</t>
         </is>
       </c>
       <c r="C102" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/VerificationGate.tsx</t>
+          <t>components/patterns/SimSwapFormStep.tsx</t>
         </is>
       </c>
       <c r="D102" s="21" t="inlineStr">
@@ -5511,7 +5541,7 @@
       </c>
       <c r="F102" s="17" t="inlineStr">
         <is>
-          <t>customer360</t>
+          <t>sim-number-management</t>
         </is>
       </c>
       <c r="G102" s="17" t="inlineStr"/>
@@ -5524,30 +5554,30 @@
     <row r="103">
       <c r="A103" s="17" t="inlineStr">
         <is>
-          <t>Wizard</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="B103" s="17" t="inlineStr">
         <is>
-          <t>AbandonDialog</t>
+          <t>VerificationGate</t>
         </is>
       </c>
       <c r="C103" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/WizardDialogs.tsx</t>
-        </is>
-      </c>
-      <c r="D103" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>components/patterns/VerificationGate.tsx</t>
+        </is>
+      </c>
+      <c r="D103" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E103" s="17" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F103" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>customer360</t>
         </is>
       </c>
       <c r="G103" s="17" t="inlineStr"/>
@@ -5565,12 +5595,12 @@
       </c>
       <c r="B104" s="17" t="inlineStr">
         <is>
-          <t>CustomerMirrorPanel</t>
+          <t>AbandonDialog</t>
         </is>
       </c>
       <c r="C104" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/CustomerMirrorPanel.tsx</t>
+          <t>components/patterns/wizard/WizardDialogs.tsx</t>
         </is>
       </c>
       <c r="D104" s="20" t="inlineStr">
@@ -5579,11 +5609,11 @@
         </is>
       </c>
       <c r="E104" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F104" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G104" s="17" t="inlineStr"/>
@@ -5601,12 +5631,12 @@
       </c>
       <c r="B105" s="17" t="inlineStr">
         <is>
-          <t>StepSummaryPanel</t>
+          <t>CustomerMirrorPanel</t>
         </is>
       </c>
       <c r="C105" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/StepSummaryPanel.tsx</t>
+          <t>components/patterns/wizard/CustomerMirrorPanel.tsx</t>
         </is>
       </c>
       <c r="D105" s="20" t="inlineStr">
@@ -5615,17 +5645,17 @@
         </is>
       </c>
       <c r="E105" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F105" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G105" s="17" t="inlineStr"/>
       <c r="H105" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5637,12 +5667,12 @@
       </c>
       <c r="B106" s="17" t="inlineStr">
         <is>
-          <t>StepSummarySection</t>
+          <t>StepSummaryPanel</t>
         </is>
       </c>
       <c r="C106" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/StepSummarySection.tsx</t>
+          <t>components/patterns/wizard/StepSummaryPanel.tsx</t>
         </is>
       </c>
       <c r="D106" s="20" t="inlineStr">
@@ -5651,21 +5681,17 @@
         </is>
       </c>
       <c r="E106" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F106" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
-        </is>
-      </c>
-      <c r="G106" s="17" t="inlineStr">
-        <is>
-          <t>StepSummaryPanel</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+      <c r="G106" s="17" t="inlineStr"/>
       <c r="H106" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5677,12 +5703,12 @@
       </c>
       <c r="B107" s="17" t="inlineStr">
         <is>
-          <t>SummaryFieldRow</t>
+          <t>StepSummarySection</t>
         </is>
       </c>
       <c r="C107" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/SummaryFieldRow.tsx</t>
+          <t>components/patterns/wizard/StepSummarySection.tsx</t>
         </is>
       </c>
       <c r="D107" s="20" t="inlineStr">
@@ -5691,11 +5717,11 @@
         </is>
       </c>
       <c r="E107" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F107" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G107" s="17" t="inlineStr">
@@ -5705,7 +5731,7 @@
       </c>
       <c r="H107" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5717,12 +5743,12 @@
       </c>
       <c r="B108" s="17" t="inlineStr">
         <is>
-          <t>WizardFooter</t>
+          <t>SummaryFieldRow</t>
         </is>
       </c>
       <c r="C108" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/WizardFooter.tsx</t>
+          <t>components/patterns/wizard/SummaryFieldRow.tsx</t>
         </is>
       </c>
       <c r="D108" s="20" t="inlineStr">
@@ -5731,17 +5757,21 @@
         </is>
       </c>
       <c r="E108" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F108" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
-        </is>
-      </c>
-      <c r="G108" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+      <c r="G108" s="17" t="inlineStr">
+        <is>
+          <t>StepSummaryPanel</t>
+        </is>
+      </c>
       <c r="H108" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5783,12 @@
       </c>
       <c r="B109" s="17" t="inlineStr">
         <is>
-          <t>WizardStepHeader</t>
+          <t>WizardFooter</t>
         </is>
       </c>
       <c r="C109" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/WizardStepHeader.tsx</t>
+          <t>components/patterns/wizard/WizardFooter.tsx</t>
         </is>
       </c>
       <c r="D109" s="20" t="inlineStr">
@@ -5767,11 +5797,11 @@
         </is>
       </c>
       <c r="E109" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F109" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G109" s="17" t="inlineStr"/>
@@ -5789,12 +5819,12 @@
       </c>
       <c r="B110" s="17" t="inlineStr">
         <is>
-          <t>WizardTitleBand</t>
+          <t>WizardStepHeader</t>
         </is>
       </c>
       <c r="C110" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/WizardTitleBand.tsx</t>
+          <t>components/patterns/wizard/WizardStepHeader.tsx</t>
         </is>
       </c>
       <c r="D110" s="20" t="inlineStr">
@@ -5803,22 +5833,58 @@
         </is>
       </c>
       <c r="E110" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F110" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G110" s="17" t="inlineStr"/>
       <c r="H110" s="17" t="inlineStr">
         <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="17" t="inlineStr">
+        <is>
+          <t>Wizard</t>
+        </is>
+      </c>
+      <c r="B111" s="17" t="inlineStr">
+        <is>
+          <t>WizardTitleBand</t>
+        </is>
+      </c>
+      <c r="C111" s="17" t="inlineStr">
+        <is>
+          <t>components/patterns/wizard/WizardTitleBand.tsx</t>
+        </is>
+      </c>
+      <c r="D111" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
+        </is>
+      </c>
+      <c r="E111" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F111" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+      <c r="G111" s="17" t="inlineStr"/>
+      <c r="H111" s="17" t="inlineStr">
+        <is>
           <t>2026-10-18</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H110"/>
+  <autoFilter ref="A1:H111"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5829,7 +5895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.50" customWidth="1" min="1" max="1"/>
@@ -5906,16 +5972,16 @@
         </is>
       </c>
       <c r="E2" s="17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2" s="17" t="inlineStr">
         <is>
-          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
+          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G2" s="17" t="inlineStr">
         <is>
-          <t>CompanySearchInput, ContactPhoneInput, CpeSerialScanner, FibreReadinessBanner, MsisdnPicker, SimSerialScanner, AppointmentBookingStep, BillingAccountAutoResolver, BillingAccountStep, CafSignatureCapture, CafTerms, FixedPlanStep, PrepaidCartStep, PrepaidCheckoutStep, PrepaidPlanStep, TicketCreationModal, VerificationGate, ZsbAddressStep, useCheckoutSummary, useIdLookup, usePostpaidPlanAddons, StepSummaryPanel, stepSummary, useDraftStepSync, useJourneyStartResume, useWizardDraftActions, LocationInput, activityEngine, agentProfileEngine, businessAccountEngine, customer360Engine, fibreServiceability, serviceLocationLookup, useAreaOptions, configStore, entityStore</t>
+          <t>CompanySearchInput, ContactPhoneInput, CpeSerialScanner, MsisdnPicker, SimSerialScanner, AppointmentBookingStep, BillingAccountAutoResolver, BillingAccountStep, CafSignatureCapture, CafTerms, FixedPlanStep, PrepaidCartStep, PrepaidCheckoutStep, PrepaidPlanStep, TicketCreationModal, VerificationGate, ZsbAddressStep, lineSelectionModel, useCheckoutSummary, useIdLookup, usePostpaidPlanAddons, StepSummaryPanel, stepSummary, useDraftStepSync, useJourneyStartResume, useWizardDraftActions, LocationInput, activityEngine, agentProfileEngine, businessAccountEngine, customer360Engine, fibreServiceability, serviceLocationLookup, useAreaOptions, configStore, entityStore</t>
         </is>
       </c>
       <c r="H2" s="17" t="inlineStr">
@@ -5946,11 +6012,11 @@
         </is>
       </c>
       <c r="E3" s="17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" s="17" t="inlineStr">
         <is>
-          <t>dashboard, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, sales, tasks, tickets</t>
+          <t>dashboard, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, sales, tasks, tickets</t>
         </is>
       </c>
       <c r="G3" s="17" t="inlineStr">
@@ -5972,12 +6038,12 @@
       </c>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t>ruleEngine</t>
+          <t>postpaidPricing</t>
         </is>
       </c>
       <c r="C4" s="17" t="inlineStr">
         <is>
-          <t>engines/ruleEngine.ts</t>
+          <t>engines/postpaidPricing.ts</t>
         </is>
       </c>
       <c r="D4" s="20" t="inlineStr">
@@ -5986,16 +6052,16 @@
         </is>
       </c>
       <c r="E4" s="17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F4" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, support</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, support</t>
         </is>
       </c>
       <c r="G4" s="17" t="inlineStr">
         <is>
-          <t>BillLimitEditor, CreditCheckPanel, eligibilityRowsModel, FixedPlanStep, TicketCreationModal</t>
+          <t>MsisdnPicker, eligibilityRowsModel, CheckoutDefaultLayout, PostpaidMonthlySummary, PostpaidPlanAddonsStep, checkoutDetailedTables, checkoutSummaryRows, useCheckoutSummary, usePostpaidPlanAddons, ruleEngine</t>
         </is>
       </c>
       <c r="H4" s="17" t="inlineStr">
@@ -6012,12 +6078,12 @@
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>customer360Engine</t>
+          <t>ruleEngine</t>
         </is>
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>engines/customer360Engine.ts</t>
+          <t>engines/ruleEngine.ts</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -6026,21 +6092,21 @@
         </is>
       </c>
       <c r="E5" s="17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, product-lines, navigation, administration, customer-search, customer360, orders</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, support</t>
         </is>
       </c>
       <c r="G5" s="17" t="inlineStr">
         <is>
-          <t>customer360Demo, customerServicesEngine</t>
+          <t>BillLimitEditor, CreditCheckPanel, eligibilityRowsModel, FixedPlanStep, TicketCreationModal</t>
         </is>
       </c>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6052,12 +6118,12 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>serviceCall</t>
+          <t>billingBalance</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>engines/serviceCall.ts</t>
+          <t>engines/billingBalance.ts</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -6066,21 +6132,21 @@
         </is>
       </c>
       <c r="E6" s="17" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, product-lines, navigation, administration, customer-search, customer360, orders</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
         <is>
-          <t>DemoFaultPanel, ValidationStatus, useIdLookup</t>
+          <t>customer360Demo, customer360Engine</t>
         </is>
       </c>
       <c r="H6" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>uncommitted</t>
         </is>
       </c>
     </row>
@@ -6092,12 +6158,12 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>activityEngine</t>
+          <t>customer360Engine</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>engines/activityEngine.ts</t>
+          <t>engines/customer360Engine.ts</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -6106,21 +6172,21 @@
         </is>
       </c>
       <c r="E7" s="17" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, product-lines, navigation, administration, customer-search, customer360, orders</t>
         </is>
       </c>
       <c r="G7" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen, useWizardDraftActions</t>
+          <t>customer360Demo, customerServicesEngine</t>
         </is>
       </c>
       <c r="H7" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -6132,12 +6198,12 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>postpaidPricing</t>
+          <t>customerServicesEngine</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>engines/postpaidPricing.ts</t>
+          <t>engines/customerServicesEngine.ts</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -6146,16 +6212,16 @@
         </is>
       </c>
       <c r="E8" s="17" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, product-lines, navigation, administration, customer-search, customer360, orders</t>
         </is>
       </c>
       <c r="G8" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, CheckoutDefaultLayout, PostpaidMonthlySummary, PostpaidPlanAddonsStep, checkoutDetailedTables, checkoutSummaryRows, useCheckoutSummary, usePostpaidPlanAddons</t>
+          <t>lineSelectionModel, customer360Demo, customer360Engine</t>
         </is>
       </c>
       <c r="H8" s="17" t="inlineStr">
@@ -6172,12 +6238,12 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>customerBenefitEngine</t>
+          <t>serviceCall</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>engines/customerBenefitEngine.ts</t>
+          <t>engines/serviceCall.ts</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -6186,21 +6252,21 @@
         </is>
       </c>
       <c r="E9" s="17" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G9" s="17" t="inlineStr">
         <is>
-          <t>PostpaidPlanAddonsStep, usePostpaidPlanAddons</t>
+          <t>DemoFaultPanel, ValidationStatus, useIdLookup</t>
         </is>
       </c>
       <c r="H9" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -6212,12 +6278,12 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>personaEngine</t>
+          <t>activityEngine</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>engines/personaEngine.ts</t>
+          <t>engines/activityEngine.ts</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -6226,21 +6292,21 @@
         </is>
       </c>
       <c r="E10" s="17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t>dashboard, order-management, product-lines, sim-number-management, navigation, administration, customer360, orders, profile</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G10" s="17" t="inlineStr">
         <is>
-          <t>approvalAuthority, navigationEngine</t>
+          <t>ActivationCompleteScreen, useWizardDraftActions</t>
         </is>
       </c>
       <c r="H10" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6252,12 +6318,12 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>addonEligibility</t>
+          <t>businessSegment</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>engines/addonEligibility.ts</t>
+          <t>engines/businessSegment.ts</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -6266,17 +6332,21 @@
         </is>
       </c>
       <c r="E11" s="17" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, navigation, administration, customer-search, customer360</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="inlineStr">
+        <is>
+          <t>BillingAccountStep, customer360Demo, businessAccountEngine</t>
+        </is>
+      </c>
       <c r="H11" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -6288,12 +6358,12 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>eligibilityEngine</t>
+          <t>customerBenefitEngine</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>engines/eligibilityEngine.ts</t>
+          <t>engines/customerBenefitEngine.ts</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -6302,16 +6372,16 @@
         </is>
       </c>
       <c r="E12" s="17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
         </is>
       </c>
       <c r="G12" s="17" t="inlineStr">
         <is>
-          <t>eligibilityRowsModel, eligibilityTypes</t>
+          <t>PostpaidPlanAddonsStep, usePostpaidPlanAddons</t>
         </is>
       </c>
       <c r="H12" s="17" t="inlineStr">
@@ -6328,12 +6398,12 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>fibreServiceability</t>
+          <t>addonEligibility</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>engines/fibreServiceability.ts</t>
+          <t>engines/addonEligibility.ts</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -6342,18 +6412,14 @@
         </is>
       </c>
       <c r="E13" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>ActivationCompleteScreen</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G13" s="17" t="inlineStr"/>
       <c r="H13" s="17" t="inlineStr">
         <is>
           <t>2026-10-05</t>
@@ -6368,12 +6434,12 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>serviceLocationLookup</t>
+          <t>eligibilityEngine</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>engines/serviceLocationLookup.ts</t>
+          <t>engines/eligibilityEngine.ts</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -6382,21 +6448,21 @@
         </is>
       </c>
       <c r="E14" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G14" s="17" t="inlineStr">
         <is>
-          <t>ZsbAddressStep</t>
+          <t>eligibilityRowsModel, eligibilityTypes</t>
         </is>
       </c>
       <c r="H14" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6408,12 +6474,12 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>agentPrivilegeEngine</t>
+          <t>fibreServiceability</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>engines/agentPrivilegeEngine.ts</t>
+          <t>engines/fibreServiceability.ts</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -6422,17 +6488,21 @@
         </is>
       </c>
       <c r="E15" s="17" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>
-          <t>trouble-ticketing-complaints, navigation, administration, customer360, profile, tasks</t>
-        </is>
-      </c>
-      <c r="G15" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G15" s="17" t="inlineStr">
+        <is>
+          <t>FibreReadinessBanner, ActivationCompleteScreen</t>
+        </is>
+      </c>
       <c r="H15" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -6444,12 +6514,12 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>agentTaskEngine</t>
+          <t>personaEngine</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>engines/agentTaskEngine.ts</t>
+          <t>engines/personaEngine.ts</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -6458,17 +6528,21 @@
         </is>
       </c>
       <c r="E16" s="17" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
-          <t>dashboard, order-management, trouble-ticketing-complaints, orders, support, tasks</t>
-        </is>
-      </c>
-      <c r="G16" s="17" t="inlineStr"/>
+          <t>dashboard, order-management, product-lines, sim-number-management, navigation, administration, customer360, orders, profile</t>
+        </is>
+      </c>
+      <c r="G16" s="17" t="inlineStr">
+        <is>
+          <t>approvalAuthority, navigationEngine</t>
+        </is>
+      </c>
       <c r="H16" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -6480,12 +6554,12 @@
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>portInEngine</t>
+          <t>serviceLocationLookup</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>engines/portInEngine.ts</t>
+          <t>engines/serviceLocationLookup.ts</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -6494,17 +6568,21 @@
         </is>
       </c>
       <c r="E17" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F17" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G17" s="17" t="inlineStr">
+        <is>
+          <t>ZsbAddressStep</t>
+        </is>
+      </c>
       <c r="H17" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6516,12 +6594,12 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>approvalAuthority</t>
+          <t>agentPrivilegeEngine</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>engines/approvalAuthority.ts</t>
+          <t>engines/agentPrivilegeEngine.ts</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -6530,11 +6608,11 @@
         </is>
       </c>
       <c r="E18" s="17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>dashboard, order-management, sim-number-management, navigation, orders</t>
+          <t>trouble-ticketing-complaints, navigation, administration, customer360, profile, tasks</t>
         </is>
       </c>
       <c r="G18" s="17" t="inlineStr"/>
@@ -6552,12 +6630,12 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>csvExport</t>
+          <t>agentTaskEngine</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>engines/csvExport.ts</t>
+          <t>engines/agentTaskEngine.ts</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -6566,11 +6644,11 @@
         </is>
       </c>
       <c r="E19" s="17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F19" s="17" t="inlineStr">
         <is>
-          <t>trouble-ticketing-complaints, customer360, profile, support</t>
+          <t>dashboard, order-management, trouble-ticketing-complaints, orders, support, tasks</t>
         </is>
       </c>
       <c r="G19" s="17" t="inlineStr"/>
@@ -6588,12 +6666,12 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>customerServicesEngine</t>
+          <t>approvalAuthority</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>engines/customerServicesEngine.ts</t>
+          <t>engines/approvalAuthority.ts</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -6602,18 +6680,14 @@
         </is>
       </c>
       <c r="E20" s="17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F20" s="17" t="inlineStr">
         <is>
-          <t>product-lines, navigation, customer360, orders</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>customer360Demo</t>
-        </is>
-      </c>
+          <t>dashboard, order-management, sim-number-management, navigation, customer360, orders</t>
+        </is>
+      </c>
+      <c r="G20" s="17" t="inlineStr"/>
       <c r="H20" s="17" t="inlineStr">
         <is>
           <t>2026-10-15</t>
@@ -6628,12 +6702,12 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>bellNotificationExpiry</t>
+          <t>portInEngine</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>engines/bellNotificationExpiry.ts</t>
+          <t>engines/portInEngine.ts</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -6642,17 +6716,17 @@
         </is>
       </c>
       <c r="E21" s="17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F21" s="17" t="inlineStr">
         <is>
-          <t>administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
         </is>
       </c>
       <c r="G21" s="17" t="inlineStr"/>
       <c r="H21" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6664,12 +6738,12 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>businessAccountEngine</t>
+          <t>csvExport</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>engines/businessAccountEngine.ts</t>
+          <t>engines/csvExport.ts</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -6678,17 +6752,17 @@
         </is>
       </c>
       <c r="E22" s="17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F22" s="17" t="inlineStr">
         <is>
-          <t>customer-search, customer360</t>
+          <t>trouble-ticketing-complaints, customer360, profile, support</t>
         </is>
       </c>
       <c r="G22" s="17" t="inlineStr"/>
       <c r="H22" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -6700,12 +6774,12 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>businessSegment</t>
+          <t>bellNotificationExpiry</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>engines/businessSegment.ts</t>
+          <t>engines/bellNotificationExpiry.ts</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -6718,17 +6792,13 @@
       </c>
       <c r="F23" s="17" t="inlineStr">
         <is>
-          <t>customer-search, customer360</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr">
-        <is>
-          <t>businessAccountEngine</t>
-        </is>
-      </c>
+          <t>administration, customer360</t>
+        </is>
+      </c>
+      <c r="G23" s="17" t="inlineStr"/>
       <c r="H23" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -6740,12 +6810,12 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>navigationEngine</t>
+          <t>businessAccountEngine</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>engines/navigationEngine.ts</t>
+          <t>engines/businessAccountEngine.ts</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -6758,13 +6828,13 @@
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>navigation, customer360</t>
+          <t>customer-search, customer360</t>
         </is>
       </c>
       <c r="G24" s="17" t="inlineStr"/>
       <c r="H24" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -6776,12 +6846,12 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>qnomyQueueEngine</t>
+          <t>navigationEngine</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>engines/qnomyQueueEngine.ts</t>
+          <t>engines/navigationEngine.ts</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -6794,7 +6864,7 @@
       </c>
       <c r="F25" s="17" t="inlineStr">
         <is>
-          <t>navigation, tickets</t>
+          <t>navigation, customer360</t>
         </is>
       </c>
       <c r="G25" s="17" t="inlineStr"/>
@@ -6812,31 +6882,31 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>agentProfileEngine</t>
+          <t>qnomyQueueEngine</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>engines/agentProfileEngine.ts</t>
-        </is>
-      </c>
-      <c r="D26" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>engines/qnomyQueueEngine.ts</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E26" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
+          <t>navigation, tickets</t>
         </is>
       </c>
       <c r="G26" s="17" t="inlineStr"/>
       <c r="H26" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6848,12 +6918,12 @@
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>customer360VisibilityEngine</t>
+          <t>agentProfileEngine</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
-          <t>engines/customer360VisibilityEngine.ts</t>
+          <t>engines/agentProfileEngine.ts</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -6866,13 +6936,13 @@
       </c>
       <c r="F27" s="17" t="inlineStr">
         <is>
-          <t>customer360</t>
+          <t>navigation</t>
         </is>
       </c>
       <c r="G27" s="17" t="inlineStr"/>
       <c r="H27" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -6884,12 +6954,12 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>profileChangeTicket</t>
+          <t>customer360VisibilityEngine</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>engines/profileChangeTicket.ts</t>
+          <t>engines/customer360VisibilityEngine.ts</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -6920,12 +6990,12 @@
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>searchScopeEngine</t>
+          <t>profileChangeTicket</t>
         </is>
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>engines/searchScopeEngine.ts</t>
+          <t>engines/profileChangeTicket.ts</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
@@ -6938,13 +7008,13 @@
       </c>
       <c r="F29" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
+          <t>customer360</t>
         </is>
       </c>
       <c r="G29" s="17" t="inlineStr"/>
       <c r="H29" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6956,27 +7026,31 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>moduleDescriptions</t>
+          <t>searchScopeEngine</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>engines/moduleDescriptions.ts</t>
-        </is>
-      </c>
-      <c r="D30" s="23" t="inlineStr">
-        <is>
-          <t>App shell only</t>
+          <t>engines/searchScopeEngine.ts</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E30" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F30" s="17" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
       <c r="G30" s="17" t="inlineStr"/>
       <c r="H30" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -6988,12 +7062,12 @@
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>screenGrouping</t>
+          <t>moduleDescriptions</t>
         </is>
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>engines/screenGrouping.ts</t>
+          <t>engines/moduleDescriptions.ts</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
@@ -7015,40 +7089,32 @@
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Engine</t>
         </is>
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>entityStore</t>
+          <t>screenGrouping</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>stores/entityStore.ts</t>
-        </is>
-      </c>
-      <c r="D32" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>engines/screenGrouping.ts</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="inlineStr">
+        <is>
+          <t>App shell only</t>
         </is>
       </c>
       <c r="E32" s="17" t="n">
-        <v>23</v>
-      </c>
-      <c r="F32" s="17" t="inlineStr">
-        <is>
-          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, sales, support, tasks, tickets</t>
-        </is>
-      </c>
-      <c r="G32" s="17" t="inlineStr">
-        <is>
-          <t>ActivationCompleteScreen, DonorAttachmentStep, DonorDetailsStep, bellNotificationExpiry, profileChangeTicket</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F32" s="17" t="inlineStr"/>
+      <c r="G32" s="17" t="inlineStr"/>
       <c r="H32" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7060,12 +7126,12 @@
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>customerContextStore</t>
+          <t>entityStore</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>stores/customerContextStore.ts</t>
+          <t>stores/entityStore.ts</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -7074,16 +7140,16 @@
         </is>
       </c>
       <c r="E33" s="17" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F33" s="17" t="inlineStr">
         <is>
-          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
+          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G33" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen, useWizardDraftActions, authStore</t>
+          <t>ActivationCompleteScreen, DonorAttachmentStep, DonorDetailsStep, bellNotificationExpiry, profileChangeTicket</t>
         </is>
       </c>
       <c r="H33" s="17" t="inlineStr">
@@ -7100,12 +7166,12 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>authStore</t>
+          <t>customerContextStore</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>stores/authStore.ts</t>
+          <t>stores/customerContextStore.ts</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -7114,16 +7180,16 @@
         </is>
       </c>
       <c r="E34" s="17" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F34" s="17" t="inlineStr">
         <is>
-          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, support, tasks, tickets</t>
+          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G34" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, ActivationCompleteScreen, useWizardDraftActions, activityEngine, agentProfileEngine, profileChangeTicket, configStore</t>
+          <t>ActivationCompleteScreen, useWizardDraftActions, authStore</t>
         </is>
       </c>
       <c r="H34" s="17" t="inlineStr">
@@ -7140,12 +7206,12 @@
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>notificationStore</t>
+          <t>authStore</t>
         </is>
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
-          <t>stores/notificationStore.ts</t>
+          <t>stores/authStore.ts</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -7154,21 +7220,21 @@
         </is>
       </c>
       <c r="E35" s="17" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F35" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, profile, support, tasks</t>
+          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G35" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, ActivationCompleteScreen, TicketCreationModal, useWizardDraftActions, profileChangeTicket, useSubmit</t>
+          <t>MsisdnPicker, ActivationCompleteScreen, useWizardDraftActions, activityEngine, agentProfileEngine, profileChangeTicket, configStore</t>
         </is>
       </c>
       <c r="H35" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7180,12 +7246,12 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>personaStore</t>
+          <t>notificationStore</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>stores/personaStore.ts</t>
+          <t>stores/notificationStore.ts</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
@@ -7194,21 +7260,21 @@
         </is>
       </c>
       <c r="E36" s="17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F36" s="17" t="inlineStr">
         <is>
-          <t>dashboard, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, tasks</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, profile, support, tasks</t>
         </is>
       </c>
       <c r="G36" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, ActivationCompleteScreen, AppointmentBookingStep, configStore</t>
+          <t>MsisdnPicker, ActivationCompleteScreen, TicketCreationModal, useWizardDraftActions, profileChangeTicket, useSubmit</t>
         </is>
       </c>
       <c r="H36" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -7220,12 +7286,12 @@
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>workflowStore</t>
+          <t>personaStore</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>stores/workflowStore.ts</t>
+          <t>stores/personaStore.ts</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
@@ -7234,16 +7300,16 @@
         </is>
       </c>
       <c r="E37" s="17" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F37" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, navigation, administration</t>
+          <t>dashboard, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, tasks</t>
         </is>
       </c>
       <c r="G37" s="17" t="inlineStr">
         <is>
-          <t>useJourneyStartResume, useMirrorChannel, useWizardDraftActions, useWizardStepNavigation</t>
+          <t>MsisdnPicker, ActivationCompleteScreen, AppointmentBookingStep, configStore</t>
         </is>
       </c>
       <c r="H37" s="17" t="inlineStr">
@@ -7260,35 +7326,35 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>customerVerificationStore</t>
+          <t>workflowStore</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>stores/customerVerificationStore.ts</t>
-        </is>
-      </c>
-      <c r="D38" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>stores/workflowStore.ts</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E38" s="17" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F38" s="17" t="inlineStr">
         <is>
-          <t>customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration</t>
         </is>
       </c>
       <c r="G38" s="17" t="inlineStr">
         <is>
-          <t>VerificationGate</t>
+          <t>useJourneyStartResume, useMirrorChannel, useWizardDraftActions, useWizardStepNavigation</t>
         </is>
       </c>
       <c r="H38" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7300,12 +7366,12 @@
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>qnomyQueueStore</t>
+          <t>customerVerificationStore</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>stores/qnomyQueueStore.ts</t>
+          <t>stores/customerVerificationStore.ts</t>
         </is>
       </c>
       <c r="D39" s="21" t="inlineStr">
@@ -7318,13 +7384,17 @@
       </c>
       <c r="F39" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="G39" s="17" t="inlineStr"/>
+          <t>customer360</t>
+        </is>
+      </c>
+      <c r="G39" s="17" t="inlineStr">
+        <is>
+          <t>VerificationGate</t>
+        </is>
+      </c>
       <c r="H39" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7336,12 +7406,12 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>regionStore</t>
+          <t>qnomyQueueStore</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>stores/regionStore.ts</t>
+          <t>stores/qnomyQueueStore.ts</t>
         </is>
       </c>
       <c r="D40" s="21" t="inlineStr">
@@ -7360,7 +7430,7 @@
       <c r="G40" s="17" t="inlineStr"/>
       <c r="H40" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -7372,12 +7442,12 @@
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>sidebarStore</t>
+          <t>regionStore</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>stores/sidebarStore.ts</t>
+          <t>stores/regionStore.ts</t>
         </is>
       </c>
       <c r="D41" s="21" t="inlineStr">
@@ -7396,7 +7466,7 @@
       <c r="G41" s="17" t="inlineStr"/>
       <c r="H41" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7408,12 +7478,12 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>themeStore</t>
+          <t>sidebarStore</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>stores/themeStore.ts</t>
+          <t>stores/sidebarStore.ts</t>
         </is>
       </c>
       <c r="D42" s="21" t="inlineStr">
@@ -7432,7 +7502,7 @@
       <c r="G42" s="17" t="inlineStr"/>
       <c r="H42" s="17" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7444,67 +7514,63 @@
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>configStore</t>
+          <t>themeStore</t>
         </is>
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>stores/configStore.ts</t>
-        </is>
-      </c>
-      <c r="D43" s="23" t="inlineStr">
-        <is>
-          <t>App shell only</t>
+          <t>stores/themeStore.ts</t>
+        </is>
+      </c>
+      <c r="D43" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E43" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F43" s="17" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
       <c r="G43" s="17" t="inlineStr"/>
       <c r="H43" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t>Hook</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>useEnterToSubmit</t>
+          <t>configStore</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>hooks/useEnterToSubmit.ts</t>
-        </is>
-      </c>
-      <c r="D44" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>stores/configStore.ts</t>
+        </is>
+      </c>
+      <c r="D44" s="23" t="inlineStr">
+        <is>
+          <t>App shell only</t>
         </is>
       </c>
       <c r="E44" s="17" t="n">
-        <v>11</v>
-      </c>
-      <c r="F44" s="17" t="inlineStr">
-        <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
-        </is>
-      </c>
-      <c r="G44" s="17" t="inlineStr">
-        <is>
-          <t>VerificationGate, useIdLookup</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F44" s="17" t="inlineStr"/>
+      <c r="G44" s="17" t="inlineStr"/>
       <c r="H44" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7516,12 +7582,12 @@
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>useSearchListNav</t>
+          <t>useEnterToSubmit</t>
         </is>
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>hooks/useSearchListNav.ts</t>
+          <t>hooks/useEnterToSubmit.ts</t>
         </is>
       </c>
       <c r="D45" s="20" t="inlineStr">
@@ -7530,21 +7596,21 @@
         </is>
       </c>
       <c r="E45" s="17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F45" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, navigation, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G45" s="17" t="inlineStr">
         <is>
-          <t>CompanySearchInput, ContactPhoneInput, PlanSearchBox, LocationInput</t>
+          <t>VerificationGate, useIdLookup</t>
         </is>
       </c>
       <c r="H45" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7622,12 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>useAreaOptions</t>
+          <t>useSearchListNav</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>hooks/useAreaOptions.ts</t>
+          <t>hooks/useSearchListNav.ts</t>
         </is>
       </c>
       <c r="D46" s="20" t="inlineStr">
@@ -7570,21 +7636,21 @@
         </is>
       </c>
       <c r="E46" s="17" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F46" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, navigation, administration, customer360</t>
         </is>
       </c>
       <c r="G46" s="17" t="inlineStr">
         <is>
-          <t>BillingAccountStep, ZsbAddressStep</t>
+          <t>CompanySearchInput, ContactPhoneInput, PlanSearchBox, LocationInput</t>
         </is>
       </c>
       <c r="H46" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -7596,12 +7662,12 @@
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>useSubmit</t>
+          <t>useAreaOptions</t>
         </is>
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>hooks/useSubmit.ts</t>
+          <t>hooks/useAreaOptions.ts</t>
         </is>
       </c>
       <c r="D47" s="20" t="inlineStr">
@@ -7610,17 +7676,21 @@
         </is>
       </c>
       <c r="E47" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F47" s="17" t="inlineStr">
         <is>
-          <t>lead-management, mnp-fnp-porting, sim-number-management, trouble-ticketing-complaints, customer360, tasks</t>
-        </is>
-      </c>
-      <c r="G47" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G47" s="17" t="inlineStr">
+        <is>
+          <t>BillingAccountStep, ZsbAddressStep</t>
+        </is>
+      </c>
       <c r="H47" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7632,71 +7702,67 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>useMinWidth</t>
+          <t>useSubmit</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>hooks/useMinWidth.ts</t>
-        </is>
-      </c>
-      <c r="D48" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>hooks/useSubmit.ts</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E48" s="17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F48" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
+          <t>lead-management, mnp-fnp-porting, sim-number-management, trouble-ticketing-complaints, customer360, tasks</t>
         </is>
       </c>
       <c r="G48" s="17" t="inlineStr"/>
       <c r="H48" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="17" t="inlineStr">
         <is>
-          <t>Helper</t>
+          <t>Hook</t>
         </is>
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>statusTone</t>
+          <t>useMinWidth</t>
         </is>
       </c>
       <c r="C49" s="17" t="inlineStr">
         <is>
-          <t>lib/statusTone.ts</t>
-        </is>
-      </c>
-      <c r="D49" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>hooks/useMinWidth.ts</t>
+        </is>
+      </c>
+      <c r="D49" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E49" s="17" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="F49" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, orders, sales, support, tasks, tickets</t>
-        </is>
-      </c>
-      <c r="G49" s="17" t="inlineStr">
-        <is>
-          <t>ruleEngine</t>
-        </is>
-      </c>
+          <t>navigation</t>
+        </is>
+      </c>
+      <c r="G49" s="17" t="inlineStr"/>
       <c r="H49" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7708,12 +7774,12 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>format</t>
+          <t>statusTone</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>lib/format.ts</t>
+          <t>lib/statusTone.ts</t>
         </is>
       </c>
       <c r="D50" s="20" t="inlineStr">
@@ -7722,16 +7788,16 @@
         </is>
       </c>
       <c r="E50" s="17" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F50" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, tasks</t>
+          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, orders, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G50" s="17" t="inlineStr">
         <is>
-          <t>AdditionalDocumentsUpload, CafDocumentUpload, MsisdnPicker, SupportingDocumentUpload, GuidedContactStep, IdLookupStep, postpaidPlanModel, StepSummaryPanel, stepSummary, postpaidPricing</t>
+          <t>ruleEngine</t>
         </is>
       </c>
       <c r="H50" s="17" t="inlineStr">
@@ -7748,12 +7814,12 @@
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>deviceType</t>
+          <t>format</t>
         </is>
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>lib/deviceType.ts</t>
+          <t>lib/format.ts</t>
         </is>
       </c>
       <c r="D51" s="20" t="inlineStr">
@@ -7762,16 +7828,16 @@
         </is>
       </c>
       <c r="E51" s="17" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F51" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, navigation, administration</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, support, tasks</t>
         </is>
       </c>
       <c r="G51" s="17" t="inlineStr">
         <is>
-          <t>SimSerialScanner, SimTypeStep, cafTypes</t>
+          <t>AdditionalDocumentsUpload, CafDocumentUpload, MsisdnPicker, SupportingDocumentUpload, GuidedContactStep, IdLookupStep, postpaidPlanModel, StepSummaryPanel, stepSummary, postpaidPricing</t>
         </is>
       </c>
       <c r="H51" s="17" t="inlineStr">
@@ -7788,12 +7854,12 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>taskId</t>
+          <t>deviceType</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>lib/taskId.ts</t>
+          <t>lib/deviceType.ts</t>
         </is>
       </c>
       <c r="D52" s="20" t="inlineStr">
@@ -7802,16 +7868,16 @@
         </is>
       </c>
       <c r="E52" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F52" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration</t>
         </is>
       </c>
       <c r="G52" s="17" t="inlineStr">
         <is>
-          <t>useWizardDraftActions</t>
+          <t>SimSerialScanner, SimTypeStep, cafTypes</t>
         </is>
       </c>
       <c r="H52" s="17" t="inlineStr">
@@ -7828,12 +7894,12 @@
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>connectionType</t>
+          <t>taskId</t>
         </is>
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>lib/connectionType.ts</t>
+          <t>lib/taskId.ts</t>
         </is>
       </c>
       <c r="D53" s="20" t="inlineStr">
@@ -7842,16 +7908,16 @@
         </is>
       </c>
       <c r="E53" s="17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F53" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G53" s="17" t="inlineStr">
         <is>
-          <t>ConnectionTypeTag</t>
+          <t>useWizardDraftActions</t>
         </is>
       </c>
       <c r="H53" s="17" t="inlineStr">
@@ -7868,28 +7934,32 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>screenName</t>
+          <t>connectionType</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>lib/screenName.ts</t>
-        </is>
-      </c>
-      <c r="D54" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>lib/connectionType.ts</t>
+        </is>
+      </c>
+      <c r="D54" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E54" s="17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F54" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="G54" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G54" s="17" t="inlineStr">
+        <is>
+          <t>ConnectionTypeTag</t>
+        </is>
+      </c>
       <c r="H54" s="17" t="inlineStr">
         <is>
           <t>2026-10-15</t>
@@ -7904,12 +7974,12 @@
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>values</t>
+          <t>screenName</t>
         </is>
       </c>
       <c r="C55" s="17" t="inlineStr">
         <is>
-          <t>lib/values.ts</t>
+          <t>lib/screenName.ts</t>
         </is>
       </c>
       <c r="D55" s="21" t="inlineStr">
@@ -7922,22 +7992,58 @@
       </c>
       <c r="F55" s="17" t="inlineStr">
         <is>
+          <t>navigation</t>
+        </is>
+      </c>
+      <c r="G55" s="17" t="inlineStr"/>
+      <c r="H55" s="17" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t>Helper</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="inlineStr">
+        <is>
+          <t>values</t>
+        </is>
+      </c>
+      <c r="C56" s="17" t="inlineStr">
+        <is>
+          <t>lib/values.ts</t>
+        </is>
+      </c>
+      <c r="D56" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
+        </is>
+      </c>
+      <c r="E56" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="17" t="inlineStr">
+        <is>
           <t>customer360</t>
         </is>
       </c>
-      <c r="G55" s="17" t="inlineStr">
+      <c r="G56" s="17" t="inlineStr">
         <is>
           <t>customer360Demo</t>
         </is>
       </c>
-      <c r="H55" s="17" t="inlineStr">
+      <c r="H56" s="17" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H55"/>
+  <autoFilter ref="A1:H56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
+++ b/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'UI Components'!$A$1:$H$111</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Shared Code'!$A$1:$H$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Shared Code'!$A$1:$H$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="C9" s="17" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D9" s="17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E9" s="17" t="n">
         <v>4</v>
@@ -855,14 +855,14 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>110 UI components + 55 non-UI files</t>
+          <t>110 UI components + 56 non-UI files</t>
         </is>
       </c>
       <c r="C13" s="18" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E13" s="18" t="n">
         <v>21</v>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="H51" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5295,7 +5295,7 @@
       </c>
       <c r="H95" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       <c r="G98" s="17" t="inlineStr"/>
       <c r="H98" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5895,7 +5895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.50" customWidth="1" min="1" max="1"/>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="G2" s="17" t="inlineStr">
         <is>
-          <t>CompanySearchInput, ContactPhoneInput, CpeSerialScanner, MsisdnPicker, SimSerialScanner, AppointmentBookingStep, BillingAccountAutoResolver, BillingAccountStep, CafSignatureCapture, CafTerms, FixedPlanStep, PrepaidCartStep, PrepaidCheckoutStep, PrepaidPlanStep, TicketCreationModal, VerificationGate, ZsbAddressStep, lineSelectionModel, useCheckoutSummary, useIdLookup, usePostpaidPlanAddons, StepSummaryPanel, stepSummary, useDraftStepSync, useJourneyStartResume, useWizardDraftActions, LocationInput, activityEngine, agentProfileEngine, businessAccountEngine, customer360Engine, fibreServiceability, serviceLocationLookup, useAreaOptions, configStore, entityStore</t>
+          <t>CompanySearchInput, ContactPhoneInput, CpeSerialScanner, MsisdnPicker, SimSerialScanner, AppointmentBookingStep, BillingAccountAutoResolver, BillingAccountStep, CafSignatureCapture, CafTerms, FixedPlanStep, PrepaidCartStep, PrepaidCheckoutStep, PrepaidPlanStep, TicketCreationModal, VerificationGate, ZsbAddressStep, lineSelectionModel, useCheckoutSummary, useIdLookup, usePostpaidPlanAddons, StepSummaryPanel, stepSummary, useJourneyStartResume, useWizardDraftActions, LocationInput, activityEngine, agentProfileEngine, businessAccountEngine, customer360Engine, fibreServiceability, serviceLocationLookup, useAreaOptions, configStore, entityStore</t>
         </is>
       </c>
       <c r="H2" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="H6" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="H7" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="H11" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>serviceLocationLookup</t>
+          <t>eligibilityGuard</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>engines/serviceLocationLookup.ts</t>
+          <t>engines/eligibilityGuard.ts</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -6572,17 +6572,13 @@
       </c>
       <c r="F17" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>ZsbAddressStep</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration</t>
+        </is>
+      </c>
+      <c r="G17" s="17" t="inlineStr"/>
       <c r="H17" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>uncommitted</t>
         </is>
       </c>
     </row>
@@ -6594,12 +6590,12 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>agentPrivilegeEngine</t>
+          <t>serviceLocationLookup</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>engines/agentPrivilegeEngine.ts</t>
+          <t>engines/serviceLocationLookup.ts</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -6608,17 +6604,21 @@
         </is>
       </c>
       <c r="E18" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>trouble-ticketing-complaints, navigation, administration, customer360, profile, tasks</t>
-        </is>
-      </c>
-      <c r="G18" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G18" s="17" t="inlineStr">
+        <is>
+          <t>ZsbAddressStep</t>
+        </is>
+      </c>
       <c r="H18" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6630,12 +6630,12 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>agentTaskEngine</t>
+          <t>agentPrivilegeEngine</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>engines/agentTaskEngine.ts</t>
+          <t>engines/agentPrivilegeEngine.ts</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -6648,13 +6648,13 @@
       </c>
       <c r="F19" s="17" t="inlineStr">
         <is>
-          <t>dashboard, order-management, trouble-ticketing-complaints, orders, support, tasks</t>
+          <t>trouble-ticketing-complaints, navigation, administration, customer360, profile, tasks</t>
         </is>
       </c>
       <c r="G19" s="17" t="inlineStr"/>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>approvalAuthority</t>
+          <t>agentTaskEngine</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>engines/approvalAuthority.ts</t>
+          <t>engines/agentTaskEngine.ts</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -6684,13 +6684,13 @@
       </c>
       <c r="F20" s="17" t="inlineStr">
         <is>
-          <t>dashboard, order-management, sim-number-management, navigation, customer360, orders</t>
+          <t>dashboard, order-management, trouble-ticketing-complaints, orders, support, tasks</t>
         </is>
       </c>
       <c r="G20" s="17" t="inlineStr"/>
       <c r="H20" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>portInEngine</t>
+          <t>approvalAuthority</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>engines/portInEngine.ts</t>
+          <t>engines/approvalAuthority.ts</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -6720,13 +6720,13 @@
       </c>
       <c r="F21" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
+          <t>dashboard, order-management, sim-number-management, navigation, customer360, orders</t>
         </is>
       </c>
       <c r="G21" s="17" t="inlineStr"/>
       <c r="H21" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6738,12 +6738,12 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>csvExport</t>
+          <t>portInEngine</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>engines/csvExport.ts</t>
+          <t>engines/portInEngine.ts</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -6752,17 +6752,17 @@
         </is>
       </c>
       <c r="E22" s="17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F22" s="17" t="inlineStr">
         <is>
-          <t>trouble-ticketing-complaints, customer360, profile, support</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
         </is>
       </c>
       <c r="G22" s="17" t="inlineStr"/>
       <c r="H22" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6774,12 +6774,12 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>bellNotificationExpiry</t>
+          <t>csvExport</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>engines/bellNotificationExpiry.ts</t>
+          <t>engines/csvExport.ts</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -6788,11 +6788,11 @@
         </is>
       </c>
       <c r="E23" s="17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F23" s="17" t="inlineStr">
         <is>
-          <t>administration, customer360</t>
+          <t>trouble-ticketing-complaints, customer360, profile, support</t>
         </is>
       </c>
       <c r="G23" s="17" t="inlineStr"/>
@@ -6810,12 +6810,12 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>businessAccountEngine</t>
+          <t>bellNotificationExpiry</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>engines/businessAccountEngine.ts</t>
+          <t>engines/bellNotificationExpiry.ts</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -6828,13 +6828,13 @@
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>customer-search, customer360</t>
+          <t>administration, customer360</t>
         </is>
       </c>
       <c r="G24" s="17" t="inlineStr"/>
       <c r="H24" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -6846,12 +6846,12 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>navigationEngine</t>
+          <t>businessAccountEngine</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>engines/navigationEngine.ts</t>
+          <t>engines/businessAccountEngine.ts</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -6864,13 +6864,13 @@
       </c>
       <c r="F25" s="17" t="inlineStr">
         <is>
-          <t>navigation, customer360</t>
+          <t>customer-search, customer360</t>
         </is>
       </c>
       <c r="G25" s="17" t="inlineStr"/>
       <c r="H25" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -6882,12 +6882,12 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>qnomyQueueEngine</t>
+          <t>navigationEngine</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>engines/qnomyQueueEngine.ts</t>
+          <t>engines/navigationEngine.ts</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>navigation, tickets</t>
+          <t>navigation, customer360</t>
         </is>
       </c>
       <c r="G26" s="17" t="inlineStr"/>
@@ -6918,31 +6918,31 @@
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>agentProfileEngine</t>
+          <t>qnomyQueueEngine</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
-          <t>engines/agentProfileEngine.ts</t>
-        </is>
-      </c>
-      <c r="D27" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>engines/qnomyQueueEngine.ts</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E27" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
+          <t>navigation, tickets</t>
         </is>
       </c>
       <c r="G27" s="17" t="inlineStr"/>
       <c r="H27" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6954,12 +6954,12 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>customer360VisibilityEngine</t>
+          <t>agentProfileEngine</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>engines/customer360VisibilityEngine.ts</t>
+          <t>engines/agentProfileEngine.ts</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -6972,13 +6972,13 @@
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>customer360</t>
+          <t>navigation</t>
         </is>
       </c>
       <c r="G28" s="17" t="inlineStr"/>
       <c r="H28" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>profileChangeTicket</t>
+          <t>customer360VisibilityEngine</t>
         </is>
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>engines/profileChangeTicket.ts</t>
+          <t>engines/customer360VisibilityEngine.ts</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>searchScopeEngine</t>
+          <t>profileChangeTicket</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>engines/searchScopeEngine.ts</t>
+          <t>engines/profileChangeTicket.ts</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
@@ -7044,13 +7044,13 @@
       </c>
       <c r="F30" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
+          <t>customer360</t>
         </is>
       </c>
       <c r="G30" s="17" t="inlineStr"/>
       <c r="H30" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7062,27 +7062,31 @@
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>moduleDescriptions</t>
+          <t>searchScopeEngine</t>
         </is>
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>engines/moduleDescriptions.ts</t>
-        </is>
-      </c>
-      <c r="D31" s="23" t="inlineStr">
-        <is>
-          <t>App shell only</t>
+          <t>engines/searchScopeEngine.ts</t>
+        </is>
+      </c>
+      <c r="D31" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E31" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F31" s="17" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
       <c r="G31" s="17" t="inlineStr"/>
       <c r="H31" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -7094,12 +7098,12 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>screenGrouping</t>
+          <t>moduleDescriptions</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>engines/screenGrouping.ts</t>
+          <t>engines/moduleDescriptions.ts</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
@@ -7121,40 +7125,32 @@
     <row r="33">
       <c r="A33" s="17" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Engine</t>
         </is>
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>entityStore</t>
+          <t>screenGrouping</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>stores/entityStore.ts</t>
-        </is>
-      </c>
-      <c r="D33" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>engines/screenGrouping.ts</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="inlineStr">
+        <is>
+          <t>App shell only</t>
         </is>
       </c>
       <c r="E33" s="17" t="n">
-        <v>24</v>
-      </c>
-      <c r="F33" s="17" t="inlineStr">
-        <is>
-          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, sales, support, tasks, tickets</t>
-        </is>
-      </c>
-      <c r="G33" s="17" t="inlineStr">
-        <is>
-          <t>ActivationCompleteScreen, DonorAttachmentStep, DonorDetailsStep, bellNotificationExpiry, profileChangeTicket</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F33" s="17" t="inlineStr"/>
+      <c r="G33" s="17" t="inlineStr"/>
       <c r="H33" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7166,12 +7162,12 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>customerContextStore</t>
+          <t>entityStore</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>stores/customerContextStore.ts</t>
+          <t>stores/entityStore.ts</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -7180,21 +7176,21 @@
         </is>
       </c>
       <c r="E34" s="17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F34" s="17" t="inlineStr">
         <is>
-          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
+          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G34" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen, useWizardDraftActions, authStore</t>
+          <t>ActivationCompleteScreen, DonorAttachmentStep, DonorDetailsStep, useDraftStepSync, useWizardDraftActions, activityEngine, bellNotificationExpiry, profileChangeTicket</t>
         </is>
       </c>
       <c r="H34" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7206,12 +7202,12 @@
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>authStore</t>
+          <t>customerContextStore</t>
         </is>
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
-          <t>stores/authStore.ts</t>
+          <t>stores/customerContextStore.ts</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -7220,16 +7216,16 @@
         </is>
       </c>
       <c r="E35" s="17" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F35" s="17" t="inlineStr">
         <is>
-          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, support, tasks, tickets</t>
+          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G35" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, ActivationCompleteScreen, useWizardDraftActions, activityEngine, agentProfileEngine, profileChangeTicket, configStore</t>
+          <t>ActivationCompleteScreen, useWizardDraftActions, authStore</t>
         </is>
       </c>
       <c r="H35" s="17" t="inlineStr">
@@ -7246,12 +7242,12 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>notificationStore</t>
+          <t>authStore</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>stores/notificationStore.ts</t>
+          <t>stores/authStore.ts</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
@@ -7260,21 +7256,21 @@
         </is>
       </c>
       <c r="E36" s="17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F36" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, profile, support, tasks</t>
+          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G36" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, ActivationCompleteScreen, TicketCreationModal, useWizardDraftActions, profileChangeTicket, useSubmit</t>
+          <t>MsisdnPicker, ActivationCompleteScreen, useWizardDraftActions, activityEngine, agentProfileEngine, profileChangeTicket, configStore</t>
         </is>
       </c>
       <c r="H36" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7286,12 +7282,12 @@
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>personaStore</t>
+          <t>notificationStore</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>stores/personaStore.ts</t>
+          <t>stores/notificationStore.ts</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
@@ -7300,21 +7296,21 @@
         </is>
       </c>
       <c r="E37" s="17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F37" s="17" t="inlineStr">
         <is>
-          <t>dashboard, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, tasks</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, profile, support, tasks</t>
         </is>
       </c>
       <c r="G37" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, ActivationCompleteScreen, AppointmentBookingStep, configStore</t>
+          <t>MsisdnPicker, ActivationCompleteScreen, TicketCreationModal, useWizardDraftActions, useWizardStepNavigation, profileChangeTicket, useSubmit</t>
         </is>
       </c>
       <c r="H37" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -7326,12 +7322,12 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>workflowStore</t>
+          <t>personaStore</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>stores/workflowStore.ts</t>
+          <t>stores/personaStore.ts</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
@@ -7340,16 +7336,16 @@
         </is>
       </c>
       <c r="E38" s="17" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F38" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration</t>
+          <t>dashboard, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, tasks</t>
         </is>
       </c>
       <c r="G38" s="17" t="inlineStr">
         <is>
-          <t>useJourneyStartResume, useMirrorChannel, useWizardDraftActions, useWizardStepNavigation</t>
+          <t>MsisdnPicker, ActivationCompleteScreen, AppointmentBookingStep, configStore</t>
         </is>
       </c>
       <c r="H38" s="17" t="inlineStr">
@@ -7366,35 +7362,35 @@
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>customerVerificationStore</t>
+          <t>workflowStore</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>stores/customerVerificationStore.ts</t>
-        </is>
-      </c>
-      <c r="D39" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>stores/workflowStore.ts</t>
+        </is>
+      </c>
+      <c r="D39" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E39" s="17" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F39" s="17" t="inlineStr">
         <is>
-          <t>customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration</t>
         </is>
       </c>
       <c r="G39" s="17" t="inlineStr">
         <is>
-          <t>VerificationGate</t>
+          <t>useJourneyStartResume, useMirrorChannel, useWizardDraftActions, useWizardStepNavigation</t>
         </is>
       </c>
       <c r="H39" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7406,12 +7402,12 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>qnomyQueueStore</t>
+          <t>customerVerificationStore</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>stores/qnomyQueueStore.ts</t>
+          <t>stores/customerVerificationStore.ts</t>
         </is>
       </c>
       <c r="D40" s="21" t="inlineStr">
@@ -7424,13 +7420,17 @@
       </c>
       <c r="F40" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="G40" s="17" t="inlineStr"/>
+          <t>customer360</t>
+        </is>
+      </c>
+      <c r="G40" s="17" t="inlineStr">
+        <is>
+          <t>VerificationGate</t>
+        </is>
+      </c>
       <c r="H40" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>regionStore</t>
+          <t>qnomyQueueStore</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>stores/regionStore.ts</t>
+          <t>stores/qnomyQueueStore.ts</t>
         </is>
       </c>
       <c r="D41" s="21" t="inlineStr">
@@ -7466,7 +7466,7 @@
       <c r="G41" s="17" t="inlineStr"/>
       <c r="H41" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -7478,12 +7478,12 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>sidebarStore</t>
+          <t>regionStore</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>stores/sidebarStore.ts</t>
+          <t>stores/regionStore.ts</t>
         </is>
       </c>
       <c r="D42" s="21" t="inlineStr">
@@ -7502,7 +7502,7 @@
       <c r="G42" s="17" t="inlineStr"/>
       <c r="H42" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7514,12 +7514,12 @@
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>themeStore</t>
+          <t>sidebarStore</t>
         </is>
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>stores/themeStore.ts</t>
+          <t>stores/sidebarStore.ts</t>
         </is>
       </c>
       <c r="D43" s="21" t="inlineStr">
@@ -7538,7 +7538,7 @@
       <c r="G43" s="17" t="inlineStr"/>
       <c r="H43" s="17" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7550,67 +7550,63 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>configStore</t>
+          <t>themeStore</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>stores/configStore.ts</t>
-        </is>
-      </c>
-      <c r="D44" s="23" t="inlineStr">
-        <is>
-          <t>App shell only</t>
+          <t>stores/themeStore.ts</t>
+        </is>
+      </c>
+      <c r="D44" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E44" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F44" s="17" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
       <c r="G44" s="17" t="inlineStr"/>
       <c r="H44" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="17" t="inlineStr">
         <is>
-          <t>Hook</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>useEnterToSubmit</t>
+          <t>configStore</t>
         </is>
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>hooks/useEnterToSubmit.ts</t>
-        </is>
-      </c>
-      <c r="D45" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>stores/configStore.ts</t>
+        </is>
+      </c>
+      <c r="D45" s="23" t="inlineStr">
+        <is>
+          <t>App shell only</t>
         </is>
       </c>
       <c r="E45" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="F45" s="17" t="inlineStr">
-        <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
-        </is>
-      </c>
-      <c r="G45" s="17" t="inlineStr">
-        <is>
-          <t>VerificationGate, useIdLookup</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F45" s="17" t="inlineStr"/>
+      <c r="G45" s="17" t="inlineStr"/>
       <c r="H45" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7622,12 +7618,12 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>useSearchListNav</t>
+          <t>useEnterToSubmit</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>hooks/useSearchListNav.ts</t>
+          <t>hooks/useEnterToSubmit.ts</t>
         </is>
       </c>
       <c r="D46" s="20" t="inlineStr">
@@ -7636,21 +7632,21 @@
         </is>
       </c>
       <c r="E46" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F46" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, navigation, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G46" s="17" t="inlineStr">
         <is>
-          <t>CompanySearchInput, ContactPhoneInput, PlanSearchBox, LocationInput</t>
+          <t>VerificationGate, useIdLookup</t>
         </is>
       </c>
       <c r="H46" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7662,12 +7658,12 @@
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>useAreaOptions</t>
+          <t>useSearchListNav</t>
         </is>
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>hooks/useAreaOptions.ts</t>
+          <t>hooks/useSearchListNav.ts</t>
         </is>
       </c>
       <c r="D47" s="20" t="inlineStr">
@@ -7676,21 +7672,21 @@
         </is>
       </c>
       <c r="E47" s="17" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F47" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, navigation, administration, customer360</t>
         </is>
       </c>
       <c r="G47" s="17" t="inlineStr">
         <is>
-          <t>BillingAccountStep, ZsbAddressStep</t>
+          <t>CompanySearchInput, ContactPhoneInput, PlanSearchBox, LocationInput</t>
         </is>
       </c>
       <c r="H47" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -7702,12 +7698,12 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>useSubmit</t>
+          <t>useAreaOptions</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>hooks/useSubmit.ts</t>
+          <t>hooks/useAreaOptions.ts</t>
         </is>
       </c>
       <c r="D48" s="20" t="inlineStr">
@@ -7716,17 +7712,21 @@
         </is>
       </c>
       <c r="E48" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F48" s="17" t="inlineStr">
         <is>
-          <t>lead-management, mnp-fnp-porting, sim-number-management, trouble-ticketing-complaints, customer360, tasks</t>
-        </is>
-      </c>
-      <c r="G48" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G48" s="17" t="inlineStr">
+        <is>
+          <t>BillingAccountStep, ZsbAddressStep</t>
+        </is>
+      </c>
       <c r="H48" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7738,71 +7738,67 @@
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>useMinWidth</t>
+          <t>useSubmit</t>
         </is>
       </c>
       <c r="C49" s="17" t="inlineStr">
         <is>
-          <t>hooks/useMinWidth.ts</t>
-        </is>
-      </c>
-      <c r="D49" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>hooks/useSubmit.ts</t>
+        </is>
+      </c>
+      <c r="D49" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E49" s="17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F49" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
+          <t>lead-management, mnp-fnp-porting, sim-number-management, trouble-ticketing-complaints, customer360, tasks</t>
         </is>
       </c>
       <c r="G49" s="17" t="inlineStr"/>
       <c r="H49" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="17" t="inlineStr">
         <is>
-          <t>Helper</t>
+          <t>Hook</t>
         </is>
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>statusTone</t>
+          <t>useMinWidth</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>lib/statusTone.ts</t>
-        </is>
-      </c>
-      <c r="D50" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>hooks/useMinWidth.ts</t>
+        </is>
+      </c>
+      <c r="D50" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E50" s="17" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F50" s="17" t="inlineStr">
         <is>
-          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, orders, sales, support, tasks, tickets</t>
-        </is>
-      </c>
-      <c r="G50" s="17" t="inlineStr">
-        <is>
-          <t>ruleEngine</t>
-        </is>
-      </c>
+          <t>navigation</t>
+        </is>
+      </c>
+      <c r="G50" s="17" t="inlineStr"/>
       <c r="H50" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7814,12 +7810,12 @@
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>format</t>
+          <t>statusTone</t>
         </is>
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>lib/format.ts</t>
+          <t>lib/statusTone.ts</t>
         </is>
       </c>
       <c r="D51" s="20" t="inlineStr">
@@ -7828,21 +7824,21 @@
         </is>
       </c>
       <c r="E51" s="17" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F51" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, support, tasks</t>
+          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, orders, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G51" s="17" t="inlineStr">
         <is>
-          <t>AdditionalDocumentsUpload, CafDocumentUpload, MsisdnPicker, SupportingDocumentUpload, GuidedContactStep, IdLookupStep, postpaidPlanModel, StepSummaryPanel, stepSummary, postpaidPricing</t>
+          <t>ruleEngine</t>
         </is>
       </c>
       <c r="H51" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7854,12 +7850,12 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>deviceType</t>
+          <t>format</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>lib/deviceType.ts</t>
+          <t>lib/format.ts</t>
         </is>
       </c>
       <c r="D52" s="20" t="inlineStr">
@@ -7868,16 +7864,16 @@
         </is>
       </c>
       <c r="E52" s="17" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F52" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, support, tasks</t>
         </is>
       </c>
       <c r="G52" s="17" t="inlineStr">
         <is>
-          <t>SimSerialScanner, SimTypeStep, cafTypes</t>
+          <t>AdditionalDocumentsUpload, CafDocumentUpload, MsisdnPicker, SupportingDocumentUpload, GuidedContactStep, IdLookupStep, postpaidPlanModel, StepSummaryPanel, stepSummary, postpaidPricing</t>
         </is>
       </c>
       <c r="H52" s="17" t="inlineStr">
@@ -7894,12 +7890,12 @@
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>taskId</t>
+          <t>deviceType</t>
         </is>
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>lib/taskId.ts</t>
+          <t>lib/deviceType.ts</t>
         </is>
       </c>
       <c r="D53" s="20" t="inlineStr">
@@ -7912,12 +7908,12 @@
       </c>
       <c r="F53" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration</t>
         </is>
       </c>
       <c r="G53" s="17" t="inlineStr">
         <is>
-          <t>useWizardDraftActions</t>
+          <t>SimSerialScanner, SimTypeStep, cafTypes</t>
         </is>
       </c>
       <c r="H53" s="17" t="inlineStr">
@@ -7934,12 +7930,12 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>connectionType</t>
+          <t>taskId</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>lib/connectionType.ts</t>
+          <t>lib/taskId.ts</t>
         </is>
       </c>
       <c r="D54" s="20" t="inlineStr">
@@ -7948,16 +7944,16 @@
         </is>
       </c>
       <c r="E54" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F54" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G54" s="17" t="inlineStr">
         <is>
-          <t>ConnectionTypeTag</t>
+          <t>useWizardDraftActions</t>
         </is>
       </c>
       <c r="H54" s="17" t="inlineStr">
@@ -7974,31 +7970,35 @@
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>screenName</t>
+          <t>connectionType</t>
         </is>
       </c>
       <c r="C55" s="17" t="inlineStr">
         <is>
-          <t>lib/screenName.ts</t>
-        </is>
-      </c>
-      <c r="D55" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>lib/connectionType.ts</t>
+        </is>
+      </c>
+      <c r="D55" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E55" s="17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F55" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="G55" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G55" s="17" t="inlineStr">
+        <is>
+          <t>ConnectionTypeTag</t>
+        </is>
+      </c>
       <c r="H55" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8010,12 +8010,12 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>values</t>
+          <t>screenName</t>
         </is>
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t>lib/values.ts</t>
+          <t>lib/screenName.ts</t>
         </is>
       </c>
       <c r="D56" s="21" t="inlineStr">
@@ -8028,22 +8028,58 @@
       </c>
       <c r="F56" s="17" t="inlineStr">
         <is>
+          <t>navigation</t>
+        </is>
+      </c>
+      <c r="G56" s="17" t="inlineStr"/>
+      <c r="H56" s="17" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="17" t="inlineStr">
+        <is>
+          <t>Helper</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="inlineStr">
+        <is>
+          <t>values</t>
+        </is>
+      </c>
+      <c r="C57" s="17" t="inlineStr">
+        <is>
+          <t>lib/values.ts</t>
+        </is>
+      </c>
+      <c r="D57" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
+        </is>
+      </c>
+      <c r="E57" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="17" t="inlineStr">
+        <is>
           <t>customer360</t>
         </is>
       </c>
-      <c r="G56" s="17" t="inlineStr">
+      <c r="G57" s="17" t="inlineStr">
         <is>
           <t>customer360Demo</t>
         </is>
       </c>
-      <c r="H56" s="17" t="inlineStr">
+      <c r="H57" s="17" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H56"/>
+  <autoFilter ref="A1:H57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
+++ b/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
@@ -14,8 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Method" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'UI Components'!$A$1:$H$111</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Shared Code'!$A$1:$H$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'UI Components'!$A$1:$H$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Shared Code'!$A$1:$H$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="C5" s="17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" s="17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5" s="17" t="n">
         <v>2</v>
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="C6" s="17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6" s="17" t="n">
         <v>3</v>
@@ -739,10 +739,10 @@
         </is>
       </c>
       <c r="C8" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" s="17" t="n">
         <v>0</v>
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="C9" s="17" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D9" s="17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E9" s="17" t="n">
         <v>4</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="C12" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="D12" s="17" t="n">
         <v>7</v>
-      </c>
-      <c r="D12" s="17" t="n">
-        <v>5</v>
       </c>
       <c r="E12" s="17" t="n">
         <v>2</v>
@@ -855,14 +855,14 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>110 UI components + 56 non-UI files</t>
+          <t>113 UI components + 59 non-UI files</t>
         </is>
       </c>
       <c r="C13" s="18" t="n">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E13" s="18" t="n">
         <v>21</v>
@@ -1616,7 +1616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H111"/>
+  <dimension ref="A1:H114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.85" customWidth="1" min="1" max="1"/>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="G2" s="17" t="inlineStr">
         <is>
-          <t>CreditCheckPanel, MsisdnPicker, SimTypeStep, ActivationCompleteScreen, AppointmentBookingStep, BillingAccountStep, BulkOperationPortal, CafSignatureCapture, DonorAttachmentStep, IdLookupStep, LineSelectionStep, PrepaidCartStep, PrepaidCheckoutStep, SimSwapFormStep, TicketCreationModal, WinCashPaymentStep, ConnectionTypeTag, Tooltip</t>
+          <t>CreditCheckPanel, MsisdnPicker, SimTypeStep, ActivationCompleteScreen, AppointmentBookingStep, BillingAccountStep, BulkOperationPortal, CafSignatureCapture, DonorAttachmentStep, IdLookupStep, PrepaidCartStep, PrepaidCheckoutStep, SimSwapFormStep, TicketCreationModal, WinCashPaymentStep, ConnectionTypeTag, Tooltip</t>
         </is>
       </c>
       <c r="H2" s="17" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="G3" s="17" t="inlineStr">
         <is>
-          <t>AdditionalDocumentsUpload, CafDocumentUpload, CompanySearchInput, ContactPhoneInput, EligibilityRows, FibreReadinessBanner, MsisdnPicker, PassportScanSections, QidImageUpload, QidInput, SimSerialScanner, AppointmentBookingStep, BillingAccountStep, CafSignatureCapture, DiscountCard, FixedPlanStep, OrderConfirmationScreen, PostpaidPlanAddonsStep, PostpaidPlanCard, PrepaidPlanCard, PrepaidPlanStep, ValidationStatus, ZsbAddressStep, StepSummarySection, WizardFooter, WizardStepHeader, ChoiceCards, DataTable, IconButton, LocationInput, Pager, PhoneNumberInput, SearchField, Select, Tabs</t>
+          <t>AdditionalDocumentsUpload, CafDocumentUpload, CompanySearchInput, ContactPhoneInput, EligibilityRows, FibreReadinessBanner, MsisdnPicker, PassportScanSections, QidImageUpload, QidInput, ScanFailureNotice, SimSerialScanner, AppointmentBookingStep, BillingAccountStep, CafSignatureCapture, DiscountCard, FixedPlanStep, OrderConfirmationScreen, PostpaidPlanAddonsStep, PostpaidPlanCard, PrepaidPlanCard, PrepaidPlanStep, ValidationStatus, ZsbAddressStep, CustomerViewButton, StepSummarySection, WizardFooter, ChoiceCards, DataTable, IconButton, LocationInput, Pager, PhoneNumberInput, SearchField, Select, Tabs</t>
         </is>
       </c>
       <c r="H3" s="17" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="G4" s="17" t="inlineStr">
         <is>
-          <t>ErrorBoundary, AdditionalDocumentsUpload, BillLimitEditor, CafDocumentUpload, EligibilityRows, MsisdnPicker, PassportScanSections, QidImageUpload, QidInput, SimSerialScanner, SimTypeStep, SupportingDocumentUpload, ActivationCompleteScreen, BillingAccountStep, BillingProfileSetupDrawer, BulkOperationPortal, CafSignatureCapture, CheckoutDefaultLayout, DemoFaultPanel, FixedPlanStep, IdLookupStatus, OrderConfirmationScreen, PostpaidDiscountsPanel, PostpaidPlanCard, PrepaidCartStep, PrepaidCheckoutStep, PrepaidPackDetailsDrawer, PrepaidPlanCard, TicketCreationModal, ValidationStatus, VerificationGate, WinCashPaymentStep, ZsbAddressStep, StepSummarySection, SummaryFieldRow, WizardDialogs, WizardFooter, WizardStepHeader, WizardTitleBand, SignaturePad</t>
+          <t>ErrorBoundary, AdditionalDocumentsUpload, BillLimitEditor, CafDocumentUpload, EligibilityRows, MsisdnPicker, PassportScanSections, QidImageUpload, QidInput, SimSerialScanner, SimTypeStep, SupportingDocumentUpload, ActivationCompleteScreen, BillingAccountStep, BillingProfileSetupDrawer, BulkOperationPortal, CafSignatureCapture, CheckoutDefaultLayout, DemoFaultPanel, FixedPlanStep, IdLookupStatus, OrderConfirmationScreen, PostpaidDiscountsPanel, PostpaidPlanCard, PrepaidCartStep, PrepaidCheckoutStep, PrepaidPackDetailsDrawer, PrepaidPlanCard, TicketCreationModal, ValidationStatus, VerificationGate, WinCashPaymentStep, ZsbAddressStep, CustomerViewButton, StepSummarySection, SummaryFieldRow, WizardDialogs, WizardFooter, WizardTitleBand, SignaturePad</t>
         </is>
       </c>
       <c r="H4" s="17" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="G5" s="17" t="inlineStr">
         <is>
-          <t>AdditionalDocumentsUpload, CafDocumentUpload, MsisdnPicker, BillingAccountStep, BillingProfileSetupDrawer, BulkOperationPortal, DonorAttachmentStep, DonorDetailsStep, GuidedContactStep, TicketCreationModal, ZsbAddressStep</t>
+          <t>AdditionalDocumentsUpload, CafDocumentUpload, MsisdnPicker, BillingAccountStep, BillingProfileSetupDrawer, BulkOperationPortal, DonorDetailsStep, GuidedContactStep, TicketCreationModal, ZsbAddressStep</t>
         </is>
       </c>
       <c r="H5" s="17" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="G9" s="17" t="inlineStr">
         <is>
-          <t>WizardStepHeader, CloseButton, Tabs</t>
+          <t>CustomerViewButton, CloseButton, Tabs</t>
         </is>
       </c>
       <c r="H9" s="17" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="G16" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, QidInput, AppointmentBookingStep, BillingAccountStep, DiscountCard, FixedPlanStep, LineSelectionStep, PostpaidPlanCard, PrepaidPlanCard, PrepaidPlanStep, ChoiceCards</t>
+          <t>MsisdnPicker, QidInput, AppointmentBookingStep, BillingAccountStep, DiscountCard, FixedPlanStep, LineSelectionStep, PostpaidPlanAddonsStep, PostpaidPlanCard, PrepaidPlanCard, PrepaidPlanStep, ChoiceCards</t>
         </is>
       </c>
       <c r="H16" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G21" s="17" t="inlineStr">
         <is>
-          <t>ContactPhoneInput, GuidedContactStep</t>
+          <t>ContactPhoneInput, DonorDetailsStep, GuidedContactStep</t>
         </is>
       </c>
       <c r="H21" s="17" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H25" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>ChoiceCards</t>
+          <t>ServiceTypeTag</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/ChoiceCards.tsx</t>
+          <t>components/primitives/ServiceTypeTag.tsx</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -2693,17 +2693,21 @@
         </is>
       </c>
       <c r="E27" s="17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F27" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
-        </is>
-      </c>
-      <c r="G27" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="inlineStr">
+        <is>
+          <t>LineSelectionStep, ConnectionTypeTag</t>
+        </is>
+      </c>
       <c r="H27" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -2715,12 +2719,12 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>PanelIcon</t>
+          <t>ChoiceCards</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/PanelIcon.tsx</t>
+          <t>components/primitives/ChoiceCards.tsx</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -2733,17 +2737,13 @@
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>trouble-ticketing-complaints, navigation, administration, customer360, orders, support</t>
-        </is>
-      </c>
-      <c r="G28" s="17" t="inlineStr">
-        <is>
-          <t>Tabs</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="inlineStr"/>
       <c r="H28" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2755,12 +2755,12 @@
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>PanelIcon</t>
         </is>
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/Radio.tsx</t>
+          <t>components/primitives/PanelIcon.tsx</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -2773,10 +2773,14 @@
       </c>
       <c r="F29" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
-        </is>
-      </c>
-      <c r="G29" s="17" t="inlineStr"/>
+          <t>trouble-ticketing-complaints, navigation, administration, customer360, orders, support</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="inlineStr">
+        <is>
+          <t>Tabs</t>
+        </is>
+      </c>
       <c r="H29" s="17" t="inlineStr">
         <is>
           <t>2026-10-15</t>
@@ -2791,12 +2795,12 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>Tabs</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/Tabs.tsx</t>
+          <t>components/primitives/Radio.tsx</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -2805,17 +2809,17 @@
         </is>
       </c>
       <c r="E30" s="17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F30" s="17" t="inlineStr">
         <is>
-          <t>trouble-ticketing-complaints, administration, customer360, orders, support</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
         </is>
       </c>
       <c r="G30" s="17" t="inlineStr"/>
       <c r="H30" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2827,31 +2831,31 @@
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>VodafoneMark</t>
+          <t>Tabs</t>
         </is>
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/VodafoneMark.tsx</t>
-        </is>
-      </c>
-      <c r="D31" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>components/primitives/Tabs.tsx</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E31" s="17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F31" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
+          <t>trouble-ticketing-complaints, administration, customer360, orders, support</t>
         </is>
       </c>
       <c r="G31" s="17" t="inlineStr"/>
       <c r="H31" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2863,12 +2867,12 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>VodafoneWordmark</t>
+          <t>VodafoneMark</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/VodafoneWordmark.tsx</t>
+          <t>components/primitives/VodafoneMark.tsx</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
@@ -2899,27 +2903,31 @@
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>LocationInput</t>
+          <t>VodafoneWordmark</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/LocationInput.tsx</t>
-        </is>
-      </c>
-      <c r="D33" s="22" t="inlineStr">
-        <is>
-          <t>No consumer</t>
+          <t>components/primitives/VodafoneWordmark.tsx</t>
+        </is>
+      </c>
+      <c r="D33" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E33" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F33" s="17" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
       <c r="G33" s="17" t="inlineStr"/>
       <c r="H33" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2931,17 +2939,17 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>OoredooMark</t>
+          <t>LocationInput</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/OoredooMark.tsx</t>
-        </is>
-      </c>
-      <c r="D34" s="23" t="inlineStr">
-        <is>
-          <t>App shell only</t>
+          <t>components/primitives/LocationInput.tsx</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
+        <is>
+          <t>No consumer</t>
         </is>
       </c>
       <c r="E34" s="17" t="n">
@@ -2951,44 +2959,36 @@
       <c r="G34" s="17" t="inlineStr"/>
       <c r="H34" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="17" t="inlineStr">
         <is>
-          <t>Domain</t>
+          <t>Primitive</t>
         </is>
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>ScannedIdPreview</t>
+          <t>OoredooMark</t>
         </is>
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
-          <t>components/domain/ScannedIdPreview.tsx</t>
-        </is>
-      </c>
-      <c r="D35" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>components/primitives/OoredooMark.tsx</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="inlineStr">
+        <is>
+          <t>App shell only</t>
         </is>
       </c>
       <c r="E35" s="17" t="n">
-        <v>13</v>
-      </c>
-      <c r="F35" s="17" t="inlineStr">
-        <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, administration, customer360</t>
-        </is>
-      </c>
-      <c r="G35" s="17" t="inlineStr">
-        <is>
-          <t>PassportScanSections, QidImageUpload, qidImageUploadModel, IdScannerPanel, useIdLookup</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F35" s="17" t="inlineStr"/>
+      <c r="G35" s="17" t="inlineStr"/>
       <c r="H35" s="17" t="inlineStr">
         <is>
           <t>2026-10-15</t>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>PassportScanSections</t>
+          <t>ScannedIdPreview</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>components/domain/PassportScanSections.tsx</t>
+          <t>components/domain/ScannedIdPreview.tsx</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
@@ -3017,16 +3017,16 @@
         </is>
       </c>
       <c r="E36" s="17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F36" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G36" s="17" t="inlineStr">
         <is>
-          <t>QidImageUpload</t>
+          <t>PassportScanSections, QidImageUpload, qidImageUploadModel, IdScannerPanel, useIdLookup</t>
         </is>
       </c>
       <c r="H36" s="17" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>QidImageUpload</t>
+          <t>PassportScanSections</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>components/domain/QidImageUpload.tsx</t>
+          <t>components/domain/PassportScanSections.tsx</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
@@ -3066,12 +3066,12 @@
       </c>
       <c r="G37" s="17" t="inlineStr">
         <is>
-          <t>IdScannerPanel</t>
+          <t>QidImageUpload</t>
         </is>
       </c>
       <c r="H37" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -3083,12 +3083,12 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>QidTypeSelector</t>
+          <t>QidImageUpload</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>components/domain/QidInput.tsx</t>
+          <t>components/domain/QidImageUpload.tsx</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="G38" s="17" t="inlineStr">
         <is>
-          <t>GuidedContactStep, IdLookupStep, IdScannerPanel, MoiResultPanel, guidedContactModel, idLookupModel, useIdLookup</t>
+          <t>IdScannerPanel</t>
         </is>
       </c>
       <c r="H38" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>SimSerialScanner</t>
+          <t>QidTypeSelector</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>components/domain/SimSerialScanner.tsx</t>
+          <t>components/domain/QidInput.tsx</t>
         </is>
       </c>
       <c r="D39" s="20" t="inlineStr">
@@ -3137,21 +3137,21 @@
         </is>
       </c>
       <c r="E39" s="17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F39" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G39" s="17" t="inlineStr">
         <is>
-          <t>SimTypeStep</t>
+          <t>GuidedContactStep, IdLookupStep, IdScannerPanel, MoiResultPanel, guidedContactModel, idLookupModel, useIdLookup</t>
         </is>
       </c>
       <c r="H39" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3163,12 +3163,12 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>AdditionalDocumentsUpload</t>
+          <t>ScanFailureNotice</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>components/domain/AdditionalDocumentsUpload.tsx</t>
+          <t>components/domain/ScanFailureNotice.tsx</t>
         </is>
       </c>
       <c r="D40" s="20" t="inlineStr">
@@ -3177,21 +3177,21 @@
         </is>
       </c>
       <c r="E40" s="17" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F40" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G40" s="17" t="inlineStr">
         <is>
-          <t>CafSignatureCapture</t>
+          <t>PassportScanSections, QidImageUpload</t>
         </is>
       </c>
       <c r="H40" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -3203,12 +3203,12 @@
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>BillLimitEditor</t>
+          <t>SimSerialScanner</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>components/domain/BillLimitEditor.tsx</t>
+          <t>components/domain/SimSerialScanner.tsx</t>
         </is>
       </c>
       <c r="D41" s="20" t="inlineStr">
@@ -3217,21 +3217,21 @@
         </is>
       </c>
       <c r="E41" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F41" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G41" s="17" t="inlineStr">
         <is>
-          <t>PostpaidAddonsPanel, PostpaidPlanAddonsStep</t>
+          <t>SimTypeStep</t>
         </is>
       </c>
       <c r="H41" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>CafDocumentUpload</t>
+          <t>AdditionalDocumentsUpload</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>components/domain/CafDocumentUpload.tsx</t>
+          <t>components/domain/AdditionalDocumentsUpload.tsx</t>
         </is>
       </c>
       <c r="D42" s="20" t="inlineStr">
@@ -3283,12 +3283,12 @@
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>CompanySearchInput</t>
+          <t>BillLimitEditor</t>
         </is>
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>components/domain/CompanySearchInput.tsx</t>
+          <t>components/domain/BillLimitEditor.tsx</t>
         </is>
       </c>
       <c r="D43" s="20" t="inlineStr">
@@ -3304,7 +3304,11 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G43" s="17" t="inlineStr"/>
+      <c r="G43" s="17" t="inlineStr">
+        <is>
+          <t>PostpaidAddonsPanel, PostpaidPlanAddonsStep</t>
+        </is>
+      </c>
       <c r="H43" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
@@ -3319,12 +3323,12 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>CreditCheckPanel</t>
+          <t>CafDocumentUpload</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>components/domain/CreditCheckPanel.tsx</t>
+          <t>components/domain/CafDocumentUpload.tsx</t>
         </is>
       </c>
       <c r="D44" s="20" t="inlineStr">
@@ -3342,7 +3346,7 @@
       </c>
       <c r="G44" s="17" t="inlineStr">
         <is>
-          <t>FixedPlanStep</t>
+          <t>CafSignatureCapture</t>
         </is>
       </c>
       <c r="H44" s="17" t="inlineStr">
@@ -3359,12 +3363,12 @@
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>EligibilityChecksList</t>
+          <t>CompanySearchInput</t>
         </is>
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>components/domain/EligibilityRows.tsx</t>
+          <t>components/domain/CompanySearchInput.tsx</t>
         </is>
       </c>
       <c r="D45" s="20" t="inlineStr">
@@ -3395,12 +3399,12 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>EsimActivationPanel</t>
+          <t>CreditCheckPanel</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>components/domain/EsimActivationPanel.tsx</t>
+          <t>components/domain/CreditCheckPanel.tsx</t>
         </is>
       </c>
       <c r="D46" s="20" t="inlineStr">
@@ -3418,12 +3422,12 @@
       </c>
       <c r="G46" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen</t>
+          <t>FixedPlanStep</t>
         </is>
       </c>
       <c r="H46" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3435,12 +3439,12 @@
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker</t>
+          <t>EligibilityChecksList</t>
         </is>
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>components/domain/MsisdnPicker.tsx</t>
+          <t>components/domain/EligibilityRows.tsx</t>
         </is>
       </c>
       <c r="D47" s="20" t="inlineStr">
@@ -3453,7 +3457,7 @@
       </c>
       <c r="F47" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G47" s="17" t="inlineStr"/>
@@ -3471,12 +3475,12 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>SimTypeStep</t>
+          <t>EsimActivationPanel</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>components/domain/SimTypeStep.tsx</t>
+          <t>components/domain/EsimActivationPanel.tsx</t>
         </is>
       </c>
       <c r="D48" s="20" t="inlineStr">
@@ -3494,7 +3498,7 @@
       </c>
       <c r="G48" s="17" t="inlineStr">
         <is>
-          <t>CheckoutSummaryStep, checkoutDetailedTables, checkoutSummaryRows, prepaidCartModel, useCheckoutSummary</t>
+          <t>ActivationCompleteScreen</t>
         </is>
       </c>
       <c r="H48" s="17" t="inlineStr">
@@ -3511,12 +3515,12 @@
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>StarStat</t>
+          <t>MsisdnPicker</t>
         </is>
       </c>
       <c r="C49" s="17" t="inlineStr">
         <is>
-          <t>components/domain/StarStat.tsx</t>
+          <t>components/domain/MsisdnPicker.tsx</t>
         </is>
       </c>
       <c r="D49" s="20" t="inlineStr">
@@ -3532,11 +3536,7 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
-      <c r="G49" s="17" t="inlineStr">
-        <is>
-          <t>MsisdnPicker</t>
-        </is>
-      </c>
+      <c r="G49" s="17" t="inlineStr"/>
       <c r="H49" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
@@ -3551,12 +3551,12 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>SupportingDocumentUpload</t>
+          <t>SimTypeStep</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>components/domain/SupportingDocumentUpload.tsx</t>
+          <t>components/domain/SimTypeStep.tsx</t>
         </is>
       </c>
       <c r="D50" s="20" t="inlineStr">
@@ -3572,10 +3572,14 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G50" s="17" t="inlineStr"/>
+      <c r="G50" s="17" t="inlineStr">
+        <is>
+          <t>CheckoutSummaryStep, checkoutDetailedTables, checkoutSummaryRows, prepaidCartModel, useCheckoutSummary</t>
+        </is>
+      </c>
       <c r="H50" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3591,12 @@
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>FibreReadinessBanner</t>
+          <t>StarStat</t>
         </is>
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>components/domain/FibreReadinessBanner.tsx</t>
+          <t>components/domain/StarStat.tsx</t>
         </is>
       </c>
       <c r="D51" s="20" t="inlineStr">
@@ -3601,16 +3605,16 @@
         </is>
       </c>
       <c r="E51" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F51" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G51" s="17" t="inlineStr">
         <is>
-          <t>ZsbAddressStep</t>
+          <t>MsisdnPicker</t>
         </is>
       </c>
       <c r="H51" s="17" t="inlineStr">
@@ -3627,31 +3631,31 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>ContactPhoneInput</t>
+          <t>SupportingDocumentUpload</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>components/domain/ContactPhoneInput.tsx</t>
-        </is>
-      </c>
-      <c r="D52" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>components/domain/SupportingDocumentUpload.tsx</t>
+        </is>
+      </c>
+      <c r="D52" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E52" s="17" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F52" s="17" t="inlineStr">
         <is>
-          <t>customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G52" s="17" t="inlineStr"/>
       <c r="H52" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3663,35 +3667,35 @@
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>CpeSerialScanner</t>
+          <t>FibreReadinessBanner</t>
         </is>
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>components/domain/CpeSerialScanner.tsx</t>
-        </is>
-      </c>
-      <c r="D53" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>components/domain/FibreReadinessBanner.tsx</t>
+        </is>
+      </c>
+      <c r="D53" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E53" s="17" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F53" s="17" t="inlineStr">
         <is>
-          <t>fwa-5g-home</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G53" s="17" t="inlineStr">
         <is>
-          <t>DualPlaySerialCheckStep</t>
+          <t>ZsbAddressStep</t>
         </is>
       </c>
       <c r="H53" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3703,12 +3707,12 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>OsmEmbed</t>
+          <t>ContactPhoneInput</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>components/domain/OsmEmbed.tsx</t>
+          <t>components/domain/ContactPhoneInput.tsx</t>
         </is>
       </c>
       <c r="D54" s="21" t="inlineStr">
@@ -3727,79 +3731,83 @@
       <c r="G54" s="17" t="inlineStr"/>
       <c r="H54" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="17" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>PageHeader</t>
+          <t>CpeSerialScanner</t>
         </is>
       </c>
       <c r="C55" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PageHeader.tsx</t>
-        </is>
-      </c>
-      <c r="D55" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>components/domain/CpeSerialScanner.tsx</t>
+        </is>
+      </c>
+      <c r="D55" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E55" s="17" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F55" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fwa-5g-home, lead-management, mnp-fnp-porting, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
-        </is>
-      </c>
-      <c r="G55" s="17" t="inlineStr"/>
+          <t>fwa-5g-home</t>
+        </is>
+      </c>
+      <c r="G55" s="17" t="inlineStr">
+        <is>
+          <t>DualPlaySerialCheckStep</t>
+        </is>
+      </c>
       <c r="H55" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="17" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>GuidedContactStep</t>
+          <t>OsmEmbed</t>
         </is>
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/GuidedContactStep.tsx</t>
-        </is>
-      </c>
-      <c r="D56" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>components/domain/OsmEmbed.tsx</t>
+        </is>
+      </c>
+      <c r="D56" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E56" s="17" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F56" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>customer360</t>
         </is>
       </c>
       <c r="G56" s="17" t="inlineStr"/>
       <c r="H56" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -3811,12 +3819,12 @@
       </c>
       <c r="B57" s="17" t="inlineStr">
         <is>
-          <t>IdLookupStatus</t>
+          <t>PageHeader</t>
         </is>
       </c>
       <c r="C57" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/IdLookupStatus.tsx</t>
+          <t>components/patterns/PageHeader.tsx</t>
         </is>
       </c>
       <c r="D57" s="20" t="inlineStr">
@@ -3825,21 +3833,17 @@
         </is>
       </c>
       <c r="E57" s="17" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F57" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
-        </is>
-      </c>
-      <c r="G57" s="17" t="inlineStr">
-        <is>
-          <t>IdLookupStep</t>
-        </is>
-      </c>
+          <t>enterprise-iot-b2b, fwa-5g-home, lead-management, mnp-fnp-porting, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
+        </is>
+      </c>
+      <c r="G57" s="17" t="inlineStr"/>
       <c r="H57" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3851,12 +3855,12 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>IdLookupStep</t>
+          <t>GuidedContactStep</t>
         </is>
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/IdLookupStep.tsx</t>
+          <t>components/patterns/GuidedContactStep.tsx</t>
         </is>
       </c>
       <c r="D58" s="20" t="inlineStr">
@@ -3872,14 +3876,10 @@
           <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
-      <c r="G58" s="17" t="inlineStr">
-        <is>
-          <t>GuidedContactStep</t>
-        </is>
-      </c>
+      <c r="G58" s="17" t="inlineStr"/>
       <c r="H58" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3891,12 +3891,12 @@
       </c>
       <c r="B59" s="17" t="inlineStr">
         <is>
-          <t>IdScannerPanel</t>
+          <t>IdLookupStatus</t>
         </is>
       </c>
       <c r="C59" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/IdScannerPanel.tsx</t>
+          <t>components/patterns/IdLookupStatus.tsx</t>
         </is>
       </c>
       <c r="D59" s="20" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>MoiResultPanel</t>
+          <t>IdLookupStep</t>
         </is>
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/MoiResultPanel.tsx</t>
+          <t>components/patterns/IdLookupStep.tsx</t>
         </is>
       </c>
       <c r="D60" s="20" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="G60" s="17" t="inlineStr">
         <is>
-          <t>IdLookupStep</t>
+          <t>GuidedContactStep</t>
         </is>
       </c>
       <c r="H60" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -3971,12 +3971,12 @@
       </c>
       <c r="B61" s="17" t="inlineStr">
         <is>
-          <t>ValidationStatus</t>
+          <t>IdScannerPanel</t>
         </is>
       </c>
       <c r="C61" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/ValidationStatus.tsx</t>
+          <t>components/patterns/IdScannerPanel.tsx</t>
         </is>
       </c>
       <c r="D61" s="20" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="G61" s="17" t="inlineStr">
         <is>
-          <t>IdLookupStatus</t>
+          <t>IdLookupStep</t>
         </is>
       </c>
       <c r="H61" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -4011,12 +4011,12 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>SignatureCapture</t>
+          <t>MoiResultPanel</t>
         </is>
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/SignatureCapture.tsx</t>
+          <t>components/patterns/MoiResultPanel.tsx</t>
         </is>
       </c>
       <c r="D62" s="20" t="inlineStr">
@@ -4025,21 +4025,21 @@
         </is>
       </c>
       <c r="E62" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F62" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G62" s="17" t="inlineStr">
         <is>
-          <t>CafSignatureCapture, DonorAttachmentStep, SimSwapFormStep</t>
+          <t>IdLookupStep</t>
         </is>
       </c>
       <c r="H62" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="B63" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen</t>
+          <t>ValidationStatus</t>
         </is>
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/ActivationCompleteScreen.tsx</t>
+          <t>components/patterns/ValidationStatus.tsx</t>
         </is>
       </c>
       <c r="D63" s="20" t="inlineStr">
@@ -4065,17 +4065,21 @@
         </is>
       </c>
       <c r="E63" s="17" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F63" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G63" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G63" s="17" t="inlineStr">
+        <is>
+          <t>IdLookupStatus</t>
+        </is>
+      </c>
       <c r="H63" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4087,12 +4091,12 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>BillingAccountAutoResolver</t>
+          <t>SignatureCapture</t>
         </is>
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/BillingAccountAutoResolver.tsx</t>
+          <t>components/patterns/SignatureCapture.tsx</t>
         </is>
       </c>
       <c r="D64" s="20" t="inlineStr">
@@ -4101,17 +4105,21 @@
         </is>
       </c>
       <c r="E64" s="17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F64" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G64" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+      <c r="G64" s="17" t="inlineStr">
+        <is>
+          <t>CafSignatureCapture, DonorAttachmentStep, SimSwapFormStep</t>
+        </is>
+      </c>
       <c r="H64" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4123,12 +4131,12 @@
       </c>
       <c r="B65" s="17" t="inlineStr">
         <is>
-          <t>CafSignatureCapture</t>
+          <t>ActivationCompleteScreen</t>
         </is>
       </c>
       <c r="C65" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CafSignatureCapture.tsx</t>
+          <t>components/patterns/ActivationCompleteScreen.tsx</t>
         </is>
       </c>
       <c r="D65" s="20" t="inlineStr">
@@ -4159,12 +4167,12 @@
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>CheckoutDefaultLayout</t>
+          <t>BillingAccountAutoResolver</t>
         </is>
       </c>
       <c r="C66" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CheckoutDefaultLayout.tsx</t>
+          <t>components/patterns/BillingAccountAutoResolver.tsx</t>
         </is>
       </c>
       <c r="D66" s="20" t="inlineStr">
@@ -4180,14 +4188,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G66" s="17" t="inlineStr">
-        <is>
-          <t>CheckoutSummaryStep</t>
-        </is>
-      </c>
+      <c r="G66" s="17" t="inlineStr"/>
       <c r="H66" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4199,12 +4203,12 @@
       </c>
       <c r="B67" s="17" t="inlineStr">
         <is>
-          <t>CheckoutSummaryStep</t>
+          <t>CafSignatureCapture</t>
         </is>
       </c>
       <c r="C67" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CheckoutSummaryStep.tsx</t>
+          <t>components/patterns/CafSignatureCapture.tsx</t>
         </is>
       </c>
       <c r="D67" s="20" t="inlineStr">
@@ -4223,7 +4227,7 @@
       <c r="G67" s="17" t="inlineStr"/>
       <c r="H67" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4235,12 +4239,12 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>DiscountCard</t>
+          <t>CheckoutDefaultLayout</t>
         </is>
       </c>
       <c r="C68" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DiscountCard.tsx</t>
+          <t>components/patterns/CheckoutDefaultLayout.tsx</t>
         </is>
       </c>
       <c r="D68" s="20" t="inlineStr">
@@ -4258,12 +4262,12 @@
       </c>
       <c r="G68" s="17" t="inlineStr">
         <is>
-          <t>PostpaidDiscountsPanel</t>
+          <t>CheckoutSummaryStep</t>
         </is>
       </c>
       <c r="H68" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4275,12 +4279,12 @@
       </c>
       <c r="B69" s="17" t="inlineStr">
         <is>
-          <t>FixedPlanStep</t>
+          <t>CheckoutSummaryStep</t>
         </is>
       </c>
       <c r="C69" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/FixedPlanStep.tsx</t>
+          <t>components/patterns/CheckoutSummaryStep.tsx</t>
         </is>
       </c>
       <c r="D69" s="20" t="inlineStr">
@@ -4299,7 +4303,7 @@
       <c r="G69" s="17" t="inlineStr"/>
       <c r="H69" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4311,12 +4315,12 @@
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>FullTerms</t>
+          <t>DiscountCard</t>
         </is>
       </c>
       <c r="C70" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CafTerms.tsx</t>
+          <t>components/patterns/DiscountCard.tsx</t>
         </is>
       </c>
       <c r="D70" s="20" t="inlineStr">
@@ -4334,7 +4338,7 @@
       </c>
       <c r="G70" s="17" t="inlineStr">
         <is>
-          <t>CafSignatureCapture</t>
+          <t>PostpaidDiscountsPanel</t>
         </is>
       </c>
       <c r="H70" s="17" t="inlineStr">
@@ -4351,12 +4355,12 @@
       </c>
       <c r="B71" s="17" t="inlineStr">
         <is>
-          <t>KeyInformationPanel</t>
+          <t>FixedPlanStep</t>
         </is>
       </c>
       <c r="C71" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/KeyInformationPanel.tsx</t>
+          <t>components/patterns/FixedPlanStep.tsx</t>
         </is>
       </c>
       <c r="D71" s="20" t="inlineStr">
@@ -4375,7 +4379,7 @@
       <c r="G71" s="17" t="inlineStr"/>
       <c r="H71" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4387,12 +4391,12 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>OrderConfirmationScreen</t>
+          <t>FullTerms</t>
         </is>
       </c>
       <c r="C72" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/OrderConfirmationScreen.tsx</t>
+          <t>components/patterns/CafTerms.tsx</t>
         </is>
       </c>
       <c r="D72" s="20" t="inlineStr">
@@ -4410,12 +4414,12 @@
       </c>
       <c r="G72" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen</t>
+          <t>CafSignatureCapture</t>
         </is>
       </c>
       <c r="H72" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4427,12 +4431,12 @@
       </c>
       <c r="B73" s="17" t="inlineStr">
         <is>
-          <t>PlanDetailsDrawer</t>
+          <t>KeyInformationPanel</t>
         </is>
       </c>
       <c r="C73" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PlanDetailsDrawer.tsx</t>
+          <t>components/patterns/KeyInformationPanel.tsx</t>
         </is>
       </c>
       <c r="D73" s="20" t="inlineStr">
@@ -4448,11 +4452,7 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G73" s="17" t="inlineStr">
-        <is>
-          <t>PostpaidPlanAddonsStep</t>
-        </is>
-      </c>
+      <c r="G73" s="17" t="inlineStr"/>
       <c r="H73" s="17" t="inlineStr">
         <is>
           <t>2026-10-15</t>
@@ -4467,12 +4467,12 @@
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>PlanGroupPanel</t>
+          <t>OrderConfirmationScreen</t>
         </is>
       </c>
       <c r="C74" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PlanGroupPanel.tsx</t>
+          <t>components/patterns/OrderConfirmationScreen.tsx</t>
         </is>
       </c>
       <c r="D74" s="20" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="G74" s="17" t="inlineStr">
         <is>
-          <t>PostpaidPlanAddonsStep</t>
+          <t>ActivationCompleteScreen</t>
         </is>
       </c>
       <c r="H74" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4507,12 +4507,12 @@
       </c>
       <c r="B75" s="17" t="inlineStr">
         <is>
-          <t>PlanSearchBox</t>
+          <t>PlanDetailsDrawer</t>
         </is>
       </c>
       <c r="C75" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PlanSearchBox.tsx</t>
+          <t>components/patterns/PlanDetailsDrawer.tsx</t>
         </is>
       </c>
       <c r="D75" s="20" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>PlanTabStrip</t>
+          <t>PlanGroupPanel</t>
         </is>
       </c>
       <c r="C76" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PlanTabStrip.tsx</t>
+          <t>components/patterns/PlanGroupPanel.tsx</t>
         </is>
       </c>
       <c r="D76" s="20" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H76" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4587,12 +4587,12 @@
       </c>
       <c r="B77" s="17" t="inlineStr">
         <is>
-          <t>PostpaidAddonsPanel</t>
+          <t>PlanSearchBox</t>
         </is>
       </c>
       <c r="C77" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidAddonsPanel.tsx</t>
+          <t>components/patterns/PlanSearchBox.tsx</t>
         </is>
       </c>
       <c r="D77" s="20" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="H77" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="B78" s="17" t="inlineStr">
         <is>
-          <t>PostpaidDiscountsPanel</t>
+          <t>PlanTabStrip</t>
         </is>
       </c>
       <c r="C78" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidDiscountsPanel.tsx</t>
+          <t>components/patterns/PlanTabStrip.tsx</t>
         </is>
       </c>
       <c r="D78" s="20" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="H78" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4667,12 +4667,12 @@
       </c>
       <c r="B79" s="17" t="inlineStr">
         <is>
-          <t>PostpaidMonthlySummary</t>
+          <t>PostpaidAddonsPanel</t>
         </is>
       </c>
       <c r="C79" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidMonthlySummary.tsx</t>
+          <t>components/patterns/PostpaidAddonsPanel.tsx</t>
         </is>
       </c>
       <c r="D79" s="20" t="inlineStr">
@@ -4707,12 +4707,12 @@
       </c>
       <c r="B80" s="17" t="inlineStr">
         <is>
-          <t>PostpaidPlanAddonsStep</t>
+          <t>PostpaidDiscountsPanel</t>
         </is>
       </c>
       <c r="C80" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidPlanAddonsStep.tsx</t>
+          <t>components/patterns/PostpaidDiscountsPanel.tsx</t>
         </is>
       </c>
       <c r="D80" s="20" t="inlineStr">
@@ -4728,10 +4728,14 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G80" s="17" t="inlineStr"/>
+      <c r="G80" s="17" t="inlineStr">
+        <is>
+          <t>PostpaidPlanAddonsStep</t>
+        </is>
+      </c>
       <c r="H80" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4743,12 +4747,12 @@
       </c>
       <c r="B81" s="17" t="inlineStr">
         <is>
-          <t>PostpaidPlanCard</t>
+          <t>PostpaidMonthlySummary</t>
         </is>
       </c>
       <c r="C81" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidPlanCard.tsx</t>
+          <t>components/patterns/PostpaidMonthlySummary.tsx</t>
         </is>
       </c>
       <c r="D81" s="20" t="inlineStr">
@@ -4766,7 +4770,7 @@
       </c>
       <c r="G81" s="17" t="inlineStr">
         <is>
-          <t>PlanGroupPanel</t>
+          <t>PostpaidPlanAddonsStep</t>
         </is>
       </c>
       <c r="H81" s="17" t="inlineStr">
@@ -4783,12 +4787,12 @@
       </c>
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>PrepaidCartStep</t>
+          <t>PostpaidPlanAddonsStep</t>
         </is>
       </c>
       <c r="C82" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidCartStep.tsx</t>
+          <t>components/patterns/PostpaidPlanAddonsStep.tsx</t>
         </is>
       </c>
       <c r="D82" s="20" t="inlineStr">
@@ -4807,7 +4811,7 @@
       <c r="G82" s="17" t="inlineStr"/>
       <c r="H82" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -4819,12 +4823,12 @@
       </c>
       <c r="B83" s="17" t="inlineStr">
         <is>
-          <t>PrepaidCheckoutStep</t>
+          <t>PostpaidPlanCard</t>
         </is>
       </c>
       <c r="C83" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidCheckoutStep.tsx</t>
+          <t>components/patterns/PostpaidPlanCard.tsx</t>
         </is>
       </c>
       <c r="D83" s="20" t="inlineStr">
@@ -4840,7 +4844,11 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G83" s="17" t="inlineStr"/>
+      <c r="G83" s="17" t="inlineStr">
+        <is>
+          <t>PlanGroupPanel</t>
+        </is>
+      </c>
       <c r="H83" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
@@ -4855,12 +4863,12 @@
       </c>
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>PrepaidPackDetailsDrawer</t>
+          <t>PrepaidCartStep</t>
         </is>
       </c>
       <c r="C84" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidPackDetailsDrawer.tsx</t>
+          <t>components/patterns/PrepaidCartStep.tsx</t>
         </is>
       </c>
       <c r="D84" s="20" t="inlineStr">
@@ -4876,14 +4884,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G84" s="17" t="inlineStr">
-        <is>
-          <t>PrepaidPlanStep</t>
-        </is>
-      </c>
+      <c r="G84" s="17" t="inlineStr"/>
       <c r="H84" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4895,12 +4899,12 @@
       </c>
       <c r="B85" s="17" t="inlineStr">
         <is>
-          <t>PrepaidPlanCard</t>
+          <t>PrepaidCheckoutStep</t>
         </is>
       </c>
       <c r="C85" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidPlanCard.tsx</t>
+          <t>components/patterns/PrepaidCheckoutStep.tsx</t>
         </is>
       </c>
       <c r="D85" s="20" t="inlineStr">
@@ -4916,11 +4920,7 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G85" s="17" t="inlineStr">
-        <is>
-          <t>PrepaidPlanStep</t>
-        </is>
-      </c>
+      <c r="G85" s="17" t="inlineStr"/>
       <c r="H85" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>PrepaidPlanStep</t>
+          <t>PrepaidPackDetailsDrawer</t>
         </is>
       </c>
       <c r="C86" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidPlanStep.tsx</t>
+          <t>components/patterns/PrepaidPackDetailsDrawer.tsx</t>
         </is>
       </c>
       <c r="D86" s="20" t="inlineStr">
@@ -4956,7 +4956,11 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G86" s="17" t="inlineStr"/>
+      <c r="G86" s="17" t="inlineStr">
+        <is>
+          <t>PrepaidPlanStep</t>
+        </is>
+      </c>
       <c r="H86" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
@@ -4971,12 +4975,12 @@
       </c>
       <c r="B87" s="17" t="inlineStr">
         <is>
-          <t>SummaryTables</t>
+          <t>PrepaidPlanCard</t>
         </is>
       </c>
       <c r="C87" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CheckoutSummaryTables.tsx</t>
+          <t>components/patterns/PrepaidPlanCard.tsx</t>
         </is>
       </c>
       <c r="D87" s="20" t="inlineStr">
@@ -4994,12 +4998,12 @@
       </c>
       <c r="G87" s="17" t="inlineStr">
         <is>
-          <t>CheckoutSummaryStep, checkoutDetailedTables</t>
+          <t>PrepaidPlanStep</t>
         </is>
       </c>
       <c r="H87" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5011,12 +5015,12 @@
       </c>
       <c r="B88" s="17" t="inlineStr">
         <is>
-          <t>WinCashPaymentStep</t>
+          <t>PrepaidPlanStep</t>
         </is>
       </c>
       <c r="C88" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/WinCashPaymentStep.tsx</t>
+          <t>components/patterns/PrepaidPlanStep.tsx</t>
         </is>
       </c>
       <c r="D88" s="20" t="inlineStr">
@@ -5035,7 +5039,7 @@
       <c r="G88" s="17" t="inlineStr"/>
       <c r="H88" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5047,12 +5051,12 @@
       </c>
       <c r="B89" s="17" t="inlineStr">
         <is>
-          <t>BillingAccountStep</t>
+          <t>SummaryTables</t>
         </is>
       </c>
       <c r="C89" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/BillingAccountStep.tsx</t>
+          <t>components/patterns/CheckoutSummaryTables.tsx</t>
         </is>
       </c>
       <c r="D89" s="20" t="inlineStr">
@@ -5061,17 +5065,21 @@
         </is>
       </c>
       <c r="E89" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F89" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G89" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G89" s="17" t="inlineStr">
+        <is>
+          <t>CheckoutSummaryStep, checkoutDetailedTables</t>
+        </is>
+      </c>
       <c r="H89" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5091,12 @@
       </c>
       <c r="B90" s="17" t="inlineStr">
         <is>
-          <t>BillingProfileSetupDrawer</t>
+          <t>WinCashPaymentStep</t>
         </is>
       </c>
       <c r="C90" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/BillingProfileSetupDrawer.tsx</t>
+          <t>components/patterns/WinCashPaymentStep.tsx</t>
         </is>
       </c>
       <c r="D90" s="20" t="inlineStr">
@@ -5097,18 +5105,14 @@
         </is>
       </c>
       <c r="E90" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F90" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G90" s="17" t="inlineStr">
-        <is>
-          <t>BillingAccountStep</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G90" s="17" t="inlineStr"/>
       <c r="H90" s="17" t="inlineStr">
         <is>
           <t>2026-10-15</t>
@@ -5123,12 +5127,12 @@
       </c>
       <c r="B91" s="17" t="inlineStr">
         <is>
-          <t>ZsbAddressStep</t>
+          <t>BillingAccountStep</t>
         </is>
       </c>
       <c r="C91" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/ZsbAddressStep.tsx</t>
+          <t>components/patterns/BillingAccountStep.tsx</t>
         </is>
       </c>
       <c r="D91" s="20" t="inlineStr">
@@ -5159,12 +5163,12 @@
       </c>
       <c r="B92" s="17" t="inlineStr">
         <is>
-          <t>AppointmentBookingStep</t>
+          <t>BillingProfileSetupDrawer</t>
         </is>
       </c>
       <c r="C92" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/AppointmentBookingStep.tsx</t>
+          <t>components/patterns/BillingProfileSetupDrawer.tsx</t>
         </is>
       </c>
       <c r="D92" s="20" t="inlineStr">
@@ -5173,17 +5177,21 @@
         </is>
       </c>
       <c r="E92" s="17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F92" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, administration</t>
-        </is>
-      </c>
-      <c r="G92" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G92" s="17" t="inlineStr">
+        <is>
+          <t>BillingAccountStep</t>
+        </is>
+      </c>
       <c r="H92" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5203,12 @@
       </c>
       <c r="B93" s="17" t="inlineStr">
         <is>
-          <t>DemoFaultPanel</t>
+          <t>ZsbAddressStep</t>
         </is>
       </c>
       <c r="C93" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DemoFaultPanel.tsx</t>
+          <t>components/patterns/ZsbAddressStep.tsx</t>
         </is>
       </c>
       <c r="D93" s="20" t="inlineStr">
@@ -5209,17 +5217,17 @@
         </is>
       </c>
       <c r="E93" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F93" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G93" s="17" t="inlineStr"/>
       <c r="H93" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5231,12 +5239,12 @@
       </c>
       <c r="B94" s="17" t="inlineStr">
         <is>
-          <t>DonorAttachmentStep</t>
+          <t>AppointmentBookingStep</t>
         </is>
       </c>
       <c r="C94" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DonorAttachmentStep.tsx</t>
+          <t>components/patterns/AppointmentBookingStep.tsx</t>
         </is>
       </c>
       <c r="D94" s="20" t="inlineStr">
@@ -5245,17 +5253,17 @@
         </is>
       </c>
       <c r="E94" s="17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F94" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, administration</t>
         </is>
       </c>
       <c r="G94" s="17" t="inlineStr"/>
       <c r="H94" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5267,12 +5275,12 @@
       </c>
       <c r="B95" s="17" t="inlineStr">
         <is>
-          <t>DonorDetailsStep</t>
+          <t>DemoFaultPanel</t>
         </is>
       </c>
       <c r="C95" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DonorDetailsStep.tsx</t>
+          <t>components/patterns/DemoFaultPanel.tsx</t>
         </is>
       </c>
       <c r="D95" s="20" t="inlineStr">
@@ -5288,14 +5296,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
         </is>
       </c>
-      <c r="G95" s="17" t="inlineStr">
-        <is>
-          <t>DonorAttachmentStep</t>
-        </is>
-      </c>
+      <c r="G95" s="17" t="inlineStr"/>
       <c r="H95" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5307,12 +5311,12 @@
       </c>
       <c r="B96" s="17" t="inlineStr">
         <is>
-          <t>EntityMissing</t>
+          <t>DonorAttachmentStep</t>
         </is>
       </c>
       <c r="C96" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/EntityMissing.tsx</t>
+          <t>components/patterns/DonorAttachmentStep.tsx</t>
         </is>
       </c>
       <c r="D96" s="20" t="inlineStr">
@@ -5325,13 +5329,13 @@
       </c>
       <c r="F96" s="17" t="inlineStr">
         <is>
-          <t>lead-management, order-management, sim-number-management, trouble-ticketing-complaints, customer360, tasks</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
         </is>
       </c>
       <c r="G96" s="17" t="inlineStr"/>
       <c r="H96" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5343,12 +5347,12 @@
       </c>
       <c r="B97" s="17" t="inlineStr">
         <is>
-          <t>ActivityCommentsStep</t>
+          <t>DonorDetailsStep</t>
         </is>
       </c>
       <c r="C97" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/ActivityCommentsStep.tsx</t>
+          <t>components/patterns/DonorDetailsStep.tsx</t>
         </is>
       </c>
       <c r="D97" s="20" t="inlineStr">
@@ -5357,17 +5361,21 @@
         </is>
       </c>
       <c r="E97" s="17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F97" s="17" t="inlineStr">
         <is>
-          <t>pre-to-post-migration, sim-number-management, administration</t>
-        </is>
-      </c>
-      <c r="G97" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
+        </is>
+      </c>
+      <c r="G97" s="17" t="inlineStr">
+        <is>
+          <t>DonorAttachmentStep</t>
+        </is>
+      </c>
       <c r="H97" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5379,12 +5387,12 @@
       </c>
       <c r="B98" s="17" t="inlineStr">
         <is>
-          <t>LineSelectionStep</t>
+          <t>EntityMissing</t>
         </is>
       </c>
       <c r="C98" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/LineSelectionStep.tsx</t>
+          <t>components/patterns/EntityMissing.tsx</t>
         </is>
       </c>
       <c r="D98" s="20" t="inlineStr">
@@ -5393,17 +5401,17 @@
         </is>
       </c>
       <c r="E98" s="17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F98" s="17" t="inlineStr">
         <is>
-          <t>mobile-service-changes, pre-to-post-migration, administration</t>
+          <t>lead-management, order-management, sim-number-management, trouble-ticketing-complaints, customer360, tasks</t>
         </is>
       </c>
       <c r="G98" s="17" t="inlineStr"/>
       <c r="H98" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5415,12 +5423,12 @@
       </c>
       <c r="B99" s="17" t="inlineStr">
         <is>
-          <t>TicketCreationModal</t>
+          <t>ActivityCommentsStep</t>
         </is>
       </c>
       <c r="C99" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/TicketCreationModal.tsx</t>
+          <t>components/patterns/ActivityCommentsStep.tsx</t>
         </is>
       </c>
       <c r="D99" s="20" t="inlineStr">
@@ -5433,13 +5441,13 @@
       </c>
       <c r="F99" s="17" t="inlineStr">
         <is>
-          <t>trouble-ticketing-complaints, customer360, support</t>
+          <t>pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G99" s="17" t="inlineStr"/>
       <c r="H99" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -5451,31 +5459,31 @@
       </c>
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>BulkOperationPortal</t>
+          <t>LineSelectionStep</t>
         </is>
       </c>
       <c r="C100" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/BulkOperationPortal.tsx</t>
-        </is>
-      </c>
-      <c r="D100" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>components/patterns/LineSelectionStep.tsx</t>
+        </is>
+      </c>
+      <c r="D100" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E100" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F100" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b</t>
+          <t>mobile-service-changes, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G100" s="17" t="inlineStr"/>
       <c r="H100" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5487,25 +5495,25 @@
       </c>
       <c r="B101" s="17" t="inlineStr">
         <is>
-          <t>DualPlaySerialCheckStep</t>
+          <t>TicketCreationModal</t>
         </is>
       </c>
       <c r="C101" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DualPlaySerialCheckStep.tsx</t>
-        </is>
-      </c>
-      <c r="D101" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>components/patterns/TicketCreationModal.tsx</t>
+        </is>
+      </c>
+      <c r="D101" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E101" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F101" s="17" t="inlineStr">
         <is>
-          <t>fwa-5g-home</t>
+          <t>trouble-ticketing-complaints, customer360, support</t>
         </is>
       </c>
       <c r="G101" s="17" t="inlineStr"/>
@@ -5523,12 +5531,12 @@
       </c>
       <c r="B102" s="17" t="inlineStr">
         <is>
-          <t>SimSwapFormStep</t>
+          <t>BulkOperationPortal</t>
         </is>
       </c>
       <c r="C102" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/SimSwapFormStep.tsx</t>
+          <t>components/patterns/BulkOperationPortal.tsx</t>
         </is>
       </c>
       <c r="D102" s="21" t="inlineStr">
@@ -5541,7 +5549,7 @@
       </c>
       <c r="F102" s="17" t="inlineStr">
         <is>
-          <t>sim-number-management</t>
+          <t>enterprise-iot-b2b</t>
         </is>
       </c>
       <c r="G102" s="17" t="inlineStr"/>
@@ -5559,12 +5567,12 @@
       </c>
       <c r="B103" s="17" t="inlineStr">
         <is>
-          <t>VerificationGate</t>
+          <t>DualPlaySerialCheckStep</t>
         </is>
       </c>
       <c r="C103" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/VerificationGate.tsx</t>
+          <t>components/patterns/DualPlaySerialCheckStep.tsx</t>
         </is>
       </c>
       <c r="D103" s="21" t="inlineStr">
@@ -5577,7 +5585,7 @@
       </c>
       <c r="F103" s="17" t="inlineStr">
         <is>
-          <t>customer360</t>
+          <t>fwa-5g-home</t>
         </is>
       </c>
       <c r="G103" s="17" t="inlineStr"/>
@@ -5590,30 +5598,30 @@
     <row r="104">
       <c r="A104" s="17" t="inlineStr">
         <is>
-          <t>Wizard</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="B104" s="17" t="inlineStr">
         <is>
-          <t>AbandonDialog</t>
+          <t>SimSwapFormStep</t>
         </is>
       </c>
       <c r="C104" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/WizardDialogs.tsx</t>
-        </is>
-      </c>
-      <c r="D104" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>components/patterns/SimSwapFormStep.tsx</t>
+        </is>
+      </c>
+      <c r="D104" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E104" s="17" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F104" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>sim-number-management</t>
         </is>
       </c>
       <c r="G104" s="17" t="inlineStr"/>
@@ -5626,30 +5634,30 @@
     <row r="105">
       <c r="A105" s="17" t="inlineStr">
         <is>
-          <t>Wizard</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="B105" s="17" t="inlineStr">
         <is>
-          <t>CustomerMirrorPanel</t>
+          <t>VerificationGate</t>
         </is>
       </c>
       <c r="C105" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/CustomerMirrorPanel.tsx</t>
-        </is>
-      </c>
-      <c r="D105" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>components/patterns/VerificationGate.tsx</t>
+        </is>
+      </c>
+      <c r="D105" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E105" s="17" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F105" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>customer360</t>
         </is>
       </c>
       <c r="G105" s="17" t="inlineStr"/>
@@ -5667,12 +5675,12 @@
       </c>
       <c r="B106" s="17" t="inlineStr">
         <is>
-          <t>StepSummaryPanel</t>
+          <t>AbandonDialog</t>
         </is>
       </c>
       <c r="C106" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/StepSummaryPanel.tsx</t>
+          <t>components/patterns/wizard/WizardDialogs.tsx</t>
         </is>
       </c>
       <c r="D106" s="20" t="inlineStr">
@@ -5691,7 +5699,7 @@
       <c r="G106" s="17" t="inlineStr"/>
       <c r="H106" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5703,12 +5711,12 @@
       </c>
       <c r="B107" s="17" t="inlineStr">
         <is>
-          <t>StepSummarySection</t>
+          <t>CustomerMirrorPanel</t>
         </is>
       </c>
       <c r="C107" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/StepSummarySection.tsx</t>
+          <t>components/patterns/wizard/CustomerMirrorPanel.tsx</t>
         </is>
       </c>
       <c r="D107" s="20" t="inlineStr">
@@ -5724,11 +5732,7 @@
           <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
-      <c r="G107" s="17" t="inlineStr">
-        <is>
-          <t>StepSummaryPanel</t>
-        </is>
-      </c>
+      <c r="G107" s="17" t="inlineStr"/>
       <c r="H107" s="17" t="inlineStr">
         <is>
           <t>2026-10-15</t>
@@ -5743,12 +5747,12 @@
       </c>
       <c r="B108" s="17" t="inlineStr">
         <is>
-          <t>SummaryFieldRow</t>
+          <t>CustomerViewButton</t>
         </is>
       </c>
       <c r="C108" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/SummaryFieldRow.tsx</t>
+          <t>components/patterns/wizard/CustomerViewButton.tsx</t>
         </is>
       </c>
       <c r="D108" s="20" t="inlineStr">
@@ -5766,12 +5770,12 @@
       </c>
       <c r="G108" s="17" t="inlineStr">
         <is>
-          <t>StepSummaryPanel</t>
+          <t>WizardStepHeader</t>
         </is>
       </c>
       <c r="H108" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5783,12 +5787,12 @@
       </c>
       <c r="B109" s="17" t="inlineStr">
         <is>
-          <t>WizardFooter</t>
+          <t>StepSummaryPanel</t>
         </is>
       </c>
       <c r="C109" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/WizardFooter.tsx</t>
+          <t>components/patterns/wizard/StepSummaryPanel.tsx</t>
         </is>
       </c>
       <c r="D109" s="20" t="inlineStr">
@@ -5807,7 +5811,7 @@
       <c r="G109" s="17" t="inlineStr"/>
       <c r="H109" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5819,12 +5823,12 @@
       </c>
       <c r="B110" s="17" t="inlineStr">
         <is>
-          <t>WizardStepHeader</t>
+          <t>StepSummarySection</t>
         </is>
       </c>
       <c r="C110" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/WizardStepHeader.tsx</t>
+          <t>components/patterns/wizard/StepSummarySection.tsx</t>
         </is>
       </c>
       <c r="D110" s="20" t="inlineStr">
@@ -5840,7 +5844,11 @@
           <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
-      <c r="G110" s="17" t="inlineStr"/>
+      <c r="G110" s="17" t="inlineStr">
+        <is>
+          <t>StepSummaryPanel</t>
+        </is>
+      </c>
       <c r="H110" s="17" t="inlineStr">
         <is>
           <t>2026-10-15</t>
@@ -5855,12 +5863,12 @@
       </c>
       <c r="B111" s="17" t="inlineStr">
         <is>
-          <t>WizardTitleBand</t>
+          <t>SummaryFieldRow</t>
         </is>
       </c>
       <c r="C111" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/WizardTitleBand.tsx</t>
+          <t>components/patterns/wizard/SummaryFieldRow.tsx</t>
         </is>
       </c>
       <c r="D111" s="20" t="inlineStr">
@@ -5876,15 +5884,127 @@
           <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
-      <c r="G111" s="17" t="inlineStr"/>
+      <c r="G111" s="17" t="inlineStr">
+        <is>
+          <t>StepSummaryPanel</t>
+        </is>
+      </c>
       <c r="H111" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="17" t="inlineStr">
+        <is>
+          <t>Wizard</t>
+        </is>
+      </c>
+      <c r="B112" s="17" t="inlineStr">
+        <is>
+          <t>WizardFooter</t>
+        </is>
+      </c>
+      <c r="C112" s="17" t="inlineStr">
+        <is>
+          <t>components/patterns/wizard/WizardFooter.tsx</t>
+        </is>
+      </c>
+      <c r="D112" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
+        </is>
+      </c>
+      <c r="E112" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F112" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+      <c r="G112" s="17" t="inlineStr"/>
+      <c r="H112" s="17" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="17" t="inlineStr">
+        <is>
+          <t>Wizard</t>
+        </is>
+      </c>
+      <c r="B113" s="17" t="inlineStr">
+        <is>
+          <t>WizardStepHeader</t>
+        </is>
+      </c>
+      <c r="C113" s="17" t="inlineStr">
+        <is>
+          <t>components/patterns/wizard/WizardStepHeader.tsx</t>
+        </is>
+      </c>
+      <c r="D113" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
+        </is>
+      </c>
+      <c r="E113" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F113" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+      <c r="G113" s="17" t="inlineStr"/>
+      <c r="H113" s="17" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="17" t="inlineStr">
+        <is>
+          <t>Wizard</t>
+        </is>
+      </c>
+      <c r="B114" s="17" t="inlineStr">
+        <is>
+          <t>WizardTitleBand</t>
+        </is>
+      </c>
+      <c r="C114" s="17" t="inlineStr">
+        <is>
+          <t>components/patterns/wizard/WizardTitleBand.tsx</t>
+        </is>
+      </c>
+      <c r="D114" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
+        </is>
+      </c>
+      <c r="E114" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F114" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+      <c r="G114" s="17" t="inlineStr"/>
+      <c r="H114" s="17" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H111"/>
+  <autoFilter ref="A1:H114"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5895,7 +6015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.50" customWidth="1" min="1" max="1"/>
@@ -5981,7 +6101,7 @@
       </c>
       <c r="G2" s="17" t="inlineStr">
         <is>
-          <t>CompanySearchInput, ContactPhoneInput, CpeSerialScanner, MsisdnPicker, SimSerialScanner, AppointmentBookingStep, BillingAccountAutoResolver, BillingAccountStep, CafSignatureCapture, CafTerms, FixedPlanStep, PrepaidCartStep, PrepaidCheckoutStep, PrepaidPlanStep, TicketCreationModal, VerificationGate, ZsbAddressStep, lineSelectionModel, useCheckoutSummary, useIdLookup, usePostpaidPlanAddons, StepSummaryPanel, stepSummary, useJourneyStartResume, useWizardDraftActions, LocationInput, activityEngine, agentProfileEngine, businessAccountEngine, customer360Engine, fibreServiceability, serviceLocationLookup, useAreaOptions, configStore, entityStore</t>
+          <t>CompanySearchInput, ContactPhoneInput, CpeSerialScanner, MsisdnPicker, SimSerialScanner, AppointmentBookingStep, BillingAccountAutoResolver, BillingAccountStep, CafSignatureCapture, CafTerms, FixedPlanStep, PrepaidCartStep, PrepaidCheckoutStep, PrepaidPlanStep, TicketCreationModal, VerificationGate, ZsbAddressStep, lineSelectionModel, useCheckoutSummary, useIdLookup, usePostpaidPlanAddons, StepSummaryPanel, stepSummary, useJourneyStartResume, useWizardDraftActions, LocationInput, activityEngine, agentProfileEngine, businessAccountEngine, connectionEligibility, customer360Engine, fibreServiceability, serviceLocationLookup, useAreaOptions, configStore, entityStore</t>
         </is>
       </c>
       <c r="H2" s="17" t="inlineStr">
@@ -6026,7 +6146,7 @@
       </c>
       <c r="H3" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6221,7 +6341,7 @@
       </c>
       <c r="G8" s="17" t="inlineStr">
         <is>
-          <t>lineSelectionModel, customer360Demo, customer360Engine</t>
+          <t>lineSelectionModel, customer360Demo, connectionEligibility, customer360Engine</t>
         </is>
       </c>
       <c r="H8" s="17" t="inlineStr">
@@ -6306,7 +6426,7 @@
       </c>
       <c r="H10" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6434,12 +6554,12 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>eligibilityEngine</t>
+          <t>connectionEligibility</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>engines/eligibilityEngine.ts</t>
+          <t>engines/connectionEligibility.ts</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -6455,14 +6575,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G14" s="17" t="inlineStr">
-        <is>
-          <t>eligibilityRowsModel, eligibilityTypes</t>
-        </is>
-      </c>
+      <c r="G14" s="17" t="inlineStr"/>
       <c r="H14" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>uncommitted</t>
         </is>
       </c>
     </row>
@@ -6474,12 +6590,12 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>fibreServiceability</t>
+          <t>eligibilityEngine</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>engines/fibreServiceability.ts</t>
+          <t>engines/eligibilityEngine.ts</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -6497,12 +6613,12 @@
       </c>
       <c r="G15" s="17" t="inlineStr">
         <is>
-          <t>FibreReadinessBanner, ActivationCompleteScreen</t>
+          <t>eligibilityRowsModel, eligibilityTypes</t>
         </is>
       </c>
       <c r="H15" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6514,12 +6630,12 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>personaEngine</t>
+          <t>fibreServiceability</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>engines/personaEngine.ts</t>
+          <t>engines/fibreServiceability.ts</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -6532,17 +6648,17 @@
       </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
-          <t>dashboard, order-management, product-lines, sim-number-management, navigation, administration, customer360, orders, profile</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G16" s="17" t="inlineStr">
         <is>
-          <t>approvalAuthority, navigationEngine</t>
+          <t>FibreReadinessBanner, ActivationCompleteScreen</t>
         </is>
       </c>
       <c r="H16" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6670,12 @@
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>eligibilityGuard</t>
+          <t>personaEngine</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>engines/eligibilityGuard.ts</t>
+          <t>engines/personaEngine.ts</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -6568,17 +6684,21 @@
         </is>
       </c>
       <c r="E17" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F17" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr"/>
+          <t>dashboard, order-management, product-lines, sim-number-management, navigation, administration, customer360, orders, profile</t>
+        </is>
+      </c>
+      <c r="G17" s="17" t="inlineStr">
+        <is>
+          <t>approvalAuthority, navigationEngine</t>
+        </is>
+      </c>
       <c r="H17" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -6590,12 +6710,12 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>serviceLocationLookup</t>
+          <t>eligibilityGuard</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>engines/serviceLocationLookup.ts</t>
+          <t>engines/eligibilityGuard.ts</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -6608,14 +6728,10 @@
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G18" s="17" t="inlineStr">
-        <is>
-          <t>ZsbAddressStep</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration</t>
+        </is>
+      </c>
+      <c r="G18" s="17" t="inlineStr"/>
       <c r="H18" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
@@ -6630,12 +6746,12 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>agentPrivilegeEngine</t>
+          <t>serviceLocationLookup</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>engines/agentPrivilegeEngine.ts</t>
+          <t>engines/serviceLocationLookup.ts</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -6644,17 +6760,21 @@
         </is>
       </c>
       <c r="E19" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F19" s="17" t="inlineStr">
         <is>
-          <t>trouble-ticketing-complaints, navigation, administration, customer360, profile, tasks</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G19" s="17" t="inlineStr">
+        <is>
+          <t>ZsbAddressStep</t>
+        </is>
+      </c>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6786,12 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>agentTaskEngine</t>
+          <t>agentPrivilegeEngine</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>engines/agentTaskEngine.ts</t>
+          <t>engines/agentPrivilegeEngine.ts</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -6684,13 +6804,13 @@
       </c>
       <c r="F20" s="17" t="inlineStr">
         <is>
-          <t>dashboard, order-management, trouble-ticketing-complaints, orders, support, tasks</t>
+          <t>trouble-ticketing-complaints, navigation, administration, customer360, profile, tasks</t>
         </is>
       </c>
       <c r="G20" s="17" t="inlineStr"/>
       <c r="H20" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6702,12 +6822,12 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>approvalAuthority</t>
+          <t>agentTaskEngine</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>engines/approvalAuthority.ts</t>
+          <t>engines/agentTaskEngine.ts</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -6720,13 +6840,13 @@
       </c>
       <c r="F21" s="17" t="inlineStr">
         <is>
-          <t>dashboard, order-management, sim-number-management, navigation, customer360, orders</t>
+          <t>dashboard, order-management, trouble-ticketing-complaints, orders, support, tasks</t>
         </is>
       </c>
       <c r="G21" s="17" t="inlineStr"/>
       <c r="H21" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -6738,12 +6858,12 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>portInEngine</t>
+          <t>approvalAuthority</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>engines/portInEngine.ts</t>
+          <t>engines/approvalAuthority.ts</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -6756,13 +6876,13 @@
       </c>
       <c r="F22" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
+          <t>dashboard, order-management, sim-number-management, navigation, customer360, orders</t>
         </is>
       </c>
       <c r="G22" s="17" t="inlineStr"/>
       <c r="H22" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6774,12 +6894,12 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>csvExport</t>
+          <t>portInEngine</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>engines/csvExport.ts</t>
+          <t>engines/portInEngine.ts</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -6788,17 +6908,17 @@
         </is>
       </c>
       <c r="E23" s="17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F23" s="17" t="inlineStr">
         <is>
-          <t>trouble-ticketing-complaints, customer360, profile, support</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
         </is>
       </c>
       <c r="G23" s="17" t="inlineStr"/>
       <c r="H23" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6810,12 +6930,12 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>bellNotificationExpiry</t>
+          <t>csvExport</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>engines/bellNotificationExpiry.ts</t>
+          <t>engines/csvExport.ts</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -6824,11 +6944,11 @@
         </is>
       </c>
       <c r="E24" s="17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>administration, customer360</t>
+          <t>trouble-ticketing-complaints, customer360, profile, support</t>
         </is>
       </c>
       <c r="G24" s="17" t="inlineStr"/>
@@ -6846,12 +6966,12 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>businessAccountEngine</t>
+          <t>bellNotificationExpiry</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>engines/businessAccountEngine.ts</t>
+          <t>engines/bellNotificationExpiry.ts</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -6864,13 +6984,13 @@
       </c>
       <c r="F25" s="17" t="inlineStr">
         <is>
-          <t>customer-search, customer360</t>
+          <t>administration, customer360</t>
         </is>
       </c>
       <c r="G25" s="17" t="inlineStr"/>
       <c r="H25" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -6882,12 +7002,12 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>navigationEngine</t>
+          <t>businessAccountEngine</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>engines/navigationEngine.ts</t>
+          <t>engines/businessAccountEngine.ts</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -6900,13 +7020,13 @@
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>navigation, customer360</t>
+          <t>customer-search, customer360</t>
         </is>
       </c>
       <c r="G26" s="17" t="inlineStr"/>
       <c r="H26" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -6918,12 +7038,12 @@
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>qnomyQueueEngine</t>
+          <t>navigationEngine</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
-          <t>engines/qnomyQueueEngine.ts</t>
+          <t>engines/navigationEngine.ts</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -6936,13 +7056,13 @@
       </c>
       <c r="F27" s="17" t="inlineStr">
         <is>
-          <t>navigation, tickets</t>
+          <t>navigation, customer360</t>
         </is>
       </c>
       <c r="G27" s="17" t="inlineStr"/>
       <c r="H27" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -6954,31 +7074,31 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>agentProfileEngine</t>
+          <t>qnomyQueueEngine</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>engines/agentProfileEngine.ts</t>
-        </is>
-      </c>
-      <c r="D28" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>engines/qnomyQueueEngine.ts</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E28" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
+          <t>navigation, tickets</t>
         </is>
       </c>
       <c r="G28" s="17" t="inlineStr"/>
       <c r="H28" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6990,12 +7110,12 @@
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>customer360VisibilityEngine</t>
+          <t>agentProfileEngine</t>
         </is>
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>engines/customer360VisibilityEngine.ts</t>
+          <t>engines/agentProfileEngine.ts</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
@@ -7008,13 +7128,13 @@
       </c>
       <c r="F29" s="17" t="inlineStr">
         <is>
-          <t>customer360</t>
+          <t>navigation</t>
         </is>
       </c>
       <c r="G29" s="17" t="inlineStr"/>
       <c r="H29" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7026,12 +7146,12 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>profileChangeTicket</t>
+          <t>customer360VisibilityEngine</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>engines/profileChangeTicket.ts</t>
+          <t>engines/customer360VisibilityEngine.ts</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
@@ -7062,12 +7182,12 @@
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>searchScopeEngine</t>
+          <t>profileChangeTicket</t>
         </is>
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>engines/searchScopeEngine.ts</t>
+          <t>engines/profileChangeTicket.ts</t>
         </is>
       </c>
       <c r="D31" s="21" t="inlineStr">
@@ -7080,13 +7200,13 @@
       </c>
       <c r="F31" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
+          <t>customer360</t>
         </is>
       </c>
       <c r="G31" s="17" t="inlineStr"/>
       <c r="H31" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7098,27 +7218,31 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>moduleDescriptions</t>
+          <t>searchScopeEngine</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>engines/moduleDescriptions.ts</t>
-        </is>
-      </c>
-      <c r="D32" s="23" t="inlineStr">
-        <is>
-          <t>App shell only</t>
+          <t>engines/searchScopeEngine.ts</t>
+        </is>
+      </c>
+      <c r="D32" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E32" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F32" s="17" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
       <c r="G32" s="17" t="inlineStr"/>
       <c r="H32" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -7130,12 +7254,12 @@
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>screenGrouping</t>
+          <t>moduleDescriptions</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>engines/screenGrouping.ts</t>
+          <t>engines/moduleDescriptions.ts</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
@@ -7157,40 +7281,32 @@
     <row r="34">
       <c r="A34" s="17" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Engine</t>
         </is>
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>entityStore</t>
+          <t>screenGrouping</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>stores/entityStore.ts</t>
-        </is>
-      </c>
-      <c r="D34" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>engines/screenGrouping.ts</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="inlineStr">
+        <is>
+          <t>App shell only</t>
         </is>
       </c>
       <c r="E34" s="17" t="n">
-        <v>24</v>
-      </c>
-      <c r="F34" s="17" t="inlineStr">
-        <is>
-          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, sales, support, tasks, tickets</t>
-        </is>
-      </c>
-      <c r="G34" s="17" t="inlineStr">
-        <is>
-          <t>ActivationCompleteScreen, DonorAttachmentStep, DonorDetailsStep, useDraftStepSync, useWizardDraftActions, activityEngine, bellNotificationExpiry, profileChangeTicket</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F34" s="17" t="inlineStr"/>
+      <c r="G34" s="17" t="inlineStr"/>
       <c r="H34" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7202,12 +7318,12 @@
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>customerContextStore</t>
+          <t>entityStore</t>
         </is>
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
-          <t>stores/customerContextStore.ts</t>
+          <t>stores/entityStore.ts</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -7216,21 +7332,21 @@
         </is>
       </c>
       <c r="E35" s="17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F35" s="17" t="inlineStr">
         <is>
-          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
+          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G35" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen, useWizardDraftActions, authStore</t>
+          <t>ActivationCompleteScreen, DonorAttachmentStep, DonorDetailsStep, useDraftStepSync, useWizardDraftActions, activityEngine, bellNotificationExpiry, profileChangeTicket</t>
         </is>
       </c>
       <c r="H35" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7242,12 +7358,12 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>authStore</t>
+          <t>customerContextStore</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>stores/authStore.ts</t>
+          <t>stores/customerContextStore.ts</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
@@ -7256,16 +7372,16 @@
         </is>
       </c>
       <c r="E36" s="17" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F36" s="17" t="inlineStr">
         <is>
-          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, support, tasks, tickets</t>
+          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G36" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, ActivationCompleteScreen, useWizardDraftActions, activityEngine, agentProfileEngine, profileChangeTicket, configStore</t>
+          <t>ActivationCompleteScreen, useActedForCustomer, useWizardDraftActions, authStore</t>
         </is>
       </c>
       <c r="H36" s="17" t="inlineStr">
@@ -7282,12 +7398,12 @@
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>notificationStore</t>
+          <t>authStore</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>stores/notificationStore.ts</t>
+          <t>stores/authStore.ts</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
@@ -7296,21 +7412,21 @@
         </is>
       </c>
       <c r="E37" s="17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F37" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, profile, support, tasks</t>
+          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G37" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, ActivationCompleteScreen, TicketCreationModal, useWizardDraftActions, useWizardStepNavigation, profileChangeTicket, useSubmit</t>
+          <t>MsisdnPicker, ActivationCompleteScreen, useWizardDraftActions, activityEngine, agentProfileEngine, profileChangeTicket, configStore</t>
         </is>
       </c>
       <c r="H37" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7322,12 +7438,12 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>personaStore</t>
+          <t>notificationStore</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>stores/personaStore.ts</t>
+          <t>stores/notificationStore.ts</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
@@ -7336,21 +7452,21 @@
         </is>
       </c>
       <c r="E38" s="17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F38" s="17" t="inlineStr">
         <is>
-          <t>dashboard, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, tasks</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, profile, support, tasks</t>
         </is>
       </c>
       <c r="G38" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, ActivationCompleteScreen, AppointmentBookingStep, configStore</t>
+          <t>MsisdnPicker, ActivationCompleteScreen, TicketCreationModal, useWizardDraftActions, useWizardStepNavigation, profileChangeTicket, useSubmit</t>
         </is>
       </c>
       <c r="H38" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -7362,12 +7478,12 @@
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>workflowStore</t>
+          <t>personaStore</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>stores/workflowStore.ts</t>
+          <t>stores/personaStore.ts</t>
         </is>
       </c>
       <c r="D39" s="20" t="inlineStr">
@@ -7376,16 +7492,16 @@
         </is>
       </c>
       <c r="E39" s="17" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F39" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration</t>
+          <t>dashboard, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, tasks</t>
         </is>
       </c>
       <c r="G39" s="17" t="inlineStr">
         <is>
-          <t>useJourneyStartResume, useMirrorChannel, useWizardDraftActions, useWizardStepNavigation</t>
+          <t>MsisdnPicker, ActivationCompleteScreen, AppointmentBookingStep, configStore</t>
         </is>
       </c>
       <c r="H39" s="17" t="inlineStr">
@@ -7402,35 +7518,35 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>customerVerificationStore</t>
+          <t>workflowStore</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>stores/customerVerificationStore.ts</t>
-        </is>
-      </c>
-      <c r="D40" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>stores/workflowStore.ts</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E40" s="17" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F40" s="17" t="inlineStr">
         <is>
-          <t>customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration</t>
         </is>
       </c>
       <c r="G40" s="17" t="inlineStr">
         <is>
-          <t>VerificationGate</t>
+          <t>useJourneyStartResume, useMirrorChannel, useWizardDraftActions, useWizardStepNavigation</t>
         </is>
       </c>
       <c r="H40" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7558,12 @@
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>qnomyQueueStore</t>
+          <t>customerVerificationStore</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>stores/qnomyQueueStore.ts</t>
+          <t>stores/customerVerificationStore.ts</t>
         </is>
       </c>
       <c r="D41" s="21" t="inlineStr">
@@ -7460,13 +7576,17 @@
       </c>
       <c r="F41" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="G41" s="17" t="inlineStr"/>
+          <t>customer360</t>
+        </is>
+      </c>
+      <c r="G41" s="17" t="inlineStr">
+        <is>
+          <t>VerificationGate</t>
+        </is>
+      </c>
       <c r="H41" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7478,12 +7598,12 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>regionStore</t>
+          <t>qnomyQueueStore</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>stores/regionStore.ts</t>
+          <t>stores/qnomyQueueStore.ts</t>
         </is>
       </c>
       <c r="D42" s="21" t="inlineStr">
@@ -7502,7 +7622,7 @@
       <c r="G42" s="17" t="inlineStr"/>
       <c r="H42" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -7514,12 +7634,12 @@
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>sidebarStore</t>
+          <t>regionStore</t>
         </is>
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>stores/sidebarStore.ts</t>
+          <t>stores/regionStore.ts</t>
         </is>
       </c>
       <c r="D43" s="21" t="inlineStr">
@@ -7538,7 +7658,7 @@
       <c r="G43" s="17" t="inlineStr"/>
       <c r="H43" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7550,12 +7670,12 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>themeStore</t>
+          <t>sidebarStore</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>stores/themeStore.ts</t>
+          <t>stores/sidebarStore.ts</t>
         </is>
       </c>
       <c r="D44" s="21" t="inlineStr">
@@ -7574,7 +7694,7 @@
       <c r="G44" s="17" t="inlineStr"/>
       <c r="H44" s="17" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7586,67 +7706,63 @@
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>configStore</t>
+          <t>themeStore</t>
         </is>
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>stores/configStore.ts</t>
-        </is>
-      </c>
-      <c r="D45" s="23" t="inlineStr">
-        <is>
-          <t>App shell only</t>
+          <t>stores/themeStore.ts</t>
+        </is>
+      </c>
+      <c r="D45" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E45" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F45" s="17" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
       <c r="G45" s="17" t="inlineStr"/>
       <c r="H45" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="17" t="inlineStr">
         <is>
-          <t>Hook</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>useEnterToSubmit</t>
+          <t>configStore</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>hooks/useEnterToSubmit.ts</t>
-        </is>
-      </c>
-      <c r="D46" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>stores/configStore.ts</t>
+        </is>
+      </c>
+      <c r="D46" s="23" t="inlineStr">
+        <is>
+          <t>App shell only</t>
         </is>
       </c>
       <c r="E46" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="F46" s="17" t="inlineStr">
-        <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
-        </is>
-      </c>
-      <c r="G46" s="17" t="inlineStr">
-        <is>
-          <t>VerificationGate, useIdLookup</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F46" s="17" t="inlineStr"/>
+      <c r="G46" s="17" t="inlineStr"/>
       <c r="H46" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7658,12 +7774,12 @@
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>useSearchListNav</t>
+          <t>useEnterToSubmit</t>
         </is>
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>hooks/useSearchListNav.ts</t>
+          <t>hooks/useEnterToSubmit.ts</t>
         </is>
       </c>
       <c r="D47" s="20" t="inlineStr">
@@ -7672,21 +7788,21 @@
         </is>
       </c>
       <c r="E47" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F47" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, navigation, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G47" s="17" t="inlineStr">
         <is>
-          <t>CompanySearchInput, ContactPhoneInput, PlanSearchBox, LocationInput</t>
+          <t>VerificationGate, useIdLookup</t>
         </is>
       </c>
       <c r="H47" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7814,12 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>useAreaOptions</t>
+          <t>useSearchListNav</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>hooks/useAreaOptions.ts</t>
+          <t>hooks/useSearchListNav.ts</t>
         </is>
       </c>
       <c r="D48" s="20" t="inlineStr">
@@ -7712,21 +7828,21 @@
         </is>
       </c>
       <c r="E48" s="17" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F48" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, navigation, administration, customer360</t>
         </is>
       </c>
       <c r="G48" s="17" t="inlineStr">
         <is>
-          <t>BillingAccountStep, ZsbAddressStep</t>
+          <t>CompanySearchInput, ContactPhoneInput, PlanSearchBox, LocationInput</t>
         </is>
       </c>
       <c r="H48" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -7738,12 +7854,12 @@
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>useSubmit</t>
+          <t>useAreaOptions</t>
         </is>
       </c>
       <c r="C49" s="17" t="inlineStr">
         <is>
-          <t>hooks/useSubmit.ts</t>
+          <t>hooks/useAreaOptions.ts</t>
         </is>
       </c>
       <c r="D49" s="20" t="inlineStr">
@@ -7752,17 +7868,21 @@
         </is>
       </c>
       <c r="E49" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F49" s="17" t="inlineStr">
         <is>
-          <t>lead-management, mnp-fnp-porting, sim-number-management, trouble-ticketing-complaints, customer360, tasks</t>
-        </is>
-      </c>
-      <c r="G49" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G49" s="17" t="inlineStr">
+        <is>
+          <t>BillingAccountStep, ZsbAddressStep</t>
+        </is>
+      </c>
       <c r="H49" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7774,68 +7894,64 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>useMinWidth</t>
+          <t>useSubmit</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>hooks/useMinWidth.ts</t>
-        </is>
-      </c>
-      <c r="D50" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>hooks/useSubmit.ts</t>
+        </is>
+      </c>
+      <c r="D50" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E50" s="17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F50" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
+          <t>lead-management, mnp-fnp-porting, sim-number-management, trouble-ticketing-complaints, customer360, tasks</t>
         </is>
       </c>
       <c r="G50" s="17" t="inlineStr"/>
       <c r="H50" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="17" t="inlineStr">
         <is>
-          <t>Helper</t>
+          <t>Hook</t>
         </is>
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>statusTone</t>
+          <t>useMinWidth</t>
         </is>
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>lib/statusTone.ts</t>
-        </is>
-      </c>
-      <c r="D51" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>hooks/useMinWidth.ts</t>
+        </is>
+      </c>
+      <c r="D51" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E51" s="17" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F51" s="17" t="inlineStr">
         <is>
-          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, orders, sales, support, tasks, tickets</t>
-        </is>
-      </c>
-      <c r="G51" s="17" t="inlineStr">
-        <is>
-          <t>ruleEngine</t>
-        </is>
-      </c>
+          <t>navigation</t>
+        </is>
+      </c>
+      <c r="G51" s="17" t="inlineStr"/>
       <c r="H51" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
@@ -7850,12 +7966,12 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>format</t>
+          <t>statusTone</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>lib/format.ts</t>
+          <t>lib/statusTone.ts</t>
         </is>
       </c>
       <c r="D52" s="20" t="inlineStr">
@@ -7864,21 +7980,21 @@
         </is>
       </c>
       <c r="E52" s="17" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F52" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, support, tasks</t>
+          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, orders, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G52" s="17" t="inlineStr">
         <is>
-          <t>AdditionalDocumentsUpload, CafDocumentUpload, MsisdnPicker, SupportingDocumentUpload, GuidedContactStep, IdLookupStep, postpaidPlanModel, StepSummaryPanel, stepSummary, postpaidPricing</t>
+          <t>ruleEngine</t>
         </is>
       </c>
       <c r="H52" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7890,12 +8006,12 @@
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>deviceType</t>
+          <t>format</t>
         </is>
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>lib/deviceType.ts</t>
+          <t>lib/format.ts</t>
         </is>
       </c>
       <c r="D53" s="20" t="inlineStr">
@@ -7904,16 +8020,16 @@
         </is>
       </c>
       <c r="E53" s="17" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F53" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, support, tasks</t>
         </is>
       </c>
       <c r="G53" s="17" t="inlineStr">
         <is>
-          <t>SimSerialScanner, SimTypeStep, cafTypes</t>
+          <t>AdditionalDocumentsUpload, CafDocumentUpload, MsisdnPicker, SupportingDocumentUpload, GuidedContactStep, IdLookupStep, postpaidPlanModel, StepSummaryPanel, stepSummary, postpaidPricing</t>
         </is>
       </c>
       <c r="H53" s="17" t="inlineStr">
@@ -7930,12 +8046,12 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>taskId</t>
+          <t>buildEnv</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>lib/taskId.ts</t>
+          <t>lib/buildEnv.ts</t>
         </is>
       </c>
       <c r="D54" s="20" t="inlineStr">
@@ -7944,21 +8060,21 @@
         </is>
       </c>
       <c r="E54" s="17" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F54" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360</t>
         </is>
       </c>
       <c r="G54" s="17" t="inlineStr">
         <is>
-          <t>useWizardDraftActions</t>
+          <t>syntheticMarker, navigationEngine</t>
         </is>
       </c>
       <c r="H54" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -7970,12 +8086,12 @@
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>connectionType</t>
+          <t>deviceType</t>
         </is>
       </c>
       <c r="C55" s="17" t="inlineStr">
         <is>
-          <t>lib/connectionType.ts</t>
+          <t>lib/deviceType.ts</t>
         </is>
       </c>
       <c r="D55" s="20" t="inlineStr">
@@ -7984,21 +8100,21 @@
         </is>
       </c>
       <c r="E55" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F55" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration</t>
         </is>
       </c>
       <c r="G55" s="17" t="inlineStr">
         <is>
-          <t>ConnectionTypeTag</t>
+          <t>SimSerialScanner, SimTypeStep, cafTypes</t>
         </is>
       </c>
       <c r="H55" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8010,28 +8126,32 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>screenName</t>
+          <t>taskId</t>
         </is>
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t>lib/screenName.ts</t>
-        </is>
-      </c>
-      <c r="D56" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>lib/taskId.ts</t>
+        </is>
+      </c>
+      <c r="D56" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E56" s="17" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F56" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="G56" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+      <c r="G56" s="17" t="inlineStr">
+        <is>
+          <t>useWizardDraftActions</t>
+        </is>
+      </c>
       <c r="H56" s="17" t="inlineStr">
         <is>
           <t>2026-10-15</t>
@@ -8046,40 +8166,156 @@
       </c>
       <c r="B57" s="17" t="inlineStr">
         <is>
+          <t>connectionType</t>
+        </is>
+      </c>
+      <c r="C57" s="17" t="inlineStr">
+        <is>
+          <t>lib/connectionType.ts</t>
+        </is>
+      </c>
+      <c r="D57" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
+        </is>
+      </c>
+      <c r="E57" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="F57" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G57" s="17" t="inlineStr">
+        <is>
+          <t>ConnectionTypeTag</t>
+        </is>
+      </c>
+      <c r="H57" s="17" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="17" t="inlineStr">
+        <is>
+          <t>Helper</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="inlineStr">
+        <is>
+          <t>serviceTypeTag</t>
+        </is>
+      </c>
+      <c r="C58" s="17" t="inlineStr">
+        <is>
+          <t>lib/serviceTypeTag.ts</t>
+        </is>
+      </c>
+      <c r="D58" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
+        </is>
+      </c>
+      <c r="E58" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="F58" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G58" s="17" t="inlineStr">
+        <is>
+          <t>ServiceTypeTag</t>
+        </is>
+      </c>
+      <c r="H58" s="17" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="17" t="inlineStr">
+        <is>
+          <t>Helper</t>
+        </is>
+      </c>
+      <c r="B59" s="17" t="inlineStr">
+        <is>
+          <t>screenName</t>
+        </is>
+      </c>
+      <c r="C59" s="17" t="inlineStr">
+        <is>
+          <t>lib/screenName.ts</t>
+        </is>
+      </c>
+      <c r="D59" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
+        </is>
+      </c>
+      <c r="E59" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" s="17" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
+      <c r="G59" s="17" t="inlineStr"/>
+      <c r="H59" s="17" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="17" t="inlineStr">
+        <is>
+          <t>Helper</t>
+        </is>
+      </c>
+      <c r="B60" s="17" t="inlineStr">
+        <is>
           <t>values</t>
         </is>
       </c>
-      <c r="C57" s="17" t="inlineStr">
+      <c r="C60" s="17" t="inlineStr">
         <is>
           <t>lib/values.ts</t>
         </is>
       </c>
-      <c r="D57" s="21" t="inlineStr">
+      <c r="D60" s="21" t="inlineStr">
         <is>
           <t>Single area</t>
         </is>
       </c>
-      <c r="E57" s="17" t="n">
+      <c r="E60" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F57" s="17" t="inlineStr">
+      <c r="F60" s="17" t="inlineStr">
         <is>
           <t>customer360</t>
         </is>
       </c>
-      <c r="G57" s="17" t="inlineStr">
+      <c r="G60" s="17" t="inlineStr">
         <is>
           <t>customer360Demo</t>
         </is>
       </c>
-      <c r="H57" s="17" t="inlineStr">
+      <c r="H60" s="17" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H57"/>
+  <autoFilter ref="A1:H60"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
+++ b/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
@@ -6578,7 +6578,7 @@
       <c r="G14" s="17" t="inlineStr"/>
       <c r="H14" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -6618,7 +6618,7 @@
       </c>
       <c r="H15" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>

--- a/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
+++ b/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
@@ -14,8 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Method" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'UI Components'!$A$1:$H$114</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Shared Code'!$A$1:$H$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'UI Components'!$A$1:$H$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Shared Code'!$A$1:$H$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="C7" s="17" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7" s="17" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E7" s="17" t="n">
         <v>4</v>
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="C9" s="17" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D9" s="17" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E9" s="17" t="n">
         <v>4</v>
@@ -855,14 +855,14 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>113 UI components + 59 non-UI files</t>
+          <t>114 UI components + 61 non-UI files</t>
         </is>
       </c>
       <c r="C13" s="18" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E13" s="18" t="n">
         <v>21</v>
@@ -887,11 +887,11 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>22 named - see the Capabilities sheet</t>
+          <t>23 named - see the Capabilities sheet</t>
         </is>
       </c>
       <c r="C15" s="17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D15" s="17" t="inlineStr"/>
       <c r="E15" s="17" t="inlineStr"/>
@@ -908,7 +908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.80" customWidth="1" min="1" max="1"/>
@@ -999,6 +999,8 @@
 components/patterns/guidedContactModel.ts
 components/domain/QidInput.tsx
 components/domain/QidImageUpload.tsx
+components/domain/IdFileUpload.tsx
+components/domain/idUploadModel.ts
 components/domain/PassportScanSections.tsx
 components/domain/ScannedIdPreview.tsx
 components/domain/qidImageUploadModel.ts</t>
@@ -1016,41 +1018,145 @@
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
+          <t>Special Discounts Identification</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>The Special Discounts section of Mobile Postpaid Activation as its own capability: choose Consumer B2B2C, Retiree or MADA, supply the evidence (company, ID number, Office ID scan or upload) and accept or reject the benefit. Independent of Customer Identification and Customer Type; always offers both Initiate scan and Upload document.</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>capabilities/SpecialDiscountsIdentification/CompanySearchInput.tsx
+capabilities/SpecialDiscountsIdentification/IdFileUpload.tsx
+capabilities/SpecialDiscountsIdentification/PassportScanSections.tsx
+capabilities/SpecialDiscountsIdentification/QidImageUpload.tsx
+capabilities/SpecialDiscountsIdentification/ScanFailureNotice.tsx
+capabilities/SpecialDiscountsIdentification/ScannedIdPreview.tsx
+capabilities/SpecialDiscountsIdentification/SpecialDiscountsIdentification.tsx
+capabilities/SpecialDiscountsIdentification/SpecialDiscountsStep.tsx
+capabilities/SpecialDiscountsIdentification/idUploadModel.ts
+capabilities/SpecialDiscountsIdentification/index.ts
+capabilities/SpecialDiscountsIdentification/qidImageUploadModel.ts
+capabilities/SpecialDiscountsIdentification/specialDiscountsModel.ts
+capabilities/SpecialDiscountsIdentification/step.tsx
+capabilities/SpecialDiscountsIdentification/CompanySearchInput.tsx
+capabilities/SpecialDiscountsIdentification/IdFileUpload.tsx
+capabilities/SpecialDiscountsIdentification/PassportScanSections.tsx
+capabilities/SpecialDiscountsIdentification/QidImageUpload.tsx
+capabilities/SpecialDiscountsIdentification/ScanFailureNotice.tsx
+capabilities/SpecialDiscountsIdentification/ScannedIdPreview.tsx
+capabilities/SpecialDiscountsIdentification/SpecialDiscountsStep.tsx
+capabilities/SpecialDiscountsIdentification/idUploadModel.ts
+capabilities/SpecialDiscountsIdentification/qidImageUploadModel.ts
+capabilities/SpecialDiscountsIdentification/specialDiscountsModel.ts</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
           <t>Guided activation wizard</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>The step shell every activation / migration / port-in journey runs in.</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>capabilities/GuidedActivationWizard/GuidedActivationWizard.tsx
 capabilities/GuidedActivationWizard/index.ts</t>
         </is>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D5" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>Eligibility gate</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>Hard-stop / soft-stop / pass eligibility check shown after identification, with the outcome panel, checks report and footer actions.</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>capabilities/EligibilityGate/EligibilityGateStep.tsx
+capabilities/EligibilityGate/EligibilityOutcomes.tsx
+capabilities/EligibilityGate/eligibilityOutcomesModel.ts
+capabilities/EligibilityGate/index.ts</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>Customer Type &amp; Discounts</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>Special customer types (retired, MADA, B2B2C): the evidence the agent collects, the rules for accepting or rejecting the benefit, and the customer's benefits.</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>capabilities/CustomerType/CustomerTypeStep.tsx
+capabilities/CustomerType/customerTypeModel.ts
+capabilities/CustomerType/index.ts
+capabilities/CustomerType/useCustomerBenefits.ts
+components/domain/CompanySearchInput.tsx</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Cross-Sell Offers</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Recommended offers for the identified customer: offer cards, details drawer, interested (lead) and select actions, and hand-off to the other journeys.</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>capabilities/CrossSellOffers/CrossSalesStep.tsx
 capabilities/CrossSellOffers/HandOff.tsx
@@ -1063,27 +1169,27 @@
 capabilities/CrossSellOffers/summary.ts</t>
         </is>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D8" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>SIM Type</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>Choose and validate the SIM: Physical (scan or enter the serial) or eSIM (issued, handed over after payment).</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>capabilities/SimType/SimSerial.tsx
 capabilities/SimType/SimType.tsx
@@ -1094,27 +1200,27 @@
 components/domain/SimSerialScanner.tsx</t>
         </is>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D9" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>Number Selection</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>Choose a number: search, Free and Star bands, price filter, plan entitlement note, reserve and clear.</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>capabilities/NumberSelection/NumberSelection.tsx
 capabilities/NumberSelection/index.ts
@@ -1124,27 +1230,27 @@
 components/domain/msisdnPickerModel.ts</t>
         </is>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D10" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Billing Account</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Set up what an order bills to: one layout everywhere - the customer's existing billing accounts, or Create New Billing Account (contact, billing address, payment, card on file, primary payment profile, billing profile setup).</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>capabilities/BillingAccount/BillingAccount.tsx
 capabilities/BillingAccount/index.ts
@@ -1157,27 +1263,27 @@
 components/patterns/billingAccountModel.ts</t>
         </is>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D11" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>Plan Selection</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>Choose the plan: postpaid plan cards then Add-ons (discounts, bill limit), prepaid packs then Add-ons, or the fixed-line / fibre plan cards with the credit check. The line's current plan or pack can be left out of the choices when a journey changes it.</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>capabilities/PlanSelection/PlanSelection.tsx
 capabilities/PlanSelection/index.ts
@@ -1191,27 +1297,27 @@
 components/patterns/PlanGroupPanel.tsx</t>
         </is>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D12" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>CAF &amp; Signature</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>The Customer Agreement Form: terms, CAF type, signature and supporting documents. Standard variant (name, key information, signature) and full variant (the customer reads back the Checkout Summary order, agrees the terms and signs; the journey locks once signed); postpaid and prepaid forms.</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>capabilities/CafSignature/CafSignature.tsx
 capabilities/CafSignature/index.ts
@@ -1222,27 +1328,27 @@
 components/patterns/cafTypes.ts</t>
         </is>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D13" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>Checkout Summary</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>The order read-back before signing and payment (plan, add-ons, discount, number, billing, monthly and one-off totals); publishes the totals and read-back rows the CAF and Payment reuse. An optional panel above it (the port-in validation gate). Includes the prepaid cart (Add another subscription) and the prepaid checkout, which a prepaid port-in also uses with its own lines, details and fees.</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>capabilities/CheckoutSummary/CheckoutSummary.tsx
 capabilities/CheckoutSummary/PrepaidCartBody.tsx
@@ -1261,27 +1367,27 @@
 components/patterns/prepaidCartModel.ts</t>
         </is>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D14" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>Payment</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>Take the amount due at the counter through WinCash and record the outcome.</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>capabilities/Payment/Payment.tsx
 capabilities/Payment/index.ts
@@ -1289,27 +1395,27 @@
 components/patterns/WinCashPaymentStep.tsx</t>
         </is>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D15" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>Activation Complete</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>The confirmation page for a submitted activation (facts, status, follow-on actions, eSIM handover, email) and the confirmed-order shape journeys hand it.</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>capabilities/ActivationComplete/ActivationComplete.tsx
 capabilities/ActivationComplete/confirmedOrder.ts
@@ -1318,82 +1424,54 @@
 components/patterns/OrderConfirmationScreen.tsx</t>
         </is>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D16" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>Eligibility gate</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>Hard-stop / soft-stop / pass eligibility check shown after identification, with the outcome panel, checks report and footer actions.</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>capabilities/EligibilityGate/EligibilityGateStep.tsx
-capabilities/EligibilityGate/EligibilityOutcomes.tsx
-capabilities/EligibilityGate/eligibilityOutcomesModel.ts
-capabilities/EligibilityGate/index.ts</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>Add-ons selection</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>Add-on rows for a plan or prepaid pack, with included-benefit handling; on its own (Add Add-On) as a step that needs at least one add-on.</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>capabilities/AddonsSelection/AddonsPicker.tsx
 capabilities/AddonsSelection/index.ts
 capabilities/AddonsSelection/step.tsx</t>
         </is>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D17" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>Customer Qualification</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>Identify the customer, run eligibility, then offer the special-discount types - the whole "Customer Identification" step of an activation, with its outcomes and footer actions.</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>capabilities/CustomerQualification/JourneyBanners.tsx
 capabilities/CustomerQualification/index.ts
@@ -1401,57 +1479,27 @@
 capabilities/CustomerQualification/summary.ts</t>
         </is>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D18" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>Customer Type &amp; Discounts</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>Special customer types (retired, MADA, B2B2C): the evidence the agent collects, the rules for accepting or rejecting the benefit, and the customer's benefits.</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>capabilities/CustomerType/CustomerTypeStep.tsx
-capabilities/CustomerType/customerTypeModel.ts
-capabilities/CustomerType/index.ts
-capabilities/CustomerType/useCustomerBenefits.ts
-components/domain/CompanySearchInput.tsx
-components/domain/SupportingDocumentUpload.tsx</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>Service Address</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>The address a service is activated at: one layout everywhere: Service Information (Kahramaa Meter ID / Vodafone Premise ID with Search), then Zone / Street / Building, then Additional Details, with Qatari-ID prefill.</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>capabilities/ServiceAddress/ServiceAddress.tsx
 capabilities/ServiceAddress/index.ts
@@ -1460,27 +1508,27 @@
 components/patterns/ZsbAddressStep.tsx</t>
         </is>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D19" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>Appointment Booking</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>Book the installation visit: SLA cluster, the date strip (next working days from the earliest, with each day's open slots), the day's time slots and technicians free, the customer's request for a specific date and time (a later date makes the order future-dated), appointment notes and the documents the technician collects (defaulted from the persona).</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>capabilities/AppointmentBooking/AppointmentBooking.tsx
 capabilities/AppointmentBooking/index.ts
@@ -1489,27 +1537,27 @@
 components/patterns/appointmentModel.ts</t>
         </is>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D20" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, administration</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>Activity Comments</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>The closing note on the actions performed, with an optional channel.</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>capabilities/ActivityComments/ActivityComments.tsx
 capabilities/ActivityComments/index.ts
@@ -1517,27 +1565,27 @@
 components/patterns/ActivityCommentsStep.tsx</t>
         </is>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="D21" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>Line Selection</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>Choose which of the identified customer's existing mobile lines an order changes (Change Postpaid Plan, Change Prepaid Pack, Add Add-On): postpaid and / or prepaid lines with their current plan and price; a line that is not active, is barred or whose billing profile is in collections is shown with its reason and cannot be chosen.</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>capabilities/LineSelection/LineSelection.tsx
 capabilities/LineSelection/index.ts
@@ -1546,60 +1594,60 @@
 components/patterns/lineSelectionModel.ts</t>
         </is>
       </c>
-      <c r="D21" s="17" t="n">
+      <c r="D22" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>mobile-service-changes, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="17" t="inlineStr">
-        <is>
-          <t>Selectable card styling</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>One selected / idle / highlighted surface for plans, offers, numbers, add-ons, discounts and ID/customer type.</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>capabilities/SelectableCard/index.ts</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>administration</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="17" t="inlineStr">
         <is>
-          <t>Side drawer</t>
+          <t>Selectable card styling</t>
         </is>
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>Fixed 50%-width drawer for forms, details and multi-step flows: the title as a small uppercase label beside the close control, the body on the page tint, and a footer whose buttons share its width equally.</t>
+          <t>One selected / idle / highlighted surface for plans, offers, numbers, add-ons, discounts and ID/customer type.</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>capabilities/SideDrawer/index.ts</t>
+          <t>capabilities/SelectableCard/index.ts</t>
         </is>
       </c>
       <c r="D23" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>administration</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>Side drawer</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>Fixed 50%-width drawer for forms, details and multi-step flows: the title as a small uppercase label beside the close control, the body on the page tint, and a footer whose buttons share its width equally.</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>capabilities/SideDrawer/index.ts</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
         <is>
           <t>administration</t>
         </is>
@@ -1616,7 +1664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H114"/>
+  <dimension ref="A1:H115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.85" customWidth="1" min="1" max="1"/>
@@ -1742,7 +1790,7 @@
       </c>
       <c r="G3" s="17" t="inlineStr">
         <is>
-          <t>AdditionalDocumentsUpload, CafDocumentUpload, CompanySearchInput, ContactPhoneInput, EligibilityRows, FibreReadinessBanner, MsisdnPicker, PassportScanSections, QidImageUpload, QidInput, ScanFailureNotice, SimSerialScanner, AppointmentBookingStep, BillingAccountStep, CafSignatureCapture, DiscountCard, FixedPlanStep, OrderConfirmationScreen, PostpaidPlanAddonsStep, PostpaidPlanCard, PrepaidPlanCard, PrepaidPlanStep, ValidationStatus, ZsbAddressStep, CustomerViewButton, StepSummarySection, WizardFooter, ChoiceCards, DataTable, IconButton, LocationInput, Pager, PhoneNumberInput, SearchField, Select, Tabs</t>
+          <t>AdditionalDocumentsUpload, CafDocumentUpload, CompanySearchInput, ContactPhoneInput, EligibilityRows, FibreReadinessBanner, IdFileUpload, MsisdnPicker, PassportScanSections, QidImageUpload, QidInput, ScanFailureNotice, SimSerialScanner, AppointmentBookingStep, BillingAccountStep, CafSignatureCapture, DiscountCard, FixedPlanStep, OrderConfirmationScreen, PostpaidPlanAddonsStep, PostpaidPlanCard, PrepaidPlanCard, PrepaidPlanStep, ValidationStatus, ZsbAddressStep, CustomerViewButton, StepSummarySection, WizardFooter, ChoiceCards, DataTable, IconButton, LocationInput, Pager, PhoneNumberInput, SearchField, Select, Tabs</t>
         </is>
       </c>
       <c r="H3" s="17" t="inlineStr">
@@ -1782,7 +1830,7 @@
       </c>
       <c r="G4" s="17" t="inlineStr">
         <is>
-          <t>ErrorBoundary, AdditionalDocumentsUpload, BillLimitEditor, CafDocumentUpload, EligibilityRows, MsisdnPicker, PassportScanSections, QidImageUpload, QidInput, SimSerialScanner, SimTypeStep, SupportingDocumentUpload, ActivationCompleteScreen, BillingAccountStep, BillingProfileSetupDrawer, BulkOperationPortal, CafSignatureCapture, CheckoutDefaultLayout, DemoFaultPanel, FixedPlanStep, IdLookupStatus, OrderConfirmationScreen, PostpaidDiscountsPanel, PostpaidPlanCard, PrepaidCartStep, PrepaidCheckoutStep, PrepaidPackDetailsDrawer, PrepaidPlanCard, TicketCreationModal, ValidationStatus, VerificationGate, WinCashPaymentStep, ZsbAddressStep, CustomerViewButton, StepSummarySection, SummaryFieldRow, WizardDialogs, WizardFooter, WizardTitleBand, SignaturePad</t>
+          <t>ErrorBoundary, AdditionalDocumentsUpload, BillLimitEditor, CafDocumentUpload, EligibilityRows, IdFileUpload, MsisdnPicker, PassportScanSections, QidImageUpload, QidInput, SimSerialScanner, SimTypeStep, ActivationCompleteScreen, BillingAccountStep, BillingProfileSetupDrawer, BulkOperationPortal, CafSignatureCapture, CheckoutDefaultLayout, DemoFaultPanel, FixedPlanStep, IdLookupStatus, NewCustomerForm, OrderConfirmationScreen, PostpaidDiscountsPanel, PostpaidPlanCard, PrepaidCartStep, PrepaidCheckoutStep, PrepaidPackDetailsDrawer, PrepaidPlanCard, TicketCreationModal, ValidationStatus, VerificationGate, WinCashPaymentStep, ZsbAddressStep, CustomerViewButton, StepSummarySection, SummaryFieldRow, WizardDialogs, WizardFooter, WizardTitleBand, SignaturePad</t>
         </is>
       </c>
       <c r="H4" s="17" t="inlineStr">
@@ -1822,7 +1870,7 @@
       </c>
       <c r="G5" s="17" t="inlineStr">
         <is>
-          <t>AdditionalDocumentsUpload, CafDocumentUpload, MsisdnPicker, BillingAccountStep, BillingProfileSetupDrawer, BulkOperationPortal, DonorDetailsStep, GuidedContactStep, TicketCreationModal, ZsbAddressStep</t>
+          <t>AdditionalDocumentsUpload, CafDocumentUpload, MsisdnPicker, BillingAccountStep, BillingProfileSetupDrawer, BulkOperationPortal, DonorDetailsStep, GuidedContactStep, NewCustomerForm, TicketCreationModal, ZsbAddressStep</t>
         </is>
       </c>
       <c r="H5" s="17" t="inlineStr">
@@ -1862,7 +1910,7 @@
       </c>
       <c r="G6" s="17" t="inlineStr">
         <is>
-          <t>AdditionalDocumentsUpload, BillLimitEditor, CpeSerialScanner, SimSerialScanner, AppointmentBookingStep, BillingAccountStep, BillingProfileSetupDrawer, BulkOperationPortal, DonorDetailsStep, GuidedContactStep, IdLookupStep, PostpaidDiscountsPanel, TicketCreationModal, VerificationGate, ZsbAddressStep, PhoneNumberInput</t>
+          <t>AdditionalDocumentsUpload, BillLimitEditor, CpeSerialScanner, SimSerialScanner, AppointmentBookingStep, BillingAccountStep, BillingProfileSetupDrawer, BulkOperationPortal, DonorDetailsStep, GuidedContactStep, IdLookupStep, NewCustomerForm, PostpaidDiscountsPanel, TicketCreationModal, ZsbAddressStep, PhoneNumberInput</t>
         </is>
       </c>
       <c r="H6" s="17" t="inlineStr">
@@ -2380,11 +2428,7 @@
           <t>lead-management, mnp-fnp-porting, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, customer360, orders, sales, support, tasks, tickets</t>
         </is>
       </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>VerificationGate</t>
-        </is>
-      </c>
+      <c r="G19" s="17" t="inlineStr"/>
       <c r="H19" s="17" t="inlineStr">
         <is>
           <t>2026-10-15</t>
@@ -2733,17 +2777,17 @@
         </is>
       </c>
       <c r="E28" s="17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, customer360</t>
         </is>
       </c>
       <c r="G28" s="17" t="inlineStr"/>
       <c r="H28" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3075,7 @@
       </c>
       <c r="H36" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -3043,12 +3087,12 @@
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>PassportScanSections</t>
+          <t>IdFileUpload</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>components/domain/PassportScanSections.tsx</t>
+          <t>components/domain/IdFileUpload.tsx</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
@@ -3066,12 +3110,12 @@
       </c>
       <c r="G37" s="17" t="inlineStr">
         <is>
-          <t>QidImageUpload</t>
+          <t>PassportScanSections, QidImageUpload</t>
         </is>
       </c>
       <c r="H37" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -3083,12 +3127,12 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>QidImageUpload</t>
+          <t>PassportScanSections</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>components/domain/QidImageUpload.tsx</t>
+          <t>components/domain/PassportScanSections.tsx</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
@@ -3106,12 +3150,12 @@
       </c>
       <c r="G38" s="17" t="inlineStr">
         <is>
-          <t>IdScannerPanel</t>
+          <t>QidImageUpload</t>
         </is>
       </c>
       <c r="H38" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3167,12 @@
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>QidTypeSelector</t>
+          <t>QidImageUpload</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>components/domain/QidInput.tsx</t>
+          <t>components/domain/QidImageUpload.tsx</t>
         </is>
       </c>
       <c r="D39" s="20" t="inlineStr">
@@ -3146,12 +3190,12 @@
       </c>
       <c r="G39" s="17" t="inlineStr">
         <is>
-          <t>GuidedContactStep, IdLookupStep, IdScannerPanel, MoiResultPanel, guidedContactModel, idLookupModel, useIdLookup</t>
+          <t>IdScannerPanel</t>
         </is>
       </c>
       <c r="H39" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -3163,12 +3207,12 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>ScanFailureNotice</t>
+          <t>QidTypeSelector</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>components/domain/ScanFailureNotice.tsx</t>
+          <t>components/domain/QidInput.tsx</t>
         </is>
       </c>
       <c r="D40" s="20" t="inlineStr">
@@ -3186,12 +3230,12 @@
       </c>
       <c r="G40" s="17" t="inlineStr">
         <is>
-          <t>PassportScanSections, QidImageUpload</t>
+          <t>GuidedContactStep, IdLookupStep, IdScannerPanel, MoiResultPanel, guidedContactModel, idLookupModel, useIdLookup</t>
         </is>
       </c>
       <c r="H40" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3203,12 +3247,12 @@
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>SimSerialScanner</t>
+          <t>ScanFailureNotice</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>components/domain/SimSerialScanner.tsx</t>
+          <t>components/domain/ScanFailureNotice.tsx</t>
         </is>
       </c>
       <c r="D41" s="20" t="inlineStr">
@@ -3217,21 +3261,21 @@
         </is>
       </c>
       <c r="E41" s="17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F41" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G41" s="17" t="inlineStr">
         <is>
-          <t>SimTypeStep</t>
+          <t>PassportScanSections, QidImageUpload</t>
         </is>
       </c>
       <c r="H41" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3287,12 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>AdditionalDocumentsUpload</t>
+          <t>CompanySearchInput</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>components/domain/AdditionalDocumentsUpload.tsx</t>
+          <t>components/domain/CompanySearchInput.tsx</t>
         </is>
       </c>
       <c r="D42" s="20" t="inlineStr">
@@ -3257,21 +3301,17 @@
         </is>
       </c>
       <c r="E42" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F42" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G42" s="17" t="inlineStr">
-        <is>
-          <t>CafSignatureCapture</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G42" s="17" t="inlineStr"/>
       <c r="H42" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3283,12 +3323,12 @@
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>BillLimitEditor</t>
+          <t>EligibilityChecksList</t>
         </is>
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>components/domain/BillLimitEditor.tsx</t>
+          <t>components/domain/EligibilityRows.tsx</t>
         </is>
       </c>
       <c r="D43" s="20" t="inlineStr">
@@ -3297,18 +3337,14 @@
         </is>
       </c>
       <c r="E43" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F43" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G43" s="17" t="inlineStr">
-        <is>
-          <t>PostpaidAddonsPanel, PostpaidPlanAddonsStep</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G43" s="17" t="inlineStr"/>
       <c r="H43" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
@@ -3323,12 +3359,12 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>CafDocumentUpload</t>
+          <t>SimSerialScanner</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>components/domain/CafDocumentUpload.tsx</t>
+          <t>components/domain/SimSerialScanner.tsx</t>
         </is>
       </c>
       <c r="D44" s="20" t="inlineStr">
@@ -3337,21 +3373,21 @@
         </is>
       </c>
       <c r="E44" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F44" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G44" s="17" t="inlineStr">
         <is>
-          <t>CafSignatureCapture</t>
+          <t>SimTypeStep</t>
         </is>
       </c>
       <c r="H44" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -3363,12 +3399,12 @@
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>CompanySearchInput</t>
+          <t>AdditionalDocumentsUpload</t>
         </is>
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>components/domain/CompanySearchInput.tsx</t>
+          <t>components/domain/AdditionalDocumentsUpload.tsx</t>
         </is>
       </c>
       <c r="D45" s="20" t="inlineStr">
@@ -3384,10 +3420,14 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G45" s="17" t="inlineStr"/>
+      <c r="G45" s="17" t="inlineStr">
+        <is>
+          <t>CafSignatureCapture</t>
+        </is>
+      </c>
       <c r="H45" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3399,12 +3439,12 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>CreditCheckPanel</t>
+          <t>BillLimitEditor</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>components/domain/CreditCheckPanel.tsx</t>
+          <t>components/domain/BillLimitEditor.tsx</t>
         </is>
       </c>
       <c r="D46" s="20" t="inlineStr">
@@ -3422,12 +3462,12 @@
       </c>
       <c r="G46" s="17" t="inlineStr">
         <is>
-          <t>FixedPlanStep</t>
+          <t>PostpaidAddonsPanel, PostpaidPlanAddonsStep</t>
         </is>
       </c>
       <c r="H46" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3439,12 +3479,12 @@
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>EligibilityChecksList</t>
+          <t>CafDocumentUpload</t>
         </is>
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>components/domain/EligibilityRows.tsx</t>
+          <t>components/domain/CafDocumentUpload.tsx</t>
         </is>
       </c>
       <c r="D47" s="20" t="inlineStr">
@@ -3460,10 +3500,14 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G47" s="17" t="inlineStr"/>
+      <c r="G47" s="17" t="inlineStr">
+        <is>
+          <t>CafSignatureCapture</t>
+        </is>
+      </c>
       <c r="H47" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3475,12 +3519,12 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>EsimActivationPanel</t>
+          <t>CreditCheckPanel</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>components/domain/EsimActivationPanel.tsx</t>
+          <t>components/domain/CreditCheckPanel.tsx</t>
         </is>
       </c>
       <c r="D48" s="20" t="inlineStr">
@@ -3498,12 +3542,12 @@
       </c>
       <c r="G48" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen</t>
+          <t>FixedPlanStep</t>
         </is>
       </c>
       <c r="H48" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3515,12 +3559,12 @@
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker</t>
+          <t>EsimActivationPanel</t>
         </is>
       </c>
       <c r="C49" s="17" t="inlineStr">
         <is>
-          <t>components/domain/MsisdnPicker.tsx</t>
+          <t>components/domain/EsimActivationPanel.tsx</t>
         </is>
       </c>
       <c r="D49" s="20" t="inlineStr">
@@ -3533,10 +3577,14 @@
       </c>
       <c r="F49" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
-        </is>
-      </c>
-      <c r="G49" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G49" s="17" t="inlineStr">
+        <is>
+          <t>ActivationCompleteScreen</t>
+        </is>
+      </c>
       <c r="H49" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
@@ -3551,12 +3599,12 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>SimTypeStep</t>
+          <t>MsisdnPicker</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>components/domain/SimTypeStep.tsx</t>
+          <t>components/domain/MsisdnPicker.tsx</t>
         </is>
       </c>
       <c r="D50" s="20" t="inlineStr">
@@ -3569,14 +3617,10 @@
       </c>
       <c r="F50" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G50" s="17" t="inlineStr">
-        <is>
-          <t>CheckoutSummaryStep, checkoutDetailedTables, checkoutSummaryRows, prepaidCartModel, useCheckoutSummary</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+      <c r="G50" s="17" t="inlineStr"/>
       <c r="H50" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
@@ -3591,12 +3635,12 @@
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>StarStat</t>
+          <t>SimTypeStep</t>
         </is>
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>components/domain/StarStat.tsx</t>
+          <t>components/domain/SimTypeStep.tsx</t>
         </is>
       </c>
       <c r="D51" s="20" t="inlineStr">
@@ -3609,17 +3653,17 @@
       </c>
       <c r="F51" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G51" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker</t>
+          <t>CheckoutSummaryStep, checkoutDetailedTables, checkoutSummaryRows, prepaidCartModel, useCheckoutSummary</t>
         </is>
       </c>
       <c r="H51" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -3631,12 +3675,12 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>SupportingDocumentUpload</t>
+          <t>StarStat</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>components/domain/SupportingDocumentUpload.tsx</t>
+          <t>components/domain/StarStat.tsx</t>
         </is>
       </c>
       <c r="D52" s="20" t="inlineStr">
@@ -3649,13 +3693,17 @@
       </c>
       <c r="F52" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G52" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+      <c r="G52" s="17" t="inlineStr">
+        <is>
+          <t>MsisdnPicker</t>
+        </is>
+      </c>
       <c r="H52" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3879,7 +3927,7 @@
       <c r="G58" s="17" t="inlineStr"/>
       <c r="H58" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3967,7 @@
       </c>
       <c r="H59" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -3959,7 +4007,7 @@
       </c>
       <c r="H60" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -3999,7 +4047,7 @@
       </c>
       <c r="H61" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4099,12 @@
       </c>
       <c r="B63" s="17" t="inlineStr">
         <is>
-          <t>ValidationStatus</t>
+          <t>NewCustomerForm</t>
         </is>
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/ValidationStatus.tsx</t>
+          <t>components/patterns/NewCustomerForm.tsx</t>
         </is>
       </c>
       <c r="D63" s="20" t="inlineStr">
@@ -4074,12 +4122,12 @@
       </c>
       <c r="G63" s="17" t="inlineStr">
         <is>
-          <t>IdLookupStatus</t>
+          <t>IdLookupStep</t>
         </is>
       </c>
       <c r="H63" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -4091,12 +4139,12 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>SignatureCapture</t>
+          <t>ValidationStatus</t>
         </is>
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/SignatureCapture.tsx</t>
+          <t>components/patterns/ValidationStatus.tsx</t>
         </is>
       </c>
       <c r="D64" s="20" t="inlineStr">
@@ -4105,21 +4153,21 @@
         </is>
       </c>
       <c r="E64" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G64" s="17" t="inlineStr">
         <is>
-          <t>CafSignatureCapture, DonorAttachmentStep, SimSwapFormStep</t>
+          <t>IdLookupStatus</t>
         </is>
       </c>
       <c r="H64" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -4131,12 +4179,12 @@
       </c>
       <c r="B65" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen</t>
+          <t>SignatureCapture</t>
         </is>
       </c>
       <c r="C65" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/ActivationCompleteScreen.tsx</t>
+          <t>components/patterns/SignatureCapture.tsx</t>
         </is>
       </c>
       <c r="D65" s="20" t="inlineStr">
@@ -4145,14 +4193,18 @@
         </is>
       </c>
       <c r="E65" s="17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F65" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G65" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+      <c r="G65" s="17" t="inlineStr">
+        <is>
+          <t>CafSignatureCapture, DonorAttachmentStep, SimSwapFormStep</t>
+        </is>
+      </c>
       <c r="H65" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
@@ -4167,12 +4219,12 @@
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>BillingAccountAutoResolver</t>
+          <t>ActivationCompleteScreen</t>
         </is>
       </c>
       <c r="C66" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/BillingAccountAutoResolver.tsx</t>
+          <t>components/patterns/ActivationCompleteScreen.tsx</t>
         </is>
       </c>
       <c r="D66" s="20" t="inlineStr">
@@ -4191,7 +4243,7 @@
       <c r="G66" s="17" t="inlineStr"/>
       <c r="H66" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -4203,12 +4255,12 @@
       </c>
       <c r="B67" s="17" t="inlineStr">
         <is>
-          <t>CafSignatureCapture</t>
+          <t>BillingAccountAutoResolver</t>
         </is>
       </c>
       <c r="C67" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CafSignatureCapture.tsx</t>
+          <t>components/patterns/BillingAccountAutoResolver.tsx</t>
         </is>
       </c>
       <c r="D67" s="20" t="inlineStr">
@@ -4227,7 +4279,7 @@
       <c r="G67" s="17" t="inlineStr"/>
       <c r="H67" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -4239,12 +4291,12 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>CheckoutDefaultLayout</t>
+          <t>CafSignatureCapture</t>
         </is>
       </c>
       <c r="C68" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CheckoutDefaultLayout.tsx</t>
+          <t>components/patterns/CafSignatureCapture.tsx</t>
         </is>
       </c>
       <c r="D68" s="20" t="inlineStr">
@@ -4260,14 +4312,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G68" s="17" t="inlineStr">
-        <is>
-          <t>CheckoutSummaryStep</t>
-        </is>
-      </c>
+      <c r="G68" s="17" t="inlineStr"/>
       <c r="H68" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -4279,12 +4327,12 @@
       </c>
       <c r="B69" s="17" t="inlineStr">
         <is>
-          <t>CheckoutSummaryStep</t>
+          <t>CheckoutDefaultLayout</t>
         </is>
       </c>
       <c r="C69" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CheckoutSummaryStep.tsx</t>
+          <t>components/patterns/CheckoutDefaultLayout.tsx</t>
         </is>
       </c>
       <c r="D69" s="20" t="inlineStr">
@@ -4300,10 +4348,14 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G69" s="17" t="inlineStr"/>
+      <c r="G69" s="17" t="inlineStr">
+        <is>
+          <t>CheckoutSummaryStep</t>
+        </is>
+      </c>
       <c r="H69" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4315,12 +4367,12 @@
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>DiscountCard</t>
+          <t>CheckoutSummaryStep</t>
         </is>
       </c>
       <c r="C70" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DiscountCard.tsx</t>
+          <t>components/patterns/CheckoutSummaryStep.tsx</t>
         </is>
       </c>
       <c r="D70" s="20" t="inlineStr">
@@ -4336,11 +4388,7 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G70" s="17" t="inlineStr">
-        <is>
-          <t>PostpaidDiscountsPanel</t>
-        </is>
-      </c>
+      <c r="G70" s="17" t="inlineStr"/>
       <c r="H70" s="17" t="inlineStr">
         <is>
           <t>2026-10-15</t>
@@ -4355,12 +4403,12 @@
       </c>
       <c r="B71" s="17" t="inlineStr">
         <is>
-          <t>FixedPlanStep</t>
+          <t>DiscountCard</t>
         </is>
       </c>
       <c r="C71" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/FixedPlanStep.tsx</t>
+          <t>components/patterns/DiscountCard.tsx</t>
         </is>
       </c>
       <c r="D71" s="20" t="inlineStr">
@@ -4376,10 +4424,14 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G71" s="17" t="inlineStr"/>
+      <c r="G71" s="17" t="inlineStr">
+        <is>
+          <t>PostpaidDiscountsPanel</t>
+        </is>
+      </c>
       <c r="H71" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4391,12 +4443,12 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>FullTerms</t>
+          <t>FixedPlanStep</t>
         </is>
       </c>
       <c r="C72" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CafTerms.tsx</t>
+          <t>components/patterns/FixedPlanStep.tsx</t>
         </is>
       </c>
       <c r="D72" s="20" t="inlineStr">
@@ -4412,14 +4464,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G72" s="17" t="inlineStr">
-        <is>
-          <t>CafSignatureCapture</t>
-        </is>
-      </c>
+      <c r="G72" s="17" t="inlineStr"/>
       <c r="H72" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4431,12 +4479,12 @@
       </c>
       <c r="B73" s="17" t="inlineStr">
         <is>
-          <t>KeyInformationPanel</t>
+          <t>FullTerms</t>
         </is>
       </c>
       <c r="C73" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/KeyInformationPanel.tsx</t>
+          <t>components/patterns/CafTerms.tsx</t>
         </is>
       </c>
       <c r="D73" s="20" t="inlineStr">
@@ -4452,7 +4500,11 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G73" s="17" t="inlineStr"/>
+      <c r="G73" s="17" t="inlineStr">
+        <is>
+          <t>CafSignatureCapture</t>
+        </is>
+      </c>
       <c r="H73" s="17" t="inlineStr">
         <is>
           <t>2026-10-15</t>
@@ -4467,12 +4519,12 @@
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>OrderConfirmationScreen</t>
+          <t>KeyInformationPanel</t>
         </is>
       </c>
       <c r="C74" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/OrderConfirmationScreen.tsx</t>
+          <t>components/patterns/KeyInformationPanel.tsx</t>
         </is>
       </c>
       <c r="D74" s="20" t="inlineStr">
@@ -4488,14 +4540,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G74" s="17" t="inlineStr">
-        <is>
-          <t>ActivationCompleteScreen</t>
-        </is>
-      </c>
+      <c r="G74" s="17" t="inlineStr"/>
       <c r="H74" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4507,12 +4555,12 @@
       </c>
       <c r="B75" s="17" t="inlineStr">
         <is>
-          <t>PlanDetailsDrawer</t>
+          <t>OrderConfirmationScreen</t>
         </is>
       </c>
       <c r="C75" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PlanDetailsDrawer.tsx</t>
+          <t>components/patterns/OrderConfirmationScreen.tsx</t>
         </is>
       </c>
       <c r="D75" s="20" t="inlineStr">
@@ -4530,12 +4578,12 @@
       </c>
       <c r="G75" s="17" t="inlineStr">
         <is>
-          <t>PostpaidPlanAddonsStep</t>
+          <t>ActivationCompleteScreen</t>
         </is>
       </c>
       <c r="H75" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4547,12 +4595,12 @@
       </c>
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>PlanGroupPanel</t>
+          <t>PlanDetailsDrawer</t>
         </is>
       </c>
       <c r="C76" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PlanGroupPanel.tsx</t>
+          <t>components/patterns/PlanDetailsDrawer.tsx</t>
         </is>
       </c>
       <c r="D76" s="20" t="inlineStr">
@@ -4587,12 +4635,12 @@
       </c>
       <c r="B77" s="17" t="inlineStr">
         <is>
-          <t>PlanSearchBox</t>
+          <t>PlanGroupPanel</t>
         </is>
       </c>
       <c r="C77" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PlanSearchBox.tsx</t>
+          <t>components/patterns/PlanGroupPanel.tsx</t>
         </is>
       </c>
       <c r="D77" s="20" t="inlineStr">
@@ -4627,12 +4675,12 @@
       </c>
       <c r="B78" s="17" t="inlineStr">
         <is>
-          <t>PlanTabStrip</t>
+          <t>PlanSearchBox</t>
         </is>
       </c>
       <c r="C78" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PlanTabStrip.tsx</t>
+          <t>components/patterns/PlanSearchBox.tsx</t>
         </is>
       </c>
       <c r="D78" s="20" t="inlineStr">
@@ -4655,7 +4703,7 @@
       </c>
       <c r="H78" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4667,12 +4715,12 @@
       </c>
       <c r="B79" s="17" t="inlineStr">
         <is>
-          <t>PostpaidAddonsPanel</t>
+          <t>PlanTabStrip</t>
         </is>
       </c>
       <c r="C79" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidAddonsPanel.tsx</t>
+          <t>components/patterns/PlanTabStrip.tsx</t>
         </is>
       </c>
       <c r="D79" s="20" t="inlineStr">
@@ -4707,12 +4755,12 @@
       </c>
       <c r="B80" s="17" t="inlineStr">
         <is>
-          <t>PostpaidDiscountsPanel</t>
+          <t>PostpaidAddonsPanel</t>
         </is>
       </c>
       <c r="C80" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidDiscountsPanel.tsx</t>
+          <t>components/patterns/PostpaidAddonsPanel.tsx</t>
         </is>
       </c>
       <c r="D80" s="20" t="inlineStr">
@@ -4735,7 +4783,7 @@
       </c>
       <c r="H80" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4747,12 +4795,12 @@
       </c>
       <c r="B81" s="17" t="inlineStr">
         <is>
-          <t>PostpaidMonthlySummary</t>
+          <t>PostpaidDiscountsPanel</t>
         </is>
       </c>
       <c r="C81" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidMonthlySummary.tsx</t>
+          <t>components/patterns/PostpaidDiscountsPanel.tsx</t>
         </is>
       </c>
       <c r="D81" s="20" t="inlineStr">
@@ -4775,7 +4823,7 @@
       </c>
       <c r="H81" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4787,12 +4835,12 @@
       </c>
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>PostpaidPlanAddonsStep</t>
+          <t>PostpaidMonthlySummary</t>
         </is>
       </c>
       <c r="C82" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidPlanAddonsStep.tsx</t>
+          <t>components/patterns/PostpaidMonthlySummary.tsx</t>
         </is>
       </c>
       <c r="D82" s="20" t="inlineStr">
@@ -4808,10 +4856,14 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G82" s="17" t="inlineStr"/>
+      <c r="G82" s="17" t="inlineStr">
+        <is>
+          <t>PostpaidPlanAddonsStep</t>
+        </is>
+      </c>
       <c r="H82" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4875,12 @@
       </c>
       <c r="B83" s="17" t="inlineStr">
         <is>
-          <t>PostpaidPlanCard</t>
+          <t>PostpaidPlanAddonsStep</t>
         </is>
       </c>
       <c r="C83" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidPlanCard.tsx</t>
+          <t>components/patterns/PostpaidPlanAddonsStep.tsx</t>
         </is>
       </c>
       <c r="D83" s="20" t="inlineStr">
@@ -4844,14 +4896,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G83" s="17" t="inlineStr">
-        <is>
-          <t>PlanGroupPanel</t>
-        </is>
-      </c>
+      <c r="G83" s="17" t="inlineStr"/>
       <c r="H83" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -4863,12 +4911,12 @@
       </c>
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>PrepaidCartStep</t>
+          <t>PostpaidPlanCard</t>
         </is>
       </c>
       <c r="C84" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidCartStep.tsx</t>
+          <t>components/patterns/PostpaidPlanCard.tsx</t>
         </is>
       </c>
       <c r="D84" s="20" t="inlineStr">
@@ -4884,10 +4932,14 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G84" s="17" t="inlineStr"/>
+      <c r="G84" s="17" t="inlineStr">
+        <is>
+          <t>PlanGroupPanel</t>
+        </is>
+      </c>
       <c r="H84" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4899,12 +4951,12 @@
       </c>
       <c r="B85" s="17" t="inlineStr">
         <is>
-          <t>PrepaidCheckoutStep</t>
+          <t>PrepaidCartStep</t>
         </is>
       </c>
       <c r="C85" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidCheckoutStep.tsx</t>
+          <t>components/patterns/PrepaidCartStep.tsx</t>
         </is>
       </c>
       <c r="D85" s="20" t="inlineStr">
@@ -4923,7 +4975,7 @@
       <c r="G85" s="17" t="inlineStr"/>
       <c r="H85" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4987,12 @@
       </c>
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>PrepaidPackDetailsDrawer</t>
+          <t>PrepaidCheckoutStep</t>
         </is>
       </c>
       <c r="C86" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidPackDetailsDrawer.tsx</t>
+          <t>components/patterns/PrepaidCheckoutStep.tsx</t>
         </is>
       </c>
       <c r="D86" s="20" t="inlineStr">
@@ -4956,11 +5008,7 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G86" s="17" t="inlineStr">
-        <is>
-          <t>PrepaidPlanStep</t>
-        </is>
-      </c>
+      <c r="G86" s="17" t="inlineStr"/>
       <c r="H86" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
@@ -4975,12 +5023,12 @@
       </c>
       <c r="B87" s="17" t="inlineStr">
         <is>
-          <t>PrepaidPlanCard</t>
+          <t>PrepaidPackDetailsDrawer</t>
         </is>
       </c>
       <c r="C87" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidPlanCard.tsx</t>
+          <t>components/patterns/PrepaidPackDetailsDrawer.tsx</t>
         </is>
       </c>
       <c r="D87" s="20" t="inlineStr">
@@ -5015,12 +5063,12 @@
       </c>
       <c r="B88" s="17" t="inlineStr">
         <is>
-          <t>PrepaidPlanStep</t>
+          <t>PrepaidPlanCard</t>
         </is>
       </c>
       <c r="C88" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidPlanStep.tsx</t>
+          <t>components/patterns/PrepaidPlanCard.tsx</t>
         </is>
       </c>
       <c r="D88" s="20" t="inlineStr">
@@ -5036,10 +5084,14 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G88" s="17" t="inlineStr"/>
+      <c r="G88" s="17" t="inlineStr">
+        <is>
+          <t>PrepaidPlanStep</t>
+        </is>
+      </c>
       <c r="H88" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5051,12 +5103,12 @@
       </c>
       <c r="B89" s="17" t="inlineStr">
         <is>
-          <t>SummaryTables</t>
+          <t>PrepaidPlanStep</t>
         </is>
       </c>
       <c r="C89" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CheckoutSummaryTables.tsx</t>
+          <t>components/patterns/PrepaidPlanStep.tsx</t>
         </is>
       </c>
       <c r="D89" s="20" t="inlineStr">
@@ -5072,14 +5124,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G89" s="17" t="inlineStr">
-        <is>
-          <t>CheckoutSummaryStep, checkoutDetailedTables</t>
-        </is>
-      </c>
+      <c r="G89" s="17" t="inlineStr"/>
       <c r="H89" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5091,12 +5139,12 @@
       </c>
       <c r="B90" s="17" t="inlineStr">
         <is>
-          <t>WinCashPaymentStep</t>
+          <t>SummaryTables</t>
         </is>
       </c>
       <c r="C90" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/WinCashPaymentStep.tsx</t>
+          <t>components/patterns/CheckoutSummaryTables.tsx</t>
         </is>
       </c>
       <c r="D90" s="20" t="inlineStr">
@@ -5112,7 +5160,11 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G90" s="17" t="inlineStr"/>
+      <c r="G90" s="17" t="inlineStr">
+        <is>
+          <t>CheckoutSummaryStep, checkoutDetailedTables</t>
+        </is>
+      </c>
       <c r="H90" s="17" t="inlineStr">
         <is>
           <t>2026-10-15</t>
@@ -5127,12 +5179,12 @@
       </c>
       <c r="B91" s="17" t="inlineStr">
         <is>
-          <t>BillingAccountStep</t>
+          <t>WinCashPaymentStep</t>
         </is>
       </c>
       <c r="C91" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/BillingAccountStep.tsx</t>
+          <t>components/patterns/WinCashPaymentStep.tsx</t>
         </is>
       </c>
       <c r="D91" s="20" t="inlineStr">
@@ -5141,17 +5193,17 @@
         </is>
       </c>
       <c r="E91" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F91" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G91" s="17" t="inlineStr"/>
       <c r="H91" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5215,12 @@
       </c>
       <c r="B92" s="17" t="inlineStr">
         <is>
-          <t>BillingProfileSetupDrawer</t>
+          <t>BillingAccountStep</t>
         </is>
       </c>
       <c r="C92" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/BillingProfileSetupDrawer.tsx</t>
+          <t>components/patterns/BillingAccountStep.tsx</t>
         </is>
       </c>
       <c r="D92" s="20" t="inlineStr">
@@ -5184,14 +5236,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G92" s="17" t="inlineStr">
-        <is>
-          <t>BillingAccountStep</t>
-        </is>
-      </c>
+      <c r="G92" s="17" t="inlineStr"/>
       <c r="H92" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -5203,12 +5251,12 @@
       </c>
       <c r="B93" s="17" t="inlineStr">
         <is>
-          <t>ZsbAddressStep</t>
+          <t>BillingProfileSetupDrawer</t>
         </is>
       </c>
       <c r="C93" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/ZsbAddressStep.tsx</t>
+          <t>components/patterns/BillingProfileSetupDrawer.tsx</t>
         </is>
       </c>
       <c r="D93" s="20" t="inlineStr">
@@ -5224,10 +5272,14 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G93" s="17" t="inlineStr"/>
+      <c r="G93" s="17" t="inlineStr">
+        <is>
+          <t>BillingAccountStep</t>
+        </is>
+      </c>
       <c r="H93" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5239,12 +5291,12 @@
       </c>
       <c r="B94" s="17" t="inlineStr">
         <is>
-          <t>AppointmentBookingStep</t>
+          <t>ZsbAddressStep</t>
         </is>
       </c>
       <c r="C94" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/AppointmentBookingStep.tsx</t>
+          <t>components/patterns/ZsbAddressStep.tsx</t>
         </is>
       </c>
       <c r="D94" s="20" t="inlineStr">
@@ -5253,11 +5305,11 @@
         </is>
       </c>
       <c r="E94" s="17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F94" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G94" s="17" t="inlineStr"/>
@@ -5275,12 +5327,12 @@
       </c>
       <c r="B95" s="17" t="inlineStr">
         <is>
-          <t>DemoFaultPanel</t>
+          <t>AppointmentBookingStep</t>
         </is>
       </c>
       <c r="C95" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DemoFaultPanel.tsx</t>
+          <t>components/patterns/AppointmentBookingStep.tsx</t>
         </is>
       </c>
       <c r="D95" s="20" t="inlineStr">
@@ -5289,17 +5341,17 @@
         </is>
       </c>
       <c r="E95" s="17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F95" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, administration</t>
         </is>
       </c>
       <c r="G95" s="17" t="inlineStr"/>
       <c r="H95" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5311,12 +5363,12 @@
       </c>
       <c r="B96" s="17" t="inlineStr">
         <is>
-          <t>DonorAttachmentStep</t>
+          <t>DemoFaultPanel</t>
         </is>
       </c>
       <c r="C96" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DonorAttachmentStep.tsx</t>
+          <t>components/patterns/DemoFaultPanel.tsx</t>
         </is>
       </c>
       <c r="D96" s="20" t="inlineStr">
@@ -5335,7 +5387,7 @@
       <c r="G96" s="17" t="inlineStr"/>
       <c r="H96" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5347,12 +5399,12 @@
       </c>
       <c r="B97" s="17" t="inlineStr">
         <is>
-          <t>DonorDetailsStep</t>
+          <t>DonorAttachmentStep</t>
         </is>
       </c>
       <c r="C97" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DonorDetailsStep.tsx</t>
+          <t>components/patterns/DonorAttachmentStep.tsx</t>
         </is>
       </c>
       <c r="D97" s="20" t="inlineStr">
@@ -5368,11 +5420,7 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
         </is>
       </c>
-      <c r="G97" s="17" t="inlineStr">
-        <is>
-          <t>DonorAttachmentStep</t>
-        </is>
-      </c>
+      <c r="G97" s="17" t="inlineStr"/>
       <c r="H97" s="17" t="inlineStr">
         <is>
           <t>2026-10-19</t>
@@ -5387,12 +5435,12 @@
       </c>
       <c r="B98" s="17" t="inlineStr">
         <is>
-          <t>EntityMissing</t>
+          <t>DonorDetailsStep</t>
         </is>
       </c>
       <c r="C98" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/EntityMissing.tsx</t>
+          <t>components/patterns/DonorDetailsStep.tsx</t>
         </is>
       </c>
       <c r="D98" s="20" t="inlineStr">
@@ -5405,13 +5453,17 @@
       </c>
       <c r="F98" s="17" t="inlineStr">
         <is>
-          <t>lead-management, order-management, sim-number-management, trouble-ticketing-complaints, customer360, tasks</t>
-        </is>
-      </c>
-      <c r="G98" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
+        </is>
+      </c>
+      <c r="G98" s="17" t="inlineStr">
+        <is>
+          <t>DonorAttachmentStep</t>
+        </is>
+      </c>
       <c r="H98" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5423,12 +5475,12 @@
       </c>
       <c r="B99" s="17" t="inlineStr">
         <is>
-          <t>ActivityCommentsStep</t>
+          <t>EntityMissing</t>
         </is>
       </c>
       <c r="C99" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/ActivityCommentsStep.tsx</t>
+          <t>components/patterns/EntityMissing.tsx</t>
         </is>
       </c>
       <c r="D99" s="20" t="inlineStr">
@@ -5437,17 +5489,17 @@
         </is>
       </c>
       <c r="E99" s="17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F99" s="17" t="inlineStr">
         <is>
-          <t>pre-to-post-migration, sim-number-management, administration</t>
+          <t>lead-management, order-management, sim-number-management, trouble-ticketing-complaints, customer360, tasks</t>
         </is>
       </c>
       <c r="G99" s="17" t="inlineStr"/>
       <c r="H99" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5459,12 +5511,12 @@
       </c>
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>LineSelectionStep</t>
+          <t>ActivityCommentsStep</t>
         </is>
       </c>
       <c r="C100" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/LineSelectionStep.tsx</t>
+          <t>components/patterns/ActivityCommentsStep.tsx</t>
         </is>
       </c>
       <c r="D100" s="20" t="inlineStr">
@@ -5477,13 +5529,13 @@
       </c>
       <c r="F100" s="17" t="inlineStr">
         <is>
-          <t>mobile-service-changes, pre-to-post-migration, administration</t>
+          <t>pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G100" s="17" t="inlineStr"/>
       <c r="H100" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -5495,12 +5547,12 @@
       </c>
       <c r="B101" s="17" t="inlineStr">
         <is>
-          <t>TicketCreationModal</t>
+          <t>LineSelectionStep</t>
         </is>
       </c>
       <c r="C101" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/TicketCreationModal.tsx</t>
+          <t>components/patterns/LineSelectionStep.tsx</t>
         </is>
       </c>
       <c r="D101" s="20" t="inlineStr">
@@ -5513,13 +5565,13 @@
       </c>
       <c r="F101" s="17" t="inlineStr">
         <is>
-          <t>trouble-ticketing-complaints, customer360, support</t>
+          <t>mobile-service-changes, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G101" s="17" t="inlineStr"/>
       <c r="H101" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5531,25 +5583,25 @@
       </c>
       <c r="B102" s="17" t="inlineStr">
         <is>
-          <t>BulkOperationPortal</t>
+          <t>TicketCreationModal</t>
         </is>
       </c>
       <c r="C102" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/BulkOperationPortal.tsx</t>
-        </is>
-      </c>
-      <c r="D102" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>components/patterns/TicketCreationModal.tsx</t>
+        </is>
+      </c>
+      <c r="D102" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E102" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F102" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b</t>
+          <t>trouble-ticketing-complaints, customer360, support</t>
         </is>
       </c>
       <c r="G102" s="17" t="inlineStr"/>
@@ -5567,12 +5619,12 @@
       </c>
       <c r="B103" s="17" t="inlineStr">
         <is>
-          <t>DualPlaySerialCheckStep</t>
+          <t>BulkOperationPortal</t>
         </is>
       </c>
       <c r="C103" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DualPlaySerialCheckStep.tsx</t>
+          <t>components/patterns/BulkOperationPortal.tsx</t>
         </is>
       </c>
       <c r="D103" s="21" t="inlineStr">
@@ -5585,7 +5637,7 @@
       </c>
       <c r="F103" s="17" t="inlineStr">
         <is>
-          <t>fwa-5g-home</t>
+          <t>enterprise-iot-b2b</t>
         </is>
       </c>
       <c r="G103" s="17" t="inlineStr"/>
@@ -5603,12 +5655,12 @@
       </c>
       <c r="B104" s="17" t="inlineStr">
         <is>
-          <t>SimSwapFormStep</t>
+          <t>DualPlaySerialCheckStep</t>
         </is>
       </c>
       <c r="C104" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/SimSwapFormStep.tsx</t>
+          <t>components/patterns/DualPlaySerialCheckStep.tsx</t>
         </is>
       </c>
       <c r="D104" s="21" t="inlineStr">
@@ -5621,7 +5673,7 @@
       </c>
       <c r="F104" s="17" t="inlineStr">
         <is>
-          <t>sim-number-management</t>
+          <t>fwa-5g-home</t>
         </is>
       </c>
       <c r="G104" s="17" t="inlineStr"/>
@@ -5639,12 +5691,12 @@
       </c>
       <c r="B105" s="17" t="inlineStr">
         <is>
-          <t>VerificationGate</t>
+          <t>SimSwapFormStep</t>
         </is>
       </c>
       <c r="C105" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/VerificationGate.tsx</t>
+          <t>components/patterns/SimSwapFormStep.tsx</t>
         </is>
       </c>
       <c r="D105" s="21" t="inlineStr">
@@ -5657,7 +5709,7 @@
       </c>
       <c r="F105" s="17" t="inlineStr">
         <is>
-          <t>customer360</t>
+          <t>sim-number-management</t>
         </is>
       </c>
       <c r="G105" s="17" t="inlineStr"/>
@@ -5670,36 +5722,36 @@
     <row r="106">
       <c r="A106" s="17" t="inlineStr">
         <is>
-          <t>Wizard</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="B106" s="17" t="inlineStr">
         <is>
-          <t>AbandonDialog</t>
+          <t>VerificationGate</t>
         </is>
       </c>
       <c r="C106" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/WizardDialogs.tsx</t>
-        </is>
-      </c>
-      <c r="D106" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>components/patterns/VerificationGate.tsx</t>
+        </is>
+      </c>
+      <c r="D106" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E106" s="17" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F106" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>customer360</t>
         </is>
       </c>
       <c r="G106" s="17" t="inlineStr"/>
       <c r="H106" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -5711,12 +5763,12 @@
       </c>
       <c r="B107" s="17" t="inlineStr">
         <is>
-          <t>CustomerMirrorPanel</t>
+          <t>AbandonDialog</t>
         </is>
       </c>
       <c r="C107" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/CustomerMirrorPanel.tsx</t>
+          <t>components/patterns/wizard/WizardDialogs.tsx</t>
         </is>
       </c>
       <c r="D107" s="20" t="inlineStr">
@@ -5735,7 +5787,7 @@
       <c r="G107" s="17" t="inlineStr"/>
       <c r="H107" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -5747,12 +5799,12 @@
       </c>
       <c r="B108" s="17" t="inlineStr">
         <is>
-          <t>CustomerViewButton</t>
+          <t>CustomerMirrorPanel</t>
         </is>
       </c>
       <c r="C108" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/CustomerViewButton.tsx</t>
+          <t>components/patterns/wizard/CustomerMirrorPanel.tsx</t>
         </is>
       </c>
       <c r="D108" s="20" t="inlineStr">
@@ -5768,14 +5820,10 @@
           <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
-      <c r="G108" s="17" t="inlineStr">
-        <is>
-          <t>WizardStepHeader</t>
-        </is>
-      </c>
+      <c r="G108" s="17" t="inlineStr"/>
       <c r="H108" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5787,12 +5835,12 @@
       </c>
       <c r="B109" s="17" t="inlineStr">
         <is>
-          <t>StepSummaryPanel</t>
+          <t>CustomerViewButton</t>
         </is>
       </c>
       <c r="C109" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/StepSummaryPanel.tsx</t>
+          <t>components/patterns/wizard/CustomerViewButton.tsx</t>
         </is>
       </c>
       <c r="D109" s="20" t="inlineStr">
@@ -5808,10 +5856,14 @@
           <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
-      <c r="G109" s="17" t="inlineStr"/>
+      <c r="G109" s="17" t="inlineStr">
+        <is>
+          <t>WizardStepHeader</t>
+        </is>
+      </c>
       <c r="H109" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5823,12 +5875,12 @@
       </c>
       <c r="B110" s="17" t="inlineStr">
         <is>
-          <t>StepSummarySection</t>
+          <t>StepSummaryPanel</t>
         </is>
       </c>
       <c r="C110" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/StepSummarySection.tsx</t>
+          <t>components/patterns/wizard/StepSummaryPanel.tsx</t>
         </is>
       </c>
       <c r="D110" s="20" t="inlineStr">
@@ -5844,14 +5896,10 @@
           <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
-      <c r="G110" s="17" t="inlineStr">
-        <is>
-          <t>StepSummaryPanel</t>
-        </is>
-      </c>
+      <c r="G110" s="17" t="inlineStr"/>
       <c r="H110" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -5863,12 +5911,12 @@
       </c>
       <c r="B111" s="17" t="inlineStr">
         <is>
-          <t>SummaryFieldRow</t>
+          <t>StepSummarySection</t>
         </is>
       </c>
       <c r="C111" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/SummaryFieldRow.tsx</t>
+          <t>components/patterns/wizard/StepSummarySection.tsx</t>
         </is>
       </c>
       <c r="D111" s="20" t="inlineStr">
@@ -5891,7 +5939,7 @@
       </c>
       <c r="H111" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -5903,12 +5951,12 @@
       </c>
       <c r="B112" s="17" t="inlineStr">
         <is>
-          <t>WizardFooter</t>
+          <t>SummaryFieldRow</t>
         </is>
       </c>
       <c r="C112" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/WizardFooter.tsx</t>
+          <t>components/patterns/wizard/SummaryFieldRow.tsx</t>
         </is>
       </c>
       <c r="D112" s="20" t="inlineStr">
@@ -5924,10 +5972,14 @@
           <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
-      <c r="G112" s="17" t="inlineStr"/>
+      <c r="G112" s="17" t="inlineStr">
+        <is>
+          <t>StepSummaryPanel</t>
+        </is>
+      </c>
       <c r="H112" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5939,12 +5991,12 @@
       </c>
       <c r="B113" s="17" t="inlineStr">
         <is>
-          <t>WizardStepHeader</t>
+          <t>WizardFooter</t>
         </is>
       </c>
       <c r="C113" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/WizardStepHeader.tsx</t>
+          <t>components/patterns/wizard/WizardFooter.tsx</t>
         </is>
       </c>
       <c r="D113" s="20" t="inlineStr">
@@ -5963,7 +6015,7 @@
       <c r="G113" s="17" t="inlineStr"/>
       <c r="H113" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5975,12 +6027,12 @@
       </c>
       <c r="B114" s="17" t="inlineStr">
         <is>
-          <t>WizardTitleBand</t>
+          <t>WizardStepHeader</t>
         </is>
       </c>
       <c r="C114" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/WizardTitleBand.tsx</t>
+          <t>components/patterns/wizard/WizardStepHeader.tsx</t>
         </is>
       </c>
       <c r="D114" s="20" t="inlineStr">
@@ -5999,12 +6051,48 @@
       <c r="G114" s="17" t="inlineStr"/>
       <c r="H114" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="17" t="inlineStr">
+        <is>
+          <t>Wizard</t>
+        </is>
+      </c>
+      <c r="B115" s="17" t="inlineStr">
+        <is>
+          <t>WizardTitleBand</t>
+        </is>
+      </c>
+      <c r="C115" s="17" t="inlineStr">
+        <is>
+          <t>components/patterns/wizard/WizardTitleBand.tsx</t>
+        </is>
+      </c>
+      <c r="D115" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
+        </is>
+      </c>
+      <c r="E115" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F115" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+      <c r="G115" s="17" t="inlineStr"/>
+      <c r="H115" s="17" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H114"/>
+  <autoFilter ref="A1:H115"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6015,7 +6103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.50" customWidth="1" min="1" max="1"/>
@@ -6101,7 +6189,7 @@
       </c>
       <c r="G2" s="17" t="inlineStr">
         <is>
-          <t>CompanySearchInput, ContactPhoneInput, CpeSerialScanner, MsisdnPicker, SimSerialScanner, AppointmentBookingStep, BillingAccountAutoResolver, BillingAccountStep, CafSignatureCapture, CafTerms, FixedPlanStep, PrepaidCartStep, PrepaidCheckoutStep, PrepaidPlanStep, TicketCreationModal, VerificationGate, ZsbAddressStep, lineSelectionModel, useCheckoutSummary, useIdLookup, usePostpaidPlanAddons, StepSummaryPanel, stepSummary, useJourneyStartResume, useWizardDraftActions, LocationInput, activityEngine, agentProfileEngine, businessAccountEngine, connectionEligibility, customer360Engine, fibreServiceability, serviceLocationLookup, useAreaOptions, configStore, entityStore</t>
+          <t>CompanySearchInput, ContactPhoneInput, CpeSerialScanner, MsisdnPicker, SimSerialScanner, AppointmentBookingStep, BillingAccountAutoResolver, BillingAccountStep, CafSignatureCapture, CafTerms, FixedPlanStep, PrepaidCartStep, PrepaidCheckoutStep, PrepaidPlanStep, TicketCreationModal, ZsbAddressStep, lineSelectionModel, useCheckoutSummary, useIdLookup, usePostpaidPlanAddons, StepSummaryPanel, stepSummary, useJourneyStartResume, useWizardDraftActions, LocationInput, activityEngine, agentProfileEngine, businessAccountEngine, connectionEligibility, customer360Engine, fibreServiceability, serviceLocationLookup, useAreaOptions, configStore, entityStore</t>
         </is>
       </c>
       <c r="H2" s="17" t="inlineStr">
@@ -6158,12 +6246,12 @@
       </c>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t>postpaidPricing</t>
+          <t>hrnConfiguration</t>
         </is>
       </c>
       <c r="C4" s="17" t="inlineStr">
         <is>
-          <t>engines/postpaidPricing.ts</t>
+          <t>engines/hrnConfiguration.ts</t>
         </is>
       </c>
       <c r="D4" s="20" t="inlineStr">
@@ -6181,12 +6269,12 @@
       </c>
       <c r="G4" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, eligibilityRowsModel, CheckoutDefaultLayout, PostpaidMonthlySummary, PostpaidPlanAddonsStep, checkoutDetailedTables, checkoutSummaryRows, useCheckoutSummary, usePostpaidPlanAddons, ruleEngine</t>
+          <t>eligibilityRowsModel, PostpaidPlanAddonsStep, useCheckoutSummary, ruleEngine</t>
         </is>
       </c>
       <c r="H4" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6314,7 @@
       </c>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -6358,12 +6446,12 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>serviceCall</t>
+          <t>milestoneEngine</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>engines/serviceCall.ts</t>
+          <t>engines/milestoneEngine.ts</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -6381,12 +6469,12 @@
       </c>
       <c r="G9" s="17" t="inlineStr">
         <is>
-          <t>DemoFaultPanel, ValidationStatus, useIdLookup</t>
+          <t>guidedWizardTypes, useJourneyMilestones</t>
         </is>
       </c>
       <c r="H9" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -6398,12 +6486,12 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>activityEngine</t>
+          <t>serviceCall</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>engines/activityEngine.ts</t>
+          <t>engines/serviceCall.ts</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -6412,21 +6500,21 @@
         </is>
       </c>
       <c r="E10" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G10" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen, useWizardDraftActions</t>
+          <t>DemoFaultPanel, ValidationStatus, useIdLookup</t>
         </is>
       </c>
       <c r="H10" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6526,12 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>businessSegment</t>
+          <t>activityEngine</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>engines/businessSegment.ts</t>
+          <t>engines/activityEngine.ts</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -6456,17 +6544,17 @@
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, navigation, administration, customer-search, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G11" s="17" t="inlineStr">
         <is>
-          <t>BillingAccountStep, customer360Demo, businessAccountEngine</t>
+          <t>ActivationCompleteScreen, useWizardDraftActions</t>
         </is>
       </c>
       <c r="H11" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -6478,12 +6566,12 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>customerBenefitEngine</t>
+          <t>businessSegment</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>engines/customerBenefitEngine.ts</t>
+          <t>engines/businessSegment.ts</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -6492,21 +6580,21 @@
         </is>
       </c>
       <c r="E12" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, navigation, administration, customer-search, customer360</t>
         </is>
       </c>
       <c r="G12" s="17" t="inlineStr">
         <is>
-          <t>PostpaidPlanAddonsStep, usePostpaidPlanAddons</t>
+          <t>BillingAccountStep, customer360Demo, businessAccountEngine</t>
         </is>
       </c>
       <c r="H12" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -6518,12 +6606,12 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>addonEligibility</t>
+          <t>postpaidPricing</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>engines/addonEligibility.ts</t>
+          <t>engines/postpaidPricing.ts</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -6532,17 +6620,21 @@
         </is>
       </c>
       <c r="E13" s="17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+      <c r="G13" s="17" t="inlineStr">
+        <is>
+          <t>MsisdnPicker, CheckoutDefaultLayout, PostpaidMonthlySummary, checkoutDetailedTables, checkoutSummaryRows, useCheckoutSummary, usePostpaidPlanAddons</t>
+        </is>
+      </c>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -6568,11 +6660,11 @@
         </is>
       </c>
       <c r="E14" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
         </is>
       </c>
       <c r="G14" s="17" t="inlineStr"/>
@@ -6590,12 +6682,12 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>eligibilityEngine</t>
+          <t>customerBenefitEngine</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>engines/eligibilityEngine.ts</t>
+          <t>engines/customerBenefitEngine.ts</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -6604,21 +6696,21 @@
         </is>
       </c>
       <c r="E15" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
         </is>
       </c>
       <c r="G15" s="17" t="inlineStr">
         <is>
-          <t>eligibilityRowsModel, eligibilityTypes</t>
+          <t>PostpaidPlanAddonsStep, usePostpaidPlanAddons</t>
         </is>
       </c>
       <c r="H15" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6630,12 +6722,12 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>fibreServiceability</t>
+          <t>eligibilityEngine</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>engines/fibreServiceability.ts</t>
+          <t>engines/eligibilityEngine.ts</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -6644,21 +6736,21 @@
         </is>
       </c>
       <c r="E16" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
         </is>
       </c>
       <c r="G16" s="17" t="inlineStr">
         <is>
-          <t>FibreReadinessBanner, ActivationCompleteScreen</t>
+          <t>eligibilityRowsModel, eligibilityTypes</t>
         </is>
       </c>
       <c r="H16" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -6670,12 +6762,12 @@
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>personaEngine</t>
+          <t>addonEligibility</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>engines/personaEngine.ts</t>
+          <t>engines/addonEligibility.ts</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -6688,17 +6780,13 @@
       </c>
       <c r="F17" s="17" t="inlineStr">
         <is>
-          <t>dashboard, order-management, product-lines, sim-number-management, navigation, administration, customer360, orders, profile</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>approvalAuthority, navigationEngine</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G17" s="17" t="inlineStr"/>
       <c r="H17" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -6710,12 +6798,12 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>eligibilityGuard</t>
+          <t>fibreServiceability</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>engines/eligibilityGuard.ts</t>
+          <t>engines/fibreServiceability.ts</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -6724,17 +6812,21 @@
         </is>
       </c>
       <c r="E18" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration</t>
-        </is>
-      </c>
-      <c r="G18" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G18" s="17" t="inlineStr">
+        <is>
+          <t>FibreReadinessBanner, ActivationCompleteScreen</t>
+        </is>
+      </c>
       <c r="H18" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -6746,12 +6838,12 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>serviceLocationLookup</t>
+          <t>personaEngine</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>engines/serviceLocationLookup.ts</t>
+          <t>engines/personaEngine.ts</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -6760,21 +6852,21 @@
         </is>
       </c>
       <c r="E19" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F19" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>dashboard, order-management, product-lines, sim-number-management, navigation, administration, customer360, orders, profile</t>
         </is>
       </c>
       <c r="G19" s="17" t="inlineStr">
         <is>
-          <t>ZsbAddressStep</t>
+          <t>approvalAuthority, navigationEngine</t>
         </is>
       </c>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -6786,12 +6878,12 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>agentPrivilegeEngine</t>
+          <t>eligibilityGuard</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>engines/agentPrivilegeEngine.ts</t>
+          <t>engines/eligibilityGuard.ts</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -6800,17 +6892,17 @@
         </is>
       </c>
       <c r="E20" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F20" s="17" t="inlineStr">
         <is>
-          <t>trouble-ticketing-complaints, navigation, administration, customer360, profile, tasks</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration</t>
         </is>
       </c>
       <c r="G20" s="17" t="inlineStr"/>
       <c r="H20" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6822,12 +6914,12 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>agentTaskEngine</t>
+          <t>serviceLocationLookup</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>engines/agentTaskEngine.ts</t>
+          <t>engines/serviceLocationLookup.ts</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -6836,17 +6928,21 @@
         </is>
       </c>
       <c r="E21" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F21" s="17" t="inlineStr">
         <is>
-          <t>dashboard, order-management, trouble-ticketing-complaints, orders, support, tasks</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G21" s="17" t="inlineStr">
+        <is>
+          <t>ZsbAddressStep</t>
+        </is>
+      </c>
       <c r="H21" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6858,12 +6954,12 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>approvalAuthority</t>
+          <t>agentPrivilegeEngine</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>engines/approvalAuthority.ts</t>
+          <t>engines/agentPrivilegeEngine.ts</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -6876,13 +6972,13 @@
       </c>
       <c r="F22" s="17" t="inlineStr">
         <is>
-          <t>dashboard, order-management, sim-number-management, navigation, customer360, orders</t>
+          <t>trouble-ticketing-complaints, navigation, administration, customer360, profile, tasks</t>
         </is>
       </c>
       <c r="G22" s="17" t="inlineStr"/>
       <c r="H22" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6990,12 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>portInEngine</t>
+          <t>agentTaskEngine</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>engines/portInEngine.ts</t>
+          <t>engines/agentTaskEngine.ts</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -6912,13 +7008,13 @@
       </c>
       <c r="F23" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
+          <t>dashboard, order-management, trouble-ticketing-complaints, orders, support, tasks</t>
         </is>
       </c>
       <c r="G23" s="17" t="inlineStr"/>
       <c r="H23" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -6930,12 +7026,12 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>csvExport</t>
+          <t>approvalAuthority</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>engines/csvExport.ts</t>
+          <t>engines/approvalAuthority.ts</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -6944,17 +7040,17 @@
         </is>
       </c>
       <c r="E24" s="17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>trouble-ticketing-complaints, customer360, profile, support</t>
+          <t>dashboard, order-management, sim-number-management, navigation, customer360, orders</t>
         </is>
       </c>
       <c r="G24" s="17" t="inlineStr"/>
       <c r="H24" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6966,12 +7062,12 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>bellNotificationExpiry</t>
+          <t>portInEngine</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>engines/bellNotificationExpiry.ts</t>
+          <t>engines/portInEngine.ts</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -6980,17 +7076,17 @@
         </is>
       </c>
       <c r="E25" s="17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F25" s="17" t="inlineStr">
         <is>
-          <t>administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
         </is>
       </c>
       <c r="G25" s="17" t="inlineStr"/>
       <c r="H25" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7002,12 +7098,12 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>businessAccountEngine</t>
+          <t>csvExport</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>engines/businessAccountEngine.ts</t>
+          <t>engines/csvExport.ts</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -7016,17 +7112,17 @@
         </is>
       </c>
       <c r="E26" s="17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>customer-search, customer360</t>
+          <t>trouble-ticketing-complaints, customer360, profile, support</t>
         </is>
       </c>
       <c r="G26" s="17" t="inlineStr"/>
       <c r="H26" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7038,12 +7134,12 @@
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>navigationEngine</t>
+          <t>bellNotificationExpiry</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
-          <t>engines/navigationEngine.ts</t>
+          <t>engines/bellNotificationExpiry.ts</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -7056,13 +7152,13 @@
       </c>
       <c r="F27" s="17" t="inlineStr">
         <is>
-          <t>navigation, customer360</t>
+          <t>administration, customer360</t>
         </is>
       </c>
       <c r="G27" s="17" t="inlineStr"/>
       <c r="H27" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7074,12 +7170,12 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>qnomyQueueEngine</t>
+          <t>businessAccountEngine</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>engines/qnomyQueueEngine.ts</t>
+          <t>engines/businessAccountEngine.ts</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -7092,13 +7188,13 @@
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>navigation, tickets</t>
+          <t>customer-search, customer360</t>
         </is>
       </c>
       <c r="G28" s="17" t="inlineStr"/>
       <c r="H28" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -7110,31 +7206,31 @@
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>agentProfileEngine</t>
+          <t>navigationEngine</t>
         </is>
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>engines/agentProfileEngine.ts</t>
-        </is>
-      </c>
-      <c r="D29" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>engines/navigationEngine.ts</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E29" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
+          <t>navigation, customer360</t>
         </is>
       </c>
       <c r="G29" s="17" t="inlineStr"/>
       <c r="H29" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -7146,25 +7242,25 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>customer360VisibilityEngine</t>
+          <t>qnomyQueueEngine</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>engines/customer360VisibilityEngine.ts</t>
-        </is>
-      </c>
-      <c r="D30" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>engines/qnomyQueueEngine.ts</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E30" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" s="17" t="inlineStr">
         <is>
-          <t>customer360</t>
+          <t>navigation, tickets</t>
         </is>
       </c>
       <c r="G30" s="17" t="inlineStr"/>
@@ -7182,12 +7278,12 @@
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>profileChangeTicket</t>
+          <t>agentProfileEngine</t>
         </is>
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>engines/profileChangeTicket.ts</t>
+          <t>engines/agentProfileEngine.ts</t>
         </is>
       </c>
       <c r="D31" s="21" t="inlineStr">
@@ -7200,13 +7296,13 @@
       </c>
       <c r="F31" s="17" t="inlineStr">
         <is>
-          <t>customer360</t>
+          <t>navigation</t>
         </is>
       </c>
       <c r="G31" s="17" t="inlineStr"/>
       <c r="H31" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7218,12 +7314,12 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>searchScopeEngine</t>
+          <t>customer360VisibilityEngine</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>engines/searchScopeEngine.ts</t>
+          <t>engines/customer360VisibilityEngine.ts</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
@@ -7236,13 +7332,13 @@
       </c>
       <c r="F32" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
+          <t>customer360</t>
         </is>
       </c>
       <c r="G32" s="17" t="inlineStr"/>
       <c r="H32" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7254,27 +7350,31 @@
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>moduleDescriptions</t>
+          <t>profileChangeTicket</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>engines/moduleDescriptions.ts</t>
-        </is>
-      </c>
-      <c r="D33" s="23" t="inlineStr">
-        <is>
-          <t>App shell only</t>
+          <t>engines/profileChangeTicket.ts</t>
+        </is>
+      </c>
+      <c r="D33" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E33" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F33" s="17" t="inlineStr">
+        <is>
+          <t>customer360</t>
+        </is>
+      </c>
       <c r="G33" s="17" t="inlineStr"/>
       <c r="H33" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -7286,107 +7386,95 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>screenGrouping</t>
+          <t>searchScopeEngine</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>engines/screenGrouping.ts</t>
-        </is>
-      </c>
-      <c r="D34" s="23" t="inlineStr">
-        <is>
-          <t>App shell only</t>
+          <t>engines/searchScopeEngine.ts</t>
+        </is>
+      </c>
+      <c r="D34" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E34" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F34" s="17" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
       <c r="G34" s="17" t="inlineStr"/>
       <c r="H34" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="17" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Engine</t>
         </is>
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>entityStore</t>
+          <t>moduleDescriptions</t>
         </is>
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
-          <t>stores/entityStore.ts</t>
-        </is>
-      </c>
-      <c r="D35" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>engines/moduleDescriptions.ts</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="inlineStr">
+        <is>
+          <t>App shell only</t>
         </is>
       </c>
       <c r="E35" s="17" t="n">
-        <v>24</v>
-      </c>
-      <c r="F35" s="17" t="inlineStr">
-        <is>
-          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, sales, support, tasks, tickets</t>
-        </is>
-      </c>
-      <c r="G35" s="17" t="inlineStr">
-        <is>
-          <t>ActivationCompleteScreen, DonorAttachmentStep, DonorDetailsStep, useDraftStepSync, useWizardDraftActions, activityEngine, bellNotificationExpiry, profileChangeTicket</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F35" s="17" t="inlineStr"/>
+      <c r="G35" s="17" t="inlineStr"/>
       <c r="H35" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="17" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Engine</t>
         </is>
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>customerContextStore</t>
+          <t>screenGrouping</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>stores/customerContextStore.ts</t>
-        </is>
-      </c>
-      <c r="D36" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>engines/screenGrouping.ts</t>
+        </is>
+      </c>
+      <c r="D36" s="23" t="inlineStr">
+        <is>
+          <t>App shell only</t>
         </is>
       </c>
       <c r="E36" s="17" t="n">
-        <v>23</v>
-      </c>
-      <c r="F36" s="17" t="inlineStr">
-        <is>
-          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
-        </is>
-      </c>
-      <c r="G36" s="17" t="inlineStr">
-        <is>
-          <t>ActivationCompleteScreen, useActedForCustomer, useWizardDraftActions, authStore</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F36" s="17" t="inlineStr"/>
+      <c r="G36" s="17" t="inlineStr"/>
       <c r="H36" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7398,12 +7486,12 @@
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>authStore</t>
+          <t>entityStore</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>stores/authStore.ts</t>
+          <t>stores/entityStore.ts</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
@@ -7412,21 +7500,21 @@
         </is>
       </c>
       <c r="E37" s="17" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F37" s="17" t="inlineStr">
         <is>
-          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, support, tasks, tickets</t>
+          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G37" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, ActivationCompleteScreen, useWizardDraftActions, activityEngine, agentProfileEngine, profileChangeTicket, configStore</t>
+          <t>ActivationCompleteScreen, DonorAttachmentStep, DonorDetailsStep, useDraftStepSync, useWizardDraftActions, activityEngine, bellNotificationExpiry, profileChangeTicket</t>
         </is>
       </c>
       <c r="H37" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7438,12 +7526,12 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>notificationStore</t>
+          <t>customerContextStore</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>stores/notificationStore.ts</t>
+          <t>stores/customerContextStore.ts</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
@@ -7452,21 +7540,21 @@
         </is>
       </c>
       <c r="E38" s="17" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F38" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, profile, support, tasks</t>
+          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G38" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, ActivationCompleteScreen, TicketCreationModal, useWizardDraftActions, useWizardStepNavigation, profileChangeTicket, useSubmit</t>
+          <t>ActivationCompleteScreen, useActedForCustomer, useWizardDraftActions, authStore</t>
         </is>
       </c>
       <c r="H38" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -7478,12 +7566,12 @@
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>personaStore</t>
+          <t>authStore</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>stores/personaStore.ts</t>
+          <t>stores/authStore.ts</t>
         </is>
       </c>
       <c r="D39" s="20" t="inlineStr">
@@ -7492,16 +7580,16 @@
         </is>
       </c>
       <c r="E39" s="17" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F39" s="17" t="inlineStr">
         <is>
-          <t>dashboard, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, tasks</t>
+          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G39" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, ActivationCompleteScreen, AppointmentBookingStep, configStore</t>
+          <t>MsisdnPicker, ActivationCompleteScreen, useWizardDraftActions, activityEngine, agentProfileEngine, profileChangeTicket, configStore</t>
         </is>
       </c>
       <c r="H39" s="17" t="inlineStr">
@@ -7518,12 +7606,12 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>workflowStore</t>
+          <t>notificationStore</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>stores/workflowStore.ts</t>
+          <t>stores/notificationStore.ts</t>
         </is>
       </c>
       <c r="D40" s="20" t="inlineStr">
@@ -7532,21 +7620,21 @@
         </is>
       </c>
       <c r="E40" s="17" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F40" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, profile, support, tasks</t>
         </is>
       </c>
       <c r="G40" s="17" t="inlineStr">
         <is>
-          <t>useJourneyStartResume, useMirrorChannel, useWizardDraftActions, useWizardStepNavigation</t>
+          <t>MsisdnPicker, ActivationCompleteScreen, TicketCreationModal, useJourneyMilestones, useWizardDraftActions, useWizardStepNavigation, profileChangeTicket, useSubmit</t>
         </is>
       </c>
       <c r="H40" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -7558,35 +7646,35 @@
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>customerVerificationStore</t>
+          <t>personaStore</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>stores/customerVerificationStore.ts</t>
-        </is>
-      </c>
-      <c r="D41" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>stores/personaStore.ts</t>
+        </is>
+      </c>
+      <c r="D41" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E41" s="17" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="F41" s="17" t="inlineStr">
         <is>
-          <t>customer360</t>
+          <t>dashboard, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, tasks</t>
         </is>
       </c>
       <c r="G41" s="17" t="inlineStr">
         <is>
-          <t>VerificationGate</t>
+          <t>MsisdnPicker, eligibilityRowsModel, ActivationCompleteScreen, AppointmentBookingStep, PostpaidPlanAddonsStep, useCheckoutSummary, configStore</t>
         </is>
       </c>
       <c r="H41" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7598,31 +7686,35 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>qnomyQueueStore</t>
+          <t>workflowStore</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>stores/qnomyQueueStore.ts</t>
-        </is>
-      </c>
-      <c r="D42" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>stores/workflowStore.ts</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E42" s="17" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F42" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="G42" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration</t>
+        </is>
+      </c>
+      <c r="G42" s="17" t="inlineStr">
+        <is>
+          <t>useJourneyStartResume, useMirrorChannel, useWizardDraftActions, useWizardStepNavigation</t>
+        </is>
+      </c>
       <c r="H42" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7634,12 +7726,12 @@
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>regionStore</t>
+          <t>customerVerificationStore</t>
         </is>
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>stores/regionStore.ts</t>
+          <t>stores/customerVerificationStore.ts</t>
         </is>
       </c>
       <c r="D43" s="21" t="inlineStr">
@@ -7652,10 +7744,14 @@
       </c>
       <c r="F43" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="G43" s="17" t="inlineStr"/>
+          <t>customer360</t>
+        </is>
+      </c>
+      <c r="G43" s="17" t="inlineStr">
+        <is>
+          <t>VerificationGate</t>
+        </is>
+      </c>
       <c r="H43" s="17" t="inlineStr">
         <is>
           <t>2026-09-24</t>
@@ -7670,12 +7766,12 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>sidebarStore</t>
+          <t>qnomyQueueStore</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>stores/sidebarStore.ts</t>
+          <t>stores/qnomyQueueStore.ts</t>
         </is>
       </c>
       <c r="D44" s="21" t="inlineStr">
@@ -7694,7 +7790,7 @@
       <c r="G44" s="17" t="inlineStr"/>
       <c r="H44" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -7706,12 +7802,12 @@
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>themeStore</t>
+          <t>regionStore</t>
         </is>
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>stores/themeStore.ts</t>
+          <t>stores/regionStore.ts</t>
         </is>
       </c>
       <c r="D45" s="21" t="inlineStr">
@@ -7730,7 +7826,7 @@
       <c r="G45" s="17" t="inlineStr"/>
       <c r="H45" s="17" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7742,23 +7838,27 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>configStore</t>
+          <t>sidebarStore</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>stores/configStore.ts</t>
-        </is>
-      </c>
-      <c r="D46" s="23" t="inlineStr">
-        <is>
-          <t>App shell only</t>
+          <t>stores/sidebarStore.ts</t>
+        </is>
+      </c>
+      <c r="D46" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E46" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F46" s="17" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
       <c r="G46" s="17" t="inlineStr"/>
       <c r="H46" s="17" t="inlineStr">
         <is>
@@ -7769,80 +7869,68 @@
     <row r="47">
       <c r="A47" s="17" t="inlineStr">
         <is>
-          <t>Hook</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>useEnterToSubmit</t>
+          <t>themeStore</t>
         </is>
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>hooks/useEnterToSubmit.ts</t>
-        </is>
-      </c>
-      <c r="D47" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>stores/themeStore.ts</t>
+        </is>
+      </c>
+      <c r="D47" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E47" s="17" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F47" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
-        </is>
-      </c>
-      <c r="G47" s="17" t="inlineStr">
-        <is>
-          <t>VerificationGate, useIdLookup</t>
-        </is>
-      </c>
+          <t>navigation</t>
+        </is>
+      </c>
+      <c r="G47" s="17" t="inlineStr"/>
       <c r="H47" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="17" t="inlineStr">
         <is>
-          <t>Hook</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>useSearchListNav</t>
+          <t>configStore</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>hooks/useSearchListNav.ts</t>
-        </is>
-      </c>
-      <c r="D48" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>stores/configStore.ts</t>
+        </is>
+      </c>
+      <c r="D48" s="23" t="inlineStr">
+        <is>
+          <t>App shell only</t>
         </is>
       </c>
       <c r="E48" s="17" t="n">
-        <v>11</v>
-      </c>
-      <c r="F48" s="17" t="inlineStr">
-        <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, navigation, administration, customer360</t>
-        </is>
-      </c>
-      <c r="G48" s="17" t="inlineStr">
-        <is>
-          <t>CompanySearchInput, ContactPhoneInput, PlanSearchBox, LocationInput</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F48" s="17" t="inlineStr"/>
+      <c r="G48" s="17" t="inlineStr"/>
       <c r="H48" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7854,12 +7942,12 @@
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>useAreaOptions</t>
+          <t>useEnterToSubmit</t>
         </is>
       </c>
       <c r="C49" s="17" t="inlineStr">
         <is>
-          <t>hooks/useAreaOptions.ts</t>
+          <t>hooks/useEnterToSubmit.ts</t>
         </is>
       </c>
       <c r="D49" s="20" t="inlineStr">
@@ -7868,21 +7956,21 @@
         </is>
       </c>
       <c r="E49" s="17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F49" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G49" s="17" t="inlineStr">
         <is>
-          <t>BillingAccountStep, ZsbAddressStep</t>
+          <t>VerificationGate, useIdLookup</t>
         </is>
       </c>
       <c r="H49" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7894,12 +7982,12 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>useSubmit</t>
+          <t>useSearchListNav</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>hooks/useSubmit.ts</t>
+          <t>hooks/useSearchListNav.ts</t>
         </is>
       </c>
       <c r="D50" s="20" t="inlineStr">
@@ -7908,17 +7996,21 @@
         </is>
       </c>
       <c r="E50" s="17" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F50" s="17" t="inlineStr">
         <is>
-          <t>lead-management, mnp-fnp-porting, sim-number-management, trouble-ticketing-complaints, customer360, tasks</t>
-        </is>
-      </c>
-      <c r="G50" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, navigation, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G50" s="17" t="inlineStr">
+        <is>
+          <t>CompanySearchInput, ContactPhoneInput, PlanSearchBox, LocationInput</t>
+        </is>
+      </c>
       <c r="H50" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -7930,28 +8022,32 @@
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>useMinWidth</t>
+          <t>useAreaOptions</t>
         </is>
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>hooks/useMinWidth.ts</t>
-        </is>
-      </c>
-      <c r="D51" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>hooks/useAreaOptions.ts</t>
+        </is>
+      </c>
+      <c r="D51" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E51" s="17" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F51" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="G51" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G51" s="17" t="inlineStr">
+        <is>
+          <t>BillingAccountStep, ZsbAddressStep</t>
+        </is>
+      </c>
       <c r="H51" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
@@ -7961,17 +8057,17 @@
     <row r="52">
       <c r="A52" s="17" t="inlineStr">
         <is>
-          <t>Helper</t>
+          <t>Hook</t>
         </is>
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>statusTone</t>
+          <t>useSubmit</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>lib/statusTone.ts</t>
+          <t>hooks/useSubmit.ts</t>
         </is>
       </c>
       <c r="D52" s="20" t="inlineStr">
@@ -7980,61 +8076,53 @@
         </is>
       </c>
       <c r="E52" s="17" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="F52" s="17" t="inlineStr">
         <is>
-          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, orders, sales, support, tasks, tickets</t>
-        </is>
-      </c>
-      <c r="G52" s="17" t="inlineStr">
-        <is>
-          <t>ruleEngine</t>
-        </is>
-      </c>
+          <t>lead-management, mnp-fnp-porting, sim-number-management, trouble-ticketing-complaints, customer360, tasks</t>
+        </is>
+      </c>
+      <c r="G52" s="17" t="inlineStr"/>
       <c r="H52" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="17" t="inlineStr">
         <is>
-          <t>Helper</t>
+          <t>Hook</t>
         </is>
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>format</t>
+          <t>useMinWidth</t>
         </is>
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>lib/format.ts</t>
-        </is>
-      </c>
-      <c r="D53" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>hooks/useMinWidth.ts</t>
+        </is>
+      </c>
+      <c r="D53" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E53" s="17" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="F53" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, support, tasks</t>
-        </is>
-      </c>
-      <c r="G53" s="17" t="inlineStr">
-        <is>
-          <t>AdditionalDocumentsUpload, CafDocumentUpload, MsisdnPicker, SupportingDocumentUpload, GuidedContactStep, IdLookupStep, postpaidPlanModel, StepSummaryPanel, stepSummary, postpaidPricing</t>
-        </is>
-      </c>
+          <t>navigation</t>
+        </is>
+      </c>
+      <c r="G53" s="17" t="inlineStr"/>
       <c r="H53" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8046,12 +8134,12 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>buildEnv</t>
+          <t>statusTone</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>lib/buildEnv.ts</t>
+          <t>lib/statusTone.ts</t>
         </is>
       </c>
       <c r="D54" s="20" t="inlineStr">
@@ -8060,21 +8148,21 @@
         </is>
       </c>
       <c r="E54" s="17" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F54" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360</t>
+          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, orders, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G54" s="17" t="inlineStr">
         <is>
-          <t>syntheticMarker, navigationEngine</t>
+          <t>ruleEngine</t>
         </is>
       </c>
       <c r="H54" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8086,12 +8174,12 @@
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>deviceType</t>
+          <t>format</t>
         </is>
       </c>
       <c r="C55" s="17" t="inlineStr">
         <is>
-          <t>lib/deviceType.ts</t>
+          <t>lib/format.ts</t>
         </is>
       </c>
       <c r="D55" s="20" t="inlineStr">
@@ -8100,16 +8188,16 @@
         </is>
       </c>
       <c r="E55" s="17" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F55" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, tasks</t>
         </is>
       </c>
       <c r="G55" s="17" t="inlineStr">
         <is>
-          <t>SimSerialScanner, SimTypeStep, cafTypes</t>
+          <t>AdditionalDocumentsUpload, CafDocumentUpload, MsisdnPicker, GuidedContactStep, IdLookupStep, postpaidPlanModel, StepSummaryPanel, stepSummary, customer360Engine, postpaidPricing</t>
         </is>
       </c>
       <c r="H55" s="17" t="inlineStr">
@@ -8126,12 +8214,12 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>taskId</t>
+          <t>buildEnv</t>
         </is>
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t>lib/taskId.ts</t>
+          <t>lib/buildEnv.ts</t>
         </is>
       </c>
       <c r="D56" s="20" t="inlineStr">
@@ -8140,21 +8228,21 @@
         </is>
       </c>
       <c r="E56" s="17" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F56" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360</t>
         </is>
       </c>
       <c r="G56" s="17" t="inlineStr">
         <is>
-          <t>useWizardDraftActions</t>
+          <t>syntheticMarker, navigationEngine</t>
         </is>
       </c>
       <c r="H56" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -8166,12 +8254,12 @@
       </c>
       <c r="B57" s="17" t="inlineStr">
         <is>
-          <t>connectionType</t>
+          <t>deviceType</t>
         </is>
       </c>
       <c r="C57" s="17" t="inlineStr">
         <is>
-          <t>lib/connectionType.ts</t>
+          <t>lib/deviceType.ts</t>
         </is>
       </c>
       <c r="D57" s="20" t="inlineStr">
@@ -8180,21 +8268,21 @@
         </is>
       </c>
       <c r="E57" s="17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F57" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration, customer360</t>
         </is>
       </c>
       <c r="G57" s="17" t="inlineStr">
         <is>
-          <t>ConnectionTypeTag</t>
+          <t>IdFileUpload, PassportScanSections, SimSerialScanner, SimTypeStep, cafTypes</t>
         </is>
       </c>
       <c r="H57" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8206,12 +8294,12 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>serviceTypeTag</t>
+          <t>taskId</t>
         </is>
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t>lib/serviceTypeTag.ts</t>
+          <t>lib/taskId.ts</t>
         </is>
       </c>
       <c r="D58" s="20" t="inlineStr">
@@ -8220,21 +8308,21 @@
         </is>
       </c>
       <c r="E58" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F58" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G58" s="17" t="inlineStr">
         <is>
-          <t>ServiceTypeTag</t>
+          <t>useWizardDraftActions</t>
         </is>
       </c>
       <c r="H58" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8246,31 +8334,35 @@
       </c>
       <c r="B59" s="17" t="inlineStr">
         <is>
-          <t>screenName</t>
+          <t>connectionType</t>
         </is>
       </c>
       <c r="C59" s="17" t="inlineStr">
         <is>
-          <t>lib/screenName.ts</t>
-        </is>
-      </c>
-      <c r="D59" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>lib/connectionType.ts</t>
+        </is>
+      </c>
+      <c r="D59" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E59" s="17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F59" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="G59" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G59" s="17" t="inlineStr">
+        <is>
+          <t>ConnectionTypeTag</t>
+        </is>
+      </c>
       <c r="H59" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -8282,40 +8374,116 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
+          <t>serviceTypeTag</t>
+        </is>
+      </c>
+      <c r="C60" s="17" t="inlineStr">
+        <is>
+          <t>lib/serviceTypeTag.ts</t>
+        </is>
+      </c>
+      <c r="D60" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
+        </is>
+      </c>
+      <c r="E60" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="F60" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G60" s="17" t="inlineStr">
+        <is>
+          <t>ServiceTypeTag</t>
+        </is>
+      </c>
+      <c r="H60" s="17" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="17" t="inlineStr">
+        <is>
+          <t>Helper</t>
+        </is>
+      </c>
+      <c r="B61" s="17" t="inlineStr">
+        <is>
+          <t>screenName</t>
+        </is>
+      </c>
+      <c r="C61" s="17" t="inlineStr">
+        <is>
+          <t>lib/screenName.ts</t>
+        </is>
+      </c>
+      <c r="D61" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
+        </is>
+      </c>
+      <c r="E61" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" s="17" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
+      <c r="G61" s="17" t="inlineStr"/>
+      <c r="H61" s="17" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="17" t="inlineStr">
+        <is>
+          <t>Helper</t>
+        </is>
+      </c>
+      <c r="B62" s="17" t="inlineStr">
+        <is>
           <t>values</t>
         </is>
       </c>
-      <c r="C60" s="17" t="inlineStr">
+      <c r="C62" s="17" t="inlineStr">
         <is>
           <t>lib/values.ts</t>
         </is>
       </c>
-      <c r="D60" s="21" t="inlineStr">
+      <c r="D62" s="21" t="inlineStr">
         <is>
           <t>Single area</t>
         </is>
       </c>
-      <c r="E60" s="17" t="n">
+      <c r="E62" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F60" s="17" t="inlineStr">
+      <c r="F62" s="17" t="inlineStr">
         <is>
           <t>customer360</t>
         </is>
       </c>
-      <c r="G60" s="17" t="inlineStr">
+      <c r="G62" s="17" t="inlineStr">
         <is>
           <t>customer360Demo</t>
         </is>
       </c>
-      <c r="H60" s="17" t="inlineStr">
+      <c r="H62" s="17" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H60"/>
+  <autoFilter ref="A1:H62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
+++ b/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
@@ -887,11 +887,11 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>23 named - see the Capabilities sheet</t>
+          <t>24 named - see the Capabilities sheet</t>
         </is>
       </c>
       <c r="C15" s="17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D15" s="17" t="inlineStr"/>
       <c r="E15" s="17" t="inlineStr"/>
@@ -908,7 +908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.80" customWidth="1" min="1" max="1"/>
@@ -1491,15 +1491,45 @@
     <row r="19">
       <c r="A19" s="17" t="inlineStr">
         <is>
+          <t>Actual User</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>Who will use the line when it is not the customer who owns it: the agent adds an actual user, who is identified like the primary customer (ID type, scan or upload, MOI, email, phone). The actual user is named on the Supplementary Form, which the one CAF signature also signs; an existing customer's changed email is written back to their record.</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>capabilities/ActualUser/ActualUser.tsx
+capabilities/ActualUser/actualUserModel.ts
+capabilities/ActualUser/index.ts
+capabilities/ActualUser/step.tsx
+capabilities/ActualUser/submit.ts
+capabilities/ActualUser/summary.ts</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
           <t>Service Address</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>The address a service is activated at: one layout everywhere: Service Information (Kahramaa Meter ID / Vodafone Premise ID with Search), then Zone / Street / Building, then Additional Details, with Qatari-ID prefill.</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>capabilities/ServiceAddress/ServiceAddress.tsx
 capabilities/ServiceAddress/index.ts
@@ -1508,27 +1538,27 @@
 components/patterns/ZsbAddressStep.tsx</t>
         </is>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D20" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>Appointment Booking</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>Book the installation visit: SLA cluster, the date strip (next working days from the earliest, with each day's open slots), the day's time slots and technicians free, the customer's request for a specific date and time (a later date makes the order future-dated), appointment notes and the documents the technician collects (defaulted from the persona).</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>capabilities/AppointmentBooking/AppointmentBooking.tsx
 capabilities/AppointmentBooking/index.ts
@@ -1537,27 +1567,27 @@
 components/patterns/appointmentModel.ts</t>
         </is>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="D21" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, administration</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>Activity Comments</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>The closing note on the actions performed, with an optional channel.</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>capabilities/ActivityComments/ActivityComments.tsx
 capabilities/ActivityComments/index.ts
@@ -1565,27 +1595,27 @@
 components/patterns/ActivityCommentsStep.tsx</t>
         </is>
       </c>
-      <c r="D21" s="17" t="n">
+      <c r="D22" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>Line Selection</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>Choose which of the identified customer's existing mobile lines an order changes (Change Postpaid Plan, Change Prepaid Pack, Add Add-On): postpaid and / or prepaid lines with their current plan and price; a line that is not active, is barred or whose billing profile is in collections is shown with its reason and cannot be chosen.</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>capabilities/LineSelection/LineSelection.tsx
 capabilities/LineSelection/index.ts
@@ -1594,60 +1624,60 @@
 components/patterns/lineSelectionModel.ts</t>
         </is>
       </c>
-      <c r="D22" s="17" t="n">
+      <c r="D23" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>mobile-service-changes, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="17" t="inlineStr">
-        <is>
-          <t>Selectable card styling</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>One selected / idle / highlighted surface for plans, offers, numbers, add-ons, discounts and ID/customer type.</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>capabilities/SelectableCard/index.ts</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>administration</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>Side drawer</t>
+          <t>Selectable card styling</t>
         </is>
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>Fixed 50%-width drawer for forms, details and multi-step flows: the title as a small uppercase label beside the close control, the body on the page tint, and a footer whose buttons share its width equally.</t>
+          <t>One selected / idle / highlighted surface for plans, offers, numbers, add-ons, discounts and ID/customer type.</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>capabilities/SideDrawer/index.ts</t>
+          <t>capabilities/SelectableCard/index.ts</t>
         </is>
       </c>
       <c r="D24" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>administration</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>Side drawer</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>Fixed 50%-width drawer for forms, details and multi-step flows: the title as a small uppercase label beside the close control, the body on the page tint, and a footer whose buttons share its width equally.</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>capabilities/SideDrawer/index.ts</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
         <is>
           <t>administration</t>
         </is>
@@ -3115,7 +3145,7 @@
       </c>
       <c r="H37" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3185,7 @@
       </c>
       <c r="H38" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3225,7 @@
       </c>
       <c r="H39" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -3623,7 +3653,7 @@
       <c r="G50" s="17" t="inlineStr"/>
       <c r="H50" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3957,7 @@
       <c r="G58" s="17" t="inlineStr"/>
       <c r="H58" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -4315,7 +4345,7 @@
       <c r="G68" s="17" t="inlineStr"/>
       <c r="H68" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -6394,7 +6424,7 @@
       </c>
       <c r="H7" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -8202,7 +8232,7 @@
       </c>
       <c r="H55" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>

--- a/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
+++ b/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
@@ -1506,7 +1506,8 @@
 capabilities/ActualUser/index.ts
 capabilities/ActualUser/step.tsx
 capabilities/ActualUser/submit.ts
-capabilities/ActualUser/summary.ts</t>
+capabilities/ActualUser/summary.ts
+capabilities/ActualUser/useDemoReaderCustomer.ts</t>
         </is>
       </c>
       <c r="D19" s="17" t="n">
@@ -4037,7 +4038,7 @@
       </c>
       <c r="H60" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5930,7 @@
       <c r="G110" s="17" t="inlineStr"/>
       <c r="H110" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5970,7 @@
       </c>
       <c r="H111" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -6780,7 +6781,7 @@
       </c>
       <c r="H16" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>

--- a/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
+++ b/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
@@ -14,8 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Method" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'UI Components'!$A$1:$H$115</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Shared Code'!$A$1:$H$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'UI Components'!$A$1:$H$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Shared Code'!$A$1:$H$65</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="C7" s="17" t="n">
+        <v>54</v>
+      </c>
+      <c r="D7" s="17" t="n">
         <v>50</v>
-      </c>
-      <c r="D7" s="17" t="n">
-        <v>46</v>
       </c>
       <c r="E7" s="17" t="n">
         <v>4</v>
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="C9" s="17" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D9" s="17" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E9" s="17" t="n">
         <v>4</v>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="C11" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" s="17" t="n">
         <v>5</v>
-      </c>
-      <c r="D11" s="17" t="n">
-        <v>4</v>
       </c>
       <c r="E11" s="17" t="n">
         <v>1</v>
@@ -855,14 +855,14 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>114 UI components + 61 non-UI files</t>
+          <t>118 UI components + 64 non-UI files</t>
         </is>
       </c>
       <c r="C13" s="18" t="n">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="E13" s="18" t="n">
         <v>21</v>
@@ -1091,49 +1091,49 @@
     <row r="6">
       <c r="A6" s="17" t="inlineStr">
         <is>
-          <t>Eligibility gate</t>
+          <t>Customer Type &amp; Discounts</t>
         </is>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>Hard-stop / soft-stop / pass eligibility check shown after identification, with the outcome panel, checks report and footer actions.</t>
+          <t>Special customer types (retired, MADA, B2B2C): the evidence the agent collects, the rules for accepting or rejecting the benefit, and the customer's benefits.</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>capabilities/EligibilityGate/EligibilityGateStep.tsx
-capabilities/EligibilityGate/EligibilityOutcomes.tsx
-capabilities/EligibilityGate/eligibilityOutcomesModel.ts
-capabilities/EligibilityGate/index.ts</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>Customer Type &amp; Discounts</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>Special customer types (retired, MADA, B2B2C): the evidence the agent collects, the rules for accepting or rejecting the benefit, and the customer's benefits.</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>capabilities/CustomerType/CustomerTypeStep.tsx
 capabilities/CustomerType/customerTypeModel.ts
 capabilities/CustomerType/index.ts
 capabilities/CustomerType/useCustomerBenefits.ts
 components/domain/CompanySearchInput.tsx</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, administration, customer360</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>Eligibility gate</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>Hard-stop / soft-stop / pass eligibility check shown after identification, with the outcome panel, checks report and footer actions.</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>capabilities/EligibilityGate/EligibilityGateStep.tsx
+capabilities/EligibilityGate/EligibilityOutcomes.tsx
+capabilities/EligibilityGate/eligibilityOutcomesModel.ts
+capabilities/EligibilityGate/index.ts</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
@@ -1695,7 +1695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H115"/>
+  <dimension ref="A1:H119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.85" customWidth="1" min="1" max="1"/>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="G2" s="17" t="inlineStr">
         <is>
-          <t>CreditCheckPanel, MsisdnPicker, SimTypeStep, ActivationCompleteScreen, AppointmentBookingStep, BillingAccountStep, BulkOperationPortal, CafSignatureCapture, DonorAttachmentStep, IdLookupStep, PrepaidCartStep, PrepaidCheckoutStep, SimSwapFormStep, TicketCreationModal, WinCashPaymentStep, ConnectionTypeTag, Tooltip</t>
+          <t>CreditCheckPanel, MsisdnPicker, SimTypeStep, ActivationCompleteScreen, AppointmentBookingStep, BillingAccountStep, BulkOperationPortal, CafSignatureCapture, DonorAttachmentStep, IdLookupStep, IdReconciliationPanel, PrepaidCartStep, PrepaidCheckoutStep, SimSwapFormStep, TicketCreationModal, WinCashPaymentStep, ConnectionTypeTag, Tooltip</t>
         </is>
       </c>
       <c r="H2" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="G3" s="17" t="inlineStr">
         <is>
-          <t>AdditionalDocumentsUpload, CafDocumentUpload, CompanySearchInput, ContactPhoneInput, EligibilityRows, FibreReadinessBanner, IdFileUpload, MsisdnPicker, PassportScanSections, QidImageUpload, QidInput, ScanFailureNotice, SimSerialScanner, AppointmentBookingStep, BillingAccountStep, CafSignatureCapture, DiscountCard, FixedPlanStep, OrderConfirmationScreen, PostpaidPlanAddonsStep, PostpaidPlanCard, PrepaidPlanCard, PrepaidPlanStep, ValidationStatus, ZsbAddressStep, CustomerViewButton, StepSummarySection, WizardFooter, ChoiceCards, DataTable, IconButton, LocationInput, Pager, PhoneNumberInput, SearchField, Select, Tabs</t>
+          <t>AdditionalDocumentsUpload, CafDocumentUpload, CompanySearchInput, ContactPhoneInput, EligibilityRows, FibreReadinessBanner, IdFileUpload, MsisdnPicker, PassportScanSections, QidImageUpload, QidInput, ScanFailureNotice, SimSerialScanner, AppointmentBookingStep, BillingAccountStep, CafSignatureCapture, DiscountCard, FixedPlanStep, OrderConfirmationScreen, PostpaidPlanAddonsStep, PostpaidPlanCard, PrepaidPlanCard, PrepaidPlanStep, RestrictedCustomerNotice, RestrictedRowsNotice, ValidationStatus, ZsbAddressStep, CustomerViewButton, StepSummarySection, WizardFooter, ChoiceCards, DataTable, IconButton, LocationInput, Pager, PhoneNumberInput, SearchField, Select, Tabs</t>
         </is>
       </c>
       <c r="H3" s="17" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="G5" s="17" t="inlineStr">
         <is>
-          <t>AdditionalDocumentsUpload, CafDocumentUpload, MsisdnPicker, BillingAccountStep, BillingProfileSetupDrawer, BulkOperationPortal, DonorDetailsStep, GuidedContactStep, NewCustomerForm, TicketCreationModal, ZsbAddressStep</t>
+          <t>AdditionalDocumentsUpload, CafDocumentUpload, MsisdnPicker, BillingAccountStep, BillingProfileSetupDrawer, BulkOperationPortal, CreditLimitCard, DonorDetailsStep, GuidedContactStep, NewCustomerForm, TicketCreationModal, ZsbAddressStep</t>
         </is>
       </c>
       <c r="H5" s="17" t="inlineStr">
@@ -1972,11 +1972,11 @@
         </is>
       </c>
       <c r="E7" s="17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, support</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, support</t>
         </is>
       </c>
       <c r="G7" s="17" t="inlineStr">
@@ -3332,11 +3332,11 @@
         </is>
       </c>
       <c r="E42" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F42" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, administration, customer360</t>
         </is>
       </c>
       <c r="G42" s="17" t="inlineStr"/>
@@ -3934,12 +3934,12 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>GuidedContactStep</t>
+          <t>RestrictedCustomerNotice</t>
         </is>
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/GuidedContactStep.tsx</t>
+          <t>components/patterns/RestrictedCustomerNotice.tsx</t>
         </is>
       </c>
       <c r="D58" s="20" t="inlineStr">
@@ -3948,17 +3948,21 @@
         </is>
       </c>
       <c r="E58" s="17" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F58" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
-        </is>
-      </c>
-      <c r="G58" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer-search, customer360, support</t>
+        </is>
+      </c>
+      <c r="G58" s="17" t="inlineStr">
+        <is>
+          <t>IdLookupStep, TicketCreationModal</t>
+        </is>
+      </c>
       <c r="H58" s="17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>uncommitted</t>
         </is>
       </c>
     </row>
@@ -3970,12 +3974,12 @@
       </c>
       <c r="B59" s="17" t="inlineStr">
         <is>
-          <t>IdLookupStatus</t>
+          <t>GuidedContactStep</t>
         </is>
       </c>
       <c r="C59" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/IdLookupStatus.tsx</t>
+          <t>components/patterns/GuidedContactStep.tsx</t>
         </is>
       </c>
       <c r="D59" s="20" t="inlineStr">
@@ -3991,14 +3995,10 @@
           <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
-      <c r="G59" s="17" t="inlineStr">
-        <is>
-          <t>IdLookupStep</t>
-        </is>
-      </c>
+      <c r="G59" s="17" t="inlineStr"/>
       <c r="H59" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -4010,12 +4010,12 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>IdLookupStep</t>
+          <t>IdLookupStatus</t>
         </is>
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/IdLookupStep.tsx</t>
+          <t>components/patterns/IdLookupStatus.tsx</t>
         </is>
       </c>
       <c r="D60" s="20" t="inlineStr">
@@ -4033,12 +4033,12 @@
       </c>
       <c r="G60" s="17" t="inlineStr">
         <is>
-          <t>GuidedContactStep</t>
+          <t>IdLookupStep</t>
         </is>
       </c>
       <c r="H60" s="17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="B61" s="17" t="inlineStr">
         <is>
-          <t>IdScannerPanel</t>
+          <t>IdLookupStep</t>
         </is>
       </c>
       <c r="C61" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/IdScannerPanel.tsx</t>
+          <t>components/patterns/IdLookupStep.tsx</t>
         </is>
       </c>
       <c r="D61" s="20" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="G61" s="17" t="inlineStr">
         <is>
-          <t>IdLookupStep</t>
+          <t>GuidedContactStep</t>
         </is>
       </c>
       <c r="H61" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -4090,12 +4090,12 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>MoiResultPanel</t>
+          <t>IdReconciliationPanel</t>
         </is>
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/MoiResultPanel.tsx</t>
+          <t>components/patterns/IdReconciliationPanel.tsx</t>
         </is>
       </c>
       <c r="D62" s="20" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="H62" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>uncommitted</t>
         </is>
       </c>
     </row>
@@ -4130,12 +4130,12 @@
       </c>
       <c r="B63" s="17" t="inlineStr">
         <is>
-          <t>NewCustomerForm</t>
+          <t>IdScannerPanel</t>
         </is>
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/NewCustomerForm.tsx</t>
+          <t>components/patterns/IdScannerPanel.tsx</t>
         </is>
       </c>
       <c r="D63" s="20" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>ValidationStatus</t>
+          <t>MoiResultPanel</t>
         </is>
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/ValidationStatus.tsx</t>
+          <t>components/patterns/MoiResultPanel.tsx</t>
         </is>
       </c>
       <c r="D64" s="20" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="G64" s="17" t="inlineStr">
         <is>
-          <t>IdLookupStatus</t>
+          <t>IdLookupStep</t>
         </is>
       </c>
       <c r="H64" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4210,12 +4210,12 @@
       </c>
       <c r="B65" s="17" t="inlineStr">
         <is>
-          <t>SignatureCapture</t>
+          <t>NewCustomerForm</t>
         </is>
       </c>
       <c r="C65" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/SignatureCapture.tsx</t>
+          <t>components/patterns/NewCustomerForm.tsx</t>
         </is>
       </c>
       <c r="D65" s="20" t="inlineStr">
@@ -4224,21 +4224,21 @@
         </is>
       </c>
       <c r="E65" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F65" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G65" s="17" t="inlineStr">
         <is>
-          <t>CafSignatureCapture, DonorAttachmentStep, SimSwapFormStep</t>
+          <t>IdLookupStep</t>
         </is>
       </c>
       <c r="H65" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -4250,12 +4250,12 @@
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen</t>
+          <t>ValidationStatus</t>
         </is>
       </c>
       <c r="C66" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/ActivationCompleteScreen.tsx</t>
+          <t>components/patterns/ValidationStatus.tsx</t>
         </is>
       </c>
       <c r="D66" s="20" t="inlineStr">
@@ -4264,17 +4264,21 @@
         </is>
       </c>
       <c r="E66" s="17" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F66" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G66" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G66" s="17" t="inlineStr">
+        <is>
+          <t>IdLookupStatus</t>
+        </is>
+      </c>
       <c r="H66" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -4286,12 +4290,12 @@
       </c>
       <c r="B67" s="17" t="inlineStr">
         <is>
-          <t>BillingAccountAutoResolver</t>
+          <t>SignatureCapture</t>
         </is>
       </c>
       <c r="C67" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/BillingAccountAutoResolver.tsx</t>
+          <t>components/patterns/SignatureCapture.tsx</t>
         </is>
       </c>
       <c r="D67" s="20" t="inlineStr">
@@ -4300,17 +4304,21 @@
         </is>
       </c>
       <c r="E67" s="17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F67" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G67" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+      <c r="G67" s="17" t="inlineStr">
+        <is>
+          <t>CafSignatureCapture, DonorAttachmentStep, SimSwapFormStep</t>
+        </is>
+      </c>
       <c r="H67" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4322,12 +4330,12 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>CafSignatureCapture</t>
+          <t>ActivationCompleteScreen</t>
         </is>
       </c>
       <c r="C68" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CafSignatureCapture.tsx</t>
+          <t>components/patterns/ActivationCompleteScreen.tsx</t>
         </is>
       </c>
       <c r="D68" s="20" t="inlineStr">
@@ -4346,7 +4354,7 @@
       <c r="G68" s="17" t="inlineStr"/>
       <c r="H68" s="17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -4358,12 +4366,12 @@
       </c>
       <c r="B69" s="17" t="inlineStr">
         <is>
-          <t>CheckoutDefaultLayout</t>
+          <t>BillingAccountAutoResolver</t>
         </is>
       </c>
       <c r="C69" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CheckoutDefaultLayout.tsx</t>
+          <t>components/patterns/BillingAccountAutoResolver.tsx</t>
         </is>
       </c>
       <c r="D69" s="20" t="inlineStr">
@@ -4379,14 +4387,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G69" s="17" t="inlineStr">
-        <is>
-          <t>CheckoutSummaryStep</t>
-        </is>
-      </c>
+      <c r="G69" s="17" t="inlineStr"/>
       <c r="H69" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4402,12 @@
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>CheckoutSummaryStep</t>
+          <t>CafSignatureCapture</t>
         </is>
       </c>
       <c r="C70" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CheckoutSummaryStep.tsx</t>
+          <t>components/patterns/CafSignatureCapture.tsx</t>
         </is>
       </c>
       <c r="D70" s="20" t="inlineStr">
@@ -4422,7 +4426,7 @@
       <c r="G70" s="17" t="inlineStr"/>
       <c r="H70" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -4434,12 +4438,12 @@
       </c>
       <c r="B71" s="17" t="inlineStr">
         <is>
-          <t>DiscountCard</t>
+          <t>CheckoutDefaultLayout</t>
         </is>
       </c>
       <c r="C71" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DiscountCard.tsx</t>
+          <t>components/patterns/CheckoutDefaultLayout.tsx</t>
         </is>
       </c>
       <c r="D71" s="20" t="inlineStr">
@@ -4457,12 +4461,12 @@
       </c>
       <c r="G71" s="17" t="inlineStr">
         <is>
-          <t>PostpaidDiscountsPanel</t>
+          <t>CheckoutSummaryStep</t>
         </is>
       </c>
       <c r="H71" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4474,12 +4478,12 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>FixedPlanStep</t>
+          <t>CheckoutSummaryStep</t>
         </is>
       </c>
       <c r="C72" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/FixedPlanStep.tsx</t>
+          <t>components/patterns/CheckoutSummaryStep.tsx</t>
         </is>
       </c>
       <c r="D72" s="20" t="inlineStr">
@@ -4498,7 +4502,7 @@
       <c r="G72" s="17" t="inlineStr"/>
       <c r="H72" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4514,12 @@
       </c>
       <c r="B73" s="17" t="inlineStr">
         <is>
-          <t>FullTerms</t>
+          <t>DiscountCard</t>
         </is>
       </c>
       <c r="C73" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CafTerms.tsx</t>
+          <t>components/patterns/DiscountCard.tsx</t>
         </is>
       </c>
       <c r="D73" s="20" t="inlineStr">
@@ -4533,7 +4537,7 @@
       </c>
       <c r="G73" s="17" t="inlineStr">
         <is>
-          <t>CafSignatureCapture</t>
+          <t>PostpaidDiscountsPanel</t>
         </is>
       </c>
       <c r="H73" s="17" t="inlineStr">
@@ -4550,12 +4554,12 @@
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>KeyInformationPanel</t>
+          <t>FixedPlanStep</t>
         </is>
       </c>
       <c r="C74" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/KeyInformationPanel.tsx</t>
+          <t>components/patterns/FixedPlanStep.tsx</t>
         </is>
       </c>
       <c r="D74" s="20" t="inlineStr">
@@ -4574,7 +4578,7 @@
       <c r="G74" s="17" t="inlineStr"/>
       <c r="H74" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4586,12 +4590,12 @@
       </c>
       <c r="B75" s="17" t="inlineStr">
         <is>
-          <t>OrderConfirmationScreen</t>
+          <t>FullTerms</t>
         </is>
       </c>
       <c r="C75" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/OrderConfirmationScreen.tsx</t>
+          <t>components/patterns/CafTerms.tsx</t>
         </is>
       </c>
       <c r="D75" s="20" t="inlineStr">
@@ -4609,12 +4613,12 @@
       </c>
       <c r="G75" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen</t>
+          <t>CafSignatureCapture</t>
         </is>
       </c>
       <c r="H75" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4626,12 +4630,12 @@
       </c>
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>PlanDetailsDrawer</t>
+          <t>KeyInformationPanel</t>
         </is>
       </c>
       <c r="C76" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PlanDetailsDrawer.tsx</t>
+          <t>components/patterns/KeyInformationPanel.tsx</t>
         </is>
       </c>
       <c r="D76" s="20" t="inlineStr">
@@ -4647,11 +4651,7 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G76" s="17" t="inlineStr">
-        <is>
-          <t>PostpaidPlanAddonsStep</t>
-        </is>
-      </c>
+      <c r="G76" s="17" t="inlineStr"/>
       <c r="H76" s="17" t="inlineStr">
         <is>
           <t>2026-10-15</t>
@@ -4666,12 +4666,12 @@
       </c>
       <c r="B77" s="17" t="inlineStr">
         <is>
-          <t>PlanGroupPanel</t>
+          <t>OrderConfirmationScreen</t>
         </is>
       </c>
       <c r="C77" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PlanGroupPanel.tsx</t>
+          <t>components/patterns/OrderConfirmationScreen.tsx</t>
         </is>
       </c>
       <c r="D77" s="20" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="G77" s="17" t="inlineStr">
         <is>
-          <t>PostpaidPlanAddonsStep</t>
+          <t>ActivationCompleteScreen</t>
         </is>
       </c>
       <c r="H77" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4706,12 +4706,12 @@
       </c>
       <c r="B78" s="17" t="inlineStr">
         <is>
-          <t>PlanSearchBox</t>
+          <t>PlanDetailsDrawer</t>
         </is>
       </c>
       <c r="C78" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PlanSearchBox.tsx</t>
+          <t>components/patterns/PlanDetailsDrawer.tsx</t>
         </is>
       </c>
       <c r="D78" s="20" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="B79" s="17" t="inlineStr">
         <is>
-          <t>PlanTabStrip</t>
+          <t>PlanGroupPanel</t>
         </is>
       </c>
       <c r="C79" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PlanTabStrip.tsx</t>
+          <t>components/patterns/PlanGroupPanel.tsx</t>
         </is>
       </c>
       <c r="D79" s="20" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="H79" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4786,12 +4786,12 @@
       </c>
       <c r="B80" s="17" t="inlineStr">
         <is>
-          <t>PostpaidAddonsPanel</t>
+          <t>PlanSearchBox</t>
         </is>
       </c>
       <c r="C80" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidAddonsPanel.tsx</t>
+          <t>components/patterns/PlanSearchBox.tsx</t>
         </is>
       </c>
       <c r="D80" s="20" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="H80" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="B81" s="17" t="inlineStr">
         <is>
-          <t>PostpaidDiscountsPanel</t>
+          <t>PlanTabStrip</t>
         </is>
       </c>
       <c r="C81" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidDiscountsPanel.tsx</t>
+          <t>components/patterns/PlanTabStrip.tsx</t>
         </is>
       </c>
       <c r="D81" s="20" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="H81" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4866,12 +4866,12 @@
       </c>
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>PostpaidMonthlySummary</t>
+          <t>PostpaidAddonsPanel</t>
         </is>
       </c>
       <c r="C82" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidMonthlySummary.tsx</t>
+          <t>components/patterns/PostpaidAddonsPanel.tsx</t>
         </is>
       </c>
       <c r="D82" s="20" t="inlineStr">
@@ -4906,12 +4906,12 @@
       </c>
       <c r="B83" s="17" t="inlineStr">
         <is>
-          <t>PostpaidPlanAddonsStep</t>
+          <t>PostpaidDiscountsPanel</t>
         </is>
       </c>
       <c r="C83" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidPlanAddonsStep.tsx</t>
+          <t>components/patterns/PostpaidDiscountsPanel.tsx</t>
         </is>
       </c>
       <c r="D83" s="20" t="inlineStr">
@@ -4927,10 +4927,14 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G83" s="17" t="inlineStr"/>
+      <c r="G83" s="17" t="inlineStr">
+        <is>
+          <t>PostpaidPlanAddonsStep</t>
+        </is>
+      </c>
       <c r="H83" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4942,12 +4946,12 @@
       </c>
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>PostpaidPlanCard</t>
+          <t>PostpaidMonthlySummary</t>
         </is>
       </c>
       <c r="C84" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidPlanCard.tsx</t>
+          <t>components/patterns/PostpaidMonthlySummary.tsx</t>
         </is>
       </c>
       <c r="D84" s="20" t="inlineStr">
@@ -4965,7 +4969,7 @@
       </c>
       <c r="G84" s="17" t="inlineStr">
         <is>
-          <t>PlanGroupPanel</t>
+          <t>PostpaidPlanAddonsStep</t>
         </is>
       </c>
       <c r="H84" s="17" t="inlineStr">
@@ -4982,12 +4986,12 @@
       </c>
       <c r="B85" s="17" t="inlineStr">
         <is>
-          <t>PrepaidCartStep</t>
+          <t>PostpaidPlanAddonsStep</t>
         </is>
       </c>
       <c r="C85" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidCartStep.tsx</t>
+          <t>components/patterns/PostpaidPlanAddonsStep.tsx</t>
         </is>
       </c>
       <c r="D85" s="20" t="inlineStr">
@@ -5006,7 +5010,7 @@
       <c r="G85" s="17" t="inlineStr"/>
       <c r="H85" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -5018,12 +5022,12 @@
       </c>
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>PrepaidCheckoutStep</t>
+          <t>PostpaidPlanCard</t>
         </is>
       </c>
       <c r="C86" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidCheckoutStep.tsx</t>
+          <t>components/patterns/PostpaidPlanCard.tsx</t>
         </is>
       </c>
       <c r="D86" s="20" t="inlineStr">
@@ -5039,7 +5043,11 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G86" s="17" t="inlineStr"/>
+      <c r="G86" s="17" t="inlineStr">
+        <is>
+          <t>PlanGroupPanel</t>
+        </is>
+      </c>
       <c r="H86" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
@@ -5054,12 +5062,12 @@
       </c>
       <c r="B87" s="17" t="inlineStr">
         <is>
-          <t>PrepaidPackDetailsDrawer</t>
+          <t>PrepaidCartStep</t>
         </is>
       </c>
       <c r="C87" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidPackDetailsDrawer.tsx</t>
+          <t>components/patterns/PrepaidCartStep.tsx</t>
         </is>
       </c>
       <c r="D87" s="20" t="inlineStr">
@@ -5075,14 +5083,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G87" s="17" t="inlineStr">
-        <is>
-          <t>PrepaidPlanStep</t>
-        </is>
-      </c>
+      <c r="G87" s="17" t="inlineStr"/>
       <c r="H87" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5094,12 +5098,12 @@
       </c>
       <c r="B88" s="17" t="inlineStr">
         <is>
-          <t>PrepaidPlanCard</t>
+          <t>PrepaidCheckoutStep</t>
         </is>
       </c>
       <c r="C88" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidPlanCard.tsx</t>
+          <t>components/patterns/PrepaidCheckoutStep.tsx</t>
         </is>
       </c>
       <c r="D88" s="20" t="inlineStr">
@@ -5115,11 +5119,7 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G88" s="17" t="inlineStr">
-        <is>
-          <t>PrepaidPlanStep</t>
-        </is>
-      </c>
+      <c r="G88" s="17" t="inlineStr"/>
       <c r="H88" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
@@ -5134,12 +5134,12 @@
       </c>
       <c r="B89" s="17" t="inlineStr">
         <is>
-          <t>PrepaidPlanStep</t>
+          <t>PrepaidPackDetailsDrawer</t>
         </is>
       </c>
       <c r="C89" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidPlanStep.tsx</t>
+          <t>components/patterns/PrepaidPackDetailsDrawer.tsx</t>
         </is>
       </c>
       <c r="D89" s="20" t="inlineStr">
@@ -5155,10 +5155,14 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G89" s="17" t="inlineStr"/>
+      <c r="G89" s="17" t="inlineStr">
+        <is>
+          <t>PrepaidPlanStep</t>
+        </is>
+      </c>
       <c r="H89" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5174,12 @@
       </c>
       <c r="B90" s="17" t="inlineStr">
         <is>
-          <t>SummaryTables</t>
+          <t>PrepaidPlanCard</t>
         </is>
       </c>
       <c r="C90" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CheckoutSummaryTables.tsx</t>
+          <t>components/patterns/PrepaidPlanCard.tsx</t>
         </is>
       </c>
       <c r="D90" s="20" t="inlineStr">
@@ -5193,12 +5197,12 @@
       </c>
       <c r="G90" s="17" t="inlineStr">
         <is>
-          <t>CheckoutSummaryStep, checkoutDetailedTables</t>
+          <t>PrepaidPlanStep</t>
         </is>
       </c>
       <c r="H90" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5210,12 +5214,12 @@
       </c>
       <c r="B91" s="17" t="inlineStr">
         <is>
-          <t>WinCashPaymentStep</t>
+          <t>PrepaidPlanStep</t>
         </is>
       </c>
       <c r="C91" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/WinCashPaymentStep.tsx</t>
+          <t>components/patterns/PrepaidPlanStep.tsx</t>
         </is>
       </c>
       <c r="D91" s="20" t="inlineStr">
@@ -5234,7 +5238,7 @@
       <c r="G91" s="17" t="inlineStr"/>
       <c r="H91" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5246,12 +5250,12 @@
       </c>
       <c r="B92" s="17" t="inlineStr">
         <is>
-          <t>BillingAccountStep</t>
+          <t>SummaryTables</t>
         </is>
       </c>
       <c r="C92" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/BillingAccountStep.tsx</t>
+          <t>components/patterns/CheckoutSummaryTables.tsx</t>
         </is>
       </c>
       <c r="D92" s="20" t="inlineStr">
@@ -5260,17 +5264,21 @@
         </is>
       </c>
       <c r="E92" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F92" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G92" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G92" s="17" t="inlineStr">
+        <is>
+          <t>CheckoutSummaryStep, checkoutDetailedTables</t>
+        </is>
+      </c>
       <c r="H92" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5290,12 @@
       </c>
       <c r="B93" s="17" t="inlineStr">
         <is>
-          <t>BillingProfileSetupDrawer</t>
+          <t>WinCashPaymentStep</t>
         </is>
       </c>
       <c r="C93" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/BillingProfileSetupDrawer.tsx</t>
+          <t>components/patterns/WinCashPaymentStep.tsx</t>
         </is>
       </c>
       <c r="D93" s="20" t="inlineStr">
@@ -5296,18 +5304,14 @@
         </is>
       </c>
       <c r="E93" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F93" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G93" s="17" t="inlineStr">
-        <is>
-          <t>BillingAccountStep</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G93" s="17" t="inlineStr"/>
       <c r="H93" s="17" t="inlineStr">
         <is>
           <t>2026-10-15</t>
@@ -5322,12 +5326,12 @@
       </c>
       <c r="B94" s="17" t="inlineStr">
         <is>
-          <t>ZsbAddressStep</t>
+          <t>BillingAccountStep</t>
         </is>
       </c>
       <c r="C94" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/ZsbAddressStep.tsx</t>
+          <t>components/patterns/BillingAccountStep.tsx</t>
         </is>
       </c>
       <c r="D94" s="20" t="inlineStr">
@@ -5346,7 +5350,7 @@
       <c r="G94" s="17" t="inlineStr"/>
       <c r="H94" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -5358,12 +5362,12 @@
       </c>
       <c r="B95" s="17" t="inlineStr">
         <is>
-          <t>AppointmentBookingStep</t>
+          <t>BillingProfileSetupDrawer</t>
         </is>
       </c>
       <c r="C95" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/AppointmentBookingStep.tsx</t>
+          <t>components/patterns/BillingProfileSetupDrawer.tsx</t>
         </is>
       </c>
       <c r="D95" s="20" t="inlineStr">
@@ -5372,17 +5376,21 @@
         </is>
       </c>
       <c r="E95" s="17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F95" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, administration</t>
-        </is>
-      </c>
-      <c r="G95" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G95" s="17" t="inlineStr">
+        <is>
+          <t>BillingAccountStep</t>
+        </is>
+      </c>
       <c r="H95" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5402,12 @@
       </c>
       <c r="B96" s="17" t="inlineStr">
         <is>
-          <t>DemoFaultPanel</t>
+          <t>CreditLimitCard</t>
         </is>
       </c>
       <c r="C96" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DemoFaultPanel.tsx</t>
+          <t>components/patterns/CreditLimitCard.tsx</t>
         </is>
       </c>
       <c r="D96" s="20" t="inlineStr">
@@ -5408,17 +5416,17 @@
         </is>
       </c>
       <c r="E96" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F96" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G96" s="17" t="inlineStr"/>
       <c r="H96" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>uncommitted</t>
         </is>
       </c>
     </row>
@@ -5430,12 +5438,12 @@
       </c>
       <c r="B97" s="17" t="inlineStr">
         <is>
-          <t>DonorAttachmentStep</t>
+          <t>ZsbAddressStep</t>
         </is>
       </c>
       <c r="C97" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DonorAttachmentStep.tsx</t>
+          <t>components/patterns/ZsbAddressStep.tsx</t>
         </is>
       </c>
       <c r="D97" s="20" t="inlineStr">
@@ -5444,17 +5452,17 @@
         </is>
       </c>
       <c r="E97" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F97" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G97" s="17" t="inlineStr"/>
       <c r="H97" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5466,12 +5474,12 @@
       </c>
       <c r="B98" s="17" t="inlineStr">
         <is>
-          <t>DonorDetailsStep</t>
+          <t>AppointmentBookingStep</t>
         </is>
       </c>
       <c r="C98" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DonorDetailsStep.tsx</t>
+          <t>components/patterns/AppointmentBookingStep.tsx</t>
         </is>
       </c>
       <c r="D98" s="20" t="inlineStr">
@@ -5480,21 +5488,17 @@
         </is>
       </c>
       <c r="E98" s="17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F98" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
-        </is>
-      </c>
-      <c r="G98" s="17" t="inlineStr">
-        <is>
-          <t>DonorAttachmentStep</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, administration</t>
+        </is>
+      </c>
+      <c r="G98" s="17" t="inlineStr"/>
       <c r="H98" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5510,12 @@
       </c>
       <c r="B99" s="17" t="inlineStr">
         <is>
-          <t>EntityMissing</t>
+          <t>DemoFaultPanel</t>
         </is>
       </c>
       <c r="C99" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/EntityMissing.tsx</t>
+          <t>components/patterns/DemoFaultPanel.tsx</t>
         </is>
       </c>
       <c r="D99" s="20" t="inlineStr">
@@ -5524,7 +5528,7 @@
       </c>
       <c r="F99" s="17" t="inlineStr">
         <is>
-          <t>lead-management, order-management, sim-number-management, trouble-ticketing-complaints, customer360, tasks</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
         </is>
       </c>
       <c r="G99" s="17" t="inlineStr"/>
@@ -5542,12 +5546,12 @@
       </c>
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>ActivityCommentsStep</t>
+          <t>DonorAttachmentStep</t>
         </is>
       </c>
       <c r="C100" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/ActivityCommentsStep.tsx</t>
+          <t>components/patterns/DonorAttachmentStep.tsx</t>
         </is>
       </c>
       <c r="D100" s="20" t="inlineStr">
@@ -5556,17 +5560,17 @@
         </is>
       </c>
       <c r="E100" s="17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F100" s="17" t="inlineStr">
         <is>
-          <t>pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
         </is>
       </c>
       <c r="G100" s="17" t="inlineStr"/>
       <c r="H100" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5578,12 +5582,12 @@
       </c>
       <c r="B101" s="17" t="inlineStr">
         <is>
-          <t>LineSelectionStep</t>
+          <t>DonorDetailsStep</t>
         </is>
       </c>
       <c r="C101" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/LineSelectionStep.tsx</t>
+          <t>components/patterns/DonorDetailsStep.tsx</t>
         </is>
       </c>
       <c r="D101" s="20" t="inlineStr">
@@ -5592,14 +5596,18 @@
         </is>
       </c>
       <c r="E101" s="17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F101" s="17" t="inlineStr">
         <is>
-          <t>mobile-service-changes, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G101" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
+        </is>
+      </c>
+      <c r="G101" s="17" t="inlineStr">
+        <is>
+          <t>DonorAttachmentStep</t>
+        </is>
+      </c>
       <c r="H101" s="17" t="inlineStr">
         <is>
           <t>2026-10-19</t>
@@ -5614,12 +5622,12 @@
       </c>
       <c r="B102" s="17" t="inlineStr">
         <is>
-          <t>TicketCreationModal</t>
+          <t>EntityMissing</t>
         </is>
       </c>
       <c r="C102" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/TicketCreationModal.tsx</t>
+          <t>components/patterns/EntityMissing.tsx</t>
         </is>
       </c>
       <c r="D102" s="20" t="inlineStr">
@@ -5628,11 +5636,11 @@
         </is>
       </c>
       <c r="E102" s="17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F102" s="17" t="inlineStr">
         <is>
-          <t>trouble-ticketing-complaints, customer360, support</t>
+          <t>lead-management, order-management, sim-number-management, trouble-ticketing-complaints, customer360, tasks</t>
         </is>
       </c>
       <c r="G102" s="17" t="inlineStr"/>
@@ -5650,31 +5658,31 @@
       </c>
       <c r="B103" s="17" t="inlineStr">
         <is>
-          <t>BulkOperationPortal</t>
+          <t>RestrictedRowsNotice</t>
         </is>
       </c>
       <c r="C103" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/BulkOperationPortal.tsx</t>
-        </is>
-      </c>
-      <c r="D103" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>components/patterns/RestrictedRowsNotice.tsx</t>
+        </is>
+      </c>
+      <c r="D103" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E103" s="17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F103" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b</t>
+          <t>order-management, trouble-ticketing-complaints, orders, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G103" s="17" t="inlineStr"/>
       <c r="H103" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>uncommitted</t>
         </is>
       </c>
     </row>
@@ -5686,31 +5694,31 @@
       </c>
       <c r="B104" s="17" t="inlineStr">
         <is>
-          <t>DualPlaySerialCheckStep</t>
+          <t>ActivityCommentsStep</t>
         </is>
       </c>
       <c r="C104" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DualPlaySerialCheckStep.tsx</t>
-        </is>
-      </c>
-      <c r="D104" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>components/patterns/ActivityCommentsStep.tsx</t>
+        </is>
+      </c>
+      <c r="D104" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E104" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F104" s="17" t="inlineStr">
         <is>
-          <t>fwa-5g-home</t>
+          <t>pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G104" s="17" t="inlineStr"/>
       <c r="H104" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -5722,31 +5730,31 @@
       </c>
       <c r="B105" s="17" t="inlineStr">
         <is>
-          <t>SimSwapFormStep</t>
+          <t>LineSelectionStep</t>
         </is>
       </c>
       <c r="C105" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/SimSwapFormStep.tsx</t>
-        </is>
-      </c>
-      <c r="D105" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>components/patterns/LineSelectionStep.tsx</t>
+        </is>
+      </c>
+      <c r="D105" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E105" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F105" s="17" t="inlineStr">
         <is>
-          <t>sim-number-management</t>
+          <t>mobile-service-changes, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G105" s="17" t="inlineStr"/>
       <c r="H105" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5758,97 +5766,97 @@
       </c>
       <c r="B106" s="17" t="inlineStr">
         <is>
-          <t>VerificationGate</t>
+          <t>TicketCreationModal</t>
         </is>
       </c>
       <c r="C106" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/VerificationGate.tsx</t>
-        </is>
-      </c>
-      <c r="D106" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>components/patterns/TicketCreationModal.tsx</t>
+        </is>
+      </c>
+      <c r="D106" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E106" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F106" s="17" t="inlineStr">
         <is>
-          <t>customer360</t>
+          <t>trouble-ticketing-complaints, customer360, support</t>
         </is>
       </c>
       <c r="G106" s="17" t="inlineStr"/>
       <c r="H106" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="17" t="inlineStr">
         <is>
-          <t>Wizard</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="B107" s="17" t="inlineStr">
         <is>
-          <t>AbandonDialog</t>
+          <t>BulkOperationPortal</t>
         </is>
       </c>
       <c r="C107" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/WizardDialogs.tsx</t>
-        </is>
-      </c>
-      <c r="D107" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>components/patterns/BulkOperationPortal.tsx</t>
+        </is>
+      </c>
+      <c r="D107" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E107" s="17" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F107" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>enterprise-iot-b2b</t>
         </is>
       </c>
       <c r="G107" s="17" t="inlineStr"/>
       <c r="H107" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="17" t="inlineStr">
         <is>
-          <t>Wizard</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="B108" s="17" t="inlineStr">
         <is>
-          <t>CustomerMirrorPanel</t>
+          <t>DualPlaySerialCheckStep</t>
         </is>
       </c>
       <c r="C108" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/CustomerMirrorPanel.tsx</t>
-        </is>
-      </c>
-      <c r="D108" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>components/patterns/DualPlaySerialCheckStep.tsx</t>
+        </is>
+      </c>
+      <c r="D108" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E108" s="17" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F108" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fwa-5g-home</t>
         </is>
       </c>
       <c r="G108" s="17" t="inlineStr"/>
@@ -5861,76 +5869,72 @@
     <row r="109">
       <c r="A109" s="17" t="inlineStr">
         <is>
-          <t>Wizard</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="B109" s="17" t="inlineStr">
         <is>
-          <t>CustomerViewButton</t>
+          <t>SimSwapFormStep</t>
         </is>
       </c>
       <c r="C109" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/CustomerViewButton.tsx</t>
-        </is>
-      </c>
-      <c r="D109" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>components/patterns/SimSwapFormStep.tsx</t>
+        </is>
+      </c>
+      <c r="D109" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E109" s="17" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F109" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
-        </is>
-      </c>
-      <c r="G109" s="17" t="inlineStr">
-        <is>
-          <t>WizardStepHeader</t>
-        </is>
-      </c>
+          <t>sim-number-management</t>
+        </is>
+      </c>
+      <c r="G109" s="17" t="inlineStr"/>
       <c r="H109" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="17" t="inlineStr">
         <is>
-          <t>Wizard</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="B110" s="17" t="inlineStr">
         <is>
-          <t>StepSummaryPanel</t>
+          <t>VerificationGate</t>
         </is>
       </c>
       <c r="C110" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/StepSummaryPanel.tsx</t>
-        </is>
-      </c>
-      <c r="D110" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>components/patterns/VerificationGate.tsx</t>
+        </is>
+      </c>
+      <c r="D110" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E110" s="17" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F110" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>customer360</t>
         </is>
       </c>
       <c r="G110" s="17" t="inlineStr"/>
       <c r="H110" s="17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -5942,12 +5946,12 @@
       </c>
       <c r="B111" s="17" t="inlineStr">
         <is>
-          <t>StepSummarySection</t>
+          <t>AbandonDialog</t>
         </is>
       </c>
       <c r="C111" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/StepSummarySection.tsx</t>
+          <t>components/patterns/wizard/WizardDialogs.tsx</t>
         </is>
       </c>
       <c r="D111" s="20" t="inlineStr">
@@ -5963,14 +5967,10 @@
           <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
-      <c r="G111" s="17" t="inlineStr">
-        <is>
-          <t>StepSummaryPanel</t>
-        </is>
-      </c>
+      <c r="G111" s="17" t="inlineStr"/>
       <c r="H111" s="17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="B112" s="17" t="inlineStr">
         <is>
-          <t>SummaryFieldRow</t>
+          <t>CustomerMirrorPanel</t>
         </is>
       </c>
       <c r="C112" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/SummaryFieldRow.tsx</t>
+          <t>components/patterns/wizard/CustomerMirrorPanel.tsx</t>
         </is>
       </c>
       <c r="D112" s="20" t="inlineStr">
@@ -6003,14 +6003,10 @@
           <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
-      <c r="G112" s="17" t="inlineStr">
-        <is>
-          <t>StepSummaryPanel</t>
-        </is>
-      </c>
+      <c r="G112" s="17" t="inlineStr"/>
       <c r="H112" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6022,12 +6018,12 @@
       </c>
       <c r="B113" s="17" t="inlineStr">
         <is>
-          <t>WizardFooter</t>
+          <t>CustomerViewButton</t>
         </is>
       </c>
       <c r="C113" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/WizardFooter.tsx</t>
+          <t>components/patterns/wizard/CustomerViewButton.tsx</t>
         </is>
       </c>
       <c r="D113" s="20" t="inlineStr">
@@ -6043,10 +6039,14 @@
           <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
-      <c r="G113" s="17" t="inlineStr"/>
+      <c r="G113" s="17" t="inlineStr">
+        <is>
+          <t>WizardStepHeader</t>
+        </is>
+      </c>
       <c r="H113" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -6058,12 +6058,12 @@
       </c>
       <c r="B114" s="17" t="inlineStr">
         <is>
-          <t>WizardStepHeader</t>
+          <t>StepSummaryPanel</t>
         </is>
       </c>
       <c r="C114" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/WizardStepHeader.tsx</t>
+          <t>components/patterns/wizard/StepSummaryPanel.tsx</t>
         </is>
       </c>
       <c r="D114" s="20" t="inlineStr">
@@ -6082,7 +6082,7 @@
       <c r="G114" s="17" t="inlineStr"/>
       <c r="H114" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -6094,12 +6094,12 @@
       </c>
       <c r="B115" s="17" t="inlineStr">
         <is>
-          <t>WizardTitleBand</t>
+          <t>StepSummarySection</t>
         </is>
       </c>
       <c r="C115" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/WizardTitleBand.tsx</t>
+          <t>components/patterns/wizard/StepSummarySection.tsx</t>
         </is>
       </c>
       <c r="D115" s="20" t="inlineStr">
@@ -6115,15 +6115,167 @@
           <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
-      <c r="G115" s="17" t="inlineStr"/>
+      <c r="G115" s="17" t="inlineStr">
+        <is>
+          <t>StepSummaryPanel</t>
+        </is>
+      </c>
       <c r="H115" s="17" t="inlineStr">
         <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="17" t="inlineStr">
+        <is>
+          <t>Wizard</t>
+        </is>
+      </c>
+      <c r="B116" s="17" t="inlineStr">
+        <is>
+          <t>SummaryFieldRow</t>
+        </is>
+      </c>
+      <c r="C116" s="17" t="inlineStr">
+        <is>
+          <t>components/patterns/wizard/SummaryFieldRow.tsx</t>
+        </is>
+      </c>
+      <c r="D116" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
+        </is>
+      </c>
+      <c r="E116" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F116" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+      <c r="G116" s="17" t="inlineStr">
+        <is>
+          <t>StepSummaryPanel</t>
+        </is>
+      </c>
+      <c r="H116" s="17" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="17" t="inlineStr">
+        <is>
+          <t>Wizard</t>
+        </is>
+      </c>
+      <c r="B117" s="17" t="inlineStr">
+        <is>
+          <t>WizardFooter</t>
+        </is>
+      </c>
+      <c r="C117" s="17" t="inlineStr">
+        <is>
+          <t>components/patterns/wizard/WizardFooter.tsx</t>
+        </is>
+      </c>
+      <c r="D117" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
+        </is>
+      </c>
+      <c r="E117" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F117" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+      <c r="G117" s="17" t="inlineStr"/>
+      <c r="H117" s="17" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="17" t="inlineStr">
+        <is>
+          <t>Wizard</t>
+        </is>
+      </c>
+      <c r="B118" s="17" t="inlineStr">
+        <is>
+          <t>WizardStepHeader</t>
+        </is>
+      </c>
+      <c r="C118" s="17" t="inlineStr">
+        <is>
+          <t>components/patterns/wizard/WizardStepHeader.tsx</t>
+        </is>
+      </c>
+      <c r="D118" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
+        </is>
+      </c>
+      <c r="E118" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F118" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+      <c r="G118" s="17" t="inlineStr"/>
+      <c r="H118" s="17" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="17" t="inlineStr">
+        <is>
+          <t>Wizard</t>
+        </is>
+      </c>
+      <c r="B119" s="17" t="inlineStr">
+        <is>
+          <t>WizardTitleBand</t>
+        </is>
+      </c>
+      <c r="C119" s="17" t="inlineStr">
+        <is>
+          <t>components/patterns/wizard/WizardTitleBand.tsx</t>
+        </is>
+      </c>
+      <c r="D119" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
+        </is>
+      </c>
+      <c r="E119" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F119" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+      <c r="G119" s="17" t="inlineStr"/>
+      <c r="H119" s="17" t="inlineStr">
+        <is>
           <t>2026-10-20</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H115"/>
+  <autoFilter ref="A1:H119"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6134,7 +6286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.50" customWidth="1" min="1" max="1"/>
@@ -6220,7 +6372,7 @@
       </c>
       <c r="G2" s="17" t="inlineStr">
         <is>
-          <t>CompanySearchInput, ContactPhoneInput, CpeSerialScanner, MsisdnPicker, SimSerialScanner, AppointmentBookingStep, BillingAccountAutoResolver, BillingAccountStep, CafSignatureCapture, CafTerms, FixedPlanStep, PrepaidCartStep, PrepaidCheckoutStep, PrepaidPlanStep, TicketCreationModal, ZsbAddressStep, lineSelectionModel, useCheckoutSummary, useIdLookup, usePostpaidPlanAddons, StepSummaryPanel, stepSummary, useJourneyStartResume, useWizardDraftActions, LocationInput, activityEngine, agentProfileEngine, businessAccountEngine, connectionEligibility, customer360Engine, fibreServiceability, serviceLocationLookup, useAreaOptions, configStore, entityStore</t>
+          <t>CompanySearchInput, ContactPhoneInput, CpeSerialScanner, MsisdnPicker, SimSerialScanner, AppointmentBookingStep, BillingAccountAutoResolver, BillingAccountStep, CafSignatureCapture, CafTerms, FixedPlanStep, PrepaidCartStep, PrepaidCheckoutStep, PrepaidPlanStep, TicketCreationModal, ZsbAddressStep, lineSelectionModel, useCheckoutSummary, useIdLookup, usePostpaidPlanAddons, StepSummaryPanel, stepSummary, useJourneyStartResume, useWizardDraftActions, LocationInput, activityEngine, agentProfileEngine, businessAccountEngine, connectionEligibility, customer360Engine, fibreServiceability, serviceLocationLookup, useAreaOptions, useRestrictedCustomers, configStore, entityStore</t>
         </is>
       </c>
       <c r="H2" s="17" t="inlineStr">
@@ -6251,11 +6403,11 @@
         </is>
       </c>
       <c r="E3" s="17" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F3" s="17" t="inlineStr">
         <is>
-          <t>dashboard, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, sales, tasks, tickets</t>
+          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G3" s="17" t="inlineStr">
@@ -6277,12 +6429,12 @@
       </c>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t>hrnConfiguration</t>
+          <t>agentPrivilegeEngine</t>
         </is>
       </c>
       <c r="C4" s="17" t="inlineStr">
         <is>
-          <t>engines/hrnConfiguration.ts</t>
+          <t>engines/agentPrivilegeEngine.ts</t>
         </is>
       </c>
       <c r="D4" s="20" t="inlineStr">
@@ -6291,21 +6443,21 @@
         </is>
       </c>
       <c r="E4" s="17" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F4" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, support</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G4" s="17" t="inlineStr">
         <is>
-          <t>eligibilityRowsModel, PostpaidPlanAddonsStep, useCheckoutSummary, ruleEngine</t>
+          <t>TicketCreationModal, useIdLookup, useRestrictedCustomers</t>
         </is>
       </c>
       <c r="H4" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6317,12 +6469,12 @@
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>ruleEngine</t>
+          <t>hrnConfiguration</t>
         </is>
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>engines/ruleEngine.ts</t>
+          <t>engines/hrnConfiguration.ts</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -6340,7 +6492,7 @@
       </c>
       <c r="G5" s="17" t="inlineStr">
         <is>
-          <t>BillLimitEditor, CreditCheckPanel, eligibilityRowsModel, FixedPlanStep, TicketCreationModal</t>
+          <t>eligibilityRowsModel, CreditLimitCard, PostpaidPlanAddonsStep, useCheckoutSummary, creditLimit, ruleEngine</t>
         </is>
       </c>
       <c r="H5" s="17" t="inlineStr">
@@ -6357,12 +6509,12 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>billingBalance</t>
+          <t>ruleEngine</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>engines/billingBalance.ts</t>
+          <t>engines/ruleEngine.ts</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -6371,21 +6523,21 @@
         </is>
       </c>
       <c r="E6" s="17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, product-lines, navigation, administration, customer-search, customer360, orders</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, support</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
         <is>
-          <t>customer360Demo, customer360Engine</t>
+          <t>BillLimitEditor, CreditCheckPanel, eligibilityRowsModel, FixedPlanStep, TicketCreationModal</t>
         </is>
       </c>
       <c r="H6" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -6397,12 +6549,12 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>customer360Engine</t>
+          <t>billingBalance</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>engines/customer360Engine.ts</t>
+          <t>engines/billingBalance.ts</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -6420,12 +6572,12 @@
       </c>
       <c r="G7" s="17" t="inlineStr">
         <is>
-          <t>customer360Demo, customerServicesEngine</t>
+          <t>customer360Demo, customer360Engine</t>
         </is>
       </c>
       <c r="H7" s="17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6589,12 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>customerServicesEngine</t>
+          <t>customer360Engine</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>engines/customerServicesEngine.ts</t>
+          <t>engines/customer360Engine.ts</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -6460,12 +6612,12 @@
       </c>
       <c r="G8" s="17" t="inlineStr">
         <is>
-          <t>lineSelectionModel, customer360Demo, connectionEligibility, customer360Engine</t>
+          <t>customer360Demo, customerServicesEngine</t>
         </is>
       </c>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -6477,12 +6629,12 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>milestoneEngine</t>
+          <t>customerServicesEngine</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>engines/milestoneEngine.ts</t>
+          <t>engines/customerServicesEngine.ts</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -6491,21 +6643,21 @@
         </is>
       </c>
       <c r="E9" s="17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, product-lines, navigation, administration, customer-search, customer360, orders</t>
         </is>
       </c>
       <c r="G9" s="17" t="inlineStr">
         <is>
-          <t>guidedWizardTypes, useJourneyMilestones</t>
+          <t>lineSelectionModel, customer360Demo, connectionEligibility, customer360Engine</t>
         </is>
       </c>
       <c r="H9" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6531,11 +6683,11 @@
         </is>
       </c>
       <c r="E10" s="17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G10" s="17" t="inlineStr">
@@ -6557,12 +6709,12 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>activityEngine</t>
+          <t>eligibilityEngine</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>engines/activityEngine.ts</t>
+          <t>engines/eligibilityEngine.ts</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -6571,21 +6723,21 @@
         </is>
       </c>
       <c r="E11" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G11" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen, useWizardDraftActions</t>
+          <t>eligibilityRowsModel, eligibilityTypes, useIdLookup</t>
         </is>
       </c>
       <c r="H11" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -6597,12 +6749,12 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>businessSegment</t>
+          <t>milestoneEngine</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>engines/businessSegment.ts</t>
+          <t>engines/milestoneEngine.ts</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -6611,16 +6763,16 @@
         </is>
       </c>
       <c r="E12" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, navigation, administration, customer-search, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G12" s="17" t="inlineStr">
         <is>
-          <t>BillingAccountStep, customer360Demo, businessAccountEngine</t>
+          <t>guidedWizardTypes, useJourneyMilestones</t>
         </is>
       </c>
       <c r="H12" s="17" t="inlineStr">
@@ -6637,12 +6789,12 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>postpaidPricing</t>
+          <t>activityEngine</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>engines/postpaidPricing.ts</t>
+          <t>engines/activityEngine.ts</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -6655,12 +6807,12 @@
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G13" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, CheckoutDefaultLayout, PostpaidMonthlySummary, checkoutDetailedTables, checkoutSummaryRows, useCheckoutSummary, usePostpaidPlanAddons</t>
+          <t>ActivationCompleteScreen, useWizardDraftActions</t>
         </is>
       </c>
       <c r="H13" s="17" t="inlineStr">
@@ -6677,12 +6829,12 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>connectionEligibility</t>
+          <t>businessSegment</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>engines/connectionEligibility.ts</t>
+          <t>engines/businessSegment.ts</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -6691,17 +6843,21 @@
         </is>
       </c>
       <c r="E14" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
-        </is>
-      </c>
-      <c r="G14" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, navigation, administration, customer-search, customer360</t>
+        </is>
+      </c>
+      <c r="G14" s="17" t="inlineStr">
+        <is>
+          <t>BillingAccountStep, customer360Demo, businessAccountEngine</t>
+        </is>
+      </c>
       <c r="H14" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -6713,12 +6869,12 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>customerBenefitEngine</t>
+          <t>creditLimit</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>engines/customerBenefitEngine.ts</t>
+          <t>engines/creditLimit.ts</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -6727,21 +6883,21 @@
         </is>
       </c>
       <c r="E15" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, administration, customer360</t>
         </is>
       </c>
       <c r="G15" s="17" t="inlineStr">
         <is>
-          <t>PostpaidPlanAddonsStep, usePostpaidPlanAddons</t>
+          <t>CreditLimitCard, billingAccountModel</t>
         </is>
       </c>
       <c r="H15" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>uncommitted</t>
         </is>
       </c>
     </row>
@@ -6753,12 +6909,12 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>eligibilityEngine</t>
+          <t>postpaidPricing</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>engines/eligibilityEngine.ts</t>
+          <t>engines/postpaidPricing.ts</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -6767,21 +6923,21 @@
         </is>
       </c>
       <c r="E16" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G16" s="17" t="inlineStr">
         <is>
-          <t>eligibilityRowsModel, eligibilityTypes</t>
+          <t>MsisdnPicker, CheckoutDefaultLayout, PostpaidMonthlySummary, checkoutDetailedTables, checkoutSummaryRows, useCheckoutSummary, usePostpaidPlanAddons</t>
         </is>
       </c>
       <c r="H16" s="17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -6793,12 +6949,12 @@
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>addonEligibility</t>
+          <t>connectionEligibility</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>engines/addonEligibility.ts</t>
+          <t>engines/connectionEligibility.ts</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -6807,17 +6963,17 @@
         </is>
       </c>
       <c r="E17" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F17" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
         </is>
       </c>
       <c r="G17" s="17" t="inlineStr"/>
       <c r="H17" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -6829,12 +6985,12 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>fibreServiceability</t>
+          <t>customerBenefitEngine</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>engines/fibreServiceability.ts</t>
+          <t>engines/customerBenefitEngine.ts</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -6843,21 +6999,21 @@
         </is>
       </c>
       <c r="E18" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
         </is>
       </c>
       <c r="G18" s="17" t="inlineStr">
         <is>
-          <t>FibreReadinessBanner, ActivationCompleteScreen</t>
+          <t>PostpaidPlanAddonsStep, usePostpaidPlanAddons</t>
         </is>
       </c>
       <c r="H18" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6869,12 +7025,12 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>personaEngine</t>
+          <t>addonEligibility</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>engines/personaEngine.ts</t>
+          <t>engines/addonEligibility.ts</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -6887,17 +7043,13 @@
       </c>
       <c r="F19" s="17" t="inlineStr">
         <is>
-          <t>dashboard, order-management, product-lines, sim-number-management, navigation, administration, customer360, orders, profile</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>approvalAuthority, navigationEngine</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G19" s="17" t="inlineStr"/>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -6909,12 +7061,12 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>eligibilityGuard</t>
+          <t>fibreServiceability</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>engines/eligibilityGuard.ts</t>
+          <t>engines/fibreServiceability.ts</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -6923,17 +7075,21 @@
         </is>
       </c>
       <c r="E20" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F20" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G20" s="17" t="inlineStr">
+        <is>
+          <t>FibreReadinessBanner, ActivationCompleteScreen</t>
+        </is>
+      </c>
       <c r="H20" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -6945,12 +7101,12 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>serviceLocationLookup</t>
+          <t>personaEngine</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>engines/serviceLocationLookup.ts</t>
+          <t>engines/personaEngine.ts</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -6959,21 +7115,21 @@
         </is>
       </c>
       <c r="E21" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F21" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>dashboard, order-management, product-lines, sim-number-management, navigation, administration, customer360, orders, profile</t>
         </is>
       </c>
       <c r="G21" s="17" t="inlineStr">
         <is>
-          <t>ZsbAddressStep</t>
+          <t>approvalAuthority, navigationEngine</t>
         </is>
       </c>
       <c r="H21" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -6985,12 +7141,12 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>agentPrivilegeEngine</t>
+          <t>eligibilityGuard</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>engines/agentPrivilegeEngine.ts</t>
+          <t>engines/eligibilityGuard.ts</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -6999,17 +7155,17 @@
         </is>
       </c>
       <c r="E22" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F22" s="17" t="inlineStr">
         <is>
-          <t>trouble-ticketing-complaints, navigation, administration, customer360, profile, tasks</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration</t>
         </is>
       </c>
       <c r="G22" s="17" t="inlineStr"/>
       <c r="H22" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7021,12 +7177,12 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>agentTaskEngine</t>
+          <t>serviceLocationLookup</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>engines/agentTaskEngine.ts</t>
+          <t>engines/serviceLocationLookup.ts</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -7035,17 +7191,21 @@
         </is>
       </c>
       <c r="E23" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F23" s="17" t="inlineStr">
         <is>
-          <t>dashboard, order-management, trouble-ticketing-complaints, orders, support, tasks</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G23" s="17" t="inlineStr">
+        <is>
+          <t>ZsbAddressStep</t>
+        </is>
+      </c>
       <c r="H23" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7057,12 +7217,12 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>approvalAuthority</t>
+          <t>restrictedCustomers</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>engines/approvalAuthority.ts</t>
+          <t>engines/restrictedCustomers.ts</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -7071,17 +7231,21 @@
         </is>
       </c>
       <c r="E24" s="17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>dashboard, order-management, sim-number-management, navigation, customer360, orders</t>
-        </is>
-      </c>
-      <c r="G24" s="17" t="inlineStr"/>
+          <t>order-management, trouble-ticketing-complaints, customer360, orders, support, tasks, tickets</t>
+        </is>
+      </c>
+      <c r="G24" s="17" t="inlineStr">
+        <is>
+          <t>useRestrictedCustomers</t>
+        </is>
+      </c>
       <c r="H24" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>uncommitted</t>
         </is>
       </c>
     </row>
@@ -7093,12 +7257,12 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>portInEngine</t>
+          <t>agentTaskEngine</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>engines/portInEngine.ts</t>
+          <t>engines/agentTaskEngine.ts</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -7111,13 +7275,13 @@
       </c>
       <c r="F25" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
+          <t>dashboard, order-management, trouble-ticketing-complaints, orders, support, tasks</t>
         </is>
       </c>
       <c r="G25" s="17" t="inlineStr"/>
       <c r="H25" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7129,12 +7293,12 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>csvExport</t>
+          <t>approvalAuthority</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>engines/csvExport.ts</t>
+          <t>engines/approvalAuthority.ts</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -7143,17 +7307,17 @@
         </is>
       </c>
       <c r="E26" s="17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>trouble-ticketing-complaints, customer360, profile, support</t>
+          <t>dashboard, order-management, sim-number-management, navigation, customer360, orders</t>
         </is>
       </c>
       <c r="G26" s="17" t="inlineStr"/>
       <c r="H26" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7165,12 +7329,12 @@
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>bellNotificationExpiry</t>
+          <t>portInEngine</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
-          <t>engines/bellNotificationExpiry.ts</t>
+          <t>engines/portInEngine.ts</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -7179,17 +7343,17 @@
         </is>
       </c>
       <c r="E27" s="17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F27" s="17" t="inlineStr">
         <is>
-          <t>administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
         </is>
       </c>
       <c r="G27" s="17" t="inlineStr"/>
       <c r="H27" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7201,12 +7365,12 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>businessAccountEngine</t>
+          <t>csvExport</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>engines/businessAccountEngine.ts</t>
+          <t>engines/csvExport.ts</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -7215,17 +7379,17 @@
         </is>
       </c>
       <c r="E28" s="17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>customer-search, customer360</t>
+          <t>trouble-ticketing-complaints, customer360, profile, support</t>
         </is>
       </c>
       <c r="G28" s="17" t="inlineStr"/>
       <c r="H28" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7237,12 +7401,12 @@
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>navigationEngine</t>
+          <t>bellNotificationExpiry</t>
         </is>
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>engines/navigationEngine.ts</t>
+          <t>engines/bellNotificationExpiry.ts</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -7255,13 +7419,13 @@
       </c>
       <c r="F29" s="17" t="inlineStr">
         <is>
-          <t>navigation, customer360</t>
+          <t>administration, customer360</t>
         </is>
       </c>
       <c r="G29" s="17" t="inlineStr"/>
       <c r="H29" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7273,12 +7437,12 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>qnomyQueueEngine</t>
+          <t>businessAccountEngine</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>engines/qnomyQueueEngine.ts</t>
+          <t>engines/businessAccountEngine.ts</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -7291,13 +7455,13 @@
       </c>
       <c r="F30" s="17" t="inlineStr">
         <is>
-          <t>navigation, tickets</t>
+          <t>customer-search, customer360</t>
         </is>
       </c>
       <c r="G30" s="17" t="inlineStr"/>
       <c r="H30" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -7309,31 +7473,31 @@
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>agentProfileEngine</t>
+          <t>navigationEngine</t>
         </is>
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>engines/agentProfileEngine.ts</t>
-        </is>
-      </c>
-      <c r="D31" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>engines/navigationEngine.ts</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E31" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
+          <t>navigation, customer360</t>
         </is>
       </c>
       <c r="G31" s="17" t="inlineStr"/>
       <c r="H31" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -7345,25 +7509,25 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>customer360VisibilityEngine</t>
+          <t>qnomyQueueEngine</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>engines/customer360VisibilityEngine.ts</t>
-        </is>
-      </c>
-      <c r="D32" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>engines/qnomyQueueEngine.ts</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E32" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" s="17" t="inlineStr">
         <is>
-          <t>customer360</t>
+          <t>navigation, tickets</t>
         </is>
       </c>
       <c r="G32" s="17" t="inlineStr"/>
@@ -7381,12 +7545,12 @@
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>profileChangeTicket</t>
+          <t>agentProfileEngine</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>engines/profileChangeTicket.ts</t>
+          <t>engines/agentProfileEngine.ts</t>
         </is>
       </c>
       <c r="D33" s="21" t="inlineStr">
@@ -7399,13 +7563,13 @@
       </c>
       <c r="F33" s="17" t="inlineStr">
         <is>
-          <t>customer360</t>
+          <t>navigation</t>
         </is>
       </c>
       <c r="G33" s="17" t="inlineStr"/>
       <c r="H33" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7417,12 +7581,12 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>searchScopeEngine</t>
+          <t>customer360VisibilityEngine</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>engines/searchScopeEngine.ts</t>
+          <t>engines/customer360VisibilityEngine.ts</t>
         </is>
       </c>
       <c r="D34" s="21" t="inlineStr">
@@ -7435,13 +7599,13 @@
       </c>
       <c r="F34" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
+          <t>customer360</t>
         </is>
       </c>
       <c r="G34" s="17" t="inlineStr"/>
       <c r="H34" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7453,27 +7617,31 @@
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>moduleDescriptions</t>
+          <t>profileChangeTicket</t>
         </is>
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
-          <t>engines/moduleDescriptions.ts</t>
-        </is>
-      </c>
-      <c r="D35" s="23" t="inlineStr">
-        <is>
-          <t>App shell only</t>
+          <t>engines/profileChangeTicket.ts</t>
+        </is>
+      </c>
+      <c r="D35" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E35" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F35" s="17" t="inlineStr">
+        <is>
+          <t>customer360</t>
+        </is>
+      </c>
       <c r="G35" s="17" t="inlineStr"/>
       <c r="H35" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -7485,107 +7653,95 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>screenGrouping</t>
+          <t>searchScopeEngine</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>engines/screenGrouping.ts</t>
-        </is>
-      </c>
-      <c r="D36" s="23" t="inlineStr">
-        <is>
-          <t>App shell only</t>
+          <t>engines/searchScopeEngine.ts</t>
+        </is>
+      </c>
+      <c r="D36" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E36" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F36" s="17" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
       <c r="G36" s="17" t="inlineStr"/>
       <c r="H36" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="17" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Engine</t>
         </is>
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>entityStore</t>
+          <t>moduleDescriptions</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>stores/entityStore.ts</t>
-        </is>
-      </c>
-      <c r="D37" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>engines/moduleDescriptions.ts</t>
+        </is>
+      </c>
+      <c r="D37" s="23" t="inlineStr">
+        <is>
+          <t>App shell only</t>
         </is>
       </c>
       <c r="E37" s="17" t="n">
-        <v>24</v>
-      </c>
-      <c r="F37" s="17" t="inlineStr">
-        <is>
-          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, sales, support, tasks, tickets</t>
-        </is>
-      </c>
-      <c r="G37" s="17" t="inlineStr">
-        <is>
-          <t>ActivationCompleteScreen, DonorAttachmentStep, DonorDetailsStep, useDraftStepSync, useWizardDraftActions, activityEngine, bellNotificationExpiry, profileChangeTicket</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F37" s="17" t="inlineStr"/>
+      <c r="G37" s="17" t="inlineStr"/>
       <c r="H37" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="17" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Engine</t>
         </is>
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>customerContextStore</t>
+          <t>screenGrouping</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>stores/customerContextStore.ts</t>
-        </is>
-      </c>
-      <c r="D38" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>engines/screenGrouping.ts</t>
+        </is>
+      </c>
+      <c r="D38" s="23" t="inlineStr">
+        <is>
+          <t>App shell only</t>
         </is>
       </c>
       <c r="E38" s="17" t="n">
-        <v>23</v>
-      </c>
-      <c r="F38" s="17" t="inlineStr">
-        <is>
-          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
-        </is>
-      </c>
-      <c r="G38" s="17" t="inlineStr">
-        <is>
-          <t>ActivationCompleteScreen, useActedForCustomer, useWizardDraftActions, authStore</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F38" s="17" t="inlineStr"/>
+      <c r="G38" s="17" t="inlineStr"/>
       <c r="H38" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7597,12 +7753,12 @@
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>authStore</t>
+          <t>entityStore</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>stores/authStore.ts</t>
+          <t>stores/entityStore.ts</t>
         </is>
       </c>
       <c r="D39" s="20" t="inlineStr">
@@ -7611,21 +7767,21 @@
         </is>
       </c>
       <c r="E39" s="17" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F39" s="17" t="inlineStr">
         <is>
-          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, support, tasks, tickets</t>
+          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G39" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, ActivationCompleteScreen, useWizardDraftActions, activityEngine, agentProfileEngine, profileChangeTicket, configStore</t>
+          <t>ActivationCompleteScreen, DonorAttachmentStep, DonorDetailsStep, useDraftStepSync, useWizardDraftActions, activityEngine, bellNotificationExpiry, profileChangeTicket</t>
         </is>
       </c>
       <c r="H39" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7637,12 +7793,12 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>notificationStore</t>
+          <t>customerContextStore</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>stores/notificationStore.ts</t>
+          <t>stores/customerContextStore.ts</t>
         </is>
       </c>
       <c r="D40" s="20" t="inlineStr">
@@ -7651,16 +7807,16 @@
         </is>
       </c>
       <c r="E40" s="17" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F40" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, profile, support, tasks</t>
+          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G40" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, ActivationCompleteScreen, TicketCreationModal, useJourneyMilestones, useWizardDraftActions, useWizardStepNavigation, profileChangeTicket, useSubmit</t>
+          <t>ActivationCompleteScreen, useActedForCustomer, useWizardDraftActions, authStore</t>
         </is>
       </c>
       <c r="H40" s="17" t="inlineStr">
@@ -7691,16 +7847,16 @@
         </is>
       </c>
       <c r="E41" s="17" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F41" s="17" t="inlineStr">
         <is>
-          <t>dashboard, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, tasks</t>
+          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G41" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, eligibilityRowsModel, ActivationCompleteScreen, AppointmentBookingStep, PostpaidPlanAddonsStep, useCheckoutSummary, configStore</t>
+          <t>MsisdnPicker, eligibilityRowsModel, ActivationCompleteScreen, AppointmentBookingStep, PostpaidPlanAddonsStep, TicketCreationModal, useCheckoutSummary, useIdLookup, useRestrictedCustomers, configStore</t>
         </is>
       </c>
       <c r="H41" s="17" t="inlineStr">
@@ -7717,12 +7873,12 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>workflowStore</t>
+          <t>authStore</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>stores/workflowStore.ts</t>
+          <t>stores/authStore.ts</t>
         </is>
       </c>
       <c r="D42" s="20" t="inlineStr">
@@ -7731,16 +7887,16 @@
         </is>
       </c>
       <c r="E42" s="17" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F42" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration</t>
+          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G42" s="17" t="inlineStr">
         <is>
-          <t>useJourneyStartResume, useMirrorChannel, useWizardDraftActions, useWizardStepNavigation</t>
+          <t>MsisdnPicker, ActivationCompleteScreen, useWizardDraftActions, activityEngine, agentProfileEngine, profileChangeTicket, configStore</t>
         </is>
       </c>
       <c r="H42" s="17" t="inlineStr">
@@ -7757,35 +7913,35 @@
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>customerVerificationStore</t>
+          <t>notificationStore</t>
         </is>
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>stores/customerVerificationStore.ts</t>
-        </is>
-      </c>
-      <c r="D43" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>stores/notificationStore.ts</t>
+        </is>
+      </c>
+      <c r="D43" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E43" s="17" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F43" s="17" t="inlineStr">
         <is>
-          <t>customer360</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, profile, support, tasks</t>
         </is>
       </c>
       <c r="G43" s="17" t="inlineStr">
         <is>
-          <t>VerificationGate</t>
+          <t>MsisdnPicker, ActivationCompleteScreen, TicketCreationModal, useJourneyMilestones, useWizardDraftActions, useWizardStepNavigation, profileChangeTicket, useSubmit</t>
         </is>
       </c>
       <c r="H43" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -7797,31 +7953,35 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>qnomyQueueStore</t>
+          <t>workflowStore</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>stores/qnomyQueueStore.ts</t>
-        </is>
-      </c>
-      <c r="D44" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>stores/workflowStore.ts</t>
+        </is>
+      </c>
+      <c r="D44" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E44" s="17" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F44" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="G44" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration</t>
+        </is>
+      </c>
+      <c r="G44" s="17" t="inlineStr">
+        <is>
+          <t>useJourneyStartResume, useMirrorChannel, useWizardDraftActions, useWizardStepNavigation</t>
+        </is>
+      </c>
       <c r="H44" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7993,12 @@
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>regionStore</t>
+          <t>customerVerificationStore</t>
         </is>
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>stores/regionStore.ts</t>
+          <t>stores/customerVerificationStore.ts</t>
         </is>
       </c>
       <c r="D45" s="21" t="inlineStr">
@@ -7851,10 +8011,14 @@
       </c>
       <c r="F45" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="G45" s="17" t="inlineStr"/>
+          <t>customer360</t>
+        </is>
+      </c>
+      <c r="G45" s="17" t="inlineStr">
+        <is>
+          <t>VerificationGate</t>
+        </is>
+      </c>
       <c r="H45" s="17" t="inlineStr">
         <is>
           <t>2026-09-24</t>
@@ -7869,12 +8033,12 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>sidebarStore</t>
+          <t>qnomyQueueStore</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>stores/sidebarStore.ts</t>
+          <t>stores/qnomyQueueStore.ts</t>
         </is>
       </c>
       <c r="D46" s="21" t="inlineStr">
@@ -7893,7 +8057,7 @@
       <c r="G46" s="17" t="inlineStr"/>
       <c r="H46" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -7905,12 +8069,12 @@
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>themeStore</t>
+          <t>regionStore</t>
         </is>
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>stores/themeStore.ts</t>
+          <t>stores/regionStore.ts</t>
         </is>
       </c>
       <c r="D47" s="21" t="inlineStr">
@@ -7929,7 +8093,7 @@
       <c r="G47" s="17" t="inlineStr"/>
       <c r="H47" s="17" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7941,23 +8105,27 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>configStore</t>
+          <t>sidebarStore</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>stores/configStore.ts</t>
-        </is>
-      </c>
-      <c r="D48" s="23" t="inlineStr">
-        <is>
-          <t>App shell only</t>
+          <t>stores/sidebarStore.ts</t>
+        </is>
+      </c>
+      <c r="D48" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E48" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F48" s="17" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
       <c r="G48" s="17" t="inlineStr"/>
       <c r="H48" s="17" t="inlineStr">
         <is>
@@ -7968,80 +8136,68 @@
     <row r="49">
       <c r="A49" s="17" t="inlineStr">
         <is>
-          <t>Hook</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>useEnterToSubmit</t>
+          <t>themeStore</t>
         </is>
       </c>
       <c r="C49" s="17" t="inlineStr">
         <is>
-          <t>hooks/useEnterToSubmit.ts</t>
-        </is>
-      </c>
-      <c r="D49" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>stores/themeStore.ts</t>
+        </is>
+      </c>
+      <c r="D49" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E49" s="17" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F49" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
-        </is>
-      </c>
-      <c r="G49" s="17" t="inlineStr">
-        <is>
-          <t>VerificationGate, useIdLookup</t>
-        </is>
-      </c>
+          <t>navigation</t>
+        </is>
+      </c>
+      <c r="G49" s="17" t="inlineStr"/>
       <c r="H49" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="17" t="inlineStr">
         <is>
-          <t>Hook</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>useSearchListNav</t>
+          <t>configStore</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>hooks/useSearchListNav.ts</t>
-        </is>
-      </c>
-      <c r="D50" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>stores/configStore.ts</t>
+        </is>
+      </c>
+      <c r="D50" s="23" t="inlineStr">
+        <is>
+          <t>App shell only</t>
         </is>
       </c>
       <c r="E50" s="17" t="n">
-        <v>11</v>
-      </c>
-      <c r="F50" s="17" t="inlineStr">
-        <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, navigation, administration, customer360</t>
-        </is>
-      </c>
-      <c r="G50" s="17" t="inlineStr">
-        <is>
-          <t>CompanySearchInput, ContactPhoneInput, PlanSearchBox, LocationInput</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F50" s="17" t="inlineStr"/>
+      <c r="G50" s="17" t="inlineStr"/>
       <c r="H50" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8053,12 +8209,12 @@
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>useAreaOptions</t>
+          <t>useEnterToSubmit</t>
         </is>
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>hooks/useAreaOptions.ts</t>
+          <t>hooks/useEnterToSubmit.ts</t>
         </is>
       </c>
       <c r="D51" s="20" t="inlineStr">
@@ -8067,21 +8223,21 @@
         </is>
       </c>
       <c r="E51" s="17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F51" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G51" s="17" t="inlineStr">
         <is>
-          <t>BillingAccountStep, ZsbAddressStep</t>
+          <t>VerificationGate, useIdLookup</t>
         </is>
       </c>
       <c r="H51" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -8093,12 +8249,12 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>useSubmit</t>
+          <t>useSearchListNav</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>hooks/useSubmit.ts</t>
+          <t>hooks/useSearchListNav.ts</t>
         </is>
       </c>
       <c r="D52" s="20" t="inlineStr">
@@ -8107,17 +8263,21 @@
         </is>
       </c>
       <c r="E52" s="17" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F52" s="17" t="inlineStr">
         <is>
-          <t>lead-management, mnp-fnp-porting, sim-number-management, trouble-ticketing-complaints, customer360, tasks</t>
-        </is>
-      </c>
-      <c r="G52" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, navigation, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G52" s="17" t="inlineStr">
+        <is>
+          <t>CompanySearchInput, ContactPhoneInput, PlanSearchBox, LocationInput</t>
+        </is>
+      </c>
       <c r="H52" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -8129,28 +8289,32 @@
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>useMinWidth</t>
+          <t>useAreaOptions</t>
         </is>
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>hooks/useMinWidth.ts</t>
-        </is>
-      </c>
-      <c r="D53" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>hooks/useAreaOptions.ts</t>
+        </is>
+      </c>
+      <c r="D53" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E53" s="17" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F53" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="G53" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G53" s="17" t="inlineStr">
+        <is>
+          <t>BillingAccountStep, ZsbAddressStep</t>
+        </is>
+      </c>
       <c r="H53" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
@@ -8160,17 +8324,17 @@
     <row r="54">
       <c r="A54" s="17" t="inlineStr">
         <is>
-          <t>Helper</t>
+          <t>Hook</t>
         </is>
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>statusTone</t>
+          <t>useRestrictedCustomers</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>lib/statusTone.ts</t>
+          <t>hooks/useRestrictedCustomers.ts</t>
         </is>
       </c>
       <c r="D54" s="20" t="inlineStr">
@@ -8179,38 +8343,38 @@
         </is>
       </c>
       <c r="E54" s="17" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F54" s="17" t="inlineStr">
         <is>
-          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, orders, sales, support, tasks, tickets</t>
+          <t>order-management, trouble-ticketing-complaints, customer360, orders, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G54" s="17" t="inlineStr">
         <is>
-          <t>ruleEngine</t>
+          <t>TicketCreationModal</t>
         </is>
       </c>
       <c r="H54" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>uncommitted</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="17" t="inlineStr">
         <is>
-          <t>Helper</t>
+          <t>Hook</t>
         </is>
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>format</t>
+          <t>useSubmit</t>
         </is>
       </c>
       <c r="C55" s="17" t="inlineStr">
         <is>
-          <t>lib/format.ts</t>
+          <t>hooks/useSubmit.ts</t>
         </is>
       </c>
       <c r="D55" s="20" t="inlineStr">
@@ -8219,61 +8383,53 @@
         </is>
       </c>
       <c r="E55" s="17" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F55" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, tasks</t>
-        </is>
-      </c>
-      <c r="G55" s="17" t="inlineStr">
-        <is>
-          <t>AdditionalDocumentsUpload, CafDocumentUpload, MsisdnPicker, GuidedContactStep, IdLookupStep, postpaidPlanModel, StepSummaryPanel, stepSummary, customer360Engine, postpaidPricing</t>
-        </is>
-      </c>
+          <t>lead-management, mnp-fnp-porting, sim-number-management, trouble-ticketing-complaints, customer360, tasks</t>
+        </is>
+      </c>
+      <c r="G55" s="17" t="inlineStr"/>
       <c r="H55" s="17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="17" t="inlineStr">
         <is>
-          <t>Helper</t>
+          <t>Hook</t>
         </is>
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>buildEnv</t>
+          <t>useMinWidth</t>
         </is>
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t>lib/buildEnv.ts</t>
-        </is>
-      </c>
-      <c r="D56" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>hooks/useMinWidth.ts</t>
+        </is>
+      </c>
+      <c r="D56" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E56" s="17" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F56" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360</t>
-        </is>
-      </c>
-      <c r="G56" s="17" t="inlineStr">
-        <is>
-          <t>syntheticMarker, navigationEngine</t>
-        </is>
-      </c>
+          <t>navigation</t>
+        </is>
+      </c>
+      <c r="G56" s="17" t="inlineStr"/>
       <c r="H56" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8285,12 +8441,12 @@
       </c>
       <c r="B57" s="17" t="inlineStr">
         <is>
-          <t>deviceType</t>
+          <t>statusTone</t>
         </is>
       </c>
       <c r="C57" s="17" t="inlineStr">
         <is>
-          <t>lib/deviceType.ts</t>
+          <t>lib/statusTone.ts</t>
         </is>
       </c>
       <c r="D57" s="20" t="inlineStr">
@@ -8299,21 +8455,21 @@
         </is>
       </c>
       <c r="E57" s="17" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F57" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration, customer360</t>
+          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, orders, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G57" s="17" t="inlineStr">
         <is>
-          <t>IdFileUpload, PassportScanSections, SimSerialScanner, SimTypeStep, cafTypes</t>
+          <t>ruleEngine</t>
         </is>
       </c>
       <c r="H57" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8325,12 +8481,12 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>taskId</t>
+          <t>format</t>
         </is>
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t>lib/taskId.ts</t>
+          <t>lib/format.ts</t>
         </is>
       </c>
       <c r="D58" s="20" t="inlineStr">
@@ -8339,21 +8495,21 @@
         </is>
       </c>
       <c r="E58" s="17" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F58" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, tasks</t>
         </is>
       </c>
       <c r="G58" s="17" t="inlineStr">
         <is>
-          <t>useWizardDraftActions</t>
+          <t>AdditionalDocumentsUpload, CafDocumentUpload, MsisdnPicker, GuidedContactStep, IdLookupStep, postpaidPlanModel, StepSummaryPanel, stepSummary, customer360Engine, postpaidPricing</t>
         </is>
       </c>
       <c r="H58" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -8365,12 +8521,12 @@
       </c>
       <c r="B59" s="17" t="inlineStr">
         <is>
-          <t>connectionType</t>
+          <t>buildEnv</t>
         </is>
       </c>
       <c r="C59" s="17" t="inlineStr">
         <is>
-          <t>lib/connectionType.ts</t>
+          <t>lib/buildEnv.ts</t>
         </is>
       </c>
       <c r="D59" s="20" t="inlineStr">
@@ -8379,16 +8535,16 @@
         </is>
       </c>
       <c r="E59" s="17" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F59" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360</t>
         </is>
       </c>
       <c r="G59" s="17" t="inlineStr">
         <is>
-          <t>ConnectionTypeTag</t>
+          <t>syntheticMarker, navigationEngine</t>
         </is>
       </c>
       <c r="H59" s="17" t="inlineStr">
@@ -8405,12 +8561,12 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>serviceTypeTag</t>
+          <t>deviceType</t>
         </is>
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t>lib/serviceTypeTag.ts</t>
+          <t>lib/deviceType.ts</t>
         </is>
       </c>
       <c r="D60" s="20" t="inlineStr">
@@ -8419,21 +8575,21 @@
         </is>
       </c>
       <c r="E60" s="17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F60" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration, customer360</t>
         </is>
       </c>
       <c r="G60" s="17" t="inlineStr">
         <is>
-          <t>ServiceTypeTag</t>
+          <t>IdFileUpload, PassportScanSections, SimSerialScanner, SimTypeStep, cafTypes</t>
         </is>
       </c>
       <c r="H60" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8445,28 +8601,32 @@
       </c>
       <c r="B61" s="17" t="inlineStr">
         <is>
-          <t>screenName</t>
+          <t>taskId</t>
         </is>
       </c>
       <c r="C61" s="17" t="inlineStr">
         <is>
-          <t>lib/screenName.ts</t>
-        </is>
-      </c>
-      <c r="D61" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>lib/taskId.ts</t>
+        </is>
+      </c>
+      <c r="D61" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E61" s="17" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F61" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="G61" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+      <c r="G61" s="17" t="inlineStr">
+        <is>
+          <t>useWizardDraftActions</t>
+        </is>
+      </c>
       <c r="H61" s="17" t="inlineStr">
         <is>
           <t>2026-10-15</t>
@@ -8481,40 +8641,156 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
+          <t>connectionType</t>
+        </is>
+      </c>
+      <c r="C62" s="17" t="inlineStr">
+        <is>
+          <t>lib/connectionType.ts</t>
+        </is>
+      </c>
+      <c r="D62" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
+        </is>
+      </c>
+      <c r="E62" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="F62" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G62" s="17" t="inlineStr">
+        <is>
+          <t>ConnectionTypeTag</t>
+        </is>
+      </c>
+      <c r="H62" s="17" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="17" t="inlineStr">
+        <is>
+          <t>Helper</t>
+        </is>
+      </c>
+      <c r="B63" s="17" t="inlineStr">
+        <is>
+          <t>serviceTypeTag</t>
+        </is>
+      </c>
+      <c r="C63" s="17" t="inlineStr">
+        <is>
+          <t>lib/serviceTypeTag.ts</t>
+        </is>
+      </c>
+      <c r="D63" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
+        </is>
+      </c>
+      <c r="E63" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="F63" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G63" s="17" t="inlineStr">
+        <is>
+          <t>ServiceTypeTag</t>
+        </is>
+      </c>
+      <c r="H63" s="17" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="17" t="inlineStr">
+        <is>
+          <t>Helper</t>
+        </is>
+      </c>
+      <c r="B64" s="17" t="inlineStr">
+        <is>
+          <t>screenName</t>
+        </is>
+      </c>
+      <c r="C64" s="17" t="inlineStr">
+        <is>
+          <t>lib/screenName.ts</t>
+        </is>
+      </c>
+      <c r="D64" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
+        </is>
+      </c>
+      <c r="E64" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" s="17" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
+      <c r="G64" s="17" t="inlineStr"/>
+      <c r="H64" s="17" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="17" t="inlineStr">
+        <is>
+          <t>Helper</t>
+        </is>
+      </c>
+      <c r="B65" s="17" t="inlineStr">
+        <is>
           <t>values</t>
         </is>
       </c>
-      <c r="C62" s="17" t="inlineStr">
+      <c r="C65" s="17" t="inlineStr">
         <is>
           <t>lib/values.ts</t>
         </is>
       </c>
-      <c r="D62" s="21" t="inlineStr">
+      <c r="D65" s="21" t="inlineStr">
         <is>
           <t>Single area</t>
         </is>
       </c>
-      <c r="E62" s="17" t="n">
+      <c r="E65" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F62" s="17" t="inlineStr">
+      <c r="F65" s="17" t="inlineStr">
         <is>
           <t>customer360</t>
         </is>
       </c>
-      <c r="G62" s="17" t="inlineStr">
+      <c r="G65" s="17" t="inlineStr">
         <is>
           <t>customer360Demo</t>
         </is>
       </c>
-      <c r="H62" s="17" t="inlineStr">
+      <c r="H65" s="17" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H62"/>
+  <autoFilter ref="A1:H65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
+++ b/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'UI Components'!$A$1:$H$119</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Shared Code'!$A$1:$H$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Shared Code'!$A$1:$H$66</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -763,13 +763,13 @@
         </is>
       </c>
       <c r="C9" s="17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D9" s="17" t="n">
         <v>31</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F9" s="17" t="n">
         <v>2</v>
@@ -855,17 +855,17 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>118 UI components + 64 non-UI files</t>
+          <t>118 UI components + 65 non-UI files</t>
         </is>
       </c>
       <c r="C13" s="18" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D13" s="18" t="n">
         <v>156</v>
       </c>
       <c r="E13" s="18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F13" s="18" t="n">
         <v>5</v>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="H36" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H39" s="17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -3948,11 +3948,11 @@
         </is>
       </c>
       <c r="E58" s="17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F58" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer-search, customer360, support</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer-search, customer360, support, tasks</t>
         </is>
       </c>
       <c r="G58" s="17" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="H58" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
       <c r="G59" s="17" t="inlineStr"/>
       <c r="H59" s="17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="H61" s="17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="H62" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="H63" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -4502,7 +4502,7 @@
       <c r="G72" s="17" t="inlineStr"/>
       <c r="H72" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       <c r="G96" s="17" t="inlineStr"/>
       <c r="H96" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       <c r="G103" s="17" t="inlineStr"/>
       <c r="H103" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       <c r="G106" s="17" t="inlineStr"/>
       <c r="H106" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.50" customWidth="1" min="1" max="1"/>
@@ -6372,12 +6372,12 @@
       </c>
       <c r="G2" s="17" t="inlineStr">
         <is>
-          <t>CompanySearchInput, ContactPhoneInput, CpeSerialScanner, MsisdnPicker, SimSerialScanner, AppointmentBookingStep, BillingAccountAutoResolver, BillingAccountStep, CafSignatureCapture, CafTerms, FixedPlanStep, PrepaidCartStep, PrepaidCheckoutStep, PrepaidPlanStep, TicketCreationModal, ZsbAddressStep, lineSelectionModel, useCheckoutSummary, useIdLookup, usePostpaidPlanAddons, StepSummaryPanel, stepSummary, useJourneyStartResume, useWizardDraftActions, LocationInput, activityEngine, agentProfileEngine, businessAccountEngine, connectionEligibility, customer360Engine, fibreServiceability, serviceLocationLookup, useAreaOptions, useRestrictedCustomers, configStore, entityStore</t>
+          <t>CompanySearchInput, ContactPhoneInput, CpeSerialScanner, MsisdnPicker, SimSerialScanner, AppointmentBookingStep, BillingAccountAutoResolver, BillingAccountStep, CafSignatureCapture, CafTerms, FixedPlanStep, PrepaidCartStep, PrepaidCheckoutStep, PrepaidPlanStep, TicketCreationModal, ZsbAddressStep, lineSelectionModel, useCheckoutSummary, useIdLookup, usePostpaidPlanAddons, StepSummaryPanel, stepSummary, useJourneyStartResume, useWizardDraftActions, LocationInput, activityEngine, agentProfileEngine, businessAccountEngine, connectionEligibility, customer360Engine, fibreServiceability, roleSwitchPurge, serviceLocationLookup, useAreaOptions, useRestrictedCustomers, configStore, entityStore</t>
         </is>
       </c>
       <c r="H2" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -6452,12 +6452,12 @@
       </c>
       <c r="G4" s="17" t="inlineStr">
         <is>
-          <t>TicketCreationModal, useIdLookup, useRestrictedCustomers</t>
+          <t>TicketCreationModal, useIdLookup, roleSwitchPurge, useRestrictedCustomers</t>
         </is>
       </c>
       <c r="H4" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -6509,12 +6509,12 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>ruleEngine</t>
+          <t>restrictedCustomers</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>engines/ruleEngine.ts</t>
+          <t>engines/restrictedCustomers.ts</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -6527,17 +6527,17 @@
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, support</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, trouble-ticketing-complaints, navigation, customer360, orders, profile, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
         <is>
-          <t>BillLimitEditor, CreditCheckPanel, eligibilityRowsModel, FixedPlanStep, TicketCreationModal</t>
+          <t>useRestrictedCustomers</t>
         </is>
       </c>
       <c r="H6" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -6549,12 +6549,12 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>billingBalance</t>
+          <t>ruleEngine</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>engines/billingBalance.ts</t>
+          <t>engines/ruleEngine.ts</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -6563,21 +6563,21 @@
         </is>
       </c>
       <c r="E7" s="17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, product-lines, navigation, administration, customer-search, customer360, orders</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, support</t>
         </is>
       </c>
       <c r="G7" s="17" t="inlineStr">
         <is>
-          <t>customer360Demo, customer360Engine</t>
+          <t>BillLimitEditor, CreditCheckPanel, eligibilityRowsModel, FixedPlanStep, TicketCreationModal</t>
         </is>
       </c>
       <c r="H7" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -6589,12 +6589,12 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>customer360Engine</t>
+          <t>billingBalance</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>engines/customer360Engine.ts</t>
+          <t>engines/billingBalance.ts</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="G8" s="17" t="inlineStr">
         <is>
-          <t>customer360Demo, customerServicesEngine</t>
+          <t>customer360Demo, customer360Engine</t>
         </is>
       </c>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6629,12 +6629,12 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>customerServicesEngine</t>
+          <t>customer360Engine</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>engines/customerServicesEngine.ts</t>
+          <t>engines/customer360Engine.ts</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -6652,12 +6652,12 @@
       </c>
       <c r="G9" s="17" t="inlineStr">
         <is>
-          <t>lineSelectionModel, customer360Demo, connectionEligibility, customer360Engine</t>
+          <t>customer360Demo, customerServicesEngine</t>
         </is>
       </c>
       <c r="H9" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>serviceCall</t>
+          <t>customerServicesEngine</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>engines/serviceCall.ts</t>
+          <t>engines/customerServicesEngine.ts</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -6683,21 +6683,21 @@
         </is>
       </c>
       <c r="E10" s="17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, product-lines, navigation, administration, customer-search, customer360, orders</t>
         </is>
       </c>
       <c r="G10" s="17" t="inlineStr">
         <is>
-          <t>DemoFaultPanel, ValidationStatus, useIdLookup</t>
+          <t>lineSelectionModel, customer360Demo, connectionEligibility, customer360Engine</t>
         </is>
       </c>
       <c r="H10" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6709,12 +6709,12 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>eligibilityEngine</t>
+          <t>serviceCall</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>engines/eligibilityEngine.ts</t>
+          <t>engines/serviceCall.ts</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -6723,21 +6723,21 @@
         </is>
       </c>
       <c r="E11" s="17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G11" s="17" t="inlineStr">
         <is>
-          <t>eligibilityRowsModel, eligibilityTypes, useIdLookup</t>
+          <t>DemoFaultPanel, ValidationStatus, useIdLookup</t>
         </is>
       </c>
       <c r="H11" s="17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -6749,12 +6749,12 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>milestoneEngine</t>
+          <t>eligibilityEngine</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>engines/milestoneEngine.ts</t>
+          <t>engines/eligibilityEngine.ts</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="G12" s="17" t="inlineStr">
         <is>
-          <t>guidedWizardTypes, useJourneyMilestones</t>
+          <t>eligibilityRowsModel, eligibilityTypes, useIdLookup</t>
         </is>
       </c>
       <c r="H12" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -6789,12 +6789,12 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>activityEngine</t>
+          <t>milestoneEngine</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>engines/activityEngine.ts</t>
+          <t>engines/milestoneEngine.ts</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -6803,16 +6803,16 @@
         </is>
       </c>
       <c r="E13" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G13" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen, useWizardDraftActions</t>
+          <t>guidedWizardTypes, useJourneyMilestones</t>
         </is>
       </c>
       <c r="H13" s="17" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>businessSegment</t>
+          <t>activityEngine</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>engines/businessSegment.ts</t>
+          <t>engines/activityEngine.ts</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -6847,12 +6847,12 @@
       </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, navigation, administration, customer-search, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G14" s="17" t="inlineStr">
         <is>
-          <t>BillingAccountStep, customer360Demo, businessAccountEngine</t>
+          <t>ActivationCompleteScreen, useWizardDraftActions</t>
         </is>
       </c>
       <c r="H14" s="17" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>creditLimit</t>
+          <t>businessSegment</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>engines/creditLimit.ts</t>
+          <t>engines/businessSegment.ts</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -6887,17 +6887,17 @@
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, navigation, administration, customer-search, customer360</t>
         </is>
       </c>
       <c r="G15" s="17" t="inlineStr">
         <is>
-          <t>CreditLimitCard, billingAccountModel</t>
+          <t>BillingAccountStep, customer360Demo, businessAccountEngine</t>
         </is>
       </c>
       <c r="H15" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -6909,12 +6909,12 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>postpaidPricing</t>
+          <t>creditLimit</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>engines/postpaidPricing.ts</t>
+          <t>engines/creditLimit.ts</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -6927,17 +6927,17 @@
       </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, administration, customer360</t>
         </is>
       </c>
       <c r="G16" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, CheckoutDefaultLayout, PostpaidMonthlySummary, checkoutDetailedTables, checkoutSummaryRows, useCheckoutSummary, usePostpaidPlanAddons</t>
+          <t>CreditLimitCard, billingAccountModel</t>
         </is>
       </c>
       <c r="H16" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -6949,12 +6949,12 @@
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>connectionEligibility</t>
+          <t>postpaidPricing</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>engines/connectionEligibility.ts</t>
+          <t>engines/postpaidPricing.ts</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -6963,17 +6963,21 @@
         </is>
       </c>
       <c r="E17" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F17" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+      <c r="G17" s="17" t="inlineStr">
+        <is>
+          <t>MsisdnPicker, CheckoutDefaultLayout, PostpaidMonthlySummary, checkoutDetailedTables, checkoutSummaryRows, useCheckoutSummary, usePostpaidPlanAddons</t>
+        </is>
+      </c>
       <c r="H17" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -6985,12 +6989,12 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>customerBenefitEngine</t>
+          <t>connectionEligibility</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>engines/customerBenefitEngine.ts</t>
+          <t>engines/connectionEligibility.ts</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -7006,14 +7010,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
         </is>
       </c>
-      <c r="G18" s="17" t="inlineStr">
-        <is>
-          <t>PostpaidPlanAddonsStep, usePostpaidPlanAddons</t>
-        </is>
-      </c>
+      <c r="G18" s="17" t="inlineStr"/>
       <c r="H18" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -7025,12 +7025,12 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>addonEligibility</t>
+          <t>customerBenefitEngine</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>engines/addonEligibility.ts</t>
+          <t>engines/customerBenefitEngine.ts</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -7039,17 +7039,21 @@
         </is>
       </c>
       <c r="E19" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F19" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G19" s="17" t="inlineStr">
+        <is>
+          <t>PostpaidPlanAddonsStep, usePostpaidPlanAddons</t>
+        </is>
+      </c>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7061,12 +7065,12 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>fibreServiceability</t>
+          <t>addonEligibility</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>engines/fibreServiceability.ts</t>
+          <t>engines/addonEligibility.ts</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -7082,11 +7086,7 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>FibreReadinessBanner, ActivationCompleteScreen</t>
-        </is>
-      </c>
+      <c r="G20" s="17" t="inlineStr"/>
       <c r="H20" s="17" t="inlineStr">
         <is>
           <t>2026-10-05</t>
@@ -7101,12 +7101,12 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>personaEngine</t>
+          <t>fibreServiceability</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>engines/personaEngine.ts</t>
+          <t>engines/fibreServiceability.ts</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -7119,17 +7119,17 @@
       </c>
       <c r="F21" s="17" t="inlineStr">
         <is>
-          <t>dashboard, order-management, product-lines, sim-number-management, navigation, administration, customer360, orders, profile</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G21" s="17" t="inlineStr">
         <is>
-          <t>approvalAuthority, navigationEngine</t>
+          <t>FibreReadinessBanner, ActivationCompleteScreen</t>
         </is>
       </c>
       <c r="H21" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -7141,12 +7141,12 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>eligibilityGuard</t>
+          <t>personaEngine</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>engines/eligibilityGuard.ts</t>
+          <t>engines/personaEngine.ts</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -7155,17 +7155,21 @@
         </is>
       </c>
       <c r="E22" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F22" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration</t>
-        </is>
-      </c>
-      <c r="G22" s="17" t="inlineStr"/>
+          <t>dashboard, order-management, product-lines, sim-number-management, navigation, administration, customer360, orders, profile</t>
+        </is>
+      </c>
+      <c r="G22" s="17" t="inlineStr">
+        <is>
+          <t>approvalAuthority, navigationEngine</t>
+        </is>
+      </c>
       <c r="H22" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -7177,12 +7181,12 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>serviceLocationLookup</t>
+          <t>eligibilityGuard</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>engines/serviceLocationLookup.ts</t>
+          <t>engines/eligibilityGuard.ts</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -7195,14 +7199,10 @@
       </c>
       <c r="F23" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr">
-        <is>
-          <t>ZsbAddressStep</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration</t>
+        </is>
+      </c>
+      <c r="G23" s="17" t="inlineStr"/>
       <c r="H23" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>restrictedCustomers</t>
+          <t>serviceLocationLookup</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>engines/restrictedCustomers.ts</t>
+          <t>engines/serviceLocationLookup.ts</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -7231,21 +7231,21 @@
         </is>
       </c>
       <c r="E24" s="17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>order-management, trouble-ticketing-complaints, customer360, orders, support, tasks, tickets</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G24" s="17" t="inlineStr">
         <is>
-          <t>useRestrictedCustomers</t>
+          <t>ZsbAddressStep</t>
         </is>
       </c>
       <c r="H24" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7653,12 +7653,12 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>searchScopeEngine</t>
+          <t>roleSwitchPurge</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>engines/searchScopeEngine.ts</t>
+          <t>engines/roleSwitchPurge.ts</t>
         </is>
       </c>
       <c r="D36" s="21" t="inlineStr">
@@ -7677,7 +7677,7 @@
       <c r="G36" s="17" t="inlineStr"/>
       <c r="H36" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>uncommitted</t>
         </is>
       </c>
     </row>
@@ -7689,27 +7689,31 @@
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>moduleDescriptions</t>
+          <t>searchScopeEngine</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>engines/moduleDescriptions.ts</t>
-        </is>
-      </c>
-      <c r="D37" s="23" t="inlineStr">
-        <is>
-          <t>App shell only</t>
+          <t>engines/searchScopeEngine.ts</t>
+        </is>
+      </c>
+      <c r="D37" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E37" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F37" s="17" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
       <c r="G37" s="17" t="inlineStr"/>
       <c r="H37" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -7721,12 +7725,12 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>screenGrouping</t>
+          <t>moduleDescriptions</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>engines/screenGrouping.ts</t>
+          <t>engines/moduleDescriptions.ts</t>
         </is>
       </c>
       <c r="D38" s="23" t="inlineStr">
@@ -7748,40 +7752,32 @@
     <row r="39">
       <c r="A39" s="17" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Engine</t>
         </is>
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>entityStore</t>
+          <t>screenGrouping</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>stores/entityStore.ts</t>
-        </is>
-      </c>
-      <c r="D39" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>engines/screenGrouping.ts</t>
+        </is>
+      </c>
+      <c r="D39" s="23" t="inlineStr">
+        <is>
+          <t>App shell only</t>
         </is>
       </c>
       <c r="E39" s="17" t="n">
-        <v>24</v>
-      </c>
-      <c r="F39" s="17" t="inlineStr">
-        <is>
-          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, sales, support, tasks, tickets</t>
-        </is>
-      </c>
-      <c r="G39" s="17" t="inlineStr">
-        <is>
-          <t>ActivationCompleteScreen, DonorAttachmentStep, DonorDetailsStep, useDraftStepSync, useWizardDraftActions, activityEngine, bellNotificationExpiry, profileChangeTicket</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F39" s="17" t="inlineStr"/>
+      <c r="G39" s="17" t="inlineStr"/>
       <c r="H39" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7789,12 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>customerContextStore</t>
+          <t>entityStore</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>stores/customerContextStore.ts</t>
+          <t>stores/entityStore.ts</t>
         </is>
       </c>
       <c r="D40" s="20" t="inlineStr">
@@ -7807,21 +7803,21 @@
         </is>
       </c>
       <c r="E40" s="17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F40" s="17" t="inlineStr">
         <is>
-          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
+          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G40" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen, useActedForCustomer, useWizardDraftActions, authStore</t>
+          <t>ActivationCompleteScreen, DonorAttachmentStep, DonorDetailsStep, useDraftStepSync, useWizardDraftActions, activityEngine, bellNotificationExpiry, profileChangeTicket</t>
         </is>
       </c>
       <c r="H40" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7829,12 @@
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>personaStore</t>
+          <t>customerContextStore</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>stores/personaStore.ts</t>
+          <t>stores/customerContextStore.ts</t>
         </is>
       </c>
       <c r="D41" s="20" t="inlineStr">
@@ -7851,17 +7847,17 @@
       </c>
       <c r="F41" s="17" t="inlineStr">
         <is>
-          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, support, tasks, tickets</t>
+          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G41" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, eligibilityRowsModel, ActivationCompleteScreen, AppointmentBookingStep, PostpaidPlanAddonsStep, TicketCreationModal, useCheckoutSummary, useIdLookup, useRestrictedCustomers, configStore</t>
+          <t>ActivationCompleteScreen, useActedForCustomer, useWizardDraftActions, roleSwitchPurge, authStore</t>
         </is>
       </c>
       <c r="H41" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -7873,12 +7869,12 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>authStore</t>
+          <t>personaStore</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>stores/authStore.ts</t>
+          <t>stores/personaStore.ts</t>
         </is>
       </c>
       <c r="D42" s="20" t="inlineStr">
@@ -7887,16 +7883,16 @@
         </is>
       </c>
       <c r="E42" s="17" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F42" s="17" t="inlineStr">
         <is>
-          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, support, tasks, tickets</t>
+          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G42" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, ActivationCompleteScreen, useWizardDraftActions, activityEngine, agentProfileEngine, profileChangeTicket, configStore</t>
+          <t>MsisdnPicker, eligibilityRowsModel, ActivationCompleteScreen, AppointmentBookingStep, PostpaidPlanAddonsStep, TicketCreationModal, useCheckoutSummary, useIdLookup, useRestrictedCustomers, configStore</t>
         </is>
       </c>
       <c r="H42" s="17" t="inlineStr">
@@ -7913,12 +7909,12 @@
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>notificationStore</t>
+          <t>authStore</t>
         </is>
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>stores/notificationStore.ts</t>
+          <t>stores/authStore.ts</t>
         </is>
       </c>
       <c r="D43" s="20" t="inlineStr">
@@ -7927,21 +7923,21 @@
         </is>
       </c>
       <c r="E43" s="17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F43" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, profile, support, tasks</t>
+          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G43" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, ActivationCompleteScreen, TicketCreationModal, useJourneyMilestones, useWizardDraftActions, useWizardStepNavigation, profileChangeTicket, useSubmit</t>
+          <t>MsisdnPicker, ActivationCompleteScreen, useWizardDraftActions, activityEngine, agentProfileEngine, profileChangeTicket, configStore</t>
         </is>
       </c>
       <c r="H43" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7953,12 +7949,12 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>workflowStore</t>
+          <t>notificationStore</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>stores/workflowStore.ts</t>
+          <t>stores/notificationStore.ts</t>
         </is>
       </c>
       <c r="D44" s="20" t="inlineStr">
@@ -7967,21 +7963,21 @@
         </is>
       </c>
       <c r="E44" s="17" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F44" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, profile, support, tasks</t>
         </is>
       </c>
       <c r="G44" s="17" t="inlineStr">
         <is>
-          <t>useJourneyStartResume, useMirrorChannel, useWizardDraftActions, useWizardStepNavigation</t>
+          <t>MsisdnPicker, ActivationCompleteScreen, TicketCreationModal, useJourneyMilestones, useWizardDraftActions, useWizardStepNavigation, profileChangeTicket, roleSwitchPurge, useSubmit</t>
         </is>
       </c>
       <c r="H44" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -7993,35 +7989,35 @@
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>customerVerificationStore</t>
+          <t>workflowStore</t>
         </is>
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>stores/customerVerificationStore.ts</t>
-        </is>
-      </c>
-      <c r="D45" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>stores/workflowStore.ts</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E45" s="17" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F45" s="17" t="inlineStr">
         <is>
-          <t>customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration</t>
         </is>
       </c>
       <c r="G45" s="17" t="inlineStr">
         <is>
-          <t>VerificationGate</t>
+          <t>useJourneyStartResume, useMirrorChannel, useWizardDraftActions, useWizardStepNavigation, roleSwitchPurge</t>
         </is>
       </c>
       <c r="H45" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8033,12 +8029,12 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>qnomyQueueStore</t>
+          <t>customerVerificationStore</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>stores/qnomyQueueStore.ts</t>
+          <t>stores/customerVerificationStore.ts</t>
         </is>
       </c>
       <c r="D46" s="21" t="inlineStr">
@@ -8051,13 +8047,17 @@
       </c>
       <c r="F46" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="G46" s="17" t="inlineStr"/>
+          <t>customer360</t>
+        </is>
+      </c>
+      <c r="G46" s="17" t="inlineStr">
+        <is>
+          <t>VerificationGate</t>
+        </is>
+      </c>
       <c r="H46" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -8069,12 +8069,12 @@
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>regionStore</t>
+          <t>qnomyQueueStore</t>
         </is>
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>stores/regionStore.ts</t>
+          <t>stores/qnomyQueueStore.ts</t>
         </is>
       </c>
       <c r="D47" s="21" t="inlineStr">
@@ -8093,7 +8093,7 @@
       <c r="G47" s="17" t="inlineStr"/>
       <c r="H47" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -8105,12 +8105,12 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>sidebarStore</t>
+          <t>regionStore</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>stores/sidebarStore.ts</t>
+          <t>stores/regionStore.ts</t>
         </is>
       </c>
       <c r="D48" s="21" t="inlineStr">
@@ -8129,7 +8129,7 @@
       <c r="G48" s="17" t="inlineStr"/>
       <c r="H48" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -8141,12 +8141,12 @@
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>themeStore</t>
+          <t>sidebarStore</t>
         </is>
       </c>
       <c r="C49" s="17" t="inlineStr">
         <is>
-          <t>stores/themeStore.ts</t>
+          <t>stores/sidebarStore.ts</t>
         </is>
       </c>
       <c r="D49" s="21" t="inlineStr">
@@ -8165,7 +8165,7 @@
       <c r="G49" s="17" t="inlineStr"/>
       <c r="H49" s="17" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8177,67 +8177,63 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>configStore</t>
+          <t>themeStore</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>stores/configStore.ts</t>
-        </is>
-      </c>
-      <c r="D50" s="23" t="inlineStr">
-        <is>
-          <t>App shell only</t>
+          <t>stores/themeStore.ts</t>
+        </is>
+      </c>
+      <c r="D50" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E50" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F50" s="17" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
       <c r="G50" s="17" t="inlineStr"/>
       <c r="H50" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="17" t="inlineStr">
         <is>
-          <t>Hook</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>useEnterToSubmit</t>
+          <t>configStore</t>
         </is>
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>hooks/useEnterToSubmit.ts</t>
-        </is>
-      </c>
-      <c r="D51" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>stores/configStore.ts</t>
+        </is>
+      </c>
+      <c r="D51" s="23" t="inlineStr">
+        <is>
+          <t>App shell only</t>
         </is>
       </c>
       <c r="E51" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="F51" s="17" t="inlineStr">
-        <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
-        </is>
-      </c>
-      <c r="G51" s="17" t="inlineStr">
-        <is>
-          <t>VerificationGate, useIdLookup</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F51" s="17" t="inlineStr"/>
+      <c r="G51" s="17" t="inlineStr"/>
       <c r="H51" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8249,12 +8245,12 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>useSearchListNav</t>
+          <t>useRestrictedCustomers</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>hooks/useSearchListNav.ts</t>
+          <t>hooks/useRestrictedCustomers.ts</t>
         </is>
       </c>
       <c r="D52" s="20" t="inlineStr">
@@ -8263,21 +8259,21 @@
         </is>
       </c>
       <c r="E52" s="17" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F52" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, navigation, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, trouble-ticketing-complaints, navigation, customer360, orders, profile, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G52" s="17" t="inlineStr">
         <is>
-          <t>CompanySearchInput, ContactPhoneInput, PlanSearchBox, LocationInput</t>
+          <t>TicketCreationModal</t>
         </is>
       </c>
       <c r="H52" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -8289,12 +8285,12 @@
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>useAreaOptions</t>
+          <t>useEnterToSubmit</t>
         </is>
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>hooks/useAreaOptions.ts</t>
+          <t>hooks/useEnterToSubmit.ts</t>
         </is>
       </c>
       <c r="D53" s="20" t="inlineStr">
@@ -8303,21 +8299,21 @@
         </is>
       </c>
       <c r="E53" s="17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F53" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G53" s="17" t="inlineStr">
         <is>
-          <t>BillingAccountStep, ZsbAddressStep</t>
+          <t>VerificationGate, useIdLookup</t>
         </is>
       </c>
       <c r="H53" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -8329,12 +8325,12 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>useRestrictedCustomers</t>
+          <t>useSearchListNav</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>hooks/useRestrictedCustomers.ts</t>
+          <t>hooks/useSearchListNav.ts</t>
         </is>
       </c>
       <c r="D54" s="20" t="inlineStr">
@@ -8343,21 +8339,21 @@
         </is>
       </c>
       <c r="E54" s="17" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F54" s="17" t="inlineStr">
         <is>
-          <t>order-management, trouble-ticketing-complaints, customer360, orders, support, tasks, tickets</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, navigation, administration, customer360</t>
         </is>
       </c>
       <c r="G54" s="17" t="inlineStr">
         <is>
-          <t>TicketCreationModal</t>
+          <t>CompanySearchInput, ContactPhoneInput, PlanSearchBox, LocationInput</t>
         </is>
       </c>
       <c r="H54" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -8369,12 +8365,12 @@
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>useSubmit</t>
+          <t>useAreaOptions</t>
         </is>
       </c>
       <c r="C55" s="17" t="inlineStr">
         <is>
-          <t>hooks/useSubmit.ts</t>
+          <t>hooks/useAreaOptions.ts</t>
         </is>
       </c>
       <c r="D55" s="20" t="inlineStr">
@@ -8383,17 +8379,21 @@
         </is>
       </c>
       <c r="E55" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F55" s="17" t="inlineStr">
         <is>
-          <t>lead-management, mnp-fnp-porting, sim-number-management, trouble-ticketing-complaints, customer360, tasks</t>
-        </is>
-      </c>
-      <c r="G55" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G55" s="17" t="inlineStr">
+        <is>
+          <t>BillingAccountStep, ZsbAddressStep</t>
+        </is>
+      </c>
       <c r="H55" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8405,68 +8405,64 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>useMinWidth</t>
+          <t>useSubmit</t>
         </is>
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t>hooks/useMinWidth.ts</t>
-        </is>
-      </c>
-      <c r="D56" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>hooks/useSubmit.ts</t>
+        </is>
+      </c>
+      <c r="D56" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E56" s="17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F56" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
+          <t>lead-management, mnp-fnp-porting, sim-number-management, trouble-ticketing-complaints, customer360, tasks</t>
         </is>
       </c>
       <c r="G56" s="17" t="inlineStr"/>
       <c r="H56" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="17" t="inlineStr">
         <is>
-          <t>Helper</t>
+          <t>Hook</t>
         </is>
       </c>
       <c r="B57" s="17" t="inlineStr">
         <is>
-          <t>statusTone</t>
+          <t>useMinWidth</t>
         </is>
       </c>
       <c r="C57" s="17" t="inlineStr">
         <is>
-          <t>lib/statusTone.ts</t>
-        </is>
-      </c>
-      <c r="D57" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>hooks/useMinWidth.ts</t>
+        </is>
+      </c>
+      <c r="D57" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E57" s="17" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F57" s="17" t="inlineStr">
         <is>
-          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, orders, sales, support, tasks, tickets</t>
-        </is>
-      </c>
-      <c r="G57" s="17" t="inlineStr">
-        <is>
-          <t>ruleEngine</t>
-        </is>
-      </c>
+          <t>navigation</t>
+        </is>
+      </c>
+      <c r="G57" s="17" t="inlineStr"/>
       <c r="H57" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
@@ -8481,12 +8477,12 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>format</t>
+          <t>statusTone</t>
         </is>
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t>lib/format.ts</t>
+          <t>lib/statusTone.ts</t>
         </is>
       </c>
       <c r="D58" s="20" t="inlineStr">
@@ -8495,21 +8491,21 @@
         </is>
       </c>
       <c r="E58" s="17" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F58" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, tasks</t>
+          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, orders, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G58" s="17" t="inlineStr">
         <is>
-          <t>AdditionalDocumentsUpload, CafDocumentUpload, MsisdnPicker, GuidedContactStep, IdLookupStep, postpaidPlanModel, StepSummaryPanel, stepSummary, customer360Engine, postpaidPricing</t>
+          <t>ruleEngine</t>
         </is>
       </c>
       <c r="H58" s="17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8517,12 @@
       </c>
       <c r="B59" s="17" t="inlineStr">
         <is>
-          <t>buildEnv</t>
+          <t>format</t>
         </is>
       </c>
       <c r="C59" s="17" t="inlineStr">
         <is>
-          <t>lib/buildEnv.ts</t>
+          <t>lib/format.ts</t>
         </is>
       </c>
       <c r="D59" s="20" t="inlineStr">
@@ -8535,21 +8531,21 @@
         </is>
       </c>
       <c r="E59" s="17" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F59" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, tasks</t>
         </is>
       </c>
       <c r="G59" s="17" t="inlineStr">
         <is>
-          <t>syntheticMarker, navigationEngine</t>
+          <t>AdditionalDocumentsUpload, CafDocumentUpload, MsisdnPicker, GuidedContactStep, IdLookupStep, postpaidPlanModel, StepSummaryPanel, stepSummary, customer360Engine, postpaidPricing</t>
         </is>
       </c>
       <c r="H59" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -8561,12 +8557,12 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>deviceType</t>
+          <t>buildEnv</t>
         </is>
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t>lib/deviceType.ts</t>
+          <t>lib/buildEnv.ts</t>
         </is>
       </c>
       <c r="D60" s="20" t="inlineStr">
@@ -8575,21 +8571,21 @@
         </is>
       </c>
       <c r="E60" s="17" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F60" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360</t>
         </is>
       </c>
       <c r="G60" s="17" t="inlineStr">
         <is>
-          <t>IdFileUpload, PassportScanSections, SimSerialScanner, SimTypeStep, cafTypes</t>
+          <t>syntheticMarker, navigationEngine</t>
         </is>
       </c>
       <c r="H60" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -8601,12 +8597,12 @@
       </c>
       <c r="B61" s="17" t="inlineStr">
         <is>
-          <t>taskId</t>
+          <t>deviceType</t>
         </is>
       </c>
       <c r="C61" s="17" t="inlineStr">
         <is>
-          <t>lib/taskId.ts</t>
+          <t>lib/deviceType.ts</t>
         </is>
       </c>
       <c r="D61" s="20" t="inlineStr">
@@ -8615,16 +8611,16 @@
         </is>
       </c>
       <c r="E61" s="17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F61" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration, customer360</t>
         </is>
       </c>
       <c r="G61" s="17" t="inlineStr">
         <is>
-          <t>useWizardDraftActions</t>
+          <t>IdFileUpload, PassportScanSections, SimSerialScanner, SimTypeStep, cafTypes</t>
         </is>
       </c>
       <c r="H61" s="17" t="inlineStr">
@@ -8641,12 +8637,12 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>connectionType</t>
+          <t>taskId</t>
         </is>
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t>lib/connectionType.ts</t>
+          <t>lib/taskId.ts</t>
         </is>
       </c>
       <c r="D62" s="20" t="inlineStr">
@@ -8655,21 +8651,21 @@
         </is>
       </c>
       <c r="E62" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F62" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G62" s="17" t="inlineStr">
         <is>
-          <t>ConnectionTypeTag</t>
+          <t>useWizardDraftActions</t>
         </is>
       </c>
       <c r="H62" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8681,12 +8677,12 @@
       </c>
       <c r="B63" s="17" t="inlineStr">
         <is>
-          <t>serviceTypeTag</t>
+          <t>connectionType</t>
         </is>
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>lib/serviceTypeTag.ts</t>
+          <t>lib/connectionType.ts</t>
         </is>
       </c>
       <c r="D63" s="20" t="inlineStr">
@@ -8704,7 +8700,7 @@
       </c>
       <c r="G63" s="17" t="inlineStr">
         <is>
-          <t>ServiceTypeTag</t>
+          <t>ConnectionTypeTag</t>
         </is>
       </c>
       <c r="H63" s="17" t="inlineStr">
@@ -8721,31 +8717,35 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>screenName</t>
+          <t>serviceTypeTag</t>
         </is>
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
-          <t>lib/screenName.ts</t>
-        </is>
-      </c>
-      <c r="D64" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>lib/serviceTypeTag.ts</t>
+        </is>
+      </c>
+      <c r="D64" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E64" s="17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F64" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="G64" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G64" s="17" t="inlineStr">
+        <is>
+          <t>ServiceTypeTag</t>
+        </is>
+      </c>
       <c r="H64" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -8757,12 +8757,12 @@
       </c>
       <c r="B65" s="17" t="inlineStr">
         <is>
-          <t>values</t>
+          <t>screenName</t>
         </is>
       </c>
       <c r="C65" s="17" t="inlineStr">
         <is>
-          <t>lib/values.ts</t>
+          <t>lib/screenName.ts</t>
         </is>
       </c>
       <c r="D65" s="21" t="inlineStr">
@@ -8775,22 +8775,58 @@
       </c>
       <c r="F65" s="17" t="inlineStr">
         <is>
+          <t>navigation</t>
+        </is>
+      </c>
+      <c r="G65" s="17" t="inlineStr"/>
+      <c r="H65" s="17" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="17" t="inlineStr">
+        <is>
+          <t>Helper</t>
+        </is>
+      </c>
+      <c r="B66" s="17" t="inlineStr">
+        <is>
+          <t>values</t>
+        </is>
+      </c>
+      <c r="C66" s="17" t="inlineStr">
+        <is>
+          <t>lib/values.ts</t>
+        </is>
+      </c>
+      <c r="D66" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
+        </is>
+      </c>
+      <c r="E66" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" s="17" t="inlineStr">
+        <is>
           <t>customer360</t>
         </is>
       </c>
-      <c r="G65" s="17" t="inlineStr">
+      <c r="G66" s="17" t="inlineStr">
         <is>
           <t>customer360Demo</t>
         </is>
       </c>
-      <c r="H65" s="17" t="inlineStr">
+      <c r="H66" s="17" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H65"/>
+  <autoFilter ref="A1:H66"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
+++ b/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'UI Components'!$A$1:$H$119</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Shared Code'!$A$1:$H$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Shared Code'!$A$1:$H$68</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -763,13 +763,13 @@
         </is>
       </c>
       <c r="C9" s="17" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D9" s="17" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F9" s="17" t="n">
         <v>2</v>
@@ -855,17 +855,17 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>118 UI components + 65 non-UI files</t>
+          <t>118 UI components + 67 non-UI files</t>
         </is>
       </c>
       <c r="C13" s="18" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E13" s="18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F13" s="18" t="n">
         <v>5</v>
@@ -6286,7 +6286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.50" customWidth="1" min="1" max="1"/>
@@ -6372,7 +6372,7 @@
       </c>
       <c r="G2" s="17" t="inlineStr">
         <is>
-          <t>CompanySearchInput, ContactPhoneInput, CpeSerialScanner, MsisdnPicker, SimSerialScanner, AppointmentBookingStep, BillingAccountAutoResolver, BillingAccountStep, CafSignatureCapture, CafTerms, FixedPlanStep, PrepaidCartStep, PrepaidCheckoutStep, PrepaidPlanStep, TicketCreationModal, ZsbAddressStep, lineSelectionModel, useCheckoutSummary, useIdLookup, usePostpaidPlanAddons, StepSummaryPanel, stepSummary, useJourneyStartResume, useWizardDraftActions, LocationInput, activityEngine, agentProfileEngine, businessAccountEngine, connectionEligibility, customer360Engine, fibreServiceability, roleSwitchPurge, serviceLocationLookup, useAreaOptions, useRestrictedCustomers, configStore, entityStore</t>
+          <t>CompanySearchInput, ContactPhoneInput, CpeSerialScanner, MsisdnPicker, SimSerialScanner, AppointmentBookingStep, BillingAccountAutoResolver, BillingAccountStep, CafSignatureCapture, CafTerms, FixedPlanStep, PrepaidCartStep, PrepaidCheckoutStep, PrepaidPlanStep, TicketCreationModal, ZsbAddressStep, lineSelectionModel, useCheckoutSummary, useIdLookup, usePostpaidPlanAddons, StepSummaryPanel, stepSummary, useJourneyStartResume, useWizardDraftActions, LocationInput, activityEngine, agentProfileEngine, businessAccountEngine, connectionEligibility, customer360Engine, customerChangeAudit, fibreServiceability, qnomyWalkIns, roleSwitchPurge, serviceLocationLookup, useAreaOptions, useRestrictedCustomers, configStore, entityStore</t>
         </is>
       </c>
       <c r="H2" s="17" t="inlineStr">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t>agentPrivilegeEngine</t>
+          <t>customerChangeAudit</t>
         </is>
       </c>
       <c r="C4" s="17" t="inlineStr">
         <is>
-          <t>engines/agentPrivilegeEngine.ts</t>
+          <t>engines/customerChangeAudit.ts</t>
         </is>
       </c>
       <c r="D4" s="20" t="inlineStr">
@@ -6443,21 +6443,21 @@
         </is>
       </c>
       <c r="E4" s="17" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F4" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, support, tasks, tickets</t>
+          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G4" s="17" t="inlineStr">
         <is>
-          <t>TicketCreationModal, useIdLookup, roleSwitchPurge, useRestrictedCustomers</t>
+          <t>entityStore</t>
         </is>
       </c>
       <c r="H4" s="17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -6469,12 +6469,12 @@
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>hrnConfiguration</t>
+          <t>agentPrivilegeEngine</t>
         </is>
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>engines/hrnConfiguration.ts</t>
+          <t>engines/agentPrivilegeEngine.ts</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -6483,16 +6483,16 @@
         </is>
       </c>
       <c r="E5" s="17" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, support</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G5" s="17" t="inlineStr">
         <is>
-          <t>eligibilityRowsModel, CreditLimitCard, PostpaidPlanAddonsStep, useCheckoutSummary, creditLimit, ruleEngine</t>
+          <t>TicketCreationModal, useIdLookup, qnomyWalkIns, roleSwitchPurge, useRestrictedCustomers</t>
         </is>
       </c>
       <c r="H5" s="17" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>restrictedCustomers</t>
+          <t>hrnConfiguration</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>engines/restrictedCustomers.ts</t>
+          <t>engines/hrnConfiguration.ts</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, trouble-ticketing-complaints, navigation, customer360, orders, profile, support, tasks, tickets</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, support</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
         <is>
-          <t>useRestrictedCustomers</t>
+          <t>eligibilityRowsModel, CreditLimitCard, PostpaidPlanAddonsStep, useCheckoutSummary, creditLimit, ruleEngine</t>
         </is>
       </c>
       <c r="H6" s="17" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>ruleEngine</t>
+          <t>restrictedCustomers</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>engines/ruleEngine.ts</t>
+          <t>engines/restrictedCustomers.ts</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, support</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, trouble-ticketing-complaints, navigation, customer360, orders, profile, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G7" s="17" t="inlineStr">
         <is>
-          <t>BillLimitEditor, CreditCheckPanel, eligibilityRowsModel, FixedPlanStep, TicketCreationModal</t>
+          <t>useRestrictedCustomers</t>
         </is>
       </c>
       <c r="H7" s="17" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>billingBalance</t>
+          <t>ruleEngine</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>engines/billingBalance.ts</t>
+          <t>engines/ruleEngine.ts</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -6603,21 +6603,21 @@
         </is>
       </c>
       <c r="E8" s="17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, product-lines, navigation, administration, customer-search, customer360, orders</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, support</t>
         </is>
       </c>
       <c r="G8" s="17" t="inlineStr">
         <is>
-          <t>customer360Demo, customer360Engine</t>
+          <t>BillLimitEditor, CreditCheckPanel, eligibilityRowsModel, FixedPlanStep, TicketCreationModal</t>
         </is>
       </c>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -6629,12 +6629,12 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>customer360Engine</t>
+          <t>billingBalance</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>engines/customer360Engine.ts</t>
+          <t>engines/billingBalance.ts</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -6652,12 +6652,12 @@
       </c>
       <c r="G9" s="17" t="inlineStr">
         <is>
-          <t>customer360Demo, customerServicesEngine</t>
+          <t>customer360Demo, customer360Engine</t>
         </is>
       </c>
       <c r="H9" s="17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>customerServicesEngine</t>
+          <t>customer360Engine</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>engines/customerServicesEngine.ts</t>
+          <t>engines/customer360Engine.ts</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="G10" s="17" t="inlineStr">
         <is>
-          <t>lineSelectionModel, customer360Demo, connectionEligibility, customer360Engine</t>
+          <t>customer360Demo, customerServicesEngine</t>
         </is>
       </c>
       <c r="H10" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -6709,12 +6709,12 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>serviceCall</t>
+          <t>customerServicesEngine</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>engines/serviceCall.ts</t>
+          <t>engines/customerServicesEngine.ts</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -6723,21 +6723,21 @@
         </is>
       </c>
       <c r="E11" s="17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, product-lines, navigation, administration, customer-search, customer360, orders</t>
         </is>
       </c>
       <c r="G11" s="17" t="inlineStr">
         <is>
-          <t>DemoFaultPanel, ValidationStatus, useIdLookup</t>
+          <t>lineSelectionModel, customer360Demo, connectionEligibility, customer360Engine</t>
         </is>
       </c>
       <c r="H11" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6749,12 +6749,12 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>eligibilityEngine</t>
+          <t>serviceCall</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>engines/eligibilityEngine.ts</t>
+          <t>engines/serviceCall.ts</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -6763,21 +6763,21 @@
         </is>
       </c>
       <c r="E12" s="17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G12" s="17" t="inlineStr">
         <is>
-          <t>eligibilityRowsModel, eligibilityTypes, useIdLookup</t>
+          <t>DemoFaultPanel, ValidationStatus, useIdLookup</t>
         </is>
       </c>
       <c r="H12" s="17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -6789,12 +6789,12 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>milestoneEngine</t>
+          <t>eligibilityEngine</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>engines/milestoneEngine.ts</t>
+          <t>engines/eligibilityEngine.ts</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -6812,12 +6812,12 @@
       </c>
       <c r="G13" s="17" t="inlineStr">
         <is>
-          <t>guidedWizardTypes, useJourneyMilestones</t>
+          <t>eligibilityRowsModel, eligibilityTypes, useIdLookup</t>
         </is>
       </c>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -6829,12 +6829,12 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>activityEngine</t>
+          <t>milestoneEngine</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>engines/activityEngine.ts</t>
+          <t>engines/milestoneEngine.ts</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -6843,16 +6843,16 @@
         </is>
       </c>
       <c r="E14" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G14" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen, useWizardDraftActions</t>
+          <t>guidedWizardTypes, useJourneyMilestones</t>
         </is>
       </c>
       <c r="H14" s="17" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>businessSegment</t>
+          <t>activityEngine</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>engines/businessSegment.ts</t>
+          <t>engines/activityEngine.ts</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, navigation, administration, customer-search, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G15" s="17" t="inlineStr">
         <is>
-          <t>BillingAccountStep, customer360Demo, businessAccountEngine</t>
+          <t>ActivationCompleteScreen, useWizardDraftActions</t>
         </is>
       </c>
       <c r="H15" s="17" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>creditLimit</t>
+          <t>businessSegment</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>engines/creditLimit.ts</t>
+          <t>engines/businessSegment.ts</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -6927,17 +6927,17 @@
       </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, navigation, administration, customer-search, customer360</t>
         </is>
       </c>
       <c r="G16" s="17" t="inlineStr">
         <is>
-          <t>CreditLimitCard, billingAccountModel</t>
+          <t>BillingAccountStep, customer360Demo, businessAccountEngine</t>
         </is>
       </c>
       <c r="H16" s="17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -6949,12 +6949,12 @@
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>postpaidPricing</t>
+          <t>creditLimit</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>engines/postpaidPricing.ts</t>
+          <t>engines/creditLimit.ts</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="F17" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, administration, customer360</t>
         </is>
       </c>
       <c r="G17" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, CheckoutDefaultLayout, PostpaidMonthlySummary, checkoutDetailedTables, checkoutSummaryRows, useCheckoutSummary, usePostpaidPlanAddons</t>
+          <t>CreditLimitCard, billingAccountModel</t>
         </is>
       </c>
       <c r="H17" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>connectionEligibility</t>
+          <t>postpaidPricing</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>engines/connectionEligibility.ts</t>
+          <t>engines/postpaidPricing.ts</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -7003,17 +7003,21 @@
         </is>
       </c>
       <c r="E18" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
-        </is>
-      </c>
-      <c r="G18" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+      <c r="G18" s="17" t="inlineStr">
+        <is>
+          <t>MsisdnPicker, CheckoutDefaultLayout, PostpaidMonthlySummary, checkoutDetailedTables, checkoutSummaryRows, useCheckoutSummary, usePostpaidPlanAddons</t>
+        </is>
+      </c>
       <c r="H18" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -7025,12 +7029,12 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>customerBenefitEngine</t>
+          <t>connectionEligibility</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>engines/customerBenefitEngine.ts</t>
+          <t>engines/connectionEligibility.ts</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -7046,14 +7050,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
         </is>
       </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>PostpaidPlanAddonsStep, usePostpaidPlanAddons</t>
-        </is>
-      </c>
+      <c r="G19" s="17" t="inlineStr"/>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -7065,12 +7065,12 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>addonEligibility</t>
+          <t>customerBenefitEngine</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>engines/addonEligibility.ts</t>
+          <t>engines/customerBenefitEngine.ts</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -7079,17 +7079,21 @@
         </is>
       </c>
       <c r="E20" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F20" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G20" s="17" t="inlineStr">
+        <is>
+          <t>PostpaidPlanAddonsStep, usePostpaidPlanAddons</t>
+        </is>
+      </c>
       <c r="H20" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7101,12 +7105,12 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>fibreServiceability</t>
+          <t>addonEligibility</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>engines/fibreServiceability.ts</t>
+          <t>engines/addonEligibility.ts</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -7122,11 +7126,7 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>FibreReadinessBanner, ActivationCompleteScreen</t>
-        </is>
-      </c>
+      <c r="G21" s="17" t="inlineStr"/>
       <c r="H21" s="17" t="inlineStr">
         <is>
           <t>2026-10-05</t>
@@ -7141,12 +7141,12 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>personaEngine</t>
+          <t>fibreServiceability</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>engines/personaEngine.ts</t>
+          <t>engines/fibreServiceability.ts</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -7159,17 +7159,17 @@
       </c>
       <c r="F22" s="17" t="inlineStr">
         <is>
-          <t>dashboard, order-management, product-lines, sim-number-management, navigation, administration, customer360, orders, profile</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
-          <t>approvalAuthority, navigationEngine</t>
+          <t>FibreReadinessBanner, ActivationCompleteScreen</t>
         </is>
       </c>
       <c r="H22" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -7181,12 +7181,12 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>eligibilityGuard</t>
+          <t>personaEngine</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>engines/eligibilityGuard.ts</t>
+          <t>engines/personaEngine.ts</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -7195,17 +7195,21 @@
         </is>
       </c>
       <c r="E23" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F23" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr"/>
+          <t>dashboard, order-management, product-lines, sim-number-management, navigation, administration, customer360, orders, profile</t>
+        </is>
+      </c>
+      <c r="G23" s="17" t="inlineStr">
+        <is>
+          <t>approvalAuthority, navigationEngine</t>
+        </is>
+      </c>
       <c r="H23" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7221,12 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>serviceLocationLookup</t>
+          <t>eligibilityGuard</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>engines/serviceLocationLookup.ts</t>
+          <t>engines/eligibilityGuard.ts</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -7235,14 +7239,10 @@
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G24" s="17" t="inlineStr">
-        <is>
-          <t>ZsbAddressStep</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration</t>
+        </is>
+      </c>
+      <c r="G24" s="17" t="inlineStr"/>
       <c r="H24" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
@@ -7257,12 +7257,12 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>agentTaskEngine</t>
+          <t>serviceLocationLookup</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>engines/agentTaskEngine.ts</t>
+          <t>engines/serviceLocationLookup.ts</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -7271,17 +7271,21 @@
         </is>
       </c>
       <c r="E25" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F25" s="17" t="inlineStr">
         <is>
-          <t>dashboard, order-management, trouble-ticketing-complaints, orders, support, tasks</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="inlineStr">
+        <is>
+          <t>ZsbAddressStep</t>
+        </is>
+      </c>
       <c r="H25" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7293,12 +7297,12 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>approvalAuthority</t>
+          <t>agentTaskEngine</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>engines/approvalAuthority.ts</t>
+          <t>engines/agentTaskEngine.ts</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -7311,13 +7315,13 @@
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>dashboard, order-management, sim-number-management, navigation, customer360, orders</t>
+          <t>dashboard, order-management, trouble-ticketing-complaints, orders, support, tasks</t>
         </is>
       </c>
       <c r="G26" s="17" t="inlineStr"/>
       <c r="H26" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7333,12 @@
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>portInEngine</t>
+          <t>approvalAuthority</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
-          <t>engines/portInEngine.ts</t>
+          <t>engines/approvalAuthority.ts</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -7347,13 +7351,13 @@
       </c>
       <c r="F27" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
+          <t>dashboard, order-management, sim-number-management, navigation, customer360, orders</t>
         </is>
       </c>
       <c r="G27" s="17" t="inlineStr"/>
       <c r="H27" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7365,12 +7369,12 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>csvExport</t>
+          <t>portInEngine</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>engines/csvExport.ts</t>
+          <t>engines/portInEngine.ts</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -7379,17 +7383,17 @@
         </is>
       </c>
       <c r="E28" s="17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>trouble-ticketing-complaints, customer360, profile, support</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
         </is>
       </c>
       <c r="G28" s="17" t="inlineStr"/>
       <c r="H28" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7401,12 +7405,12 @@
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>bellNotificationExpiry</t>
+          <t>csvExport</t>
         </is>
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>engines/bellNotificationExpiry.ts</t>
+          <t>engines/csvExport.ts</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -7415,11 +7419,11 @@
         </is>
       </c>
       <c r="E29" s="17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F29" s="17" t="inlineStr">
         <is>
-          <t>administration, customer360</t>
+          <t>trouble-ticketing-complaints, customer360, profile, support</t>
         </is>
       </c>
       <c r="G29" s="17" t="inlineStr"/>
@@ -7437,12 +7441,12 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>businessAccountEngine</t>
+          <t>bellNotificationExpiry</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>engines/businessAccountEngine.ts</t>
+          <t>engines/bellNotificationExpiry.ts</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -7455,13 +7459,13 @@
       </c>
       <c r="F30" s="17" t="inlineStr">
         <is>
-          <t>customer-search, customer360</t>
+          <t>administration, customer360</t>
         </is>
       </c>
       <c r="G30" s="17" t="inlineStr"/>
       <c r="H30" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7473,12 +7477,12 @@
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>navigationEngine</t>
+          <t>businessAccountEngine</t>
         </is>
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>engines/navigationEngine.ts</t>
+          <t>engines/businessAccountEngine.ts</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -7491,13 +7495,13 @@
       </c>
       <c r="F31" s="17" t="inlineStr">
         <is>
-          <t>navigation, customer360</t>
+          <t>customer-search, customer360</t>
         </is>
       </c>
       <c r="G31" s="17" t="inlineStr"/>
       <c r="H31" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -7509,12 +7513,12 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>qnomyQueueEngine</t>
+          <t>navigationEngine</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>engines/qnomyQueueEngine.ts</t>
+          <t>engines/navigationEngine.ts</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -7527,13 +7531,13 @@
       </c>
       <c r="F32" s="17" t="inlineStr">
         <is>
-          <t>navigation, tickets</t>
+          <t>navigation, customer360</t>
         </is>
       </c>
       <c r="G32" s="17" t="inlineStr"/>
       <c r="H32" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -7545,31 +7549,35 @@
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>agentProfileEngine</t>
+          <t>qnomyQueueEngine</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>engines/agentProfileEngine.ts</t>
-        </is>
-      </c>
-      <c r="D33" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>engines/qnomyQueueEngine.ts</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E33" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="G33" s="17" t="inlineStr"/>
+          <t>navigation, tickets</t>
+        </is>
+      </c>
+      <c r="G33" s="17" t="inlineStr">
+        <is>
+          <t>qnomyWalkIns</t>
+        </is>
+      </c>
       <c r="H33" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7589,12 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>customer360VisibilityEngine</t>
+          <t>agentProfileEngine</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>engines/customer360VisibilityEngine.ts</t>
+          <t>engines/agentProfileEngine.ts</t>
         </is>
       </c>
       <c r="D34" s="21" t="inlineStr">
@@ -7599,13 +7607,13 @@
       </c>
       <c r="F34" s="17" t="inlineStr">
         <is>
-          <t>customer360</t>
+          <t>navigation</t>
         </is>
       </c>
       <c r="G34" s="17" t="inlineStr"/>
       <c r="H34" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7617,12 +7625,12 @@
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>profileChangeTicket</t>
+          <t>customer360VisibilityEngine</t>
         </is>
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
-          <t>engines/profileChangeTicket.ts</t>
+          <t>engines/customer360VisibilityEngine.ts</t>
         </is>
       </c>
       <c r="D35" s="21" t="inlineStr">
@@ -7641,7 +7649,7 @@
       <c r="G35" s="17" t="inlineStr"/>
       <c r="H35" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7653,12 +7661,12 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>roleSwitchPurge</t>
+          <t>profileChangeTicket</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>engines/roleSwitchPurge.ts</t>
+          <t>engines/profileChangeTicket.ts</t>
         </is>
       </c>
       <c r="D36" s="21" t="inlineStr">
@@ -7671,13 +7679,13 @@
       </c>
       <c r="F36" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
+          <t>customer360</t>
         </is>
       </c>
       <c r="G36" s="17" t="inlineStr"/>
       <c r="H36" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -7689,12 +7697,12 @@
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>searchScopeEngine</t>
+          <t>qnomyWalkIns</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>engines/searchScopeEngine.ts</t>
+          <t>engines/qnomyWalkIns.ts</t>
         </is>
       </c>
       <c r="D37" s="21" t="inlineStr">
@@ -7713,7 +7721,7 @@
       <c r="G37" s="17" t="inlineStr"/>
       <c r="H37" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>uncommitted</t>
         </is>
       </c>
     </row>
@@ -7725,27 +7733,31 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>moduleDescriptions</t>
+          <t>roleSwitchPurge</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>engines/moduleDescriptions.ts</t>
-        </is>
-      </c>
-      <c r="D38" s="23" t="inlineStr">
-        <is>
-          <t>App shell only</t>
+          <t>engines/roleSwitchPurge.ts</t>
+        </is>
+      </c>
+      <c r="D38" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E38" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F38" s="17" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
       <c r="G38" s="17" t="inlineStr"/>
       <c r="H38" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -7757,107 +7769,95 @@
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>screenGrouping</t>
+          <t>searchScopeEngine</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>engines/screenGrouping.ts</t>
-        </is>
-      </c>
-      <c r="D39" s="23" t="inlineStr">
-        <is>
-          <t>App shell only</t>
+          <t>engines/searchScopeEngine.ts</t>
+        </is>
+      </c>
+      <c r="D39" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E39" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F39" s="17" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
       <c r="G39" s="17" t="inlineStr"/>
       <c r="H39" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="17" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Engine</t>
         </is>
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>entityStore</t>
+          <t>moduleDescriptions</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>stores/entityStore.ts</t>
-        </is>
-      </c>
-      <c r="D40" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>engines/moduleDescriptions.ts</t>
+        </is>
+      </c>
+      <c r="D40" s="23" t="inlineStr">
+        <is>
+          <t>App shell only</t>
         </is>
       </c>
       <c r="E40" s="17" t="n">
-        <v>24</v>
-      </c>
-      <c r="F40" s="17" t="inlineStr">
-        <is>
-          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, sales, support, tasks, tickets</t>
-        </is>
-      </c>
-      <c r="G40" s="17" t="inlineStr">
-        <is>
-          <t>ActivationCompleteScreen, DonorAttachmentStep, DonorDetailsStep, useDraftStepSync, useWizardDraftActions, activityEngine, bellNotificationExpiry, profileChangeTicket</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F40" s="17" t="inlineStr"/>
+      <c r="G40" s="17" t="inlineStr"/>
       <c r="H40" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Engine</t>
         </is>
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>customerContextStore</t>
+          <t>screenGrouping</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>stores/customerContextStore.ts</t>
-        </is>
-      </c>
-      <c r="D41" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>engines/screenGrouping.ts</t>
+        </is>
+      </c>
+      <c r="D41" s="23" t="inlineStr">
+        <is>
+          <t>App shell only</t>
         </is>
       </c>
       <c r="E41" s="17" t="n">
-        <v>23</v>
-      </c>
-      <c r="F41" s="17" t="inlineStr">
-        <is>
-          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
-        </is>
-      </c>
-      <c r="G41" s="17" t="inlineStr">
-        <is>
-          <t>ActivationCompleteScreen, useActedForCustomer, useWizardDraftActions, roleSwitchPurge, authStore</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F41" s="17" t="inlineStr"/>
+      <c r="G41" s="17" t="inlineStr"/>
       <c r="H41" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7869,12 +7869,12 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>personaStore</t>
+          <t>customerContextStore</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>stores/personaStore.ts</t>
+          <t>stores/customerContextStore.ts</t>
         </is>
       </c>
       <c r="D42" s="20" t="inlineStr">
@@ -7883,21 +7883,21 @@
         </is>
       </c>
       <c r="E42" s="17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F42" s="17" t="inlineStr">
         <is>
-          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, support, tasks, tickets</t>
+          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G42" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, eligibilityRowsModel, ActivationCompleteScreen, AppointmentBookingStep, PostpaidPlanAddonsStep, TicketCreationModal, useCheckoutSummary, useIdLookup, useRestrictedCustomers, configStore</t>
+          <t>ActivationCompleteScreen, useActedForCustomer, useWizardDraftActions, roleSwitchPurge, authStore</t>
         </is>
       </c>
       <c r="H42" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -7923,16 +7923,16 @@
         </is>
       </c>
       <c r="E43" s="17" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F43" s="17" t="inlineStr">
         <is>
-          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, support, tasks, tickets</t>
+          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G43" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, ActivationCompleteScreen, useWizardDraftActions, activityEngine, agentProfileEngine, profileChangeTicket, configStore</t>
+          <t>MsisdnPicker, ActivationCompleteScreen, useWizardDraftActions, activityEngine, agentProfileEngine, profileChangeTicket, configStore, entityStore</t>
         </is>
       </c>
       <c r="H43" s="17" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>notificationStore</t>
+          <t>entityStore</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>stores/notificationStore.ts</t>
+          <t>stores/entityStore.ts</t>
         </is>
       </c>
       <c r="D44" s="20" t="inlineStr">
@@ -7963,21 +7963,21 @@
         </is>
       </c>
       <c r="E44" s="17" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F44" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, profile, support, tasks</t>
+          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G44" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, ActivationCompleteScreen, TicketCreationModal, useJourneyMilestones, useWizardDraftActions, useWizardStepNavigation, profileChangeTicket, roleSwitchPurge, useSubmit</t>
+          <t>ActivationCompleteScreen, DonorAttachmentStep, DonorDetailsStep, useIdLookup, useDraftStepSync, useWizardDraftActions, activityEngine, bellNotificationExpiry, profileChangeTicket</t>
         </is>
       </c>
       <c r="H44" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -7989,12 +7989,12 @@
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>workflowStore</t>
+          <t>personaStore</t>
         </is>
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>stores/workflowStore.ts</t>
+          <t>stores/personaStore.ts</t>
         </is>
       </c>
       <c r="D45" s="20" t="inlineStr">
@@ -8003,16 +8003,16 @@
         </is>
       </c>
       <c r="E45" s="17" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F45" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration</t>
+          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G45" s="17" t="inlineStr">
         <is>
-          <t>useJourneyStartResume, useMirrorChannel, useWizardDraftActions, useWizardStepNavigation, roleSwitchPurge</t>
+          <t>MsisdnPicker, eligibilityRowsModel, ActivationCompleteScreen, AppointmentBookingStep, PostpaidPlanAddonsStep, TicketCreationModal, useCheckoutSummary, useIdLookup, useRestrictedCustomers, configStore</t>
         </is>
       </c>
       <c r="H45" s="17" t="inlineStr">
@@ -8029,35 +8029,35 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>customerVerificationStore</t>
+          <t>notificationStore</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>stores/customerVerificationStore.ts</t>
-        </is>
-      </c>
-      <c r="D46" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>stores/notificationStore.ts</t>
+        </is>
+      </c>
+      <c r="D46" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E46" s="17" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F46" s="17" t="inlineStr">
         <is>
-          <t>customer360</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, profile, support, tasks</t>
         </is>
       </c>
       <c r="G46" s="17" t="inlineStr">
         <is>
-          <t>VerificationGate</t>
+          <t>MsisdnPicker, ActivationCompleteScreen, TicketCreationModal, useJourneyMilestones, useWizardDraftActions, useWizardStepNavigation, profileChangeTicket, roleSwitchPurge, useSubmit</t>
         </is>
       </c>
       <c r="H46" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -8069,31 +8069,35 @@
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>qnomyQueueStore</t>
+          <t>workflowStore</t>
         </is>
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>stores/qnomyQueueStore.ts</t>
-        </is>
-      </c>
-      <c r="D47" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>stores/workflowStore.ts</t>
+        </is>
+      </c>
+      <c r="D47" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E47" s="17" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F47" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="G47" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration</t>
+        </is>
+      </c>
+      <c r="G47" s="17" t="inlineStr">
+        <is>
+          <t>useJourneyStartResume, useMirrorChannel, useWizardDraftActions, useWizardStepNavigation, roleSwitchPurge</t>
+        </is>
+      </c>
       <c r="H47" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8105,12 +8109,12 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>regionStore</t>
+          <t>customerVerificationStore</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>stores/regionStore.ts</t>
+          <t>stores/customerVerificationStore.ts</t>
         </is>
       </c>
       <c r="D48" s="21" t="inlineStr">
@@ -8123,10 +8127,14 @@
       </c>
       <c r="F48" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="G48" s="17" t="inlineStr"/>
+          <t>customer360</t>
+        </is>
+      </c>
+      <c r="G48" s="17" t="inlineStr">
+        <is>
+          <t>VerificationGate</t>
+        </is>
+      </c>
       <c r="H48" s="17" t="inlineStr">
         <is>
           <t>2026-09-24</t>
@@ -8141,12 +8149,12 @@
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>sidebarStore</t>
+          <t>qnomyQueueStore</t>
         </is>
       </c>
       <c r="C49" s="17" t="inlineStr">
         <is>
-          <t>stores/sidebarStore.ts</t>
+          <t>stores/qnomyQueueStore.ts</t>
         </is>
       </c>
       <c r="D49" s="21" t="inlineStr">
@@ -8165,7 +8173,7 @@
       <c r="G49" s="17" t="inlineStr"/>
       <c r="H49" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -8177,12 +8185,12 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>themeStore</t>
+          <t>regionStore</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>stores/themeStore.ts</t>
+          <t>stores/regionStore.ts</t>
         </is>
       </c>
       <c r="D50" s="21" t="inlineStr">
@@ -8201,7 +8209,7 @@
       <c r="G50" s="17" t="inlineStr"/>
       <c r="H50" s="17" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -8213,23 +8221,27 @@
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>configStore</t>
+          <t>sidebarStore</t>
         </is>
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>stores/configStore.ts</t>
-        </is>
-      </c>
-      <c r="D51" s="23" t="inlineStr">
-        <is>
-          <t>App shell only</t>
+          <t>stores/sidebarStore.ts</t>
+        </is>
+      </c>
+      <c r="D51" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E51" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F51" s="17" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
       <c r="G51" s="17" t="inlineStr"/>
       <c r="H51" s="17" t="inlineStr">
         <is>
@@ -8240,80 +8252,68 @@
     <row r="52">
       <c r="A52" s="17" t="inlineStr">
         <is>
-          <t>Hook</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>useRestrictedCustomers</t>
+          <t>themeStore</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>hooks/useRestrictedCustomers.ts</t>
-        </is>
-      </c>
-      <c r="D52" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>stores/themeStore.ts</t>
+        </is>
+      </c>
+      <c r="D52" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E52" s="17" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F52" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, trouble-ticketing-complaints, navigation, customer360, orders, profile, support, tasks, tickets</t>
-        </is>
-      </c>
-      <c r="G52" s="17" t="inlineStr">
-        <is>
-          <t>TicketCreationModal</t>
-        </is>
-      </c>
+          <t>navigation</t>
+        </is>
+      </c>
+      <c r="G52" s="17" t="inlineStr"/>
       <c r="H52" s="17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="17" t="inlineStr">
         <is>
-          <t>Hook</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>useEnterToSubmit</t>
+          <t>configStore</t>
         </is>
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>hooks/useEnterToSubmit.ts</t>
-        </is>
-      </c>
-      <c r="D53" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>stores/configStore.ts</t>
+        </is>
+      </c>
+      <c r="D53" s="23" t="inlineStr">
+        <is>
+          <t>App shell only</t>
         </is>
       </c>
       <c r="E53" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="F53" s="17" t="inlineStr">
-        <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
-        </is>
-      </c>
-      <c r="G53" s="17" t="inlineStr">
-        <is>
-          <t>VerificationGate, useIdLookup</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F53" s="17" t="inlineStr"/>
+      <c r="G53" s="17" t="inlineStr"/>
       <c r="H53" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8325,12 +8325,12 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>useSearchListNav</t>
+          <t>useRestrictedCustomers</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>hooks/useSearchListNav.ts</t>
+          <t>hooks/useRestrictedCustomers.ts</t>
         </is>
       </c>
       <c r="D54" s="20" t="inlineStr">
@@ -8339,21 +8339,21 @@
         </is>
       </c>
       <c r="E54" s="17" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F54" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, navigation, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, trouble-ticketing-complaints, navigation, customer360, orders, profile, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G54" s="17" t="inlineStr">
         <is>
-          <t>CompanySearchInput, ContactPhoneInput, PlanSearchBox, LocationInput</t>
+          <t>TicketCreationModal</t>
         </is>
       </c>
       <c r="H54" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -8365,12 +8365,12 @@
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>useAreaOptions</t>
+          <t>useEnterToSubmit</t>
         </is>
       </c>
       <c r="C55" s="17" t="inlineStr">
         <is>
-          <t>hooks/useAreaOptions.ts</t>
+          <t>hooks/useEnterToSubmit.ts</t>
         </is>
       </c>
       <c r="D55" s="20" t="inlineStr">
@@ -8379,21 +8379,21 @@
         </is>
       </c>
       <c r="E55" s="17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F55" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G55" s="17" t="inlineStr">
         <is>
-          <t>BillingAccountStep, ZsbAddressStep</t>
+          <t>VerificationGate, useIdLookup</t>
         </is>
       </c>
       <c r="H55" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -8405,12 +8405,12 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>useSubmit</t>
+          <t>useSearchListNav</t>
         </is>
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t>hooks/useSubmit.ts</t>
+          <t>hooks/useSearchListNav.ts</t>
         </is>
       </c>
       <c r="D56" s="20" t="inlineStr">
@@ -8419,17 +8419,21 @@
         </is>
       </c>
       <c r="E56" s="17" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F56" s="17" t="inlineStr">
         <is>
-          <t>lead-management, mnp-fnp-porting, sim-number-management, trouble-ticketing-complaints, customer360, tasks</t>
-        </is>
-      </c>
-      <c r="G56" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, navigation, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G56" s="17" t="inlineStr">
+        <is>
+          <t>CompanySearchInput, ContactPhoneInput, PlanSearchBox, LocationInput</t>
+        </is>
+      </c>
       <c r="H56" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -8441,28 +8445,32 @@
       </c>
       <c r="B57" s="17" t="inlineStr">
         <is>
-          <t>useMinWidth</t>
+          <t>useAreaOptions</t>
         </is>
       </c>
       <c r="C57" s="17" t="inlineStr">
         <is>
-          <t>hooks/useMinWidth.ts</t>
-        </is>
-      </c>
-      <c r="D57" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>hooks/useAreaOptions.ts</t>
+        </is>
+      </c>
+      <c r="D57" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E57" s="17" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F57" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="G57" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G57" s="17" t="inlineStr">
+        <is>
+          <t>BillingAccountStep, ZsbAddressStep</t>
+        </is>
+      </c>
       <c r="H57" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
@@ -8472,17 +8480,17 @@
     <row r="58">
       <c r="A58" s="17" t="inlineStr">
         <is>
-          <t>Helper</t>
+          <t>Hook</t>
         </is>
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>statusTone</t>
+          <t>useSubmit</t>
         </is>
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t>lib/statusTone.ts</t>
+          <t>hooks/useSubmit.ts</t>
         </is>
       </c>
       <c r="D58" s="20" t="inlineStr">
@@ -8491,61 +8499,53 @@
         </is>
       </c>
       <c r="E58" s="17" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="F58" s="17" t="inlineStr">
         <is>
-          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, orders, sales, support, tasks, tickets</t>
-        </is>
-      </c>
-      <c r="G58" s="17" t="inlineStr">
-        <is>
-          <t>ruleEngine</t>
-        </is>
-      </c>
+          <t>lead-management, mnp-fnp-porting, sim-number-management, trouble-ticketing-complaints, customer360, tasks</t>
+        </is>
+      </c>
+      <c r="G58" s="17" t="inlineStr"/>
       <c r="H58" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="17" t="inlineStr">
         <is>
-          <t>Helper</t>
+          <t>Hook</t>
         </is>
       </c>
       <c r="B59" s="17" t="inlineStr">
         <is>
-          <t>format</t>
+          <t>useMinWidth</t>
         </is>
       </c>
       <c r="C59" s="17" t="inlineStr">
         <is>
-          <t>lib/format.ts</t>
-        </is>
-      </c>
-      <c r="D59" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>hooks/useMinWidth.ts</t>
+        </is>
+      </c>
+      <c r="D59" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E59" s="17" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="F59" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, tasks</t>
-        </is>
-      </c>
-      <c r="G59" s="17" t="inlineStr">
-        <is>
-          <t>AdditionalDocumentsUpload, CafDocumentUpload, MsisdnPicker, GuidedContactStep, IdLookupStep, postpaidPlanModel, StepSummaryPanel, stepSummary, customer360Engine, postpaidPricing</t>
-        </is>
-      </c>
+          <t>navigation</t>
+        </is>
+      </c>
+      <c r="G59" s="17" t="inlineStr"/>
       <c r="H59" s="17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8557,12 +8557,12 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>buildEnv</t>
+          <t>statusTone</t>
         </is>
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t>lib/buildEnv.ts</t>
+          <t>lib/statusTone.ts</t>
         </is>
       </c>
       <c r="D60" s="20" t="inlineStr">
@@ -8571,21 +8571,21 @@
         </is>
       </c>
       <c r="E60" s="17" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F60" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360</t>
+          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, orders, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G60" s="17" t="inlineStr">
         <is>
-          <t>syntheticMarker, navigationEngine</t>
+          <t>ruleEngine</t>
         </is>
       </c>
       <c r="H60" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8597,12 +8597,12 @@
       </c>
       <c r="B61" s="17" t="inlineStr">
         <is>
-          <t>deviceType</t>
+          <t>format</t>
         </is>
       </c>
       <c r="C61" s="17" t="inlineStr">
         <is>
-          <t>lib/deviceType.ts</t>
+          <t>lib/format.ts</t>
         </is>
       </c>
       <c r="D61" s="20" t="inlineStr">
@@ -8611,21 +8611,21 @@
         </is>
       </c>
       <c r="E61" s="17" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F61" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, tasks</t>
         </is>
       </c>
       <c r="G61" s="17" t="inlineStr">
         <is>
-          <t>IdFileUpload, PassportScanSections, SimSerialScanner, SimTypeStep, cafTypes</t>
+          <t>AdditionalDocumentsUpload, CafDocumentUpload, MsisdnPicker, GuidedContactStep, IdLookupStep, postpaidPlanModel, StepSummaryPanel, stepSummary, customer360Engine, postpaidPricing</t>
         </is>
       </c>
       <c r="H61" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -8637,12 +8637,12 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>taskId</t>
+          <t>buildEnv</t>
         </is>
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t>lib/taskId.ts</t>
+          <t>lib/buildEnv.ts</t>
         </is>
       </c>
       <c r="D62" s="20" t="inlineStr">
@@ -8651,21 +8651,21 @@
         </is>
       </c>
       <c r="E62" s="17" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F62" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360</t>
         </is>
       </c>
       <c r="G62" s="17" t="inlineStr">
         <is>
-          <t>useWizardDraftActions</t>
+          <t>syntheticMarker, navigationEngine</t>
         </is>
       </c>
       <c r="H62" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -8677,12 +8677,12 @@
       </c>
       <c r="B63" s="17" t="inlineStr">
         <is>
-          <t>connectionType</t>
+          <t>deviceType</t>
         </is>
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>lib/connectionType.ts</t>
+          <t>lib/deviceType.ts</t>
         </is>
       </c>
       <c r="D63" s="20" t="inlineStr">
@@ -8691,21 +8691,21 @@
         </is>
       </c>
       <c r="E63" s="17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F63" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration, customer360</t>
         </is>
       </c>
       <c r="G63" s="17" t="inlineStr">
         <is>
-          <t>ConnectionTypeTag</t>
+          <t>IdFileUpload, PassportScanSections, SimSerialScanner, SimTypeStep, cafTypes</t>
         </is>
       </c>
       <c r="H63" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8717,12 +8717,12 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>serviceTypeTag</t>
+          <t>taskId</t>
         </is>
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
-          <t>lib/serviceTypeTag.ts</t>
+          <t>lib/taskId.ts</t>
         </is>
       </c>
       <c r="D64" s="20" t="inlineStr">
@@ -8731,21 +8731,21 @@
         </is>
       </c>
       <c r="E64" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F64" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G64" s="17" t="inlineStr">
         <is>
-          <t>ServiceTypeTag</t>
+          <t>useWizardDraftActions</t>
         </is>
       </c>
       <c r="H64" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8757,31 +8757,35 @@
       </c>
       <c r="B65" s="17" t="inlineStr">
         <is>
-          <t>screenName</t>
+          <t>connectionType</t>
         </is>
       </c>
       <c r="C65" s="17" t="inlineStr">
         <is>
-          <t>lib/screenName.ts</t>
-        </is>
-      </c>
-      <c r="D65" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>lib/connectionType.ts</t>
+        </is>
+      </c>
+      <c r="D65" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E65" s="17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F65" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="G65" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G65" s="17" t="inlineStr">
+        <is>
+          <t>ConnectionTypeTag</t>
+        </is>
+      </c>
       <c r="H65" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -8793,40 +8797,116 @@
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
+          <t>serviceTypeTag</t>
+        </is>
+      </c>
+      <c r="C66" s="17" t="inlineStr">
+        <is>
+          <t>lib/serviceTypeTag.ts</t>
+        </is>
+      </c>
+      <c r="D66" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
+        </is>
+      </c>
+      <c r="E66" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="F66" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G66" s="17" t="inlineStr">
+        <is>
+          <t>ServiceTypeTag</t>
+        </is>
+      </c>
+      <c r="H66" s="17" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="17" t="inlineStr">
+        <is>
+          <t>Helper</t>
+        </is>
+      </c>
+      <c r="B67" s="17" t="inlineStr">
+        <is>
+          <t>screenName</t>
+        </is>
+      </c>
+      <c r="C67" s="17" t="inlineStr">
+        <is>
+          <t>lib/screenName.ts</t>
+        </is>
+      </c>
+      <c r="D67" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
+        </is>
+      </c>
+      <c r="E67" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="17" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
+      <c r="G67" s="17" t="inlineStr"/>
+      <c r="H67" s="17" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="17" t="inlineStr">
+        <is>
+          <t>Helper</t>
+        </is>
+      </c>
+      <c r="B68" s="17" t="inlineStr">
+        <is>
           <t>values</t>
         </is>
       </c>
-      <c r="C66" s="17" t="inlineStr">
+      <c r="C68" s="17" t="inlineStr">
         <is>
           <t>lib/values.ts</t>
         </is>
       </c>
-      <c r="D66" s="21" t="inlineStr">
+      <c r="D68" s="21" t="inlineStr">
         <is>
           <t>Single area</t>
         </is>
       </c>
-      <c r="E66" s="17" t="n">
+      <c r="E68" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F66" s="17" t="inlineStr">
+      <c r="F68" s="17" t="inlineStr">
         <is>
           <t>customer360</t>
         </is>
       </c>
-      <c r="G66" s="17" t="inlineStr">
+      <c r="G68" s="17" t="inlineStr">
         <is>
           <t>customer360Demo</t>
         </is>
       </c>
-      <c r="H66" s="17" t="inlineStr">
+      <c r="H68" s="17" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H66"/>
+  <autoFilter ref="A1:H68"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
+++ b/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="C5" s="17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" s="17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5" s="17" t="n">
         <v>2</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="C7" s="17" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D7" s="17" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E7" s="17" t="n">
         <v>4</v>
@@ -887,11 +887,11 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>24 named - see the Capabilities sheet</t>
+          <t>25 named - see the Capabilities sheet</t>
         </is>
       </c>
       <c r="C15" s="17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D15" s="17" t="inlineStr"/>
       <c r="E15" s="17" t="inlineStr"/>
@@ -908,7 +908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.80" customWidth="1" min="1" max="1"/>
@@ -975,7 +975,7 @@
     <row r="3">
       <c r="A3" s="17" t="inlineStr">
         <is>
-          <t>Customer Identification</t>
+          <t>Customer Verification</t>
         </is>
       </c>
       <c r="B3" s="17" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t>The Special Discounts section of Mobile Postpaid Activation as its own capability: choose Consumer B2B2C, Retiree or MADA, supply the evidence (company, ID number, Office ID scan or upload) and accept or reject the benefit. Independent of Customer Identification and Customer Type; always offers both Initiate scan and Upload document.</t>
+          <t>The Special Discounts section of Mobile Postpaid Activation as its own capability: choose Consumer B2B2C, Retiree or MADA, supply the evidence (company, ID number, Office ID scan or upload) and accept or reject the benefit. Independent of Customer Verification and Customer Type; always offers both Initiate scan and Upload document.</t>
         </is>
       </c>
       <c r="C4" s="17" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>Identify the customer, run eligibility, then offer the special-discount types - the whole "Customer Identification" step of an activation, with its outcomes and footer actions.</t>
+          <t>Identify the customer, run eligibility, then offer the special-discount types - the whole "Customer Verification" step of an activation, with its outcomes and footer actions.</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
@@ -1532,7 +1532,8 @@
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>capabilities/ServiceAddress/ServiceAddress.tsx
+          <t>capabilities/ServiceAddress/AddressPrefill.tsx
+capabilities/ServiceAddress/ServiceAddress.tsx
 capabilities/ServiceAddress/index.ts
 capabilities/ServiceAddress/step.tsx
 capabilities/ServiceAddress/summary.ts
@@ -1679,6 +1680,31 @@
         <v>1</v>
       </c>
       <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>administration</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>The one way to page a list: usePagination (1-based pages, a changed list returns to page 1, a page that no longer exists is clamped), the "Showing a-b of N" summary and the numbered pager, hidden on a single page. Used by the number picker, data tables and every paged Customer 360 and Telesales list.</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>capabilities/Pagination/index.ts</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
         <is>
           <t>administration</t>
         </is>
@@ -1781,7 +1807,7 @@
       </c>
       <c r="G2" s="17" t="inlineStr">
         <is>
-          <t>CreditCheckPanel, MsisdnPicker, SimTypeStep, ActivationCompleteScreen, AppointmentBookingStep, BillingAccountStep, BulkOperationPortal, CafSignatureCapture, DonorAttachmentStep, IdLookupStep, IdReconciliationPanel, PrepaidCartStep, PrepaidCheckoutStep, SimSwapFormStep, TicketCreationModal, WinCashPaymentStep, ConnectionTypeTag, Tooltip</t>
+          <t>CreditCheckPanel, MsisdnPicker, SimTypeStep, ActivationCompleteScreen, AppointmentBookingStep, BillingAccountStep, BulkOperationPortal, CafSignatureCapture, DonorAttachmentStep, IdLookupStep, PrepaidCartStep, PrepaidCheckoutStep, SimSwapFormStep, TicketCreationModal, WinCashPaymentStep, ConnectionTypeTag, Tooltip</t>
         </is>
       </c>
       <c r="H2" s="17" t="inlineStr">
@@ -1918,12 +1944,12 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Pager</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/Input.tsx</t>
+          <t>components/primitives/Pager.tsx</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -1932,21 +1958,21 @@
         </is>
       </c>
       <c r="E6" s="17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, profile, support</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, orders, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
         <is>
-          <t>AdditionalDocumentsUpload, BillLimitEditor, CpeSerialScanner, SimSerialScanner, AppointmentBookingStep, BillingAccountStep, BillingProfileSetupDrawer, BulkOperationPortal, DonorDetailsStep, GuidedContactStep, IdLookupStep, NewCustomerForm, PostpaidDiscountsPanel, TicketCreationModal, ZsbAddressStep, PhoneNumberInput</t>
+          <t>Pagination</t>
         </is>
       </c>
       <c r="H6" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1958,12 +1984,12 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>SearchField</t>
+          <t>Pagination</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/SearchField.tsx</t>
+          <t>components/primitives/Pagination.tsx</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -1972,21 +1998,21 @@
         </is>
       </c>
       <c r="E7" s="17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, support</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, orders, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G7" s="17" t="inlineStr">
         <is>
-          <t>CompanySearchInput, MsisdnPicker, PlanSearchBox</t>
+          <t>MsisdnPicker, DataTable</t>
         </is>
       </c>
       <c r="H7" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>uncommitted</t>
         </is>
       </c>
     </row>
@@ -1998,12 +2024,12 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>Textarea</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/Textarea.tsx</t>
+          <t>components/primitives/Input.tsx</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -2012,16 +2038,16 @@
         </is>
       </c>
       <c r="E8" s="17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, support</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, profile, support</t>
         </is>
       </c>
       <c r="G8" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen, ActivityCommentsStep, AppointmentBookingStep, TicketCreationModal, ZsbAddressStep, WizardDialogs</t>
+          <t>AdditionalDocumentsUpload, BillLimitEditor, CpeSerialScanner, SimSerialScanner, AppointmentBookingStep, BillingAccountStep, BillingProfileSetupDrawer, BulkOperationPortal, DonorDetailsStep, GuidedContactStep, IdLookupStep, NewCustomerForm, TicketCreationModal, ZsbAddressStep, PhoneNumberInput</t>
         </is>
       </c>
       <c r="H8" s="17" t="inlineStr">
@@ -2038,12 +2064,12 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>Tooltip</t>
+          <t>SearchField</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/Tooltip.tsx</t>
+          <t>components/primitives/SearchField.tsx</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -2052,16 +2078,16 @@
         </is>
       </c>
       <c r="E9" s="17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, support</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, support</t>
         </is>
       </c>
       <c r="G9" s="17" t="inlineStr">
         <is>
-          <t>CustomerViewButton, CloseButton, Tabs</t>
+          <t>CompanySearchInput, MsisdnPicker, PlanSearchBox</t>
         </is>
       </c>
       <c r="H9" s="17" t="inlineStr">
@@ -2078,12 +2104,12 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>TooltipGroup</t>
+          <t>Textarea</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/TooltipContext.tsx</t>
+          <t>components/primitives/Textarea.tsx</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -2096,17 +2122,17 @@
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, support</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, support</t>
         </is>
       </c>
       <c r="G10" s="17" t="inlineStr">
         <is>
-          <t>Tooltip</t>
+          <t>ActivationCompleteScreen, ActivityCommentsStep, AppointmentBookingStep, TicketCreationModal, ZsbAddressStep, WizardDialogs</t>
         </is>
       </c>
       <c r="H10" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2118,12 +2144,12 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>CloseButton</t>
+          <t>Tooltip</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/CloseButton.tsx</t>
+          <t>components/primitives/Tooltip.tsx</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -2132,16 +2158,16 @@
         </is>
       </c>
       <c r="E11" s="17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, support</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, support</t>
         </is>
       </c>
       <c r="G11" s="17" t="inlineStr">
         <is>
-          <t>Drawer, Modal</t>
+          <t>CustomerViewButton, CloseButton, Tabs</t>
         </is>
       </c>
       <c r="H11" s="17" t="inlineStr">
@@ -2158,12 +2184,12 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>TooltipGroup</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/Checkbox.tsx</t>
+          <t>components/primitives/TooltipContext.tsx</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -2172,21 +2198,21 @@
         </is>
       </c>
       <c r="E12" s="17" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, support</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, support</t>
         </is>
       </c>
       <c r="G12" s="17" t="inlineStr">
         <is>
-          <t>CreditCheckPanel, MsisdnPicker, AppointmentBookingStep, BillingAccountStep, CafSignatureCapture, PrepaidPlanStep</t>
+          <t>Tooltip</t>
         </is>
       </c>
       <c r="H12" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -2198,12 +2224,12 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>TabStrip</t>
+          <t>CloseButton</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/TabStrip.tsx</t>
+          <t>components/primitives/CloseButton.tsx</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -2212,21 +2238,21 @@
         </is>
       </c>
       <c r="E13" s="17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, trouble-ticketing-complaints, administration, customer360, orders, support</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, support</t>
         </is>
       </c>
       <c r="G13" s="17" t="inlineStr">
         <is>
-          <t>PlanTabStrip, Tabs</t>
+          <t>Drawer, Modal</t>
         </is>
       </c>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2238,12 +2264,12 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>DataTable</t>
+          <t>TabStrip</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/DataTable.tsx</t>
+          <t>components/primitives/TabStrip.tsx</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -2252,21 +2278,21 @@
         </is>
       </c>
       <c r="E14" s="17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, lead-management, mnp-fnp-porting, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, customer360, orders, sales, support, tasks, tickets</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, orders, support</t>
         </is>
       </c>
       <c r="G14" s="17" t="inlineStr">
         <is>
-          <t>BulkOperationPortal</t>
+          <t>MsisdnPicker, PlanTabStrip, Tabs</t>
         </is>
       </c>
       <c r="H14" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2278,12 +2304,12 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>Pager</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/Pager.tsx</t>
+          <t>components/primitives/Checkbox.tsx</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -2292,16 +2318,16 @@
         </is>
       </c>
       <c r="E15" s="17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, lead-management, mnp-fnp-porting, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, customer360, orders, sales, support, tasks, tickets</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, support</t>
         </is>
       </c>
       <c r="G15" s="17" t="inlineStr">
         <is>
-          <t>DataTable</t>
+          <t>CreditCheckPanel, MsisdnPicker, AppointmentBookingStep, BillingAccountStep, CafSignatureCapture, PrepaidPlanStep</t>
         </is>
       </c>
       <c r="H15" s="17" t="inlineStr">
@@ -2318,12 +2344,12 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>CARD_SELECTED</t>
+          <t>DataTable</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/offerCardParts.tsx</t>
+          <t>components/primitives/DataTable.tsx</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -2332,21 +2358,21 @@
         </is>
       </c>
       <c r="E16" s="17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>enterprise-iot-b2b, lead-management, mnp-fnp-porting, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, customer360, orders, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G16" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, QidInput, AppointmentBookingStep, BillingAccountStep, DiscountCard, FixedPlanStep, LineSelectionStep, PostpaidPlanAddonsStep, PostpaidPlanCard, PrepaidPlanCard, PrepaidPlanStep, ChoiceCards</t>
+          <t>BulkOperationPortal</t>
         </is>
       </c>
       <c r="H16" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2358,12 +2384,12 @@
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>CountryMarker</t>
+          <t>CARD_SELECTED</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/CountryMarker.tsx</t>
+          <t>components/primitives/offerCardParts.tsx</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -2381,12 +2407,12 @@
       </c>
       <c r="G17" s="17" t="inlineStr">
         <is>
-          <t>PhoneNumberInput</t>
+          <t>MsisdnPicker, QidInput, AppointmentBookingStep, BillingAccountStep, DiscountCard, FixedPlanStep, LineSelectionStep, PostpaidPlanAddonsStep, PostpaidPlanCard, PrepaidPlanCard, PrepaidPlanStep, ChoiceCards</t>
         </is>
       </c>
       <c r="H17" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -2398,12 +2424,12 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>Drawer</t>
+          <t>CountryMarker</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/Drawer.tsx</t>
+          <t>components/primitives/CountryMarker.tsx</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -2416,17 +2442,17 @@
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, trouble-ticketing-complaints, administration, customer360, support</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G18" s="17" t="inlineStr">
         <is>
-          <t>EligibilityRows, BillingProfileSetupDrawer, PrepaidPackDetailsDrawer, TicketCreationModal, VerificationGate</t>
+          <t>PhoneNumberInput</t>
         </is>
       </c>
       <c r="H18" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2438,12 +2464,12 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>ErrorBanner</t>
+          <t>Drawer</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/ErrorBanner.tsx</t>
+          <t>components/primitives/Drawer.tsx</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -2456,13 +2482,17 @@
       </c>
       <c r="F19" s="17" t="inlineStr">
         <is>
-          <t>lead-management, mnp-fnp-porting, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, customer360, orders, sales, support, tasks, tickets</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, trouble-ticketing-complaints, administration, customer360, support</t>
+        </is>
+      </c>
+      <c r="G19" s="17" t="inlineStr">
+        <is>
+          <t>EligibilityRows, BillingProfileSetupDrawer, PrepaidPackDetailsDrawer, TicketCreationModal, VerificationGate</t>
+        </is>
+      </c>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2474,12 +2504,12 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>Modal</t>
+          <t>ErrorBanner</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/Modal.tsx</t>
+          <t>components/primitives/ErrorBanner.tsx</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -2492,14 +2522,10 @@
       </c>
       <c r="F20" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>ActivationCompleteScreen, WizardDialogs</t>
-        </is>
-      </c>
+          <t>lead-management, mnp-fnp-porting, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, customer360, orders, sales, support, tasks, tickets</t>
+        </is>
+      </c>
+      <c r="G20" s="17" t="inlineStr"/>
       <c r="H20" s="17" t="inlineStr">
         <is>
           <t>2026-10-15</t>
@@ -2514,12 +2540,12 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>PhoneNumberInput</t>
+          <t>Modal</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/PhoneNumberInput.tsx</t>
+          <t>components/primitives/Modal.tsx</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -2532,12 +2558,12 @@
       </c>
       <c r="F21" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration</t>
         </is>
       </c>
       <c r="G21" s="17" t="inlineStr">
         <is>
-          <t>ContactPhoneInput, DonorDetailsStep, GuidedContactStep</t>
+          <t>ActivationCompleteScreen, WizardDialogs</t>
         </is>
       </c>
       <c r="H21" s="17" t="inlineStr">
@@ -2554,12 +2580,12 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>Spinner</t>
+          <t>PhoneNumberInput</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/Spinner.tsx</t>
+          <t>components/primitives/PhoneNumberInput.tsx</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -2577,7 +2603,7 @@
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
-          <t>PassportScanSections, QidImageUpload, ValidationStatus</t>
+          <t>ContactPhoneInput, DonorDetailsStep, GuidedContactStep</t>
         </is>
       </c>
       <c r="H22" s="17" t="inlineStr">
@@ -2594,12 +2620,12 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>SegmentedTabs</t>
+          <t>Spinner</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/SegmentedTabs.tsx</t>
+          <t>components/primitives/Spinner.tsx</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -2608,21 +2634,21 @@
         </is>
       </c>
       <c r="E23" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F23" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration, customer360, tickets</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G23" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker</t>
+          <t>PassportScanSections, QidImageUpload, ValidationStatus</t>
         </is>
       </c>
       <c r="H23" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2942,31 +2968,31 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>VodafoneMark</t>
+          <t>SegmentedTabs</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/VodafoneMark.tsx</t>
-        </is>
-      </c>
-      <c r="D32" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>components/primitives/SegmentedTabs.tsx</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E32" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F32" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
+          <t>administration, customer360, tickets</t>
         </is>
       </c>
       <c r="G32" s="17" t="inlineStr"/>
       <c r="H32" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2978,12 +3004,12 @@
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>VodafoneWordmark</t>
+          <t>VodafoneMark</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/VodafoneWordmark.tsx</t>
+          <t>components/primitives/VodafoneMark.tsx</t>
         </is>
       </c>
       <c r="D33" s="21" t="inlineStr">
@@ -3014,27 +3040,31 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>LocationInput</t>
+          <t>VodafoneWordmark</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/LocationInput.tsx</t>
-        </is>
-      </c>
-      <c r="D34" s="22" t="inlineStr">
-        <is>
-          <t>No consumer</t>
+          <t>components/primitives/VodafoneWordmark.tsx</t>
+        </is>
+      </c>
+      <c r="D34" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E34" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F34" s="17" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
       <c r="G34" s="17" t="inlineStr"/>
       <c r="H34" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3046,17 +3076,17 @@
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>OoredooMark</t>
+          <t>LocationInput</t>
         </is>
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/OoredooMark.tsx</t>
-        </is>
-      </c>
-      <c r="D35" s="23" t="inlineStr">
-        <is>
-          <t>App shell only</t>
+          <t>components/primitives/LocationInput.tsx</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>No consumer</t>
         </is>
       </c>
       <c r="E35" s="17" t="n">
@@ -3066,47 +3096,39 @@
       <c r="G35" s="17" t="inlineStr"/>
       <c r="H35" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="17" t="inlineStr">
         <is>
-          <t>Domain</t>
+          <t>Primitive</t>
         </is>
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>ScannedIdPreview</t>
+          <t>OoredooMark</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>components/domain/ScannedIdPreview.tsx</t>
-        </is>
-      </c>
-      <c r="D36" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>components/primitives/OoredooMark.tsx</t>
+        </is>
+      </c>
+      <c r="D36" s="23" t="inlineStr">
+        <is>
+          <t>App shell only</t>
         </is>
       </c>
       <c r="E36" s="17" t="n">
-        <v>13</v>
-      </c>
-      <c r="F36" s="17" t="inlineStr">
-        <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, administration, customer360</t>
-        </is>
-      </c>
-      <c r="G36" s="17" t="inlineStr">
-        <is>
-          <t>PassportScanSections, QidImageUpload, qidImageUploadModel, IdScannerPanel, useIdLookup</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F36" s="17" t="inlineStr"/>
+      <c r="G36" s="17" t="inlineStr"/>
       <c r="H36" s="17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3140,12 @@
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>IdFileUpload</t>
+          <t>ScannedIdPreview</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>components/domain/IdFileUpload.tsx</t>
+          <t>components/domain/ScannedIdPreview.tsx</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
@@ -3132,21 +3154,21 @@
         </is>
       </c>
       <c r="E37" s="17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F37" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G37" s="17" t="inlineStr">
         <is>
-          <t>PassportScanSections, QidImageUpload</t>
+          <t>PassportScanSections, QidImageUpload, qidImageUploadModel, IdScannerPanel, useIdLookup</t>
         </is>
       </c>
       <c r="H37" s="17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -3158,12 +3180,12 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>PassportScanSections</t>
+          <t>IdFileUpload</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>components/domain/PassportScanSections.tsx</t>
+          <t>components/domain/IdFileUpload.tsx</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
@@ -3181,7 +3203,7 @@
       </c>
       <c r="G38" s="17" t="inlineStr">
         <is>
-          <t>QidImageUpload</t>
+          <t>PassportScanSections, QidImageUpload</t>
         </is>
       </c>
       <c r="H38" s="17" t="inlineStr">
@@ -3198,12 +3220,12 @@
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>QidImageUpload</t>
+          <t>PassportScanSections</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>components/domain/QidImageUpload.tsx</t>
+          <t>components/domain/PassportScanSections.tsx</t>
         </is>
       </c>
       <c r="D39" s="20" t="inlineStr">
@@ -3221,12 +3243,12 @@
       </c>
       <c r="G39" s="17" t="inlineStr">
         <is>
-          <t>IdScannerPanel</t>
+          <t>QidImageUpload</t>
         </is>
       </c>
       <c r="H39" s="17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3260,12 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>QidTypeSelector</t>
+          <t>QidImageUpload</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>components/domain/QidInput.tsx</t>
+          <t>components/domain/QidImageUpload.tsx</t>
         </is>
       </c>
       <c r="D40" s="20" t="inlineStr">
@@ -3261,12 +3283,12 @@
       </c>
       <c r="G40" s="17" t="inlineStr">
         <is>
-          <t>GuidedContactStep, IdLookupStep, IdScannerPanel, MoiResultPanel, guidedContactModel, idLookupModel, useIdLookup</t>
+          <t>IdScannerPanel</t>
         </is>
       </c>
       <c r="H40" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -3278,12 +3300,12 @@
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>ScanFailureNotice</t>
+          <t>QidTypeSelector</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>components/domain/ScanFailureNotice.tsx</t>
+          <t>components/domain/QidInput.tsx</t>
         </is>
       </c>
       <c r="D41" s="20" t="inlineStr">
@@ -3301,12 +3323,12 @@
       </c>
       <c r="G41" s="17" t="inlineStr">
         <is>
-          <t>PassportScanSections, QidImageUpload</t>
+          <t>GuidedContactStep, IdLookupStep, IdScannerPanel, MoiResultPanel, guidedContactModel, idLookupModel, useIdLookup</t>
         </is>
       </c>
       <c r="H41" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3318,12 +3340,12 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>CompanySearchInput</t>
+          <t>ScanFailureNotice</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>components/domain/CompanySearchInput.tsx</t>
+          <t>components/domain/ScanFailureNotice.tsx</t>
         </is>
       </c>
       <c r="D42" s="20" t="inlineStr">
@@ -3332,17 +3354,21 @@
         </is>
       </c>
       <c r="E42" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F42" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, administration, customer360</t>
-        </is>
-      </c>
-      <c r="G42" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G42" s="17" t="inlineStr">
+        <is>
+          <t>PassportScanSections, QidImageUpload</t>
+        </is>
+      </c>
       <c r="H42" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -3354,12 +3380,12 @@
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>EligibilityChecksList</t>
+          <t>CompanySearchInput</t>
         </is>
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>components/domain/EligibilityRows.tsx</t>
+          <t>components/domain/CompanySearchInput.tsx</t>
         </is>
       </c>
       <c r="D43" s="20" t="inlineStr">
@@ -3368,11 +3394,11 @@
         </is>
       </c>
       <c r="E43" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F43" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, administration, customer360</t>
         </is>
       </c>
       <c r="G43" s="17" t="inlineStr"/>
@@ -3390,12 +3416,12 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>SimSerialScanner</t>
+          <t>EligibilityChecksList</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>components/domain/SimSerialScanner.tsx</t>
+          <t>components/domain/EligibilityRows.tsx</t>
         </is>
       </c>
       <c r="D44" s="20" t="inlineStr">
@@ -3408,17 +3434,13 @@
       </c>
       <c r="F44" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
-        </is>
-      </c>
-      <c r="G44" s="17" t="inlineStr">
-        <is>
-          <t>SimTypeStep</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G44" s="17" t="inlineStr"/>
       <c r="H44" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3430,12 +3452,12 @@
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>AdditionalDocumentsUpload</t>
+          <t>SimSerialScanner</t>
         </is>
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>components/domain/AdditionalDocumentsUpload.tsx</t>
+          <t>components/domain/SimSerialScanner.tsx</t>
         </is>
       </c>
       <c r="D45" s="20" t="inlineStr">
@@ -3444,21 +3466,21 @@
         </is>
       </c>
       <c r="E45" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F45" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G45" s="17" t="inlineStr">
         <is>
-          <t>CafSignatureCapture</t>
+          <t>SimTypeStep</t>
         </is>
       </c>
       <c r="H45" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3492,12 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>BillLimitEditor</t>
+          <t>AdditionalDocumentsUpload</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>components/domain/BillLimitEditor.tsx</t>
+          <t>components/domain/AdditionalDocumentsUpload.tsx</t>
         </is>
       </c>
       <c r="D46" s="20" t="inlineStr">
@@ -3493,12 +3515,12 @@
       </c>
       <c r="G46" s="17" t="inlineStr">
         <is>
-          <t>PostpaidAddonsPanel, PostpaidPlanAddonsStep</t>
+          <t>CafSignatureCapture</t>
         </is>
       </c>
       <c r="H46" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3510,12 +3532,12 @@
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>CafDocumentUpload</t>
+          <t>BillLimitEditor</t>
         </is>
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>components/domain/CafDocumentUpload.tsx</t>
+          <t>components/domain/BillLimitEditor.tsx</t>
         </is>
       </c>
       <c r="D47" s="20" t="inlineStr">
@@ -3533,12 +3555,12 @@
       </c>
       <c r="G47" s="17" t="inlineStr">
         <is>
-          <t>CafSignatureCapture</t>
+          <t>PostpaidAddonsPanel, PostpaidPlanAddonsStep</t>
         </is>
       </c>
       <c r="H47" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3550,12 +3572,12 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>CreditCheckPanel</t>
+          <t>CafDocumentUpload</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>components/domain/CreditCheckPanel.tsx</t>
+          <t>components/domain/CafDocumentUpload.tsx</t>
         </is>
       </c>
       <c r="D48" s="20" t="inlineStr">
@@ -3573,7 +3595,7 @@
       </c>
       <c r="G48" s="17" t="inlineStr">
         <is>
-          <t>FixedPlanStep</t>
+          <t>CafSignatureCapture</t>
         </is>
       </c>
       <c r="H48" s="17" t="inlineStr">
@@ -3590,12 +3612,12 @@
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>EsimActivationPanel</t>
+          <t>CreditCheckPanel</t>
         </is>
       </c>
       <c r="C49" s="17" t="inlineStr">
         <is>
-          <t>components/domain/EsimActivationPanel.tsx</t>
+          <t>components/domain/CreditCheckPanel.tsx</t>
         </is>
       </c>
       <c r="D49" s="20" t="inlineStr">
@@ -3613,12 +3635,12 @@
       </c>
       <c r="G49" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen</t>
+          <t>FixedPlanStep</t>
         </is>
       </c>
       <c r="H49" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3630,12 +3652,12 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker</t>
+          <t>EsimActivationPanel</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>components/domain/MsisdnPicker.tsx</t>
+          <t>components/domain/EsimActivationPanel.tsx</t>
         </is>
       </c>
       <c r="D50" s="20" t="inlineStr">
@@ -3648,13 +3670,17 @@
       </c>
       <c r="F50" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
-        </is>
-      </c>
-      <c r="G50" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G50" s="17" t="inlineStr">
+        <is>
+          <t>ActivationCompleteScreen</t>
+        </is>
+      </c>
       <c r="H50" s="17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3666,12 +3692,12 @@
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>SimTypeStep</t>
+          <t>MsisdnPicker</t>
         </is>
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>components/domain/SimTypeStep.tsx</t>
+          <t>components/domain/MsisdnPicker.tsx</t>
         </is>
       </c>
       <c r="D51" s="20" t="inlineStr">
@@ -3684,17 +3710,13 @@
       </c>
       <c r="F51" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G51" s="17" t="inlineStr">
-        <is>
-          <t>CheckoutSummaryStep, checkoutDetailedTables, checkoutSummaryRows, prepaidCartModel, useCheckoutSummary</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+      <c r="G51" s="17" t="inlineStr"/>
       <c r="H51" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -3706,12 +3728,12 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>StarStat</t>
+          <t>SimTypeStep</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>components/domain/StarStat.tsx</t>
+          <t>components/domain/SimTypeStep.tsx</t>
         </is>
       </c>
       <c r="D52" s="20" t="inlineStr">
@@ -3724,17 +3746,17 @@
       </c>
       <c r="F52" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G52" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker</t>
+          <t>CheckoutSummaryStep, checkoutDetailedTables, checkoutSummaryRows, prepaidCartModel, useCheckoutSummary</t>
         </is>
       </c>
       <c r="H52" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -3746,12 +3768,12 @@
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>FibreReadinessBanner</t>
+          <t>StarStat</t>
         </is>
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>components/domain/FibreReadinessBanner.tsx</t>
+          <t>components/domain/StarStat.tsx</t>
         </is>
       </c>
       <c r="D53" s="20" t="inlineStr">
@@ -3760,16 +3782,16 @@
         </is>
       </c>
       <c r="E53" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F53" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G53" s="17" t="inlineStr">
         <is>
-          <t>ZsbAddressStep</t>
+          <t>MsisdnPicker</t>
         </is>
       </c>
       <c r="H53" s="17" t="inlineStr">
@@ -3786,28 +3808,32 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>ContactPhoneInput</t>
+          <t>FibreReadinessBanner</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>components/domain/ContactPhoneInput.tsx</t>
-        </is>
-      </c>
-      <c r="D54" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>components/domain/FibreReadinessBanner.tsx</t>
+        </is>
+      </c>
+      <c r="D54" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E54" s="17" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F54" s="17" t="inlineStr">
         <is>
-          <t>customer360</t>
-        </is>
-      </c>
-      <c r="G54" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G54" s="17" t="inlineStr">
+        <is>
+          <t>ZsbAddressStep</t>
+        </is>
+      </c>
       <c r="H54" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
@@ -3822,12 +3848,12 @@
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>CpeSerialScanner</t>
+          <t>ContactPhoneInput</t>
         </is>
       </c>
       <c r="C55" s="17" t="inlineStr">
         <is>
-          <t>components/domain/CpeSerialScanner.tsx</t>
+          <t>components/domain/ContactPhoneInput.tsx</t>
         </is>
       </c>
       <c r="D55" s="21" t="inlineStr">
@@ -3840,17 +3866,13 @@
       </c>
       <c r="F55" s="17" t="inlineStr">
         <is>
-          <t>fwa-5g-home</t>
-        </is>
-      </c>
-      <c r="G55" s="17" t="inlineStr">
-        <is>
-          <t>DualPlaySerialCheckStep</t>
-        </is>
-      </c>
+          <t>customer360</t>
+        </is>
+      </c>
+      <c r="G55" s="17" t="inlineStr"/>
       <c r="H55" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3862,12 +3884,12 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>OsmEmbed</t>
+          <t>CpeSerialScanner</t>
         </is>
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t>components/domain/OsmEmbed.tsx</t>
+          <t>components/domain/CpeSerialScanner.tsx</t>
         </is>
       </c>
       <c r="D56" s="21" t="inlineStr">
@@ -3880,49 +3902,53 @@
       </c>
       <c r="F56" s="17" t="inlineStr">
         <is>
-          <t>customer360</t>
-        </is>
-      </c>
-      <c r="G56" s="17" t="inlineStr"/>
+          <t>fwa-5g-home</t>
+        </is>
+      </c>
+      <c r="G56" s="17" t="inlineStr">
+        <is>
+          <t>DualPlaySerialCheckStep</t>
+        </is>
+      </c>
       <c r="H56" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="17" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="B57" s="17" t="inlineStr">
         <is>
-          <t>PageHeader</t>
+          <t>OsmEmbed</t>
         </is>
       </c>
       <c r="C57" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PageHeader.tsx</t>
-        </is>
-      </c>
-      <c r="D57" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>components/domain/OsmEmbed.tsx</t>
+        </is>
+      </c>
+      <c r="D57" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E57" s="17" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F57" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fwa-5g-home, lead-management, mnp-fnp-porting, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
+          <t>customer360</t>
         </is>
       </c>
       <c r="G57" s="17" t="inlineStr"/>
       <c r="H57" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -3934,12 +3960,12 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>RestrictedCustomerNotice</t>
+          <t>PageHeader</t>
         </is>
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/RestrictedCustomerNotice.tsx</t>
+          <t>components/patterns/PageHeader.tsx</t>
         </is>
       </c>
       <c r="D58" s="20" t="inlineStr">
@@ -3948,21 +3974,17 @@
         </is>
       </c>
       <c r="E58" s="17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F58" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer-search, customer360, support, tasks</t>
-        </is>
-      </c>
-      <c r="G58" s="17" t="inlineStr">
-        <is>
-          <t>IdLookupStep, TicketCreationModal</t>
-        </is>
-      </c>
+          <t>enterprise-iot-b2b, fwa-5g-home, lead-management, mnp-fnp-porting, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
+        </is>
+      </c>
+      <c r="G58" s="17" t="inlineStr"/>
       <c r="H58" s="17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3974,12 +3996,12 @@
       </c>
       <c r="B59" s="17" t="inlineStr">
         <is>
-          <t>GuidedContactStep</t>
+          <t>RestrictedCustomerNotice</t>
         </is>
       </c>
       <c r="C59" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/GuidedContactStep.tsx</t>
+          <t>components/patterns/RestrictedCustomerNotice.tsx</t>
         </is>
       </c>
       <c r="D59" s="20" t="inlineStr">
@@ -3988,14 +4010,18 @@
         </is>
       </c>
       <c r="E59" s="17" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F59" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
-        </is>
-      </c>
-      <c r="G59" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer-search, customer360, support, tasks</t>
+        </is>
+      </c>
+      <c r="G59" s="17" t="inlineStr">
+        <is>
+          <t>IdLookupStep, TicketCreationModal</t>
+        </is>
+      </c>
       <c r="H59" s="17" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -4010,12 +4036,12 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>IdLookupStatus</t>
+          <t>GuidedContactStep</t>
         </is>
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/IdLookupStatus.tsx</t>
+          <t>components/patterns/GuidedContactStep.tsx</t>
         </is>
       </c>
       <c r="D60" s="20" t="inlineStr">
@@ -4031,14 +4057,10 @@
           <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
-      <c r="G60" s="17" t="inlineStr">
-        <is>
-          <t>IdLookupStep</t>
-        </is>
-      </c>
+      <c r="G60" s="17" t="inlineStr"/>
       <c r="H60" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -4050,12 +4072,12 @@
       </c>
       <c r="B61" s="17" t="inlineStr">
         <is>
-          <t>IdLookupStep</t>
+          <t>IdLookupStatus</t>
         </is>
       </c>
       <c r="C61" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/IdLookupStep.tsx</t>
+          <t>components/patterns/IdLookupStatus.tsx</t>
         </is>
       </c>
       <c r="D61" s="20" t="inlineStr">
@@ -4073,12 +4095,12 @@
       </c>
       <c r="G61" s="17" t="inlineStr">
         <is>
-          <t>GuidedContactStep</t>
+          <t>IdLookupStep</t>
         </is>
       </c>
       <c r="H61" s="17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -4090,12 +4112,12 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>IdReconciliationPanel</t>
+          <t>IdLookupStep</t>
         </is>
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/IdReconciliationPanel.tsx</t>
+          <t>components/patterns/IdLookupStep.tsx</t>
         </is>
       </c>
       <c r="D62" s="20" t="inlineStr">
@@ -4113,12 +4135,12 @@
       </c>
       <c r="G62" s="17" t="inlineStr">
         <is>
-          <t>IdLookupStep</t>
+          <t>GuidedContactStep</t>
         </is>
       </c>
       <c r="H62" s="17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4180,7 @@
       </c>
       <c r="H63" s="17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4956,7 @@
       </c>
       <c r="H83" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5010,7 +5032,7 @@
       <c r="G85" s="17" t="inlineStr"/>
       <c r="H85" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5481,11 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G97" s="17" t="inlineStr"/>
+      <c r="G97" s="17" t="inlineStr">
+        <is>
+          <t>addressFromBilling</t>
+        </is>
+      </c>
       <c r="H97" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
@@ -6457,7 +6483,7 @@
       </c>
       <c r="H4" s="17" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -6523,16 +6549,16 @@
         </is>
       </c>
       <c r="E6" s="17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, support</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, support</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
         <is>
-          <t>eligibilityRowsModel, CreditLimitCard, PostpaidPlanAddonsStep, useCheckoutSummary, creditLimit, ruleEngine</t>
+          <t>eligibilityRowsModel, CreditLimitCard, idLookupModel, useCheckoutSummary, creditLimit, ruleEngine</t>
         </is>
       </c>
       <c r="H6" s="17" t="inlineStr">
@@ -6812,7 +6838,7 @@
       </c>
       <c r="G13" s="17" t="inlineStr">
         <is>
-          <t>eligibilityRowsModel, eligibilityTypes, useIdLookup</t>
+          <t>eligibilityRowsModel, eligibilityTypes, idLookupModel, useIdLookup</t>
         </is>
       </c>
       <c r="H13" s="17" t="inlineStr">
@@ -7721,7 +7747,7 @@
       <c r="G37" s="17" t="inlineStr"/>
       <c r="H37" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -8012,7 +8038,7 @@
       </c>
       <c r="G45" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, eligibilityRowsModel, ActivationCompleteScreen, AppointmentBookingStep, PostpaidPlanAddonsStep, TicketCreationModal, useCheckoutSummary, useIdLookup, useRestrictedCustomers, configStore</t>
+          <t>MsisdnPicker, eligibilityRowsModel, ActivationCompleteScreen, AppointmentBookingStep, TicketCreationModal, useCheckoutSummary, useIdLookup, useRestrictedCustomers, configStore</t>
         </is>
       </c>
       <c r="H45" s="17" t="inlineStr">
@@ -8620,7 +8646,7 @@
       </c>
       <c r="G61" s="17" t="inlineStr">
         <is>
-          <t>AdditionalDocumentsUpload, CafDocumentUpload, MsisdnPicker, GuidedContactStep, IdLookupStep, postpaidPlanModel, StepSummaryPanel, stepSummary, customer360Engine, postpaidPricing</t>
+          <t>AdditionalDocumentsUpload, CafDocumentUpload, MsisdnPicker, GuidedContactStep, IdLookupStep, StepSummaryPanel, stepSummary, customer360Engine, postpaidPricing</t>
         </is>
       </c>
       <c r="H61" s="17" t="inlineStr">
@@ -8956,7 +8982,7 @@
       </c>
       <c r="B3" s="27" t="inlineStr">
         <is>
-          <t>A journey or workspace folder: src/modules/&lt;x&gt;, src/workspace/&lt;x&gt;, or src/navigation. Resolved transitively - through other shared components AND through journey files that another journey reuses (Fixed Line reusing New Connection's contact step reaches Customer Identification that way).</t>
+          <t>A journey or workspace folder: src/modules/&lt;x&gt;, src/workspace/&lt;x&gt;, or src/navigation. Resolved transitively - through other shared components AND through journey files that another journey reuses (Fixed Line reusing New Connection's contact step reaches Customer Verification that way).</t>
         </is>
       </c>
     </row>

--- a/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
+++ b/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
@@ -1932,7 +1932,7 @@
       </c>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="H6" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="H7" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H9" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="H15" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="H16" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -2920,7 +2920,7 @@
       <c r="G30" s="17" t="inlineStr"/>
       <c r="H30" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="H37" s="17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="H38" s="17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       <c r="G43" s="17" t="inlineStr"/>
       <c r="H43" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -3440,7 +3440,7 @@
       <c r="G44" s="17" t="inlineStr"/>
       <c r="H44" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="H46" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H48" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="H49" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       <c r="G51" s="17" t="inlineStr"/>
       <c r="H51" s="17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -4060,7 +4060,7 @@
       <c r="G60" s="17" t="inlineStr"/>
       <c r="H60" s="17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="H66" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       <c r="G68" s="17" t="inlineStr"/>
       <c r="H68" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -4448,7 +4448,7 @@
       <c r="G70" s="17" t="inlineStr"/>
       <c r="H70" s="17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="H71" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="H82" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="H84" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="H86" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5108,7 +5108,7 @@
       <c r="G87" s="17" t="inlineStr"/>
       <c r="H87" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       <c r="G88" s="17" t="inlineStr"/>
       <c r="H88" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5260,7 +5260,7 @@
       <c r="G91" s="17" t="inlineStr"/>
       <c r="H91" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5336,7 +5336,7 @@
       <c r="G93" s="17" t="inlineStr"/>
       <c r="H93" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       <c r="G94" s="17" t="inlineStr"/>
       <c r="H94" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       <c r="G96" s="17" t="inlineStr"/>
       <c r="H96" s="17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="H97" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       <c r="G98" s="17" t="inlineStr"/>
       <c r="H98" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5560,7 +5560,7 @@
       <c r="G99" s="17" t="inlineStr"/>
       <c r="H99" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5596,7 +5596,7 @@
       <c r="G100" s="17" t="inlineStr"/>
       <c r="H100" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="H101" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       <c r="G102" s="17" t="inlineStr"/>
       <c r="H102" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5816,7 +5816,7 @@
       <c r="G106" s="17" t="inlineStr"/>
       <c r="H106" s="17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       <c r="G110" s="17" t="inlineStr"/>
       <c r="H110" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5996,7 @@
       <c r="G111" s="17" t="inlineStr"/>
       <c r="H111" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -6775,12 +6775,12 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>serviceCall</t>
+          <t>eligibilityEngine</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>engines/serviceCall.ts</t>
+          <t>engines/eligibilityEngine.ts</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -6789,21 +6789,21 @@
         </is>
       </c>
       <c r="E12" s="17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G12" s="17" t="inlineStr">
         <is>
-          <t>DemoFaultPanel, ValidationStatus, useIdLookup</t>
+          <t>eligibilityRowsModel, eligibilityTypes, idLookupModel, useIdLookup</t>
         </is>
       </c>
       <c r="H12" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -6815,12 +6815,12 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>eligibilityEngine</t>
+          <t>milestoneEngine</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>engines/eligibilityEngine.ts</t>
+          <t>engines/milestoneEngine.ts</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -6838,12 +6838,12 @@
       </c>
       <c r="G13" s="17" t="inlineStr">
         <is>
-          <t>eligibilityRowsModel, eligibilityTypes, idLookupModel, useIdLookup</t>
+          <t>guidedWizardTypes, useJourneyMilestones</t>
         </is>
       </c>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -6855,12 +6855,12 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>milestoneEngine</t>
+          <t>serviceCall</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>engines/milestoneEngine.ts</t>
+          <t>engines/serviceCall.ts</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -6878,12 +6878,12 @@
       </c>
       <c r="G14" s="17" t="inlineStr">
         <is>
-          <t>guidedWizardTypes, useJourneyMilestones</t>
+          <t>DemoFaultPanel, ValidationStatus, useIdLookup</t>
         </is>
       </c>
       <c r="H14" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -7271,7 +7271,7 @@
       <c r="G24" s="17" t="inlineStr"/>
       <c r="H24" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="H65" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>

--- a/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
+++ b/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'UI Components'!$A$1:$H$119</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Shared Code'!$A$1:$H$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Shared Code'!$A$1:$H$69</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="C9" s="17" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D9" s="17" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E9" s="17" t="n">
         <v>6</v>
@@ -855,14 +855,14 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>118 UI components + 67 non-UI files</t>
+          <t>118 UI components + 68 non-UI files</t>
         </is>
       </c>
       <c r="C13" s="18" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E13" s="18" t="n">
         <v>23</v>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="G3" s="17" t="inlineStr">
         <is>
-          <t>AdditionalDocumentsUpload, CafDocumentUpload, CompanySearchInput, ContactPhoneInput, EligibilityRows, FibreReadinessBanner, IdFileUpload, MsisdnPicker, PassportScanSections, QidImageUpload, QidInput, ScanFailureNotice, SimSerialScanner, AppointmentBookingStep, BillingAccountStep, CafSignatureCapture, DiscountCard, FixedPlanStep, OrderConfirmationScreen, PostpaidPlanAddonsStep, PostpaidPlanCard, PrepaidPlanCard, PrepaidPlanStep, RestrictedCustomerNotice, RestrictedRowsNotice, ValidationStatus, ZsbAddressStep, CustomerViewButton, StepSummarySection, WizardFooter, ChoiceCards, DataTable, IconButton, LocationInput, Pager, PhoneNumberInput, SearchField, Select, Tabs</t>
+          <t>AdditionalDocumentsUpload, CafDocumentUpload, CompanySearchInput, ContactPhoneInput, EligibilityRows, FibreReadinessBanner, IdFileUpload, MsisdnPicker, PassportScanSections, QidImageUpload, QidInput, ScanFailureNotice, SimSerialScanner, AppointmentBookingStep, BillingAccountStep, CafSignatureCapture, DiscountCard, FixedPlanStep, OrderConfirmationScreen, PostpaidPlanCard, PrepaidPlanCard, PrepaidPlanStep, RestrictedCustomerNotice, RestrictedRowsNotice, ValidationStatus, ZsbAddressStep, CustomerViewButton, StepSummarySection, WizardFooter, ChoiceCards, DataTable, IconButton, LocationInput, Pager, PhoneNumberInput, SearchField, Select, Tabs</t>
         </is>
       </c>
       <c r="H3" s="17" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="G17" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, QidInput, AppointmentBookingStep, BillingAccountStep, DiscountCard, FixedPlanStep, LineSelectionStep, PostpaidPlanAddonsStep, PostpaidPlanCard, PrepaidPlanCard, PrepaidPlanStep, ChoiceCards</t>
+          <t>MsisdnPicker, QidInput, AppointmentBookingStep, BillingAccountStep, DiscountCard, FixedPlanStep, LineSelectionStep, PostpaidPlanCard, PrepaidPlanCard, PrepaidPlanStep, ChoiceCards</t>
         </is>
       </c>
       <c r="H17" s="17" t="inlineStr">
@@ -2660,12 +2660,12 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>SignaturePad</t>
+          <t>SegmentedTabs</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/SignaturePad.tsx</t>
+          <t>components/primitives/SegmentedTabs.tsx</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -2678,14 +2678,10 @@
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
-        </is>
-      </c>
-      <c r="G24" s="17" t="inlineStr">
-        <is>
-          <t>SignatureCapture</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360, tickets</t>
+        </is>
+      </c>
+      <c r="G24" s="17" t="inlineStr"/>
       <c r="H24" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
@@ -2700,12 +2696,12 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>ConnectionTypeTag</t>
+          <t>SignaturePad</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/ConnectionTypeTag.tsx</t>
+          <t>components/primitives/SignaturePad.tsx</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -2714,21 +2710,21 @@
         </is>
       </c>
       <c r="E25" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F25" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G25" s="17" t="inlineStr">
         <is>
-          <t>FixedPlanStep, PostpaidPlanCard, PrepaidPlanCard</t>
+          <t>SignatureCapture</t>
         </is>
       </c>
       <c r="H25" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2740,12 +2736,12 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>IconButton</t>
+          <t>ConnectionTypeTag</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/IconButton.tsx</t>
+          <t>components/primitives/ConnectionTypeTag.tsx</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -2763,12 +2759,12 @@
       </c>
       <c r="G26" s="17" t="inlineStr">
         <is>
-          <t>AdditionalDocumentsUpload, CafDocumentUpload</t>
+          <t>FixedPlanStep, PostpaidPlanCard, PrepaidPlanCard</t>
         </is>
       </c>
       <c r="H26" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2776,12 @@
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>ServiceTypeTag</t>
+          <t>IconButton</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/ServiceTypeTag.tsx</t>
+          <t>components/primitives/IconButton.tsx</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -2803,12 +2799,12 @@
       </c>
       <c r="G27" s="17" t="inlineStr">
         <is>
-          <t>LineSelectionStep, ConnectionTypeTag</t>
+          <t>AdditionalDocumentsUpload, CafDocumentUpload</t>
         </is>
       </c>
       <c r="H27" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2820,12 +2816,12 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>ChoiceCards</t>
+          <t>ServiceTypeTag</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/ChoiceCards.tsx</t>
+          <t>components/primitives/ServiceTypeTag.tsx</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -2834,17 +2830,21 @@
         </is>
       </c>
       <c r="E28" s="17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, customer360</t>
-        </is>
-      </c>
-      <c r="G28" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="inlineStr">
+        <is>
+          <t>LineSelectionStep, ConnectionTypeTag</t>
+        </is>
+      </c>
       <c r="H28" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -2856,12 +2856,12 @@
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>PanelIcon</t>
+          <t>ChoiceCards</t>
         </is>
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/PanelIcon.tsx</t>
+          <t>components/primitives/ChoiceCards.tsx</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -2870,21 +2870,17 @@
         </is>
       </c>
       <c r="E29" s="17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F29" s="17" t="inlineStr">
         <is>
-          <t>trouble-ticketing-complaints, navigation, administration, customer360, orders, support</t>
-        </is>
-      </c>
-      <c r="G29" s="17" t="inlineStr">
-        <is>
-          <t>Tabs</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, customer360</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="inlineStr"/>
       <c r="H29" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -2896,12 +2892,12 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>PanelIcon</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/Radio.tsx</t>
+          <t>components/primitives/PanelIcon.tsx</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -2914,13 +2910,17 @@
       </c>
       <c r="F30" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
-        </is>
-      </c>
-      <c r="G30" s="17" t="inlineStr"/>
+          <t>trouble-ticketing-complaints, navigation, administration, customer360, orders, support</t>
+        </is>
+      </c>
+      <c r="G30" s="17" t="inlineStr">
+        <is>
+          <t>Tabs</t>
+        </is>
+      </c>
       <c r="H30" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2932,12 +2932,12 @@
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>Tabs</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/Tabs.tsx</t>
+          <t>components/primitives/Radio.tsx</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -2946,17 +2946,17 @@
         </is>
       </c>
       <c r="E31" s="17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F31" s="17" t="inlineStr">
         <is>
-          <t>trouble-ticketing-complaints, administration, customer360, orders, support</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
         </is>
       </c>
       <c r="G31" s="17" t="inlineStr"/>
       <c r="H31" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -2968,12 +2968,12 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>SegmentedTabs</t>
+          <t>Tabs</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/SegmentedTabs.tsx</t>
+          <t>components/primitives/Tabs.tsx</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -2982,11 +2982,11 @@
         </is>
       </c>
       <c r="E32" s="17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F32" s="17" t="inlineStr">
         <is>
-          <t>administration, customer360, tickets</t>
+          <t>trouble-ticketing-complaints, administration, customer360, orders, support</t>
         </is>
       </c>
       <c r="G32" s="17" t="inlineStr"/>
@@ -6312,7 +6312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.50" customWidth="1" min="1" max="1"/>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="G3" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen, agentPrivilegeEngine, agentProfileEngine, approvalAuthority, customer360VisibilityEngine, navigationEngine, personaEngine, qnomyQueueEngine, screenGrouping, configStore</t>
+          <t>agentPrivilegeEngine, agentProfileEngine, approvalAuthority, customer360VisibilityEngine, navigationEngine, personaEngine, qnomyQueueEngine, screenGrouping, configStore</t>
         </is>
       </c>
       <c r="H3" s="17" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>restrictedCustomers</t>
+          <t>personaEngine</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>engines/restrictedCustomers.ts</t>
+          <t>engines/personaEngine.ts</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -6593,17 +6593,17 @@
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, trouble-ticketing-complaints, navigation, customer360, orders, profile, support, tasks, tickets</t>
+          <t>dashboard, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, product-lines, sim-number-management, navigation, administration, customer360, orders, profile</t>
         </is>
       </c>
       <c r="G7" s="17" t="inlineStr">
         <is>
-          <t>useRestrictedCustomers</t>
+          <t>approvalAuthority, navigationEngine</t>
         </is>
       </c>
       <c r="H7" s="17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -6615,12 +6615,12 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>ruleEngine</t>
+          <t>restrictedCustomers</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>engines/ruleEngine.ts</t>
+          <t>engines/restrictedCustomers.ts</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -6633,12 +6633,12 @@
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, support</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, trouble-ticketing-complaints, navigation, customer360, orders, profile, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G8" s="17" t="inlineStr">
         <is>
-          <t>BillLimitEditor, CreditCheckPanel, eligibilityRowsModel, FixedPlanStep, TicketCreationModal</t>
+          <t>useRestrictedCustomers</t>
         </is>
       </c>
       <c r="H8" s="17" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>billingBalance</t>
+          <t>ruleEngine</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>engines/billingBalance.ts</t>
+          <t>engines/ruleEngine.ts</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -6669,21 +6669,21 @@
         </is>
       </c>
       <c r="E9" s="17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, product-lines, navigation, administration, customer-search, customer360, orders</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, support</t>
         </is>
       </c>
       <c r="G9" s="17" t="inlineStr">
         <is>
-          <t>customer360Demo, customer360Engine</t>
+          <t>BillLimitEditor, CreditCheckPanel, eligibilityRowsModel, FixedPlanStep, TicketCreationModal</t>
         </is>
       </c>
       <c r="H9" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -6695,12 +6695,12 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>customer360Engine</t>
+          <t>billingBalance</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>engines/customer360Engine.ts</t>
+          <t>engines/billingBalance.ts</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="G10" s="17" t="inlineStr">
         <is>
-          <t>customer360Demo, customerServicesEngine</t>
+          <t>customer360Demo, customer360Engine</t>
         </is>
       </c>
       <c r="H10" s="17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>customerServicesEngine</t>
+          <t>customer360Engine</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>engines/customerServicesEngine.ts</t>
+          <t>engines/customer360Engine.ts</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="G11" s="17" t="inlineStr">
         <is>
-          <t>lineSelectionModel, customer360Demo, connectionEligibility, customer360Engine</t>
+          <t>customer360Demo, customerServicesEngine</t>
         </is>
       </c>
       <c r="H11" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -6775,12 +6775,12 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>eligibilityEngine</t>
+          <t>customerServicesEngine</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>engines/eligibilityEngine.ts</t>
+          <t>engines/customerServicesEngine.ts</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -6789,21 +6789,21 @@
         </is>
       </c>
       <c r="E12" s="17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, product-lines, navigation, administration, customer-search, customer360, orders</t>
         </is>
       </c>
       <c r="G12" s="17" t="inlineStr">
         <is>
-          <t>eligibilityRowsModel, eligibilityTypes, idLookupModel, useIdLookup</t>
+          <t>lineSelectionModel, customer360Demo, connectionEligibility, customer360Engine</t>
         </is>
       </c>
       <c r="H12" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6815,12 +6815,12 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>milestoneEngine</t>
+          <t>eligibilityEngine</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>engines/milestoneEngine.ts</t>
+          <t>engines/eligibilityEngine.ts</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -6838,12 +6838,12 @@
       </c>
       <c r="G13" s="17" t="inlineStr">
         <is>
-          <t>guidedWizardTypes, useJourneyMilestones</t>
+          <t>eligibilityRowsModel, eligibilityTypes, idLookupModel, useIdLookup</t>
         </is>
       </c>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -6855,12 +6855,12 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>serviceCall</t>
+          <t>milestoneEngine</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>engines/serviceCall.ts</t>
+          <t>engines/milestoneEngine.ts</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -6878,12 +6878,12 @@
       </c>
       <c r="G14" s="17" t="inlineStr">
         <is>
-          <t>DemoFaultPanel, ValidationStatus, useIdLookup</t>
+          <t>guidedWizardTypes, useJourneyMilestones</t>
         </is>
       </c>
       <c r="H14" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>activityEngine</t>
+          <t>serviceCall</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>engines/activityEngine.ts</t>
+          <t>engines/serviceCall.ts</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -6909,21 +6909,21 @@
         </is>
       </c>
       <c r="E15" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G15" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen, useWizardDraftActions</t>
+          <t>DemoFaultPanel, ValidationStatus, useIdLookup</t>
         </is>
       </c>
       <c r="H15" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -6935,12 +6935,12 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>businessSegment</t>
+          <t>activityEngine</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>engines/businessSegment.ts</t>
+          <t>engines/activityEngine.ts</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, navigation, administration, customer-search, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G16" s="17" t="inlineStr">
         <is>
-          <t>BillingAccountStep, customer360Demo, businessAccountEngine</t>
+          <t>ActivationCompleteScreen, useWizardDraftActions</t>
         </is>
       </c>
       <c r="H16" s="17" t="inlineStr">
@@ -6975,12 +6975,12 @@
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>creditLimit</t>
+          <t>businessSegment</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>engines/creditLimit.ts</t>
+          <t>engines/businessSegment.ts</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -6993,17 +6993,17 @@
       </c>
       <c r="F17" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, navigation, administration, customer-search, customer360</t>
         </is>
       </c>
       <c r="G17" s="17" t="inlineStr">
         <is>
-          <t>CreditLimitCard, billingAccountModel</t>
+          <t>BillingAccountStep, customer360Demo, businessAccountEngine</t>
         </is>
       </c>
       <c r="H17" s="17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -7015,12 +7015,12 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>postpaidPricing</t>
+          <t>creditLimit</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>engines/postpaidPricing.ts</t>
+          <t>engines/creditLimit.ts</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -7033,17 +7033,17 @@
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, administration, customer360</t>
         </is>
       </c>
       <c r="G18" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, CheckoutDefaultLayout, PostpaidMonthlySummary, checkoutDetailedTables, checkoutSummaryRows, useCheckoutSummary, usePostpaidPlanAddons</t>
+          <t>CreditLimitCard, billingAccountModel</t>
         </is>
       </c>
       <c r="H18" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -7055,12 +7055,12 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>connectionEligibility</t>
+          <t>postpaidPricing</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>engines/connectionEligibility.ts</t>
+          <t>engines/postpaidPricing.ts</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -7069,17 +7069,21 @@
         </is>
       </c>
       <c r="E19" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F19" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+      <c r="G19" s="17" t="inlineStr">
+        <is>
+          <t>MsisdnPicker, CheckoutDefaultLayout, PostpaidMonthlySummary, checkoutDetailedTables, checkoutSummaryRows, useCheckoutSummary, usePostpaidPlanAddons</t>
+        </is>
+      </c>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -7091,12 +7095,12 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>customerBenefitEngine</t>
+          <t>connectionEligibility</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>engines/customerBenefitEngine.ts</t>
+          <t>engines/connectionEligibility.ts</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -7112,14 +7116,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
         </is>
       </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>PostpaidPlanAddonsStep, usePostpaidPlanAddons</t>
-        </is>
-      </c>
+      <c r="G20" s="17" t="inlineStr"/>
       <c r="H20" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -7131,12 +7131,12 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>addonEligibility</t>
+          <t>customerBenefitEngine</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>engines/addonEligibility.ts</t>
+          <t>engines/customerBenefitEngine.ts</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -7145,17 +7145,21 @@
         </is>
       </c>
       <c r="E21" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F21" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G21" s="17" t="inlineStr">
+        <is>
+          <t>PostpaidPlanAddonsStep, usePostpaidPlanAddons</t>
+        </is>
+      </c>
       <c r="H21" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7167,12 +7171,12 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>fibreServiceability</t>
+          <t>addonCategories</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>engines/fibreServiceability.ts</t>
+          <t>engines/addonCategories.ts</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -7188,14 +7192,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G22" s="17" t="inlineStr">
-        <is>
-          <t>FibreReadinessBanner, ActivationCompleteScreen</t>
-        </is>
-      </c>
+      <c r="G22" s="17" t="inlineStr"/>
       <c r="H22" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>uncommitted</t>
         </is>
       </c>
     </row>
@@ -7207,12 +7207,12 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>personaEngine</t>
+          <t>addonEligibility</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>engines/personaEngine.ts</t>
+          <t>engines/addonEligibility.ts</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -7225,17 +7225,13 @@
       </c>
       <c r="F23" s="17" t="inlineStr">
         <is>
-          <t>dashboard, order-management, product-lines, sim-number-management, navigation, administration, customer360, orders, profile</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr">
-        <is>
-          <t>approvalAuthority, navigationEngine</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G23" s="17" t="inlineStr"/>
       <c r="H23" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -7247,12 +7243,12 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>eligibilityGuard</t>
+          <t>fibreServiceability</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>engines/eligibilityGuard.ts</t>
+          <t>engines/fibreServiceability.ts</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -7261,17 +7257,21 @@
         </is>
       </c>
       <c r="E24" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration</t>
-        </is>
-      </c>
-      <c r="G24" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G24" s="17" t="inlineStr">
+        <is>
+          <t>FibreReadinessBanner, ActivationCompleteScreen</t>
+        </is>
+      </c>
       <c r="H24" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -7283,12 +7283,12 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>serviceLocationLookup</t>
+          <t>eligibilityGuard</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>engines/serviceLocationLookup.ts</t>
+          <t>engines/eligibilityGuard.ts</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -7301,17 +7301,13 @@
       </c>
       <c r="F25" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="inlineStr">
-        <is>
-          <t>ZsbAddressStep</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="inlineStr"/>
       <c r="H25" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -7323,12 +7319,12 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>agentTaskEngine</t>
+          <t>serviceLocationLookup</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>engines/agentTaskEngine.ts</t>
+          <t>engines/serviceLocationLookup.ts</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -7337,17 +7333,21 @@
         </is>
       </c>
       <c r="E26" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>dashboard, order-management, trouble-ticketing-complaints, orders, support, tasks</t>
-        </is>
-      </c>
-      <c r="G26" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="inlineStr">
+        <is>
+          <t>ZsbAddressStep</t>
+        </is>
+      </c>
       <c r="H26" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7359,12 +7359,12 @@
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>approvalAuthority</t>
+          <t>agentTaskEngine</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
-          <t>engines/approvalAuthority.ts</t>
+          <t>engines/agentTaskEngine.ts</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -7377,13 +7377,13 @@
       </c>
       <c r="F27" s="17" t="inlineStr">
         <is>
-          <t>dashboard, order-management, sim-number-management, navigation, customer360, orders</t>
+          <t>dashboard, order-management, trouble-ticketing-complaints, orders, support, tasks</t>
         </is>
       </c>
       <c r="G27" s="17" t="inlineStr"/>
       <c r="H27" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7395,12 +7395,12 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>portInEngine</t>
+          <t>approvalAuthority</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>engines/portInEngine.ts</t>
+          <t>engines/approvalAuthority.ts</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -7413,13 +7413,13 @@
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
+          <t>dashboard, order-management, sim-number-management, navigation, customer360, orders</t>
         </is>
       </c>
       <c r="G28" s="17" t="inlineStr"/>
       <c r="H28" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7431,12 +7431,12 @@
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>csvExport</t>
+          <t>portInEngine</t>
         </is>
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>engines/csvExport.ts</t>
+          <t>engines/portInEngine.ts</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -7445,17 +7445,17 @@
         </is>
       </c>
       <c r="E29" s="17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F29" s="17" t="inlineStr">
         <is>
-          <t>trouble-ticketing-complaints, customer360, profile, support</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
         </is>
       </c>
       <c r="G29" s="17" t="inlineStr"/>
       <c r="H29" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>bellNotificationExpiry</t>
+          <t>csvExport</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>engines/bellNotificationExpiry.ts</t>
+          <t>engines/csvExport.ts</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -7481,11 +7481,11 @@
         </is>
       </c>
       <c r="E30" s="17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F30" s="17" t="inlineStr">
         <is>
-          <t>administration, customer360</t>
+          <t>trouble-ticketing-complaints, customer360, profile, support</t>
         </is>
       </c>
       <c r="G30" s="17" t="inlineStr"/>
@@ -7503,12 +7503,12 @@
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>businessAccountEngine</t>
+          <t>bellNotificationExpiry</t>
         </is>
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>engines/businessAccountEngine.ts</t>
+          <t>engines/bellNotificationExpiry.ts</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -7521,13 +7521,13 @@
       </c>
       <c r="F31" s="17" t="inlineStr">
         <is>
-          <t>customer-search, customer360</t>
+          <t>administration, customer360</t>
         </is>
       </c>
       <c r="G31" s="17" t="inlineStr"/>
       <c r="H31" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7539,12 +7539,12 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>navigationEngine</t>
+          <t>businessAccountEngine</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>engines/navigationEngine.ts</t>
+          <t>engines/businessAccountEngine.ts</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -7557,13 +7557,13 @@
       </c>
       <c r="F32" s="17" t="inlineStr">
         <is>
-          <t>navigation, customer360</t>
+          <t>customer-search, customer360</t>
         </is>
       </c>
       <c r="G32" s="17" t="inlineStr"/>
       <c r="H32" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -7575,12 +7575,12 @@
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>qnomyQueueEngine</t>
+          <t>navigationEngine</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>engines/qnomyQueueEngine.ts</t>
+          <t>engines/navigationEngine.ts</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -7593,17 +7593,13 @@
       </c>
       <c r="F33" s="17" t="inlineStr">
         <is>
-          <t>navigation, tickets</t>
-        </is>
-      </c>
-      <c r="G33" s="17" t="inlineStr">
-        <is>
-          <t>qnomyWalkIns</t>
-        </is>
-      </c>
+          <t>navigation, customer360</t>
+        </is>
+      </c>
+      <c r="G33" s="17" t="inlineStr"/>
       <c r="H33" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -7615,31 +7611,35 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>agentProfileEngine</t>
+          <t>qnomyQueueEngine</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>engines/agentProfileEngine.ts</t>
-        </is>
-      </c>
-      <c r="D34" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>engines/qnomyQueueEngine.ts</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E34" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="G34" s="17" t="inlineStr"/>
+          <t>navigation, tickets</t>
+        </is>
+      </c>
+      <c r="G34" s="17" t="inlineStr">
+        <is>
+          <t>qnomyWalkIns</t>
+        </is>
+      </c>
       <c r="H34" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7651,12 +7651,12 @@
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>customer360VisibilityEngine</t>
+          <t>agentProfileEngine</t>
         </is>
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
-          <t>engines/customer360VisibilityEngine.ts</t>
+          <t>engines/agentProfileEngine.ts</t>
         </is>
       </c>
       <c r="D35" s="21" t="inlineStr">
@@ -7669,13 +7669,13 @@
       </c>
       <c r="F35" s="17" t="inlineStr">
         <is>
-          <t>customer360</t>
+          <t>navigation</t>
         </is>
       </c>
       <c r="G35" s="17" t="inlineStr"/>
       <c r="H35" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7687,12 +7687,12 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>profileChangeTicket</t>
+          <t>customer360VisibilityEngine</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>engines/profileChangeTicket.ts</t>
+          <t>engines/customer360VisibilityEngine.ts</t>
         </is>
       </c>
       <c r="D36" s="21" t="inlineStr">
@@ -7711,7 +7711,7 @@
       <c r="G36" s="17" t="inlineStr"/>
       <c r="H36" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7723,12 +7723,12 @@
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>qnomyWalkIns</t>
+          <t>profileChangeTicket</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>engines/qnomyWalkIns.ts</t>
+          <t>engines/profileChangeTicket.ts</t>
         </is>
       </c>
       <c r="D37" s="21" t="inlineStr">
@@ -7741,13 +7741,13 @@
       </c>
       <c r="F37" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
+          <t>customer360</t>
         </is>
       </c>
       <c r="G37" s="17" t="inlineStr"/>
       <c r="H37" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -7759,12 +7759,12 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>roleSwitchPurge</t>
+          <t>qnomyWalkIns</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>engines/roleSwitchPurge.ts</t>
+          <t>engines/qnomyWalkIns.ts</t>
         </is>
       </c>
       <c r="D38" s="21" t="inlineStr">
@@ -7783,7 +7783,7 @@
       <c r="G38" s="17" t="inlineStr"/>
       <c r="H38" s="17" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>searchScopeEngine</t>
+          <t>roleSwitchPurge</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>engines/searchScopeEngine.ts</t>
+          <t>engines/roleSwitchPurge.ts</t>
         </is>
       </c>
       <c r="D39" s="21" t="inlineStr">
@@ -7819,7 +7819,7 @@
       <c r="G39" s="17" t="inlineStr"/>
       <c r="H39" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -7831,27 +7831,31 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>moduleDescriptions</t>
+          <t>searchScopeEngine</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>engines/moduleDescriptions.ts</t>
-        </is>
-      </c>
-      <c r="D40" s="23" t="inlineStr">
-        <is>
-          <t>App shell only</t>
+          <t>engines/searchScopeEngine.ts</t>
+        </is>
+      </c>
+      <c r="D40" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E40" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F40" s="17" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
       <c r="G40" s="17" t="inlineStr"/>
       <c r="H40" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -7863,12 +7867,12 @@
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>screenGrouping</t>
+          <t>moduleDescriptions</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>engines/screenGrouping.ts</t>
+          <t>engines/moduleDescriptions.ts</t>
         </is>
       </c>
       <c r="D41" s="23" t="inlineStr">
@@ -7890,40 +7894,32 @@
     <row r="42">
       <c r="A42" s="17" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Engine</t>
         </is>
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>customerContextStore</t>
+          <t>screenGrouping</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>stores/customerContextStore.ts</t>
-        </is>
-      </c>
-      <c r="D42" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>engines/screenGrouping.ts</t>
+        </is>
+      </c>
+      <c r="D42" s="23" t="inlineStr">
+        <is>
+          <t>App shell only</t>
         </is>
       </c>
       <c r="E42" s="17" t="n">
-        <v>25</v>
-      </c>
-      <c r="F42" s="17" t="inlineStr">
-        <is>
-          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
-        </is>
-      </c>
-      <c r="G42" s="17" t="inlineStr">
-        <is>
-          <t>ActivationCompleteScreen, useActedForCustomer, useWizardDraftActions, roleSwitchPurge, authStore</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F42" s="17" t="inlineStr"/>
+      <c r="G42" s="17" t="inlineStr"/>
       <c r="H42" s="17" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7935,12 +7931,12 @@
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>authStore</t>
+          <t>customerContextStore</t>
         </is>
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>stores/authStore.ts</t>
+          <t>stores/customerContextStore.ts</t>
         </is>
       </c>
       <c r="D43" s="20" t="inlineStr">
@@ -7949,21 +7945,21 @@
         </is>
       </c>
       <c r="E43" s="17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F43" s="17" t="inlineStr">
         <is>
-          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, sales, support, tasks, tickets</t>
+          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G43" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, ActivationCompleteScreen, useWizardDraftActions, activityEngine, agentProfileEngine, profileChangeTicket, configStore, entityStore</t>
+          <t>ActivationCompleteScreen, useActedForCustomer, useWizardDraftActions, roleSwitchPurge, authStore</t>
         </is>
       </c>
       <c r="H43" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -7975,12 +7971,12 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>entityStore</t>
+          <t>authStore</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>stores/entityStore.ts</t>
+          <t>stores/authStore.ts</t>
         </is>
       </c>
       <c r="D44" s="20" t="inlineStr">
@@ -7998,12 +7994,12 @@
       </c>
       <c r="G44" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen, DonorAttachmentStep, DonorDetailsStep, useIdLookup, useDraftStepSync, useWizardDraftActions, activityEngine, bellNotificationExpiry, profileChangeTicket</t>
+          <t>MsisdnPicker, ActivationCompleteScreen, useWizardDraftActions, activityEngine, agentProfileEngine, profileChangeTicket, configStore, entityStore</t>
         </is>
       </c>
       <c r="H44" s="17" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8011,12 @@
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>personaStore</t>
+          <t>entityStore</t>
         </is>
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>stores/personaStore.ts</t>
+          <t>stores/entityStore.ts</t>
         </is>
       </c>
       <c r="D45" s="20" t="inlineStr">
@@ -8029,21 +8025,21 @@
         </is>
       </c>
       <c r="E45" s="17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F45" s="17" t="inlineStr">
         <is>
-          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, support, tasks, tickets</t>
+          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G45" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, eligibilityRowsModel, ActivationCompleteScreen, AppointmentBookingStep, TicketCreationModal, useCheckoutSummary, useIdLookup, useRestrictedCustomers, configStore</t>
+          <t>ActivationCompleteScreen, DonorAttachmentStep, DonorDetailsStep, useIdLookup, useDraftStepSync, useWizardDraftActions, activityEngine, bellNotificationExpiry, profileChangeTicket</t>
         </is>
       </c>
       <c r="H45" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -8055,12 +8051,12 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>notificationStore</t>
+          <t>personaStore</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>stores/notificationStore.ts</t>
+          <t>stores/personaStore.ts</t>
         </is>
       </c>
       <c r="D46" s="20" t="inlineStr">
@@ -8069,21 +8065,21 @@
         </is>
       </c>
       <c r="E46" s="17" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F46" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, profile, support, tasks</t>
+          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G46" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, ActivationCompleteScreen, TicketCreationModal, useJourneyMilestones, useWizardDraftActions, useWizardStepNavigation, profileChangeTicket, roleSwitchPurge, useSubmit</t>
+          <t>MsisdnPicker, eligibilityRowsModel, AppointmentBookingStep, TicketCreationModal, useCheckoutSummary, useIdLookup, useRestrictedCustomers, configStore</t>
         </is>
       </c>
       <c r="H46" s="17" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8095,12 +8091,12 @@
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>workflowStore</t>
+          <t>notificationStore</t>
         </is>
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>stores/workflowStore.ts</t>
+          <t>stores/notificationStore.ts</t>
         </is>
       </c>
       <c r="D47" s="20" t="inlineStr">
@@ -8109,21 +8105,21 @@
         </is>
       </c>
       <c r="E47" s="17" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F47" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, profile, support, tasks</t>
         </is>
       </c>
       <c r="G47" s="17" t="inlineStr">
         <is>
-          <t>useJourneyStartResume, useMirrorChannel, useWizardDraftActions, useWizardStepNavigation, roleSwitchPurge</t>
+          <t>MsisdnPicker, ActivationCompleteScreen, TicketCreationModal, useJourneyMilestones, useWizardDraftActions, useWizardStepNavigation, profileChangeTicket, roleSwitchPurge, useSubmit</t>
         </is>
       </c>
       <c r="H47" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -8135,35 +8131,35 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>customerVerificationStore</t>
+          <t>workflowStore</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>stores/customerVerificationStore.ts</t>
-        </is>
-      </c>
-      <c r="D48" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>stores/workflowStore.ts</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E48" s="17" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F48" s="17" t="inlineStr">
         <is>
-          <t>customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration</t>
         </is>
       </c>
       <c r="G48" s="17" t="inlineStr">
         <is>
-          <t>VerificationGate</t>
+          <t>useJourneyStartResume, useMirrorChannel, useWizardDraftActions, useWizardStepNavigation, roleSwitchPurge</t>
         </is>
       </c>
       <c r="H48" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8175,12 +8171,12 @@
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>qnomyQueueStore</t>
+          <t>customerVerificationStore</t>
         </is>
       </c>
       <c r="C49" s="17" t="inlineStr">
         <is>
-          <t>stores/qnomyQueueStore.ts</t>
+          <t>stores/customerVerificationStore.ts</t>
         </is>
       </c>
       <c r="D49" s="21" t="inlineStr">
@@ -8193,13 +8189,17 @@
       </c>
       <c r="F49" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="G49" s="17" t="inlineStr"/>
+          <t>customer360</t>
+        </is>
+      </c>
+      <c r="G49" s="17" t="inlineStr">
+        <is>
+          <t>VerificationGate</t>
+        </is>
+      </c>
       <c r="H49" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -8211,12 +8211,12 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>regionStore</t>
+          <t>qnomyQueueStore</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>stores/regionStore.ts</t>
+          <t>stores/qnomyQueueStore.ts</t>
         </is>
       </c>
       <c r="D50" s="21" t="inlineStr">
@@ -8235,7 +8235,7 @@
       <c r="G50" s="17" t="inlineStr"/>
       <c r="H50" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -8247,12 +8247,12 @@
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>sidebarStore</t>
+          <t>regionStore</t>
         </is>
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>stores/sidebarStore.ts</t>
+          <t>stores/regionStore.ts</t>
         </is>
       </c>
       <c r="D51" s="21" t="inlineStr">
@@ -8271,7 +8271,7 @@
       <c r="G51" s="17" t="inlineStr"/>
       <c r="H51" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -8283,12 +8283,12 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>themeStore</t>
+          <t>sidebarStore</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>stores/themeStore.ts</t>
+          <t>stores/sidebarStore.ts</t>
         </is>
       </c>
       <c r="D52" s="21" t="inlineStr">
@@ -8307,7 +8307,7 @@
       <c r="G52" s="17" t="inlineStr"/>
       <c r="H52" s="17" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8319,67 +8319,63 @@
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>configStore</t>
+          <t>themeStore</t>
         </is>
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>stores/configStore.ts</t>
-        </is>
-      </c>
-      <c r="D53" s="23" t="inlineStr">
-        <is>
-          <t>App shell only</t>
+          <t>stores/themeStore.ts</t>
+        </is>
+      </c>
+      <c r="D53" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E53" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F53" s="17" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
       <c r="G53" s="17" t="inlineStr"/>
       <c r="H53" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="17" t="inlineStr">
         <is>
-          <t>Hook</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>useRestrictedCustomers</t>
+          <t>configStore</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>hooks/useRestrictedCustomers.ts</t>
-        </is>
-      </c>
-      <c r="D54" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>stores/configStore.ts</t>
+        </is>
+      </c>
+      <c r="D54" s="23" t="inlineStr">
+        <is>
+          <t>App shell only</t>
         </is>
       </c>
       <c r="E54" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="F54" s="17" t="inlineStr">
-        <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, trouble-ticketing-complaints, navigation, customer360, orders, profile, support, tasks, tickets</t>
-        </is>
-      </c>
-      <c r="G54" s="17" t="inlineStr">
-        <is>
-          <t>TicketCreationModal</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F54" s="17" t="inlineStr"/>
+      <c r="G54" s="17" t="inlineStr"/>
       <c r="H54" s="17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8391,12 +8387,12 @@
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>useEnterToSubmit</t>
+          <t>useRestrictedCustomers</t>
         </is>
       </c>
       <c r="C55" s="17" t="inlineStr">
         <is>
-          <t>hooks/useEnterToSubmit.ts</t>
+          <t>hooks/useRestrictedCustomers.ts</t>
         </is>
       </c>
       <c r="D55" s="20" t="inlineStr">
@@ -8405,21 +8401,21 @@
         </is>
       </c>
       <c r="E55" s="17" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F55" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, trouble-ticketing-complaints, navigation, customer360, orders, profile, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G55" s="17" t="inlineStr">
         <is>
-          <t>VerificationGate, useIdLookup</t>
+          <t>TicketCreationModal</t>
         </is>
       </c>
       <c r="H55" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -8431,12 +8427,12 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>useSearchListNav</t>
+          <t>useEnterToSubmit</t>
         </is>
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t>hooks/useSearchListNav.ts</t>
+          <t>hooks/useEnterToSubmit.ts</t>
         </is>
       </c>
       <c r="D56" s="20" t="inlineStr">
@@ -8449,17 +8445,17 @@
       </c>
       <c r="F56" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, navigation, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G56" s="17" t="inlineStr">
         <is>
-          <t>CompanySearchInput, ContactPhoneInput, PlanSearchBox, LocationInput</t>
+          <t>VerificationGate, useIdLookup</t>
         </is>
       </c>
       <c r="H56" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -8471,12 +8467,12 @@
       </c>
       <c r="B57" s="17" t="inlineStr">
         <is>
-          <t>useAreaOptions</t>
+          <t>useSearchListNav</t>
         </is>
       </c>
       <c r="C57" s="17" t="inlineStr">
         <is>
-          <t>hooks/useAreaOptions.ts</t>
+          <t>hooks/useSearchListNav.ts</t>
         </is>
       </c>
       <c r="D57" s="20" t="inlineStr">
@@ -8485,21 +8481,21 @@
         </is>
       </c>
       <c r="E57" s="17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F57" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, navigation, administration, customer360</t>
         </is>
       </c>
       <c r="G57" s="17" t="inlineStr">
         <is>
-          <t>BillingAccountStep, ZsbAddressStep</t>
+          <t>CompanySearchInput, ContactPhoneInput, PlanSearchBox, LocationInput</t>
         </is>
       </c>
       <c r="H57" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -8511,12 +8507,12 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>useSubmit</t>
+          <t>useAreaOptions</t>
         </is>
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t>hooks/useSubmit.ts</t>
+          <t>hooks/useAreaOptions.ts</t>
         </is>
       </c>
       <c r="D58" s="20" t="inlineStr">
@@ -8525,17 +8521,21 @@
         </is>
       </c>
       <c r="E58" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F58" s="17" t="inlineStr">
         <is>
-          <t>lead-management, mnp-fnp-porting, sim-number-management, trouble-ticketing-complaints, customer360, tasks</t>
-        </is>
-      </c>
-      <c r="G58" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G58" s="17" t="inlineStr">
+        <is>
+          <t>BillingAccountStep, ZsbAddressStep</t>
+        </is>
+      </c>
       <c r="H58" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8547,68 +8547,64 @@
       </c>
       <c r="B59" s="17" t="inlineStr">
         <is>
-          <t>useMinWidth</t>
+          <t>useSubmit</t>
         </is>
       </c>
       <c r="C59" s="17" t="inlineStr">
         <is>
-          <t>hooks/useMinWidth.ts</t>
-        </is>
-      </c>
-      <c r="D59" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>hooks/useSubmit.ts</t>
+        </is>
+      </c>
+      <c r="D59" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E59" s="17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F59" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
+          <t>lead-management, mnp-fnp-porting, sim-number-management, trouble-ticketing-complaints, customer360, tasks</t>
         </is>
       </c>
       <c r="G59" s="17" t="inlineStr"/>
       <c r="H59" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="17" t="inlineStr">
         <is>
-          <t>Helper</t>
+          <t>Hook</t>
         </is>
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>statusTone</t>
+          <t>useMinWidth</t>
         </is>
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t>lib/statusTone.ts</t>
-        </is>
-      </c>
-      <c r="D60" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>hooks/useMinWidth.ts</t>
+        </is>
+      </c>
+      <c r="D60" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E60" s="17" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F60" s="17" t="inlineStr">
         <is>
-          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, orders, sales, support, tasks, tickets</t>
-        </is>
-      </c>
-      <c r="G60" s="17" t="inlineStr">
-        <is>
-          <t>ruleEngine</t>
-        </is>
-      </c>
+          <t>navigation</t>
+        </is>
+      </c>
+      <c r="G60" s="17" t="inlineStr"/>
       <c r="H60" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
@@ -8623,12 +8619,12 @@
       </c>
       <c r="B61" s="17" t="inlineStr">
         <is>
-          <t>format</t>
+          <t>statusTone</t>
         </is>
       </c>
       <c r="C61" s="17" t="inlineStr">
         <is>
-          <t>lib/format.ts</t>
+          <t>lib/statusTone.ts</t>
         </is>
       </c>
       <c r="D61" s="20" t="inlineStr">
@@ -8637,21 +8633,21 @@
         </is>
       </c>
       <c r="E61" s="17" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F61" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, tasks</t>
+          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, orders, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G61" s="17" t="inlineStr">
         <is>
-          <t>AdditionalDocumentsUpload, CafDocumentUpload, MsisdnPicker, GuidedContactStep, IdLookupStep, StepSummaryPanel, stepSummary, customer360Engine, postpaidPricing</t>
+          <t>ruleEngine</t>
         </is>
       </c>
       <c r="H61" s="17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8663,12 +8659,12 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>buildEnv</t>
+          <t>format</t>
         </is>
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t>lib/buildEnv.ts</t>
+          <t>lib/format.ts</t>
         </is>
       </c>
       <c r="D62" s="20" t="inlineStr">
@@ -8677,21 +8673,21 @@
         </is>
       </c>
       <c r="E62" s="17" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F62" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, tasks</t>
         </is>
       </c>
       <c r="G62" s="17" t="inlineStr">
         <is>
-          <t>syntheticMarker, navigationEngine</t>
+          <t>AdditionalDocumentsUpload, CafDocumentUpload, MsisdnPicker, GuidedContactStep, IdLookupStep, StepSummaryPanel, stepSummary, customer360Engine, postpaidPricing</t>
         </is>
       </c>
       <c r="H62" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -8703,12 +8699,12 @@
       </c>
       <c r="B63" s="17" t="inlineStr">
         <is>
-          <t>deviceType</t>
+          <t>buildEnv</t>
         </is>
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>lib/deviceType.ts</t>
+          <t>lib/buildEnv.ts</t>
         </is>
       </c>
       <c r="D63" s="20" t="inlineStr">
@@ -8717,21 +8713,21 @@
         </is>
       </c>
       <c r="E63" s="17" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F63" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360</t>
         </is>
       </c>
       <c r="G63" s="17" t="inlineStr">
         <is>
-          <t>IdFileUpload, PassportScanSections, SimSerialScanner, SimTypeStep, cafTypes</t>
+          <t>syntheticMarker, navigationEngine</t>
         </is>
       </c>
       <c r="H63" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -8743,12 +8739,12 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>taskId</t>
+          <t>deviceType</t>
         </is>
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
-          <t>lib/taskId.ts</t>
+          <t>lib/deviceType.ts</t>
         </is>
       </c>
       <c r="D64" s="20" t="inlineStr">
@@ -8757,16 +8753,16 @@
         </is>
       </c>
       <c r="E64" s="17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F64" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration, customer360</t>
         </is>
       </c>
       <c r="G64" s="17" t="inlineStr">
         <is>
-          <t>useWizardDraftActions</t>
+          <t>IdFileUpload, PassportScanSections, SimSerialScanner, SimTypeStep, cafTypes</t>
         </is>
       </c>
       <c r="H64" s="17" t="inlineStr">
@@ -8783,12 +8779,12 @@
       </c>
       <c r="B65" s="17" t="inlineStr">
         <is>
-          <t>connectionType</t>
+          <t>taskId</t>
         </is>
       </c>
       <c r="C65" s="17" t="inlineStr">
         <is>
-          <t>lib/connectionType.ts</t>
+          <t>lib/taskId.ts</t>
         </is>
       </c>
       <c r="D65" s="20" t="inlineStr">
@@ -8797,21 +8793,21 @@
         </is>
       </c>
       <c r="E65" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F65" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G65" s="17" t="inlineStr">
         <is>
-          <t>ConnectionTypeTag</t>
+          <t>useWizardDraftActions</t>
         </is>
       </c>
       <c r="H65" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8823,12 +8819,12 @@
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>serviceTypeTag</t>
+          <t>connectionType</t>
         </is>
       </c>
       <c r="C66" s="17" t="inlineStr">
         <is>
-          <t>lib/serviceTypeTag.ts</t>
+          <t>lib/connectionType.ts</t>
         </is>
       </c>
       <c r="D66" s="20" t="inlineStr">
@@ -8846,12 +8842,12 @@
       </c>
       <c r="G66" s="17" t="inlineStr">
         <is>
-          <t>ServiceTypeTag</t>
+          <t>ConnectionTypeTag</t>
         </is>
       </c>
       <c r="H66" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -8863,31 +8859,35 @@
       </c>
       <c r="B67" s="17" t="inlineStr">
         <is>
-          <t>screenName</t>
+          <t>serviceTypeTag</t>
         </is>
       </c>
       <c r="C67" s="17" t="inlineStr">
         <is>
-          <t>lib/screenName.ts</t>
-        </is>
-      </c>
-      <c r="D67" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>lib/serviceTypeTag.ts</t>
+        </is>
+      </c>
+      <c r="D67" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E67" s="17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F67" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="G67" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G67" s="17" t="inlineStr">
+        <is>
+          <t>ServiceTypeTag</t>
+        </is>
+      </c>
       <c r="H67" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>values</t>
+          <t>screenName</t>
         </is>
       </c>
       <c r="C68" s="17" t="inlineStr">
         <is>
-          <t>lib/values.ts</t>
+          <t>lib/screenName.ts</t>
         </is>
       </c>
       <c r="D68" s="21" t="inlineStr">
@@ -8917,22 +8917,58 @@
       </c>
       <c r="F68" s="17" t="inlineStr">
         <is>
+          <t>navigation</t>
+        </is>
+      </c>
+      <c r="G68" s="17" t="inlineStr"/>
+      <c r="H68" s="17" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="17" t="inlineStr">
+        <is>
+          <t>Helper</t>
+        </is>
+      </c>
+      <c r="B69" s="17" t="inlineStr">
+        <is>
+          <t>values</t>
+        </is>
+      </c>
+      <c r="C69" s="17" t="inlineStr">
+        <is>
+          <t>lib/values.ts</t>
+        </is>
+      </c>
+      <c r="D69" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
+        </is>
+      </c>
+      <c r="E69" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" s="17" t="inlineStr">
+        <is>
           <t>customer360</t>
         </is>
       </c>
-      <c r="G68" s="17" t="inlineStr">
+      <c r="G69" s="17" t="inlineStr">
         <is>
           <t>customer360Demo</t>
         </is>
       </c>
-      <c r="H68" s="17" t="inlineStr">
+      <c r="H69" s="17" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H68"/>
+  <autoFilter ref="A1:H69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
+++ b/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
@@ -14,8 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Method" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'UI Components'!$A$1:$H$119</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Shared Code'!$A$1:$H$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'UI Components'!$A$1:$H$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Shared Code'!$A$1:$H$70</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="C5" s="17" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D5" s="17" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E5" s="17" t="n">
         <v>2</v>
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="C9" s="17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D9" s="17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E9" s="17" t="n">
         <v>6</v>
@@ -855,14 +855,14 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>118 UI components + 68 non-UI files</t>
+          <t>120 UI components + 69 non-UI files</t>
         </is>
       </c>
       <c r="C13" s="18" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E13" s="18" t="n">
         <v>23</v>
@@ -887,11 +887,11 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>25 named - see the Capabilities sheet</t>
+          <t>27 named - see the Capabilities sheet</t>
         </is>
       </c>
       <c r="C15" s="17" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D15" s="17" t="inlineStr"/>
       <c r="E15" s="17" t="inlineStr"/>
@@ -908,7 +908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.80" customWidth="1" min="1" max="1"/>
@@ -1018,15 +1018,43 @@
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
+          <t>Document Upload</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>The one way to attach documents to an order: Additional Documents (choose the document type, then the file; a type is not offered twice; a document type picked without its file blocks Continue), the signed-CAF upload, and the shared rules every upload reads (accepted types, size limit, refusal wording) so a limit is changed once. Used by the CAF step; the identity-document upload reads the same rules.</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>capabilities/DocumentUpload/index.ts
+components/domain/AdditionalDocumentsUpload.tsx
+components/domain/CafDocumentUpload.tsx
+components/domain/documentUploadRules.ts</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
           <t>Special Discounts Identification</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>The Special Discounts section of Mobile Postpaid Activation as its own capability: choose Consumer B2B2C, Retiree or MADA, supply the evidence (company, ID number, Office ID scan or upload) and accept or reject the benefit. Independent of Customer Verification and Customer Type; always offers both Initiate scan and Upload document.</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>capabilities/SpecialDiscountsIdentification/CompanySearchInput.tsx
 capabilities/SpecialDiscountsIdentification/IdFileUpload.tsx
@@ -1053,53 +1081,53 @@
 capabilities/SpecialDiscountsIdentification/specialDiscountsModel.ts</t>
         </is>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D5" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>Guided activation wizard</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>The step shell every activation / migration / port-in journey runs in.</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>capabilities/GuidedActivationWizard/GuidedActivationWizard.tsx
 capabilities/GuidedActivationWizard/index.ts</t>
         </is>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D6" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>Customer Type &amp; Discounts</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>Special customer types (retired, MADA, B2B2C): the evidence the agent collects, the rules for accepting or rejecting the benefit, and the customer's benefits.</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>capabilities/CustomerType/CustomerTypeStep.tsx
 capabilities/CustomerType/customerTypeModel.ts
@@ -1108,27 +1136,27 @@
 components/domain/CompanySearchInput.tsx</t>
         </is>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D7" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, administration, customer360</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Eligibility gate</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Hard-stop / soft-stop / pass eligibility check shown after identification, with the outcome panel, checks report and footer actions.</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>capabilities/EligibilityGate/EligibilityGateStep.tsx
 capabilities/EligibilityGate/EligibilityOutcomes.tsx
@@ -1136,27 +1164,27 @@
 capabilities/EligibilityGate/index.ts</t>
         </is>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D8" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Cross-Sell Offers</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>Recommended offers for the identified customer: offer cards, details drawer, interested (lead) and select actions, and hand-off to the other journeys.</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>capabilities/CrossSellOffers/CrossSalesStep.tsx
 capabilities/CrossSellOffers/HandOff.tsx
@@ -1169,27 +1197,27 @@
 capabilities/CrossSellOffers/summary.ts</t>
         </is>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D9" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>SIM Type</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>Choose and validate the SIM: Physical (scan or enter the serial) or eSIM (issued, handed over after payment).</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>capabilities/SimType/SimSerial.tsx
 capabilities/SimType/SimType.tsx
@@ -1200,29 +1228,30 @@
 components/domain/SimSerialScanner.tsx</t>
         </is>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D10" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Number Selection</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Choose a number: search, Free and Star bands, price filter, plan entitlement note, reserve and clear.</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>capabilities/NumberSelection/NumberSelection.tsx
+capabilities/NumberSelection/WaiveOff.tsx
 capabilities/NumberSelection/index.ts
 capabilities/NumberSelection/step.tsx
 capabilities/NumberSelection/summary.ts
@@ -1230,27 +1259,27 @@
 components/domain/msisdnPickerModel.ts</t>
         </is>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D11" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>Billing Account</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>Set up what an order bills to: one layout everywhere - the customer's existing billing accounts, or Create New Billing Account (contact, billing address, payment, card on file, primary payment profile, billing profile setup).</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>capabilities/BillingAccount/BillingAccount.tsx
 capabilities/BillingAccount/index.ts
@@ -1263,27 +1292,27 @@
 components/patterns/billingAccountModel.ts</t>
         </is>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D12" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>Plan Selection</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>Choose the plan: postpaid plan cards then Add-ons (discounts, bill limit), prepaid packs then Add-ons, or the fixed-line / fibre plan cards with the credit check. The line's current plan or pack can be left out of the choices when a journey changes it.</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>capabilities/PlanSelection/PlanSelection.tsx
 capabilities/PlanSelection/index.ts
@@ -1297,27 +1326,27 @@
 components/patterns/PlanGroupPanel.tsx</t>
         </is>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D13" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>CAF &amp; Signature</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>The Customer Agreement Form: terms, CAF type, signature and supporting documents. Standard variant (name, key information, signature) and full variant (the customer reads back the Checkout Summary order, agrees the terms and signs; the journey locks once signed); postpaid and prepaid forms.</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>capabilities/CafSignature/CafSignature.tsx
 capabilities/CafSignature/index.ts
@@ -1328,27 +1357,27 @@
 components/patterns/cafTypes.ts</t>
         </is>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D14" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>Checkout Summary</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>The order read-back before signing and payment (plan, add-ons, discount, number, billing, monthly and one-off totals); publishes the totals and read-back rows the CAF and Payment reuse. An optional panel above it (the port-in validation gate). Includes the prepaid cart (Add another subscription) and the prepaid checkout, which a prepaid port-in also uses with its own lines, details and fees.</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>capabilities/CheckoutSummary/CheckoutSummary.tsx
 capabilities/CheckoutSummary/PrepaidCartBody.tsx
@@ -1367,27 +1396,27 @@
 components/patterns/prepaidCartModel.ts</t>
         </is>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D15" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>Payment</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>Take the amount due at the counter through WinCash and record the outcome.</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>capabilities/Payment/Payment.tsx
 capabilities/Payment/index.ts
@@ -1395,27 +1424,27 @@
 components/patterns/WinCashPaymentStep.tsx</t>
         </is>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D16" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>Activation Complete</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>The confirmation page for a submitted activation (facts, status, follow-on actions, eSIM handover, email) and the confirmed-order shape journeys hand it.</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>capabilities/ActivationComplete/ActivationComplete.tsx
 capabilities/ActivationComplete/confirmedOrder.ts
@@ -1424,54 +1453,54 @@
 components/patterns/OrderConfirmationScreen.tsx</t>
         </is>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D17" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>Add-ons selection</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>Add-on rows for a plan or prepaid pack, with included-benefit handling; on its own (Add Add-On) as a step that needs at least one add-on.</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>capabilities/AddonsSelection/AddonsPicker.tsx
 capabilities/AddonsSelection/index.ts
 capabilities/AddonsSelection/step.tsx</t>
         </is>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D18" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>Customer Qualification</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>Identify the customer, run eligibility, then offer the special-discount types - the whole "Customer Verification" step of an activation, with its outcomes and footer actions.</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>capabilities/CustomerQualification/JourneyBanners.tsx
 capabilities/CustomerQualification/index.ts
@@ -1479,27 +1508,27 @@
 capabilities/CustomerQualification/summary.ts</t>
         </is>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D19" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>Actual User</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>Who will use the line when it is not the customer who owns it: the agent adds an actual user, who is identified like the primary customer (ID type, scan or upload, MOI, email, phone). The actual user is named on the Supplementary Form, which the one CAF signature also signs; an existing customer's changed email is written back to their record.</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>capabilities/ActualUser/ActualUser.tsx
 capabilities/ActualUser/actualUserModel.ts
@@ -1510,27 +1539,27 @@
 capabilities/ActualUser/useDemoReaderCustomer.ts</t>
         </is>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D20" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>Service Address</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>The address a service is activated at: one layout everywhere: Service Information (Kahramaa Meter ID / Vodafone Premise ID with Search), then Zone / Street / Building, then Additional Details, with Qatari-ID prefill.</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>capabilities/ServiceAddress/AddressPrefill.tsx
 capabilities/ServiceAddress/ServiceAddress.tsx
@@ -1540,27 +1569,27 @@
 components/patterns/ZsbAddressStep.tsx</t>
         </is>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="D21" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>Appointment Booking</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>Book the installation visit: SLA cluster, the date strip (next working days from the earliest, with each day's open slots), the day's time slots and technicians free, the customer's request for a specific date and time (a later date makes the order future-dated), appointment notes and the documents the technician collects (defaulted from the persona).</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>capabilities/AppointmentBooking/AppointmentBooking.tsx
 capabilities/AppointmentBooking/index.ts
@@ -1569,27 +1598,27 @@
 components/patterns/appointmentModel.ts</t>
         </is>
       </c>
-      <c r="D21" s="17" t="n">
+      <c r="D22" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, administration</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>Activity Comments</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>The closing note on the actions performed, with an optional channel.</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>capabilities/ActivityComments/ActivityComments.tsx
 capabilities/ActivityComments/index.ts
@@ -1597,27 +1626,27 @@
 components/patterns/ActivityCommentsStep.tsx</t>
         </is>
       </c>
-      <c r="D22" s="17" t="n">
+      <c r="D23" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>Line Selection</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>Choose which of the identified customer's existing mobile lines an order changes (Change Postpaid Plan, Change Prepaid Pack, Add Add-On): postpaid and / or prepaid lines with their current plan and price; a line that is not active, is barred or whose billing profile is in collections is shown with its reason and cannot be chosen.</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>capabilities/LineSelection/LineSelection.tsx
 capabilities/LineSelection/index.ts
@@ -1626,54 +1655,29 @@
 components/patterns/lineSelectionModel.ts</t>
         </is>
       </c>
-      <c r="D23" s="17" t="n">
+      <c r="D24" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="E24" s="17" t="inlineStr">
         <is>
           <t>mobile-service-changes, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="17" t="inlineStr">
-        <is>
-          <t>Selectable card styling</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>One selected / idle / highlighted surface for plans, offers, numbers, add-ons, discounts and ID/customer type.</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>capabilities/SelectableCard/index.ts</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>administration</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="17" t="inlineStr">
         <is>
-          <t>Side drawer</t>
+          <t>Selectable card styling</t>
         </is>
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>Fixed 50%-width drawer for forms, details and multi-step flows: the title as a small uppercase label beside the close control, the body on the page tint, and a footer whose buttons share its width equally.</t>
+          <t>One selected / idle / highlighted surface for plans, offers, numbers, add-ons, discounts and ID/customer type.</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>capabilities/SideDrawer/index.ts</t>
+          <t>capabilities/SelectableCard/index.ts</t>
         </is>
       </c>
       <c r="D25" s="17" t="n">
@@ -1688,23 +1692,73 @@
     <row r="26">
       <c r="A26" s="17" t="inlineStr">
         <is>
-          <t>Pagination</t>
+          <t>Side drawer</t>
         </is>
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>The one way to page a list: usePagination (1-based pages, a changed list returns to page 1, a page that no longer exists is clamped), the "Showing a-b of N" summary and the numbered pager, hidden on a single page. Used by the number picker, data tables and every paged Customer 360 and Telesales list.</t>
+          <t>Fixed 50%-width drawer for forms, details and multi-step flows: the title as a small uppercase label beside the close control, the body on the page tint, and a footer whose buttons share its width equally.</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>capabilities/Pagination/index.ts</t>
+          <t>capabilities/SideDrawer/index.ts</t>
         </is>
       </c>
       <c r="D26" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>administration</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>The one way to page a list: usePagination (1-based pages, a changed list returns to page 1, a page that no longer exists is clamped), the "Showing a-b of N" summary and the numbered pager, hidden on a single page. Used by the number picker, data tables and every paged Customer 360 and Telesales list.</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>capabilities/Pagination/index.ts</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>administration</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>Empty State</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>The one empty state: a picture, an optional title, the scenario's own message and an optional action, centred, in a full-page or compact size. Data tables, the number picker, add-ons and discounts, billing accounts, ticket tabs, notifications and the not-found pages all show nothing through it, so what "empty" looks like is changed once.</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>capabilities/EmptyState/index.ts</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>administration</t>
         </is>
@@ -1721,7 +1775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H119"/>
+  <dimension ref="A1:H121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.85" customWidth="1" min="1" max="1"/>
@@ -1847,7 +1901,7 @@
       </c>
       <c r="G3" s="17" t="inlineStr">
         <is>
-          <t>AdditionalDocumentsUpload, CafDocumentUpload, CompanySearchInput, ContactPhoneInput, EligibilityRows, FibreReadinessBanner, IdFileUpload, MsisdnPicker, PassportScanSections, QidImageUpload, QidInput, ScanFailureNotice, SimSerialScanner, AppointmentBookingStep, BillingAccountStep, CafSignatureCapture, DiscountCard, FixedPlanStep, OrderConfirmationScreen, PostpaidPlanCard, PrepaidPlanCard, PrepaidPlanStep, RestrictedCustomerNotice, RestrictedRowsNotice, ValidationStatus, ZsbAddressStep, CustomerViewButton, StepSummarySection, WizardFooter, ChoiceCards, DataTable, IconButton, LocationInput, Pager, PhoneNumberInput, SearchField, Select, Tabs</t>
+          <t>AdditionalDocumentsUpload, CafDocumentUpload, CompanySearchInput, ContactPhoneInput, EligibilityRows, FibreReadinessBanner, IdFileUpload, MsisdnPicker, PassportScanSections, QidImageUpload, QidInput, ScanFailureNotice, SimSerialScanner, AppointmentBookingStep, BillingAccountStep, CafSignatureCapture, DiscountCard, FixedPlanStep, OrderConfirmationScreen, PostpaidPlanCard, PrepaidPlanCard, PrepaidPlanStep, RestrictedCustomerNotice, RestrictedRowsNotice, ValidationStatus, ZsbAddressStep, CustomerViewButton, StepSummarySection, WizardFooter, ChoiceCards, DataTable, EmptyState, IconButton, LocationInput, Pager, PhoneNumberInput, SearchField, Select, Tabs</t>
         </is>
       </c>
       <c r="H3" s="17" t="inlineStr">
@@ -1904,12 +1958,12 @@
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>EMPTY_STATE_ICON</t>
         </is>
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/Select.tsx</t>
+          <t>components/primitives/EmptyState.tsx</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -1918,21 +1972,21 @@
         </is>
       </c>
       <c r="E5" s="17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, profile, support, tasks</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G5" s="17" t="inlineStr">
         <is>
-          <t>AdditionalDocumentsUpload, CafDocumentUpload, MsisdnPicker, BillingAccountStep, BillingProfileSetupDrawer, BulkOperationPortal, CreditLimitCard, DonorDetailsStep, GuidedContactStep, NewCustomerForm, TicketCreationModal, ZsbAddressStep</t>
+          <t>MsisdnPicker, BillingAccountStep, PostpaidDiscountsPanel, DataTable</t>
         </is>
       </c>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>uncommitted</t>
         </is>
       </c>
     </row>
@@ -1944,12 +1998,12 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>Pager</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/Pager.tsx</t>
+          <t>components/primitives/Select.tsx</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -1958,16 +2012,16 @@
         </is>
       </c>
       <c r="E6" s="17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, orders, sales, support, tasks, tickets</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, profile, support, tasks</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
         <is>
-          <t>Pagination</t>
+          <t>AdditionalDocumentsUpload, CafDocumentUpload, MsisdnPicker, BillingAccountStep, BillingProfileSetupDrawer, BulkOperationPortal, CreditLimitCard, DonorDetailsStep, GuidedContactStep, NewCustomerForm, TicketCreationModal, ZsbAddressStep</t>
         </is>
       </c>
       <c r="H6" s="17" t="inlineStr">
@@ -1984,12 +2038,12 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>Pagination</t>
+          <t>Pager</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/Pagination.tsx</t>
+          <t>components/primitives/Pager.tsx</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -2007,7 +2061,7 @@
       </c>
       <c r="G7" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, DataTable</t>
+          <t>Pagination</t>
         </is>
       </c>
       <c r="H7" s="17" t="inlineStr">
@@ -2024,12 +2078,12 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Pagination</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/Input.tsx</t>
+          <t>components/primitives/Pagination.tsx</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -2038,21 +2092,21 @@
         </is>
       </c>
       <c r="E8" s="17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, profile, support</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, orders, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G8" s="17" t="inlineStr">
         <is>
-          <t>AdditionalDocumentsUpload, BillLimitEditor, CpeSerialScanner, SimSerialScanner, AppointmentBookingStep, BillingAccountStep, BillingProfileSetupDrawer, BulkOperationPortal, DonorDetailsStep, GuidedContactStep, IdLookupStep, NewCustomerForm, TicketCreationModal, ZsbAddressStep, PhoneNumberInput</t>
+          <t>MsisdnPicker, DataTable</t>
         </is>
       </c>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -2064,12 +2118,12 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>SearchField</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/SearchField.tsx</t>
+          <t>components/primitives/Input.tsx</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -2082,17 +2136,17 @@
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, support</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, profile, support</t>
         </is>
       </c>
       <c r="G9" s="17" t="inlineStr">
         <is>
-          <t>CompanySearchInput, MsisdnPicker, PlanSearchBox</t>
+          <t>AdditionalDocumentsUpload, BillLimitEditor, CpeSerialScanner, SimSerialScanner, AppointmentBookingStep, BillingAccountStep, BillingProfileSetupDrawer, BulkOperationPortal, DonorDetailsStep, GuidedContactStep, IdLookupStep, NewCustomerForm, TicketCreationModal, ZsbAddressStep, PhoneNumberInput</t>
         </is>
       </c>
       <c r="H9" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2158,12 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>Textarea</t>
+          <t>SearchField</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/Textarea.tsx</t>
+          <t>components/primitives/SearchField.tsx</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -2118,21 +2172,21 @@
         </is>
       </c>
       <c r="E10" s="17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, support</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, support</t>
         </is>
       </c>
       <c r="G10" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen, ActivityCommentsStep, AppointmentBookingStep, TicketCreationModal, ZsbAddressStep, WizardDialogs</t>
+          <t>CompanySearchInput, MsisdnPicker, PlanSearchBox</t>
         </is>
       </c>
       <c r="H10" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -2144,12 +2198,12 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>Tooltip</t>
+          <t>SegmentedTabs</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/Tooltip.tsx</t>
+          <t>components/primitives/SegmentedTabs.tsx</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -2162,17 +2216,17 @@
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, support</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, orders, support, tickets</t>
         </is>
       </c>
       <c r="G11" s="17" t="inlineStr">
         <is>
-          <t>CustomerViewButton, CloseButton, Tabs</t>
+          <t>TabStrip</t>
         </is>
       </c>
       <c r="H11" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2184,12 +2238,12 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>TooltipGroup</t>
+          <t>Textarea</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/TooltipContext.tsx</t>
+          <t>components/primitives/Textarea.tsx</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -2202,17 +2256,17 @@
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, support</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, support</t>
         </is>
       </c>
       <c r="G12" s="17" t="inlineStr">
         <is>
-          <t>Tooltip</t>
+          <t>ActivationCompleteScreen, ActivityCommentsStep, AppointmentBookingStep, TicketCreationModal, ZsbAddressStep, WizardDialogs</t>
         </is>
       </c>
       <c r="H12" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2224,12 +2278,12 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>CloseButton</t>
+          <t>Tooltip</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/CloseButton.tsx</t>
+          <t>components/primitives/Tooltip.tsx</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -2238,16 +2292,16 @@
         </is>
       </c>
       <c r="E13" s="17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, support</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, support</t>
         </is>
       </c>
       <c r="G13" s="17" t="inlineStr">
         <is>
-          <t>Drawer, Modal</t>
+          <t>CustomerViewButton, CloseButton, Tabs</t>
         </is>
       </c>
       <c r="H13" s="17" t="inlineStr">
@@ -2264,12 +2318,12 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>TabStrip</t>
+          <t>TooltipGroup</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/TabStrip.tsx</t>
+          <t>components/primitives/TooltipContext.tsx</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -2278,21 +2332,21 @@
         </is>
       </c>
       <c r="E14" s="17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, orders, support</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, support</t>
         </is>
       </c>
       <c r="G14" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, PlanTabStrip, Tabs</t>
+          <t>Tooltip</t>
         </is>
       </c>
       <c r="H14" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -2304,12 +2358,12 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>CloseButton</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/Checkbox.tsx</t>
+          <t>components/primitives/CloseButton.tsx</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -2318,21 +2372,21 @@
         </is>
       </c>
       <c r="E15" s="17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, support</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, support</t>
         </is>
       </c>
       <c r="G15" s="17" t="inlineStr">
         <is>
-          <t>CreditCheckPanel, MsisdnPicker, AppointmentBookingStep, BillingAccountStep, CafSignatureCapture, PrepaidPlanStep</t>
+          <t>Drawer, Modal</t>
         </is>
       </c>
       <c r="H15" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2344,12 +2398,12 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>DataTable</t>
+          <t>NestedTabs</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/DataTable.tsx</t>
+          <t>components/primitives/TabLevel.tsx</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -2358,21 +2412,21 @@
         </is>
       </c>
       <c r="E16" s="17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, lead-management, mnp-fnp-porting, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, customer360, orders, sales, support, tasks, tickets</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, orders, support</t>
         </is>
       </c>
       <c r="G16" s="17" t="inlineStr">
         <is>
-          <t>BulkOperationPortal</t>
+          <t>TabStrip, Tabs</t>
         </is>
       </c>
       <c r="H16" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>uncommitted</t>
         </is>
       </c>
     </row>
@@ -2384,12 +2438,12 @@
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>CARD_SELECTED</t>
+          <t>TabStrip</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/offerCardParts.tsx</t>
+          <t>components/primitives/TabStrip.tsx</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -2398,21 +2452,21 @@
         </is>
       </c>
       <c r="E17" s="17" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F17" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, orders, support</t>
         </is>
       </c>
       <c r="G17" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, QidInput, AppointmentBookingStep, BillingAccountStep, DiscountCard, FixedPlanStep, LineSelectionStep, PostpaidPlanCard, PrepaidPlanCard, PrepaidPlanStep, ChoiceCards</t>
+          <t>MsisdnPicker, PlanTabStrip, Tabs</t>
         </is>
       </c>
       <c r="H17" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2424,12 +2478,12 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>CountryMarker</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/CountryMarker.tsx</t>
+          <t>components/primitives/Checkbox.tsx</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -2438,21 +2492,21 @@
         </is>
       </c>
       <c r="E18" s="17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, support</t>
         </is>
       </c>
       <c r="G18" s="17" t="inlineStr">
         <is>
-          <t>PhoneNumberInput</t>
+          <t>CreditCheckPanel, MsisdnPicker, AppointmentBookingStep, BillingAccountStep, CafSignatureCapture, PrepaidPlanStep</t>
         </is>
       </c>
       <c r="H18" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -2464,12 +2518,12 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>Drawer</t>
+          <t>DataTable</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/Drawer.tsx</t>
+          <t>components/primitives/DataTable.tsx</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -2478,21 +2532,21 @@
         </is>
       </c>
       <c r="E19" s="17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F19" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, trouble-ticketing-complaints, administration, customer360, support</t>
+          <t>enterprise-iot-b2b, lead-management, mnp-fnp-porting, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, customer360, orders, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G19" s="17" t="inlineStr">
         <is>
-          <t>EligibilityRows, BillingProfileSetupDrawer, PrepaidPackDetailsDrawer, TicketCreationModal, VerificationGate</t>
+          <t>BulkOperationPortal</t>
         </is>
       </c>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -2504,12 +2558,12 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>ErrorBanner</t>
+          <t>CARD_SELECTED</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/ErrorBanner.tsx</t>
+          <t>components/primitives/offerCardParts.tsx</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -2522,13 +2576,17 @@
       </c>
       <c r="F20" s="17" t="inlineStr">
         <is>
-          <t>lead-management, mnp-fnp-porting, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, customer360, orders, sales, support, tasks, tickets</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G20" s="17" t="inlineStr">
+        <is>
+          <t>MsisdnPicker, QidInput, AppointmentBookingStep, BillingAccountStep, DiscountCard, FixedPlanStep, LineSelectionStep, PostpaidPlanCard, PrepaidPlanCard, PrepaidPlanStep, ChoiceCards</t>
+        </is>
+      </c>
       <c r="H20" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -2540,12 +2598,12 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>Modal</t>
+          <t>CountryMarker</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/Modal.tsx</t>
+          <t>components/primitives/CountryMarker.tsx</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -2558,12 +2616,12 @@
       </c>
       <c r="F21" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G21" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen, WizardDialogs</t>
+          <t>PhoneNumberInput</t>
         </is>
       </c>
       <c r="H21" s="17" t="inlineStr">
@@ -2580,12 +2638,12 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>PhoneNumberInput</t>
+          <t>Drawer</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/PhoneNumberInput.tsx</t>
+          <t>components/primitives/Drawer.tsx</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -2598,17 +2656,17 @@
       </c>
       <c r="F22" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, trouble-ticketing-complaints, administration, customer360, support</t>
         </is>
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
-          <t>ContactPhoneInput, DonorDetailsStep, GuidedContactStep</t>
+          <t>EligibilityRows, BillingProfileSetupDrawer, PrepaidPackDetailsDrawer, TicketCreationModal, VerificationGate</t>
         </is>
       </c>
       <c r="H22" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2620,12 +2678,12 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>Spinner</t>
+          <t>ErrorBanner</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/Spinner.tsx</t>
+          <t>components/primitives/ErrorBanner.tsx</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -2638,14 +2696,10 @@
       </c>
       <c r="F23" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr">
-        <is>
-          <t>PassportScanSections, QidImageUpload, ValidationStatus</t>
-        </is>
-      </c>
+          <t>lead-management, mnp-fnp-porting, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, customer360, orders, sales, support, tasks, tickets</t>
+        </is>
+      </c>
+      <c r="G23" s="17" t="inlineStr"/>
       <c r="H23" s="17" t="inlineStr">
         <is>
           <t>2026-10-15</t>
@@ -2660,12 +2714,12 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>SegmentedTabs</t>
+          <t>Modal</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/SegmentedTabs.tsx</t>
+          <t>components/primitives/Modal.tsx</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -2674,17 +2728,21 @@
         </is>
       </c>
       <c r="E24" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360, tickets</t>
-        </is>
-      </c>
-      <c r="G24" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration</t>
+        </is>
+      </c>
+      <c r="G24" s="17" t="inlineStr">
+        <is>
+          <t>ActivationCompleteScreen, WizardDialogs</t>
+        </is>
+      </c>
       <c r="H24" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2696,12 +2754,12 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>SignaturePad</t>
+          <t>PhoneNumberInput</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/SignaturePad.tsx</t>
+          <t>components/primitives/PhoneNumberInput.tsx</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -2710,21 +2768,21 @@
         </is>
       </c>
       <c r="E25" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F25" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G25" s="17" t="inlineStr">
         <is>
-          <t>SignatureCapture</t>
+          <t>ContactPhoneInput, DonorDetailsStep, GuidedContactStep</t>
         </is>
       </c>
       <c r="H25" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2736,12 +2794,12 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>ConnectionTypeTag</t>
+          <t>Spinner</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/ConnectionTypeTag.tsx</t>
+          <t>components/primitives/Spinner.tsx</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -2750,21 +2808,21 @@
         </is>
       </c>
       <c r="E26" s="17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G26" s="17" t="inlineStr">
         <is>
-          <t>FixedPlanStep, PostpaidPlanCard, PrepaidPlanCard</t>
+          <t>PassportScanSections, QidImageUpload, ValidationStatus</t>
         </is>
       </c>
       <c r="H26" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2834,12 @@
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>IconButton</t>
+          <t>SignaturePad</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/IconButton.tsx</t>
+          <t>components/primitives/SignaturePad.tsx</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -2790,21 +2848,21 @@
         </is>
       </c>
       <c r="E27" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F27" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G27" s="17" t="inlineStr">
         <is>
-          <t>AdditionalDocumentsUpload, CafDocumentUpload</t>
+          <t>SignatureCapture</t>
         </is>
       </c>
       <c r="H27" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2816,12 +2874,12 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>ServiceTypeTag</t>
+          <t>ConnectionTypeTag</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/ServiceTypeTag.tsx</t>
+          <t>components/primitives/ConnectionTypeTag.tsx</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -2839,7 +2897,7 @@
       </c>
       <c r="G28" s="17" t="inlineStr">
         <is>
-          <t>LineSelectionStep, ConnectionTypeTag</t>
+          <t>FixedPlanStep, PostpaidPlanCard, PrepaidPlanCard</t>
         </is>
       </c>
       <c r="H28" s="17" t="inlineStr">
@@ -2856,12 +2914,12 @@
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>ChoiceCards</t>
+          <t>IconButton</t>
         </is>
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/ChoiceCards.tsx</t>
+          <t>components/primitives/IconButton.tsx</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -2870,17 +2928,21 @@
         </is>
       </c>
       <c r="E29" s="17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F29" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, customer360</t>
-        </is>
-      </c>
-      <c r="G29" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="inlineStr">
+        <is>
+          <t>AdditionalDocumentsUpload, CafDocumentUpload</t>
+        </is>
+      </c>
       <c r="H29" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2954,12 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>PanelIcon</t>
+          <t>ServiceTypeTag</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/PanelIcon.tsx</t>
+          <t>components/primitives/ServiceTypeTag.tsx</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -2906,21 +2968,21 @@
         </is>
       </c>
       <c r="E30" s="17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F30" s="17" t="inlineStr">
         <is>
-          <t>trouble-ticketing-complaints, navigation, administration, customer360, orders, support</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
         </is>
       </c>
       <c r="G30" s="17" t="inlineStr">
         <is>
-          <t>Tabs</t>
+          <t>LineSelectionStep, ConnectionTypeTag</t>
         </is>
       </c>
       <c r="H30" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -2946,11 +3008,11 @@
         </is>
       </c>
       <c r="E31" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F31" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G31" s="17" t="inlineStr"/>
@@ -2968,12 +3030,12 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>Tabs</t>
+          <t>ChoiceCards</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/Tabs.tsx</t>
+          <t>components/primitives/ChoiceCards.tsx</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -2982,17 +3044,17 @@
         </is>
       </c>
       <c r="E32" s="17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F32" s="17" t="inlineStr">
         <is>
-          <t>trouble-ticketing-complaints, administration, customer360, orders, support</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, customer360</t>
         </is>
       </c>
       <c r="G32" s="17" t="inlineStr"/>
       <c r="H32" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -3004,28 +3066,32 @@
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>VodafoneMark</t>
+          <t>PanelIcon</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/VodafoneMark.tsx</t>
-        </is>
-      </c>
-      <c r="D33" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>components/primitives/PanelIcon.tsx</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E33" s="17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F33" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="G33" s="17" t="inlineStr"/>
+          <t>trouble-ticketing-complaints, navigation, administration, customer360, orders, support</t>
+        </is>
+      </c>
+      <c r="G33" s="17" t="inlineStr">
+        <is>
+          <t>Tabs</t>
+        </is>
+      </c>
       <c r="H33" s="17" t="inlineStr">
         <is>
           <t>2026-10-15</t>
@@ -3040,31 +3106,31 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>VodafoneWordmark</t>
+          <t>Tabs</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/VodafoneWordmark.tsx</t>
-        </is>
-      </c>
-      <c r="D34" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>components/primitives/Tabs.tsx</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E34" s="17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F34" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
+          <t>trouble-ticketing-complaints, administration, customer360, orders, support</t>
         </is>
       </c>
       <c r="G34" s="17" t="inlineStr"/>
       <c r="H34" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3076,27 +3142,31 @@
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>LocationInput</t>
+          <t>VodafoneMark</t>
         </is>
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/LocationInput.tsx</t>
-        </is>
-      </c>
-      <c r="D35" s="22" t="inlineStr">
-        <is>
-          <t>No consumer</t>
+          <t>components/primitives/VodafoneMark.tsx</t>
+        </is>
+      </c>
+      <c r="D35" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E35" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F35" s="17" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
       <c r="G35" s="17" t="inlineStr"/>
       <c r="H35" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3108,23 +3178,27 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>OoredooMark</t>
+          <t>VodafoneWordmark</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>components/primitives/OoredooMark.tsx</t>
-        </is>
-      </c>
-      <c r="D36" s="23" t="inlineStr">
-        <is>
-          <t>App shell only</t>
+          <t>components/primitives/VodafoneWordmark.tsx</t>
+        </is>
+      </c>
+      <c r="D36" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E36" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F36" s="17" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
       <c r="G36" s="17" t="inlineStr"/>
       <c r="H36" s="17" t="inlineStr">
         <is>
@@ -3135,80 +3209,64 @@
     <row r="37">
       <c r="A37" s="17" t="inlineStr">
         <is>
-          <t>Domain</t>
+          <t>Primitive</t>
         </is>
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>ScannedIdPreview</t>
+          <t>LocationInput</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>components/domain/ScannedIdPreview.tsx</t>
-        </is>
-      </c>
-      <c r="D37" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>components/primitives/LocationInput.tsx</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="inlineStr">
+        <is>
+          <t>No consumer</t>
         </is>
       </c>
       <c r="E37" s="17" t="n">
-        <v>13</v>
-      </c>
-      <c r="F37" s="17" t="inlineStr">
-        <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, administration, customer360</t>
-        </is>
-      </c>
-      <c r="G37" s="17" t="inlineStr">
-        <is>
-          <t>PassportScanSections, QidImageUpload, qidImageUploadModel, IdScannerPanel, useIdLookup</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F37" s="17" t="inlineStr"/>
+      <c r="G37" s="17" t="inlineStr"/>
       <c r="H37" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="17" t="inlineStr">
         <is>
-          <t>Domain</t>
+          <t>Primitive</t>
         </is>
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>IdFileUpload</t>
+          <t>OoredooMark</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>components/domain/IdFileUpload.tsx</t>
-        </is>
-      </c>
-      <c r="D38" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>components/primitives/OoredooMark.tsx</t>
+        </is>
+      </c>
+      <c r="D38" s="23" t="inlineStr">
+        <is>
+          <t>App shell only</t>
         </is>
       </c>
       <c r="E38" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="F38" s="17" t="inlineStr">
-        <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
-        </is>
-      </c>
-      <c r="G38" s="17" t="inlineStr">
-        <is>
-          <t>PassportScanSections, QidImageUpload</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F38" s="17" t="inlineStr"/>
+      <c r="G38" s="17" t="inlineStr"/>
       <c r="H38" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3220,12 +3278,12 @@
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>PassportScanSections</t>
+          <t>ScannedIdPreview</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>components/domain/PassportScanSections.tsx</t>
+          <t>components/domain/ScannedIdPreview.tsx</t>
         </is>
       </c>
       <c r="D39" s="20" t="inlineStr">
@@ -3234,16 +3292,16 @@
         </is>
       </c>
       <c r="E39" s="17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F39" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G39" s="17" t="inlineStr">
         <is>
-          <t>QidImageUpload</t>
+          <t>PassportScanSections, QidImageUpload, qidImageUploadModel, IdScannerPanel, useIdLookup</t>
         </is>
       </c>
       <c r="H39" s="17" t="inlineStr">
@@ -3260,12 +3318,12 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>QidImageUpload</t>
+          <t>IdFileUpload</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>components/domain/QidImageUpload.tsx</t>
+          <t>components/domain/IdFileUpload.tsx</t>
         </is>
       </c>
       <c r="D40" s="20" t="inlineStr">
@@ -3283,7 +3341,7 @@
       </c>
       <c r="G40" s="17" t="inlineStr">
         <is>
-          <t>IdScannerPanel</t>
+          <t>PassportScanSections, QidImageUpload</t>
         </is>
       </c>
       <c r="H40" s="17" t="inlineStr">
@@ -3300,12 +3358,12 @@
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>QidTypeSelector</t>
+          <t>PassportScanSections</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>components/domain/QidInput.tsx</t>
+          <t>components/domain/PassportScanSections.tsx</t>
         </is>
       </c>
       <c r="D41" s="20" t="inlineStr">
@@ -3323,12 +3381,12 @@
       </c>
       <c r="G41" s="17" t="inlineStr">
         <is>
-          <t>GuidedContactStep, IdLookupStep, IdScannerPanel, MoiResultPanel, guidedContactModel, idLookupModel, useIdLookup</t>
+          <t>QidImageUpload</t>
         </is>
       </c>
       <c r="H41" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -3340,12 +3398,12 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>ScanFailureNotice</t>
+          <t>QidImageUpload</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>components/domain/ScanFailureNotice.tsx</t>
+          <t>components/domain/QidImageUpload.tsx</t>
         </is>
       </c>
       <c r="D42" s="20" t="inlineStr">
@@ -3363,12 +3421,12 @@
       </c>
       <c r="G42" s="17" t="inlineStr">
         <is>
-          <t>PassportScanSections, QidImageUpload</t>
+          <t>IdScannerPanel</t>
         </is>
       </c>
       <c r="H42" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -3380,12 +3438,12 @@
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>CompanySearchInput</t>
+          <t>QidTypeSelector</t>
         </is>
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>components/domain/CompanySearchInput.tsx</t>
+          <t>components/domain/QidInput.tsx</t>
         </is>
       </c>
       <c r="D43" s="20" t="inlineStr">
@@ -3394,17 +3452,21 @@
         </is>
       </c>
       <c r="E43" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F43" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, administration, customer360</t>
-        </is>
-      </c>
-      <c r="G43" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G43" s="17" t="inlineStr">
+        <is>
+          <t>GuidedContactStep, IdLookupStep, IdScannerPanel, MoiResultPanel, guidedContactModel, idLookupModel, useIdLookup</t>
+        </is>
+      </c>
       <c r="H43" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3416,12 +3478,12 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>EligibilityChecksList</t>
+          <t>ScanFailureNotice</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>components/domain/EligibilityRows.tsx</t>
+          <t>components/domain/ScanFailureNotice.tsx</t>
         </is>
       </c>
       <c r="D44" s="20" t="inlineStr">
@@ -3430,17 +3492,21 @@
         </is>
       </c>
       <c r="E44" s="17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F44" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
-        </is>
-      </c>
-      <c r="G44" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G44" s="17" t="inlineStr">
+        <is>
+          <t>PassportScanSections, QidImageUpload</t>
+        </is>
+      </c>
       <c r="H44" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -3452,12 +3518,12 @@
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>SimSerialScanner</t>
+          <t>CompanySearchInput</t>
         </is>
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>components/domain/SimSerialScanner.tsx</t>
+          <t>components/domain/CompanySearchInput.tsx</t>
         </is>
       </c>
       <c r="D45" s="20" t="inlineStr">
@@ -3466,21 +3532,17 @@
         </is>
       </c>
       <c r="E45" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F45" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
-        </is>
-      </c>
-      <c r="G45" s="17" t="inlineStr">
-        <is>
-          <t>SimTypeStep</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G45" s="17" t="inlineStr"/>
       <c r="H45" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -3492,12 +3554,12 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>AdditionalDocumentsUpload</t>
+          <t>EligibilityChecksList</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>components/domain/AdditionalDocumentsUpload.tsx</t>
+          <t>components/domain/EligibilityRows.tsx</t>
         </is>
       </c>
       <c r="D46" s="20" t="inlineStr">
@@ -3506,18 +3568,14 @@
         </is>
       </c>
       <c r="E46" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F46" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G46" s="17" t="inlineStr">
-        <is>
-          <t>CafSignatureCapture</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G46" s="17" t="inlineStr"/>
       <c r="H46" s="17" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -3532,12 +3590,12 @@
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>BillLimitEditor</t>
+          <t>SimSerialScanner</t>
         </is>
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>components/domain/BillLimitEditor.tsx</t>
+          <t>components/domain/SimSerialScanner.tsx</t>
         </is>
       </c>
       <c r="D47" s="20" t="inlineStr">
@@ -3546,21 +3604,21 @@
         </is>
       </c>
       <c r="E47" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F47" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G47" s="17" t="inlineStr">
         <is>
-          <t>PostpaidAddonsPanel, PostpaidPlanAddonsStep</t>
+          <t>SimTypeStep</t>
         </is>
       </c>
       <c r="H47" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3630,12 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>CafDocumentUpload</t>
+          <t>AdditionalDocumentsUpload</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>components/domain/CafDocumentUpload.tsx</t>
+          <t>components/domain/AdditionalDocumentsUpload.tsx</t>
         </is>
       </c>
       <c r="D48" s="20" t="inlineStr">
@@ -3612,12 +3670,12 @@
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>CreditCheckPanel</t>
+          <t>BillLimitEditor</t>
         </is>
       </c>
       <c r="C49" s="17" t="inlineStr">
         <is>
-          <t>components/domain/CreditCheckPanel.tsx</t>
+          <t>components/domain/BillLimitEditor.tsx</t>
         </is>
       </c>
       <c r="D49" s="20" t="inlineStr">
@@ -3635,7 +3693,7 @@
       </c>
       <c r="G49" s="17" t="inlineStr">
         <is>
-          <t>FixedPlanStep</t>
+          <t>PostpaidAddonsPanel, PostpaidPlanAddonsStep</t>
         </is>
       </c>
       <c r="H49" s="17" t="inlineStr">
@@ -3652,12 +3710,12 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>EsimActivationPanel</t>
+          <t>CafDocumentUpload</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>components/domain/EsimActivationPanel.tsx</t>
+          <t>components/domain/CafDocumentUpload.tsx</t>
         </is>
       </c>
       <c r="D50" s="20" t="inlineStr">
@@ -3675,12 +3733,12 @@
       </c>
       <c r="G50" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen</t>
+          <t>CafSignatureCapture</t>
         </is>
       </c>
       <c r="H50" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3750,12 @@
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker</t>
+          <t>CreditCheckPanel</t>
         </is>
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>components/domain/MsisdnPicker.tsx</t>
+          <t>components/domain/CreditCheckPanel.tsx</t>
         </is>
       </c>
       <c r="D51" s="20" t="inlineStr">
@@ -3710,10 +3768,14 @@
       </c>
       <c r="F51" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
-        </is>
-      </c>
-      <c r="G51" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G51" s="17" t="inlineStr">
+        <is>
+          <t>FixedPlanStep</t>
+        </is>
+      </c>
       <c r="H51" s="17" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -3728,12 +3790,12 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>SimTypeStep</t>
+          <t>EsimActivationPanel</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>components/domain/SimTypeStep.tsx</t>
+          <t>components/domain/EsimActivationPanel.tsx</t>
         </is>
       </c>
       <c r="D52" s="20" t="inlineStr">
@@ -3751,12 +3813,12 @@
       </c>
       <c r="G52" s="17" t="inlineStr">
         <is>
-          <t>CheckoutSummaryStep, checkoutDetailedTables, checkoutSummaryRows, prepaidCartModel, useCheckoutSummary</t>
+          <t>ActivationCompleteScreen</t>
         </is>
       </c>
       <c r="H52" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3768,12 +3830,12 @@
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>StarStat</t>
+          <t>MsisdnPicker</t>
         </is>
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>components/domain/StarStat.tsx</t>
+          <t>components/domain/MsisdnPicker.tsx</t>
         </is>
       </c>
       <c r="D53" s="20" t="inlineStr">
@@ -3789,14 +3851,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
-      <c r="G53" s="17" t="inlineStr">
-        <is>
-          <t>MsisdnPicker</t>
-        </is>
-      </c>
+      <c r="G53" s="17" t="inlineStr"/>
       <c r="H53" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -3808,12 +3866,12 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>FibreReadinessBanner</t>
+          <t>SimTypeStep</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>components/domain/FibreReadinessBanner.tsx</t>
+          <t>components/domain/SimTypeStep.tsx</t>
         </is>
       </c>
       <c r="D54" s="20" t="inlineStr">
@@ -3822,21 +3880,21 @@
         </is>
       </c>
       <c r="E54" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F54" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G54" s="17" t="inlineStr">
         <is>
-          <t>ZsbAddressStep</t>
+          <t>CheckoutSummaryStep, checkoutDetailedTables, checkoutSummaryRows, prepaidCartModel, useCheckoutSummary</t>
         </is>
       </c>
       <c r="H54" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -3848,28 +3906,32 @@
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>ContactPhoneInput</t>
+          <t>StarStat</t>
         </is>
       </c>
       <c r="C55" s="17" t="inlineStr">
         <is>
-          <t>components/domain/ContactPhoneInput.tsx</t>
-        </is>
-      </c>
-      <c r="D55" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>components/domain/StarStat.tsx</t>
+        </is>
+      </c>
+      <c r="D55" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E55" s="17" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F55" s="17" t="inlineStr">
         <is>
-          <t>customer360</t>
-        </is>
-      </c>
-      <c r="G55" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+      <c r="G55" s="17" t="inlineStr">
+        <is>
+          <t>MsisdnPicker</t>
+        </is>
+      </c>
       <c r="H55" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
@@ -3884,35 +3946,35 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>CpeSerialScanner</t>
+          <t>FibreReadinessBanner</t>
         </is>
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t>components/domain/CpeSerialScanner.tsx</t>
-        </is>
-      </c>
-      <c r="D56" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>components/domain/FibreReadinessBanner.tsx</t>
+        </is>
+      </c>
+      <c r="D56" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E56" s="17" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F56" s="17" t="inlineStr">
         <is>
-          <t>fwa-5g-home</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G56" s="17" t="inlineStr">
         <is>
-          <t>DualPlaySerialCheckStep</t>
+          <t>ZsbAddressStep</t>
         </is>
       </c>
       <c r="H56" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3986,12 @@
       </c>
       <c r="B57" s="17" t="inlineStr">
         <is>
-          <t>OsmEmbed</t>
+          <t>ContactPhoneInput</t>
         </is>
       </c>
       <c r="C57" s="17" t="inlineStr">
         <is>
-          <t>components/domain/OsmEmbed.tsx</t>
+          <t>components/domain/ContactPhoneInput.tsx</t>
         </is>
       </c>
       <c r="D57" s="21" t="inlineStr">
@@ -3948,83 +4010,83 @@
       <c r="G57" s="17" t="inlineStr"/>
       <c r="H57" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="17" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>PageHeader</t>
+          <t>CpeSerialScanner</t>
         </is>
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PageHeader.tsx</t>
-        </is>
-      </c>
-      <c r="D58" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>components/domain/CpeSerialScanner.tsx</t>
+        </is>
+      </c>
+      <c r="D58" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E58" s="17" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F58" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fwa-5g-home, lead-management, mnp-fnp-porting, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
-        </is>
-      </c>
-      <c r="G58" s="17" t="inlineStr"/>
+          <t>fwa-5g-home</t>
+        </is>
+      </c>
+      <c r="G58" s="17" t="inlineStr">
+        <is>
+          <t>DualPlaySerialCheckStep</t>
+        </is>
+      </c>
       <c r="H58" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="17" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="B59" s="17" t="inlineStr">
         <is>
-          <t>RestrictedCustomerNotice</t>
+          <t>OsmEmbed</t>
         </is>
       </c>
       <c r="C59" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/RestrictedCustomerNotice.tsx</t>
-        </is>
-      </c>
-      <c r="D59" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>components/domain/OsmEmbed.tsx</t>
+        </is>
+      </c>
+      <c r="D59" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E59" s="17" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="F59" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer-search, customer360, support, tasks</t>
-        </is>
-      </c>
-      <c r="G59" s="17" t="inlineStr">
-        <is>
-          <t>IdLookupStep, TicketCreationModal</t>
-        </is>
-      </c>
+          <t>customer360</t>
+        </is>
+      </c>
+      <c r="G59" s="17" t="inlineStr"/>
       <c r="H59" s="17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4098,12 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>GuidedContactStep</t>
+          <t>PageHeader</t>
         </is>
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/GuidedContactStep.tsx</t>
+          <t>components/patterns/PageHeader.tsx</t>
         </is>
       </c>
       <c r="D60" s="20" t="inlineStr">
@@ -4050,17 +4112,17 @@
         </is>
       </c>
       <c r="E60" s="17" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F60" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>enterprise-iot-b2b, fwa-5g-home, lead-management, mnp-fnp-porting, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G60" s="17" t="inlineStr"/>
       <c r="H60" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4072,12 +4134,12 @@
       </c>
       <c r="B61" s="17" t="inlineStr">
         <is>
-          <t>IdLookupStatus</t>
+          <t>RestrictedCustomerNotice</t>
         </is>
       </c>
       <c r="C61" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/IdLookupStatus.tsx</t>
+          <t>components/patterns/RestrictedCustomerNotice.tsx</t>
         </is>
       </c>
       <c r="D61" s="20" t="inlineStr">
@@ -4086,21 +4148,21 @@
         </is>
       </c>
       <c r="E61" s="17" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F61" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer-search, customer360, support, tasks</t>
         </is>
       </c>
       <c r="G61" s="17" t="inlineStr">
         <is>
-          <t>IdLookupStep</t>
+          <t>IdLookupStep, TicketCreationModal</t>
         </is>
       </c>
       <c r="H61" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -4112,12 +4174,12 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>IdLookupStep</t>
+          <t>GuidedContactStep</t>
         </is>
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/IdLookupStep.tsx</t>
+          <t>components/patterns/GuidedContactStep.tsx</t>
         </is>
       </c>
       <c r="D62" s="20" t="inlineStr">
@@ -4133,11 +4195,7 @@
           <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
-      <c r="G62" s="17" t="inlineStr">
-        <is>
-          <t>GuidedContactStep</t>
-        </is>
-      </c>
+      <c r="G62" s="17" t="inlineStr"/>
       <c r="H62" s="17" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -4152,12 +4210,12 @@
       </c>
       <c r="B63" s="17" t="inlineStr">
         <is>
-          <t>IdScannerPanel</t>
+          <t>IdLookupStatus</t>
         </is>
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/IdScannerPanel.tsx</t>
+          <t>components/patterns/IdLookupStatus.tsx</t>
         </is>
       </c>
       <c r="D63" s="20" t="inlineStr">
@@ -4180,7 +4238,7 @@
       </c>
       <c r="H63" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -4192,12 +4250,12 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>MoiResultPanel</t>
+          <t>IdLookupStep</t>
         </is>
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/MoiResultPanel.tsx</t>
+          <t>components/patterns/IdLookupStep.tsx</t>
         </is>
       </c>
       <c r="D64" s="20" t="inlineStr">
@@ -4215,12 +4273,12 @@
       </c>
       <c r="G64" s="17" t="inlineStr">
         <is>
-          <t>IdLookupStep</t>
+          <t>GuidedContactStep</t>
         </is>
       </c>
       <c r="H64" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -4232,12 +4290,12 @@
       </c>
       <c r="B65" s="17" t="inlineStr">
         <is>
-          <t>NewCustomerForm</t>
+          <t>IdScannerPanel</t>
         </is>
       </c>
       <c r="C65" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/NewCustomerForm.tsx</t>
+          <t>components/patterns/IdScannerPanel.tsx</t>
         </is>
       </c>
       <c r="D65" s="20" t="inlineStr">
@@ -4260,7 +4318,7 @@
       </c>
       <c r="H65" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4330,12 @@
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>ValidationStatus</t>
+          <t>MoiResultPanel</t>
         </is>
       </c>
       <c r="C66" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/ValidationStatus.tsx</t>
+          <t>components/patterns/MoiResultPanel.tsx</t>
         </is>
       </c>
       <c r="D66" s="20" t="inlineStr">
@@ -4295,12 +4353,12 @@
       </c>
       <c r="G66" s="17" t="inlineStr">
         <is>
-          <t>IdLookupStatus</t>
+          <t>IdLookupStep</t>
         </is>
       </c>
       <c r="H66" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4312,12 +4370,12 @@
       </c>
       <c r="B67" s="17" t="inlineStr">
         <is>
-          <t>SignatureCapture</t>
+          <t>NewCustomerForm</t>
         </is>
       </c>
       <c r="C67" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/SignatureCapture.tsx</t>
+          <t>components/patterns/NewCustomerForm.tsx</t>
         </is>
       </c>
       <c r="D67" s="20" t="inlineStr">
@@ -4326,21 +4384,21 @@
         </is>
       </c>
       <c r="E67" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F67" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G67" s="17" t="inlineStr">
         <is>
-          <t>CafSignatureCapture, DonorAttachmentStep, SimSwapFormStep</t>
+          <t>IdLookupStep</t>
         </is>
       </c>
       <c r="H67" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -4352,12 +4410,12 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen</t>
+          <t>ValidationStatus</t>
         </is>
       </c>
       <c r="C68" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/ActivationCompleteScreen.tsx</t>
+          <t>components/patterns/ValidationStatus.tsx</t>
         </is>
       </c>
       <c r="D68" s="20" t="inlineStr">
@@ -4366,14 +4424,18 @@
         </is>
       </c>
       <c r="E68" s="17" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F68" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G68" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G68" s="17" t="inlineStr">
+        <is>
+          <t>IdLookupStatus</t>
+        </is>
+      </c>
       <c r="H68" s="17" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -4388,12 +4450,12 @@
       </c>
       <c r="B69" s="17" t="inlineStr">
         <is>
-          <t>BillingAccountAutoResolver</t>
+          <t>SignatureCapture</t>
         </is>
       </c>
       <c r="C69" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/BillingAccountAutoResolver.tsx</t>
+          <t>components/patterns/SignatureCapture.tsx</t>
         </is>
       </c>
       <c r="D69" s="20" t="inlineStr">
@@ -4402,17 +4464,21 @@
         </is>
       </c>
       <c r="E69" s="17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F69" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G69" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+      <c r="G69" s="17" t="inlineStr">
+        <is>
+          <t>CafSignatureCapture, DonorAttachmentStep, SimSwapFormStep</t>
+        </is>
+      </c>
       <c r="H69" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4424,12 +4490,12 @@
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>CafSignatureCapture</t>
+          <t>ActivationCompleteScreen</t>
         </is>
       </c>
       <c r="C70" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CafSignatureCapture.tsx</t>
+          <t>components/patterns/ActivationCompleteScreen.tsx</t>
         </is>
       </c>
       <c r="D70" s="20" t="inlineStr">
@@ -4460,12 +4526,12 @@
       </c>
       <c r="B71" s="17" t="inlineStr">
         <is>
-          <t>CheckoutDefaultLayout</t>
+          <t>BillingAccountAutoResolver</t>
         </is>
       </c>
       <c r="C71" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CheckoutDefaultLayout.tsx</t>
+          <t>components/patterns/BillingAccountAutoResolver.tsx</t>
         </is>
       </c>
       <c r="D71" s="20" t="inlineStr">
@@ -4481,11 +4547,7 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G71" s="17" t="inlineStr">
-        <is>
-          <t>CheckoutSummaryStep</t>
-        </is>
-      </c>
+      <c r="G71" s="17" t="inlineStr"/>
       <c r="H71" s="17" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -4500,12 +4562,12 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>CheckoutSummaryStep</t>
+          <t>CafSignatureCapture</t>
         </is>
       </c>
       <c r="C72" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CheckoutSummaryStep.tsx</t>
+          <t>components/patterns/CafSignatureCapture.tsx</t>
         </is>
       </c>
       <c r="D72" s="20" t="inlineStr">
@@ -4524,7 +4586,7 @@
       <c r="G72" s="17" t="inlineStr"/>
       <c r="H72" s="17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -4536,12 +4598,12 @@
       </c>
       <c r="B73" s="17" t="inlineStr">
         <is>
-          <t>DiscountCard</t>
+          <t>CheckoutDefaultLayout</t>
         </is>
       </c>
       <c r="C73" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DiscountCard.tsx</t>
+          <t>components/patterns/CheckoutDefaultLayout.tsx</t>
         </is>
       </c>
       <c r="D73" s="20" t="inlineStr">
@@ -4559,12 +4621,12 @@
       </c>
       <c r="G73" s="17" t="inlineStr">
         <is>
-          <t>PostpaidDiscountsPanel</t>
+          <t>CheckoutSummaryStep</t>
         </is>
       </c>
       <c r="H73" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -4576,12 +4638,12 @@
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>FixedPlanStep</t>
+          <t>CheckoutSummaryStep</t>
         </is>
       </c>
       <c r="C74" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/FixedPlanStep.tsx</t>
+          <t>components/patterns/CheckoutSummaryStep.tsx</t>
         </is>
       </c>
       <c r="D74" s="20" t="inlineStr">
@@ -4600,7 +4662,7 @@
       <c r="G74" s="17" t="inlineStr"/>
       <c r="H74" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4674,12 @@
       </c>
       <c r="B75" s="17" t="inlineStr">
         <is>
-          <t>FullTerms</t>
+          <t>DiscountCard</t>
         </is>
       </c>
       <c r="C75" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CafTerms.tsx</t>
+          <t>components/patterns/DiscountCard.tsx</t>
         </is>
       </c>
       <c r="D75" s="20" t="inlineStr">
@@ -4635,7 +4697,7 @@
       </c>
       <c r="G75" s="17" t="inlineStr">
         <is>
-          <t>CafSignatureCapture</t>
+          <t>PostpaidDiscountsPanel</t>
         </is>
       </c>
       <c r="H75" s="17" t="inlineStr">
@@ -4652,12 +4714,12 @@
       </c>
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>KeyInformationPanel</t>
+          <t>FixedPlanStep</t>
         </is>
       </c>
       <c r="C76" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/KeyInformationPanel.tsx</t>
+          <t>components/patterns/FixedPlanStep.tsx</t>
         </is>
       </c>
       <c r="D76" s="20" t="inlineStr">
@@ -4676,7 +4738,7 @@
       <c r="G76" s="17" t="inlineStr"/>
       <c r="H76" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4688,12 +4750,12 @@
       </c>
       <c r="B77" s="17" t="inlineStr">
         <is>
-          <t>OrderConfirmationScreen</t>
+          <t>FullTerms</t>
         </is>
       </c>
       <c r="C77" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/OrderConfirmationScreen.tsx</t>
+          <t>components/patterns/CafTerms.tsx</t>
         </is>
       </c>
       <c r="D77" s="20" t="inlineStr">
@@ -4711,12 +4773,12 @@
       </c>
       <c r="G77" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen</t>
+          <t>CafSignatureCapture</t>
         </is>
       </c>
       <c r="H77" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4790,12 @@
       </c>
       <c r="B78" s="17" t="inlineStr">
         <is>
-          <t>PlanDetailsDrawer</t>
+          <t>KeyInformationPanel</t>
         </is>
       </c>
       <c r="C78" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PlanDetailsDrawer.tsx</t>
+          <t>components/patterns/KeyInformationPanel.tsx</t>
         </is>
       </c>
       <c r="D78" s="20" t="inlineStr">
@@ -4749,11 +4811,7 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G78" s="17" t="inlineStr">
-        <is>
-          <t>PostpaidPlanAddonsStep</t>
-        </is>
-      </c>
+      <c r="G78" s="17" t="inlineStr"/>
       <c r="H78" s="17" t="inlineStr">
         <is>
           <t>2026-10-15</t>
@@ -4768,12 +4826,12 @@
       </c>
       <c r="B79" s="17" t="inlineStr">
         <is>
-          <t>PlanGroupPanel</t>
+          <t>OrderConfirmationScreen</t>
         </is>
       </c>
       <c r="C79" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PlanGroupPanel.tsx</t>
+          <t>components/patterns/OrderConfirmationScreen.tsx</t>
         </is>
       </c>
       <c r="D79" s="20" t="inlineStr">
@@ -4791,12 +4849,12 @@
       </c>
       <c r="G79" s="17" t="inlineStr">
         <is>
-          <t>PostpaidPlanAddonsStep</t>
+          <t>ActivationCompleteScreen</t>
         </is>
       </c>
       <c r="H79" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4808,12 +4866,12 @@
       </c>
       <c r="B80" s="17" t="inlineStr">
         <is>
-          <t>PlanSearchBox</t>
+          <t>PlanDetailsDrawer</t>
         </is>
       </c>
       <c r="C80" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PlanSearchBox.tsx</t>
+          <t>components/patterns/PlanDetailsDrawer.tsx</t>
         </is>
       </c>
       <c r="D80" s="20" t="inlineStr">
@@ -4848,12 +4906,12 @@
       </c>
       <c r="B81" s="17" t="inlineStr">
         <is>
-          <t>PlanTabStrip</t>
+          <t>PlanGroupPanel</t>
         </is>
       </c>
       <c r="C81" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PlanTabStrip.tsx</t>
+          <t>components/patterns/PlanGroupPanel.tsx</t>
         </is>
       </c>
       <c r="D81" s="20" t="inlineStr">
@@ -4876,7 +4934,7 @@
       </c>
       <c r="H81" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4888,12 +4946,12 @@
       </c>
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>PostpaidAddonsPanel</t>
+          <t>PlanSearchBox</t>
         </is>
       </c>
       <c r="C82" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidAddonsPanel.tsx</t>
+          <t>components/patterns/PlanSearchBox.tsx</t>
         </is>
       </c>
       <c r="D82" s="20" t="inlineStr">
@@ -4916,7 +4974,7 @@
       </c>
       <c r="H82" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4928,12 +4986,12 @@
       </c>
       <c r="B83" s="17" t="inlineStr">
         <is>
-          <t>PostpaidDiscountsPanel</t>
+          <t>PlanTabStrip</t>
         </is>
       </c>
       <c r="C83" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidDiscountsPanel.tsx</t>
+          <t>components/patterns/PlanTabStrip.tsx</t>
         </is>
       </c>
       <c r="D83" s="20" t="inlineStr">
@@ -4956,7 +5014,7 @@
       </c>
       <c r="H83" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4968,12 +5026,12 @@
       </c>
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>PostpaidMonthlySummary</t>
+          <t>PostpaidAddonsPanel</t>
         </is>
       </c>
       <c r="C84" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidMonthlySummary.tsx</t>
+          <t>components/patterns/PostpaidAddonsPanel.tsx</t>
         </is>
       </c>
       <c r="D84" s="20" t="inlineStr">
@@ -5008,12 +5066,12 @@
       </c>
       <c r="B85" s="17" t="inlineStr">
         <is>
-          <t>PostpaidPlanAddonsStep</t>
+          <t>PostpaidDiscountsPanel</t>
         </is>
       </c>
       <c r="C85" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidPlanAddonsStep.tsx</t>
+          <t>components/patterns/PostpaidDiscountsPanel.tsx</t>
         </is>
       </c>
       <c r="D85" s="20" t="inlineStr">
@@ -5029,7 +5087,11 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G85" s="17" t="inlineStr"/>
+      <c r="G85" s="17" t="inlineStr">
+        <is>
+          <t>PostpaidPlanAddonsStep</t>
+        </is>
+      </c>
       <c r="H85" s="17" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -5044,12 +5106,12 @@
       </c>
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>PostpaidPlanCard</t>
+          <t>PostpaidMonthlySummary</t>
         </is>
       </c>
       <c r="C86" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidPlanCard.tsx</t>
+          <t>components/patterns/PostpaidMonthlySummary.tsx</t>
         </is>
       </c>
       <c r="D86" s="20" t="inlineStr">
@@ -5067,7 +5129,7 @@
       </c>
       <c r="G86" s="17" t="inlineStr">
         <is>
-          <t>PlanGroupPanel</t>
+          <t>PostpaidPlanAddonsStep</t>
         </is>
       </c>
       <c r="H86" s="17" t="inlineStr">
@@ -5084,12 +5146,12 @@
       </c>
       <c r="B87" s="17" t="inlineStr">
         <is>
-          <t>PrepaidCartStep</t>
+          <t>PostpaidPlanAddonsStep</t>
         </is>
       </c>
       <c r="C87" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidCartStep.tsx</t>
+          <t>components/patterns/PostpaidPlanAddonsStep.tsx</t>
         </is>
       </c>
       <c r="D87" s="20" t="inlineStr">
@@ -5120,12 +5182,12 @@
       </c>
       <c r="B88" s="17" t="inlineStr">
         <is>
-          <t>PrepaidCheckoutStep</t>
+          <t>PostpaidPlanCard</t>
         </is>
       </c>
       <c r="C88" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidCheckoutStep.tsx</t>
+          <t>components/patterns/PostpaidPlanCard.tsx</t>
         </is>
       </c>
       <c r="D88" s="20" t="inlineStr">
@@ -5141,7 +5203,11 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G88" s="17" t="inlineStr"/>
+      <c r="G88" s="17" t="inlineStr">
+        <is>
+          <t>PlanGroupPanel</t>
+        </is>
+      </c>
       <c r="H88" s="17" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -5156,12 +5222,12 @@
       </c>
       <c r="B89" s="17" t="inlineStr">
         <is>
-          <t>PrepaidPackDetailsDrawer</t>
+          <t>PrepaidCartStep</t>
         </is>
       </c>
       <c r="C89" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidPackDetailsDrawer.tsx</t>
+          <t>components/patterns/PrepaidCartStep.tsx</t>
         </is>
       </c>
       <c r="D89" s="20" t="inlineStr">
@@ -5177,14 +5243,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G89" s="17" t="inlineStr">
-        <is>
-          <t>PrepaidPlanStep</t>
-        </is>
-      </c>
+      <c r="G89" s="17" t="inlineStr"/>
       <c r="H89" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5258,12 @@
       </c>
       <c r="B90" s="17" t="inlineStr">
         <is>
-          <t>PrepaidPlanCard</t>
+          <t>PrepaidCheckoutStep</t>
         </is>
       </c>
       <c r="C90" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidPlanCard.tsx</t>
+          <t>components/patterns/PrepaidCheckoutStep.tsx</t>
         </is>
       </c>
       <c r="D90" s="20" t="inlineStr">
@@ -5217,14 +5279,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G90" s="17" t="inlineStr">
-        <is>
-          <t>PrepaidPlanStep</t>
-        </is>
-      </c>
+      <c r="G90" s="17" t="inlineStr"/>
       <c r="H90" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5236,12 +5294,12 @@
       </c>
       <c r="B91" s="17" t="inlineStr">
         <is>
-          <t>PrepaidPlanStep</t>
+          <t>PrepaidPackDetailsDrawer</t>
         </is>
       </c>
       <c r="C91" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidPlanStep.tsx</t>
+          <t>components/patterns/PrepaidPackDetailsDrawer.tsx</t>
         </is>
       </c>
       <c r="D91" s="20" t="inlineStr">
@@ -5257,10 +5315,14 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G91" s="17" t="inlineStr"/>
+      <c r="G91" s="17" t="inlineStr">
+        <is>
+          <t>PrepaidPlanStep</t>
+        </is>
+      </c>
       <c r="H91" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5272,12 +5334,12 @@
       </c>
       <c r="B92" s="17" t="inlineStr">
         <is>
-          <t>SummaryTables</t>
+          <t>PrepaidPlanCard</t>
         </is>
       </c>
       <c r="C92" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CheckoutSummaryTables.tsx</t>
+          <t>components/patterns/PrepaidPlanCard.tsx</t>
         </is>
       </c>
       <c r="D92" s="20" t="inlineStr">
@@ -5295,12 +5357,12 @@
       </c>
       <c r="G92" s="17" t="inlineStr">
         <is>
-          <t>CheckoutSummaryStep, checkoutDetailedTables</t>
+          <t>PrepaidPlanStep</t>
         </is>
       </c>
       <c r="H92" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5374,12 @@
       </c>
       <c r="B93" s="17" t="inlineStr">
         <is>
-          <t>WinCashPaymentStep</t>
+          <t>PrepaidPlanStep</t>
         </is>
       </c>
       <c r="C93" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/WinCashPaymentStep.tsx</t>
+          <t>components/patterns/PrepaidPlanStep.tsx</t>
         </is>
       </c>
       <c r="D93" s="20" t="inlineStr">
@@ -5348,12 +5410,12 @@
       </c>
       <c r="B94" s="17" t="inlineStr">
         <is>
-          <t>BillingAccountStep</t>
+          <t>SummaryTables</t>
         </is>
       </c>
       <c r="C94" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/BillingAccountStep.tsx</t>
+          <t>components/patterns/CheckoutSummaryTables.tsx</t>
         </is>
       </c>
       <c r="D94" s="20" t="inlineStr">
@@ -5362,14 +5424,18 @@
         </is>
       </c>
       <c r="E94" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F94" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G94" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G94" s="17" t="inlineStr">
+        <is>
+          <t>CheckoutSummaryStep, checkoutDetailedTables</t>
+        </is>
+      </c>
       <c r="H94" s="17" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -5384,12 +5450,12 @@
       </c>
       <c r="B95" s="17" t="inlineStr">
         <is>
-          <t>BillingProfileSetupDrawer</t>
+          <t>WinCashPaymentStep</t>
         </is>
       </c>
       <c r="C95" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/BillingProfileSetupDrawer.tsx</t>
+          <t>components/patterns/WinCashPaymentStep.tsx</t>
         </is>
       </c>
       <c r="D95" s="20" t="inlineStr">
@@ -5398,21 +5464,17 @@
         </is>
       </c>
       <c r="E95" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F95" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G95" s="17" t="inlineStr">
-        <is>
-          <t>BillingAccountStep</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G95" s="17" t="inlineStr"/>
       <c r="H95" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5424,12 +5486,12 @@
       </c>
       <c r="B96" s="17" t="inlineStr">
         <is>
-          <t>CreditLimitCard</t>
+          <t>BillingAccountStep</t>
         </is>
       </c>
       <c r="C96" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CreditLimitCard.tsx</t>
+          <t>components/patterns/BillingAccountStep.tsx</t>
         </is>
       </c>
       <c r="D96" s="20" t="inlineStr">
@@ -5460,12 +5522,12 @@
       </c>
       <c r="B97" s="17" t="inlineStr">
         <is>
-          <t>ZsbAddressStep</t>
+          <t>BillingProfileSetupDrawer</t>
         </is>
       </c>
       <c r="C97" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/ZsbAddressStep.tsx</t>
+          <t>components/patterns/BillingProfileSetupDrawer.tsx</t>
         </is>
       </c>
       <c r="D97" s="20" t="inlineStr">
@@ -5483,12 +5545,12 @@
       </c>
       <c r="G97" s="17" t="inlineStr">
         <is>
-          <t>addressFromBilling</t>
+          <t>BillingAccountStep</t>
         </is>
       </c>
       <c r="H97" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5500,12 +5562,12 @@
       </c>
       <c r="B98" s="17" t="inlineStr">
         <is>
-          <t>AppointmentBookingStep</t>
+          <t>CreditLimitCard</t>
         </is>
       </c>
       <c r="C98" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/AppointmentBookingStep.tsx</t>
+          <t>components/patterns/CreditLimitCard.tsx</t>
         </is>
       </c>
       <c r="D98" s="20" t="inlineStr">
@@ -5514,11 +5576,11 @@
         </is>
       </c>
       <c r="E98" s="17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F98" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G98" s="17" t="inlineStr"/>
@@ -5536,12 +5598,12 @@
       </c>
       <c r="B99" s="17" t="inlineStr">
         <is>
-          <t>DemoFaultPanel</t>
+          <t>ZsbAddressStep</t>
         </is>
       </c>
       <c r="C99" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DemoFaultPanel.tsx</t>
+          <t>components/patterns/ZsbAddressStep.tsx</t>
         </is>
       </c>
       <c r="D99" s="20" t="inlineStr">
@@ -5550,14 +5612,18 @@
         </is>
       </c>
       <c r="E99" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F99" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
-        </is>
-      </c>
-      <c r="G99" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G99" s="17" t="inlineStr">
+        <is>
+          <t>addressFromBilling</t>
+        </is>
+      </c>
       <c r="H99" s="17" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -5572,12 +5638,12 @@
       </c>
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>DonorAttachmentStep</t>
+          <t>AppointmentBookingStep</t>
         </is>
       </c>
       <c r="C100" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DonorAttachmentStep.tsx</t>
+          <t>components/patterns/AppointmentBookingStep.tsx</t>
         </is>
       </c>
       <c r="D100" s="20" t="inlineStr">
@@ -5586,11 +5652,11 @@
         </is>
       </c>
       <c r="E100" s="17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F100" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, administration</t>
         </is>
       </c>
       <c r="G100" s="17" t="inlineStr"/>
@@ -5608,12 +5674,12 @@
       </c>
       <c r="B101" s="17" t="inlineStr">
         <is>
-          <t>DonorDetailsStep</t>
+          <t>DemoFaultPanel</t>
         </is>
       </c>
       <c r="C101" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DonorDetailsStep.tsx</t>
+          <t>components/patterns/DemoFaultPanel.tsx</t>
         </is>
       </c>
       <c r="D101" s="20" t="inlineStr">
@@ -5629,11 +5695,7 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
         </is>
       </c>
-      <c r="G101" s="17" t="inlineStr">
-        <is>
-          <t>DonorAttachmentStep</t>
-        </is>
-      </c>
+      <c r="G101" s="17" t="inlineStr"/>
       <c r="H101" s="17" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -5648,12 +5710,12 @@
       </c>
       <c r="B102" s="17" t="inlineStr">
         <is>
-          <t>EntityMissing</t>
+          <t>DonorAttachmentStep</t>
         </is>
       </c>
       <c r="C102" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/EntityMissing.tsx</t>
+          <t>components/patterns/DonorAttachmentStep.tsx</t>
         </is>
       </c>
       <c r="D102" s="20" t="inlineStr">
@@ -5666,7 +5728,7 @@
       </c>
       <c r="F102" s="17" t="inlineStr">
         <is>
-          <t>lead-management, order-management, sim-number-management, trouble-ticketing-complaints, customer360, tasks</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
         </is>
       </c>
       <c r="G102" s="17" t="inlineStr"/>
@@ -5684,12 +5746,12 @@
       </c>
       <c r="B103" s="17" t="inlineStr">
         <is>
-          <t>RestrictedRowsNotice</t>
+          <t>DonorDetailsStep</t>
         </is>
       </c>
       <c r="C103" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/RestrictedRowsNotice.tsx</t>
+          <t>components/patterns/DonorDetailsStep.tsx</t>
         </is>
       </c>
       <c r="D103" s="20" t="inlineStr">
@@ -5702,13 +5764,17 @@
       </c>
       <c r="F103" s="17" t="inlineStr">
         <is>
-          <t>order-management, trouble-ticketing-complaints, orders, support, tasks, tickets</t>
-        </is>
-      </c>
-      <c r="G103" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
+        </is>
+      </c>
+      <c r="G103" s="17" t="inlineStr">
+        <is>
+          <t>DonorAttachmentStep</t>
+        </is>
+      </c>
       <c r="H103" s="17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5720,12 +5786,12 @@
       </c>
       <c r="B104" s="17" t="inlineStr">
         <is>
-          <t>ActivityCommentsStep</t>
+          <t>EntityMissing</t>
         </is>
       </c>
       <c r="C104" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/ActivityCommentsStep.tsx</t>
+          <t>components/patterns/EntityMissing.tsx</t>
         </is>
       </c>
       <c r="D104" s="20" t="inlineStr">
@@ -5734,17 +5800,17 @@
         </is>
       </c>
       <c r="E104" s="17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F104" s="17" t="inlineStr">
         <is>
-          <t>pre-to-post-migration, sim-number-management, administration</t>
+          <t>lead-management, order-management, sim-number-management, trouble-ticketing-complaints, customer360, tasks</t>
         </is>
       </c>
       <c r="G104" s="17" t="inlineStr"/>
       <c r="H104" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5756,12 +5822,12 @@
       </c>
       <c r="B105" s="17" t="inlineStr">
         <is>
-          <t>LineSelectionStep</t>
+          <t>RestrictedRowsNotice</t>
         </is>
       </c>
       <c r="C105" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/LineSelectionStep.tsx</t>
+          <t>components/patterns/RestrictedRowsNotice.tsx</t>
         </is>
       </c>
       <c r="D105" s="20" t="inlineStr">
@@ -5770,17 +5836,17 @@
         </is>
       </c>
       <c r="E105" s="17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F105" s="17" t="inlineStr">
         <is>
-          <t>mobile-service-changes, pre-to-post-migration, administration</t>
+          <t>order-management, trouble-ticketing-complaints, orders, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G105" s="17" t="inlineStr"/>
       <c r="H105" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -5792,12 +5858,12 @@
       </c>
       <c r="B106" s="17" t="inlineStr">
         <is>
-          <t>TicketCreationModal</t>
+          <t>ActivityCommentsStep</t>
         </is>
       </c>
       <c r="C106" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/TicketCreationModal.tsx</t>
+          <t>components/patterns/ActivityCommentsStep.tsx</t>
         </is>
       </c>
       <c r="D106" s="20" t="inlineStr">
@@ -5810,13 +5876,13 @@
       </c>
       <c r="F106" s="17" t="inlineStr">
         <is>
-          <t>trouble-ticketing-complaints, customer360, support</t>
+          <t>pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G106" s="17" t="inlineStr"/>
       <c r="H106" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -5828,31 +5894,31 @@
       </c>
       <c r="B107" s="17" t="inlineStr">
         <is>
-          <t>BulkOperationPortal</t>
+          <t>LineSelectionStep</t>
         </is>
       </c>
       <c r="C107" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/BulkOperationPortal.tsx</t>
-        </is>
-      </c>
-      <c r="D107" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>components/patterns/LineSelectionStep.tsx</t>
+        </is>
+      </c>
+      <c r="D107" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E107" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F107" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b</t>
+          <t>mobile-service-changes, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G107" s="17" t="inlineStr"/>
       <c r="H107" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5864,31 +5930,31 @@
       </c>
       <c r="B108" s="17" t="inlineStr">
         <is>
-          <t>DualPlaySerialCheckStep</t>
+          <t>TicketCreationModal</t>
         </is>
       </c>
       <c r="C108" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DualPlaySerialCheckStep.tsx</t>
-        </is>
-      </c>
-      <c r="D108" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>components/patterns/TicketCreationModal.tsx</t>
+        </is>
+      </c>
+      <c r="D108" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E108" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F108" s="17" t="inlineStr">
         <is>
-          <t>fwa-5g-home</t>
+          <t>trouble-ticketing-complaints, customer360, support</t>
         </is>
       </c>
       <c r="G108" s="17" t="inlineStr"/>
       <c r="H108" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5900,12 +5966,12 @@
       </c>
       <c r="B109" s="17" t="inlineStr">
         <is>
-          <t>SimSwapFormStep</t>
+          <t>BulkOperationPortal</t>
         </is>
       </c>
       <c r="C109" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/SimSwapFormStep.tsx</t>
+          <t>components/patterns/BulkOperationPortal.tsx</t>
         </is>
       </c>
       <c r="D109" s="21" t="inlineStr">
@@ -5918,7 +5984,7 @@
       </c>
       <c r="F109" s="17" t="inlineStr">
         <is>
-          <t>sim-number-management</t>
+          <t>enterprise-iot-b2b</t>
         </is>
       </c>
       <c r="G109" s="17" t="inlineStr"/>
@@ -5936,12 +6002,12 @@
       </c>
       <c r="B110" s="17" t="inlineStr">
         <is>
-          <t>VerificationGate</t>
+          <t>DualPlaySerialCheckStep</t>
         </is>
       </c>
       <c r="C110" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/VerificationGate.tsx</t>
+          <t>components/patterns/DualPlaySerialCheckStep.tsx</t>
         </is>
       </c>
       <c r="D110" s="21" t="inlineStr">
@@ -5954,85 +6020,85 @@
       </c>
       <c r="F110" s="17" t="inlineStr">
         <is>
-          <t>customer360</t>
+          <t>fwa-5g-home</t>
         </is>
       </c>
       <c r="G110" s="17" t="inlineStr"/>
       <c r="H110" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="17" t="inlineStr">
         <is>
-          <t>Wizard</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="B111" s="17" t="inlineStr">
         <is>
-          <t>AbandonDialog</t>
+          <t>SimSwapFormStep</t>
         </is>
       </c>
       <c r="C111" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/WizardDialogs.tsx</t>
-        </is>
-      </c>
-      <c r="D111" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>components/patterns/SimSwapFormStep.tsx</t>
+        </is>
+      </c>
+      <c r="D111" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E111" s="17" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F111" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>sim-number-management</t>
         </is>
       </c>
       <c r="G111" s="17" t="inlineStr"/>
       <c r="H111" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="17" t="inlineStr">
         <is>
-          <t>Wizard</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="B112" s="17" t="inlineStr">
         <is>
-          <t>CustomerMirrorPanel</t>
+          <t>VerificationGate</t>
         </is>
       </c>
       <c r="C112" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/CustomerMirrorPanel.tsx</t>
-        </is>
-      </c>
-      <c r="D112" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>components/patterns/VerificationGate.tsx</t>
+        </is>
+      </c>
+      <c r="D112" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E112" s="17" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F112" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>customer360</t>
         </is>
       </c>
       <c r="G112" s="17" t="inlineStr"/>
       <c r="H112" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -6044,12 +6110,12 @@
       </c>
       <c r="B113" s="17" t="inlineStr">
         <is>
-          <t>CustomerViewButton</t>
+          <t>AbandonDialog</t>
         </is>
       </c>
       <c r="C113" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/CustomerViewButton.tsx</t>
+          <t>components/patterns/wizard/WizardDialogs.tsx</t>
         </is>
       </c>
       <c r="D113" s="20" t="inlineStr">
@@ -6065,14 +6131,10 @@
           <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
-      <c r="G113" s="17" t="inlineStr">
-        <is>
-          <t>WizardStepHeader</t>
-        </is>
-      </c>
+      <c r="G113" s="17" t="inlineStr"/>
       <c r="H113" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -6084,12 +6146,12 @@
       </c>
       <c r="B114" s="17" t="inlineStr">
         <is>
-          <t>StepSummaryPanel</t>
+          <t>CustomerMirrorPanel</t>
         </is>
       </c>
       <c r="C114" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/StepSummaryPanel.tsx</t>
+          <t>components/patterns/wizard/CustomerMirrorPanel.tsx</t>
         </is>
       </c>
       <c r="D114" s="20" t="inlineStr">
@@ -6108,7 +6170,7 @@
       <c r="G114" s="17" t="inlineStr"/>
       <c r="H114" s="17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6120,12 +6182,12 @@
       </c>
       <c r="B115" s="17" t="inlineStr">
         <is>
-          <t>StepSummarySection</t>
+          <t>CustomerViewButton</t>
         </is>
       </c>
       <c r="C115" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/StepSummarySection.tsx</t>
+          <t>components/patterns/wizard/CustomerViewButton.tsx</t>
         </is>
       </c>
       <c r="D115" s="20" t="inlineStr">
@@ -6143,12 +6205,12 @@
       </c>
       <c r="G115" s="17" t="inlineStr">
         <is>
-          <t>StepSummaryPanel</t>
+          <t>WizardStepHeader</t>
         </is>
       </c>
       <c r="H115" s="17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -6160,12 +6222,12 @@
       </c>
       <c r="B116" s="17" t="inlineStr">
         <is>
-          <t>SummaryFieldRow</t>
+          <t>StepSummaryPanel</t>
         </is>
       </c>
       <c r="C116" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/SummaryFieldRow.tsx</t>
+          <t>components/patterns/wizard/StepSummaryPanel.tsx</t>
         </is>
       </c>
       <c r="D116" s="20" t="inlineStr">
@@ -6181,14 +6243,10 @@
           <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
-      <c r="G116" s="17" t="inlineStr">
-        <is>
-          <t>StepSummaryPanel</t>
-        </is>
-      </c>
+      <c r="G116" s="17" t="inlineStr"/>
       <c r="H116" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -6200,12 +6258,12 @@
       </c>
       <c r="B117" s="17" t="inlineStr">
         <is>
-          <t>WizardFooter</t>
+          <t>StepSummarySection</t>
         </is>
       </c>
       <c r="C117" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/WizardFooter.tsx</t>
+          <t>components/patterns/wizard/StepSummarySection.tsx</t>
         </is>
       </c>
       <c r="D117" s="20" t="inlineStr">
@@ -6221,10 +6279,14 @@
           <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
-      <c r="G117" s="17" t="inlineStr"/>
+      <c r="G117" s="17" t="inlineStr">
+        <is>
+          <t>StepSummaryPanel</t>
+        </is>
+      </c>
       <c r="H117" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -6236,12 +6298,12 @@
       </c>
       <c r="B118" s="17" t="inlineStr">
         <is>
-          <t>WizardStepHeader</t>
+          <t>SummaryFieldRow</t>
         </is>
       </c>
       <c r="C118" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/WizardStepHeader.tsx</t>
+          <t>components/patterns/wizard/SummaryFieldRow.tsx</t>
         </is>
       </c>
       <c r="D118" s="20" t="inlineStr">
@@ -6257,10 +6319,14 @@
           <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
-      <c r="G118" s="17" t="inlineStr"/>
+      <c r="G118" s="17" t="inlineStr">
+        <is>
+          <t>StepSummaryPanel</t>
+        </is>
+      </c>
       <c r="H118" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6272,12 +6338,12 @@
       </c>
       <c r="B119" s="17" t="inlineStr">
         <is>
-          <t>WizardTitleBand</t>
+          <t>WizardFooter</t>
         </is>
       </c>
       <c r="C119" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/wizard/WizardTitleBand.tsx</t>
+          <t>components/patterns/wizard/WizardFooter.tsx</t>
         </is>
       </c>
       <c r="D119" s="20" t="inlineStr">
@@ -6296,12 +6362,84 @@
       <c r="G119" s="17" t="inlineStr"/>
       <c r="H119" s="17" t="inlineStr">
         <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="17" t="inlineStr">
+        <is>
+          <t>Wizard</t>
+        </is>
+      </c>
+      <c r="B120" s="17" t="inlineStr">
+        <is>
+          <t>WizardStepHeader</t>
+        </is>
+      </c>
+      <c r="C120" s="17" t="inlineStr">
+        <is>
+          <t>components/patterns/wizard/WizardStepHeader.tsx</t>
+        </is>
+      </c>
+      <c r="D120" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
+        </is>
+      </c>
+      <c r="E120" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F120" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+      <c r="G120" s="17" t="inlineStr"/>
+      <c r="H120" s="17" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="17" t="inlineStr">
+        <is>
+          <t>Wizard</t>
+        </is>
+      </c>
+      <c r="B121" s="17" t="inlineStr">
+        <is>
+          <t>WizardTitleBand</t>
+        </is>
+      </c>
+      <c r="C121" s="17" t="inlineStr">
+        <is>
+          <t>components/patterns/wizard/WizardTitleBand.tsx</t>
+        </is>
+      </c>
+      <c r="D121" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
+        </is>
+      </c>
+      <c r="E121" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F121" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+      <c r="G121" s="17" t="inlineStr"/>
+      <c r="H121" s="17" t="inlineStr">
+        <is>
           <t>2026-10-20</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H119"/>
+  <autoFilter ref="A1:H121"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6312,7 +6450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.50" customWidth="1" min="1" max="1"/>
@@ -7192,10 +7330,14 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G22" s="17" t="inlineStr"/>
+      <c r="G22" s="17" t="inlineStr">
+        <is>
+          <t>PostpaidAddonsPanel, PostpaidPlanAddonsStep</t>
+        </is>
+      </c>
       <c r="H22" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -7283,12 +7425,12 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>eligibilityGuard</t>
+          <t>numberWaiver</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>engines/eligibilityGuard.ts</t>
+          <t>engines/numberWaiver.ts</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -7297,17 +7439,21 @@
         </is>
       </c>
       <c r="E25" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F25" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="inlineStr">
+        <is>
+          <t>CheckoutDefaultLayout, CheckoutSummaryStep, checkoutDetailedTables, checkoutSummaryRows, useCheckoutSummary</t>
+        </is>
+      </c>
       <c r="H25" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>uncommitted</t>
         </is>
       </c>
     </row>
@@ -7319,12 +7465,12 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>serviceLocationLookup</t>
+          <t>eligibilityGuard</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>engines/serviceLocationLookup.ts</t>
+          <t>engines/eligibilityGuard.ts</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -7337,17 +7483,13 @@
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G26" s="17" t="inlineStr">
-        <is>
-          <t>ZsbAddressStep</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="inlineStr"/>
       <c r="H26" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -7359,12 +7501,12 @@
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>agentTaskEngine</t>
+          <t>serviceLocationLookup</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
-          <t>engines/agentTaskEngine.ts</t>
+          <t>engines/serviceLocationLookup.ts</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -7373,17 +7515,21 @@
         </is>
       </c>
       <c r="E27" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F27" s="17" t="inlineStr">
         <is>
-          <t>dashboard, order-management, trouble-ticketing-complaints, orders, support, tasks</t>
-        </is>
-      </c>
-      <c r="G27" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="inlineStr">
+        <is>
+          <t>ZsbAddressStep</t>
+        </is>
+      </c>
       <c r="H27" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7395,12 +7541,12 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>approvalAuthority</t>
+          <t>agentTaskEngine</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>engines/approvalAuthority.ts</t>
+          <t>engines/agentTaskEngine.ts</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -7413,13 +7559,13 @@
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>dashboard, order-management, sim-number-management, navigation, customer360, orders</t>
+          <t>dashboard, order-management, trouble-ticketing-complaints, orders, support, tasks</t>
         </is>
       </c>
       <c r="G28" s="17" t="inlineStr"/>
       <c r="H28" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7431,12 +7577,12 @@
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>portInEngine</t>
+          <t>approvalAuthority</t>
         </is>
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>engines/portInEngine.ts</t>
+          <t>engines/approvalAuthority.ts</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -7449,13 +7595,13 @@
       </c>
       <c r="F29" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
+          <t>dashboard, order-management, sim-number-management, navigation, customer360, orders</t>
         </is>
       </c>
       <c r="G29" s="17" t="inlineStr"/>
       <c r="H29" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7613,12 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>csvExport</t>
+          <t>portInEngine</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>engines/csvExport.ts</t>
+          <t>engines/portInEngine.ts</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -7481,17 +7627,17 @@
         </is>
       </c>
       <c r="E30" s="17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F30" s="17" t="inlineStr">
         <is>
-          <t>trouble-ticketing-complaints, customer360, profile, support</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
         </is>
       </c>
       <c r="G30" s="17" t="inlineStr"/>
       <c r="H30" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7503,12 +7649,12 @@
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>bellNotificationExpiry</t>
+          <t>csvExport</t>
         </is>
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>engines/bellNotificationExpiry.ts</t>
+          <t>engines/csvExport.ts</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -7517,11 +7663,11 @@
         </is>
       </c>
       <c r="E31" s="17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F31" s="17" t="inlineStr">
         <is>
-          <t>administration, customer360</t>
+          <t>trouble-ticketing-complaints, customer360, profile, support</t>
         </is>
       </c>
       <c r="G31" s="17" t="inlineStr"/>
@@ -7539,12 +7685,12 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>businessAccountEngine</t>
+          <t>bellNotificationExpiry</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>engines/businessAccountEngine.ts</t>
+          <t>engines/bellNotificationExpiry.ts</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -7557,13 +7703,13 @@
       </c>
       <c r="F32" s="17" t="inlineStr">
         <is>
-          <t>customer-search, customer360</t>
+          <t>administration, customer360</t>
         </is>
       </c>
       <c r="G32" s="17" t="inlineStr"/>
       <c r="H32" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7575,12 +7721,12 @@
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>navigationEngine</t>
+          <t>businessAccountEngine</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>engines/navigationEngine.ts</t>
+          <t>engines/businessAccountEngine.ts</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -7593,13 +7739,13 @@
       </c>
       <c r="F33" s="17" t="inlineStr">
         <is>
-          <t>navigation, customer360</t>
+          <t>customer-search, customer360</t>
         </is>
       </c>
       <c r="G33" s="17" t="inlineStr"/>
       <c r="H33" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -7611,12 +7757,12 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>qnomyQueueEngine</t>
+          <t>navigationEngine</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>engines/qnomyQueueEngine.ts</t>
+          <t>engines/navigationEngine.ts</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -7629,17 +7775,13 @@
       </c>
       <c r="F34" s="17" t="inlineStr">
         <is>
-          <t>navigation, tickets</t>
-        </is>
-      </c>
-      <c r="G34" s="17" t="inlineStr">
-        <is>
-          <t>qnomyWalkIns</t>
-        </is>
-      </c>
+          <t>navigation, customer360</t>
+        </is>
+      </c>
+      <c r="G34" s="17" t="inlineStr"/>
       <c r="H34" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -7651,31 +7793,35 @@
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>agentProfileEngine</t>
+          <t>qnomyQueueEngine</t>
         </is>
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
-          <t>engines/agentProfileEngine.ts</t>
-        </is>
-      </c>
-      <c r="D35" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>engines/qnomyQueueEngine.ts</t>
+        </is>
+      </c>
+      <c r="D35" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E35" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="G35" s="17" t="inlineStr"/>
+          <t>navigation, tickets</t>
+        </is>
+      </c>
+      <c r="G35" s="17" t="inlineStr">
+        <is>
+          <t>qnomyWalkIns</t>
+        </is>
+      </c>
       <c r="H35" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7687,12 +7833,12 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>customer360VisibilityEngine</t>
+          <t>agentProfileEngine</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>engines/customer360VisibilityEngine.ts</t>
+          <t>engines/agentProfileEngine.ts</t>
         </is>
       </c>
       <c r="D36" s="21" t="inlineStr">
@@ -7705,13 +7851,13 @@
       </c>
       <c r="F36" s="17" t="inlineStr">
         <is>
-          <t>customer360</t>
+          <t>navigation</t>
         </is>
       </c>
       <c r="G36" s="17" t="inlineStr"/>
       <c r="H36" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7723,12 +7869,12 @@
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>profileChangeTicket</t>
+          <t>customer360VisibilityEngine</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>engines/profileChangeTicket.ts</t>
+          <t>engines/customer360VisibilityEngine.ts</t>
         </is>
       </c>
       <c r="D37" s="21" t="inlineStr">
@@ -7747,7 +7893,7 @@
       <c r="G37" s="17" t="inlineStr"/>
       <c r="H37" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7759,12 +7905,12 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>qnomyWalkIns</t>
+          <t>profileChangeTicket</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>engines/qnomyWalkIns.ts</t>
+          <t>engines/profileChangeTicket.ts</t>
         </is>
       </c>
       <c r="D38" s="21" t="inlineStr">
@@ -7777,13 +7923,13 @@
       </c>
       <c r="F38" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
+          <t>customer360</t>
         </is>
       </c>
       <c r="G38" s="17" t="inlineStr"/>
       <c r="H38" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7941,12 @@
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>roleSwitchPurge</t>
+          <t>qnomyWalkIns</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>engines/roleSwitchPurge.ts</t>
+          <t>engines/qnomyWalkIns.ts</t>
         </is>
       </c>
       <c r="D39" s="21" t="inlineStr">
@@ -7819,7 +7965,7 @@
       <c r="G39" s="17" t="inlineStr"/>
       <c r="H39" s="17" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7977,12 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>searchScopeEngine</t>
+          <t>roleSwitchPurge</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>engines/searchScopeEngine.ts</t>
+          <t>engines/roleSwitchPurge.ts</t>
         </is>
       </c>
       <c r="D40" s="21" t="inlineStr">
@@ -7855,7 +8001,7 @@
       <c r="G40" s="17" t="inlineStr"/>
       <c r="H40" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -7867,27 +8013,31 @@
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>moduleDescriptions</t>
+          <t>searchScopeEngine</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>engines/moduleDescriptions.ts</t>
-        </is>
-      </c>
-      <c r="D41" s="23" t="inlineStr">
-        <is>
-          <t>App shell only</t>
+          <t>engines/searchScopeEngine.ts</t>
+        </is>
+      </c>
+      <c r="D41" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E41" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F41" s="17" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
       <c r="G41" s="17" t="inlineStr"/>
       <c r="H41" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -7899,12 +8049,12 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>screenGrouping</t>
+          <t>moduleDescriptions</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>engines/screenGrouping.ts</t>
+          <t>engines/moduleDescriptions.ts</t>
         </is>
       </c>
       <c r="D42" s="23" t="inlineStr">
@@ -7926,40 +8076,32 @@
     <row r="43">
       <c r="A43" s="17" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Engine</t>
         </is>
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>customerContextStore</t>
+          <t>screenGrouping</t>
         </is>
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>stores/customerContextStore.ts</t>
-        </is>
-      </c>
-      <c r="D43" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>engines/screenGrouping.ts</t>
+        </is>
+      </c>
+      <c r="D43" s="23" t="inlineStr">
+        <is>
+          <t>App shell only</t>
         </is>
       </c>
       <c r="E43" s="17" t="n">
-        <v>25</v>
-      </c>
-      <c r="F43" s="17" t="inlineStr">
-        <is>
-          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
-        </is>
-      </c>
-      <c r="G43" s="17" t="inlineStr">
-        <is>
-          <t>ActivationCompleteScreen, useActedForCustomer, useWizardDraftActions, roleSwitchPurge, authStore</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F43" s="17" t="inlineStr"/>
+      <c r="G43" s="17" t="inlineStr"/>
       <c r="H43" s="17" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7971,12 +8113,12 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>authStore</t>
+          <t>customerContextStore</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>stores/authStore.ts</t>
+          <t>stores/customerContextStore.ts</t>
         </is>
       </c>
       <c r="D44" s="20" t="inlineStr">
@@ -7985,21 +8127,21 @@
         </is>
       </c>
       <c r="E44" s="17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F44" s="17" t="inlineStr">
         <is>
-          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, sales, support, tasks, tickets</t>
+          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G44" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, ActivationCompleteScreen, useWizardDraftActions, activityEngine, agentProfileEngine, profileChangeTicket, configStore, entityStore</t>
+          <t>ActivationCompleteScreen, useActedForCustomer, useWizardDraftActions, roleSwitchPurge, authStore</t>
         </is>
       </c>
       <c r="H44" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -8011,12 +8153,12 @@
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>entityStore</t>
+          <t>authStore</t>
         </is>
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>stores/entityStore.ts</t>
+          <t>stores/authStore.ts</t>
         </is>
       </c>
       <c r="D45" s="20" t="inlineStr">
@@ -8034,12 +8176,12 @@
       </c>
       <c r="G45" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen, DonorAttachmentStep, DonorDetailsStep, useIdLookup, useDraftStepSync, useWizardDraftActions, activityEngine, bellNotificationExpiry, profileChangeTicket</t>
+          <t>ActivationCompleteScreen, useWizardDraftActions, activityEngine, agentProfileEngine, profileChangeTicket, configStore, entityStore</t>
         </is>
       </c>
       <c r="H45" s="17" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8051,12 +8193,12 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>personaStore</t>
+          <t>entityStore</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>stores/personaStore.ts</t>
+          <t>stores/entityStore.ts</t>
         </is>
       </c>
       <c r="D46" s="20" t="inlineStr">
@@ -8065,21 +8207,21 @@
         </is>
       </c>
       <c r="E46" s="17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F46" s="17" t="inlineStr">
         <is>
-          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, support, tasks, tickets</t>
+          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G46" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, eligibilityRowsModel, AppointmentBookingStep, TicketCreationModal, useCheckoutSummary, useIdLookup, useRestrictedCustomers, configStore</t>
+          <t>ActivationCompleteScreen, DonorAttachmentStep, DonorDetailsStep, useIdLookup, useDraftStepSync, useWizardDraftActions, activityEngine, bellNotificationExpiry, profileChangeTicket</t>
         </is>
       </c>
       <c r="H46" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -8091,12 +8233,12 @@
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>notificationStore</t>
+          <t>personaStore</t>
         </is>
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>stores/notificationStore.ts</t>
+          <t>stores/personaStore.ts</t>
         </is>
       </c>
       <c r="D47" s="20" t="inlineStr">
@@ -8105,21 +8247,21 @@
         </is>
       </c>
       <c r="E47" s="17" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F47" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, profile, support, tasks</t>
+          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G47" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, ActivationCompleteScreen, TicketCreationModal, useJourneyMilestones, useWizardDraftActions, useWizardStepNavigation, profileChangeTicket, roleSwitchPurge, useSubmit</t>
+          <t>MsisdnPicker, eligibilityRowsModel, AppointmentBookingStep, TicketCreationModal, useCheckoutSummary, useIdLookup, useRestrictedCustomers, configStore</t>
         </is>
       </c>
       <c r="H47" s="17" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8131,12 +8273,12 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>workflowStore</t>
+          <t>notificationStore</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>stores/workflowStore.ts</t>
+          <t>stores/notificationStore.ts</t>
         </is>
       </c>
       <c r="D48" s="20" t="inlineStr">
@@ -8145,21 +8287,21 @@
         </is>
       </c>
       <c r="E48" s="17" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F48" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, profile, support, tasks</t>
         </is>
       </c>
       <c r="G48" s="17" t="inlineStr">
         <is>
-          <t>useJourneyStartResume, useMirrorChannel, useWizardDraftActions, useWizardStepNavigation, roleSwitchPurge</t>
+          <t>MsisdnPicker, ActivationCompleteScreen, TicketCreationModal, useJourneyMilestones, useWizardDraftActions, useWizardStepNavigation, profileChangeTicket, roleSwitchPurge, useSubmit</t>
         </is>
       </c>
       <c r="H48" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -8171,35 +8313,35 @@
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>customerVerificationStore</t>
+          <t>workflowStore</t>
         </is>
       </c>
       <c r="C49" s="17" t="inlineStr">
         <is>
-          <t>stores/customerVerificationStore.ts</t>
-        </is>
-      </c>
-      <c r="D49" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>stores/workflowStore.ts</t>
+        </is>
+      </c>
+      <c r="D49" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E49" s="17" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F49" s="17" t="inlineStr">
         <is>
-          <t>customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration</t>
         </is>
       </c>
       <c r="G49" s="17" t="inlineStr">
         <is>
-          <t>VerificationGate</t>
+          <t>useJourneyStartResume, useMirrorChannel, useWizardDraftActions, useWizardStepNavigation, roleSwitchPurge</t>
         </is>
       </c>
       <c r="H49" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8211,12 +8353,12 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>qnomyQueueStore</t>
+          <t>customerVerificationStore</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>stores/qnomyQueueStore.ts</t>
+          <t>stores/customerVerificationStore.ts</t>
         </is>
       </c>
       <c r="D50" s="21" t="inlineStr">
@@ -8229,13 +8371,17 @@
       </c>
       <c r="F50" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="G50" s="17" t="inlineStr"/>
+          <t>customer360</t>
+        </is>
+      </c>
+      <c r="G50" s="17" t="inlineStr">
+        <is>
+          <t>VerificationGate</t>
+        </is>
+      </c>
       <c r="H50" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -8247,12 +8393,12 @@
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>regionStore</t>
+          <t>qnomyQueueStore</t>
         </is>
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>stores/regionStore.ts</t>
+          <t>stores/qnomyQueueStore.ts</t>
         </is>
       </c>
       <c r="D51" s="21" t="inlineStr">
@@ -8271,7 +8417,7 @@
       <c r="G51" s="17" t="inlineStr"/>
       <c r="H51" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -8283,12 +8429,12 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>sidebarStore</t>
+          <t>regionStore</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>stores/sidebarStore.ts</t>
+          <t>stores/regionStore.ts</t>
         </is>
       </c>
       <c r="D52" s="21" t="inlineStr">
@@ -8307,7 +8453,7 @@
       <c r="G52" s="17" t="inlineStr"/>
       <c r="H52" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -8319,12 +8465,12 @@
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>themeStore</t>
+          <t>sidebarStore</t>
         </is>
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>stores/themeStore.ts</t>
+          <t>stores/sidebarStore.ts</t>
         </is>
       </c>
       <c r="D53" s="21" t="inlineStr">
@@ -8343,7 +8489,7 @@
       <c r="G53" s="17" t="inlineStr"/>
       <c r="H53" s="17" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8355,67 +8501,63 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>configStore</t>
+          <t>themeStore</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>stores/configStore.ts</t>
-        </is>
-      </c>
-      <c r="D54" s="23" t="inlineStr">
-        <is>
-          <t>App shell only</t>
+          <t>stores/themeStore.ts</t>
+        </is>
+      </c>
+      <c r="D54" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E54" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F54" s="17" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
       <c r="G54" s="17" t="inlineStr"/>
       <c r="H54" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="17" t="inlineStr">
         <is>
-          <t>Hook</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>useRestrictedCustomers</t>
+          <t>configStore</t>
         </is>
       </c>
       <c r="C55" s="17" t="inlineStr">
         <is>
-          <t>hooks/useRestrictedCustomers.ts</t>
-        </is>
-      </c>
-      <c r="D55" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>stores/configStore.ts</t>
+        </is>
+      </c>
+      <c r="D55" s="23" t="inlineStr">
+        <is>
+          <t>App shell only</t>
         </is>
       </c>
       <c r="E55" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="F55" s="17" t="inlineStr">
-        <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, trouble-ticketing-complaints, navigation, customer360, orders, profile, support, tasks, tickets</t>
-        </is>
-      </c>
-      <c r="G55" s="17" t="inlineStr">
-        <is>
-          <t>TicketCreationModal</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F55" s="17" t="inlineStr"/>
+      <c r="G55" s="17" t="inlineStr"/>
       <c r="H55" s="17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8427,12 +8569,12 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>useEnterToSubmit</t>
+          <t>useRestrictedCustomers</t>
         </is>
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t>hooks/useEnterToSubmit.ts</t>
+          <t>hooks/useRestrictedCustomers.ts</t>
         </is>
       </c>
       <c r="D56" s="20" t="inlineStr">
@@ -8441,21 +8583,21 @@
         </is>
       </c>
       <c r="E56" s="17" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F56" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, trouble-ticketing-complaints, navigation, customer360, orders, profile, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G56" s="17" t="inlineStr">
         <is>
-          <t>VerificationGate, useIdLookup</t>
+          <t>TicketCreationModal</t>
         </is>
       </c>
       <c r="H56" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8609,12 @@
       </c>
       <c r="B57" s="17" t="inlineStr">
         <is>
-          <t>useSearchListNav</t>
+          <t>useEnterToSubmit</t>
         </is>
       </c>
       <c r="C57" s="17" t="inlineStr">
         <is>
-          <t>hooks/useSearchListNav.ts</t>
+          <t>hooks/useEnterToSubmit.ts</t>
         </is>
       </c>
       <c r="D57" s="20" t="inlineStr">
@@ -8485,17 +8627,17 @@
       </c>
       <c r="F57" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, navigation, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G57" s="17" t="inlineStr">
         <is>
-          <t>CompanySearchInput, ContactPhoneInput, PlanSearchBox, LocationInput</t>
+          <t>VerificationGate, useIdLookup</t>
         </is>
       </c>
       <c r="H57" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -8507,12 +8649,12 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>useAreaOptions</t>
+          <t>useSearchListNav</t>
         </is>
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t>hooks/useAreaOptions.ts</t>
+          <t>hooks/useSearchListNav.ts</t>
         </is>
       </c>
       <c r="D58" s="20" t="inlineStr">
@@ -8521,21 +8663,21 @@
         </is>
       </c>
       <c r="E58" s="17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F58" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, navigation, administration, customer360</t>
         </is>
       </c>
       <c r="G58" s="17" t="inlineStr">
         <is>
-          <t>BillingAccountStep, ZsbAddressStep</t>
+          <t>CompanySearchInput, ContactPhoneInput, PlanSearchBox, LocationInput</t>
         </is>
       </c>
       <c r="H58" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -8547,12 +8689,12 @@
       </c>
       <c r="B59" s="17" t="inlineStr">
         <is>
-          <t>useSubmit</t>
+          <t>useAreaOptions</t>
         </is>
       </c>
       <c r="C59" s="17" t="inlineStr">
         <is>
-          <t>hooks/useSubmit.ts</t>
+          <t>hooks/useAreaOptions.ts</t>
         </is>
       </c>
       <c r="D59" s="20" t="inlineStr">
@@ -8561,17 +8703,21 @@
         </is>
       </c>
       <c r="E59" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F59" s="17" t="inlineStr">
         <is>
-          <t>lead-management, mnp-fnp-porting, sim-number-management, trouble-ticketing-complaints, customer360, tasks</t>
-        </is>
-      </c>
-      <c r="G59" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G59" s="17" t="inlineStr">
+        <is>
+          <t>BillingAccountStep, ZsbAddressStep</t>
+        </is>
+      </c>
       <c r="H59" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8583,68 +8729,64 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>useMinWidth</t>
+          <t>useSubmit</t>
         </is>
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t>hooks/useMinWidth.ts</t>
-        </is>
-      </c>
-      <c r="D60" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>hooks/useSubmit.ts</t>
+        </is>
+      </c>
+      <c r="D60" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E60" s="17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F60" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
+          <t>lead-management, mnp-fnp-porting, sim-number-management, trouble-ticketing-complaints, customer360, tasks</t>
         </is>
       </c>
       <c r="G60" s="17" t="inlineStr"/>
       <c r="H60" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="17" t="inlineStr">
         <is>
-          <t>Helper</t>
+          <t>Hook</t>
         </is>
       </c>
       <c r="B61" s="17" t="inlineStr">
         <is>
-          <t>statusTone</t>
+          <t>useMinWidth</t>
         </is>
       </c>
       <c r="C61" s="17" t="inlineStr">
         <is>
-          <t>lib/statusTone.ts</t>
-        </is>
-      </c>
-      <c r="D61" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>hooks/useMinWidth.ts</t>
+        </is>
+      </c>
+      <c r="D61" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E61" s="17" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F61" s="17" t="inlineStr">
         <is>
-          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, orders, sales, support, tasks, tickets</t>
-        </is>
-      </c>
-      <c r="G61" s="17" t="inlineStr">
-        <is>
-          <t>ruleEngine</t>
-        </is>
-      </c>
+          <t>navigation</t>
+        </is>
+      </c>
+      <c r="G61" s="17" t="inlineStr"/>
       <c r="H61" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
@@ -8659,12 +8801,12 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>format</t>
+          <t>statusTone</t>
         </is>
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t>lib/format.ts</t>
+          <t>lib/statusTone.ts</t>
         </is>
       </c>
       <c r="D62" s="20" t="inlineStr">
@@ -8673,21 +8815,21 @@
         </is>
       </c>
       <c r="E62" s="17" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F62" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, tasks</t>
+          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, orders, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G62" s="17" t="inlineStr">
         <is>
-          <t>AdditionalDocumentsUpload, CafDocumentUpload, MsisdnPicker, GuidedContactStep, IdLookupStep, StepSummaryPanel, stepSummary, customer360Engine, postpaidPricing</t>
+          <t>ruleEngine</t>
         </is>
       </c>
       <c r="H62" s="17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8841,12 @@
       </c>
       <c r="B63" s="17" t="inlineStr">
         <is>
-          <t>buildEnv</t>
+          <t>format</t>
         </is>
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>lib/buildEnv.ts</t>
+          <t>lib/format.ts</t>
         </is>
       </c>
       <c r="D63" s="20" t="inlineStr">
@@ -8713,21 +8855,21 @@
         </is>
       </c>
       <c r="E63" s="17" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F63" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, tasks</t>
         </is>
       </c>
       <c r="G63" s="17" t="inlineStr">
         <is>
-          <t>syntheticMarker, navigationEngine</t>
+          <t>AdditionalDocumentsUpload, CafDocumentUpload, MsisdnPicker, documentUploadRules, GuidedContactStep, IdLookupStep, StepSummaryPanel, stepSummary, customer360Engine, postpaidPricing</t>
         </is>
       </c>
       <c r="H63" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -8739,12 +8881,12 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>deviceType</t>
+          <t>buildEnv</t>
         </is>
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
-          <t>lib/deviceType.ts</t>
+          <t>lib/buildEnv.ts</t>
         </is>
       </c>
       <c r="D64" s="20" t="inlineStr">
@@ -8753,21 +8895,21 @@
         </is>
       </c>
       <c r="E64" s="17" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F64" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360</t>
         </is>
       </c>
       <c r="G64" s="17" t="inlineStr">
         <is>
-          <t>IdFileUpload, PassportScanSections, SimSerialScanner, SimTypeStep, cafTypes</t>
+          <t>syntheticMarker, navigationEngine</t>
         </is>
       </c>
       <c r="H64" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -8779,12 +8921,12 @@
       </c>
       <c r="B65" s="17" t="inlineStr">
         <is>
-          <t>taskId</t>
+          <t>deviceType</t>
         </is>
       </c>
       <c r="C65" s="17" t="inlineStr">
         <is>
-          <t>lib/taskId.ts</t>
+          <t>lib/deviceType.ts</t>
         </is>
       </c>
       <c r="D65" s="20" t="inlineStr">
@@ -8793,16 +8935,16 @@
         </is>
       </c>
       <c r="E65" s="17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F65" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration, customer360</t>
         </is>
       </c>
       <c r="G65" s="17" t="inlineStr">
         <is>
-          <t>useWizardDraftActions</t>
+          <t>IdFileUpload, PassportScanSections, SimSerialScanner, SimTypeStep, cafTypes</t>
         </is>
       </c>
       <c r="H65" s="17" t="inlineStr">
@@ -8819,12 +8961,12 @@
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>connectionType</t>
+          <t>taskId</t>
         </is>
       </c>
       <c r="C66" s="17" t="inlineStr">
         <is>
-          <t>lib/connectionType.ts</t>
+          <t>lib/taskId.ts</t>
         </is>
       </c>
       <c r="D66" s="20" t="inlineStr">
@@ -8833,21 +8975,21 @@
         </is>
       </c>
       <c r="E66" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F66" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G66" s="17" t="inlineStr">
         <is>
-          <t>ConnectionTypeTag</t>
+          <t>useWizardDraftActions</t>
         </is>
       </c>
       <c r="H66" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8859,12 +9001,12 @@
       </c>
       <c r="B67" s="17" t="inlineStr">
         <is>
-          <t>serviceTypeTag</t>
+          <t>connectionType</t>
         </is>
       </c>
       <c r="C67" s="17" t="inlineStr">
         <is>
-          <t>lib/serviceTypeTag.ts</t>
+          <t>lib/connectionType.ts</t>
         </is>
       </c>
       <c r="D67" s="20" t="inlineStr">
@@ -8882,12 +9024,12 @@
       </c>
       <c r="G67" s="17" t="inlineStr">
         <is>
-          <t>ServiceTypeTag</t>
+          <t>ConnectionTypeTag</t>
         </is>
       </c>
       <c r="H67" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -8899,31 +9041,35 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>screenName</t>
+          <t>serviceTypeTag</t>
         </is>
       </c>
       <c r="C68" s="17" t="inlineStr">
         <is>
-          <t>lib/screenName.ts</t>
-        </is>
-      </c>
-      <c r="D68" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>lib/serviceTypeTag.ts</t>
+        </is>
+      </c>
+      <c r="D68" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E68" s="17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F68" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="G68" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G68" s="17" t="inlineStr">
+        <is>
+          <t>ServiceTypeTag</t>
+        </is>
+      </c>
       <c r="H68" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -8935,12 +9081,12 @@
       </c>
       <c r="B69" s="17" t="inlineStr">
         <is>
-          <t>values</t>
+          <t>screenName</t>
         </is>
       </c>
       <c r="C69" s="17" t="inlineStr">
         <is>
-          <t>lib/values.ts</t>
+          <t>lib/screenName.ts</t>
         </is>
       </c>
       <c r="D69" s="21" t="inlineStr">
@@ -8953,22 +9099,58 @@
       </c>
       <c r="F69" s="17" t="inlineStr">
         <is>
+          <t>navigation</t>
+        </is>
+      </c>
+      <c r="G69" s="17" t="inlineStr"/>
+      <c r="H69" s="17" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="17" t="inlineStr">
+        <is>
+          <t>Helper</t>
+        </is>
+      </c>
+      <c r="B70" s="17" t="inlineStr">
+        <is>
+          <t>values</t>
+        </is>
+      </c>
+      <c r="C70" s="17" t="inlineStr">
+        <is>
+          <t>lib/values.ts</t>
+        </is>
+      </c>
+      <c r="D70" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
+        </is>
+      </c>
+      <c r="E70" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="17" t="inlineStr">
+        <is>
           <t>customer360</t>
         </is>
       </c>
-      <c r="G69" s="17" t="inlineStr">
+      <c r="G70" s="17" t="inlineStr">
         <is>
           <t>customer360Demo</t>
         </is>
       </c>
-      <c r="H69" s="17" t="inlineStr">
+      <c r="H70" s="17" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H69"/>
+  <autoFilter ref="A1:H70"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
+++ b/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'UI Components'!$A$1:$H$121</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Shared Code'!$A$1:$H$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Shared Code'!$A$1:$H$72</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="C9" s="17" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D9" s="17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E9" s="17" t="n">
         <v>6</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="C12" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" s="17" t="n">
         <v>2</v>
@@ -855,14 +855,14 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>120 UI components + 69 non-UI files</t>
+          <t>120 UI components + 71 non-UI files</t>
         </is>
       </c>
       <c r="C13" s="18" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E13" s="18" t="n">
         <v>23</v>
@@ -1093,41 +1093,72 @@
     <row r="6">
       <c r="A6" s="17" t="inlineStr">
         <is>
+          <t>Number Selection</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>Choose a number: search, Free and Star bands, price filter, plan entitlement note, reserve and clear.</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>capabilities/NumberSelection/NumberSelection.tsx
+capabilities/NumberSelection/WaiveOff.tsx
+capabilities/NumberSelection/index.ts
+capabilities/NumberSelection/step.tsx
+capabilities/NumberSelection/summary.ts
+components/domain/MsisdnPicker.tsx
+components/domain/msisdnPickerModel.ts</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
           <t>Guided activation wizard</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>The step shell every activation / migration / port-in journey runs in.</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>capabilities/GuidedActivationWizard/GuidedActivationWizard.tsx
 capabilities/GuidedActivationWizard/index.ts</t>
         </is>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D7" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Customer Type &amp; Discounts</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Special customer types (retired, MADA, B2B2C): the evidence the agent collects, the rules for accepting or rejecting the benefit, and the customer's benefits.</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>capabilities/CustomerType/CustomerTypeStep.tsx
 capabilities/CustomerType/customerTypeModel.ts
@@ -1136,55 +1167,56 @@
 components/domain/CompanySearchInput.tsx</t>
         </is>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D8" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, administration, customer360</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Eligibility gate</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>Hard-stop / soft-stop / pass eligibility check shown after identification, with the outcome panel, checks report and footer actions.</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>capabilities/EligibilityGate/EligibilityGateStep.tsx
 capabilities/EligibilityGate/EligibilityOutcomes.tsx
 capabilities/EligibilityGate/eligibilityOutcomesModel.ts
-capabilities/EligibilityGate/index.ts</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="n">
+capabilities/EligibilityGate/index.ts
+capabilities/EligibilityGate/newIdentity.ts</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>Cross-Sell Offers</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>Recommended offers for the identified customer: offer cards, details drawer, interested (lead) and select actions, and hand-off to the other journeys.</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>capabilities/CrossSellOffers/CrossSalesStep.tsx
 capabilities/CrossSellOffers/HandOff.tsx
@@ -1197,27 +1229,27 @@
 capabilities/CrossSellOffers/summary.ts</t>
         </is>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D10" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>SIM Type</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Choose and validate the SIM: Physical (scan or enter the serial) or eSIM (issued, handed over after payment).</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>capabilities/SimType/SimSerial.tsx
 capabilities/SimType/SimType.tsx
@@ -1228,43 +1260,12 @@
 components/domain/SimSerialScanner.tsx</t>
         </is>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D11" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="17" t="inlineStr">
-        <is>
-          <t>Number Selection</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>Choose a number: search, Free and Star bands, price filter, plan entitlement note, reserve and clear.</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>capabilities/NumberSelection/NumberSelection.tsx
-capabilities/NumberSelection/WaiveOff.tsx
-capabilities/NumberSelection/index.ts
-capabilities/NumberSelection/step.tsx
-capabilities/NumberSelection/summary.ts
-components/domain/MsisdnPicker.tsx
-components/domain/msisdnPickerModel.ts</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1867,7 @@
       </c>
       <c r="H2" s="17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1982,12 @@
       </c>
       <c r="G5" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, BillingAccountStep, PostpaidDiscountsPanel, DataTable</t>
+          <t>MsisdnPicker, BillingAccountStep, PostpaidDiscountsPanel, PostpaidPlanAddonsStep, DataTable</t>
         </is>
       </c>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2147,7 @@
       </c>
       <c r="H9" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2227,7 @@
       </c>
       <c r="H11" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2302,7 @@
       </c>
       <c r="G13" s="17" t="inlineStr">
         <is>
-          <t>CustomerViewButton, CloseButton, Tabs</t>
+          <t>AdditionalDocumentsUpload, CustomerViewButton, CloseButton, Tabs</t>
         </is>
       </c>
       <c r="H13" s="17" t="inlineStr">
@@ -2426,7 +2427,7 @@
       </c>
       <c r="H16" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2467,7 @@
       </c>
       <c r="H17" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -2546,7 +2547,7 @@
       </c>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -2977,7 +2978,7 @@
       </c>
       <c r="G30" s="17" t="inlineStr">
         <is>
-          <t>LineSelectionStep, ConnectionTypeTag</t>
+          <t>LineSelectionStep, PostpaidPlanCard, ConnectionTypeTag</t>
         </is>
       </c>
       <c r="H30" s="17" t="inlineStr">
@@ -3130,7 +3131,7 @@
       <c r="G34" s="17" t="inlineStr"/>
       <c r="H34" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3347,7 @@
       </c>
       <c r="H40" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3467,7 @@
       </c>
       <c r="H43" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3579,7 @@
       <c r="G46" s="17" t="inlineStr"/>
       <c r="H46" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -3618,7 +3619,7 @@
       </c>
       <c r="H47" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3659,7 @@
       </c>
       <c r="H48" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3699,7 @@
       </c>
       <c r="H49" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3739,7 @@
       </c>
       <c r="H50" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3855,7 @@
       <c r="G53" s="17" t="inlineStr"/>
       <c r="H53" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3895,7 @@
       </c>
       <c r="H54" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4112,17 +4113,17 @@
         </is>
       </c>
       <c r="E60" s="17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F60" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fwa-5g-home, lead-management, mnp-fnp-porting, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
+          <t>enterprise-iot-b2b, fwa-5g-home, lead-management, mnp-fnp-porting, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, administration, bill-formatter, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G60" s="17" t="inlineStr"/>
       <c r="H60" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4198,7 +4199,7 @@
       <c r="G62" s="17" t="inlineStr"/>
       <c r="H62" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4515,7 @@
       <c r="G70" s="17" t="inlineStr"/>
       <c r="H70" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4627,7 @@
       </c>
       <c r="H73" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4662,7 +4663,7 @@
       <c r="G74" s="17" t="inlineStr"/>
       <c r="H74" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4739,7 @@
       <c r="G76" s="17" t="inlineStr"/>
       <c r="H76" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4974,7 +4975,7 @@
       </c>
       <c r="H82" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5014,7 +5015,7 @@
       </c>
       <c r="H83" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5054,7 +5055,7 @@
       </c>
       <c r="H84" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5095,7 @@
       </c>
       <c r="H85" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5170,7 +5171,7 @@
       <c r="G87" s="17" t="inlineStr"/>
       <c r="H87" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5211,7 @@
       </c>
       <c r="H88" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5283,7 @@
       <c r="G90" s="17" t="inlineStr"/>
       <c r="H90" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5323,7 @@
       </c>
       <c r="H91" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5362,7 +5363,7 @@
       </c>
       <c r="H92" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5399,7 @@
       <c r="G93" s="17" t="inlineStr"/>
       <c r="H93" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5475,7 @@
       <c r="G95" s="17" t="inlineStr"/>
       <c r="H95" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5511,7 @@
       <c r="G96" s="17" t="inlineStr"/>
       <c r="H96" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5586,7 +5587,7 @@
       <c r="G98" s="17" t="inlineStr"/>
       <c r="H98" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5627,7 @@
       </c>
       <c r="H99" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5919,7 @@
       <c r="G107" s="17" t="inlineStr"/>
       <c r="H107" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -6398,7 +6399,7 @@
       <c r="G120" s="17" t="inlineStr"/>
       <c r="H120" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6435,7 @@
       <c r="G121" s="17" t="inlineStr"/>
       <c r="H121" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -6450,7 +6451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.50" customWidth="1" min="1" max="1"/>
@@ -6647,11 +6648,11 @@
         </is>
       </c>
       <c r="E5" s="17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, support, tasks, tickets</t>
+          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G5" s="17" t="inlineStr">
@@ -6821,7 +6822,7 @@
       </c>
       <c r="H9" s="17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -6981,7 +6982,7 @@
       </c>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -7181,7 +7182,7 @@
       </c>
       <c r="H18" s="17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7217,12 @@
       </c>
       <c r="G19" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, CheckoutDefaultLayout, PostpaidMonthlySummary, checkoutDetailedTables, checkoutSummaryRows, useCheckoutSummary, usePostpaidPlanAddons</t>
+          <t>MsisdnPicker, CheckoutDefaultLayout, PostpaidAddonsPanel, PostpaidMonthlySummary, PostpaidPlanAddonsStep, checkoutDetailedTables, checkoutSummaryRows, useCheckoutSummary, usePostpaidPlanAddons</t>
         </is>
       </c>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7333,12 @@
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
-          <t>PostpaidAddonsPanel, PostpaidPlanAddonsStep</t>
+          <t>PostpaidAddonsPanel, PostpaidPlanAddonsStep, useCheckoutSummary, usePostpaidPlanAddons</t>
         </is>
       </c>
       <c r="H22" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -7425,12 +7426,12 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>numberWaiver</t>
+          <t>journeyDocuments</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>engines/numberWaiver.ts</t>
+          <t>engines/journeyDocuments.ts</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -7448,7 +7449,7 @@
       </c>
       <c r="G25" s="17" t="inlineStr">
         <is>
-          <t>CheckoutDefaultLayout, CheckoutSummaryStep, checkoutDetailedTables, checkoutSummaryRows, useCheckoutSummary</t>
+          <t>AdditionalDocumentsUpload, CafSignatureCapture</t>
         </is>
       </c>
       <c r="H25" s="17" t="inlineStr">
@@ -7465,12 +7466,12 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>eligibilityGuard</t>
+          <t>numberWaiver</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>engines/eligibilityGuard.ts</t>
+          <t>engines/numberWaiver.ts</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -7479,17 +7480,21 @@
         </is>
       </c>
       <c r="E26" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration</t>
-        </is>
-      </c>
-      <c r="G26" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="inlineStr">
+        <is>
+          <t>CheckoutDefaultLayout, CheckoutSummaryStep, checkoutDetailedTables, checkoutSummaryRows, useCheckoutSummary</t>
+        </is>
+      </c>
       <c r="H26" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -7501,12 +7506,12 @@
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>serviceLocationLookup</t>
+          <t>eligibilityGuard</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
-          <t>engines/serviceLocationLookup.ts</t>
+          <t>engines/eligibilityGuard.ts</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -7519,17 +7524,13 @@
       </c>
       <c r="F27" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G27" s="17" t="inlineStr">
-        <is>
-          <t>ZsbAddressStep</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="inlineStr"/>
       <c r="H27" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -7541,12 +7542,12 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>agentTaskEngine</t>
+          <t>serviceLocationLookup</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>engines/agentTaskEngine.ts</t>
+          <t>engines/serviceLocationLookup.ts</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -7555,17 +7556,21 @@
         </is>
       </c>
       <c r="E28" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>dashboard, order-management, trouble-ticketing-complaints, orders, support, tasks</t>
-        </is>
-      </c>
-      <c r="G28" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="inlineStr">
+        <is>
+          <t>ZsbAddressStep</t>
+        </is>
+      </c>
       <c r="H28" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7577,12 +7582,12 @@
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>approvalAuthority</t>
+          <t>agentTaskEngine</t>
         </is>
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>engines/approvalAuthority.ts</t>
+          <t>engines/agentTaskEngine.ts</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -7595,13 +7600,13 @@
       </c>
       <c r="F29" s="17" t="inlineStr">
         <is>
-          <t>dashboard, order-management, sim-number-management, navigation, customer360, orders</t>
+          <t>dashboard, order-management, trouble-ticketing-complaints, orders, support, tasks</t>
         </is>
       </c>
       <c r="G29" s="17" t="inlineStr"/>
       <c r="H29" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7613,12 +7618,12 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>portInEngine</t>
+          <t>approvalAuthority</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>engines/portInEngine.ts</t>
+          <t>engines/approvalAuthority.ts</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -7631,13 +7636,13 @@
       </c>
       <c r="F30" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
+          <t>dashboard, order-management, sim-number-management, navigation, customer360, orders</t>
         </is>
       </c>
       <c r="G30" s="17" t="inlineStr"/>
       <c r="H30" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7649,12 +7654,12 @@
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>csvExport</t>
+          <t>portInEngine</t>
         </is>
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>engines/csvExport.ts</t>
+          <t>engines/portInEngine.ts</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -7663,17 +7668,17 @@
         </is>
       </c>
       <c r="E31" s="17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F31" s="17" t="inlineStr">
         <is>
-          <t>trouble-ticketing-complaints, customer360, profile, support</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
         </is>
       </c>
       <c r="G31" s="17" t="inlineStr"/>
       <c r="H31" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7685,12 +7690,12 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>bellNotificationExpiry</t>
+          <t>csvExport</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>engines/bellNotificationExpiry.ts</t>
+          <t>engines/csvExport.ts</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -7699,11 +7704,11 @@
         </is>
       </c>
       <c r="E32" s="17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F32" s="17" t="inlineStr">
         <is>
-          <t>administration, customer360</t>
+          <t>trouble-ticketing-complaints, customer360, profile, support</t>
         </is>
       </c>
       <c r="G32" s="17" t="inlineStr"/>
@@ -7721,12 +7726,12 @@
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>businessAccountEngine</t>
+          <t>bellNotificationExpiry</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>engines/businessAccountEngine.ts</t>
+          <t>engines/bellNotificationExpiry.ts</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -7739,13 +7744,13 @@
       </c>
       <c r="F33" s="17" t="inlineStr">
         <is>
-          <t>customer-search, customer360</t>
+          <t>administration, customer360</t>
         </is>
       </c>
       <c r="G33" s="17" t="inlineStr"/>
       <c r="H33" s="17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7757,12 +7762,12 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>navigationEngine</t>
+          <t>businessAccountEngine</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>engines/navigationEngine.ts</t>
+          <t>engines/businessAccountEngine.ts</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -7775,13 +7780,13 @@
       </c>
       <c r="F34" s="17" t="inlineStr">
         <is>
-          <t>navigation, customer360</t>
+          <t>customer-search, customer360</t>
         </is>
       </c>
       <c r="G34" s="17" t="inlineStr"/>
       <c r="H34" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7798,12 @@
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>qnomyQueueEngine</t>
+          <t>navigationEngine</t>
         </is>
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
-          <t>engines/qnomyQueueEngine.ts</t>
+          <t>engines/navigationEngine.ts</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -7811,17 +7816,13 @@
       </c>
       <c r="F35" s="17" t="inlineStr">
         <is>
-          <t>navigation, tickets</t>
-        </is>
-      </c>
-      <c r="G35" s="17" t="inlineStr">
-        <is>
-          <t>qnomyWalkIns</t>
-        </is>
-      </c>
+          <t>navigation, customer360</t>
+        </is>
+      </c>
+      <c r="G35" s="17" t="inlineStr"/>
       <c r="H35" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -7833,31 +7834,35 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>agentProfileEngine</t>
+          <t>qnomyQueueEngine</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>engines/agentProfileEngine.ts</t>
-        </is>
-      </c>
-      <c r="D36" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>engines/qnomyQueueEngine.ts</t>
+        </is>
+      </c>
+      <c r="D36" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E36" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="G36" s="17" t="inlineStr"/>
+          <t>navigation, tickets</t>
+        </is>
+      </c>
+      <c r="G36" s="17" t="inlineStr">
+        <is>
+          <t>qnomyWalkIns</t>
+        </is>
+      </c>
       <c r="H36" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7869,12 +7874,12 @@
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>customer360VisibilityEngine</t>
+          <t>agentProfileEngine</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>engines/customer360VisibilityEngine.ts</t>
+          <t>engines/agentProfileEngine.ts</t>
         </is>
       </c>
       <c r="D37" s="21" t="inlineStr">
@@ -7887,13 +7892,13 @@
       </c>
       <c r="F37" s="17" t="inlineStr">
         <is>
-          <t>customer360</t>
+          <t>navigation</t>
         </is>
       </c>
       <c r="G37" s="17" t="inlineStr"/>
       <c r="H37" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7905,12 +7910,12 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>profileChangeTicket</t>
+          <t>customer360VisibilityEngine</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>engines/profileChangeTicket.ts</t>
+          <t>engines/customer360VisibilityEngine.ts</t>
         </is>
       </c>
       <c r="D38" s="21" t="inlineStr">
@@ -7929,7 +7934,7 @@
       <c r="G38" s="17" t="inlineStr"/>
       <c r="H38" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7941,12 +7946,12 @@
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>qnomyWalkIns</t>
+          <t>profileChangeTicket</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>engines/qnomyWalkIns.ts</t>
+          <t>engines/profileChangeTicket.ts</t>
         </is>
       </c>
       <c r="D39" s="21" t="inlineStr">
@@ -7959,13 +7964,13 @@
       </c>
       <c r="F39" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
+          <t>customer360</t>
         </is>
       </c>
       <c r="G39" s="17" t="inlineStr"/>
       <c r="H39" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -7977,12 +7982,12 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>roleSwitchPurge</t>
+          <t>qnomyWalkIns</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>engines/roleSwitchPurge.ts</t>
+          <t>engines/qnomyWalkIns.ts</t>
         </is>
       </c>
       <c r="D40" s="21" t="inlineStr">
@@ -8001,7 +8006,7 @@
       <c r="G40" s="17" t="inlineStr"/>
       <c r="H40" s="17" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -8013,12 +8018,12 @@
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>searchScopeEngine</t>
+          <t>roleSwitchPurge</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>engines/searchScopeEngine.ts</t>
+          <t>engines/roleSwitchPurge.ts</t>
         </is>
       </c>
       <c r="D41" s="21" t="inlineStr">
@@ -8037,7 +8042,7 @@
       <c r="G41" s="17" t="inlineStr"/>
       <c r="H41" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -8049,27 +8054,31 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>moduleDescriptions</t>
+          <t>searchScopeEngine</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>engines/moduleDescriptions.ts</t>
-        </is>
-      </c>
-      <c r="D42" s="23" t="inlineStr">
-        <is>
-          <t>App shell only</t>
+          <t>engines/searchScopeEngine.ts</t>
+        </is>
+      </c>
+      <c r="D42" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E42" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F42" s="17" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
       <c r="G42" s="17" t="inlineStr"/>
       <c r="H42" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -8081,12 +8090,12 @@
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>screenGrouping</t>
+          <t>moduleDescriptions</t>
         </is>
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>engines/screenGrouping.ts</t>
+          <t>engines/moduleDescriptions.ts</t>
         </is>
       </c>
       <c r="D43" s="23" t="inlineStr">
@@ -8108,40 +8117,32 @@
     <row r="44">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Engine</t>
         </is>
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>customerContextStore</t>
+          <t>screenGrouping</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>stores/customerContextStore.ts</t>
-        </is>
-      </c>
-      <c r="D44" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>engines/screenGrouping.ts</t>
+        </is>
+      </c>
+      <c r="D44" s="23" t="inlineStr">
+        <is>
+          <t>App shell only</t>
         </is>
       </c>
       <c r="E44" s="17" t="n">
-        <v>25</v>
-      </c>
-      <c r="F44" s="17" t="inlineStr">
-        <is>
-          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
-        </is>
-      </c>
-      <c r="G44" s="17" t="inlineStr">
-        <is>
-          <t>ActivationCompleteScreen, useActedForCustomer, useWizardDraftActions, roleSwitchPurge, authStore</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F44" s="17" t="inlineStr"/>
+      <c r="G44" s="17" t="inlineStr"/>
       <c r="H44" s="17" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -8153,12 +8154,12 @@
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>authStore</t>
+          <t>customerContextStore</t>
         </is>
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>stores/authStore.ts</t>
+          <t>stores/customerContextStore.ts</t>
         </is>
       </c>
       <c r="D45" s="20" t="inlineStr">
@@ -8167,21 +8168,21 @@
         </is>
       </c>
       <c r="E45" s="17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F45" s="17" t="inlineStr">
         <is>
-          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, sales, support, tasks, tickets</t>
+          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G45" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen, useWizardDraftActions, activityEngine, agentProfileEngine, profileChangeTicket, configStore, entityStore</t>
+          <t>ActivationCompleteScreen, useActedForCustomer, useWizardDraftActions, roleSwitchPurge, authStore</t>
         </is>
       </c>
       <c r="H45" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -8193,12 +8194,12 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>entityStore</t>
+          <t>authStore</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>stores/entityStore.ts</t>
+          <t>stores/authStore.ts</t>
         </is>
       </c>
       <c r="D46" s="20" t="inlineStr">
@@ -8216,12 +8217,12 @@
       </c>
       <c r="G46" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen, DonorAttachmentStep, DonorDetailsStep, useIdLookup, useDraftStepSync, useWizardDraftActions, activityEngine, bellNotificationExpiry, profileChangeTicket</t>
+          <t>ActivationCompleteScreen, useWizardDraftActions, activityEngine, agentProfileEngine, profileChangeTicket, configStore, entityStore</t>
         </is>
       </c>
       <c r="H46" s="17" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8233,12 +8234,12 @@
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>personaStore</t>
+          <t>entityStore</t>
         </is>
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>stores/personaStore.ts</t>
+          <t>stores/entityStore.ts</t>
         </is>
       </c>
       <c r="D47" s="20" t="inlineStr">
@@ -8247,21 +8248,21 @@
         </is>
       </c>
       <c r="E47" s="17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F47" s="17" t="inlineStr">
         <is>
-          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, support, tasks, tickets</t>
+          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, orders, profile, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G47" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, eligibilityRowsModel, AppointmentBookingStep, TicketCreationModal, useCheckoutSummary, useIdLookup, useRestrictedCustomers, configStore</t>
+          <t>ActivationCompleteScreen, DonorAttachmentStep, DonorDetailsStep, useIdLookup, useDraftStepSync, useWizardDraftActions, activityEngine, bellNotificationExpiry, profileChangeTicket</t>
         </is>
       </c>
       <c r="H47" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -8273,12 +8274,12 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>notificationStore</t>
+          <t>personaStore</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>stores/notificationStore.ts</t>
+          <t>stores/personaStore.ts</t>
         </is>
       </c>
       <c r="D48" s="20" t="inlineStr">
@@ -8287,21 +8288,21 @@
         </is>
       </c>
       <c r="E48" s="17" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F48" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, profile, support, tasks</t>
+          <t>dashboard, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, profile, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G48" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, ActivationCompleteScreen, TicketCreationModal, useJourneyMilestones, useWizardDraftActions, useWizardStepNavigation, profileChangeTicket, roleSwitchPurge, useSubmit</t>
+          <t>MsisdnPicker, eligibilityRowsModel, AppointmentBookingStep, TicketCreationModal, useCheckoutSummary, useIdLookup, useRestrictedCustomers, configStore</t>
         </is>
       </c>
       <c r="H48" s="17" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8313,12 +8314,12 @@
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>workflowStore</t>
+          <t>notificationStore</t>
         </is>
       </c>
       <c r="C49" s="17" t="inlineStr">
         <is>
-          <t>stores/workflowStore.ts</t>
+          <t>stores/notificationStore.ts</t>
         </is>
       </c>
       <c r="D49" s="20" t="inlineStr">
@@ -8327,21 +8328,21 @@
         </is>
       </c>
       <c r="E49" s="17" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F49" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360, profile, support, tasks</t>
         </is>
       </c>
       <c r="G49" s="17" t="inlineStr">
         <is>
-          <t>useJourneyStartResume, useMirrorChannel, useWizardDraftActions, useWizardStepNavigation, roleSwitchPurge</t>
+          <t>MsisdnPicker, ActivationCompleteScreen, TicketCreationModal, useJourneyMilestones, useWizardDraftActions, useWizardStepNavigation, profileChangeTicket, roleSwitchPurge, useSubmit</t>
         </is>
       </c>
       <c r="H49" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -8353,35 +8354,35 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>customerVerificationStore</t>
+          <t>workflowStore</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>stores/customerVerificationStore.ts</t>
-        </is>
-      </c>
-      <c r="D50" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>stores/workflowStore.ts</t>
+        </is>
+      </c>
+      <c r="D50" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E50" s="17" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F50" s="17" t="inlineStr">
         <is>
-          <t>customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration</t>
         </is>
       </c>
       <c r="G50" s="17" t="inlineStr">
         <is>
-          <t>VerificationGate</t>
+          <t>useJourneyStartResume, useMirrorChannel, useWizardDraftActions, useWizardStepNavigation, roleSwitchPurge</t>
         </is>
       </c>
       <c r="H50" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8393,12 +8394,12 @@
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>qnomyQueueStore</t>
+          <t>customerVerificationStore</t>
         </is>
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>stores/qnomyQueueStore.ts</t>
+          <t>stores/customerVerificationStore.ts</t>
         </is>
       </c>
       <c r="D51" s="21" t="inlineStr">
@@ -8411,13 +8412,17 @@
       </c>
       <c r="F51" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="G51" s="17" t="inlineStr"/>
+          <t>customer360</t>
+        </is>
+      </c>
+      <c r="G51" s="17" t="inlineStr">
+        <is>
+          <t>VerificationGate</t>
+        </is>
+      </c>
       <c r="H51" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -8429,12 +8434,12 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>regionStore</t>
+          <t>qnomyQueueStore</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>stores/regionStore.ts</t>
+          <t>stores/qnomyQueueStore.ts</t>
         </is>
       </c>
       <c r="D52" s="21" t="inlineStr">
@@ -8453,7 +8458,7 @@
       <c r="G52" s="17" t="inlineStr"/>
       <c r="H52" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -8465,12 +8470,12 @@
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>sidebarStore</t>
+          <t>regionStore</t>
         </is>
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>stores/sidebarStore.ts</t>
+          <t>stores/regionStore.ts</t>
         </is>
       </c>
       <c r="D53" s="21" t="inlineStr">
@@ -8489,7 +8494,7 @@
       <c r="G53" s="17" t="inlineStr"/>
       <c r="H53" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -8501,12 +8506,12 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>themeStore</t>
+          <t>sidebarStore</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>stores/themeStore.ts</t>
+          <t>stores/sidebarStore.ts</t>
         </is>
       </c>
       <c r="D54" s="21" t="inlineStr">
@@ -8525,7 +8530,7 @@
       <c r="G54" s="17" t="inlineStr"/>
       <c r="H54" s="17" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8537,67 +8542,63 @@
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>configStore</t>
+          <t>themeStore</t>
         </is>
       </c>
       <c r="C55" s="17" t="inlineStr">
         <is>
-          <t>stores/configStore.ts</t>
-        </is>
-      </c>
-      <c r="D55" s="23" t="inlineStr">
-        <is>
-          <t>App shell only</t>
+          <t>stores/themeStore.ts</t>
+        </is>
+      </c>
+      <c r="D55" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E55" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F55" s="17" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
       <c r="G55" s="17" t="inlineStr"/>
       <c r="H55" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="17" t="inlineStr">
         <is>
-          <t>Hook</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>useRestrictedCustomers</t>
+          <t>configStore</t>
         </is>
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t>hooks/useRestrictedCustomers.ts</t>
-        </is>
-      </c>
-      <c r="D56" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>stores/configStore.ts</t>
+        </is>
+      </c>
+      <c r="D56" s="23" t="inlineStr">
+        <is>
+          <t>App shell only</t>
         </is>
       </c>
       <c r="E56" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="F56" s="17" t="inlineStr">
-        <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, trouble-ticketing-complaints, navigation, customer360, orders, profile, support, tasks, tickets</t>
-        </is>
-      </c>
-      <c r="G56" s="17" t="inlineStr">
-        <is>
-          <t>TicketCreationModal</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F56" s="17" t="inlineStr"/>
+      <c r="G56" s="17" t="inlineStr"/>
       <c r="H56" s="17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8609,12 +8610,12 @@
       </c>
       <c r="B57" s="17" t="inlineStr">
         <is>
-          <t>useEnterToSubmit</t>
+          <t>useRestrictedCustomers</t>
         </is>
       </c>
       <c r="C57" s="17" t="inlineStr">
         <is>
-          <t>hooks/useEnterToSubmit.ts</t>
+          <t>hooks/useRestrictedCustomers.ts</t>
         </is>
       </c>
       <c r="D57" s="20" t="inlineStr">
@@ -8623,21 +8624,21 @@
         </is>
       </c>
       <c r="E57" s="17" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F57" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, order-management, trouble-ticketing-complaints, navigation, customer360, orders, profile, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G57" s="17" t="inlineStr">
         <is>
-          <t>VerificationGate, useIdLookup</t>
+          <t>TicketCreationModal</t>
         </is>
       </c>
       <c r="H57" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -8649,12 +8650,12 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>useSearchListNav</t>
+          <t>useEnterToSubmit</t>
         </is>
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t>hooks/useSearchListNav.ts</t>
+          <t>hooks/useEnterToSubmit.ts</t>
         </is>
       </c>
       <c r="D58" s="20" t="inlineStr">
@@ -8667,17 +8668,17 @@
       </c>
       <c r="F58" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, navigation, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
         </is>
       </c>
       <c r="G58" s="17" t="inlineStr">
         <is>
-          <t>CompanySearchInput, ContactPhoneInput, PlanSearchBox, LocationInput</t>
+          <t>VerificationGate, useIdLookup</t>
         </is>
       </c>
       <c r="H58" s="17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -8689,12 +8690,12 @@
       </c>
       <c r="B59" s="17" t="inlineStr">
         <is>
-          <t>useAreaOptions</t>
+          <t>useSearchListNav</t>
         </is>
       </c>
       <c r="C59" s="17" t="inlineStr">
         <is>
-          <t>hooks/useAreaOptions.ts</t>
+          <t>hooks/useSearchListNav.ts</t>
         </is>
       </c>
       <c r="D59" s="20" t="inlineStr">
@@ -8703,21 +8704,21 @@
         </is>
       </c>
       <c r="E59" s="17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F59" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, navigation, administration, customer360</t>
         </is>
       </c>
       <c r="G59" s="17" t="inlineStr">
         <is>
-          <t>BillingAccountStep, ZsbAddressStep</t>
+          <t>CompanySearchInput, ContactPhoneInput, PlanSearchBox, LocationInput</t>
         </is>
       </c>
       <c r="H59" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -8729,12 +8730,12 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>useSubmit</t>
+          <t>useAreaOptions</t>
         </is>
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t>hooks/useSubmit.ts</t>
+          <t>hooks/useAreaOptions.ts</t>
         </is>
       </c>
       <c r="D60" s="20" t="inlineStr">
@@ -8743,17 +8744,21 @@
         </is>
       </c>
       <c r="E60" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F60" s="17" t="inlineStr">
         <is>
-          <t>lead-management, mnp-fnp-porting, sim-number-management, trouble-ticketing-complaints, customer360, tasks</t>
-        </is>
-      </c>
-      <c r="G60" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G60" s="17" t="inlineStr">
+        <is>
+          <t>BillingAccountStep, ZsbAddressStep</t>
+        </is>
+      </c>
       <c r="H60" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8765,68 +8770,64 @@
       </c>
       <c r="B61" s="17" t="inlineStr">
         <is>
-          <t>useMinWidth</t>
+          <t>useSubmit</t>
         </is>
       </c>
       <c r="C61" s="17" t="inlineStr">
         <is>
-          <t>hooks/useMinWidth.ts</t>
-        </is>
-      </c>
-      <c r="D61" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>hooks/useSubmit.ts</t>
+        </is>
+      </c>
+      <c r="D61" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E61" s="17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F61" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
+          <t>lead-management, mnp-fnp-porting, sim-number-management, trouble-ticketing-complaints, customer360, tasks</t>
         </is>
       </c>
       <c r="G61" s="17" t="inlineStr"/>
       <c r="H61" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="17" t="inlineStr">
         <is>
-          <t>Helper</t>
+          <t>Hook</t>
         </is>
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>statusTone</t>
+          <t>useMinWidth</t>
         </is>
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t>lib/statusTone.ts</t>
-        </is>
-      </c>
-      <c r="D62" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>hooks/useMinWidth.ts</t>
+        </is>
+      </c>
+      <c r="D62" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E62" s="17" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F62" s="17" t="inlineStr">
         <is>
-          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, orders, sales, support, tasks, tickets</t>
-        </is>
-      </c>
-      <c r="G62" s="17" t="inlineStr">
-        <is>
-          <t>ruleEngine</t>
-        </is>
-      </c>
+          <t>navigation</t>
+        </is>
+      </c>
+      <c r="G62" s="17" t="inlineStr"/>
       <c r="H62" s="17" t="inlineStr">
         <is>
           <t>2026-10-18</t>
@@ -8855,21 +8856,21 @@
         </is>
       </c>
       <c r="E63" s="17" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F63" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, tasks</t>
+          <t>enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer-search, customer360, orders, support, tasks</t>
         </is>
       </c>
       <c r="G63" s="17" t="inlineStr">
         <is>
-          <t>AdditionalDocumentsUpload, CafDocumentUpload, MsisdnPicker, documentUploadRules, GuidedContactStep, IdLookupStep, StepSummaryPanel, stepSummary, customer360Engine, postpaidPricing</t>
+          <t>AdditionalDocumentsUpload, BillLimitEditor, CafDocumentUpload, MsisdnPicker, documentUploadRules, eligibilityRowsModel, ActivationCompleteScreen, CheckoutDefaultLayout, CreditLimitCard, FixedPlanStep, GuidedContactStep, IdLookupStep, LineSelectionStep, PlanSearchBox, PostpaidPlanCard, PrepaidCheckoutStep, PrepaidPackDetailsDrawer, PrepaidPlanCard, PrepaidPlanStep, WinCashPaymentStep, checkoutDetailedTables, StepSummaryPanel, stepSummary, prepaidSimCharge, addonCategories, creditLimit, customer360Engine, eligibilityEngine, postpaidPricing, ruleEngine</t>
         </is>
       </c>
       <c r="H63" s="17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -8881,12 +8882,12 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>buildEnv</t>
+          <t>statusTone</t>
         </is>
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
-          <t>lib/buildEnv.ts</t>
+          <t>lib/statusTone.ts</t>
         </is>
       </c>
       <c r="D64" s="20" t="inlineStr">
@@ -8895,21 +8896,21 @@
         </is>
       </c>
       <c r="E64" s="17" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F64" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360</t>
+          <t>dashboard, enterprise-iot-b2b, fixed-line-fibre, fwa-5g-home, lead-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, sim-number-management, trouble-ticketing-complaints, administration, customer360, orders, sales, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G64" s="17" t="inlineStr">
         <is>
-          <t>syntheticMarker, navigationEngine</t>
+          <t>ruleEngine</t>
         </is>
       </c>
       <c r="H64" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8921,12 +8922,12 @@
       </c>
       <c r="B65" s="17" t="inlineStr">
         <is>
-          <t>deviceType</t>
+          <t>buildEnv</t>
         </is>
       </c>
       <c r="C65" s="17" t="inlineStr">
         <is>
-          <t>lib/deviceType.ts</t>
+          <t>lib/buildEnv.ts</t>
         </is>
       </c>
       <c r="D65" s="20" t="inlineStr">
@@ -8935,21 +8936,21 @@
         </is>
       </c>
       <c r="E65" s="17" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F65" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, order-management, pre-to-post-migration, product-lines, sim-number-management, trouble-ticketing-complaints, navigation, administration, customer360</t>
         </is>
       </c>
       <c r="G65" s="17" t="inlineStr">
         <is>
-          <t>IdFileUpload, PassportScanSections, SimSerialScanner, SimTypeStep, cafTypes</t>
+          <t>syntheticMarker, navigationEngine</t>
         </is>
       </c>
       <c r="H65" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -8961,12 +8962,12 @@
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>taskId</t>
+          <t>deviceType</t>
         </is>
       </c>
       <c r="C66" s="17" t="inlineStr">
         <is>
-          <t>lib/taskId.ts</t>
+          <t>lib/deviceType.ts</t>
         </is>
       </c>
       <c r="D66" s="20" t="inlineStr">
@@ -8975,16 +8976,16 @@
         </is>
       </c>
       <c r="E66" s="17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F66" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, navigation, administration, customer360</t>
         </is>
       </c>
       <c r="G66" s="17" t="inlineStr">
         <is>
-          <t>useWizardDraftActions</t>
+          <t>IdFileUpload, PassportScanSections, SimSerialScanner, SimTypeStep, cafTypes</t>
         </is>
       </c>
       <c r="H66" s="17" t="inlineStr">
@@ -9001,12 +9002,12 @@
       </c>
       <c r="B67" s="17" t="inlineStr">
         <is>
-          <t>connectionType</t>
+          <t>taskId</t>
         </is>
       </c>
       <c r="C67" s="17" t="inlineStr">
         <is>
-          <t>lib/connectionType.ts</t>
+          <t>lib/taskId.ts</t>
         </is>
       </c>
       <c r="D67" s="20" t="inlineStr">
@@ -9015,21 +9016,21 @@
         </is>
       </c>
       <c r="E67" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F67" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G67" s="17" t="inlineStr">
         <is>
-          <t>ConnectionTypeTag</t>
+          <t>useWizardDraftActions</t>
         </is>
       </c>
       <c r="H67" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -9041,12 +9042,12 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>serviceTypeTag</t>
+          <t>connectionType</t>
         </is>
       </c>
       <c r="C68" s="17" t="inlineStr">
         <is>
-          <t>lib/serviceTypeTag.ts</t>
+          <t>lib/connectionType.ts</t>
         </is>
       </c>
       <c r="D68" s="20" t="inlineStr">
@@ -9064,12 +9065,12 @@
       </c>
       <c r="G68" s="17" t="inlineStr">
         <is>
-          <t>ServiceTypeTag</t>
+          <t>ConnectionTypeTag</t>
         </is>
       </c>
       <c r="H68" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -9081,31 +9082,35 @@
       </c>
       <c r="B69" s="17" t="inlineStr">
         <is>
-          <t>screenName</t>
+          <t>serviceTypeTag</t>
         </is>
       </c>
       <c r="C69" s="17" t="inlineStr">
         <is>
-          <t>lib/screenName.ts</t>
-        </is>
-      </c>
-      <c r="D69" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>lib/serviceTypeTag.ts</t>
+        </is>
+      </c>
+      <c r="D69" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
         </is>
       </c>
       <c r="E69" s="17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F69" s="17" t="inlineStr">
         <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="G69" s="17" t="inlineStr"/>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration, customer360</t>
+        </is>
+      </c>
+      <c r="G69" s="17" t="inlineStr">
+        <is>
+          <t>ServiceTypeTag</t>
+        </is>
+      </c>
       <c r="H69" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -9117,40 +9122,116 @@
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
+          <t>documentFileStore</t>
+        </is>
+      </c>
+      <c r="C70" s="17" t="inlineStr">
+        <is>
+          <t>lib/documentFileStore.ts</t>
+        </is>
+      </c>
+      <c r="D70" s="20" t="inlineStr">
+        <is>
+          <t>Shared (2+ areas)</t>
+        </is>
+      </c>
+      <c r="E70" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="F70" s="17" t="inlineStr">
+        <is>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G70" s="17" t="inlineStr">
+        <is>
+          <t>AdditionalDocumentsUpload</t>
+        </is>
+      </c>
+      <c r="H70" s="17" t="inlineStr">
+        <is>
+          <t>uncommitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="17" t="inlineStr">
+        <is>
+          <t>Helper</t>
+        </is>
+      </c>
+      <c r="B71" s="17" t="inlineStr">
+        <is>
+          <t>screenName</t>
+        </is>
+      </c>
+      <c r="C71" s="17" t="inlineStr">
+        <is>
+          <t>lib/screenName.ts</t>
+        </is>
+      </c>
+      <c r="D71" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
+        </is>
+      </c>
+      <c r="E71" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" s="17" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
+      <c r="G71" s="17" t="inlineStr"/>
+      <c r="H71" s="17" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="17" t="inlineStr">
+        <is>
+          <t>Helper</t>
+        </is>
+      </c>
+      <c r="B72" s="17" t="inlineStr">
+        <is>
           <t>values</t>
         </is>
       </c>
-      <c r="C70" s="17" t="inlineStr">
+      <c r="C72" s="17" t="inlineStr">
         <is>
           <t>lib/values.ts</t>
         </is>
       </c>
-      <c r="D70" s="21" t="inlineStr">
+      <c r="D72" s="21" t="inlineStr">
         <is>
           <t>Single area</t>
         </is>
       </c>
-      <c r="E70" s="17" t="n">
+      <c r="E72" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F70" s="17" t="inlineStr">
+      <c r="F72" s="17" t="inlineStr">
         <is>
           <t>customer360</t>
         </is>
       </c>
-      <c r="G70" s="17" t="inlineStr">
+      <c r="G72" s="17" t="inlineStr">
         <is>
           <t>customer360Demo</t>
         </is>
       </c>
-      <c r="H70" s="17" t="inlineStr">
+      <c r="H72" s="17" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H70"/>
+  <autoFilter ref="A1:H72"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
+++ b/vfq-dxp-app/reference/outputs/Reusable_Capabilities_Inventory_Reference.xlsx
@@ -718,13 +718,13 @@
         <v>53</v>
       </c>
       <c r="D7" s="17" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E7" s="17" t="n">
         <v>4</v>
       </c>
       <c r="F7" s="17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -862,13 +862,13 @@
         <v>191</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E13" s="18" t="n">
         <v>23</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="G3" s="17" t="inlineStr">
         <is>
-          <t>AdditionalDocumentsUpload, CafDocumentUpload, CompanySearchInput, ContactPhoneInput, EligibilityRows, FibreReadinessBanner, IdFileUpload, MsisdnPicker, PassportScanSections, QidImageUpload, QidInput, ScanFailureNotice, SimSerialScanner, AppointmentBookingStep, BillingAccountStep, CafSignatureCapture, DiscountCard, FixedPlanStep, OrderConfirmationScreen, PostpaidPlanCard, PrepaidPlanCard, PrepaidPlanStep, RestrictedCustomerNotice, RestrictedRowsNotice, ValidationStatus, ZsbAddressStep, CustomerViewButton, StepSummarySection, WizardFooter, ChoiceCards, DataTable, EmptyState, IconButton, LocationInput, Pager, PhoneNumberInput, SearchField, Select, Tabs</t>
+          <t>AdditionalDocumentsUpload, CafDocumentUpload, CompanySearchInput, ContactPhoneInput, EligibilityRows, FibreReadinessBanner, IdFileUpload, MsisdnPicker, PassportScanSections, QidImageUpload, QidInput, ScanFailureNotice, SimSerialScanner, AppointmentBookingStep, BillingAccountStep, CafSignatureCapture, FixedPlanStep, OrderConfirmationScreen, PostpaidPlanCard, PrepaidPlanCard, PrepaidPlanStep, RestrictedCustomerNotice, RestrictedRowsNotice, ValidationStatus, ZsbAddressStep, CustomerViewButton, StepSummarySection, WizardFooter, ChoiceCards, DataTable, EmptyState, IconButton, LocationInput, Pager, PhoneNumberInput, SearchField, Select, Tabs, offerCardParts</t>
         </is>
       </c>
       <c r="H3" s="17" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="G4" s="17" t="inlineStr">
         <is>
-          <t>ErrorBoundary, AdditionalDocumentsUpload, BillLimitEditor, CafDocumentUpload, EligibilityRows, IdFileUpload, MsisdnPicker, PassportScanSections, QidImageUpload, QidInput, SimSerialScanner, SimTypeStep, ActivationCompleteScreen, BillingAccountStep, BillingProfileSetupDrawer, BulkOperationPortal, CafSignatureCapture, CheckoutDefaultLayout, DemoFaultPanel, FixedPlanStep, IdLookupStatus, NewCustomerForm, OrderConfirmationScreen, PostpaidDiscountsPanel, PostpaidPlanCard, PrepaidCartStep, PrepaidCheckoutStep, PrepaidPackDetailsDrawer, PrepaidPlanCard, TicketCreationModal, ValidationStatus, VerificationGate, WinCashPaymentStep, ZsbAddressStep, CustomerViewButton, StepSummarySection, SummaryFieldRow, WizardDialogs, WizardFooter, WizardTitleBand, SignaturePad</t>
+          <t>ErrorBoundary, AdditionalDocumentsUpload, BillLimitEditor, CafDocumentUpload, EligibilityRows, IdFileUpload, MsisdnPicker, PassportScanSections, QidImageUpload, QidInput, SimSerialScanner, SimTypeStep, ActivationCompleteScreen, BillingAccountStep, BillingProfileSetupDrawer, BulkOperationPortal, CafSignatureCapture, CheckoutDefaultLayout, DemoFaultPanel, FixedPlanStep, IdLookupStatus, NewCustomerForm, OrderConfirmationScreen, PostpaidDiscountsPanel, PrepaidCartStep, PrepaidCheckoutStep, PrepaidPackDetailsDrawer, PrepaidPlanCard, TicketCreationModal, ValidationStatus, VerificationGate, WinCashPaymentStep, ZsbAddressStep, CustomerViewButton, StepSummarySection, SummaryFieldRow, WizardDialogs, WizardFooter, WizardTitleBand, SignaturePad</t>
         </is>
       </c>
       <c r="H4" s="17" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="G6" s="17" t="inlineStr">
         <is>
-          <t>AdditionalDocumentsUpload, CafDocumentUpload, MsisdnPicker, BillingAccountStep, BillingProfileSetupDrawer, BulkOperationPortal, CreditLimitCard, DonorDetailsStep, GuidedContactStep, NewCustomerForm, TicketCreationModal, ZsbAddressStep</t>
+          <t>AdditionalDocumentsUpload, CafDocumentUpload, MsisdnPicker, BillingAccountStep, BillingProfileSetupDrawer, BulkOperationPortal, CreditLimitCard, DonorDetailsStep, GuidedContactStep, NewCustomerForm, PostpaidPlanAddonsStep, TicketCreationModal, ZsbAddressStep</t>
         </is>
       </c>
       <c r="H6" s="17" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="G20" s="17" t="inlineStr">
         <is>
-          <t>MsisdnPicker, QidInput, AppointmentBookingStep, BillingAccountStep, DiscountCard, FixedPlanStep, LineSelectionStep, PostpaidPlanCard, PrepaidPlanCard, PrepaidPlanStep, ChoiceCards</t>
+          <t>MsisdnPicker, QidInput, AppointmentBookingStep, BillingAccountStep, CafSignatureCapture, DiscountCard, FixedPlanStep, LineSelectionStep, PostpaidPlanCard, PrepaidPlanCard, PrepaidPlanStep, ChoiceCards</t>
         </is>
       </c>
       <c r="H20" s="17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       <c r="G32" s="17" t="inlineStr"/>
       <c r="H32" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -3467,7 +3467,7 @@
       </c>
       <c r="H43" s="17" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="H48" s="17" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -3855,7 +3855,7 @@
       <c r="G53" s="17" t="inlineStr"/>
       <c r="H53" s="17" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="H54" s="17" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       <c r="G62" s="17" t="inlineStr"/>
       <c r="H62" s="17" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -4371,12 +4371,12 @@
       </c>
       <c r="B67" s="17" t="inlineStr">
         <is>
-          <t>NewCustomerForm</t>
+          <t>ValidationStatus</t>
         </is>
       </c>
       <c r="C67" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/NewCustomerForm.tsx</t>
+          <t>components/patterns/ValidationStatus.tsx</t>
         </is>
       </c>
       <c r="D67" s="20" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="G67" s="17" t="inlineStr">
         <is>
-          <t>IdLookupStep</t>
+          <t>IdLookupStatus</t>
         </is>
       </c>
       <c r="H67" s="17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -4411,12 +4411,12 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>ValidationStatus</t>
+          <t>SignatureCapture</t>
         </is>
       </c>
       <c r="C68" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/ValidationStatus.tsx</t>
+          <t>components/patterns/SignatureCapture.tsx</t>
         </is>
       </c>
       <c r="D68" s="20" t="inlineStr">
@@ -4425,21 +4425,21 @@
         </is>
       </c>
       <c r="E68" s="17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F68" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration, customer360</t>
+          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G68" s="17" t="inlineStr">
         <is>
-          <t>IdLookupStatus</t>
+          <t>CafSignatureCapture, DonorAttachmentStep, SimSwapFormStep</t>
         </is>
       </c>
       <c r="H68" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4451,12 +4451,12 @@
       </c>
       <c r="B69" s="17" t="inlineStr">
         <is>
-          <t>SignatureCapture</t>
+          <t>ActivationCompleteScreen</t>
         </is>
       </c>
       <c r="C69" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/SignatureCapture.tsx</t>
+          <t>components/patterns/ActivationCompleteScreen.tsx</t>
         </is>
       </c>
       <c r="D69" s="20" t="inlineStr">
@@ -4465,21 +4465,17 @@
         </is>
       </c>
       <c r="E69" s="17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F69" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, identity-customer-management, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, sim-number-management, administration</t>
-        </is>
-      </c>
-      <c r="G69" s="17" t="inlineStr">
-        <is>
-          <t>CafSignatureCapture, DonorAttachmentStep, SimSwapFormStep</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+        </is>
+      </c>
+      <c r="G69" s="17" t="inlineStr"/>
       <c r="H69" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4487,12 @@
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen</t>
+          <t>BillingAccountAutoResolver</t>
         </is>
       </c>
       <c r="C70" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/ActivationCompleteScreen.tsx</t>
+          <t>components/patterns/BillingAccountAutoResolver.tsx</t>
         </is>
       </c>
       <c r="D70" s="20" t="inlineStr">
@@ -4515,7 +4511,7 @@
       <c r="G70" s="17" t="inlineStr"/>
       <c r="H70" s="17" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -4527,12 +4523,12 @@
       </c>
       <c r="B71" s="17" t="inlineStr">
         <is>
-          <t>BillingAccountAutoResolver</t>
+          <t>CafSignatureCapture</t>
         </is>
       </c>
       <c r="C71" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/BillingAccountAutoResolver.tsx</t>
+          <t>components/patterns/CafSignatureCapture.tsx</t>
         </is>
       </c>
       <c r="D71" s="20" t="inlineStr">
@@ -4551,7 +4547,7 @@
       <c r="G71" s="17" t="inlineStr"/>
       <c r="H71" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -4563,12 +4559,12 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>CafSignatureCapture</t>
+          <t>CheckoutDefaultLayout</t>
         </is>
       </c>
       <c r="C72" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CafSignatureCapture.tsx</t>
+          <t>components/patterns/CheckoutDefaultLayout.tsx</t>
         </is>
       </c>
       <c r="D72" s="20" t="inlineStr">
@@ -4584,10 +4580,14 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G72" s="17" t="inlineStr"/>
+      <c r="G72" s="17" t="inlineStr">
+        <is>
+          <t>CheckoutSummaryStep</t>
+        </is>
+      </c>
       <c r="H72" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="B73" s="17" t="inlineStr">
         <is>
-          <t>CheckoutDefaultLayout</t>
+          <t>CheckoutSummaryStep</t>
         </is>
       </c>
       <c r="C73" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CheckoutDefaultLayout.tsx</t>
+          <t>components/patterns/CheckoutSummaryStep.tsx</t>
         </is>
       </c>
       <c r="D73" s="20" t="inlineStr">
@@ -4620,11 +4620,7 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G73" s="17" t="inlineStr">
-        <is>
-          <t>CheckoutSummaryStep</t>
-        </is>
-      </c>
+      <c r="G73" s="17" t="inlineStr"/>
       <c r="H73" s="17" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -4639,12 +4635,12 @@
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>CheckoutSummaryStep</t>
+          <t>DiscountCard</t>
         </is>
       </c>
       <c r="C74" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CheckoutSummaryStep.tsx</t>
+          <t>components/patterns/DiscountCard.tsx</t>
         </is>
       </c>
       <c r="D74" s="20" t="inlineStr">
@@ -4660,10 +4656,14 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G74" s="17" t="inlineStr"/>
+      <c r="G74" s="17" t="inlineStr">
+        <is>
+          <t>PostpaidDiscountsPanel</t>
+        </is>
+      </c>
       <c r="H74" s="17" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -4675,12 +4675,12 @@
       </c>
       <c r="B75" s="17" t="inlineStr">
         <is>
-          <t>DiscountCard</t>
+          <t>FixedPlanStep</t>
         </is>
       </c>
       <c r="C75" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DiscountCard.tsx</t>
+          <t>components/patterns/FixedPlanStep.tsx</t>
         </is>
       </c>
       <c r="D75" s="20" t="inlineStr">
@@ -4696,14 +4696,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G75" s="17" t="inlineStr">
-        <is>
-          <t>PostpaidDiscountsPanel</t>
-        </is>
-      </c>
+      <c r="G75" s="17" t="inlineStr"/>
       <c r="H75" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -4715,12 +4711,12 @@
       </c>
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>FixedPlanStep</t>
+          <t>FullTerms</t>
         </is>
       </c>
       <c r="C76" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/FixedPlanStep.tsx</t>
+          <t>components/patterns/CafTerms.tsx</t>
         </is>
       </c>
       <c r="D76" s="20" t="inlineStr">
@@ -4736,10 +4732,14 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G76" s="17" t="inlineStr"/>
+      <c r="G76" s="17" t="inlineStr">
+        <is>
+          <t>CafSignatureCapture</t>
+        </is>
+      </c>
       <c r="H76" s="17" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4751,12 +4751,12 @@
       </c>
       <c r="B77" s="17" t="inlineStr">
         <is>
-          <t>FullTerms</t>
+          <t>KeyInformationPanel</t>
         </is>
       </c>
       <c r="C77" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CafTerms.tsx</t>
+          <t>components/patterns/KeyInformationPanel.tsx</t>
         </is>
       </c>
       <c r="D77" s="20" t="inlineStr">
@@ -4772,11 +4772,7 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G77" s="17" t="inlineStr">
-        <is>
-          <t>CafSignatureCapture</t>
-        </is>
-      </c>
+      <c r="G77" s="17" t="inlineStr"/>
       <c r="H77" s="17" t="inlineStr">
         <is>
           <t>2026-10-15</t>
@@ -4791,12 +4787,12 @@
       </c>
       <c r="B78" s="17" t="inlineStr">
         <is>
-          <t>KeyInformationPanel</t>
+          <t>OrderConfirmationScreen</t>
         </is>
       </c>
       <c r="C78" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/KeyInformationPanel.tsx</t>
+          <t>components/patterns/OrderConfirmationScreen.tsx</t>
         </is>
       </c>
       <c r="D78" s="20" t="inlineStr">
@@ -4812,10 +4808,14 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G78" s="17" t="inlineStr"/>
+      <c r="G78" s="17" t="inlineStr">
+        <is>
+          <t>ActivationCompleteScreen</t>
+        </is>
+      </c>
       <c r="H78" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="B79" s="17" t="inlineStr">
         <is>
-          <t>OrderConfirmationScreen</t>
+          <t>PlanDetailsDrawer</t>
         </is>
       </c>
       <c r="C79" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/OrderConfirmationScreen.tsx</t>
+          <t>components/patterns/PlanDetailsDrawer.tsx</t>
         </is>
       </c>
       <c r="D79" s="20" t="inlineStr">
@@ -4850,12 +4850,12 @@
       </c>
       <c r="G79" s="17" t="inlineStr">
         <is>
-          <t>ActivationCompleteScreen</t>
+          <t>PostpaidPlanAddonsStep</t>
         </is>
       </c>
       <c r="H79" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4867,12 +4867,12 @@
       </c>
       <c r="B80" s="17" t="inlineStr">
         <is>
-          <t>PlanDetailsDrawer</t>
+          <t>PlanGroupPanel</t>
         </is>
       </c>
       <c r="C80" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PlanDetailsDrawer.tsx</t>
+          <t>components/patterns/PlanGroupPanel.tsx</t>
         </is>
       </c>
       <c r="D80" s="20" t="inlineStr">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="H80" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -4907,12 +4907,12 @@
       </c>
       <c r="B81" s="17" t="inlineStr">
         <is>
-          <t>PlanGroupPanel</t>
+          <t>PlanSearchBox</t>
         </is>
       </c>
       <c r="C81" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PlanGroupPanel.tsx</t>
+          <t>components/patterns/PlanSearchBox.tsx</t>
         </is>
       </c>
       <c r="D81" s="20" t="inlineStr">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="H81" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>PlanSearchBox</t>
+          <t>PlanTabStrip</t>
         </is>
       </c>
       <c r="C82" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PlanSearchBox.tsx</t>
+          <t>components/patterns/PlanTabStrip.tsx</t>
         </is>
       </c>
       <c r="D82" s="20" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="B83" s="17" t="inlineStr">
         <is>
-          <t>PlanTabStrip</t>
+          <t>PostpaidAddonsPanel</t>
         </is>
       </c>
       <c r="C83" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PlanTabStrip.tsx</t>
+          <t>components/patterns/PostpaidAddonsPanel.tsx</t>
         </is>
       </c>
       <c r="D83" s="20" t="inlineStr">
@@ -5027,12 +5027,12 @@
       </c>
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>PostpaidAddonsPanel</t>
+          <t>PostpaidDiscountsPanel</t>
         </is>
       </c>
       <c r="C84" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidAddonsPanel.tsx</t>
+          <t>components/patterns/PostpaidDiscountsPanel.tsx</t>
         </is>
       </c>
       <c r="D84" s="20" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="B85" s="17" t="inlineStr">
         <is>
-          <t>PostpaidDiscountsPanel</t>
+          <t>PostpaidMonthlySummary</t>
         </is>
       </c>
       <c r="C85" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidDiscountsPanel.tsx</t>
+          <t>components/patterns/PostpaidMonthlySummary.tsx</t>
         </is>
       </c>
       <c r="D85" s="20" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="H85" s="17" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5107,12 +5107,12 @@
       </c>
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>PostpaidMonthlySummary</t>
+          <t>PostpaidPlanAddonsStep</t>
         </is>
       </c>
       <c r="C86" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidMonthlySummary.tsx</t>
+          <t>components/patterns/PostpaidPlanAddonsStep.tsx</t>
         </is>
       </c>
       <c r="D86" s="20" t="inlineStr">
@@ -5128,14 +5128,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G86" s="17" t="inlineStr">
-        <is>
-          <t>PostpaidPlanAddonsStep</t>
-        </is>
-      </c>
+      <c r="G86" s="17" t="inlineStr"/>
       <c r="H86" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -5147,12 +5143,12 @@
       </c>
       <c r="B87" s="17" t="inlineStr">
         <is>
-          <t>PostpaidPlanAddonsStep</t>
+          <t>PostpaidPlanCard</t>
         </is>
       </c>
       <c r="C87" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidPlanAddonsStep.tsx</t>
+          <t>components/patterns/PostpaidPlanCard.tsx</t>
         </is>
       </c>
       <c r="D87" s="20" t="inlineStr">
@@ -5168,10 +5164,14 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G87" s="17" t="inlineStr"/>
+      <c r="G87" s="17" t="inlineStr">
+        <is>
+          <t>PlanGroupPanel</t>
+        </is>
+      </c>
       <c r="H87" s="17" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="B88" s="17" t="inlineStr">
         <is>
-          <t>PostpaidPlanCard</t>
+          <t>PrepaidCartStep</t>
         </is>
       </c>
       <c r="C88" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PostpaidPlanCard.tsx</t>
+          <t>components/patterns/PrepaidCartStep.tsx</t>
         </is>
       </c>
       <c r="D88" s="20" t="inlineStr">
@@ -5204,14 +5204,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G88" s="17" t="inlineStr">
-        <is>
-          <t>PlanGroupPanel</t>
-        </is>
-      </c>
+      <c r="G88" s="17" t="inlineStr"/>
       <c r="H88" s="17" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5223,12 +5219,12 @@
       </c>
       <c r="B89" s="17" t="inlineStr">
         <is>
-          <t>PrepaidCartStep</t>
+          <t>PrepaidCheckoutStep</t>
         </is>
       </c>
       <c r="C89" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidCartStep.tsx</t>
+          <t>components/patterns/PrepaidCheckoutStep.tsx</t>
         </is>
       </c>
       <c r="D89" s="20" t="inlineStr">
@@ -5247,7 +5243,7 @@
       <c r="G89" s="17" t="inlineStr"/>
       <c r="H89" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -5259,12 +5255,12 @@
       </c>
       <c r="B90" s="17" t="inlineStr">
         <is>
-          <t>PrepaidCheckoutStep</t>
+          <t>PrepaidPackDetailsDrawer</t>
         </is>
       </c>
       <c r="C90" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidCheckoutStep.tsx</t>
+          <t>components/patterns/PrepaidPackDetailsDrawer.tsx</t>
         </is>
       </c>
       <c r="D90" s="20" t="inlineStr">
@@ -5280,7 +5276,11 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G90" s="17" t="inlineStr"/>
+      <c r="G90" s="17" t="inlineStr">
+        <is>
+          <t>PrepaidPlanStep</t>
+        </is>
+      </c>
       <c r="H90" s="17" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="B91" s="17" t="inlineStr">
         <is>
-          <t>PrepaidPackDetailsDrawer</t>
+          <t>PrepaidPlanCard</t>
         </is>
       </c>
       <c r="C91" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidPackDetailsDrawer.tsx</t>
+          <t>components/patterns/PrepaidPlanCard.tsx</t>
         </is>
       </c>
       <c r="D91" s="20" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="H91" s="17" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -5335,12 +5335,12 @@
       </c>
       <c r="B92" s="17" t="inlineStr">
         <is>
-          <t>PrepaidPlanCard</t>
+          <t>PrepaidPlanStep</t>
         </is>
       </c>
       <c r="C92" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidPlanCard.tsx</t>
+          <t>components/patterns/PrepaidPlanStep.tsx</t>
         </is>
       </c>
       <c r="D92" s="20" t="inlineStr">
@@ -5356,14 +5356,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G92" s="17" t="inlineStr">
-        <is>
-          <t>PrepaidPlanStep</t>
-        </is>
-      </c>
+      <c r="G92" s="17" t="inlineStr"/>
       <c r="H92" s="17" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -5375,12 +5371,12 @@
       </c>
       <c r="B93" s="17" t="inlineStr">
         <is>
-          <t>PrepaidPlanStep</t>
+          <t>SummaryTables</t>
         </is>
       </c>
       <c r="C93" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/PrepaidPlanStep.tsx</t>
+          <t>components/patterns/CheckoutSummaryTables.tsx</t>
         </is>
       </c>
       <c r="D93" s="20" t="inlineStr">
@@ -5396,10 +5392,14 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G93" s="17" t="inlineStr"/>
+      <c r="G93" s="17" t="inlineStr">
+        <is>
+          <t>CheckoutSummaryStep, checkoutDetailedTables</t>
+        </is>
+      </c>
       <c r="H93" s="17" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5411,12 +5411,12 @@
       </c>
       <c r="B94" s="17" t="inlineStr">
         <is>
-          <t>SummaryTables</t>
+          <t>WinCashPaymentStep</t>
         </is>
       </c>
       <c r="C94" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CheckoutSummaryTables.tsx</t>
+          <t>components/patterns/WinCashPaymentStep.tsx</t>
         </is>
       </c>
       <c r="D94" s="20" t="inlineStr">
@@ -5432,14 +5432,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G94" s="17" t="inlineStr">
-        <is>
-          <t>CheckoutSummaryStep, checkoutDetailedTables</t>
-        </is>
-      </c>
+      <c r="G94" s="17" t="inlineStr"/>
       <c r="H94" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -5451,12 +5447,12 @@
       </c>
       <c r="B95" s="17" t="inlineStr">
         <is>
-          <t>WinCashPaymentStep</t>
+          <t>BillingAccountStep</t>
         </is>
       </c>
       <c r="C95" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/WinCashPaymentStep.tsx</t>
+          <t>components/patterns/BillingAccountStep.tsx</t>
         </is>
       </c>
       <c r="D95" s="20" t="inlineStr">
@@ -5465,17 +5461,17 @@
         </is>
       </c>
       <c r="E95" s="17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F95" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, mobile-service-changes, new-connection, pre-to-post-migration, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G95" s="17" t="inlineStr"/>
       <c r="H95" s="17" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -5487,12 +5483,12 @@
       </c>
       <c r="B96" s="17" t="inlineStr">
         <is>
-          <t>BillingAccountStep</t>
+          <t>BillingProfileSetupDrawer</t>
         </is>
       </c>
       <c r="C96" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/BillingAccountStep.tsx</t>
+          <t>components/patterns/BillingProfileSetupDrawer.tsx</t>
         </is>
       </c>
       <c r="D96" s="20" t="inlineStr">
@@ -5508,10 +5504,14 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G96" s="17" t="inlineStr"/>
+      <c r="G96" s="17" t="inlineStr">
+        <is>
+          <t>BillingAccountStep</t>
+        </is>
+      </c>
       <c r="H96" s="17" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5523,12 +5523,12 @@
       </c>
       <c r="B97" s="17" t="inlineStr">
         <is>
-          <t>BillingProfileSetupDrawer</t>
+          <t>CreditLimitCard</t>
         </is>
       </c>
       <c r="C97" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/BillingProfileSetupDrawer.tsx</t>
+          <t>components/patterns/CreditLimitCard.tsx</t>
         </is>
       </c>
       <c r="D97" s="20" t="inlineStr">
@@ -5544,14 +5544,10 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G97" s="17" t="inlineStr">
-        <is>
-          <t>BillingAccountStep</t>
-        </is>
-      </c>
+      <c r="G97" s="17" t="inlineStr"/>
       <c r="H97" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5563,12 +5559,12 @@
       </c>
       <c r="B98" s="17" t="inlineStr">
         <is>
-          <t>CreditLimitCard</t>
+          <t>ZsbAddressStep</t>
         </is>
       </c>
       <c r="C98" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/CreditLimitCard.tsx</t>
+          <t>components/patterns/ZsbAddressStep.tsx</t>
         </is>
       </c>
       <c r="D98" s="20" t="inlineStr">
@@ -5584,7 +5580,11 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
         </is>
       </c>
-      <c r="G98" s="17" t="inlineStr"/>
+      <c r="G98" s="17" t="inlineStr">
+        <is>
+          <t>addressFromBilling</t>
+        </is>
+      </c>
       <c r="H98" s="17" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -5599,12 +5599,12 @@
       </c>
       <c r="B99" s="17" t="inlineStr">
         <is>
-          <t>ZsbAddressStep</t>
+          <t>AppointmentBookingStep</t>
         </is>
       </c>
       <c r="C99" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/ZsbAddressStep.tsx</t>
+          <t>components/patterns/AppointmentBookingStep.tsx</t>
         </is>
       </c>
       <c r="D99" s="20" t="inlineStr">
@@ -5613,21 +5613,17 @@
         </is>
       </c>
       <c r="E99" s="17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F99" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, pre-to-post-migration, administration</t>
-        </is>
-      </c>
-      <c r="G99" s="17" t="inlineStr">
-        <is>
-          <t>addressFromBilling</t>
-        </is>
-      </c>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, administration</t>
+        </is>
+      </c>
+      <c r="G99" s="17" t="inlineStr"/>
       <c r="H99" s="17" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5635,12 @@
       </c>
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>AppointmentBookingStep</t>
+          <t>DemoFaultPanel</t>
         </is>
       </c>
       <c r="C100" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/AppointmentBookingStep.tsx</t>
+          <t>components/patterns/DemoFaultPanel.tsx</t>
         </is>
       </c>
       <c r="D100" s="20" t="inlineStr">
@@ -5653,11 +5649,11 @@
         </is>
       </c>
       <c r="E100" s="17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F100" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection, administration</t>
+          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
         </is>
       </c>
       <c r="G100" s="17" t="inlineStr"/>
@@ -5675,12 +5671,12 @@
       </c>
       <c r="B101" s="17" t="inlineStr">
         <is>
-          <t>DemoFaultPanel</t>
+          <t>DonorAttachmentStep</t>
         </is>
       </c>
       <c r="C101" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DemoFaultPanel.tsx</t>
+          <t>components/patterns/DonorAttachmentStep.tsx</t>
         </is>
       </c>
       <c r="D101" s="20" t="inlineStr">
@@ -5711,12 +5707,12 @@
       </c>
       <c r="B102" s="17" t="inlineStr">
         <is>
-          <t>DonorAttachmentStep</t>
+          <t>DonorDetailsStep</t>
         </is>
       </c>
       <c r="C102" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DonorAttachmentStep.tsx</t>
+          <t>components/patterns/DonorDetailsStep.tsx</t>
         </is>
       </c>
       <c r="D102" s="20" t="inlineStr">
@@ -5732,7 +5728,11 @@
           <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
         </is>
       </c>
-      <c r="G102" s="17" t="inlineStr"/>
+      <c r="G102" s="17" t="inlineStr">
+        <is>
+          <t>DonorAttachmentStep</t>
+        </is>
+      </c>
       <c r="H102" s="17" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="B103" s="17" t="inlineStr">
         <is>
-          <t>DonorDetailsStep</t>
+          <t>EntityMissing</t>
         </is>
       </c>
       <c r="C103" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DonorDetailsStep.tsx</t>
+          <t>components/patterns/EntityMissing.tsx</t>
         </is>
       </c>
       <c r="D103" s="20" t="inlineStr">
@@ -5765,14 +5765,10 @@
       </c>
       <c r="F103" s="17" t="inlineStr">
         <is>
-          <t>fixed-line-fibre, fwa-5g-home, mnp-fnp-porting, mobile-postpaid, mobile-prepaid, new-connection</t>
-        </is>
-      </c>
-      <c r="G103" s="17" t="inlineStr">
-        <is>
-          <t>DonorAttachmentStep</t>
-        </is>
-      </c>
+          <t>lead-management, order-management, sim-number-management, trouble-ticketing-complaints, customer360, tasks</t>
+        </is>
+      </c>
+      <c r="G103" s="17" t="inlineStr"/>
       <c r="H103" s="17" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -5787,12 +5783,12 @@
       </c>
       <c r="B104" s="17" t="inlineStr">
         <is>
-          <t>EntityMissing</t>
+          <t>RestrictedRowsNotice</t>
         </is>
       </c>
       <c r="C104" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/EntityMissing.tsx</t>
+          <t>components/patterns/RestrictedRowsNotice.tsx</t>
         </is>
       </c>
       <c r="D104" s="20" t="inlineStr">
@@ -5805,13 +5801,13 @@
       </c>
       <c r="F104" s="17" t="inlineStr">
         <is>
-          <t>lead-management, order-management, sim-number-management, trouble-ticketing-complaints, customer360, tasks</t>
+          <t>order-management, trouble-ticketing-complaints, orders, support, tasks, tickets</t>
         </is>
       </c>
       <c r="G104" s="17" t="inlineStr"/>
       <c r="H104" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -5823,12 +5819,12 @@
       </c>
       <c r="B105" s="17" t="inlineStr">
         <is>
-          <t>RestrictedRowsNotice</t>
+          <t>ActivityCommentsStep</t>
         </is>
       </c>
       <c r="C105" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/RestrictedRowsNotice.tsx</t>
+          <t>components/patterns/ActivityCommentsStep.tsx</t>
         </is>
       </c>
       <c r="D105" s="20" t="inlineStr">
@@ -5837,17 +5833,17 @@
         </is>
       </c>
       <c r="E105" s="17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F105" s="17" t="inlineStr">
         <is>
-          <t>order-management, trouble-ticketing-complaints, orders, support, tasks, tickets</t>
+          <t>pre-to-post-migration, sim-number-management, administration</t>
         </is>
       </c>
       <c r="G105" s="17" t="inlineStr"/>
       <c r="H105" s="17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -5859,12 +5855,12 @@
       </c>
       <c r="B106" s="17" t="inlineStr">
         <is>
-          <t>ActivityCommentsStep</t>
+          <t>LineSelectionStep</t>
         </is>
       </c>
       <c r="C106" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/ActivityCommentsStep.tsx</t>
+          <t>components/patterns/LineSelectionStep.tsx</t>
         </is>
       </c>
       <c r="D106" s="20" t="inlineStr">
@@ -5877,13 +5873,13 @@
       </c>
       <c r="F106" s="17" t="inlineStr">
         <is>
-          <t>pre-to-post-migration, sim-number-management, administration</t>
+          <t>mobile-service-changes, pre-to-post-migration, administration</t>
         </is>
       </c>
       <c r="G106" s="17" t="inlineStr"/>
       <c r="H106" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -5895,12 +5891,12 @@
       </c>
       <c r="B107" s="17" t="inlineStr">
         <is>
-          <t>LineSelectionStep</t>
+          <t>TicketCreationModal</t>
         </is>
       </c>
       <c r="C107" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/LineSelectionStep.tsx</t>
+          <t>components/patterns/TicketCreationModal.tsx</t>
         </is>
       </c>
       <c r="D107" s="20" t="inlineStr">
@@ -5913,13 +5909,13 @@
       </c>
       <c r="F107" s="17" t="inlineStr">
         <is>
-          <t>mobile-service-changes, pre-to-post-migration, administration</t>
+          <t>trouble-ticketing-complaints, customer360, support</t>
         </is>
       </c>
       <c r="G107" s="17" t="inlineStr"/>
       <c r="H107" s="17" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5931,31 +5927,31 @@
       </c>
       <c r="B108" s="17" t="inlineStr">
         <is>
-          <t>TicketCreationModal</t>
+          <t>BulkOperationPortal</t>
         </is>
       </c>
       <c r="C108" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/TicketCreationModal.tsx</t>
-        </is>
-      </c>
-      <c r="D108" s="20" t="inlineStr">
-        <is>
-          <t>Shared (2+ areas)</t>
+          <t>components/patterns/BulkOperationPortal.tsx</t>
+        </is>
+      </c>
+      <c r="D108" s="21" t="inlineStr">
+        <is>
+          <t>Single area</t>
         </is>
       </c>
       <c r="E108" s="17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F108" s="17" t="inlineStr">
         <is>
-          <t>trouble-ticketing-complaints, customer360, support</t>
+          <t>enterprise-iot-b2b</t>
         </is>
       </c>
       <c r="G108" s="17" t="inlineStr"/>
       <c r="H108" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5967,12 +5963,12 @@
       </c>
       <c r="B109" s="17" t="inlineStr">
         <is>
-          <t>BulkOperationPortal</t>
+          <t>DualPlaySerialCheckStep</t>
         </is>
       </c>
       <c r="C109" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/BulkOperationPortal.tsx</t>
+          <t>components/patterns/DualPlaySerialCheckStep.tsx</t>
         </is>
       </c>
       <c r="D109" s="21" t="inlineStr">
@@ -5985,7 +5981,7 @@
       </c>
       <c r="F109" s="17" t="inlineStr">
         <is>
-          <t>enterprise-iot-b2b</t>
+          <t>fwa-5g-home</t>
         </is>
       </c>
       <c r="G109" s="17" t="inlineStr"/>
@@ -6003,12 +5999,12 @@
       </c>
       <c r="B110" s="17" t="inlineStr">
         <is>
-          <t>DualPlaySerialCheckStep</t>
+          <t>SimSwapFormStep</t>
         </is>
       </c>
       <c r="C110" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/DualPlaySerialCheckStep.tsx</t>
+          <t>components/patterns/SimSwapFormStep.tsx</t>
         </is>
       </c>
       <c r="D110" s="21" t="inlineStr">
@@ -6021,7 +6017,7 @@
       </c>
       <c r="F110" s="17" t="inlineStr">
         <is>
-          <t>fwa-5g-home</t>
+          <t>sim-number-management</t>
         </is>
       </c>
       <c r="G110" s="17" t="inlineStr"/>
@@ -6039,12 +6035,12 @@
       </c>
       <c r="B111" s="17" t="inlineStr">
         <is>
-          <t>SimSwapFormStep</t>
+          <t>VerificationGate</t>
         </is>
       </c>
       <c r="C111" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/SimSwapFormStep.tsx</t>
+          <t>components/patterns/VerificationGate.tsx</t>
         </is>
       </c>
       <c r="D111" s="21" t="inlineStr">
@@ -6057,13 +6053,13 @@
       </c>
       <c r="F111" s="17" t="inlineStr">
         <is>
-          <t>sim-number-management</t>
+          <t>customer360</t>
         </is>
       </c>
       <c r="G111" s="17" t="inlineStr"/>
       <c r="H111" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -6075,31 +6071,27 @@
       </c>
       <c r="B112" s="17" t="inlineStr">
         <is>
-          <t>VerificationGate</t>
+          <t>NewCustomerForm</t>
         </is>
       </c>
       <c r="C112" s="17" t="inlineStr">
         <is>
-          <t>components/patterns/VerificationGate.tsx</t>
-        </is>
-      </c>
-      <c r="D112" s="21" t="inlineStr">
-        <is>
-          <t>Single area</t>
+          <t>components/patterns/NewCustomerForm.tsx</t>
+        </is>
+      </c>
+      <c r="D112" s="22" t="inlineStr">
+        <is>
+          <t>No consumer</t>
         </is>
       </c>
       <c r="E112" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F112" s="17" t="inlineStr">
-        <is>
-          <t>customer360</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F112" s="17" t="inlineStr"/>
       <c r="G112" s="17" t="inlineStr"/>
       <c r="H112" s="17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6239,7 @@
       <c r="G116" s="17" t="inlineStr"/>
       <c r="H116" s="17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -6537,7 +6529,7 @@
       </c>
       <c r="G2" s="17" t="inlineStr">
         <is>
-          <t>CompanySearchInput, ContactPhoneInput, CpeSerialScanner, MsisdnPicker, SimSerialScanner, AppointmentBookingStep, BillingAccountAutoResolver, BillingAccountStep, CafSignatureCapture, CafTerms, FixedPlanStep, PrepaidCartStep, PrepaidCheckoutStep, PrepaidPlanStep, TicketCreationModal, ZsbAddressStep, lineSelectionModel, useCheckoutSummary, useIdLookup, usePostpaidPlanAddons, StepSummaryPanel, stepSummary, useJourneyStartResume, useWizardDraftActions, LocationInput, activityEngine, agentProfileEngine, businessAccountEngine, connectionEligibility, customer360Engine, customerChangeAudit, fibreServiceability, qnomyWalkIns, roleSwitchPurge, serviceLocationLookup, useAreaOptions, useRestrictedCustomers, configStore, entityStore</t>
+          <t>CompanySearchInput, ContactPhoneInput, CpeSerialScanner, MsisdnPicker, SimSerialScanner, SimTypeStep, AppointmentBookingStep, BillingAccountAutoResolver, BillingAccountStep, CafSignatureCapture, CafTerms, FixedPlanStep, PrepaidCartStep, PrepaidCheckoutStep, PrepaidPlanStep, TicketCreationModal, ZsbAddressStep, lineSelectionModel, useCheckoutSummary, useIdLookup, usePostpaidPlanAddons, StepSummaryPanel, stepSummary, useJourneyStartResume, useWizardDraftActions, LocationInput, activityEngine, agentProfileEngine, businessAccountEngine, connectionEligibility, customer360Engine, customerChangeAudit, fibreServiceability, qnomyWalkIns, roleSwitchPurge, serviceLocationLookup, useAreaOptions, useRestrictedCustomers, configStore, entityStore</t>
         </is>
       </c>
       <c r="H2" s="17" t="inlineStr">
@@ -6577,12 +6569,12 @@
       </c>
       <c r="G3" s="17" t="inlineStr">
         <is>
-          <t>agentPrivilegeEngine, agentProfileEngine, approvalAuthority, customer360VisibilityEngine, navigationEngine, personaEngine, qnomyQueueEngine, screenGrouping, configStore</t>
+          <t>GuidedContactStep, agentPrivilegeEngine, agentProfileEngine, approvalAuthority, customer360VisibilityEngine, journeyDocuments, navigationEngine, personaEngine, qnomyQueueEngine, screenGrouping, configStore</t>
         </is>
       </c>
       <c r="H3" s="17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7446,7 @@
       </c>
       <c r="H25" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -8182,7 +8174,7 @@
       </c>
       <c r="H45" s="17" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -8382,7 +8374,7 @@
       </c>
       <c r="H50" s="17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -9150,7 +9142,7 @@
       </c>
       <c r="H70" s="17" t="inlineStr">
         <is>
-          <t>uncommitted</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
